--- a/companydirectorypdf/companydir.xlsx
+++ b/companydirectorypdf/companydir.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\living\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\kwlrportal\companydirectorypdf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B7F046-6EA2-4521-B4C6-870AAD324F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3F3213-AC2A-4E59-85C5-3292C02687E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{AE6EE1E0-C559-4053-97E8-B14EEDB6E6F6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{AE6EE1E0-C559-4053-97E8-B14EEDB6E6F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Letter Size" sheetId="8" r:id="rId1"/>
@@ -2005,23 +2005,23 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L364"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.44140625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="23.109375" style="7" customWidth="1"/>
-    <col min="3" max="3" width="67.6640625" style="7" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" style="7" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="32.109375" style="7" customWidth="1"/>
-    <col min="7" max="7" width="0.88671875" style="7" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" style="7" customWidth="1"/>
-    <col min="9" max="9" width="5.33203125" style="7" customWidth="1"/>
-    <col min="10" max="51" width="15.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="10.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="53" max="16384" width="8.6640625" style="7"/>
+    <col min="1" max="1" width="4.42578125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="67.7109375" style="7" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="32.140625" style="7" customWidth="1"/>
+    <col min="7" max="7" width="0.85546875" style="7" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" style="7" customWidth="1"/>
+    <col min="9" max="9" width="5.28515625" style="7" customWidth="1"/>
+    <col min="10" max="51" width="15.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="10.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="53" max="16384" width="8.7109375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
@@ -2060,7 +2060,7 @@
       <c r="K2"/>
       <c r="L2"/>
     </row>
-    <row r="3" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="str">
         <f>IF(LEN(ContactData!H2)&lt;3,"",ContactData!H2)</f>
         <v/>
@@ -2098,7 +2098,7 @@
       <c r="K3"/>
       <c r="L3"/>
     </row>
-    <row r="4" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <f>IF(LEN(ContactData!H3)&lt;3,"",ContactData!H3)</f>
         <v>500</v>
@@ -2136,7 +2136,7 @@
       <c r="K4"/>
       <c r="L4"/>
     </row>
-    <row r="5" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>IF(LEN(ContactData!H4)&lt;3,"",ContactData!H4)</f>
         <v>511</v>
@@ -2174,7 +2174,7 @@
       <c r="K5"/>
       <c r="L5"/>
     </row>
-    <row r="6" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <f>IF(LEN(ContactData!H5)&lt;3,"",ContactData!H5)</f>
         <v>228</v>
@@ -2212,7 +2212,7 @@
       <c r="K6"/>
       <c r="L6"/>
     </row>
-    <row r="7" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <f>IF(LEN(ContactData!H6)&lt;3,"",ContactData!H6)</f>
         <v>521</v>
@@ -2250,7 +2250,7 @@
       <c r="K7"/>
       <c r="L7"/>
     </row>
-    <row r="8" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <f>IF(LEN(ContactData!H7)&lt;3,"",ContactData!H7)</f>
         <v>165</v>
@@ -2288,7 +2288,7 @@
       <c r="K8"/>
       <c r="L8"/>
     </row>
-    <row r="9" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <f>IF(LEN(ContactData!H8)&lt;3,"",ContactData!H8)</f>
         <v>502</v>
@@ -2320,7 +2320,7 @@
       <c r="K9"/>
       <c r="L9"/>
     </row>
-    <row r="10" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="str">
         <f>IF(LEN(ContactData!H9)&lt;3,"",ContactData!H9)</f>
         <v>---</v>
@@ -2352,7 +2352,7 @@
       <c r="K10"/>
       <c r="L10"/>
     </row>
-    <row r="11" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="str">
         <f>IF(LEN(ContactData!H10)&lt;3,"",ContactData!H10)</f>
         <v>---</v>
@@ -2384,7 +2384,7 @@
       <c r="K11"/>
       <c r="L11"/>
     </row>
-    <row r="12" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <f>IF(LEN(ContactData!H11)&lt;3,"",ContactData!H11)</f>
         <v>509</v>
@@ -2416,7 +2416,7 @@
       <c r="K12"/>
       <c r="L12"/>
     </row>
-    <row r="13" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <f>IF(LEN(ContactData!H12)&lt;3,"",ContactData!H12)</f>
         <v>504</v>
@@ -2448,7 +2448,7 @@
       <c r="K13"/>
       <c r="L13"/>
     </row>
-    <row r="14" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <f>IF(LEN(ContactData!H13)&lt;3,"",ContactData!H13)</f>
         <v>514</v>
@@ -2480,7 +2480,7 @@
       <c r="K14"/>
       <c r="L14"/>
     </row>
-    <row r="15" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <f>IF(LEN(ContactData!H14)&lt;3,"",ContactData!H14)</f>
         <v>224</v>
@@ -2512,7 +2512,7 @@
       <c r="K15"/>
       <c r="L15"/>
     </row>
-    <row r="16" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <f>IF(LEN(ContactData!H15)&lt;3,"",ContactData!H15)</f>
         <v>123</v>
@@ -2544,7 +2544,7 @@
       <c r="K16"/>
       <c r="L16"/>
     </row>
-    <row r="17" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <f>IF(LEN(ContactData!H16)&lt;3,"",ContactData!H16)</f>
         <v>206</v>
@@ -2576,7 +2576,7 @@
       <c r="K17"/>
       <c r="L17"/>
     </row>
-    <row r="18" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <f>IF(LEN(ContactData!H17)&lt;3,"",ContactData!H17)</f>
         <v>507</v>
@@ -2608,7 +2608,7 @@
       <c r="K18"/>
       <c r="L18"/>
     </row>
-    <row r="19" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <f>IF(LEN(ContactData!H18)&lt;3,"",ContactData!H18)</f>
         <v>508</v>
@@ -2640,7 +2640,7 @@
       <c r="K19"/>
       <c r="L19"/>
     </row>
-    <row r="20" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <f>IF(LEN(ContactData!H19)&lt;3,"",ContactData!H19)</f>
         <v>255</v>
@@ -2672,7 +2672,7 @@
       <c r="K20"/>
       <c r="L20"/>
     </row>
-    <row r="21" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <f>IF(LEN(ContactData!H20)&lt;3,"",ContactData!H20)</f>
         <v>506</v>
@@ -2704,7 +2704,7 @@
       <c r="K21"/>
       <c r="L21"/>
     </row>
-    <row r="22" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <f>IF(LEN(ContactData!H21)&lt;3,"",ContactData!H21)</f>
         <v>519</v>
@@ -2736,7 +2736,7 @@
       <c r="K22"/>
       <c r="L22"/>
     </row>
-    <row r="23" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="str">
         <f>IF(LEN(ContactData!H22)&lt;3,"",ContactData!H22)</f>
         <v>---</v>
@@ -2768,7 +2768,7 @@
       <c r="K23"/>
       <c r="L23"/>
     </row>
-    <row r="24" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <f>IF(LEN(ContactData!H23)&lt;3,"",ContactData!H23)</f>
         <v>121</v>
@@ -2800,7 +2800,7 @@
       <c r="K24"/>
       <c r="L24"/>
     </row>
-    <row r="25" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <f>IF(LEN(ContactData!H24)&lt;3,"",ContactData!H24)</f>
         <v>522</v>
@@ -2832,7 +2832,7 @@
       <c r="K25"/>
       <c r="L25"/>
     </row>
-    <row r="26" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <f>IF(LEN(ContactData!H25)&lt;3,"",ContactData!H25)</f>
         <v>522</v>
@@ -2864,7 +2864,7 @@
       <c r="K26"/>
       <c r="L26"/>
     </row>
-    <row r="27" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="str">
         <f>IF(LEN(ContactData!H26)&lt;3,"",ContactData!H26)</f>
         <v/>
@@ -2896,7 +2896,7 @@
       <c r="K27"/>
       <c r="L27"/>
     </row>
-    <row r="28" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="str">
         <f>IF(LEN(ContactData!H27)&lt;3,"",ContactData!H27)</f>
         <v>---</v>
@@ -2928,7 +2928,7 @@
       <c r="K28"/>
       <c r="L28"/>
     </row>
-    <row r="29" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="str">
         <f>IF(LEN(ContactData!H28)&lt;3,"",ContactData!H28)</f>
         <v>---</v>
@@ -2960,7 +2960,7 @@
       <c r="K29"/>
       <c r="L29"/>
     </row>
-    <row r="30" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="str">
         <f>IF(LEN(ContactData!H29)&lt;3,"",ContactData!H29)</f>
         <v>---</v>
@@ -2992,7 +2992,7 @@
       <c r="K30"/>
       <c r="L30"/>
     </row>
-    <row r="31" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="str">
         <f>IF(LEN(ContactData!H30)&lt;3,"",ContactData!H30)</f>
         <v/>
@@ -3024,7 +3024,7 @@
       <c r="K31"/>
       <c r="L31"/>
     </row>
-    <row r="32" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="str">
         <f>IF(LEN(ContactData!H31)&lt;3,"",ContactData!H31)</f>
         <v>---</v>
@@ -3056,7 +3056,7 @@
       <c r="K32"/>
       <c r="L32"/>
     </row>
-    <row r="33" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="str">
         <f>IF(LEN(ContactData!H32)&lt;3,"",ContactData!H32)</f>
         <v>---</v>
@@ -3088,7 +3088,7 @@
       <c r="K33"/>
       <c r="L33"/>
     </row>
-    <row r="34" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="str">
         <f>IF(LEN(ContactData!H33)&lt;3,"",ContactData!H33)</f>
         <v>---</v>
@@ -3120,7 +3120,7 @@
       <c r="K34"/>
       <c r="L34"/>
     </row>
-    <row r="35" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="str">
         <f>IF(LEN(ContactData!H34)&lt;3,"",ContactData!H34)</f>
         <v/>
@@ -3152,7 +3152,7 @@
       <c r="K35"/>
       <c r="L35"/>
     </row>
-    <row r="36" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
         <f>IF(LEN(ContactData!H35)&lt;3,"",ContactData!H35)</f>
         <v>176</v>
@@ -3184,7 +3184,7 @@
       <c r="K36"/>
       <c r="L36"/>
     </row>
-    <row r="37" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <f>IF(LEN(ContactData!H36)&lt;3,"",ContactData!H36)</f>
         <v>104</v>
@@ -3216,7 +3216,7 @@
       <c r="K37"/>
       <c r="L37"/>
     </row>
-    <row r="38" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
         <f>IF(LEN(ContactData!H37)&lt;3,"",ContactData!H37)</f>
         <v>100</v>
@@ -3248,7 +3248,7 @@
       <c r="K38"/>
       <c r="L38"/>
     </row>
-    <row r="39" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="str">
         <f>IF(LEN(ContactData!H38)&lt;3,"",ContactData!H38)</f>
         <v/>
@@ -3280,7 +3280,7 @@
       <c r="K39"/>
       <c r="L39"/>
     </row>
-    <row r="40" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="str">
         <f>IF(LEN(ContactData!H39)&lt;3,"",ContactData!H39)</f>
         <v>---</v>
@@ -3312,7 +3312,7 @@
       <c r="K40"/>
       <c r="L40"/>
     </row>
-    <row r="41" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="str">
         <f>IF(LEN(ContactData!H40)&lt;3,"",ContactData!H40)</f>
         <v>---</v>
@@ -3344,7 +3344,7 @@
       <c r="K41"/>
       <c r="L41"/>
     </row>
-    <row r="42" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="str">
         <f>IF(LEN(ContactData!H41)&lt;3,"",ContactData!H41)</f>
         <v/>
@@ -3376,7 +3376,7 @@
       <c r="K42"/>
       <c r="L42"/>
     </row>
-    <row r="43" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A43" s="9">
         <f>IF(LEN(ContactData!H42)&lt;3,"",ContactData!H42)</f>
         <v>228</v>
@@ -3408,7 +3408,7 @@
       <c r="K43"/>
       <c r="L43"/>
     </row>
-    <row r="44" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="str">
         <f>IF(LEN(ContactData!H43)&lt;3,"",ContactData!H43)</f>
         <v/>
@@ -3440,7 +3440,7 @@
       <c r="K44"/>
       <c r="L44"/>
     </row>
-    <row r="45" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A45" s="9">
         <f>IF(LEN(ContactData!H44)&lt;3,"",ContactData!H44)</f>
         <v>521</v>
@@ -3472,7 +3472,7 @@
       <c r="K45"/>
       <c r="L45"/>
     </row>
-    <row r="46" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A46" s="9">
         <f>IF(LEN(ContactData!H45)&lt;3,"",ContactData!H45)</f>
         <v>514</v>
@@ -3504,7 +3504,7 @@
       <c r="K46"/>
       <c r="L46"/>
     </row>
-    <row r="47" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
         <f>IF(LEN(ContactData!H46)&lt;3,"",ContactData!H46)</f>
         <v>286</v>
@@ -3536,7 +3536,7 @@
       <c r="K47"/>
       <c r="L47"/>
     </row>
-    <row r="48" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A48" s="9">
         <f>IF(LEN(ContactData!H47)&lt;3,"",ContactData!H47)</f>
         <v>516</v>
@@ -3568,7 +3568,7 @@
       <c r="K48"/>
       <c r="L48"/>
     </row>
-    <row r="49" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
         <f>IF(LEN(ContactData!H48)&lt;3,"",ContactData!H48)</f>
         <v>512</v>
@@ -3600,7 +3600,7 @@
       <c r="K49"/>
       <c r="L49"/>
     </row>
-    <row r="50" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A50" s="9">
         <f>IF(LEN(ContactData!H49)&lt;3,"",ContactData!H49)</f>
         <v>284</v>
@@ -3632,10 +3632,10 @@
       <c r="K50"/>
       <c r="L50"/>
     </row>
-    <row r="51" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
         <f>IF(LEN(ContactData!H50)&lt;3,"",ContactData!H50)</f>
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="B51" s="3" t="str">
         <f>ContactData!E50</f>
@@ -3664,7 +3664,7 @@
       <c r="K51"/>
       <c r="L51"/>
     </row>
-    <row r="52" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
         <f>IF(LEN(ContactData!H51)&lt;3,"",ContactData!H51)</f>
         <v>520</v>
@@ -3696,7 +3696,7 @@
       <c r="K52"/>
       <c r="L52"/>
     </row>
-    <row r="53" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
         <f>IF(LEN(ContactData!H52)&lt;3,"",ContactData!H52)</f>
         <v>168</v>
@@ -3728,7 +3728,7 @@
       <c r="K53"/>
       <c r="L53"/>
     </row>
-    <row r="54" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
         <f>IF(LEN(ContactData!H53)&lt;3,"",ContactData!H53)</f>
         <v>210</v>
@@ -3760,7 +3760,7 @@
       <c r="K54"/>
       <c r="L54"/>
     </row>
-    <row r="55" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <f>IF(LEN(ContactData!H54)&lt;3,"",ContactData!H54)</f>
         <v>518</v>
@@ -3792,7 +3792,7 @@
       <c r="K55"/>
       <c r="L55"/>
     </row>
-    <row r="56" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
         <f>IF(LEN(ContactData!H55)&lt;3,"",ContactData!H55)</f>
         <v>281</v>
@@ -3824,7 +3824,7 @@
       <c r="K56"/>
       <c r="L56"/>
     </row>
-    <row r="57" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
         <f>IF(LEN(ContactData!H56)&lt;3,"",ContactData!H56)</f>
         <v>523</v>
@@ -3856,7 +3856,7 @@
       <c r="K57"/>
       <c r="L57"/>
     </row>
-    <row r="58" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
         <f>IF(LEN(ContactData!H57)&lt;3,"",ContactData!H57)</f>
         <v>223</v>
@@ -3888,7 +3888,7 @@
       <c r="K58"/>
       <c r="L58"/>
     </row>
-    <row r="59" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <f>IF(LEN(ContactData!H58)&lt;3,"",ContactData!H58)</f>
         <v>172</v>
@@ -3920,7 +3920,7 @@
       <c r="K59"/>
       <c r="L59"/>
     </row>
-    <row r="60" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
         <f>IF(LEN(ContactData!H59)&lt;3,"",ContactData!H59)</f>
         <v>182</v>
@@ -3952,7 +3952,7 @@
       <c r="K60"/>
       <c r="L60"/>
     </row>
-    <row r="61" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="str">
         <f>IF(LEN(ContactData!H60)&lt;3,"",ContactData!H60)</f>
         <v>---</v>
@@ -3984,7 +3984,7 @@
       <c r="K61"/>
       <c r="L61"/>
     </row>
-    <row r="62" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
         <f>IF(LEN(ContactData!H61)&lt;3,"",ContactData!H61)</f>
         <v>229</v>
@@ -4016,7 +4016,7 @@
       <c r="K62"/>
       <c r="L62"/>
     </row>
-    <row r="63" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A63" s="9" t="str">
         <f>IF(LEN(ContactData!H62)&lt;3,"",ContactData!H62)</f>
         <v/>
@@ -4048,7 +4048,7 @@
       <c r="K63"/>
       <c r="L63"/>
     </row>
-    <row r="64" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="str">
         <f>IF(LEN(ContactData!H63)&lt;3,"",ContactData!H63)</f>
         <v>---</v>
@@ -4080,7 +4080,7 @@
       <c r="K64"/>
       <c r="L64"/>
     </row>
-    <row r="65" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A65" s="9" t="str">
         <f>IF(LEN(ContactData!H64)&lt;3,"",ContactData!H64)</f>
         <v>---</v>
@@ -4112,7 +4112,7 @@
       <c r="K65"/>
       <c r="L65"/>
     </row>
-    <row r="66" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="str">
         <f>IF(LEN(ContactData!H65)&lt;3,"",ContactData!H65)</f>
         <v>---</v>
@@ -4144,7 +4144,7 @@
       <c r="K66"/>
       <c r="L66"/>
     </row>
-    <row r="67" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A67" s="9" t="str">
         <f>IF(LEN(ContactData!H66)&lt;3,"",ContactData!H66)</f>
         <v/>
@@ -4176,7 +4176,7 @@
       <c r="K67"/>
       <c r="L67"/>
     </row>
-    <row r="68" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="str">
         <f>IF(LEN(ContactData!H67)&lt;3,"",ContactData!H67)</f>
         <v>---</v>
@@ -4208,7 +4208,7 @@
       <c r="K68"/>
       <c r="L68"/>
     </row>
-    <row r="69" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A69" s="9" t="str">
         <f>IF(LEN(ContactData!H68)&lt;3,"",ContactData!H68)</f>
         <v>---</v>
@@ -4240,7 +4240,7 @@
       <c r="K69"/>
       <c r="L69"/>
     </row>
-    <row r="70" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="str">
         <f>IF(LEN(ContactData!H69)&lt;3,"",ContactData!H69)</f>
         <v/>
@@ -4272,7 +4272,7 @@
       <c r="K70"/>
       <c r="L70"/>
     </row>
-    <row r="71" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="str">
         <f>IF(LEN(ContactData!H70)&lt;3,"",ContactData!H70)</f>
         <v>---</v>
@@ -4304,7 +4304,7 @@
       <c r="K71"/>
       <c r="L71"/>
     </row>
-    <row r="72" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A72" s="9" t="str">
         <f>IF(LEN(ContactData!H71)&lt;3,"",ContactData!H71)</f>
         <v>---</v>
@@ -4336,7 +4336,7 @@
       <c r="K72"/>
       <c r="L72"/>
     </row>
-    <row r="73" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A73" s="9" t="str">
         <f>IF(LEN(ContactData!H72)&lt;3,"",ContactData!H72)</f>
         <v/>
@@ -4368,7 +4368,7 @@
       <c r="K73"/>
       <c r="L73"/>
     </row>
-    <row r="74" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A74" s="9" t="str">
         <f>IF(LEN(ContactData!H73)&lt;3,"",ContactData!H73)</f>
         <v>---</v>
@@ -4400,7 +4400,7 @@
       <c r="K74"/>
       <c r="L74"/>
     </row>
-    <row r="75" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A75" s="9" t="str">
         <f>IF(LEN(ContactData!H74)&lt;3,"",ContactData!H74)</f>
         <v>---</v>
@@ -4432,7 +4432,7 @@
       <c r="K75"/>
       <c r="L75"/>
     </row>
-    <row r="76" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A76" s="9" t="str">
         <f>IF(LEN(ContactData!H75)&lt;3,"",ContactData!H75)</f>
         <v>---</v>
@@ -4464,7 +4464,7 @@
       <c r="K76"/>
       <c r="L76"/>
     </row>
-    <row r="77" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A77" s="9" t="str">
         <f>IF(LEN(ContactData!H76)&lt;3,"",ContactData!H76)</f>
         <v/>
@@ -4496,7 +4496,7 @@
       <c r="K77"/>
       <c r="L77"/>
     </row>
-    <row r="78" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A78" s="9" t="str">
         <f>IF(LEN(ContactData!H77)&lt;3,"",ContactData!H77)</f>
         <v/>
@@ -4528,7 +4528,7 @@
       <c r="K78"/>
       <c r="L78"/>
     </row>
-    <row r="79" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
         <f>IF(LEN(ContactData!H78)&lt;3,"",ContactData!H78)</f>
         <v>120</v>
@@ -4560,7 +4560,7 @@
       <c r="K79"/>
       <c r="L79"/>
     </row>
-    <row r="80" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
         <f>IF(LEN(ContactData!H79)&lt;3,"",ContactData!H79)</f>
         <v>187</v>
@@ -4592,7 +4592,7 @@
       <c r="K80"/>
       <c r="L80"/>
     </row>
-    <row r="81" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81"/>
       <c r="C81"/>
@@ -4606,7 +4606,7 @@
       <c r="K81"/>
       <c r="L81"/>
     </row>
-    <row r="82" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82"/>
       <c r="C82"/>
@@ -4620,7 +4620,7 @@
       <c r="K82"/>
       <c r="L82"/>
     </row>
-    <row r="83" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83"/>
       <c r="C83"/>
@@ -4634,7 +4634,7 @@
       <c r="K83"/>
       <c r="L83"/>
     </row>
-    <row r="84" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84"/>
       <c r="C84"/>
@@ -4648,7 +4648,7 @@
       <c r="K84"/>
       <c r="L84"/>
     </row>
-    <row r="85" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85"/>
       <c r="C85"/>
@@ -4662,7 +4662,7 @@
       <c r="K85"/>
       <c r="L85"/>
     </row>
-    <row r="86" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86"/>
       <c r="C86"/>
@@ -4676,7 +4676,7 @@
       <c r="K86"/>
       <c r="L86"/>
     </row>
-    <row r="87" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87"/>
       <c r="C87"/>
@@ -4690,7 +4690,7 @@
       <c r="K87"/>
       <c r="L87"/>
     </row>
-    <row r="88" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88"/>
       <c r="C88"/>
@@ -4704,7 +4704,7 @@
       <c r="K88"/>
       <c r="L88"/>
     </row>
-    <row r="89" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89"/>
       <c r="C89"/>
@@ -4718,7 +4718,7 @@
       <c r="K89"/>
       <c r="L89"/>
     </row>
-    <row r="90" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90"/>
       <c r="C90"/>
@@ -4732,7 +4732,7 @@
       <c r="K90"/>
       <c r="L90"/>
     </row>
-    <row r="91" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91"/>
       <c r="C91"/>
@@ -4746,7 +4746,7 @@
       <c r="K91"/>
       <c r="L91"/>
     </row>
-    <row r="92" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92"/>
       <c r="C92"/>
@@ -4760,7 +4760,7 @@
       <c r="K92"/>
       <c r="L92"/>
     </row>
-    <row r="93" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93"/>
       <c r="C93"/>
@@ -4774,7 +4774,7 @@
       <c r="K93"/>
       <c r="L93"/>
     </row>
-    <row r="94" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94"/>
       <c r="C94"/>
@@ -4788,7 +4788,7 @@
       <c r="K94"/>
       <c r="L94"/>
     </row>
-    <row r="95" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95"/>
       <c r="C95"/>
@@ -4802,7 +4802,7 @@
       <c r="K95"/>
       <c r="L95"/>
     </row>
-    <row r="96" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96"/>
       <c r="C96"/>
@@ -4816,7 +4816,7 @@
       <c r="K96"/>
       <c r="L96"/>
     </row>
-    <row r="97" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97"/>
       <c r="C97"/>
@@ -4830,7 +4830,7 @@
       <c r="K97"/>
       <c r="L97"/>
     </row>
-    <row r="98" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98"/>
       <c r="C98"/>
@@ -4844,7 +4844,7 @@
       <c r="K98"/>
       <c r="L98"/>
     </row>
-    <row r="99" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99"/>
       <c r="C99"/>
@@ -4858,7 +4858,7 @@
       <c r="K99"/>
       <c r="L99"/>
     </row>
-    <row r="100" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100"/>
       <c r="C100"/>
@@ -4872,7 +4872,7 @@
       <c r="K100"/>
       <c r="L100"/>
     </row>
-    <row r="101" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101"/>
       <c r="C101"/>
@@ -4886,7 +4886,7 @@
       <c r="K101"/>
       <c r="L101"/>
     </row>
-    <row r="102" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102"/>
       <c r="C102"/>
@@ -4900,7 +4900,7 @@
       <c r="K102"/>
       <c r="L102"/>
     </row>
-    <row r="103" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103"/>
       <c r="C103"/>
@@ -4914,7 +4914,7 @@
       <c r="K103"/>
       <c r="L103"/>
     </row>
-    <row r="104" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104"/>
       <c r="C104"/>
@@ -4928,7 +4928,7 @@
       <c r="K104"/>
       <c r="L104"/>
     </row>
-    <row r="105" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105"/>
       <c r="C105"/>
@@ -4942,7 +4942,7 @@
       <c r="K105"/>
       <c r="L105"/>
     </row>
-    <row r="106" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106"/>
       <c r="C106"/>
@@ -4956,7 +4956,7 @@
       <c r="K106"/>
       <c r="L106"/>
     </row>
-    <row r="107" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107"/>
       <c r="C107"/>
@@ -4970,7 +4970,7 @@
       <c r="K107"/>
       <c r="L107"/>
     </row>
-    <row r="108" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108"/>
       <c r="C108"/>
@@ -4984,7 +4984,7 @@
       <c r="K108"/>
       <c r="L108"/>
     </row>
-    <row r="109" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109"/>
       <c r="C109"/>
@@ -4998,7 +4998,7 @@
       <c r="K109"/>
       <c r="L109"/>
     </row>
-    <row r="110" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110"/>
       <c r="C110"/>
@@ -5012,7 +5012,7 @@
       <c r="K110"/>
       <c r="L110"/>
     </row>
-    <row r="111" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111"/>
       <c r="C111"/>
@@ -5026,7 +5026,7 @@
       <c r="K111"/>
       <c r="L111"/>
     </row>
-    <row r="112" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112"/>
       <c r="C112"/>
@@ -5040,7 +5040,7 @@
       <c r="K112"/>
       <c r="L112"/>
     </row>
-    <row r="113" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113"/>
       <c r="C113"/>
@@ -5054,7 +5054,7 @@
       <c r="K113"/>
       <c r="L113"/>
     </row>
-    <row r="114" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114"/>
       <c r="C114"/>
@@ -5068,7 +5068,7 @@
       <c r="K114"/>
       <c r="L114"/>
     </row>
-    <row r="115" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115"/>
       <c r="C115"/>
@@ -5082,7 +5082,7 @@
       <c r="K115"/>
       <c r="L115"/>
     </row>
-    <row r="116" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116"/>
       <c r="C116"/>
@@ -5096,7 +5096,7 @@
       <c r="K116"/>
       <c r="L116"/>
     </row>
-    <row r="117" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117"/>
       <c r="C117"/>
@@ -5110,7 +5110,7 @@
       <c r="K117"/>
       <c r="L117"/>
     </row>
-    <row r="118" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118"/>
       <c r="C118"/>
@@ -5124,7 +5124,7 @@
       <c r="K118"/>
       <c r="L118"/>
     </row>
-    <row r="119" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119"/>
       <c r="C119"/>
@@ -5138,7 +5138,7 @@
       <c r="K119"/>
       <c r="L119"/>
     </row>
-    <row r="120" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120"/>
       <c r="C120"/>
@@ -5152,7 +5152,7 @@
       <c r="K120"/>
       <c r="L120"/>
     </row>
-    <row r="121" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121"/>
       <c r="C121"/>
@@ -5166,7 +5166,7 @@
       <c r="K121"/>
       <c r="L121"/>
     </row>
-    <row r="122" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122"/>
       <c r="C122"/>
@@ -5180,7 +5180,7 @@
       <c r="K122"/>
       <c r="L122"/>
     </row>
-    <row r="123" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123"/>
       <c r="C123"/>
@@ -5194,7 +5194,7 @@
       <c r="K123"/>
       <c r="L123"/>
     </row>
-    <row r="124" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124"/>
       <c r="C124"/>
@@ -5208,7 +5208,7 @@
       <c r="K124"/>
       <c r="L124"/>
     </row>
-    <row r="125" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125"/>
       <c r="C125"/>
@@ -5222,7 +5222,7 @@
       <c r="K125"/>
       <c r="L125"/>
     </row>
-    <row r="126" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126"/>
       <c r="C126"/>
@@ -5236,7 +5236,7 @@
       <c r="K126"/>
       <c r="L126"/>
     </row>
-    <row r="127" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127"/>
       <c r="C127"/>
@@ -5250,7 +5250,7 @@
       <c r="K127"/>
       <c r="L127"/>
     </row>
-    <row r="128" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128"/>
       <c r="C128"/>
@@ -5264,7 +5264,7 @@
       <c r="K128"/>
       <c r="L128"/>
     </row>
-    <row r="129" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129"/>
       <c r="C129"/>
@@ -5278,7 +5278,7 @@
       <c r="K129"/>
       <c r="L129"/>
     </row>
-    <row r="130" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130"/>
       <c r="C130"/>
@@ -5292,7 +5292,7 @@
       <c r="K130"/>
       <c r="L130"/>
     </row>
-    <row r="131" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131"/>
       <c r="C131"/>
@@ -5306,7 +5306,7 @@
       <c r="K131"/>
       <c r="L131"/>
     </row>
-    <row r="132" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132"/>
       <c r="C132"/>
@@ -5320,7 +5320,7 @@
       <c r="K132"/>
       <c r="L132"/>
     </row>
-    <row r="133" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133"/>
       <c r="C133"/>
@@ -5334,7 +5334,7 @@
       <c r="K133"/>
       <c r="L133"/>
     </row>
-    <row r="134" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134"/>
       <c r="C134"/>
@@ -5348,7 +5348,7 @@
       <c r="K134"/>
       <c r="L134"/>
     </row>
-    <row r="135" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135"/>
       <c r="C135"/>
@@ -5362,7 +5362,7 @@
       <c r="K135"/>
       <c r="L135"/>
     </row>
-    <row r="136" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136"/>
       <c r="C136"/>
@@ -5376,7 +5376,7 @@
       <c r="K136"/>
       <c r="L136"/>
     </row>
-    <row r="137" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137"/>
       <c r="C137"/>
@@ -5390,7 +5390,7 @@
       <c r="K137"/>
       <c r="L137"/>
     </row>
-    <row r="138" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138"/>
       <c r="C138"/>
@@ -5404,7 +5404,7 @@
       <c r="K138"/>
       <c r="L138"/>
     </row>
-    <row r="139" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139"/>
       <c r="C139"/>
@@ -5418,7 +5418,7 @@
       <c r="K139"/>
       <c r="L139"/>
     </row>
-    <row r="140" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140"/>
       <c r="C140"/>
@@ -5432,7 +5432,7 @@
       <c r="K140"/>
       <c r="L140"/>
     </row>
-    <row r="141" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141"/>
       <c r="C141"/>
@@ -5446,7 +5446,7 @@
       <c r="K141"/>
       <c r="L141"/>
     </row>
-    <row r="142" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142"/>
       <c r="C142"/>
@@ -5460,7 +5460,7 @@
       <c r="K142"/>
       <c r="L142"/>
     </row>
-    <row r="143" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143"/>
       <c r="C143"/>
@@ -5474,7 +5474,7 @@
       <c r="K143"/>
       <c r="L143"/>
     </row>
-    <row r="144" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144"/>
       <c r="C144"/>
@@ -5488,7 +5488,7 @@
       <c r="K144"/>
       <c r="L144"/>
     </row>
-    <row r="145" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145"/>
       <c r="C145"/>
@@ -5502,7 +5502,7 @@
       <c r="K145"/>
       <c r="L145"/>
     </row>
-    <row r="146" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146"/>
       <c r="C146"/>
@@ -5516,7 +5516,7 @@
       <c r="K146"/>
       <c r="L146"/>
     </row>
-    <row r="147" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147"/>
       <c r="C147"/>
@@ -5530,7 +5530,7 @@
       <c r="K147"/>
       <c r="L147"/>
     </row>
-    <row r="148" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148"/>
       <c r="C148"/>
@@ -5544,7 +5544,7 @@
       <c r="K148"/>
       <c r="L148"/>
     </row>
-    <row r="149" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149"/>
       <c r="C149"/>
@@ -5558,7 +5558,7 @@
       <c r="K149"/>
       <c r="L149"/>
     </row>
-    <row r="150" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150"/>
       <c r="C150"/>
@@ -5572,7 +5572,7 @@
       <c r="K150"/>
       <c r="L150"/>
     </row>
-    <row r="151" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151"/>
       <c r="C151"/>
@@ -5586,7 +5586,7 @@
       <c r="K151"/>
       <c r="L151"/>
     </row>
-    <row r="152" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152"/>
       <c r="C152"/>
@@ -5600,7 +5600,7 @@
       <c r="K152"/>
       <c r="L152"/>
     </row>
-    <row r="153" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153"/>
       <c r="C153"/>
@@ -5614,7 +5614,7 @@
       <c r="K153"/>
       <c r="L153"/>
     </row>
-    <row r="154" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154"/>
       <c r="C154"/>
@@ -5628,7 +5628,7 @@
       <c r="K154"/>
       <c r="L154"/>
     </row>
-    <row r="155" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155"/>
       <c r="C155"/>
@@ -5642,7 +5642,7 @@
       <c r="K155"/>
       <c r="L155"/>
     </row>
-    <row r="156" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156"/>
       <c r="C156"/>
@@ -5656,7 +5656,7 @@
       <c r="K156"/>
       <c r="L156"/>
     </row>
-    <row r="157" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157"/>
       <c r="C157"/>
@@ -5670,7 +5670,7 @@
       <c r="K157"/>
       <c r="L157"/>
     </row>
-    <row r="158" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158"/>
       <c r="C158"/>
@@ -5684,7 +5684,7 @@
       <c r="K158"/>
       <c r="L158"/>
     </row>
-    <row r="159" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159"/>
       <c r="C159"/>
@@ -5698,7 +5698,7 @@
       <c r="K159"/>
       <c r="L159"/>
     </row>
-    <row r="160" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160"/>
       <c r="C160"/>
@@ -5712,7 +5712,7 @@
       <c r="K160"/>
       <c r="L160"/>
     </row>
-    <row r="161" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161"/>
       <c r="C161"/>
@@ -5726,7 +5726,7 @@
       <c r="K161"/>
       <c r="L161"/>
     </row>
-    <row r="162" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162"/>
       <c r="C162"/>
@@ -5740,7 +5740,7 @@
       <c r="K162"/>
       <c r="L162"/>
     </row>
-    <row r="163" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163"/>
       <c r="C163"/>
@@ -5754,7 +5754,7 @@
       <c r="K163"/>
       <c r="L163"/>
     </row>
-    <row r="164" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164"/>
       <c r="C164"/>
@@ -5768,7 +5768,7 @@
       <c r="K164"/>
       <c r="L164"/>
     </row>
-    <row r="165" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165"/>
       <c r="C165"/>
@@ -5782,7 +5782,7 @@
       <c r="K165"/>
       <c r="L165"/>
     </row>
-    <row r="166" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166"/>
       <c r="C166"/>
@@ -5796,7 +5796,7 @@
       <c r="K166"/>
       <c r="L166"/>
     </row>
-    <row r="167" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167"/>
       <c r="C167"/>
@@ -5810,7 +5810,7 @@
       <c r="K167"/>
       <c r="L167"/>
     </row>
-    <row r="168" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168"/>
       <c r="C168"/>
@@ -5824,7 +5824,7 @@
       <c r="K168"/>
       <c r="L168"/>
     </row>
-    <row r="169" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169"/>
       <c r="C169"/>
@@ -5838,7 +5838,7 @@
       <c r="K169"/>
       <c r="L169"/>
     </row>
-    <row r="170" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170"/>
       <c r="C170"/>
@@ -5852,7 +5852,7 @@
       <c r="K170"/>
       <c r="L170"/>
     </row>
-    <row r="171" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171"/>
       <c r="C171"/>
@@ -5866,7 +5866,7 @@
       <c r="K171"/>
       <c r="L171"/>
     </row>
-    <row r="172" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172"/>
       <c r="C172"/>
@@ -5880,7 +5880,7 @@
       <c r="K172"/>
       <c r="L172"/>
     </row>
-    <row r="173" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173"/>
       <c r="C173"/>
@@ -5894,7 +5894,7 @@
       <c r="K173"/>
       <c r="L173"/>
     </row>
-    <row r="174" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174"/>
       <c r="C174"/>
@@ -5908,7 +5908,7 @@
       <c r="K174"/>
       <c r="L174"/>
     </row>
-    <row r="175" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175"/>
       <c r="C175"/>
@@ -5922,7 +5922,7 @@
       <c r="K175"/>
       <c r="L175"/>
     </row>
-    <row r="176" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176"/>
       <c r="C176"/>
@@ -5936,7 +5936,7 @@
       <c r="K176"/>
       <c r="L176"/>
     </row>
-    <row r="177" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177"/>
       <c r="C177"/>
@@ -5950,7 +5950,7 @@
       <c r="K177"/>
       <c r="L177"/>
     </row>
-    <row r="178" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178"/>
       <c r="C178"/>
@@ -5964,7 +5964,7 @@
       <c r="K178"/>
       <c r="L178"/>
     </row>
-    <row r="179" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179"/>
       <c r="C179"/>
@@ -5978,7 +5978,7 @@
       <c r="K179"/>
       <c r="L179"/>
     </row>
-    <row r="180" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180"/>
       <c r="C180"/>
@@ -5992,7 +5992,7 @@
       <c r="K180"/>
       <c r="L180"/>
     </row>
-    <row r="181" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181"/>
       <c r="C181"/>
@@ -6006,7 +6006,7 @@
       <c r="K181"/>
       <c r="L181"/>
     </row>
-    <row r="182" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182"/>
       <c r="C182"/>
@@ -6020,7 +6020,7 @@
       <c r="K182"/>
       <c r="L182"/>
     </row>
-    <row r="183" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183"/>
       <c r="C183"/>
@@ -6034,7 +6034,7 @@
       <c r="K183"/>
       <c r="L183"/>
     </row>
-    <row r="184" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184"/>
       <c r="C184"/>
@@ -6048,7 +6048,7 @@
       <c r="K184"/>
       <c r="L184"/>
     </row>
-    <row r="185" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185"/>
       <c r="C185"/>
@@ -6062,7 +6062,7 @@
       <c r="K185"/>
       <c r="L185"/>
     </row>
-    <row r="186" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186"/>
       <c r="C186"/>
@@ -6076,7 +6076,7 @@
       <c r="K186"/>
       <c r="L186"/>
     </row>
-    <row r="187" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187"/>
       <c r="C187"/>
@@ -6090,7 +6090,7 @@
       <c r="K187"/>
       <c r="L187"/>
     </row>
-    <row r="188" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188"/>
       <c r="C188"/>
@@ -6104,7 +6104,7 @@
       <c r="K188"/>
       <c r="L188"/>
     </row>
-    <row r="189" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189"/>
       <c r="C189"/>
@@ -6118,7 +6118,7 @@
       <c r="K189"/>
       <c r="L189"/>
     </row>
-    <row r="190" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190"/>
       <c r="C190"/>
@@ -6132,7 +6132,7 @@
       <c r="K190"/>
       <c r="L190"/>
     </row>
-    <row r="191" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191"/>
       <c r="C191"/>
@@ -6146,7 +6146,7 @@
       <c r="K191"/>
       <c r="L191"/>
     </row>
-    <row r="192" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192"/>
       <c r="C192"/>
@@ -6160,7 +6160,7 @@
       <c r="K192"/>
       <c r="L192"/>
     </row>
-    <row r="193" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193"/>
       <c r="C193"/>
@@ -6174,7 +6174,7 @@
       <c r="K193"/>
       <c r="L193"/>
     </row>
-    <row r="194" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194"/>
       <c r="C194"/>
@@ -6188,7 +6188,7 @@
       <c r="K194"/>
       <c r="L194"/>
     </row>
-    <row r="195" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195"/>
       <c r="C195"/>
@@ -6202,7 +6202,7 @@
       <c r="K195"/>
       <c r="L195"/>
     </row>
-    <row r="196" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196"/>
       <c r="C196"/>
@@ -6216,7 +6216,7 @@
       <c r="K196"/>
       <c r="L196"/>
     </row>
-    <row r="197" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197"/>
       <c r="C197"/>
@@ -6230,7 +6230,7 @@
       <c r="K197"/>
       <c r="L197"/>
     </row>
-    <row r="198" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198"/>
       <c r="C198"/>
@@ -6244,7 +6244,7 @@
       <c r="K198"/>
       <c r="L198"/>
     </row>
-    <row r="199" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199"/>
       <c r="C199"/>
@@ -6258,7 +6258,7 @@
       <c r="K199"/>
       <c r="L199"/>
     </row>
-    <row r="200" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200"/>
       <c r="C200"/>
@@ -6272,7 +6272,7 @@
       <c r="K200"/>
       <c r="L200"/>
     </row>
-    <row r="201" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201"/>
       <c r="C201"/>
@@ -6286,7 +6286,7 @@
       <c r="K201"/>
       <c r="L201"/>
     </row>
-    <row r="202" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="B202"/>
       <c r="C202"/>
@@ -6300,7 +6300,7 @@
       <c r="K202"/>
       <c r="L202"/>
     </row>
-    <row r="203" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="B203"/>
       <c r="C203"/>
@@ -6314,7 +6314,7 @@
       <c r="K203"/>
       <c r="L203"/>
     </row>
-    <row r="204" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204"/>
       <c r="C204"/>
@@ -6328,7 +6328,7 @@
       <c r="K204"/>
       <c r="L204"/>
     </row>
-    <row r="205" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A205" s="1"/>
       <c r="B205"/>
       <c r="C205"/>
@@ -6342,7 +6342,7 @@
       <c r="K205"/>
       <c r="L205"/>
     </row>
-    <row r="206" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206"/>
       <c r="C206"/>
@@ -6356,7 +6356,7 @@
       <c r="K206"/>
       <c r="L206"/>
     </row>
-    <row r="207" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207"/>
       <c r="C207"/>
@@ -6370,7 +6370,7 @@
       <c r="K207"/>
       <c r="L207"/>
     </row>
-    <row r="208" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="B208"/>
       <c r="C208"/>
@@ -6384,7 +6384,7 @@
       <c r="K208"/>
       <c r="L208"/>
     </row>
-    <row r="209" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="B209"/>
       <c r="C209"/>
@@ -6398,7 +6398,7 @@
       <c r="K209"/>
       <c r="L209"/>
     </row>
-    <row r="210" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="B210"/>
       <c r="C210"/>
@@ -6412,7 +6412,7 @@
       <c r="K210"/>
       <c r="L210"/>
     </row>
-    <row r="211" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="B211"/>
       <c r="C211"/>
@@ -6426,7 +6426,7 @@
       <c r="K211"/>
       <c r="L211"/>
     </row>
-    <row r="212" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="B212"/>
       <c r="C212"/>
@@ -6440,7 +6440,7 @@
       <c r="K212"/>
       <c r="L212"/>
     </row>
-    <row r="213" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="B213"/>
       <c r="C213"/>
@@ -6454,7 +6454,7 @@
       <c r="K213"/>
       <c r="L213"/>
     </row>
-    <row r="214" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="B214"/>
       <c r="C214"/>
@@ -6468,7 +6468,7 @@
       <c r="K214"/>
       <c r="L214"/>
     </row>
-    <row r="215" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215"/>
       <c r="C215"/>
@@ -6482,7 +6482,7 @@
       <c r="K215"/>
       <c r="L215"/>
     </row>
-    <row r="216" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="B216"/>
       <c r="C216"/>
@@ -6496,7 +6496,7 @@
       <c r="K216"/>
       <c r="L216"/>
     </row>
-    <row r="217" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="B217"/>
       <c r="C217"/>
@@ -6510,7 +6510,7 @@
       <c r="K217"/>
       <c r="L217"/>
     </row>
-    <row r="218" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="B218"/>
       <c r="C218"/>
@@ -6524,7 +6524,7 @@
       <c r="K218"/>
       <c r="L218"/>
     </row>
-    <row r="219" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219"/>
       <c r="C219"/>
@@ -6538,7 +6538,7 @@
       <c r="K219"/>
       <c r="L219"/>
     </row>
-    <row r="220" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="B220"/>
       <c r="C220"/>
@@ -6552,7 +6552,7 @@
       <c r="K220"/>
       <c r="L220"/>
     </row>
-    <row r="221" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="B221"/>
       <c r="C221"/>
@@ -6566,7 +6566,7 @@
       <c r="K221"/>
       <c r="L221"/>
     </row>
-    <row r="222" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="B222"/>
       <c r="C222"/>
@@ -6580,7 +6580,7 @@
       <c r="K222"/>
       <c r="L222"/>
     </row>
-    <row r="223" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="B223"/>
       <c r="C223"/>
@@ -6594,7 +6594,7 @@
       <c r="K223"/>
       <c r="L223"/>
     </row>
-    <row r="224" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="B224"/>
       <c r="C224"/>
@@ -6608,7 +6608,7 @@
       <c r="K224"/>
       <c r="L224"/>
     </row>
-    <row r="225" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A225" s="1"/>
       <c r="B225"/>
       <c r="C225"/>
@@ -6622,7 +6622,7 @@
       <c r="K225"/>
       <c r="L225"/>
     </row>
-    <row r="226" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="B226"/>
       <c r="C226"/>
@@ -6636,7 +6636,7 @@
       <c r="K226"/>
       <c r="L226"/>
     </row>
-    <row r="227" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A227" s="1"/>
       <c r="B227"/>
       <c r="C227"/>
@@ -6650,7 +6650,7 @@
       <c r="K227"/>
       <c r="L227"/>
     </row>
-    <row r="228" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A228" s="1"/>
       <c r="B228"/>
       <c r="C228"/>
@@ -6664,7 +6664,7 @@
       <c r="K228"/>
       <c r="L228"/>
     </row>
-    <row r="229" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A229" s="1"/>
       <c r="B229"/>
       <c r="C229"/>
@@ -6678,7 +6678,7 @@
       <c r="K229"/>
       <c r="L229"/>
     </row>
-    <row r="230" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A230" s="1"/>
       <c r="B230"/>
       <c r="C230"/>
@@ -6692,7 +6692,7 @@
       <c r="K230"/>
       <c r="L230"/>
     </row>
-    <row r="231" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A231" s="1"/>
       <c r="B231"/>
       <c r="C231"/>
@@ -6706,7 +6706,7 @@
       <c r="K231"/>
       <c r="L231"/>
     </row>
-    <row r="232" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A232" s="1"/>
       <c r="B232"/>
       <c r="C232"/>
@@ -6720,7 +6720,7 @@
       <c r="K232"/>
       <c r="L232"/>
     </row>
-    <row r="233" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A233" s="1"/>
       <c r="B233"/>
       <c r="C233"/>
@@ -6734,7 +6734,7 @@
       <c r="K233"/>
       <c r="L233"/>
     </row>
-    <row r="234" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A234" s="1"/>
       <c r="B234"/>
       <c r="C234"/>
@@ -6748,7 +6748,7 @@
       <c r="K234"/>
       <c r="L234"/>
     </row>
-    <row r="235" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A235" s="1"/>
       <c r="B235"/>
       <c r="C235"/>
@@ -6762,7 +6762,7 @@
       <c r="K235"/>
       <c r="L235"/>
     </row>
-    <row r="236" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A236" s="1"/>
       <c r="B236"/>
       <c r="C236"/>
@@ -6776,7 +6776,7 @@
       <c r="K236"/>
       <c r="L236"/>
     </row>
-    <row r="237" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A237" s="1"/>
       <c r="B237"/>
       <c r="C237"/>
@@ -6790,7 +6790,7 @@
       <c r="K237"/>
       <c r="L237"/>
     </row>
-    <row r="238" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A238" s="1"/>
       <c r="B238"/>
       <c r="C238"/>
@@ -6804,7 +6804,7 @@
       <c r="K238"/>
       <c r="L238"/>
     </row>
-    <row r="239" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A239" s="1"/>
       <c r="B239"/>
       <c r="C239"/>
@@ -6818,7 +6818,7 @@
       <c r="K239"/>
       <c r="L239"/>
     </row>
-    <row r="240" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A240" s="1"/>
       <c r="B240"/>
       <c r="C240"/>
@@ -6832,7 +6832,7 @@
       <c r="K240"/>
       <c r="L240"/>
     </row>
-    <row r="241" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A241" s="1"/>
       <c r="B241"/>
       <c r="C241"/>
@@ -6846,7 +6846,7 @@
       <c r="K241"/>
       <c r="L241"/>
     </row>
-    <row r="242" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A242" s="1"/>
       <c r="B242"/>
       <c r="C242"/>
@@ -6860,7 +6860,7 @@
       <c r="K242"/>
       <c r="L242"/>
     </row>
-    <row r="243" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A243" s="1"/>
       <c r="B243"/>
       <c r="C243"/>
@@ -6874,7 +6874,7 @@
       <c r="K243"/>
       <c r="L243"/>
     </row>
-    <row r="244" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A244" s="1"/>
       <c r="B244"/>
       <c r="C244"/>
@@ -6888,7 +6888,7 @@
       <c r="K244"/>
       <c r="L244"/>
     </row>
-    <row r="245" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A245" s="1"/>
       <c r="B245"/>
       <c r="C245"/>
@@ -6902,7 +6902,7 @@
       <c r="K245"/>
       <c r="L245"/>
     </row>
-    <row r="246" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A246" s="1"/>
       <c r="B246"/>
       <c r="C246"/>
@@ -6916,7 +6916,7 @@
       <c r="K246"/>
       <c r="L246"/>
     </row>
-    <row r="247" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A247" s="1"/>
       <c r="B247"/>
       <c r="C247"/>
@@ -6930,7 +6930,7 @@
       <c r="K247"/>
       <c r="L247"/>
     </row>
-    <row r="248" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A248" s="1"/>
       <c r="B248"/>
       <c r="C248"/>
@@ -6944,7 +6944,7 @@
       <c r="K248"/>
       <c r="L248"/>
     </row>
-    <row r="249" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A249" s="1"/>
       <c r="B249"/>
       <c r="C249"/>
@@ -6958,7 +6958,7 @@
       <c r="K249"/>
       <c r="L249"/>
     </row>
-    <row r="250" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A250" s="1"/>
       <c r="B250"/>
       <c r="C250"/>
@@ -6972,7 +6972,7 @@
       <c r="K250"/>
       <c r="L250"/>
     </row>
-    <row r="251" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A251" s="1"/>
       <c r="B251"/>
       <c r="C251"/>
@@ -6986,7 +6986,7 @@
       <c r="K251"/>
       <c r="L251"/>
     </row>
-    <row r="252" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A252" s="1"/>
       <c r="B252"/>
       <c r="C252"/>
@@ -7000,7 +7000,7 @@
       <c r="K252"/>
       <c r="L252"/>
     </row>
-    <row r="253" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A253" s="1"/>
       <c r="B253"/>
       <c r="C253"/>
@@ -7014,7 +7014,7 @@
       <c r="K253"/>
       <c r="L253"/>
     </row>
-    <row r="254" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A254" s="1"/>
       <c r="B254"/>
       <c r="C254"/>
@@ -7028,7 +7028,7 @@
       <c r="K254"/>
       <c r="L254"/>
     </row>
-    <row r="255" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A255" s="1"/>
       <c r="B255"/>
       <c r="C255"/>
@@ -7042,7 +7042,7 @@
       <c r="K255"/>
       <c r="L255"/>
     </row>
-    <row r="256" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A256" s="1"/>
       <c r="B256"/>
       <c r="C256"/>
@@ -7056,7 +7056,7 @@
       <c r="K256"/>
       <c r="L256"/>
     </row>
-    <row r="257" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A257" s="1"/>
       <c r="B257"/>
       <c r="C257"/>
@@ -7070,7 +7070,7 @@
       <c r="K257"/>
       <c r="L257"/>
     </row>
-    <row r="258" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A258" s="1"/>
       <c r="B258"/>
       <c r="C258"/>
@@ -7084,7 +7084,7 @@
       <c r="K258"/>
       <c r="L258"/>
     </row>
-    <row r="259" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A259" s="1"/>
       <c r="B259"/>
       <c r="C259"/>
@@ -7098,7 +7098,7 @@
       <c r="K259"/>
       <c r="L259"/>
     </row>
-    <row r="260" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A260" s="1"/>
       <c r="B260"/>
       <c r="C260"/>
@@ -7112,7 +7112,7 @@
       <c r="K260"/>
       <c r="L260"/>
     </row>
-    <row r="261" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A261" s="1"/>
       <c r="B261"/>
       <c r="C261"/>
@@ -7126,7 +7126,7 @@
       <c r="K261"/>
       <c r="L261"/>
     </row>
-    <row r="262" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A262" s="1"/>
       <c r="B262"/>
       <c r="C262"/>
@@ -7140,7 +7140,7 @@
       <c r="K262"/>
       <c r="L262"/>
     </row>
-    <row r="263" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A263" s="1"/>
       <c r="B263"/>
       <c r="C263"/>
@@ -7154,7 +7154,7 @@
       <c r="K263"/>
       <c r="L263"/>
     </row>
-    <row r="264" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A264" s="1"/>
       <c r="B264"/>
       <c r="C264"/>
@@ -7168,7 +7168,7 @@
       <c r="K264"/>
       <c r="L264"/>
     </row>
-    <row r="265" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A265" s="1"/>
       <c r="B265"/>
       <c r="C265"/>
@@ -7182,7 +7182,7 @@
       <c r="K265"/>
       <c r="L265"/>
     </row>
-    <row r="266" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A266" s="1"/>
       <c r="B266"/>
       <c r="C266"/>
@@ -7196,7 +7196,7 @@
       <c r="K266"/>
       <c r="L266"/>
     </row>
-    <row r="267" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A267" s="1"/>
       <c r="B267"/>
       <c r="C267"/>
@@ -7210,7 +7210,7 @@
       <c r="K267"/>
       <c r="L267"/>
     </row>
-    <row r="268" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A268" s="1"/>
       <c r="B268"/>
       <c r="C268"/>
@@ -7224,7 +7224,7 @@
       <c r="K268"/>
       <c r="L268"/>
     </row>
-    <row r="269" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A269" s="1"/>
       <c r="B269"/>
       <c r="C269"/>
@@ -7238,7 +7238,7 @@
       <c r="K269"/>
       <c r="L269"/>
     </row>
-    <row r="270" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A270" s="1"/>
       <c r="B270"/>
       <c r="C270"/>
@@ -7252,7 +7252,7 @@
       <c r="K270"/>
       <c r="L270"/>
     </row>
-    <row r="271" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A271" s="1"/>
       <c r="B271"/>
       <c r="C271"/>
@@ -7266,7 +7266,7 @@
       <c r="K271"/>
       <c r="L271"/>
     </row>
-    <row r="272" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A272" s="1"/>
       <c r="B272"/>
       <c r="C272"/>
@@ -7280,7 +7280,7 @@
       <c r="K272"/>
       <c r="L272"/>
     </row>
-    <row r="273" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A273" s="1"/>
       <c r="B273"/>
       <c r="C273"/>
@@ -7294,7 +7294,7 @@
       <c r="K273"/>
       <c r="L273"/>
     </row>
-    <row r="274" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A274" s="1"/>
       <c r="B274"/>
       <c r="C274"/>
@@ -7308,7 +7308,7 @@
       <c r="K274"/>
       <c r="L274"/>
     </row>
-    <row r="275" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A275" s="1"/>
       <c r="B275"/>
       <c r="C275"/>
@@ -7322,7 +7322,7 @@
       <c r="K275"/>
       <c r="L275"/>
     </row>
-    <row r="276" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A276" s="1"/>
       <c r="B276"/>
       <c r="C276"/>
@@ -7336,7 +7336,7 @@
       <c r="K276"/>
       <c r="L276"/>
     </row>
-    <row r="277" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A277" s="1"/>
       <c r="B277"/>
       <c r="C277"/>
@@ -7350,7 +7350,7 @@
       <c r="K277"/>
       <c r="L277"/>
     </row>
-    <row r="278" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A278" s="1"/>
       <c r="B278"/>
       <c r="C278"/>
@@ -7364,7 +7364,7 @@
       <c r="K278"/>
       <c r="L278"/>
     </row>
-    <row r="279" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A279" s="1"/>
       <c r="B279"/>
       <c r="C279"/>
@@ -7378,7 +7378,7 @@
       <c r="K279"/>
       <c r="L279"/>
     </row>
-    <row r="280" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A280" s="1"/>
       <c r="B280"/>
       <c r="C280"/>
@@ -7392,7 +7392,7 @@
       <c r="K280"/>
       <c r="L280"/>
     </row>
-    <row r="281" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A281" s="1"/>
       <c r="B281"/>
       <c r="C281"/>
@@ -7406,7 +7406,7 @@
       <c r="K281"/>
       <c r="L281"/>
     </row>
-    <row r="282" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A282" s="1"/>
       <c r="B282"/>
       <c r="C282"/>
@@ -7420,7 +7420,7 @@
       <c r="K282"/>
       <c r="L282"/>
     </row>
-    <row r="283" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A283" s="1"/>
       <c r="B283"/>
       <c r="C283"/>
@@ -7434,7 +7434,7 @@
       <c r="K283"/>
       <c r="L283"/>
     </row>
-    <row r="284" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A284" s="1"/>
       <c r="B284"/>
       <c r="C284"/>
@@ -7448,7 +7448,7 @@
       <c r="K284"/>
       <c r="L284"/>
     </row>
-    <row r="285" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A285" s="1"/>
       <c r="B285"/>
       <c r="C285"/>
@@ -7462,7 +7462,7 @@
       <c r="K285"/>
       <c r="L285"/>
     </row>
-    <row r="286" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A286" s="1"/>
       <c r="B286"/>
       <c r="C286"/>
@@ -7476,7 +7476,7 @@
       <c r="K286"/>
       <c r="L286"/>
     </row>
-    <row r="287" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A287" s="1"/>
       <c r="B287"/>
       <c r="C287"/>
@@ -7490,7 +7490,7 @@
       <c r="K287"/>
       <c r="L287"/>
     </row>
-    <row r="288" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A288" s="1"/>
       <c r="B288"/>
       <c r="C288"/>
@@ -7504,7 +7504,7 @@
       <c r="K288"/>
       <c r="L288"/>
     </row>
-    <row r="289" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A289" s="1"/>
       <c r="B289"/>
       <c r="C289"/>
@@ -7518,7 +7518,7 @@
       <c r="K289"/>
       <c r="L289"/>
     </row>
-    <row r="290" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A290" s="1"/>
       <c r="B290"/>
       <c r="C290"/>
@@ -7532,7 +7532,7 @@
       <c r="K290"/>
       <c r="L290"/>
     </row>
-    <row r="291" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A291" s="1"/>
       <c r="B291"/>
       <c r="C291"/>
@@ -7546,7 +7546,7 @@
       <c r="K291"/>
       <c r="L291"/>
     </row>
-    <row r="292" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A292" s="1"/>
       <c r="B292"/>
       <c r="C292"/>
@@ -7560,7 +7560,7 @@
       <c r="K292"/>
       <c r="L292"/>
     </row>
-    <row r="293" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A293" s="1"/>
       <c r="B293"/>
       <c r="C293"/>
@@ -7574,7 +7574,7 @@
       <c r="K293"/>
       <c r="L293"/>
     </row>
-    <row r="294" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A294" s="1"/>
       <c r="B294"/>
       <c r="C294"/>
@@ -7588,7 +7588,7 @@
       <c r="K294"/>
       <c r="L294"/>
     </row>
-    <row r="295" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A295" s="1"/>
       <c r="B295"/>
       <c r="C295"/>
@@ -7602,7 +7602,7 @@
       <c r="K295"/>
       <c r="L295"/>
     </row>
-    <row r="296" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A296" s="1"/>
       <c r="B296"/>
       <c r="C296"/>
@@ -7616,7 +7616,7 @@
       <c r="K296"/>
       <c r="L296"/>
     </row>
-    <row r="297" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A297" s="1"/>
       <c r="B297"/>
       <c r="C297"/>
@@ -7630,7 +7630,7 @@
       <c r="K297"/>
       <c r="L297"/>
     </row>
-    <row r="298" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A298" s="1"/>
       <c r="B298"/>
       <c r="C298"/>
@@ -7644,7 +7644,7 @@
       <c r="K298"/>
       <c r="L298"/>
     </row>
-    <row r="299" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A299" s="1"/>
       <c r="B299"/>
       <c r="C299"/>
@@ -7658,7 +7658,7 @@
       <c r="K299"/>
       <c r="L299"/>
     </row>
-    <row r="300" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A300" s="1"/>
       <c r="B300"/>
       <c r="C300"/>
@@ -7672,7 +7672,7 @@
       <c r="K300"/>
       <c r="L300"/>
     </row>
-    <row r="301" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A301" s="1"/>
       <c r="B301"/>
       <c r="C301"/>
@@ -7686,7 +7686,7 @@
       <c r="K301"/>
       <c r="L301"/>
     </row>
-    <row r="302" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A302" s="1"/>
       <c r="B302"/>
       <c r="C302"/>
@@ -7700,7 +7700,7 @@
       <c r="K302"/>
       <c r="L302"/>
     </row>
-    <row r="303" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A303" s="1"/>
       <c r="B303"/>
       <c r="C303"/>
@@ -7714,7 +7714,7 @@
       <c r="K303"/>
       <c r="L303"/>
     </row>
-    <row r="304" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A304" s="1"/>
       <c r="B304"/>
       <c r="C304"/>
@@ -7728,7 +7728,7 @@
       <c r="K304"/>
       <c r="L304"/>
     </row>
-    <row r="305" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A305" s="1"/>
       <c r="B305"/>
       <c r="C305"/>
@@ -7742,7 +7742,7 @@
       <c r="K305"/>
       <c r="L305"/>
     </row>
-    <row r="306" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A306" s="1"/>
       <c r="B306"/>
       <c r="C306"/>
@@ -7756,7 +7756,7 @@
       <c r="K306"/>
       <c r="L306"/>
     </row>
-    <row r="307" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A307" s="1"/>
       <c r="B307"/>
       <c r="C307"/>
@@ -7770,7 +7770,7 @@
       <c r="K307"/>
       <c r="L307"/>
     </row>
-    <row r="308" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A308" s="1"/>
       <c r="B308"/>
       <c r="C308"/>
@@ -7784,7 +7784,7 @@
       <c r="K308"/>
       <c r="L308"/>
     </row>
-    <row r="309" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A309" s="1"/>
       <c r="B309"/>
       <c r="C309"/>
@@ -7798,7 +7798,7 @@
       <c r="K309"/>
       <c r="L309"/>
     </row>
-    <row r="310" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A310" s="1"/>
       <c r="B310"/>
       <c r="C310"/>
@@ -7812,7 +7812,7 @@
       <c r="K310"/>
       <c r="L310"/>
     </row>
-    <row r="311" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
       <c r="B311"/>
       <c r="C311"/>
@@ -7826,7 +7826,7 @@
       <c r="K311"/>
       <c r="L311"/>
     </row>
-    <row r="312" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A312" s="1"/>
       <c r="B312"/>
       <c r="C312"/>
@@ -7840,7 +7840,7 @@
       <c r="K312"/>
       <c r="L312"/>
     </row>
-    <row r="313" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>
       <c r="B313"/>
       <c r="C313"/>
@@ -7854,7 +7854,7 @@
       <c r="K313"/>
       <c r="L313"/>
     </row>
-    <row r="314" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
       <c r="B314"/>
       <c r="C314"/>
@@ -7868,7 +7868,7 @@
       <c r="K314"/>
       <c r="L314"/>
     </row>
-    <row r="315" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A315" s="1"/>
       <c r="B315"/>
       <c r="C315"/>
@@ -7882,7 +7882,7 @@
       <c r="K315"/>
       <c r="L315"/>
     </row>
-    <row r="316" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>
       <c r="B316"/>
       <c r="C316"/>
@@ -7896,7 +7896,7 @@
       <c r="K316"/>
       <c r="L316"/>
     </row>
-    <row r="317" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A317" s="1"/>
       <c r="B317"/>
       <c r="C317"/>
@@ -7910,7 +7910,7 @@
       <c r="K317"/>
       <c r="L317"/>
     </row>
-    <row r="318" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
       <c r="B318"/>
       <c r="C318"/>
@@ -7924,7 +7924,7 @@
       <c r="K318"/>
       <c r="L318"/>
     </row>
-    <row r="319" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
       <c r="B319"/>
       <c r="C319"/>
@@ -7938,7 +7938,7 @@
       <c r="K319"/>
       <c r="L319"/>
     </row>
-    <row r="320" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
       <c r="B320"/>
       <c r="C320"/>
@@ -7952,7 +7952,7 @@
       <c r="K320"/>
       <c r="L320"/>
     </row>
-    <row r="321" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A321" s="1"/>
       <c r="B321"/>
       <c r="C321"/>
@@ -7966,7 +7966,7 @@
       <c r="K321"/>
       <c r="L321"/>
     </row>
-    <row r="322" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
       <c r="B322"/>
       <c r="C322"/>
@@ -7980,7 +7980,7 @@
       <c r="K322"/>
       <c r="L322"/>
     </row>
-    <row r="323" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
       <c r="B323"/>
       <c r="C323"/>
@@ -7994,7 +7994,7 @@
       <c r="K323"/>
       <c r="L323"/>
     </row>
-    <row r="324" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
       <c r="B324"/>
       <c r="C324"/>
@@ -8008,7 +8008,7 @@
       <c r="K324"/>
       <c r="L324"/>
     </row>
-    <row r="325" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
       <c r="B325"/>
       <c r="C325"/>
@@ -8022,7 +8022,7 @@
       <c r="K325"/>
       <c r="L325"/>
     </row>
-    <row r="326" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
       <c r="B326"/>
       <c r="C326"/>
@@ -8036,7 +8036,7 @@
       <c r="K326"/>
       <c r="L326"/>
     </row>
-    <row r="327" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
       <c r="B327"/>
       <c r="C327"/>
@@ -8050,7 +8050,7 @@
       <c r="K327"/>
       <c r="L327"/>
     </row>
-    <row r="328" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
       <c r="B328"/>
       <c r="C328"/>
@@ -8064,7 +8064,7 @@
       <c r="K328"/>
       <c r="L328"/>
     </row>
-    <row r="329" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
       <c r="B329"/>
       <c r="C329"/>
@@ -8078,7 +8078,7 @@
       <c r="K329"/>
       <c r="L329"/>
     </row>
-    <row r="330" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
       <c r="B330"/>
       <c r="C330"/>
@@ -8092,7 +8092,7 @@
       <c r="K330"/>
       <c r="L330"/>
     </row>
-    <row r="331" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
       <c r="B331"/>
       <c r="C331"/>
@@ -8106,7 +8106,7 @@
       <c r="K331"/>
       <c r="L331"/>
     </row>
-    <row r="332" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>
       <c r="B332"/>
       <c r="C332"/>
@@ -8120,7 +8120,7 @@
       <c r="K332"/>
       <c r="L332"/>
     </row>
-    <row r="333" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A333" s="1"/>
       <c r="B333"/>
       <c r="C333"/>
@@ -8134,7 +8134,7 @@
       <c r="K333"/>
       <c r="L333"/>
     </row>
-    <row r="334" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A334" s="1"/>
       <c r="B334"/>
       <c r="C334"/>
@@ -8148,7 +8148,7 @@
       <c r="K334"/>
       <c r="L334"/>
     </row>
-    <row r="335" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A335" s="1"/>
       <c r="B335"/>
       <c r="C335"/>
@@ -8162,7 +8162,7 @@
       <c r="K335"/>
       <c r="L335"/>
     </row>
-    <row r="336" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A336" s="1"/>
       <c r="B336"/>
       <c r="C336"/>
@@ -8176,7 +8176,7 @@
       <c r="K336"/>
       <c r="L336"/>
     </row>
-    <row r="337" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A337" s="1"/>
       <c r="B337"/>
       <c r="C337"/>
@@ -8190,7 +8190,7 @@
       <c r="K337"/>
       <c r="L337"/>
     </row>
-    <row r="338" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A338" s="1"/>
       <c r="B338"/>
       <c r="C338"/>
@@ -8204,7 +8204,7 @@
       <c r="K338"/>
       <c r="L338"/>
     </row>
-    <row r="339" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A339" s="1"/>
       <c r="B339"/>
       <c r="C339"/>
@@ -8218,7 +8218,7 @@
       <c r="K339"/>
       <c r="L339"/>
     </row>
-    <row r="340" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A340" s="1"/>
       <c r="B340"/>
       <c r="C340"/>
@@ -8232,7 +8232,7 @@
       <c r="K340"/>
       <c r="L340"/>
     </row>
-    <row r="341" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A341" s="1"/>
       <c r="B341"/>
       <c r="C341"/>
@@ -8246,7 +8246,7 @@
       <c r="K341"/>
       <c r="L341"/>
     </row>
-    <row r="342" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A342" s="1"/>
       <c r="B342"/>
       <c r="C342"/>
@@ -8260,7 +8260,7 @@
       <c r="K342"/>
       <c r="L342"/>
     </row>
-    <row r="343" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A343" s="1"/>
       <c r="B343"/>
       <c r="C343"/>
@@ -8274,7 +8274,7 @@
       <c r="K343"/>
       <c r="L343"/>
     </row>
-    <row r="344" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A344" s="1"/>
       <c r="B344"/>
       <c r="C344"/>
@@ -8288,7 +8288,7 @@
       <c r="K344"/>
       <c r="L344"/>
     </row>
-    <row r="345" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A345" s="1"/>
       <c r="B345"/>
       <c r="C345"/>
@@ -8302,7 +8302,7 @@
       <c r="K345"/>
       <c r="L345"/>
     </row>
-    <row r="346" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A346" s="1"/>
       <c r="B346"/>
       <c r="C346"/>
@@ -8316,7 +8316,7 @@
       <c r="K346"/>
       <c r="L346"/>
     </row>
-    <row r="347" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A347" s="1"/>
       <c r="B347"/>
       <c r="C347"/>
@@ -8330,7 +8330,7 @@
       <c r="K347"/>
       <c r="L347"/>
     </row>
-    <row r="348" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A348" s="1"/>
       <c r="B348"/>
       <c r="C348"/>
@@ -8344,7 +8344,7 @@
       <c r="K348"/>
       <c r="L348"/>
     </row>
-    <row r="349" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A349" s="1"/>
       <c r="B349"/>
       <c r="C349"/>
@@ -8358,7 +8358,7 @@
       <c r="K349"/>
       <c r="L349"/>
     </row>
-    <row r="350" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A350" s="1"/>
       <c r="B350"/>
       <c r="C350"/>
@@ -8372,7 +8372,7 @@
       <c r="K350"/>
       <c r="L350"/>
     </row>
-    <row r="351" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A351" s="1"/>
       <c r="B351"/>
       <c r="C351"/>
@@ -8386,7 +8386,7 @@
       <c r="K351"/>
       <c r="L351"/>
     </row>
-    <row r="352" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A352" s="1"/>
       <c r="B352"/>
       <c r="C352"/>
@@ -8400,7 +8400,7 @@
       <c r="K352"/>
       <c r="L352"/>
     </row>
-    <row r="353" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A353" s="1"/>
       <c r="B353"/>
       <c r="C353"/>
@@ -8414,7 +8414,7 @@
       <c r="K353"/>
       <c r="L353"/>
     </row>
-    <row r="354" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A354" s="1"/>
       <c r="B354"/>
       <c r="C354"/>
@@ -8428,7 +8428,7 @@
       <c r="K354"/>
       <c r="L354"/>
     </row>
-    <row r="355" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A355" s="1"/>
       <c r="B355"/>
       <c r="C355"/>
@@ -8442,7 +8442,7 @@
       <c r="K355"/>
       <c r="L355"/>
     </row>
-    <row r="356" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A356" s="1"/>
       <c r="B356"/>
       <c r="C356"/>
@@ -8456,7 +8456,7 @@
       <c r="K356"/>
       <c r="L356"/>
     </row>
-    <row r="357" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A357" s="1"/>
       <c r="B357"/>
       <c r="C357"/>
@@ -8470,7 +8470,7 @@
       <c r="K357"/>
       <c r="L357"/>
     </row>
-    <row r="358" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A358" s="1"/>
       <c r="B358"/>
       <c r="C358"/>
@@ -8484,7 +8484,7 @@
       <c r="K358"/>
       <c r="L358"/>
     </row>
-    <row r="359" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A359" s="1"/>
       <c r="B359"/>
       <c r="C359"/>
@@ -8498,7 +8498,7 @@
       <c r="K359"/>
       <c r="L359"/>
     </row>
-    <row r="360" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A360" s="1"/>
       <c r="B360"/>
       <c r="C360"/>
@@ -8512,7 +8512,7 @@
       <c r="K360"/>
       <c r="L360"/>
     </row>
-    <row r="361" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A361" s="1"/>
       <c r="B361"/>
       <c r="C361"/>
@@ -8526,7 +8526,7 @@
       <c r="K361"/>
       <c r="L361"/>
     </row>
-    <row r="362" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A362" s="1"/>
       <c r="B362"/>
       <c r="C362"/>
@@ -8540,7 +8540,7 @@
       <c r="K362"/>
       <c r="L362"/>
     </row>
-    <row r="363" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A363" s="1"/>
       <c r="B363"/>
       <c r="C363"/>
@@ -8554,7 +8554,7 @@
       <c r="K363"/>
       <c r="L363"/>
     </row>
-    <row r="364" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A364" s="1"/>
       <c r="B364"/>
       <c r="C364"/>
@@ -8643,20 +8643,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I368"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.44140625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="21.44140625" style="7" customWidth="1"/>
+    <col min="1" max="1" width="4.42578125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" style="7" customWidth="1"/>
     <col min="3" max="3" width="68" style="7" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" style="7" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="31.88671875" style="7" customWidth="1"/>
-    <col min="7" max="48" width="15.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="10.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="50" max="16384" width="8.6640625" style="7"/>
+    <col min="4" max="4" width="13.42578125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="7" customWidth="1"/>
+    <col min="6" max="6" width="31.85546875" style="7" customWidth="1"/>
+    <col min="7" max="48" width="15.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="10.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="50" max="16384" width="8.7109375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="23.25" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8664,7 +8664,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
@@ -8687,7 +8687,7 @@
       <c r="H2"/>
       <c r="I2"/>
     </row>
-    <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="str">
         <f>IF(LEN(ContactData!H2)&lt;3,"",ContactData!H2)</f>
         <v/>
@@ -8716,7 +8716,7 @@
       <c r="H3"/>
       <c r="I3"/>
     </row>
-    <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="9">
         <f>IF(LEN(ContactData!H3)&lt;3,"",ContactData!H3)</f>
         <v>500</v>
@@ -8745,7 +8745,7 @@
       <c r="H4"/>
       <c r="I4"/>
     </row>
-    <row r="5" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
         <f>IF(LEN(ContactData!H4)&lt;3,"",ContactData!H4)</f>
         <v>511</v>
@@ -8774,7 +8774,7 @@
       <c r="H5"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <f>IF(LEN(ContactData!H5)&lt;3,"",ContactData!H5)</f>
         <v>228</v>
@@ -8803,7 +8803,7 @@
       <c r="H6"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <f>IF(LEN(ContactData!H6)&lt;3,"",ContactData!H6)</f>
         <v>521</v>
@@ -8832,7 +8832,7 @@
       <c r="H7"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <f>IF(LEN(ContactData!H7)&lt;3,"",ContactData!H7)</f>
         <v>165</v>
@@ -8861,7 +8861,7 @@
       <c r="H8"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <f>IF(LEN(ContactData!H8)&lt;3,"",ContactData!H8)</f>
         <v>502</v>
@@ -8890,7 +8890,7 @@
       <c r="H9"/>
       <c r="I9"/>
     </row>
-    <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="str">
         <f>IF(LEN(ContactData!H9)&lt;3,"",ContactData!H9)</f>
         <v>---</v>
@@ -8919,7 +8919,7 @@
       <c r="H10"/>
       <c r="I10"/>
     </row>
-    <row r="11" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="str">
         <f>IF(LEN(ContactData!H10)&lt;3,"",ContactData!H10)</f>
         <v>---</v>
@@ -8948,7 +8948,7 @@
       <c r="H11"/>
       <c r="I11"/>
     </row>
-    <row r="12" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <f>IF(LEN(ContactData!H11)&lt;3,"",ContactData!H11)</f>
         <v>509</v>
@@ -8977,7 +8977,7 @@
       <c r="H12"/>
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <f>IF(LEN(ContactData!H12)&lt;3,"",ContactData!H12)</f>
         <v>504</v>
@@ -9006,7 +9006,7 @@
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <f>IF(LEN(ContactData!H13)&lt;3,"",ContactData!H13)</f>
         <v>514</v>
@@ -9035,7 +9035,7 @@
       <c r="H14"/>
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <f>IF(LEN(ContactData!H14)&lt;3,"",ContactData!H14)</f>
         <v>224</v>
@@ -9064,7 +9064,7 @@
       <c r="H15"/>
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <f>IF(LEN(ContactData!H15)&lt;3,"",ContactData!H15)</f>
         <v>123</v>
@@ -9093,7 +9093,7 @@
       <c r="H16"/>
       <c r="I16"/>
     </row>
-    <row r="17" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <f>IF(LEN(ContactData!H16)&lt;3,"",ContactData!H16)</f>
         <v>206</v>
@@ -9122,7 +9122,7 @@
       <c r="H17"/>
       <c r="I17"/>
     </row>
-    <row r="18" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <f>IF(LEN(ContactData!H17)&lt;3,"",ContactData!H17)</f>
         <v>507</v>
@@ -9151,7 +9151,7 @@
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <f>IF(LEN(ContactData!H18)&lt;3,"",ContactData!H18)</f>
         <v>508</v>
@@ -9180,7 +9180,7 @@
       <c r="H19"/>
       <c r="I19"/>
     </row>
-    <row r="20" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <f>IF(LEN(ContactData!H19)&lt;3,"",ContactData!H19)</f>
         <v>255</v>
@@ -9209,7 +9209,7 @@
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <f>IF(LEN(ContactData!H20)&lt;3,"",ContactData!H20)</f>
         <v>506</v>
@@ -9238,7 +9238,7 @@
       <c r="H21"/>
       <c r="I21"/>
     </row>
-    <row r="22" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <f>IF(LEN(ContactData!H21)&lt;3,"",ContactData!H21)</f>
         <v>519</v>
@@ -9267,7 +9267,7 @@
       <c r="H22"/>
       <c r="I22"/>
     </row>
-    <row r="23" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="str">
         <f>IF(LEN(ContactData!H22)&lt;3,"",ContactData!H22)</f>
         <v>---</v>
@@ -9296,7 +9296,7 @@
       <c r="H23"/>
       <c r="I23"/>
     </row>
-    <row r="24" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <f>IF(LEN(ContactData!H23)&lt;3,"",ContactData!H23)</f>
         <v>121</v>
@@ -9325,7 +9325,7 @@
       <c r="H24"/>
       <c r="I24"/>
     </row>
-    <row r="25" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <f>IF(LEN(ContactData!H24)&lt;3,"",ContactData!H24)</f>
         <v>522</v>
@@ -9354,7 +9354,7 @@
       <c r="H25"/>
       <c r="I25"/>
     </row>
-    <row r="26" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <f>IF(LEN(ContactData!H25)&lt;3,"",ContactData!H25)</f>
         <v>522</v>
@@ -9383,7 +9383,7 @@
       <c r="H26"/>
       <c r="I26"/>
     </row>
-    <row r="27" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A27" s="9" t="str">
         <f>IF(LEN(ContactData!H26)&lt;3,"",ContactData!H26)</f>
         <v/>
@@ -9412,7 +9412,7 @@
       <c r="H27"/>
       <c r="I27"/>
     </row>
-    <row r="28" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="str">
         <f>IF(LEN(ContactData!H27)&lt;3,"",ContactData!H27)</f>
         <v>---</v>
@@ -9441,7 +9441,7 @@
       <c r="H28"/>
       <c r="I28"/>
     </row>
-    <row r="29" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="str">
         <f>IF(LEN(ContactData!H28)&lt;3,"",ContactData!H28)</f>
         <v>---</v>
@@ -9470,7 +9470,7 @@
       <c r="H29"/>
       <c r="I29"/>
     </row>
-    <row r="30" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="str">
         <f>IF(LEN(ContactData!H29)&lt;3,"",ContactData!H29)</f>
         <v>---</v>
@@ -9499,7 +9499,7 @@
       <c r="H30"/>
       <c r="I30"/>
     </row>
-    <row r="31" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="str">
         <f>IF(LEN(ContactData!H30)&lt;3,"",ContactData!H30)</f>
         <v/>
@@ -9528,7 +9528,7 @@
       <c r="H31"/>
       <c r="I31"/>
     </row>
-    <row r="32" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="str">
         <f>IF(LEN(ContactData!H31)&lt;3,"",ContactData!H31)</f>
         <v>---</v>
@@ -9557,7 +9557,7 @@
       <c r="H32"/>
       <c r="I32"/>
     </row>
-    <row r="33" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="str">
         <f>IF(LEN(ContactData!H32)&lt;3,"",ContactData!H32)</f>
         <v>---</v>
@@ -9586,7 +9586,7 @@
       <c r="H33"/>
       <c r="I33"/>
     </row>
-    <row r="34" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="str">
         <f>IF(LEN(ContactData!H33)&lt;3,"",ContactData!H33)</f>
         <v>---</v>
@@ -9615,7 +9615,7 @@
       <c r="H34"/>
       <c r="I34"/>
     </row>
-    <row r="35" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="str">
         <f>IF(LEN(ContactData!H34)&lt;3,"",ContactData!H34)</f>
         <v/>
@@ -9644,7 +9644,7 @@
       <c r="H35"/>
       <c r="I35"/>
     </row>
-    <row r="36" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
         <f>IF(LEN(ContactData!H35)&lt;3,"",ContactData!H35)</f>
         <v>176</v>
@@ -9673,7 +9673,7 @@
       <c r="H36"/>
       <c r="I36"/>
     </row>
-    <row r="37" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <f>IF(LEN(ContactData!H36)&lt;3,"",ContactData!H36)</f>
         <v>104</v>
@@ -9702,7 +9702,7 @@
       <c r="H37"/>
       <c r="I37"/>
     </row>
-    <row r="38" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
         <f>IF(LEN(ContactData!H37)&lt;3,"",ContactData!H37)</f>
         <v>100</v>
@@ -9731,7 +9731,7 @@
       <c r="H38"/>
       <c r="I38"/>
     </row>
-    <row r="39" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="str">
         <f>IF(LEN(ContactData!H38)&lt;3,"",ContactData!H38)</f>
         <v/>
@@ -9760,7 +9760,7 @@
       <c r="H39"/>
       <c r="I39"/>
     </row>
-    <row r="40" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="str">
         <f>IF(LEN(ContactData!H39)&lt;3,"",ContactData!H39)</f>
         <v>---</v>
@@ -9789,7 +9789,7 @@
       <c r="H40"/>
       <c r="I40"/>
     </row>
-    <row r="41" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="str">
         <f>IF(LEN(ContactData!H40)&lt;3,"",ContactData!H40)</f>
         <v>---</v>
@@ -9818,7 +9818,7 @@
       <c r="H41"/>
       <c r="I41"/>
     </row>
-    <row r="42" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="str">
         <f>IF(LEN(ContactData!H41)&lt;3,"",ContactData!H41)</f>
         <v/>
@@ -9847,7 +9847,7 @@
       <c r="H42"/>
       <c r="I42"/>
     </row>
-    <row r="43" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A43" s="9">
         <f>IF(LEN(ContactData!H42)&lt;3,"",ContactData!H42)</f>
         <v>228</v>
@@ -9876,7 +9876,7 @@
       <c r="H43"/>
       <c r="I43"/>
     </row>
-    <row r="44" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="str">
         <f>IF(LEN(ContactData!H43)&lt;3,"",ContactData!H43)</f>
         <v/>
@@ -9905,7 +9905,7 @@
       <c r="H44"/>
       <c r="I44"/>
     </row>
-    <row r="45" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A45" s="9">
         <f>IF(LEN(ContactData!H44)&lt;3,"",ContactData!H44)</f>
         <v>521</v>
@@ -9934,7 +9934,7 @@
       <c r="H45"/>
       <c r="I45"/>
     </row>
-    <row r="46" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A46" s="9">
         <f>IF(LEN(ContactData!H45)&lt;3,"",ContactData!H45)</f>
         <v>514</v>
@@ -9963,7 +9963,7 @@
       <c r="H46"/>
       <c r="I46"/>
     </row>
-    <row r="47" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
         <f>IF(LEN(ContactData!H46)&lt;3,"",ContactData!H46)</f>
         <v>286</v>
@@ -9992,7 +9992,7 @@
       <c r="H47"/>
       <c r="I47"/>
     </row>
-    <row r="48" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A48" s="9">
         <f>IF(LEN(ContactData!H47)&lt;3,"",ContactData!H47)</f>
         <v>516</v>
@@ -10021,7 +10021,7 @@
       <c r="H48"/>
       <c r="I48"/>
     </row>
-    <row r="49" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
         <f>IF(LEN(ContactData!H48)&lt;3,"",ContactData!H48)</f>
         <v>512</v>
@@ -10050,7 +10050,7 @@
       <c r="H49"/>
       <c r="I49"/>
     </row>
-    <row r="50" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A50" s="9">
         <f>IF(LEN(ContactData!H49)&lt;3,"",ContactData!H49)</f>
         <v>284</v>
@@ -10079,10 +10079,10 @@
       <c r="H50"/>
       <c r="I50"/>
     </row>
-    <row r="51" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
         <f>IF(LEN(ContactData!H50)&lt;3,"",ContactData!H50)</f>
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="B51" s="3" t="str">
         <f>ContactData!E50</f>
@@ -10108,7 +10108,7 @@
       <c r="H51"/>
       <c r="I51"/>
     </row>
-    <row r="52" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
         <f>IF(LEN(ContactData!H51)&lt;3,"",ContactData!H51)</f>
         <v>520</v>
@@ -10137,7 +10137,7 @@
       <c r="H52"/>
       <c r="I52"/>
     </row>
-    <row r="53" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
         <f>IF(LEN(ContactData!H52)&lt;3,"",ContactData!H52)</f>
         <v>168</v>
@@ -10166,7 +10166,7 @@
       <c r="H53"/>
       <c r="I53"/>
     </row>
-    <row r="54" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
         <f>IF(LEN(ContactData!H53)&lt;3,"",ContactData!H53)</f>
         <v>210</v>
@@ -10195,7 +10195,7 @@
       <c r="H54"/>
       <c r="I54"/>
     </row>
-    <row r="55" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <f>IF(LEN(ContactData!H54)&lt;3,"",ContactData!H54)</f>
         <v>518</v>
@@ -10224,7 +10224,7 @@
       <c r="H55"/>
       <c r="I55"/>
     </row>
-    <row r="56" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
         <f>IF(LEN(ContactData!H55)&lt;3,"",ContactData!H55)</f>
         <v>281</v>
@@ -10253,7 +10253,7 @@
       <c r="H56"/>
       <c r="I56"/>
     </row>
-    <row r="57" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
         <f>IF(LEN(ContactData!H56)&lt;3,"",ContactData!H56)</f>
         <v>523</v>
@@ -10282,7 +10282,7 @@
       <c r="H57"/>
       <c r="I57"/>
     </row>
-    <row r="58" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
         <f>IF(LEN(ContactData!H57)&lt;3,"",ContactData!H57)</f>
         <v>223</v>
@@ -10311,7 +10311,7 @@
       <c r="H58"/>
       <c r="I58"/>
     </row>
-    <row r="59" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <f>IF(LEN(ContactData!H58)&lt;3,"",ContactData!H58)</f>
         <v>172</v>
@@ -10340,7 +10340,7 @@
       <c r="H59"/>
       <c r="I59"/>
     </row>
-    <row r="60" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
         <f>IF(LEN(ContactData!H59)&lt;3,"",ContactData!H59)</f>
         <v>182</v>
@@ -10369,7 +10369,7 @@
       <c r="H60"/>
       <c r="I60"/>
     </row>
-    <row r="61" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="str">
         <f>IF(LEN(ContactData!H60)&lt;3,"",ContactData!H60)</f>
         <v>---</v>
@@ -10398,7 +10398,7 @@
       <c r="H61"/>
       <c r="I61"/>
     </row>
-    <row r="62" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
         <f>IF(LEN(ContactData!H61)&lt;3,"",ContactData!H61)</f>
         <v>229</v>
@@ -10427,7 +10427,7 @@
       <c r="H62"/>
       <c r="I62"/>
     </row>
-    <row r="63" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A63" s="9" t="str">
         <f>IF(LEN(ContactData!H62)&lt;3,"",ContactData!H62)</f>
         <v/>
@@ -10456,7 +10456,7 @@
       <c r="H63"/>
       <c r="I63"/>
     </row>
-    <row r="64" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="str">
         <f>IF(LEN(ContactData!H63)&lt;3,"",ContactData!H63)</f>
         <v>---</v>
@@ -10485,7 +10485,7 @@
       <c r="H64"/>
       <c r="I64"/>
     </row>
-    <row r="65" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A65" s="9" t="str">
         <f>IF(LEN(ContactData!H64)&lt;3,"",ContactData!H64)</f>
         <v>---</v>
@@ -10514,7 +10514,7 @@
       <c r="H65"/>
       <c r="I65"/>
     </row>
-    <row r="66" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="str">
         <f>IF(LEN(ContactData!H65)&lt;3,"",ContactData!H65)</f>
         <v>---</v>
@@ -10543,7 +10543,7 @@
       <c r="H66"/>
       <c r="I66"/>
     </row>
-    <row r="67" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A67" s="9" t="str">
         <f>IF(LEN(ContactData!H66)&lt;3,"",ContactData!H66)</f>
         <v/>
@@ -10572,7 +10572,7 @@
       <c r="H67"/>
       <c r="I67"/>
     </row>
-    <row r="68" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="str">
         <f>IF(LEN(ContactData!H67)&lt;3,"",ContactData!H67)</f>
         <v>---</v>
@@ -10601,7 +10601,7 @@
       <c r="H68"/>
       <c r="I68"/>
     </row>
-    <row r="69" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A69" s="9" t="str">
         <f>IF(LEN(ContactData!H68)&lt;3,"",ContactData!H68)</f>
         <v>---</v>
@@ -10630,7 +10630,7 @@
       <c r="H69"/>
       <c r="I69"/>
     </row>
-    <row r="70" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="str">
         <f>IF(LEN(ContactData!H69)&lt;3,"",ContactData!H69)</f>
         <v/>
@@ -10659,7 +10659,7 @@
       <c r="H70"/>
       <c r="I70"/>
     </row>
-    <row r="71" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="str">
         <f>IF(LEN(ContactData!H70)&lt;3,"",ContactData!H70)</f>
         <v>---</v>
@@ -10688,7 +10688,7 @@
       <c r="H71"/>
       <c r="I71"/>
     </row>
-    <row r="72" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A72" s="9" t="str">
         <f>IF(LEN(ContactData!H71)&lt;3,"",ContactData!H71)</f>
         <v>---</v>
@@ -10717,7 +10717,7 @@
       <c r="H72"/>
       <c r="I72"/>
     </row>
-    <row r="73" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A73" s="9" t="str">
         <f>IF(LEN(ContactData!H72)&lt;3,"",ContactData!H72)</f>
         <v/>
@@ -10746,7 +10746,7 @@
       <c r="H73"/>
       <c r="I73"/>
     </row>
-    <row r="74" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A74" s="9" t="str">
         <f>IF(LEN(ContactData!H73)&lt;3,"",ContactData!H73)</f>
         <v>---</v>
@@ -10775,7 +10775,7 @@
       <c r="H74"/>
       <c r="I74"/>
     </row>
-    <row r="75" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A75" s="9" t="str">
         <f>IF(LEN(ContactData!H74)&lt;3,"",ContactData!H74)</f>
         <v>---</v>
@@ -10804,7 +10804,7 @@
       <c r="H75"/>
       <c r="I75"/>
     </row>
-    <row r="76" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A76" s="9" t="str">
         <f>IF(LEN(ContactData!H75)&lt;3,"",ContactData!H75)</f>
         <v>---</v>
@@ -10833,7 +10833,7 @@
       <c r="H76"/>
       <c r="I76"/>
     </row>
-    <row r="77" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A77" s="9" t="str">
         <f>IF(LEN(ContactData!H76)&lt;3,"",ContactData!H76)</f>
         <v/>
@@ -10862,7 +10862,7 @@
       <c r="H77"/>
       <c r="I77"/>
     </row>
-    <row r="78" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A78" s="9" t="str">
         <f>IF(LEN(ContactData!H77)&lt;3,"",ContactData!H77)</f>
         <v/>
@@ -10891,7 +10891,7 @@
       <c r="H78"/>
       <c r="I78"/>
     </row>
-    <row r="79" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
         <f>IF(LEN(ContactData!H78)&lt;3,"",ContactData!H78)</f>
         <v>120</v>
@@ -10920,7 +10920,7 @@
       <c r="H79"/>
       <c r="I79"/>
     </row>
-    <row r="80" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
         <f>IF(LEN(ContactData!H79)&lt;3,"",ContactData!H79)</f>
         <v>187</v>
@@ -10949,7 +10949,7 @@
       <c r="H80"/>
       <c r="I80"/>
     </row>
-    <row r="81" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81"/>
       <c r="C81"/>
@@ -10960,7 +10960,7 @@
       <c r="H81"/>
       <c r="I81"/>
     </row>
-    <row r="82" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82"/>
       <c r="C82"/>
@@ -10971,7 +10971,7 @@
       <c r="H82"/>
       <c r="I82"/>
     </row>
-    <row r="83" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83"/>
       <c r="C83"/>
@@ -10982,7 +10982,7 @@
       <c r="H83"/>
       <c r="I83"/>
     </row>
-    <row r="84" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84"/>
       <c r="C84"/>
@@ -10993,7 +10993,7 @@
       <c r="H84"/>
       <c r="I84"/>
     </row>
-    <row r="85" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85"/>
       <c r="C85"/>
@@ -11004,7 +11004,7 @@
       <c r="H85"/>
       <c r="I85"/>
     </row>
-    <row r="86" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86"/>
       <c r="C86"/>
@@ -11015,7 +11015,7 @@
       <c r="H86"/>
       <c r="I86"/>
     </row>
-    <row r="87" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87"/>
       <c r="C87"/>
@@ -11026,7 +11026,7 @@
       <c r="H87"/>
       <c r="I87"/>
     </row>
-    <row r="88" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88"/>
       <c r="C88"/>
@@ -11037,7 +11037,7 @@
       <c r="H88"/>
       <c r="I88"/>
     </row>
-    <row r="89" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89"/>
       <c r="C89"/>
@@ -11048,7 +11048,7 @@
       <c r="H89"/>
       <c r="I89"/>
     </row>
-    <row r="90" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90"/>
       <c r="C90"/>
@@ -11059,7 +11059,7 @@
       <c r="H90"/>
       <c r="I90"/>
     </row>
-    <row r="91" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91"/>
       <c r="C91"/>
@@ -11070,7 +11070,7 @@
       <c r="H91"/>
       <c r="I91"/>
     </row>
-    <row r="92" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92"/>
       <c r="C92"/>
@@ -11081,7 +11081,7 @@
       <c r="H92"/>
       <c r="I92"/>
     </row>
-    <row r="93" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93"/>
       <c r="C93"/>
@@ -11092,7 +11092,7 @@
       <c r="H93"/>
       <c r="I93"/>
     </row>
-    <row r="94" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94"/>
       <c r="C94"/>
@@ -11103,7 +11103,7 @@
       <c r="H94"/>
       <c r="I94"/>
     </row>
-    <row r="95" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95"/>
       <c r="C95"/>
@@ -11114,7 +11114,7 @@
       <c r="H95"/>
       <c r="I95"/>
     </row>
-    <row r="96" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96"/>
       <c r="C96"/>
@@ -11125,7 +11125,7 @@
       <c r="H96"/>
       <c r="I96"/>
     </row>
-    <row r="97" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97"/>
       <c r="C97"/>
@@ -11136,7 +11136,7 @@
       <c r="H97"/>
       <c r="I97"/>
     </row>
-    <row r="98" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98"/>
       <c r="C98"/>
@@ -11147,7 +11147,7 @@
       <c r="H98"/>
       <c r="I98"/>
     </row>
-    <row r="99" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99"/>
       <c r="C99"/>
@@ -11158,7 +11158,7 @@
       <c r="H99"/>
       <c r="I99"/>
     </row>
-    <row r="100" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100"/>
       <c r="C100"/>
@@ -11169,7 +11169,7 @@
       <c r="H100"/>
       <c r="I100"/>
     </row>
-    <row r="101" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101"/>
       <c r="C101"/>
@@ -11180,7 +11180,7 @@
       <c r="H101"/>
       <c r="I101"/>
     </row>
-    <row r="102" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102"/>
       <c r="C102"/>
@@ -11191,7 +11191,7 @@
       <c r="H102"/>
       <c r="I102"/>
     </row>
-    <row r="103" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103"/>
       <c r="C103"/>
@@ -11202,7 +11202,7 @@
       <c r="H103"/>
       <c r="I103"/>
     </row>
-    <row r="104" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104"/>
       <c r="C104"/>
@@ -11213,7 +11213,7 @@
       <c r="H104"/>
       <c r="I104"/>
     </row>
-    <row r="105" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105"/>
       <c r="C105"/>
@@ -11224,7 +11224,7 @@
       <c r="H105"/>
       <c r="I105"/>
     </row>
-    <row r="106" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106"/>
       <c r="C106"/>
@@ -11235,7 +11235,7 @@
       <c r="H106"/>
       <c r="I106"/>
     </row>
-    <row r="107" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107"/>
       <c r="C107"/>
@@ -11246,7 +11246,7 @@
       <c r="H107"/>
       <c r="I107"/>
     </row>
-    <row r="108" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108"/>
       <c r="C108"/>
@@ -11257,7 +11257,7 @@
       <c r="H108"/>
       <c r="I108"/>
     </row>
-    <row r="109" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109"/>
       <c r="C109"/>
@@ -11268,7 +11268,7 @@
       <c r="H109"/>
       <c r="I109"/>
     </row>
-    <row r="110" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110"/>
       <c r="C110"/>
@@ -11279,7 +11279,7 @@
       <c r="H110"/>
       <c r="I110"/>
     </row>
-    <row r="111" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111"/>
       <c r="C111"/>
@@ -11290,7 +11290,7 @@
       <c r="H111"/>
       <c r="I111"/>
     </row>
-    <row r="112" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112"/>
       <c r="C112"/>
@@ -11301,7 +11301,7 @@
       <c r="H112"/>
       <c r="I112"/>
     </row>
-    <row r="113" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113"/>
       <c r="C113"/>
@@ -11312,7 +11312,7 @@
       <c r="H113"/>
       <c r="I113"/>
     </row>
-    <row r="114" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114"/>
       <c r="C114"/>
@@ -11323,7 +11323,7 @@
       <c r="H114"/>
       <c r="I114"/>
     </row>
-    <row r="115" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115"/>
       <c r="C115"/>
@@ -11334,7 +11334,7 @@
       <c r="H115"/>
       <c r="I115"/>
     </row>
-    <row r="116" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116"/>
       <c r="C116"/>
@@ -11345,7 +11345,7 @@
       <c r="H116"/>
       <c r="I116"/>
     </row>
-    <row r="117" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117"/>
       <c r="C117"/>
@@ -11356,7 +11356,7 @@
       <c r="H117"/>
       <c r="I117"/>
     </row>
-    <row r="118" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118"/>
       <c r="C118"/>
@@ -11367,7 +11367,7 @@
       <c r="H118"/>
       <c r="I118"/>
     </row>
-    <row r="119" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119"/>
       <c r="C119"/>
@@ -11378,7 +11378,7 @@
       <c r="H119"/>
       <c r="I119"/>
     </row>
-    <row r="120" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120"/>
       <c r="C120"/>
@@ -11389,7 +11389,7 @@
       <c r="H120"/>
       <c r="I120"/>
     </row>
-    <row r="121" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121"/>
       <c r="C121"/>
@@ -11400,7 +11400,7 @@
       <c r="H121"/>
       <c r="I121"/>
     </row>
-    <row r="122" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122"/>
       <c r="C122"/>
@@ -11411,7 +11411,7 @@
       <c r="H122"/>
       <c r="I122"/>
     </row>
-    <row r="123" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123"/>
       <c r="C123"/>
@@ -11422,7 +11422,7 @@
       <c r="H123"/>
       <c r="I123"/>
     </row>
-    <row r="124" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124"/>
       <c r="C124"/>
@@ -11433,7 +11433,7 @@
       <c r="H124"/>
       <c r="I124"/>
     </row>
-    <row r="125" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125"/>
       <c r="C125"/>
@@ -11444,7 +11444,7 @@
       <c r="H125"/>
       <c r="I125"/>
     </row>
-    <row r="126" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126"/>
       <c r="C126"/>
@@ -11455,7 +11455,7 @@
       <c r="H126"/>
       <c r="I126"/>
     </row>
-    <row r="127" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127"/>
       <c r="C127"/>
@@ -11466,7 +11466,7 @@
       <c r="H127"/>
       <c r="I127"/>
     </row>
-    <row r="128" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128"/>
       <c r="C128"/>
@@ -11477,7 +11477,7 @@
       <c r="H128"/>
       <c r="I128"/>
     </row>
-    <row r="129" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129"/>
       <c r="C129"/>
@@ -11488,7 +11488,7 @@
       <c r="H129"/>
       <c r="I129"/>
     </row>
-    <row r="130" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130"/>
       <c r="C130"/>
@@ -11499,7 +11499,7 @@
       <c r="H130"/>
       <c r="I130"/>
     </row>
-    <row r="131" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131"/>
       <c r="C131"/>
@@ -11510,7 +11510,7 @@
       <c r="H131"/>
       <c r="I131"/>
     </row>
-    <row r="132" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132"/>
       <c r="C132"/>
@@ -11521,7 +11521,7 @@
       <c r="H132"/>
       <c r="I132"/>
     </row>
-    <row r="133" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133"/>
       <c r="C133"/>
@@ -11532,7 +11532,7 @@
       <c r="H133"/>
       <c r="I133"/>
     </row>
-    <row r="134" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134"/>
       <c r="C134"/>
@@ -11543,7 +11543,7 @@
       <c r="H134"/>
       <c r="I134"/>
     </row>
-    <row r="135" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135"/>
       <c r="C135"/>
@@ -11554,7 +11554,7 @@
       <c r="H135"/>
       <c r="I135"/>
     </row>
-    <row r="136" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136"/>
       <c r="C136"/>
@@ -11565,7 +11565,7 @@
       <c r="H136"/>
       <c r="I136"/>
     </row>
-    <row r="137" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137"/>
       <c r="C137"/>
@@ -11576,7 +11576,7 @@
       <c r="H137"/>
       <c r="I137"/>
     </row>
-    <row r="138" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138"/>
       <c r="C138"/>
@@ -11587,7 +11587,7 @@
       <c r="H138"/>
       <c r="I138"/>
     </row>
-    <row r="139" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139"/>
       <c r="C139"/>
@@ -11598,7 +11598,7 @@
       <c r="H139"/>
       <c r="I139"/>
     </row>
-    <row r="140" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140"/>
       <c r="C140"/>
@@ -11609,7 +11609,7 @@
       <c r="H140"/>
       <c r="I140"/>
     </row>
-    <row r="141" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141"/>
       <c r="C141"/>
@@ -11620,7 +11620,7 @@
       <c r="H141"/>
       <c r="I141"/>
     </row>
-    <row r="142" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142"/>
       <c r="C142"/>
@@ -11631,7 +11631,7 @@
       <c r="H142"/>
       <c r="I142"/>
     </row>
-    <row r="143" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143"/>
       <c r="C143"/>
@@ -11642,7 +11642,7 @@
       <c r="H143"/>
       <c r="I143"/>
     </row>
-    <row r="144" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144"/>
       <c r="C144"/>
@@ -11653,7 +11653,7 @@
       <c r="H144"/>
       <c r="I144"/>
     </row>
-    <row r="145" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145"/>
       <c r="C145"/>
@@ -11664,7 +11664,7 @@
       <c r="H145"/>
       <c r="I145"/>
     </row>
-    <row r="146" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146"/>
       <c r="C146"/>
@@ -11675,7 +11675,7 @@
       <c r="H146"/>
       <c r="I146"/>
     </row>
-    <row r="147" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147"/>
       <c r="C147"/>
@@ -11686,7 +11686,7 @@
       <c r="H147"/>
       <c r="I147"/>
     </row>
-    <row r="148" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148"/>
       <c r="C148"/>
@@ -11697,7 +11697,7 @@
       <c r="H148"/>
       <c r="I148"/>
     </row>
-    <row r="149" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149"/>
       <c r="C149"/>
@@ -11708,7 +11708,7 @@
       <c r="H149"/>
       <c r="I149"/>
     </row>
-    <row r="150" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150"/>
       <c r="C150"/>
@@ -11719,7 +11719,7 @@
       <c r="H150"/>
       <c r="I150"/>
     </row>
-    <row r="151" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151"/>
       <c r="C151"/>
@@ -11730,7 +11730,7 @@
       <c r="H151"/>
       <c r="I151"/>
     </row>
-    <row r="152" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152"/>
       <c r="C152"/>
@@ -11741,7 +11741,7 @@
       <c r="H152"/>
       <c r="I152"/>
     </row>
-    <row r="153" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153"/>
       <c r="C153"/>
@@ -11752,7 +11752,7 @@
       <c r="H153"/>
       <c r="I153"/>
     </row>
-    <row r="154" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154"/>
       <c r="C154"/>
@@ -11763,7 +11763,7 @@
       <c r="H154"/>
       <c r="I154"/>
     </row>
-    <row r="155" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155"/>
       <c r="C155"/>
@@ -11774,7 +11774,7 @@
       <c r="H155"/>
       <c r="I155"/>
     </row>
-    <row r="156" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156"/>
       <c r="C156"/>
@@ -11785,7 +11785,7 @@
       <c r="H156"/>
       <c r="I156"/>
     </row>
-    <row r="157" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157"/>
       <c r="C157"/>
@@ -11796,7 +11796,7 @@
       <c r="H157"/>
       <c r="I157"/>
     </row>
-    <row r="158" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158"/>
       <c r="C158"/>
@@ -11807,7 +11807,7 @@
       <c r="H158"/>
       <c r="I158"/>
     </row>
-    <row r="159" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159"/>
       <c r="C159"/>
@@ -11818,7 +11818,7 @@
       <c r="H159"/>
       <c r="I159"/>
     </row>
-    <row r="160" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160"/>
       <c r="C160"/>
@@ -11829,7 +11829,7 @@
       <c r="H160"/>
       <c r="I160"/>
     </row>
-    <row r="161" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161"/>
       <c r="C161"/>
@@ -11840,7 +11840,7 @@
       <c r="H161"/>
       <c r="I161"/>
     </row>
-    <row r="162" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162"/>
       <c r="C162"/>
@@ -11851,7 +11851,7 @@
       <c r="H162"/>
       <c r="I162"/>
     </row>
-    <row r="163" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163"/>
       <c r="C163"/>
@@ -11862,7 +11862,7 @@
       <c r="H163"/>
       <c r="I163"/>
     </row>
-    <row r="164" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164"/>
       <c r="C164"/>
@@ -11873,7 +11873,7 @@
       <c r="H164"/>
       <c r="I164"/>
     </row>
-    <row r="165" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165"/>
       <c r="C165"/>
@@ -11884,7 +11884,7 @@
       <c r="H165"/>
       <c r="I165"/>
     </row>
-    <row r="166" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166"/>
       <c r="C166"/>
@@ -11895,7 +11895,7 @@
       <c r="H166"/>
       <c r="I166"/>
     </row>
-    <row r="167" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167"/>
       <c r="C167"/>
@@ -11906,7 +11906,7 @@
       <c r="H167"/>
       <c r="I167"/>
     </row>
-    <row r="168" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168"/>
       <c r="C168"/>
@@ -11917,7 +11917,7 @@
       <c r="H168"/>
       <c r="I168"/>
     </row>
-    <row r="169" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169"/>
       <c r="C169"/>
@@ -11928,7 +11928,7 @@
       <c r="H169"/>
       <c r="I169"/>
     </row>
-    <row r="170" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170"/>
       <c r="C170"/>
@@ -11939,7 +11939,7 @@
       <c r="H170"/>
       <c r="I170"/>
     </row>
-    <row r="171" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171"/>
       <c r="C171"/>
@@ -11950,7 +11950,7 @@
       <c r="H171"/>
       <c r="I171"/>
     </row>
-    <row r="172" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172"/>
       <c r="C172"/>
@@ -11961,7 +11961,7 @@
       <c r="H172"/>
       <c r="I172"/>
     </row>
-    <row r="173" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173"/>
       <c r="C173"/>
@@ -11972,7 +11972,7 @@
       <c r="H173"/>
       <c r="I173"/>
     </row>
-    <row r="174" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174"/>
       <c r="C174"/>
@@ -11983,7 +11983,7 @@
       <c r="H174"/>
       <c r="I174"/>
     </row>
-    <row r="175" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175"/>
       <c r="C175"/>
@@ -11994,7 +11994,7 @@
       <c r="H175"/>
       <c r="I175"/>
     </row>
-    <row r="176" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176"/>
       <c r="C176"/>
@@ -12005,7 +12005,7 @@
       <c r="H176"/>
       <c r="I176"/>
     </row>
-    <row r="177" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177"/>
       <c r="C177"/>
@@ -12016,7 +12016,7 @@
       <c r="H177"/>
       <c r="I177"/>
     </row>
-    <row r="178" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178"/>
       <c r="C178"/>
@@ -12027,7 +12027,7 @@
       <c r="H178"/>
       <c r="I178"/>
     </row>
-    <row r="179" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179"/>
       <c r="C179"/>
@@ -12038,7 +12038,7 @@
       <c r="H179"/>
       <c r="I179"/>
     </row>
-    <row r="180" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180"/>
       <c r="C180"/>
@@ -12049,7 +12049,7 @@
       <c r="H180"/>
       <c r="I180"/>
     </row>
-    <row r="181" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181"/>
       <c r="C181"/>
@@ -12060,7 +12060,7 @@
       <c r="H181"/>
       <c r="I181"/>
     </row>
-    <row r="182" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182"/>
       <c r="C182"/>
@@ -12071,7 +12071,7 @@
       <c r="H182"/>
       <c r="I182"/>
     </row>
-    <row r="183" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183"/>
       <c r="C183"/>
@@ -12082,7 +12082,7 @@
       <c r="H183"/>
       <c r="I183"/>
     </row>
-    <row r="184" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184"/>
       <c r="C184"/>
@@ -12093,7 +12093,7 @@
       <c r="H184"/>
       <c r="I184"/>
     </row>
-    <row r="185" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185"/>
       <c r="C185"/>
@@ -12104,7 +12104,7 @@
       <c r="H185"/>
       <c r="I185"/>
     </row>
-    <row r="186" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186"/>
       <c r="C186"/>
@@ -12115,7 +12115,7 @@
       <c r="H186"/>
       <c r="I186"/>
     </row>
-    <row r="187" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187"/>
       <c r="C187"/>
@@ -12126,7 +12126,7 @@
       <c r="H187"/>
       <c r="I187"/>
     </row>
-    <row r="188" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188"/>
       <c r="C188"/>
@@ -12137,7 +12137,7 @@
       <c r="H188"/>
       <c r="I188"/>
     </row>
-    <row r="189" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189"/>
       <c r="C189"/>
@@ -12148,7 +12148,7 @@
       <c r="H189"/>
       <c r="I189"/>
     </row>
-    <row r="190" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190"/>
       <c r="C190"/>
@@ -12159,7 +12159,7 @@
       <c r="H190"/>
       <c r="I190"/>
     </row>
-    <row r="191" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191"/>
       <c r="C191"/>
@@ -12170,7 +12170,7 @@
       <c r="H191"/>
       <c r="I191"/>
     </row>
-    <row r="192" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192"/>
       <c r="C192"/>
@@ -12181,7 +12181,7 @@
       <c r="H192"/>
       <c r="I192"/>
     </row>
-    <row r="193" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193"/>
       <c r="C193"/>
@@ -12192,7 +12192,7 @@
       <c r="H193"/>
       <c r="I193"/>
     </row>
-    <row r="194" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194"/>
       <c r="C194"/>
@@ -12203,7 +12203,7 @@
       <c r="H194"/>
       <c r="I194"/>
     </row>
-    <row r="195" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195"/>
       <c r="C195"/>
@@ -12214,7 +12214,7 @@
       <c r="H195"/>
       <c r="I195"/>
     </row>
-    <row r="196" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196"/>
       <c r="C196"/>
@@ -12225,7 +12225,7 @@
       <c r="H196"/>
       <c r="I196"/>
     </row>
-    <row r="197" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197"/>
       <c r="C197"/>
@@ -12236,7 +12236,7 @@
       <c r="H197"/>
       <c r="I197"/>
     </row>
-    <row r="198" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198"/>
       <c r="C198"/>
@@ -12247,7 +12247,7 @@
       <c r="H198"/>
       <c r="I198"/>
     </row>
-    <row r="199" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199"/>
       <c r="C199"/>
@@ -12258,7 +12258,7 @@
       <c r="H199"/>
       <c r="I199"/>
     </row>
-    <row r="200" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200"/>
       <c r="C200"/>
@@ -12269,7 +12269,7 @@
       <c r="H200"/>
       <c r="I200"/>
     </row>
-    <row r="201" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201"/>
       <c r="C201"/>
@@ -12280,7 +12280,7 @@
       <c r="H201"/>
       <c r="I201"/>
     </row>
-    <row r="202" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="B202"/>
       <c r="C202"/>
@@ -12291,7 +12291,7 @@
       <c r="H202"/>
       <c r="I202"/>
     </row>
-    <row r="203" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="B203"/>
       <c r="C203"/>
@@ -12302,7 +12302,7 @@
       <c r="H203"/>
       <c r="I203"/>
     </row>
-    <row r="204" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204"/>
       <c r="C204"/>
@@ -12313,7 +12313,7 @@
       <c r="H204"/>
       <c r="I204"/>
     </row>
-    <row r="205" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A205" s="1"/>
       <c r="B205"/>
       <c r="C205"/>
@@ -12324,7 +12324,7 @@
       <c r="H205"/>
       <c r="I205"/>
     </row>
-    <row r="206" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206"/>
       <c r="C206"/>
@@ -12335,7 +12335,7 @@
       <c r="H206"/>
       <c r="I206"/>
     </row>
-    <row r="207" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207"/>
       <c r="C207"/>
@@ -12346,7 +12346,7 @@
       <c r="H207"/>
       <c r="I207"/>
     </row>
-    <row r="208" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="B208"/>
       <c r="C208"/>
@@ -12357,7 +12357,7 @@
       <c r="H208"/>
       <c r="I208"/>
     </row>
-    <row r="209" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="B209"/>
       <c r="C209"/>
@@ -12368,7 +12368,7 @@
       <c r="H209"/>
       <c r="I209"/>
     </row>
-    <row r="210" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="B210"/>
       <c r="C210"/>
@@ -12379,7 +12379,7 @@
       <c r="H210"/>
       <c r="I210"/>
     </row>
-    <row r="211" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="B211"/>
       <c r="C211"/>
@@ -12390,7 +12390,7 @@
       <c r="H211"/>
       <c r="I211"/>
     </row>
-    <row r="212" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="B212"/>
       <c r="C212"/>
@@ -12401,7 +12401,7 @@
       <c r="H212"/>
       <c r="I212"/>
     </row>
-    <row r="213" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="B213"/>
       <c r="C213"/>
@@ -12412,7 +12412,7 @@
       <c r="H213"/>
       <c r="I213"/>
     </row>
-    <row r="214" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="B214"/>
       <c r="C214"/>
@@ -12423,7 +12423,7 @@
       <c r="H214"/>
       <c r="I214"/>
     </row>
-    <row r="215" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215"/>
       <c r="C215"/>
@@ -12434,7 +12434,7 @@
       <c r="H215"/>
       <c r="I215"/>
     </row>
-    <row r="216" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="B216"/>
       <c r="C216"/>
@@ -12445,7 +12445,7 @@
       <c r="H216"/>
       <c r="I216"/>
     </row>
-    <row r="217" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="B217"/>
       <c r="C217"/>
@@ -12456,7 +12456,7 @@
       <c r="H217"/>
       <c r="I217"/>
     </row>
-    <row r="218" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="B218"/>
       <c r="C218"/>
@@ -12467,7 +12467,7 @@
       <c r="H218"/>
       <c r="I218"/>
     </row>
-    <row r="219" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219"/>
       <c r="C219"/>
@@ -12478,7 +12478,7 @@
       <c r="H219"/>
       <c r="I219"/>
     </row>
-    <row r="220" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="B220"/>
       <c r="C220"/>
@@ -12489,7 +12489,7 @@
       <c r="H220"/>
       <c r="I220"/>
     </row>
-    <row r="221" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="B221"/>
       <c r="C221"/>
@@ -12500,7 +12500,7 @@
       <c r="H221"/>
       <c r="I221"/>
     </row>
-    <row r="222" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="B222"/>
       <c r="C222"/>
@@ -12511,7 +12511,7 @@
       <c r="H222"/>
       <c r="I222"/>
     </row>
-    <row r="223" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="B223"/>
       <c r="C223"/>
@@ -12522,7 +12522,7 @@
       <c r="H223"/>
       <c r="I223"/>
     </row>
-    <row r="224" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="B224"/>
       <c r="C224"/>
@@ -12533,7 +12533,7 @@
       <c r="H224"/>
       <c r="I224"/>
     </row>
-    <row r="225" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A225" s="1"/>
       <c r="B225"/>
       <c r="C225"/>
@@ -12544,7 +12544,7 @@
       <c r="H225"/>
       <c r="I225"/>
     </row>
-    <row r="226" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="B226"/>
       <c r="C226"/>
@@ -12555,7 +12555,7 @@
       <c r="H226"/>
       <c r="I226"/>
     </row>
-    <row r="227" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A227" s="1"/>
       <c r="B227"/>
       <c r="C227"/>
@@ -12566,7 +12566,7 @@
       <c r="H227"/>
       <c r="I227"/>
     </row>
-    <row r="228" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A228" s="1"/>
       <c r="B228"/>
       <c r="C228"/>
@@ -12577,7 +12577,7 @@
       <c r="H228"/>
       <c r="I228"/>
     </row>
-    <row r="229" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A229" s="1"/>
       <c r="B229"/>
       <c r="C229"/>
@@ -12588,7 +12588,7 @@
       <c r="H229"/>
       <c r="I229"/>
     </row>
-    <row r="230" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A230" s="1"/>
       <c r="B230"/>
       <c r="C230"/>
@@ -12599,7 +12599,7 @@
       <c r="H230"/>
       <c r="I230"/>
     </row>
-    <row r="231" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A231" s="1"/>
       <c r="B231"/>
       <c r="C231"/>
@@ -12610,7 +12610,7 @@
       <c r="H231"/>
       <c r="I231"/>
     </row>
-    <row r="232" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A232" s="1"/>
       <c r="B232"/>
       <c r="C232"/>
@@ -12621,7 +12621,7 @@
       <c r="H232"/>
       <c r="I232"/>
     </row>
-    <row r="233" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A233" s="1"/>
       <c r="B233"/>
       <c r="C233"/>
@@ -12632,7 +12632,7 @@
       <c r="H233"/>
       <c r="I233"/>
     </row>
-    <row r="234" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A234" s="1"/>
       <c r="B234"/>
       <c r="C234"/>
@@ -12643,7 +12643,7 @@
       <c r="H234"/>
       <c r="I234"/>
     </row>
-    <row r="235" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A235" s="1"/>
       <c r="B235"/>
       <c r="C235"/>
@@ -12654,7 +12654,7 @@
       <c r="H235"/>
       <c r="I235"/>
     </row>
-    <row r="236" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A236" s="1"/>
       <c r="B236"/>
       <c r="C236"/>
@@ -12665,7 +12665,7 @@
       <c r="H236"/>
       <c r="I236"/>
     </row>
-    <row r="237" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A237" s="1"/>
       <c r="B237"/>
       <c r="C237"/>
@@ -12676,7 +12676,7 @@
       <c r="H237"/>
       <c r="I237"/>
     </row>
-    <row r="238" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A238" s="1"/>
       <c r="B238"/>
       <c r="C238"/>
@@ -12687,7 +12687,7 @@
       <c r="H238"/>
       <c r="I238"/>
     </row>
-    <row r="239" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A239" s="1"/>
       <c r="B239"/>
       <c r="C239"/>
@@ -12698,7 +12698,7 @@
       <c r="H239"/>
       <c r="I239"/>
     </row>
-    <row r="240" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A240" s="1"/>
       <c r="B240"/>
       <c r="C240"/>
@@ -12709,7 +12709,7 @@
       <c r="H240"/>
       <c r="I240"/>
     </row>
-    <row r="241" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A241" s="1"/>
       <c r="B241"/>
       <c r="C241"/>
@@ -12720,7 +12720,7 @@
       <c r="H241"/>
       <c r="I241"/>
     </row>
-    <row r="242" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A242" s="1"/>
       <c r="B242"/>
       <c r="C242"/>
@@ -12731,7 +12731,7 @@
       <c r="H242"/>
       <c r="I242"/>
     </row>
-    <row r="243" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A243" s="1"/>
       <c r="B243"/>
       <c r="C243"/>
@@ -12742,7 +12742,7 @@
       <c r="H243"/>
       <c r="I243"/>
     </row>
-    <row r="244" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A244" s="1"/>
       <c r="B244"/>
       <c r="C244"/>
@@ -12753,7 +12753,7 @@
       <c r="H244"/>
       <c r="I244"/>
     </row>
-    <row r="245" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A245" s="1"/>
       <c r="B245"/>
       <c r="C245"/>
@@ -12764,7 +12764,7 @@
       <c r="H245"/>
       <c r="I245"/>
     </row>
-    <row r="246" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A246" s="1"/>
       <c r="B246"/>
       <c r="C246"/>
@@ -12775,7 +12775,7 @@
       <c r="H246"/>
       <c r="I246"/>
     </row>
-    <row r="247" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A247" s="1"/>
       <c r="B247"/>
       <c r="C247"/>
@@ -12786,7 +12786,7 @@
       <c r="H247"/>
       <c r="I247"/>
     </row>
-    <row r="248" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A248" s="1"/>
       <c r="B248"/>
       <c r="C248"/>
@@ -12797,7 +12797,7 @@
       <c r="H248"/>
       <c r="I248"/>
     </row>
-    <row r="249" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A249" s="1"/>
       <c r="B249"/>
       <c r="C249"/>
@@ -12808,7 +12808,7 @@
       <c r="H249"/>
       <c r="I249"/>
     </row>
-    <row r="250" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A250" s="1"/>
       <c r="B250"/>
       <c r="C250"/>
@@ -12819,7 +12819,7 @@
       <c r="H250"/>
       <c r="I250"/>
     </row>
-    <row r="251" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A251" s="1"/>
       <c r="B251"/>
       <c r="C251"/>
@@ -12830,7 +12830,7 @@
       <c r="H251"/>
       <c r="I251"/>
     </row>
-    <row r="252" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A252" s="1"/>
       <c r="B252"/>
       <c r="C252"/>
@@ -12841,7 +12841,7 @@
       <c r="H252"/>
       <c r="I252"/>
     </row>
-    <row r="253" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A253" s="1"/>
       <c r="B253"/>
       <c r="C253"/>
@@ -12852,7 +12852,7 @@
       <c r="H253"/>
       <c r="I253"/>
     </row>
-    <row r="254" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A254" s="1"/>
       <c r="B254"/>
       <c r="C254"/>
@@ -12863,7 +12863,7 @@
       <c r="H254"/>
       <c r="I254"/>
     </row>
-    <row r="255" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A255" s="1"/>
       <c r="B255"/>
       <c r="C255"/>
@@ -12874,7 +12874,7 @@
       <c r="H255"/>
       <c r="I255"/>
     </row>
-    <row r="256" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A256" s="1"/>
       <c r="B256"/>
       <c r="C256"/>
@@ -12885,7 +12885,7 @@
       <c r="H256"/>
       <c r="I256"/>
     </row>
-    <row r="257" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A257" s="1"/>
       <c r="B257"/>
       <c r="C257"/>
@@ -12896,7 +12896,7 @@
       <c r="H257"/>
       <c r="I257"/>
     </row>
-    <row r="258" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A258" s="1"/>
       <c r="B258"/>
       <c r="C258"/>
@@ -12907,7 +12907,7 @@
       <c r="H258"/>
       <c r="I258"/>
     </row>
-    <row r="259" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A259" s="1"/>
       <c r="B259"/>
       <c r="C259"/>
@@ -12918,7 +12918,7 @@
       <c r="H259"/>
       <c r="I259"/>
     </row>
-    <row r="260" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A260" s="1"/>
       <c r="B260"/>
       <c r="C260"/>
@@ -12929,7 +12929,7 @@
       <c r="H260"/>
       <c r="I260"/>
     </row>
-    <row r="261" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A261" s="1"/>
       <c r="B261"/>
       <c r="C261"/>
@@ -12940,7 +12940,7 @@
       <c r="H261"/>
       <c r="I261"/>
     </row>
-    <row r="262" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A262" s="1"/>
       <c r="B262"/>
       <c r="C262"/>
@@ -12951,7 +12951,7 @@
       <c r="H262"/>
       <c r="I262"/>
     </row>
-    <row r="263" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A263" s="1"/>
       <c r="B263"/>
       <c r="C263"/>
@@ -12962,7 +12962,7 @@
       <c r="H263"/>
       <c r="I263"/>
     </row>
-    <row r="264" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A264" s="1"/>
       <c r="B264"/>
       <c r="C264"/>
@@ -12973,7 +12973,7 @@
       <c r="H264"/>
       <c r="I264"/>
     </row>
-    <row r="265" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A265" s="1"/>
       <c r="B265"/>
       <c r="C265"/>
@@ -12984,7 +12984,7 @@
       <c r="H265"/>
       <c r="I265"/>
     </row>
-    <row r="266" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A266" s="1"/>
       <c r="B266"/>
       <c r="C266"/>
@@ -12995,7 +12995,7 @@
       <c r="H266"/>
       <c r="I266"/>
     </row>
-    <row r="267" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A267" s="1"/>
       <c r="B267"/>
       <c r="C267"/>
@@ -13006,7 +13006,7 @@
       <c r="H267"/>
       <c r="I267"/>
     </row>
-    <row r="268" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A268" s="1"/>
       <c r="B268"/>
       <c r="C268"/>
@@ -13017,7 +13017,7 @@
       <c r="H268"/>
       <c r="I268"/>
     </row>
-    <row r="269" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A269" s="1"/>
       <c r="B269"/>
       <c r="C269"/>
@@ -13028,7 +13028,7 @@
       <c r="H269"/>
       <c r="I269"/>
     </row>
-    <row r="270" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A270" s="1"/>
       <c r="B270"/>
       <c r="C270"/>
@@ -13039,7 +13039,7 @@
       <c r="H270"/>
       <c r="I270"/>
     </row>
-    <row r="271" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A271" s="1"/>
       <c r="B271"/>
       <c r="C271"/>
@@ -13050,7 +13050,7 @@
       <c r="H271"/>
       <c r="I271"/>
     </row>
-    <row r="272" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A272" s="1"/>
       <c r="B272"/>
       <c r="C272"/>
@@ -13061,7 +13061,7 @@
       <c r="H272"/>
       <c r="I272"/>
     </row>
-    <row r="273" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A273" s="1"/>
       <c r="B273"/>
       <c r="C273"/>
@@ -13072,7 +13072,7 @@
       <c r="H273"/>
       <c r="I273"/>
     </row>
-    <row r="274" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A274" s="1"/>
       <c r="B274"/>
       <c r="C274"/>
@@ -13083,7 +13083,7 @@
       <c r="H274"/>
       <c r="I274"/>
     </row>
-    <row r="275" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A275" s="1"/>
       <c r="B275"/>
       <c r="C275"/>
@@ -13094,7 +13094,7 @@
       <c r="H275"/>
       <c r="I275"/>
     </row>
-    <row r="276" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A276" s="1"/>
       <c r="B276"/>
       <c r="C276"/>
@@ -13105,7 +13105,7 @@
       <c r="H276"/>
       <c r="I276"/>
     </row>
-    <row r="277" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A277" s="1"/>
       <c r="B277"/>
       <c r="C277"/>
@@ -13116,7 +13116,7 @@
       <c r="H277"/>
       <c r="I277"/>
     </row>
-    <row r="278" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A278" s="1"/>
       <c r="B278"/>
       <c r="C278"/>
@@ -13127,7 +13127,7 @@
       <c r="H278"/>
       <c r="I278"/>
     </row>
-    <row r="279" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A279" s="1"/>
       <c r="B279"/>
       <c r="C279"/>
@@ -13138,7 +13138,7 @@
       <c r="H279"/>
       <c r="I279"/>
     </row>
-    <row r="280" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A280" s="1"/>
       <c r="B280"/>
       <c r="C280"/>
@@ -13149,7 +13149,7 @@
       <c r="H280"/>
       <c r="I280"/>
     </row>
-    <row r="281" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A281" s="1"/>
       <c r="B281"/>
       <c r="C281"/>
@@ -13160,7 +13160,7 @@
       <c r="H281"/>
       <c r="I281"/>
     </row>
-    <row r="282" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A282" s="1"/>
       <c r="B282"/>
       <c r="C282"/>
@@ -13171,7 +13171,7 @@
       <c r="H282"/>
       <c r="I282"/>
     </row>
-    <row r="283" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A283" s="1"/>
       <c r="B283"/>
       <c r="C283"/>
@@ -13182,7 +13182,7 @@
       <c r="H283"/>
       <c r="I283"/>
     </row>
-    <row r="284" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A284" s="1"/>
       <c r="B284"/>
       <c r="C284"/>
@@ -13193,7 +13193,7 @@
       <c r="H284"/>
       <c r="I284"/>
     </row>
-    <row r="285" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A285" s="1"/>
       <c r="B285"/>
       <c r="C285"/>
@@ -13204,7 +13204,7 @@
       <c r="H285"/>
       <c r="I285"/>
     </row>
-    <row r="286" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A286" s="1"/>
       <c r="B286"/>
       <c r="C286"/>
@@ -13215,7 +13215,7 @@
       <c r="H286"/>
       <c r="I286"/>
     </row>
-    <row r="287" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A287" s="1"/>
       <c r="B287"/>
       <c r="C287"/>
@@ -13226,7 +13226,7 @@
       <c r="H287"/>
       <c r="I287"/>
     </row>
-    <row r="288" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A288" s="1"/>
       <c r="B288"/>
       <c r="C288"/>
@@ -13237,7 +13237,7 @@
       <c r="H288"/>
       <c r="I288"/>
     </row>
-    <row r="289" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A289" s="1"/>
       <c r="B289"/>
       <c r="C289"/>
@@ -13248,7 +13248,7 @@
       <c r="H289"/>
       <c r="I289"/>
     </row>
-    <row r="290" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A290" s="1"/>
       <c r="B290"/>
       <c r="C290"/>
@@ -13259,7 +13259,7 @@
       <c r="H290"/>
       <c r="I290"/>
     </row>
-    <row r="291" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A291" s="1"/>
       <c r="B291"/>
       <c r="C291"/>
@@ -13270,7 +13270,7 @@
       <c r="H291"/>
       <c r="I291"/>
     </row>
-    <row r="292" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A292" s="1"/>
       <c r="B292"/>
       <c r="C292"/>
@@ -13281,7 +13281,7 @@
       <c r="H292"/>
       <c r="I292"/>
     </row>
-    <row r="293" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A293" s="1"/>
       <c r="B293"/>
       <c r="C293"/>
@@ -13292,7 +13292,7 @@
       <c r="H293"/>
       <c r="I293"/>
     </row>
-    <row r="294" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A294" s="1"/>
       <c r="B294"/>
       <c r="C294"/>
@@ -13303,7 +13303,7 @@
       <c r="H294"/>
       <c r="I294"/>
     </row>
-    <row r="295" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A295" s="1"/>
       <c r="B295"/>
       <c r="C295"/>
@@ -13314,7 +13314,7 @@
       <c r="H295"/>
       <c r="I295"/>
     </row>
-    <row r="296" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A296" s="1"/>
       <c r="B296"/>
       <c r="C296"/>
@@ -13325,7 +13325,7 @@
       <c r="H296"/>
       <c r="I296"/>
     </row>
-    <row r="297" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A297" s="1"/>
       <c r="B297"/>
       <c r="C297"/>
@@ -13336,7 +13336,7 @@
       <c r="H297"/>
       <c r="I297"/>
     </row>
-    <row r="298" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A298" s="1"/>
       <c r="B298"/>
       <c r="C298"/>
@@ -13347,7 +13347,7 @@
       <c r="H298"/>
       <c r="I298"/>
     </row>
-    <row r="299" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A299" s="1"/>
       <c r="B299"/>
       <c r="C299"/>
@@ -13358,7 +13358,7 @@
       <c r="H299"/>
       <c r="I299"/>
     </row>
-    <row r="300" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A300" s="1"/>
       <c r="B300"/>
       <c r="C300"/>
@@ -13369,7 +13369,7 @@
       <c r="H300"/>
       <c r="I300"/>
     </row>
-    <row r="301" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A301" s="1"/>
       <c r="B301"/>
       <c r="C301"/>
@@ -13380,7 +13380,7 @@
       <c r="H301"/>
       <c r="I301"/>
     </row>
-    <row r="302" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A302" s="1"/>
       <c r="B302"/>
       <c r="C302"/>
@@ -13391,7 +13391,7 @@
       <c r="H302"/>
       <c r="I302"/>
     </row>
-    <row r="303" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A303" s="1"/>
       <c r="B303"/>
       <c r="C303"/>
@@ -13402,7 +13402,7 @@
       <c r="H303"/>
       <c r="I303"/>
     </row>
-    <row r="304" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A304" s="1"/>
       <c r="B304"/>
       <c r="C304"/>
@@ -13413,7 +13413,7 @@
       <c r="H304"/>
       <c r="I304"/>
     </row>
-    <row r="305" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A305" s="1"/>
       <c r="B305"/>
       <c r="C305"/>
@@ -13424,7 +13424,7 @@
       <c r="H305"/>
       <c r="I305"/>
     </row>
-    <row r="306" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A306" s="1"/>
       <c r="B306"/>
       <c r="C306"/>
@@ -13435,7 +13435,7 @@
       <c r="H306"/>
       <c r="I306"/>
     </row>
-    <row r="307" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A307" s="1"/>
       <c r="B307"/>
       <c r="C307"/>
@@ -13446,7 +13446,7 @@
       <c r="H307"/>
       <c r="I307"/>
     </row>
-    <row r="308" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A308" s="1"/>
       <c r="B308"/>
       <c r="C308"/>
@@ -13457,7 +13457,7 @@
       <c r="H308"/>
       <c r="I308"/>
     </row>
-    <row r="309" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A309" s="1"/>
       <c r="B309"/>
       <c r="C309"/>
@@ -13468,7 +13468,7 @@
       <c r="H309"/>
       <c r="I309"/>
     </row>
-    <row r="310" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A310" s="1"/>
       <c r="B310"/>
       <c r="C310"/>
@@ -13479,7 +13479,7 @@
       <c r="H310"/>
       <c r="I310"/>
     </row>
-    <row r="311" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
       <c r="B311"/>
       <c r="C311"/>
@@ -13490,7 +13490,7 @@
       <c r="H311"/>
       <c r="I311"/>
     </row>
-    <row r="312" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A312" s="1"/>
       <c r="B312"/>
       <c r="C312"/>
@@ -13501,7 +13501,7 @@
       <c r="H312"/>
       <c r="I312"/>
     </row>
-    <row r="313" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>
       <c r="B313"/>
       <c r="C313"/>
@@ -13512,7 +13512,7 @@
       <c r="H313"/>
       <c r="I313"/>
     </row>
-    <row r="314" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
       <c r="B314"/>
       <c r="C314"/>
@@ -13523,7 +13523,7 @@
       <c r="H314"/>
       <c r="I314"/>
     </row>
-    <row r="315" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A315" s="1"/>
       <c r="B315"/>
       <c r="C315"/>
@@ -13534,7 +13534,7 @@
       <c r="H315"/>
       <c r="I315"/>
     </row>
-    <row r="316" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>
       <c r="B316"/>
       <c r="C316"/>
@@ -13545,7 +13545,7 @@
       <c r="H316"/>
       <c r="I316"/>
     </row>
-    <row r="317" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A317" s="1"/>
       <c r="B317"/>
       <c r="C317"/>
@@ -13556,7 +13556,7 @@
       <c r="H317"/>
       <c r="I317"/>
     </row>
-    <row r="318" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
       <c r="B318"/>
       <c r="C318"/>
@@ -13567,7 +13567,7 @@
       <c r="H318"/>
       <c r="I318"/>
     </row>
-    <row r="319" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
       <c r="B319"/>
       <c r="C319"/>
@@ -13578,7 +13578,7 @@
       <c r="H319"/>
       <c r="I319"/>
     </row>
-    <row r="320" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
       <c r="B320"/>
       <c r="C320"/>
@@ -13589,7 +13589,7 @@
       <c r="H320"/>
       <c r="I320"/>
     </row>
-    <row r="321" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A321" s="1"/>
       <c r="B321"/>
       <c r="C321"/>
@@ -13600,7 +13600,7 @@
       <c r="H321"/>
       <c r="I321"/>
     </row>
-    <row r="322" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
       <c r="B322"/>
       <c r="C322"/>
@@ -13611,7 +13611,7 @@
       <c r="H322"/>
       <c r="I322"/>
     </row>
-    <row r="323" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
       <c r="B323"/>
       <c r="C323"/>
@@ -13622,7 +13622,7 @@
       <c r="H323"/>
       <c r="I323"/>
     </row>
-    <row r="324" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
       <c r="B324"/>
       <c r="C324"/>
@@ -13633,7 +13633,7 @@
       <c r="H324"/>
       <c r="I324"/>
     </row>
-    <row r="325" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
       <c r="B325"/>
       <c r="C325"/>
@@ -13644,7 +13644,7 @@
       <c r="H325"/>
       <c r="I325"/>
     </row>
-    <row r="326" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
       <c r="B326"/>
       <c r="C326"/>
@@ -13655,7 +13655,7 @@
       <c r="H326"/>
       <c r="I326"/>
     </row>
-    <row r="327" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
       <c r="B327"/>
       <c r="C327"/>
@@ -13666,7 +13666,7 @@
       <c r="H327"/>
       <c r="I327"/>
     </row>
-    <row r="328" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
       <c r="B328"/>
       <c r="C328"/>
@@ -13677,7 +13677,7 @@
       <c r="H328"/>
       <c r="I328"/>
     </row>
-    <row r="329" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
       <c r="B329"/>
       <c r="C329"/>
@@ -13688,7 +13688,7 @@
       <c r="H329"/>
       <c r="I329"/>
     </row>
-    <row r="330" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
       <c r="B330"/>
       <c r="C330"/>
@@ -13699,7 +13699,7 @@
       <c r="H330"/>
       <c r="I330"/>
     </row>
-    <row r="331" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
       <c r="B331"/>
       <c r="C331"/>
@@ -13710,7 +13710,7 @@
       <c r="H331"/>
       <c r="I331"/>
     </row>
-    <row r="332" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>
       <c r="B332"/>
       <c r="C332"/>
@@ -13721,7 +13721,7 @@
       <c r="H332"/>
       <c r="I332"/>
     </row>
-    <row r="333" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A333" s="1"/>
       <c r="B333"/>
       <c r="C333"/>
@@ -13732,7 +13732,7 @@
       <c r="H333"/>
       <c r="I333"/>
     </row>
-    <row r="334" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A334" s="1"/>
       <c r="B334"/>
       <c r="C334"/>
@@ -13743,7 +13743,7 @@
       <c r="H334"/>
       <c r="I334"/>
     </row>
-    <row r="335" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A335" s="1"/>
       <c r="B335"/>
       <c r="C335"/>
@@ -13754,7 +13754,7 @@
       <c r="H335"/>
       <c r="I335"/>
     </row>
-    <row r="336" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A336" s="1"/>
       <c r="B336"/>
       <c r="C336"/>
@@ -13765,7 +13765,7 @@
       <c r="H336"/>
       <c r="I336"/>
     </row>
-    <row r="337" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A337" s="1"/>
       <c r="B337"/>
       <c r="C337"/>
@@ -13776,7 +13776,7 @@
       <c r="H337"/>
       <c r="I337"/>
     </row>
-    <row r="338" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A338" s="1"/>
       <c r="B338"/>
       <c r="C338"/>
@@ -13787,7 +13787,7 @@
       <c r="H338"/>
       <c r="I338"/>
     </row>
-    <row r="339" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A339" s="1"/>
       <c r="B339"/>
       <c r="C339"/>
@@ -13798,7 +13798,7 @@
       <c r="H339"/>
       <c r="I339"/>
     </row>
-    <row r="340" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A340" s="1"/>
       <c r="B340"/>
       <c r="C340"/>
@@ -13809,7 +13809,7 @@
       <c r="H340"/>
       <c r="I340"/>
     </row>
-    <row r="341" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A341" s="1"/>
       <c r="B341"/>
       <c r="C341"/>
@@ -13820,7 +13820,7 @@
       <c r="H341"/>
       <c r="I341"/>
     </row>
-    <row r="342" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A342" s="1"/>
       <c r="B342"/>
       <c r="C342"/>
@@ -13831,7 +13831,7 @@
       <c r="H342"/>
       <c r="I342"/>
     </row>
-    <row r="343" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A343" s="1"/>
       <c r="B343"/>
       <c r="C343"/>
@@ -13842,7 +13842,7 @@
       <c r="H343"/>
       <c r="I343"/>
     </row>
-    <row r="344" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A344" s="1"/>
       <c r="B344"/>
       <c r="C344"/>
@@ -13853,7 +13853,7 @@
       <c r="H344"/>
       <c r="I344"/>
     </row>
-    <row r="345" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A345" s="1"/>
       <c r="B345"/>
       <c r="C345"/>
@@ -13864,7 +13864,7 @@
       <c r="H345"/>
       <c r="I345"/>
     </row>
-    <row r="346" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A346" s="1"/>
       <c r="B346"/>
       <c r="C346"/>
@@ -13875,7 +13875,7 @@
       <c r="H346"/>
       <c r="I346"/>
     </row>
-    <row r="347" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A347" s="1"/>
       <c r="B347"/>
       <c r="C347"/>
@@ -13886,7 +13886,7 @@
       <c r="H347"/>
       <c r="I347"/>
     </row>
-    <row r="348" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A348" s="1"/>
       <c r="B348"/>
       <c r="C348"/>
@@ -13897,7 +13897,7 @@
       <c r="H348"/>
       <c r="I348"/>
     </row>
-    <row r="349" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A349" s="1"/>
       <c r="B349"/>
       <c r="C349"/>
@@ -13908,7 +13908,7 @@
       <c r="H349"/>
       <c r="I349"/>
     </row>
-    <row r="350" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A350" s="1"/>
       <c r="B350"/>
       <c r="C350"/>
@@ -13919,7 +13919,7 @@
       <c r="H350"/>
       <c r="I350"/>
     </row>
-    <row r="351" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A351" s="1"/>
       <c r="B351"/>
       <c r="C351"/>
@@ -13930,7 +13930,7 @@
       <c r="H351"/>
       <c r="I351"/>
     </row>
-    <row r="352" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A352" s="1"/>
       <c r="B352"/>
       <c r="C352"/>
@@ -13941,7 +13941,7 @@
       <c r="H352"/>
       <c r="I352"/>
     </row>
-    <row r="353" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A353" s="1"/>
       <c r="B353"/>
       <c r="C353"/>
@@ -13952,7 +13952,7 @@
       <c r="H353"/>
       <c r="I353"/>
     </row>
-    <row r="354" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A354" s="1"/>
       <c r="B354"/>
       <c r="C354"/>
@@ -13963,7 +13963,7 @@
       <c r="H354"/>
       <c r="I354"/>
     </row>
-    <row r="355" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A355" s="1"/>
       <c r="B355"/>
       <c r="C355"/>
@@ -13974,7 +13974,7 @@
       <c r="H355"/>
       <c r="I355"/>
     </row>
-    <row r="356" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A356" s="1"/>
       <c r="B356"/>
       <c r="C356"/>
@@ -13985,7 +13985,7 @@
       <c r="H356"/>
       <c r="I356"/>
     </row>
-    <row r="357" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A357" s="1"/>
       <c r="B357"/>
       <c r="C357"/>
@@ -13996,7 +13996,7 @@
       <c r="H357"/>
       <c r="I357"/>
     </row>
-    <row r="358" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A358" s="1"/>
       <c r="B358"/>
       <c r="C358"/>
@@ -14007,7 +14007,7 @@
       <c r="H358"/>
       <c r="I358"/>
     </row>
-    <row r="359" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A359" s="1"/>
       <c r="B359"/>
       <c r="C359"/>
@@ -14018,7 +14018,7 @@
       <c r="H359"/>
       <c r="I359"/>
     </row>
-    <row r="360" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A360" s="1"/>
       <c r="B360"/>
       <c r="C360"/>
@@ -14029,7 +14029,7 @@
       <c r="H360"/>
       <c r="I360"/>
     </row>
-    <row r="361" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A361" s="1"/>
       <c r="B361"/>
       <c r="C361"/>
@@ -14040,7 +14040,7 @@
       <c r="H361"/>
       <c r="I361"/>
     </row>
-    <row r="362" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A362" s="1"/>
       <c r="B362"/>
       <c r="C362"/>
@@ -14051,7 +14051,7 @@
       <c r="H362"/>
       <c r="I362"/>
     </row>
-    <row r="363" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A363" s="1"/>
       <c r="B363"/>
       <c r="C363"/>
@@ -14062,7 +14062,7 @@
       <c r="H363"/>
       <c r="I363"/>
     </row>
-    <row r="364" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A364" s="1"/>
       <c r="B364"/>
       <c r="C364"/>
@@ -14073,7 +14073,7 @@
       <c r="H364"/>
       <c r="I364"/>
     </row>
-    <row r="365" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A365" s="1"/>
       <c r="B365"/>
       <c r="C365"/>
@@ -14084,7 +14084,7 @@
       <c r="H365"/>
       <c r="I365"/>
     </row>
-    <row r="366" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A366" s="1"/>
       <c r="B366"/>
       <c r="C366"/>
@@ -14095,7 +14095,7 @@
       <c r="H366"/>
       <c r="I366"/>
     </row>
-    <row r="367" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A367" s="1"/>
       <c r="B367"/>
       <c r="C367"/>
@@ -14106,7 +14106,7 @@
       <c r="H367"/>
       <c r="I367"/>
     </row>
-    <row r="368" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A368" s="1"/>
       <c r="B368"/>
       <c r="C368"/>
@@ -14187,23 +14187,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D4DBD61-A264-4E77-BA12-BABDDFA736C5}">
   <dimension ref="A1:M85"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" customWidth="1"/>
-    <col min="3" max="4" width="13.109375" customWidth="1"/>
-    <col min="5" max="5" width="26.88671875" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" customWidth="1"/>
-    <col min="7" max="7" width="66.5546875" customWidth="1"/>
-    <col min="8" max="8" width="6.33203125" customWidth="1"/>
-    <col min="9" max="9" width="16.33203125" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" customWidth="1"/>
-    <col min="11" max="11" width="34.6640625" customWidth="1"/>
-    <col min="12" max="12" width="16.6640625" customWidth="1"/>
-    <col min="13" max="13" width="98.33203125" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="3" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="26.85546875" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="7" max="7" width="66.5703125" customWidth="1"/>
+    <col min="8" max="8" width="6.28515625" customWidth="1"/>
+    <col min="9" max="9" width="16.28515625" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" customWidth="1"/>
+    <col min="11" max="11" width="34.7109375" customWidth="1"/>
+    <col min="12" max="12" width="16.7109375" customWidth="1"/>
+    <col min="13" max="13" width="98.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>173</v>
       </c>
@@ -14244,7 +14244,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -14283,7 +14283,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('1','1','LRI Head Office','8 Steelcase Road West, Markham, ON, L3R 1B2','--','--','T: (905) 474-0590','--','Office Header');</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -14325,7 +14325,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('2','1','Stephen Wong','Chairman','500','---','(905) 752-3500','stephenwong@livinggroupinc.com','Staff');</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -14367,7 +14367,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('3','1','William Lau','President','511','(647) 918-9886','(905) 752-3511','williamlau@livinggroupinc.com','Staff');</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -14409,7 +14409,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('4','1','Kelvin Wong','Broker of Record, Operating Principal','228','(416) 567-7882','---','kelvin@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -14451,7 +14451,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('5','1','Ben Wong','President &amp; C.L.O.','521','(416) 399-2311','(905) 752-3521','benwong@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -14493,7 +14493,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('6','1','David Wong','Vice President','165','(416) 230-8866','(905) 752-3176','davidwong@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -14535,7 +14535,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('7','1','Peter Woo','Broker of Record, Living Realty','502','(416) 569-6569','(905) 752-3502','pwoo@livinggroupinc.com','Staff');</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -14577,7 +14577,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('8','1','Alan Cheung','Vice Presidnet, New Homes, Broker','---','(416) 669-0325','---','alancheung@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -14619,7 +14619,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('9','1','Andrew Chiang','Education and Training Co-ordinator','---','(647) 704-2388','---','andrewchiang@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -14661,7 +14661,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('10','1','Rocky Chow','Executive Assistant to Chairman','509','(647) 818-1818','---','rockychow@livinggroupinc.com','Staff');</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -14700,7 +14700,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('11','1','Eddie Tang','Market Center Administrator, Executive Group Controller','504','(416) 723-8329','(905) 752-3504','eddietang@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -14742,7 +14742,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('12','1','Winnie Tsui','Senior Manager, Accounting &amp; Operations','514','(647) 286-0145','(905) 752-3514','winniet@livingproperties.com','Staff');</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -14784,7 +14784,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('13','1','Dan Flomen','Team Leader','224','---','(905) 489-8989','dan@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -14826,7 +14826,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('14','1','Wendy Chung','Administration Officer ','123','---','---','wendychung@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -14868,7 +14868,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('15','1','Benjamin Wong','Assistant to the Broker of Record','206','---','---','benjaminwongici@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -14910,7 +14910,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('16','1','Luvie Chao','Senior Deal Administrator','507','---','(905) 752-3507','luvie@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -14952,7 +14952,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('17','1','Maria Leung','Deal Administrator','508','---','(905) 752-3508','marialeung@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -14994,7 +14994,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('18','1','Ken Cheung','Deal Administrator','255','---','---','kencheung@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -15036,7 +15036,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('19','1','Connie Cheung','Accounting Bookkeeper','506','---','(905) 752-3506','conniecheung@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -15078,7 +15078,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('20','1','Simon Chan','Operations Assistant','519','---','(905) 752-3519','simonchan@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -15120,7 +15120,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('21','1','Ben Dowson','Digitial Marketing &amp; Web Developer','---','---','---','socialmedia@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -15162,7 +15162,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('22','1','Kelly Wan','Digital Artist &amp; Content Creator ','121','---','---','kellywan@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -15204,7 +15204,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('23','1','Nelson Lau','Senior Technical Specialist','522','(647) 701-8828','(905) 752-3522','nelsonlau@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -15243,7 +15243,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('24','1','IT Support','Information Technology Technical Support','522','---','(905) 752-3522','itsupport@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -15285,7 +15285,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('25','2','North Markham Office','735 Markland St, Unit 12&amp;13, Markham, ON, L6C 0G6','--','--','T: (905) 888-8188','northmarkham@livingrealtykw.com','Office Header');</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -15327,7 +15327,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('26','2','Chris Tam','Manager North Markham Branch','---','(416) 505-6625','---','christam@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -15369,7 +15369,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('27','2','Grace Chui','Head Secretary','---','---','(905) 888-8188','gracemschui@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -15411,7 +15411,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('28','2','Kiran Li','Secretary','---','---','(905) 888-8188','kiranli@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -15453,7 +15453,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('29','4','Mississauga Office','1177 Central Parkway West, Golden Square, Unit 32, Mississauga, ON, L5C 4P3','--','--','T: (905) 896-0002','mississauga@livingrealtykw.com','Office Header');</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>30</v>
       </c>
@@ -15495,7 +15495,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('30','4','Hui Wang','Manager Mississauga Branch','---','(416) 274-9789','---','huiwang@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>31</v>
       </c>
@@ -15537,7 +15537,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('31','4','Vasanthan Jeyapragasam','Secretary','---','---','(905) 896-0002','vasanthanj@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -15579,7 +15579,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('32','4','Katie Wong','Secretary','---','---','(905) 896-0002','katiewong@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>33</v>
       </c>
@@ -15621,7 +15621,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('33','5','Woodbine Office','8 Steelcase Road West, Markham, ON, L3R 1B2','--','--','T: (905) 474-0500','woodbine@livingrealtykw.com','Office Header');</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>34</v>
       </c>
@@ -15663,7 +15663,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('34','5','Anita Huang','Manager Woobine Branch','176','(416) 523-1888','---','anitahuang@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>35</v>
       </c>
@@ -15705,7 +15705,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('35','5','Jimmy Lo','Secretary','104','---','(905) 474-0500','jimmylo@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -15747,7 +15747,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('36','5','Savanna Joo','Secretary','100','---','(905) 474-0500','savannajoo@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>37</v>
       </c>
@@ -15789,7 +15789,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('37','3','Yonge &amp; Eglinton Office','2301 Yonge Street, Toronto, ON, M4P 2C6','--','--','T: (416) 223-8833','ye@livingrealtykw.com','Office Header');</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>38</v>
       </c>
@@ -15831,7 +15831,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('38','3','Tony Prochilo ','Manager Yonge &amp; Eglinton','---','(416) 576-6312','---','tonyprochilo@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>39</v>
       </c>
@@ -15873,7 +15873,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('39','3','Lydia Ng','Secretary','---','---','(416) 223-8833','lydiang@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>40</v>
       </c>
@@ -15912,7 +15912,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('40','7','I.C.&amp;I. Office','8 Steelcase Road West, Unit C, Markham, ON, L3R 1B2','--','--','T: (905) 474-1772','--','Office Header');</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>41</v>
       </c>
@@ -15954,7 +15954,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('41','7','Kelvin Wong','Manager I.C.&amp;I. Branch','228','(416) 567-7882','---','kelvin@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>42</v>
       </c>
@@ -15993,7 +15993,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('42','8','LPI Head Office','8 Steelcase Road West, Markham, ON, L3R 1B2','--','--','T: (905) 477-2090','--','Office Header');</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>43</v>
       </c>
@@ -16032,7 +16032,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('43','8','Ben Wong','President','521','(416) 399-2311','(905) 752-3521','benw@livingproperties.com','Staff');</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -16071,7 +16071,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('44','8','Winnie Tsui','Director of Operations','514','(647) 286-0145','(905) 752-3514 ','winniet@livingproperties.com','Staff');</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>45</v>
       </c>
@@ -16110,7 +16110,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('45','8','Frederick Tang','Director of Business Development','286','(416) 618-5898','-','fredt@livingproperties.com','Staff');</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>46</v>
       </c>
@@ -16149,7 +16149,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('46','8','Karl Park','Senior Property Manager','516','(647) 286-0142','(905) 752-3516','karlp@livingproperties.com','Staff');</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>47</v>
       </c>
@@ -16188,7 +16188,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('47','8','Stanley Chow','Property Manager','512','(416) 277-6098','(905) 752-3512','stanleyc@livingproperties.com','Staff');</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>48</v>
       </c>
@@ -16227,7 +16227,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('48','8','Richard Baksh','Property Manager','284','(647) 967-0088','(905) 258-0632','richardb@livingproperties.com','Staff');</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>49</v>
       </c>
@@ -16247,7 +16247,7 @@
         <v>93</v>
       </c>
       <c r="H50" s="6">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="I50" s="6" t="s">
         <v>222</v>
@@ -16263,10 +16263,10 @@
       </c>
       <c r="M50" t="str">
         <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A50 &amp; "','" &amp; D50 &amp; "','" &amp; E50 &amp; "','" &amp; G50 &amp; "','" &amp; H50 &amp; "','" &amp; I50 &amp;  "','" &amp; J50 &amp;  "','" &amp; K50 &amp;  "','" &amp; L50 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('49','8','Ken Kam','Property Manager','527','(647) 204-4455','(905) 477-2090','kenk@livingproperties.com','Staff');</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('49','8','Ken Kam','Property Manager','517','(647) 204-4455','(905) 477-2090','kenk@livingproperties.com','Staff');</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -16305,7 +16305,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('50','8','Raymond Chin','Property Manager','520','(437) 331-6038','(905) 477-2090','raymondc@livingproperties.com','Staff');</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -16344,7 +16344,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('51','8','Thomas Lee','Assistant Property Manager','168','(416) 567-4274','(905) 477-2090','Thomasl@livingproperties.com','Staff');</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>52</v>
       </c>
@@ -16383,7 +16383,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('52','8','Loretta Leung','Executive Assistant','210','---','---','lorettal@livingproperties.com','Staff');</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>53</v>
       </c>
@@ -16422,7 +16422,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('53','8','Simon Li','Senior Accountant','518','---','(905) 752-3518','simonl@livingproperties.com','Staff');</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>54</v>
       </c>
@@ -16461,7 +16461,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('54','8','Nicole Leung','Property Accountant','281','---','---','nicolel@livingproperties.com','Staff');</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>55</v>
       </c>
@@ -16500,7 +16500,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('55','8','Vivian Lum','Accounts Receivable Clerk','523','---','(905) 752-3523','vivianl@livingproperties.com','Staff');</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <v>56</v>
       </c>
@@ -16539,7 +16539,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('56','8','Jessica Lee','Accounting Clerk ','223','---','---','jessical@livingproperties.com','Staff');</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>57</v>
       </c>
@@ -16578,7 +16578,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('57','8','Rebecca Lau','Administrative Assistant','172','---','---','rebeccal@livingproperties.com','Staff');</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>58</v>
       </c>
@@ -16617,7 +16617,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('58','8','Kelvin Chan','Administrative Assistant','182','---','---','kelvinc@livingproperties.com','Staff');</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>59</v>
       </c>
@@ -16656,7 +16656,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('59','8','Calmaine Hewitt','Handyman','---','---','(905) 477-2090','calmaineh@livingproperties.com','Staff');</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>60</v>
       </c>
@@ -16695,7 +16695,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('60','8','Matthew Wong','Accounting Clerk','229','---','---','mattheww@livingproperties.com','Staff');</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -16734,7 +16734,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('61','9','Centro Towers Office','25 Town Centre Crt, Scarborough, ON, M1P 0B4','--','--','T: (416) 290-1242','--','Office Header');</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <v>62</v>
       </c>
@@ -16773,7 +16773,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('62','9','Henry Fu','Property Manager','---','(416) 278-2953','(416) 290-1242','henry@centrotowers.com','Staff');</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>63</v>
       </c>
@@ -16812,7 +16812,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('63','9','Sophia Yip','Property Administrator','---','---','(416) 290-1242','sophia@centrotowers.com','Staff');</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>64</v>
       </c>
@@ -16848,7 +16848,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('64','9','Security Desk ','Centro Security Desk ','---','---','(416) 296-0099','---','');</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>65</v>
       </c>
@@ -16887,7 +16887,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('65','11','EQ1 Office','70 Town Centre Court, Scarborough, ON, M1P 0B2','--','--','T: (416) 279-0603 ','eq1@livingproperties.com','Office Header');</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <v>66</v>
       </c>
@@ -16926,7 +16926,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('66','11','Ming Ip','Property Manager','---','(647) 286-0147','(416) 279-0603 ','eq1manager@livingproperties.com','Staff');</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <v>67</v>
       </c>
@@ -16962,7 +16962,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('67','11','Security Desk ','EQ1 Security Desk ','---','---','(416) 279-1894','---','');</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <v>68</v>
       </c>
@@ -17001,7 +17001,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('68','12','EQ2 Office','60 Town Centre Court, Scarborough, ON, M1P 0B1','--','--','T: (416) 279-0591 ','--','Office Header');</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>69</v>
       </c>
@@ -17040,7 +17040,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('69','12','Aaron Ma','Property Manager','---','(416) 684-2236','(416) 279-0591','eq2manager@livingproperties.com','Staff');</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <v>70</v>
       </c>
@@ -17076,7 +17076,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('70','12','Security Desk ','EQ2 Security Desk ','---','---','(416) 279-1211','---','');</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>71</v>
       </c>
@@ -17115,7 +17115,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('71','13','Alton Tower Office','160 Alton Towers Cir, Toronto, ON, M1V 4X8','--','--','T: (437)-533-1208','--','Office Header');</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <v>72</v>
       </c>
@@ -17154,7 +17154,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('72','13','Ken Kam','Property Manager','---','(647) 204-4455','(905) 477-2090','kenk@livingproperties.com','Staff');</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <v>73</v>
       </c>
@@ -17193,7 +17193,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('73','13','Christie Ip','Administrative Assistant','---','(437)-533-1208','---','optima2@livingproperties.com ','Staff');</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <v>74</v>
       </c>
@@ -17232,7 +17232,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('74','13','Security Desk ','Alton Tower Security Desk ','---','---','(416) 754-3131','---','Staff');</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>75</v>
       </c>
@@ -17271,7 +17271,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('75','14','IHMG Office','8 Steelcase Road West, Markham, ON, L3R 1B2','--','--','T: (905) 475-6000','info@ihmg.ca','Office Header');</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
         <v>76</v>
       </c>
@@ -17310,7 +17310,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('76','14','IHMGRI Office','8 Steelcase Road West, Unit E, Markham, ON, L3R 1B2','--','--','T: (905) 489-8989','realestate@ihmg.ca','Office Header');</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <v>77</v>
       </c>
@@ -17349,7 +17349,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('77','14','Eddie Tang','Financial Controller','120','(416) 723-8329','(905) 489-0186','eddie@ihmg.ca','Staff');</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
         <v>78</v>
       </c>
@@ -17388,7 +17388,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('78','14','Lily Hou','Senior Accounting Analyst &amp; Operations Support','187','(647) 774-8994','---','lily@ihmg.ca','Staff');</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <v>79</v>
       </c>
@@ -17427,7 +17427,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('79','1','Lunch Room','Meeting Room','541','---','---','-','Meeting Room');</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <v>80</v>
       </c>
@@ -17466,7 +17466,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('80','1','Markham Room','Meeting Room','250','---','---','-','Meeting Room');</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
         <v>81</v>
       </c>
@@ -17505,7 +17505,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('81','1','Mississauga Room','Meeting Room','226','---','---','-','Meeting Room');</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <v>82</v>
       </c>
@@ -17544,7 +17544,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('82','1','The Living Room','Meeting Room','288','---','---','-','Meeting Room');</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
         <v>83</v>
       </c>
@@ -17583,7 +17583,7 @@
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('83','1','Toronto Room','Meeting Room','208','---','---','-','Meeting Room');</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
         <v>84</v>
       </c>
@@ -17690,74 +17690,74 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E61CBDC-8347-4AEC-8B09-BF931AC71ED2}">
   <dimension ref="B1:B14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>131</v>
       </c>
@@ -17768,6 +17768,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FCEEF5D6F9A2C14292C82E7F88E7D4C7" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="770a5493e01cc46570af888c0fd11107">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6e07a911-1c82-455b-ae09-b73935b22a66" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="de63ad8f9259e2f5a7ae7a5921e0e8ad" ns2:_="">
     <xsd:import namespace="6e07a911-1c82-455b-ae09-b73935b22a66"/>
@@ -17899,22 +17914,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDCD3F55-29C2-4E12-8D9A-9EC0083C9C49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="6e07a911-1c82-455b-ae09-b73935b22a66"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C569B7B-6177-4C5F-B641-1220485D9B3F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4188865-1BAB-459E-8F28-5F6AB5F6EAC9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17930,28 +17954,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C569B7B-6177-4C5F-B641-1220485D9B3F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDCD3F55-29C2-4E12-8D9A-9EC0083C9C49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="6e07a911-1c82-455b-ae09-b73935b22a66"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/companydirectorypdf/companydir.xlsx
+++ b/companydirectorypdf/companydir.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\kwlrportal\companydirectorypdf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3F3213-AC2A-4E59-85C5-3292C02687E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D1132CD-A6D9-4ACB-AD99-E614CF9250CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{AE6EE1E0-C559-4053-97E8-B14EEDB6E6F6}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="321">
   <si>
     <t>Company Directory</t>
   </si>
@@ -253,15 +253,9 @@
     <t>T: (905) 896-0002</t>
   </si>
   <si>
-    <t>Hui Wang</t>
-  </si>
-  <si>
     <t>Manager Mississauga Branch</t>
   </si>
   <si>
-    <t>(416) 274-9789</t>
-  </si>
-  <si>
     <t>(905) 896-0002</t>
   </si>
   <si>
@@ -337,18 +331,6 @@
     <t>(905) 477-2090</t>
   </si>
   <si>
-    <t>Karl Park</t>
-  </si>
-  <si>
-    <t>(647) 286-0142</t>
-  </si>
-  <si>
-    <t>(905) 752-3516</t>
-  </si>
-  <si>
-    <t>karlp@livingproperties.com</t>
-  </si>
-  <si>
     <t>Richard Baksh</t>
   </si>
   <si>
@@ -487,9 +469,6 @@
     <t xml:space="preserve">T: (416) 279-0603 </t>
   </si>
   <si>
-    <t>Senior Property Manager</t>
-  </si>
-  <si>
     <t xml:space="preserve">(416) 279-0603 </t>
   </si>
   <si>
@@ -685,15 +664,6 @@
     <t>jessical@livingproperties.com</t>
   </si>
   <si>
-    <t>Jimmy Lo</t>
-  </si>
-  <si>
-    <t>Ben Dowson</t>
-  </si>
-  <si>
-    <t>Digitial Marketing &amp; Web Developer</t>
-  </si>
-  <si>
     <t>Ken Kam</t>
   </si>
   <si>
@@ -835,9 +805,6 @@
     <t>simonchan@livingrealtykw.com</t>
   </si>
   <si>
-    <t>socialmedia@livingrealtykw.com</t>
-  </si>
-  <si>
     <t>kellywan@livingrealtykw.com</t>
   </si>
   <si>
@@ -862,27 +829,15 @@
     <t>mississauga@livingrealtykw.com</t>
   </si>
   <si>
-    <t>huiwang@livingrealtykw.com</t>
-  </si>
-  <si>
     <t>woodbine@livingrealtykw.com</t>
   </si>
   <si>
     <t>anitahuang@livingrealtykw.com</t>
   </si>
   <si>
-    <t>jimmylo@livingrealtykw.com</t>
-  </si>
-  <si>
     <t>lydiang@livingrealtykw.com</t>
   </si>
   <si>
-    <t>vasanthanj@livingrealtykw.com</t>
-  </si>
-  <si>
-    <t>Vasanthan Jeyapragasam</t>
-  </si>
-  <si>
     <t>savannajoo@livingrealtykw.com</t>
   </si>
   <si>
@@ -1028,6 +983,27 @@
   </si>
   <si>
     <t>(905) 489-8989</t>
+  </si>
+  <si>
+    <t>Joanna Xie</t>
+  </si>
+  <si>
+    <t>Agent Services Coordinator</t>
+  </si>
+  <si>
+    <t>joannaxie@livingrealtykw.com</t>
+  </si>
+  <si>
+    <t>Cassandra Pacitto</t>
+  </si>
+  <si>
+    <t>cassandrapacitto@livingrealtykw.com</t>
+  </si>
+  <si>
+    <t>Kim Jin</t>
+  </si>
+  <si>
+    <t>kimjin@livingrealtykw.com</t>
   </si>
 </sst>
 </file>
@@ -1681,8 +1657,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{64C18C99-1B03-459F-9F00-A5922F0E9AD8}" name="Table2" displayName="Table2" ref="A1:M85" totalsRowShown="0">
-  <autoFilter ref="A1:M85" xr:uid="{64C18C99-1B03-459F-9F00-A5922F0E9AD8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{64C18C99-1B03-459F-9F00-A5922F0E9AD8}" name="Table2" displayName="Table2" ref="A1:M83" totalsRowShown="0">
+  <autoFilter ref="A1:M83" xr:uid="{64C18C99-1B03-459F-9F00-A5922F0E9AD8}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{84EE687C-25F0-49A0-A543-1CDE4F771B0E}" name="DisplayOrder" dataDxfId="33"/>
     <tableColumn id="2" xr3:uid="{289F04FD-E089-4D5D-A4E6-C7BA80BB6642}" name="OfficeCode"/>
@@ -2027,7 +2003,7 @@
       </c>
       <c r="H1" s="11"/>
       <c r="I1" s="11" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.25">
@@ -2038,7 +2014,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>3</v>
@@ -2051,7 +2027,7 @@
       </c>
       <c r="G2"/>
       <c r="H2" s="10" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="I2" s="10" t="s">
         <v>1</v>
@@ -2087,11 +2063,11 @@
       </c>
       <c r="G3"/>
       <c r="H3" t="str">
-        <f>ContactData!E80</f>
+        <f>ContactData!E78</f>
         <v>Lunch Room</v>
       </c>
       <c r="I3">
-        <f>ContactData!H80</f>
+        <f>ContactData!H78</f>
         <v>541</v>
       </c>
       <c r="J3"/>
@@ -2125,11 +2101,11 @@
       </c>
       <c r="G4"/>
       <c r="H4" t="str">
-        <f>ContactData!E81</f>
+        <f>ContactData!E79</f>
         <v>Markham Room</v>
       </c>
       <c r="I4">
-        <f>ContactData!H81</f>
+        <f>ContactData!H79</f>
         <v>250</v>
       </c>
       <c r="J4"/>
@@ -2163,11 +2139,11 @@
       </c>
       <c r="G5"/>
       <c r="H5" t="str">
-        <f>ContactData!E82</f>
+        <f>ContactData!E80</f>
         <v>Mississauga Room</v>
       </c>
       <c r="I5">
-        <f>ContactData!H82</f>
+        <f>ContactData!H80</f>
         <v>226</v>
       </c>
       <c r="J5"/>
@@ -2201,11 +2177,11 @@
       </c>
       <c r="G6"/>
       <c r="H6" t="str">
-        <f>ContactData!E83</f>
+        <f>ContactData!E81</f>
         <v>The Living Room</v>
       </c>
       <c r="I6">
-        <f>ContactData!H83</f>
+        <f>ContactData!H81</f>
         <v>288</v>
       </c>
       <c r="J6"/>
@@ -2239,11 +2215,11 @@
       </c>
       <c r="G7"/>
       <c r="H7" t="str">
-        <f>ContactData!E84</f>
+        <f>ContactData!E82</f>
         <v>Toronto Room</v>
       </c>
       <c r="I7">
-        <f>ContactData!H84</f>
+        <f>ContactData!H82</f>
         <v>208</v>
       </c>
       <c r="J7"/>
@@ -2277,11 +2253,11 @@
       </c>
       <c r="G8"/>
       <c r="H8" t="str">
-        <f>ContactData!E85</f>
+        <f>ContactData!E83</f>
         <v>York Room</v>
       </c>
       <c r="I8">
-        <f>ContactData!H85</f>
+        <f>ContactData!H83</f>
         <v>524</v>
       </c>
       <c r="J8"/>
@@ -2514,27 +2490,27 @@
     </row>
     <row r="16" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
-        <f>IF(LEN(ContactData!H15)&lt;3,"",ContactData!H15)</f>
+        <f>IF(LEN(ContactData!H16)&lt;3,"",ContactData!H16)</f>
         <v>123</v>
       </c>
       <c r="B16" s="3" t="str">
-        <f>ContactData!E15</f>
+        <f>ContactData!E16</f>
         <v>Wendy Chung</v>
       </c>
       <c r="C16" s="3" t="str">
-        <f>ContactData!G15</f>
+        <f>ContactData!G16</f>
         <v xml:space="preserve">Administration Officer </v>
       </c>
       <c r="D16" s="9" t="str">
-        <f>IF(LEN(ContactData!I15)&lt;3,"",ContactData!I15)</f>
+        <f>IF(LEN(ContactData!I16)&lt;3,"",ContactData!I16)</f>
         <v>---</v>
       </c>
       <c r="E16" s="3" t="str">
-        <f>ContactData!J15</f>
+        <f>ContactData!J16</f>
         <v>---</v>
       </c>
       <c r="F16" s="3" t="str">
-        <f>IF(LEN(ContactData!K15)&lt;3,"",ContactData!K15)</f>
+        <f>IF(LEN(ContactData!K16)&lt;3,"",ContactData!K16)</f>
         <v>wendychung@livingrealtykw.com</v>
       </c>
       <c r="G16"/>
@@ -2546,27 +2522,27 @@
     </row>
     <row r="17" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
-        <f>IF(LEN(ContactData!H16)&lt;3,"",ContactData!H16)</f>
+        <f>IF(LEN(ContactData!H17)&lt;3,"",ContactData!H17)</f>
         <v>206</v>
       </c>
       <c r="B17" s="3" t="str">
-        <f>ContactData!E16</f>
+        <f>ContactData!E17</f>
         <v>Benjamin Wong</v>
       </c>
       <c r="C17" s="3" t="str">
-        <f>ContactData!G16</f>
+        <f>ContactData!G17</f>
         <v>Assistant to the Broker of Record</v>
       </c>
       <c r="D17" s="9" t="str">
-        <f>IF(LEN(ContactData!I16)&lt;3,"",ContactData!I16)</f>
+        <f>IF(LEN(ContactData!I17)&lt;3,"",ContactData!I17)</f>
         <v>---</v>
       </c>
       <c r="E17" s="3" t="str">
-        <f>ContactData!J16</f>
+        <f>ContactData!J17</f>
         <v>---</v>
       </c>
       <c r="F17" s="3" t="str">
-        <f>IF(LEN(ContactData!K16)&lt;3,"",ContactData!K16)</f>
+        <f>IF(LEN(ContactData!K17)&lt;3,"",ContactData!K17)</f>
         <v>benjaminwongici@livingrealtykw.com</v>
       </c>
       <c r="G17"/>
@@ -2578,27 +2554,27 @@
     </row>
     <row r="18" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
-        <f>IF(LEN(ContactData!H17)&lt;3,"",ContactData!H17)</f>
+        <f>IF(LEN(ContactData!H18)&lt;3,"",ContactData!H18)</f>
         <v>507</v>
       </c>
       <c r="B18" s="3" t="str">
-        <f>ContactData!E17</f>
+        <f>ContactData!E18</f>
         <v>Luvie Chao</v>
       </c>
       <c r="C18" s="3" t="str">
-        <f>ContactData!G17</f>
+        <f>ContactData!G18</f>
         <v>Senior Deal Administrator</v>
       </c>
       <c r="D18" s="9" t="str">
-        <f>IF(LEN(ContactData!I17)&lt;3,"",ContactData!I17)</f>
+        <f>IF(LEN(ContactData!I18)&lt;3,"",ContactData!I18)</f>
         <v>---</v>
       </c>
       <c r="E18" s="3" t="str">
-        <f>ContactData!J17</f>
+        <f>ContactData!J18</f>
         <v>(905) 752-3507</v>
       </c>
       <c r="F18" s="3" t="str">
-        <f>IF(LEN(ContactData!K17)&lt;3,"",ContactData!K17)</f>
+        <f>IF(LEN(ContactData!K18)&lt;3,"",ContactData!K18)</f>
         <v>luvie@livingrealtykw.com</v>
       </c>
       <c r="G18"/>
@@ -2610,27 +2586,27 @@
     </row>
     <row r="19" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
-        <f>IF(LEN(ContactData!H18)&lt;3,"",ContactData!H18)</f>
+        <f>IF(LEN(ContactData!H19)&lt;3,"",ContactData!H19)</f>
         <v>508</v>
       </c>
       <c r="B19" s="3" t="str">
-        <f>ContactData!E18</f>
+        <f>ContactData!E19</f>
         <v>Maria Leung</v>
       </c>
       <c r="C19" s="3" t="str">
-        <f>ContactData!G18</f>
+        <f>ContactData!G19</f>
         <v>Deal Administrator</v>
       </c>
       <c r="D19" s="9" t="str">
-        <f>IF(LEN(ContactData!I18)&lt;3,"",ContactData!I18)</f>
+        <f>IF(LEN(ContactData!I19)&lt;3,"",ContactData!I19)</f>
         <v>---</v>
       </c>
       <c r="E19" s="3" t="str">
-        <f>ContactData!J18</f>
+        <f>ContactData!J19</f>
         <v>(905) 752-3508</v>
       </c>
       <c r="F19" s="3" t="str">
-        <f>IF(LEN(ContactData!K18)&lt;3,"",ContactData!K18)</f>
+        <f>IF(LEN(ContactData!K19)&lt;3,"",ContactData!K19)</f>
         <v>marialeung@livingrealtykw.com</v>
       </c>
       <c r="G19"/>
@@ -2642,27 +2618,27 @@
     </row>
     <row r="20" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
-        <f>IF(LEN(ContactData!H19)&lt;3,"",ContactData!H19)</f>
+        <f>IF(LEN(ContactData!H20)&lt;3,"",ContactData!H20)</f>
         <v>255</v>
       </c>
       <c r="B20" s="3" t="str">
-        <f>ContactData!E19</f>
+        <f>ContactData!E20</f>
         <v>Ken Cheung</v>
       </c>
       <c r="C20" s="3" t="str">
-        <f>ContactData!G19</f>
+        <f>ContactData!G20</f>
         <v>Deal Administrator</v>
       </c>
       <c r="D20" s="9" t="str">
-        <f>IF(LEN(ContactData!I19)&lt;3,"",ContactData!I19)</f>
+        <f>IF(LEN(ContactData!I20)&lt;3,"",ContactData!I20)</f>
         <v>---</v>
       </c>
       <c r="E20" s="3" t="str">
-        <f>ContactData!J19</f>
+        <f>ContactData!J20</f>
         <v>---</v>
       </c>
       <c r="F20" s="3" t="str">
-        <f>IF(LEN(ContactData!K19)&lt;3,"",ContactData!K19)</f>
+        <f>IF(LEN(ContactData!K20)&lt;3,"",ContactData!K20)</f>
         <v>kencheung@livingrealtykw.com</v>
       </c>
       <c r="G20"/>
@@ -2674,27 +2650,27 @@
     </row>
     <row r="21" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
-        <f>IF(LEN(ContactData!H20)&lt;3,"",ContactData!H20)</f>
+        <f>IF(LEN(ContactData!H21)&lt;3,"",ContactData!H21)</f>
         <v>506</v>
       </c>
       <c r="B21" s="3" t="str">
-        <f>ContactData!E20</f>
+        <f>ContactData!E21</f>
         <v>Connie Cheung</v>
       </c>
       <c r="C21" s="3" t="str">
-        <f>ContactData!G20</f>
+        <f>ContactData!G21</f>
         <v>Accounting Bookkeeper</v>
       </c>
       <c r="D21" s="9" t="str">
-        <f>IF(LEN(ContactData!I20)&lt;3,"",ContactData!I20)</f>
+        <f>IF(LEN(ContactData!I21)&lt;3,"",ContactData!I21)</f>
         <v>---</v>
       </c>
       <c r="E21" s="3" t="str">
-        <f>ContactData!J20</f>
+        <f>ContactData!J21</f>
         <v>(905) 752-3506</v>
       </c>
       <c r="F21" s="3" t="str">
-        <f>IF(LEN(ContactData!K20)&lt;3,"",ContactData!K20)</f>
+        <f>IF(LEN(ContactData!K21)&lt;3,"",ContactData!K21)</f>
         <v>conniecheung@livingrealtykw.com</v>
       </c>
       <c r="G21"/>
@@ -2706,27 +2682,27 @@
     </row>
     <row r="22" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
-        <f>IF(LEN(ContactData!H21)&lt;3,"",ContactData!H21)</f>
+        <f>IF(LEN(ContactData!H22)&lt;3,"",ContactData!H22)</f>
         <v>519</v>
       </c>
       <c r="B22" s="3" t="str">
-        <f>ContactData!E21</f>
+        <f>ContactData!E22</f>
         <v>Simon Chan</v>
       </c>
       <c r="C22" s="3" t="str">
-        <f>ContactData!G21</f>
+        <f>ContactData!G22</f>
         <v>Operations Assistant</v>
       </c>
       <c r="D22" s="9" t="str">
-        <f>IF(LEN(ContactData!I21)&lt;3,"",ContactData!I21)</f>
+        <f>IF(LEN(ContactData!I22)&lt;3,"",ContactData!I22)</f>
         <v>---</v>
       </c>
       <c r="E22" s="3" t="str">
-        <f>ContactData!J21</f>
+        <f>ContactData!J22</f>
         <v>(905) 752-3519</v>
       </c>
       <c r="F22" s="3" t="str">
-        <f>IF(LEN(ContactData!K21)&lt;3,"",ContactData!K21)</f>
+        <f>IF(LEN(ContactData!K22)&lt;3,"",ContactData!K22)</f>
         <v>simonchan@livingrealtykw.com</v>
       </c>
       <c r="G22"/>
@@ -2737,29 +2713,29 @@
       <c r="L22"/>
     </row>
     <row r="23" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="str">
-        <f>IF(LEN(ContactData!H22)&lt;3,"",ContactData!H22)</f>
-        <v>---</v>
-      </c>
-      <c r="B23" s="3" t="str">
-        <f>ContactData!E22</f>
-        <v>Ben Dowson</v>
-      </c>
-      <c r="C23" s="3" t="str">
-        <f>ContactData!G22</f>
-        <v>Digitial Marketing &amp; Web Developer</v>
-      </c>
-      <c r="D23" s="9" t="str">
-        <f>IF(LEN(ContactData!I22)&lt;3,"",ContactData!I22)</f>
-        <v>---</v>
-      </c>
-      <c r="E23" s="3" t="str">
-        <f>ContactData!J22</f>
-        <v>---</v>
-      </c>
-      <c r="F23" s="3" t="str">
-        <f>IF(LEN(ContactData!K22)&lt;3,"",ContactData!K22)</f>
-        <v>socialmedia@livingrealtykw.com</v>
+      <c r="A23" s="9" t="e">
+        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B23" s="3" t="e">
+        <f>ContactData!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C23" s="3" t="e">
+        <f>ContactData!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D23" s="9" t="e">
+        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E23" s="3" t="e">
+        <f>ContactData!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F23" s="3" t="e">
+        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
+        <v>#REF!</v>
       </c>
       <c r="G23"/>
       <c r="H23"/>
@@ -3031,7 +3007,7 @@
       </c>
       <c r="B32" s="3" t="str">
         <f>ContactData!E31</f>
-        <v>Hui Wang</v>
+        <v>Cassandra Pacitto</v>
       </c>
       <c r="C32" s="3" t="str">
         <f>ContactData!G31</f>
@@ -3039,7 +3015,7 @@
       </c>
       <c r="D32" s="9" t="str">
         <f>IF(LEN(ContactData!I31)&lt;3,"",ContactData!I31)</f>
-        <v>(416) 274-9789</v>
+        <v>(905) 896-0002</v>
       </c>
       <c r="E32" s="3" t="str">
         <f>ContactData!J31</f>
@@ -3047,7 +3023,7 @@
       </c>
       <c r="F32" s="3" t="str">
         <f>IF(LEN(ContactData!K31)&lt;3,"",ContactData!K31)</f>
-        <v>huiwang@livingrealtykw.com</v>
+        <v>cassandrapacitto@livingrealtykw.com</v>
       </c>
       <c r="G32"/>
       <c r="H32"/>
@@ -3057,29 +3033,29 @@
       <c r="L32"/>
     </row>
     <row r="33" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A33" s="9" t="str">
-        <f>IF(LEN(ContactData!H32)&lt;3,"",ContactData!H32)</f>
-        <v>---</v>
-      </c>
-      <c r="B33" s="3" t="str">
-        <f>ContactData!E32</f>
-        <v>Vasanthan Jeyapragasam</v>
-      </c>
-      <c r="C33" s="3" t="str">
-        <f>ContactData!G32</f>
-        <v>Secretary</v>
-      </c>
-      <c r="D33" s="9" t="str">
-        <f>IF(LEN(ContactData!I32)&lt;3,"",ContactData!I32)</f>
-        <v>---</v>
-      </c>
-      <c r="E33" s="3" t="str">
-        <f>ContactData!J32</f>
-        <v>(905) 896-0002</v>
-      </c>
-      <c r="F33" s="3" t="str">
-        <f>IF(LEN(ContactData!K32)&lt;3,"",ContactData!K32)</f>
-        <v>vasanthanj@livingrealtykw.com</v>
+      <c r="A33" s="9" t="e">
+        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B33" s="3" t="e">
+        <f>ContactData!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C33" s="3" t="e">
+        <f>ContactData!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D33" s="9" t="e">
+        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E33" s="3" t="e">
+        <f>ContactData!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F33" s="3" t="e">
+        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
+        <v>#REF!</v>
       </c>
       <c r="G33"/>
       <c r="H33"/>
@@ -3090,27 +3066,27 @@
     </row>
     <row r="34" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="str">
-        <f>IF(LEN(ContactData!H33)&lt;3,"",ContactData!H33)</f>
+        <f>IF(LEN(ContactData!H32)&lt;3,"",ContactData!H32)</f>
         <v>---</v>
       </c>
       <c r="B34" s="3" t="str">
-        <f>ContactData!E33</f>
+        <f>ContactData!E32</f>
         <v>Katie Wong</v>
       </c>
       <c r="C34" s="3" t="str">
-        <f>ContactData!G33</f>
+        <f>ContactData!G32</f>
         <v>Secretary</v>
       </c>
       <c r="D34" s="9" t="str">
-        <f>IF(LEN(ContactData!I33)&lt;3,"",ContactData!I33)</f>
+        <f>IF(LEN(ContactData!I32)&lt;3,"",ContactData!I32)</f>
         <v>---</v>
       </c>
       <c r="E34" s="3" t="str">
-        <f>ContactData!J33</f>
+        <f>ContactData!J32</f>
         <v>(905) 896-0002</v>
       </c>
       <c r="F34" s="3" t="str">
-        <f>IF(LEN(ContactData!K33)&lt;3,"",ContactData!K33)</f>
+        <f>IF(LEN(ContactData!K32)&lt;3,"",ContactData!K32)</f>
         <v>katiewong@livingrealtykw.com</v>
       </c>
       <c r="G34"/>
@@ -3122,27 +3098,27 @@
     </row>
     <row r="35" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="str">
-        <f>IF(LEN(ContactData!H34)&lt;3,"",ContactData!H34)</f>
+        <f>IF(LEN(ContactData!H33)&lt;3,"",ContactData!H33)</f>
         <v/>
       </c>
       <c r="B35" s="3" t="str">
-        <f>ContactData!E34</f>
+        <f>ContactData!E33</f>
         <v>Woodbine Office</v>
       </c>
       <c r="C35" s="3" t="str">
-        <f>ContactData!G34</f>
+        <f>ContactData!G33</f>
         <v>8 Steelcase Road West, Markham, ON, L3R 1B2</v>
       </c>
       <c r="D35" s="9" t="str">
-        <f>IF(LEN(ContactData!I34)&lt;3,"",ContactData!I34)</f>
+        <f>IF(LEN(ContactData!I33)&lt;3,"",ContactData!I33)</f>
         <v/>
       </c>
       <c r="E35" s="3" t="str">
-        <f>ContactData!J34</f>
+        <f>ContactData!J33</f>
         <v>T: (905) 474-0500</v>
       </c>
       <c r="F35" s="3" t="str">
-        <f>IF(LEN(ContactData!K34)&lt;3,"",ContactData!K34)</f>
+        <f>IF(LEN(ContactData!K33)&lt;3,"",ContactData!K33)</f>
         <v>woodbine@livingrealtykw.com</v>
       </c>
       <c r="G35"/>
@@ -3154,27 +3130,27 @@
     </row>
     <row r="36" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
-        <f>IF(LEN(ContactData!H35)&lt;3,"",ContactData!H35)</f>
+        <f>IF(LEN(ContactData!H34)&lt;3,"",ContactData!H34)</f>
         <v>176</v>
       </c>
       <c r="B36" s="3" t="str">
-        <f>ContactData!E35</f>
+        <f>ContactData!E34</f>
         <v>Anita Huang</v>
       </c>
       <c r="C36" s="3" t="str">
-        <f>ContactData!G35</f>
+        <f>ContactData!G34</f>
         <v>Manager Woobine Branch</v>
       </c>
       <c r="D36" s="9" t="str">
-        <f>IF(LEN(ContactData!I35)&lt;3,"",ContactData!I35)</f>
+        <f>IF(LEN(ContactData!I34)&lt;3,"",ContactData!I34)</f>
         <v>(416) 523-1888</v>
       </c>
       <c r="E36" s="3" t="str">
-        <f>ContactData!J35</f>
+        <f>ContactData!J34</f>
         <v>---</v>
       </c>
       <c r="F36" s="3" t="str">
-        <f>IF(LEN(ContactData!K35)&lt;3,"",ContactData!K35)</f>
+        <f>IF(LEN(ContactData!K34)&lt;3,"",ContactData!K34)</f>
         <v>anitahuang@livingrealtykw.com</v>
       </c>
       <c r="G36"/>
@@ -3186,28 +3162,28 @@
     </row>
     <row r="37" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
-        <f>IF(LEN(ContactData!H36)&lt;3,"",ContactData!H36)</f>
+        <f>IF(LEN(ContactData!H35)&lt;3,"",ContactData!H35)</f>
         <v>104</v>
       </c>
       <c r="B37" s="3" t="str">
-        <f>ContactData!E36</f>
-        <v>Jimmy Lo</v>
+        <f>ContactData!E35</f>
+        <v>Kim Jin</v>
       </c>
       <c r="C37" s="3" t="str">
-        <f>ContactData!G36</f>
+        <f>ContactData!G35</f>
         <v>Secretary</v>
       </c>
       <c r="D37" s="9" t="str">
-        <f>IF(LEN(ContactData!I36)&lt;3,"",ContactData!I36)</f>
+        <f>IF(LEN(ContactData!I35)&lt;3,"",ContactData!I35)</f>
         <v>---</v>
       </c>
       <c r="E37" s="3" t="str">
-        <f>ContactData!J36</f>
+        <f>ContactData!J35</f>
         <v>(905) 474-0500</v>
       </c>
       <c r="F37" s="3" t="str">
-        <f>IF(LEN(ContactData!K36)&lt;3,"",ContactData!K36)</f>
-        <v>jimmylo@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K35)&lt;3,"",ContactData!K35)</f>
+        <v>kimjin@livingrealtykw.com</v>
       </c>
       <c r="G37"/>
       <c r="H37"/>
@@ -3218,27 +3194,27 @@
     </row>
     <row r="38" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
-        <f>IF(LEN(ContactData!H37)&lt;3,"",ContactData!H37)</f>
+        <f>IF(LEN(ContactData!H36)&lt;3,"",ContactData!H36)</f>
         <v>100</v>
       </c>
       <c r="B38" s="3" t="str">
-        <f>ContactData!E37</f>
+        <f>ContactData!E36</f>
         <v>Savanna Joo</v>
       </c>
       <c r="C38" s="3" t="str">
-        <f>ContactData!G37</f>
+        <f>ContactData!G36</f>
         <v>Secretary</v>
       </c>
       <c r="D38" s="9" t="str">
-        <f>IF(LEN(ContactData!I37)&lt;3,"",ContactData!I37)</f>
+        <f>IF(LEN(ContactData!I36)&lt;3,"",ContactData!I36)</f>
         <v>---</v>
       </c>
       <c r="E38" s="3" t="str">
-        <f>ContactData!J37</f>
+        <f>ContactData!J36</f>
         <v>(905) 474-0500</v>
       </c>
       <c r="F38" s="3" t="str">
-        <f>IF(LEN(ContactData!K37)&lt;3,"",ContactData!K37)</f>
+        <f>IF(LEN(ContactData!K36)&lt;3,"",ContactData!K36)</f>
         <v>savannajoo@livingrealtykw.com</v>
       </c>
       <c r="G38"/>
@@ -3250,27 +3226,27 @@
     </row>
     <row r="39" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="str">
-        <f>IF(LEN(ContactData!H38)&lt;3,"",ContactData!H38)</f>
+        <f>IF(LEN(ContactData!H37)&lt;3,"",ContactData!H37)</f>
         <v/>
       </c>
       <c r="B39" s="3" t="str">
-        <f>ContactData!E38</f>
+        <f>ContactData!E37</f>
         <v>Yonge &amp; Eglinton Office</v>
       </c>
       <c r="C39" s="3" t="str">
-        <f>ContactData!G38</f>
+        <f>ContactData!G37</f>
         <v>2301 Yonge Street, Toronto, ON, M4P 2C6</v>
       </c>
       <c r="D39" s="9" t="str">
-        <f>IF(LEN(ContactData!I38)&lt;3,"",ContactData!I38)</f>
+        <f>IF(LEN(ContactData!I37)&lt;3,"",ContactData!I37)</f>
         <v/>
       </c>
       <c r="E39" s="3" t="str">
-        <f>ContactData!J38</f>
+        <f>ContactData!J37</f>
         <v>T: (416) 223-8833</v>
       </c>
       <c r="F39" s="3" t="str">
-        <f>IF(LEN(ContactData!K38)&lt;3,"",ContactData!K38)</f>
+        <f>IF(LEN(ContactData!K37)&lt;3,"",ContactData!K37)</f>
         <v>ye@livingrealtykw.com</v>
       </c>
       <c r="G39"/>
@@ -3282,27 +3258,27 @@
     </row>
     <row r="40" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="str">
-        <f>IF(LEN(ContactData!H39)&lt;3,"",ContactData!H39)</f>
+        <f>IF(LEN(ContactData!H38)&lt;3,"",ContactData!H38)</f>
         <v>---</v>
       </c>
       <c r="B40" s="3" t="str">
-        <f>ContactData!E39</f>
+        <f>ContactData!E38</f>
         <v xml:space="preserve">Tony Prochilo </v>
       </c>
       <c r="C40" s="3" t="str">
-        <f>ContactData!G39</f>
+        <f>ContactData!G38</f>
         <v>Manager Yonge &amp; Eglinton</v>
       </c>
       <c r="D40" s="9" t="str">
-        <f>IF(LEN(ContactData!I39)&lt;3,"",ContactData!I39)</f>
+        <f>IF(LEN(ContactData!I38)&lt;3,"",ContactData!I38)</f>
         <v>(416) 576-6312</v>
       </c>
       <c r="E40" s="3" t="str">
-        <f>ContactData!J39</f>
+        <f>ContactData!J38</f>
         <v>---</v>
       </c>
       <c r="F40" s="3" t="str">
-        <f>IF(LEN(ContactData!K39)&lt;3,"",ContactData!K39)</f>
+        <f>IF(LEN(ContactData!K38)&lt;3,"",ContactData!K38)</f>
         <v>tonyprochilo@livingrealtykw.com</v>
       </c>
       <c r="G40"/>
@@ -3314,27 +3290,27 @@
     </row>
     <row r="41" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="str">
-        <f>IF(LEN(ContactData!H40)&lt;3,"",ContactData!H40)</f>
+        <f>IF(LEN(ContactData!H39)&lt;3,"",ContactData!H39)</f>
         <v>---</v>
       </c>
       <c r="B41" s="3" t="str">
-        <f>ContactData!E40</f>
+        <f>ContactData!E39</f>
         <v>Lydia Ng</v>
       </c>
       <c r="C41" s="3" t="str">
-        <f>ContactData!G40</f>
+        <f>ContactData!G39</f>
         <v>Secretary</v>
       </c>
       <c r="D41" s="9" t="str">
-        <f>IF(LEN(ContactData!I40)&lt;3,"",ContactData!I40)</f>
+        <f>IF(LEN(ContactData!I39)&lt;3,"",ContactData!I39)</f>
         <v>---</v>
       </c>
       <c r="E41" s="3" t="str">
-        <f>ContactData!J40</f>
+        <f>ContactData!J39</f>
         <v>(416) 223-8833</v>
       </c>
       <c r="F41" s="3" t="str">
-        <f>IF(LEN(ContactData!K40)&lt;3,"",ContactData!K40)</f>
+        <f>IF(LEN(ContactData!K39)&lt;3,"",ContactData!K39)</f>
         <v>lydiang@livingrealtykw.com</v>
       </c>
       <c r="G41"/>
@@ -3346,27 +3322,27 @@
     </row>
     <row r="42" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="str">
-        <f>IF(LEN(ContactData!H41)&lt;3,"",ContactData!H41)</f>
+        <f>IF(LEN(ContactData!H40)&lt;3,"",ContactData!H40)</f>
         <v/>
       </c>
       <c r="B42" s="3" t="str">
-        <f>ContactData!E41</f>
+        <f>ContactData!E40</f>
         <v>I.C.&amp;I. Office</v>
       </c>
       <c r="C42" s="3" t="str">
-        <f>ContactData!G41</f>
+        <f>ContactData!G40</f>
         <v>8 Steelcase Road West, Unit C, Markham, ON, L3R 1B2</v>
       </c>
       <c r="D42" s="9" t="str">
-        <f>IF(LEN(ContactData!I41)&lt;3,"",ContactData!I41)</f>
+        <f>IF(LEN(ContactData!I40)&lt;3,"",ContactData!I40)</f>
         <v/>
       </c>
       <c r="E42" s="3" t="str">
-        <f>ContactData!J41</f>
+        <f>ContactData!J40</f>
         <v>T: (905) 474-1772</v>
       </c>
       <c r="F42" s="3" t="str">
-        <f>IF(LEN(ContactData!K41)&lt;3,"",ContactData!K41)</f>
+        <f>IF(LEN(ContactData!K40)&lt;3,"",ContactData!K40)</f>
         <v/>
       </c>
       <c r="G42"/>
@@ -3378,27 +3354,27 @@
     </row>
     <row r="43" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A43" s="9">
-        <f>IF(LEN(ContactData!H42)&lt;3,"",ContactData!H42)</f>
+        <f>IF(LEN(ContactData!H41)&lt;3,"",ContactData!H41)</f>
         <v>228</v>
       </c>
       <c r="B43" s="3" t="str">
-        <f>ContactData!E42</f>
+        <f>ContactData!E41</f>
         <v>Kelvin Wong</v>
       </c>
       <c r="C43" s="3" t="str">
-        <f>ContactData!G42</f>
+        <f>ContactData!G41</f>
         <v>Manager I.C.&amp;I. Branch</v>
       </c>
       <c r="D43" s="9" t="str">
-        <f>IF(LEN(ContactData!I42)&lt;3,"",ContactData!I42)</f>
+        <f>IF(LEN(ContactData!I41)&lt;3,"",ContactData!I41)</f>
         <v>(416) 567-7882</v>
       </c>
       <c r="E43" s="3" t="str">
-        <f>ContactData!J42</f>
+        <f>ContactData!J41</f>
         <v>---</v>
       </c>
       <c r="F43" s="3" t="str">
-        <f>IF(LEN(ContactData!K42)&lt;3,"",ContactData!K42)</f>
+        <f>IF(LEN(ContactData!K41)&lt;3,"",ContactData!K41)</f>
         <v>kelvin@livingrealtykw.com</v>
       </c>
       <c r="G43"/>
@@ -3410,27 +3386,27 @@
     </row>
     <row r="44" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="str">
-        <f>IF(LEN(ContactData!H43)&lt;3,"",ContactData!H43)</f>
+        <f>IF(LEN(ContactData!H42)&lt;3,"",ContactData!H42)</f>
         <v/>
       </c>
       <c r="B44" s="3" t="str">
-        <f>ContactData!E43</f>
+        <f>ContactData!E42</f>
         <v>LPI Head Office</v>
       </c>
       <c r="C44" s="3" t="str">
-        <f>ContactData!G43</f>
+        <f>ContactData!G42</f>
         <v>8 Steelcase Road West, Markham, ON, L3R 1B2</v>
       </c>
       <c r="D44" s="9" t="str">
-        <f>IF(LEN(ContactData!I43)&lt;3,"",ContactData!I43)</f>
+        <f>IF(LEN(ContactData!I42)&lt;3,"",ContactData!I42)</f>
         <v/>
       </c>
       <c r="E44" s="3" t="str">
-        <f>ContactData!J43</f>
+        <f>ContactData!J42</f>
         <v>T: (905) 477-2090</v>
       </c>
       <c r="F44" s="3" t="str">
-        <f>IF(LEN(ContactData!K43)&lt;3,"",ContactData!K43)</f>
+        <f>IF(LEN(ContactData!K42)&lt;3,"",ContactData!K42)</f>
         <v/>
       </c>
       <c r="G44"/>
@@ -3442,27 +3418,27 @@
     </row>
     <row r="45" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A45" s="9">
-        <f>IF(LEN(ContactData!H44)&lt;3,"",ContactData!H44)</f>
+        <f>IF(LEN(ContactData!H43)&lt;3,"",ContactData!H43)</f>
         <v>521</v>
       </c>
       <c r="B45" s="3" t="str">
-        <f>ContactData!E44</f>
+        <f>ContactData!E43</f>
         <v>Ben Wong</v>
       </c>
       <c r="C45" s="3" t="str">
-        <f>ContactData!G44</f>
+        <f>ContactData!G43</f>
         <v>President</v>
       </c>
       <c r="D45" s="9" t="str">
-        <f>IF(LEN(ContactData!I44)&lt;3,"",ContactData!I44)</f>
+        <f>IF(LEN(ContactData!I43)&lt;3,"",ContactData!I43)</f>
         <v>(416) 399-2311</v>
       </c>
       <c r="E45" s="3" t="str">
-        <f>ContactData!J44</f>
+        <f>ContactData!J43</f>
         <v>(905) 752-3521</v>
       </c>
       <c r="F45" s="3" t="str">
-        <f>IF(LEN(ContactData!K44)&lt;3,"",ContactData!K44)</f>
+        <f>IF(LEN(ContactData!K43)&lt;3,"",ContactData!K43)</f>
         <v>benw@livingproperties.com</v>
       </c>
       <c r="G45"/>
@@ -3474,27 +3450,27 @@
     </row>
     <row r="46" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A46" s="9">
-        <f>IF(LEN(ContactData!H45)&lt;3,"",ContactData!H45)</f>
+        <f>IF(LEN(ContactData!H44)&lt;3,"",ContactData!H44)</f>
         <v>514</v>
       </c>
       <c r="B46" s="3" t="str">
-        <f>ContactData!E45</f>
+        <f>ContactData!E44</f>
         <v>Winnie Tsui</v>
       </c>
       <c r="C46" s="3" t="str">
-        <f>ContactData!G45</f>
+        <f>ContactData!G44</f>
         <v>Director of Operations</v>
       </c>
       <c r="D46" s="9" t="str">
-        <f>IF(LEN(ContactData!I45)&lt;3,"",ContactData!I45)</f>
+        <f>IF(LEN(ContactData!I44)&lt;3,"",ContactData!I44)</f>
         <v>(647) 286-0145</v>
       </c>
       <c r="E46" s="3" t="str">
-        <f>ContactData!J45</f>
+        <f>ContactData!J44</f>
         <v xml:space="preserve">(905) 752-3514 </v>
       </c>
       <c r="F46" s="3" t="str">
-        <f>IF(LEN(ContactData!K45)&lt;3,"",ContactData!K45)</f>
+        <f>IF(LEN(ContactData!K44)&lt;3,"",ContactData!K44)</f>
         <v>winniet@livingproperties.com</v>
       </c>
       <c r="G46"/>
@@ -3506,27 +3482,27 @@
     </row>
     <row r="47" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
-        <f>IF(LEN(ContactData!H46)&lt;3,"",ContactData!H46)</f>
+        <f>IF(LEN(ContactData!H45)&lt;3,"",ContactData!H45)</f>
         <v>286</v>
       </c>
       <c r="B47" s="3" t="str">
-        <f>ContactData!E46</f>
+        <f>ContactData!E45</f>
         <v>Frederick Tang</v>
       </c>
       <c r="C47" s="3" t="str">
-        <f>ContactData!G46</f>
+        <f>ContactData!G45</f>
         <v>Director of Business Development</v>
       </c>
       <c r="D47" s="9" t="str">
-        <f>IF(LEN(ContactData!I46)&lt;3,"",ContactData!I46)</f>
+        <f>IF(LEN(ContactData!I45)&lt;3,"",ContactData!I45)</f>
         <v>(416) 618-5898</v>
       </c>
       <c r="E47" s="3" t="str">
-        <f>ContactData!J46</f>
+        <f>ContactData!J45</f>
         <v>-</v>
       </c>
       <c r="F47" s="3" t="str">
-        <f>IF(LEN(ContactData!K46)&lt;3,"",ContactData!K46)</f>
+        <f>IF(LEN(ContactData!K45)&lt;3,"",ContactData!K45)</f>
         <v>fredt@livingproperties.com</v>
       </c>
       <c r="G47"/>
@@ -3537,29 +3513,29 @@
       <c r="L47"/>
     </row>
     <row r="48" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A48" s="9">
-        <f>IF(LEN(ContactData!H47)&lt;3,"",ContactData!H47)</f>
-        <v>516</v>
-      </c>
-      <c r="B48" s="3" t="str">
-        <f>ContactData!E47</f>
-        <v>Karl Park</v>
-      </c>
-      <c r="C48" s="3" t="str">
-        <f>ContactData!G47</f>
-        <v>Senior Property Manager</v>
-      </c>
-      <c r="D48" s="9" t="str">
-        <f>IF(LEN(ContactData!I47)&lt;3,"",ContactData!I47)</f>
-        <v>(647) 286-0142</v>
-      </c>
-      <c r="E48" s="3" t="str">
-        <f>ContactData!J47</f>
-        <v>(905) 752-3516</v>
-      </c>
-      <c r="F48" s="3" t="str">
-        <f>IF(LEN(ContactData!K47)&lt;3,"",ContactData!K47)</f>
-        <v>karlp@livingproperties.com</v>
+      <c r="A48" s="9" t="e">
+        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B48" s="3" t="e">
+        <f>ContactData!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C48" s="3" t="e">
+        <f>ContactData!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D48" s="9" t="e">
+        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E48" s="3" t="e">
+        <f>ContactData!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F48" s="3" t="e">
+        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
+        <v>#REF!</v>
       </c>
       <c r="G48"/>
       <c r="H48"/>
@@ -3570,27 +3546,27 @@
     </row>
     <row r="49" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
-        <f>IF(LEN(ContactData!H48)&lt;3,"",ContactData!H48)</f>
+        <f>IF(LEN(ContactData!H46)&lt;3,"",ContactData!H46)</f>
         <v>512</v>
       </c>
       <c r="B49" s="3" t="str">
-        <f>ContactData!E48</f>
+        <f>ContactData!E46</f>
         <v>Stanley Chow</v>
       </c>
       <c r="C49" s="3" t="str">
-        <f>ContactData!G48</f>
+        <f>ContactData!G46</f>
         <v>Property Manager</v>
       </c>
       <c r="D49" s="9" t="str">
-        <f>IF(LEN(ContactData!I48)&lt;3,"",ContactData!I48)</f>
+        <f>IF(LEN(ContactData!I46)&lt;3,"",ContactData!I46)</f>
         <v>(416) 277-6098</v>
       </c>
       <c r="E49" s="3" t="str">
-        <f>ContactData!J48</f>
+        <f>ContactData!J46</f>
         <v>(905) 752-3512</v>
       </c>
       <c r="F49" s="3" t="str">
-        <f>IF(LEN(ContactData!K48)&lt;3,"",ContactData!K48)</f>
+        <f>IF(LEN(ContactData!K46)&lt;3,"",ContactData!K46)</f>
         <v>stanleyc@livingproperties.com</v>
       </c>
       <c r="G49"/>
@@ -3602,27 +3578,27 @@
     </row>
     <row r="50" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A50" s="9">
-        <f>IF(LEN(ContactData!H49)&lt;3,"",ContactData!H49)</f>
+        <f>IF(LEN(ContactData!H47)&lt;3,"",ContactData!H47)</f>
         <v>284</v>
       </c>
       <c r="B50" s="3" t="str">
-        <f>ContactData!E49</f>
+        <f>ContactData!E47</f>
         <v>Richard Baksh</v>
       </c>
       <c r="C50" s="3" t="str">
-        <f>ContactData!G49</f>
+        <f>ContactData!G47</f>
         <v>Property Manager</v>
       </c>
       <c r="D50" s="9" t="str">
-        <f>IF(LEN(ContactData!I49)&lt;3,"",ContactData!I49)</f>
+        <f>IF(LEN(ContactData!I47)&lt;3,"",ContactData!I47)</f>
         <v>(647) 967-0088</v>
       </c>
       <c r="E50" s="3" t="str">
-        <f>ContactData!J49</f>
+        <f>ContactData!J47</f>
         <v>(905) 258-0632</v>
       </c>
       <c r="F50" s="3" t="str">
-        <f>IF(LEN(ContactData!K49)&lt;3,"",ContactData!K49)</f>
+        <f>IF(LEN(ContactData!K47)&lt;3,"",ContactData!K47)</f>
         <v>richardb@livingproperties.com</v>
       </c>
       <c r="G50"/>
@@ -3634,27 +3610,27 @@
     </row>
     <row r="51" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
-        <f>IF(LEN(ContactData!H50)&lt;3,"",ContactData!H50)</f>
+        <f>IF(LEN(ContactData!H48)&lt;3,"",ContactData!H48)</f>
         <v>517</v>
       </c>
       <c r="B51" s="3" t="str">
-        <f>ContactData!E50</f>
+        <f>ContactData!E48</f>
         <v>Ken Kam</v>
       </c>
       <c r="C51" s="3" t="str">
-        <f>ContactData!G50</f>
+        <f>ContactData!G48</f>
         <v>Property Manager</v>
       </c>
       <c r="D51" s="9" t="str">
-        <f>IF(LEN(ContactData!I50)&lt;3,"",ContactData!I50)</f>
+        <f>IF(LEN(ContactData!I48)&lt;3,"",ContactData!I48)</f>
         <v>(647) 204-4455</v>
       </c>
       <c r="E51" s="3" t="str">
-        <f>ContactData!J50</f>
+        <f>ContactData!J48</f>
         <v>(905) 477-2090</v>
       </c>
       <c r="F51" s="3" t="str">
-        <f>IF(LEN(ContactData!K50)&lt;3,"",ContactData!K50)</f>
+        <f>IF(LEN(ContactData!K48)&lt;3,"",ContactData!K48)</f>
         <v>kenk@livingproperties.com</v>
       </c>
       <c r="G51"/>
@@ -3666,27 +3642,27 @@
     </row>
     <row r="52" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
-        <f>IF(LEN(ContactData!H51)&lt;3,"",ContactData!H51)</f>
+        <f>IF(LEN(ContactData!H49)&lt;3,"",ContactData!H49)</f>
         <v>520</v>
       </c>
       <c r="B52" s="3" t="str">
-        <f>ContactData!E51</f>
+        <f>ContactData!E49</f>
         <v>Raymond Chin</v>
       </c>
       <c r="C52" s="3" t="str">
-        <f>ContactData!G51</f>
+        <f>ContactData!G49</f>
         <v>Property Manager</v>
       </c>
       <c r="D52" s="9" t="str">
-        <f>IF(LEN(ContactData!I51)&lt;3,"",ContactData!I51)</f>
+        <f>IF(LEN(ContactData!I49)&lt;3,"",ContactData!I49)</f>
         <v>(437) 331-6038</v>
       </c>
       <c r="E52" s="3" t="str">
-        <f>ContactData!J51</f>
+        <f>ContactData!J49</f>
         <v>(905) 477-2090</v>
       </c>
       <c r="F52" s="3" t="str">
-        <f>IF(LEN(ContactData!K51)&lt;3,"",ContactData!K51)</f>
+        <f>IF(LEN(ContactData!K49)&lt;3,"",ContactData!K49)</f>
         <v>raymondc@livingproperties.com</v>
       </c>
       <c r="G52"/>
@@ -3698,27 +3674,27 @@
     </row>
     <row r="53" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
-        <f>IF(LEN(ContactData!H52)&lt;3,"",ContactData!H52)</f>
+        <f>IF(LEN(ContactData!H50)&lt;3,"",ContactData!H50)</f>
         <v>168</v>
       </c>
       <c r="B53" s="3" t="str">
-        <f>ContactData!E52</f>
+        <f>ContactData!E50</f>
         <v>Thomas Lee</v>
       </c>
       <c r="C53" s="3" t="str">
-        <f>ContactData!G52</f>
+        <f>ContactData!G50</f>
         <v>Assistant Property Manager</v>
       </c>
       <c r="D53" s="9" t="str">
-        <f>IF(LEN(ContactData!I52)&lt;3,"",ContactData!I52)</f>
+        <f>IF(LEN(ContactData!I50)&lt;3,"",ContactData!I50)</f>
         <v>(416) 567-4274</v>
       </c>
       <c r="E53" s="3" t="str">
-        <f>ContactData!J52</f>
+        <f>ContactData!J50</f>
         <v>(905) 477-2090</v>
       </c>
       <c r="F53" s="3" t="str">
-        <f>IF(LEN(ContactData!K52)&lt;3,"",ContactData!K52)</f>
+        <f>IF(LEN(ContactData!K50)&lt;3,"",ContactData!K50)</f>
         <v>Thomasl@livingproperties.com</v>
       </c>
       <c r="G53"/>
@@ -3730,27 +3706,27 @@
     </row>
     <row r="54" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
-        <f>IF(LEN(ContactData!H53)&lt;3,"",ContactData!H53)</f>
+        <f>IF(LEN(ContactData!H51)&lt;3,"",ContactData!H51)</f>
         <v>210</v>
       </c>
       <c r="B54" s="3" t="str">
-        <f>ContactData!E53</f>
+        <f>ContactData!E51</f>
         <v>Loretta Leung</v>
       </c>
       <c r="C54" s="3" t="str">
-        <f>ContactData!G53</f>
+        <f>ContactData!G51</f>
         <v>Executive Assistant</v>
       </c>
       <c r="D54" s="9" t="str">
-        <f>IF(LEN(ContactData!I53)&lt;3,"",ContactData!I53)</f>
+        <f>IF(LEN(ContactData!I51)&lt;3,"",ContactData!I51)</f>
         <v>---</v>
       </c>
       <c r="E54" s="3" t="str">
-        <f>ContactData!J53</f>
+        <f>ContactData!J51</f>
         <v>---</v>
       </c>
       <c r="F54" s="3" t="str">
-        <f>IF(LEN(ContactData!K53)&lt;3,"",ContactData!K53)</f>
+        <f>IF(LEN(ContactData!K51)&lt;3,"",ContactData!K51)</f>
         <v>lorettal@livingproperties.com</v>
       </c>
       <c r="G54"/>
@@ -3762,27 +3738,27 @@
     </row>
     <row r="55" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
-        <f>IF(LEN(ContactData!H54)&lt;3,"",ContactData!H54)</f>
+        <f>IF(LEN(ContactData!H52)&lt;3,"",ContactData!H52)</f>
         <v>518</v>
       </c>
       <c r="B55" s="3" t="str">
-        <f>ContactData!E54</f>
+        <f>ContactData!E52</f>
         <v>Simon Li</v>
       </c>
       <c r="C55" s="3" t="str">
-        <f>ContactData!G54</f>
+        <f>ContactData!G52</f>
         <v>Senior Accountant</v>
       </c>
       <c r="D55" s="9" t="str">
-        <f>IF(LEN(ContactData!I54)&lt;3,"",ContactData!I54)</f>
+        <f>IF(LEN(ContactData!I52)&lt;3,"",ContactData!I52)</f>
         <v>---</v>
       </c>
       <c r="E55" s="3" t="str">
-        <f>ContactData!J54</f>
+        <f>ContactData!J52</f>
         <v>(905) 752-3518</v>
       </c>
       <c r="F55" s="3" t="str">
-        <f>IF(LEN(ContactData!K54)&lt;3,"",ContactData!K54)</f>
+        <f>IF(LEN(ContactData!K52)&lt;3,"",ContactData!K52)</f>
         <v>simonl@livingproperties.com</v>
       </c>
       <c r="G55"/>
@@ -3794,27 +3770,27 @@
     </row>
     <row r="56" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
-        <f>IF(LEN(ContactData!H55)&lt;3,"",ContactData!H55)</f>
+        <f>IF(LEN(ContactData!H53)&lt;3,"",ContactData!H53)</f>
         <v>281</v>
       </c>
       <c r="B56" s="3" t="str">
-        <f>ContactData!E55</f>
+        <f>ContactData!E53</f>
         <v>Nicole Leung</v>
       </c>
       <c r="C56" s="3" t="str">
-        <f>ContactData!G55</f>
+        <f>ContactData!G53</f>
         <v>Property Accountant</v>
       </c>
       <c r="D56" s="9" t="str">
-        <f>IF(LEN(ContactData!I55)&lt;3,"",ContactData!I55)</f>
+        <f>IF(LEN(ContactData!I53)&lt;3,"",ContactData!I53)</f>
         <v>---</v>
       </c>
       <c r="E56" s="3" t="str">
-        <f>ContactData!J55</f>
+        <f>ContactData!J53</f>
         <v>---</v>
       </c>
       <c r="F56" s="3" t="str">
-        <f>IF(LEN(ContactData!K55)&lt;3,"",ContactData!K55)</f>
+        <f>IF(LEN(ContactData!K53)&lt;3,"",ContactData!K53)</f>
         <v>nicolel@livingproperties.com</v>
       </c>
       <c r="G56"/>
@@ -3826,27 +3802,27 @@
     </row>
     <row r="57" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
-        <f>IF(LEN(ContactData!H56)&lt;3,"",ContactData!H56)</f>
+        <f>IF(LEN(ContactData!H54)&lt;3,"",ContactData!H54)</f>
         <v>523</v>
       </c>
       <c r="B57" s="3" t="str">
-        <f>ContactData!E56</f>
+        <f>ContactData!E54</f>
         <v>Vivian Lum</v>
       </c>
       <c r="C57" s="3" t="str">
-        <f>ContactData!G56</f>
+        <f>ContactData!G54</f>
         <v>Accounts Receivable Clerk</v>
       </c>
       <c r="D57" s="9" t="str">
-        <f>IF(LEN(ContactData!I56)&lt;3,"",ContactData!I56)</f>
+        <f>IF(LEN(ContactData!I54)&lt;3,"",ContactData!I54)</f>
         <v>---</v>
       </c>
       <c r="E57" s="3" t="str">
-        <f>ContactData!J56</f>
+        <f>ContactData!J54</f>
         <v>(905) 752-3523</v>
       </c>
       <c r="F57" s="3" t="str">
-        <f>IF(LEN(ContactData!K56)&lt;3,"",ContactData!K56)</f>
+        <f>IF(LEN(ContactData!K54)&lt;3,"",ContactData!K54)</f>
         <v>vivianl@livingproperties.com</v>
       </c>
       <c r="G57"/>
@@ -3858,27 +3834,27 @@
     </row>
     <row r="58" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
-        <f>IF(LEN(ContactData!H57)&lt;3,"",ContactData!H57)</f>
+        <f>IF(LEN(ContactData!H55)&lt;3,"",ContactData!H55)</f>
         <v>223</v>
       </c>
       <c r="B58" s="3" t="str">
-        <f>ContactData!E57</f>
+        <f>ContactData!E55</f>
         <v>Jessica Lee</v>
       </c>
       <c r="C58" s="3" t="str">
-        <f>ContactData!G57</f>
+        <f>ContactData!G55</f>
         <v xml:space="preserve">Accounting Clerk </v>
       </c>
       <c r="D58" s="9" t="str">
-        <f>IF(LEN(ContactData!I57)&lt;3,"",ContactData!I57)</f>
+        <f>IF(LEN(ContactData!I55)&lt;3,"",ContactData!I55)</f>
         <v>---</v>
       </c>
       <c r="E58" s="3" t="str">
-        <f>ContactData!J57</f>
+        <f>ContactData!J55</f>
         <v>---</v>
       </c>
       <c r="F58" s="3" t="str">
-        <f>IF(LEN(ContactData!K57)&lt;3,"",ContactData!K57)</f>
+        <f>IF(LEN(ContactData!K55)&lt;3,"",ContactData!K55)</f>
         <v>jessical@livingproperties.com</v>
       </c>
       <c r="G58"/>
@@ -3890,27 +3866,27 @@
     </row>
     <row r="59" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
-        <f>IF(LEN(ContactData!H58)&lt;3,"",ContactData!H58)</f>
+        <f>IF(LEN(ContactData!H56)&lt;3,"",ContactData!H56)</f>
         <v>172</v>
       </c>
       <c r="B59" s="3" t="str">
-        <f>ContactData!E58</f>
+        <f>ContactData!E56</f>
         <v>Rebecca Lau</v>
       </c>
       <c r="C59" s="3" t="str">
-        <f>ContactData!G58</f>
+        <f>ContactData!G56</f>
         <v>Administrative Assistant</v>
       </c>
       <c r="D59" s="9" t="str">
-        <f>IF(LEN(ContactData!I58)&lt;3,"",ContactData!I58)</f>
+        <f>IF(LEN(ContactData!I56)&lt;3,"",ContactData!I56)</f>
         <v>---</v>
       </c>
       <c r="E59" s="3" t="str">
-        <f>ContactData!J58</f>
+        <f>ContactData!J56</f>
         <v>---</v>
       </c>
       <c r="F59" s="3" t="str">
-        <f>IF(LEN(ContactData!K58)&lt;3,"",ContactData!K58)</f>
+        <f>IF(LEN(ContactData!K56)&lt;3,"",ContactData!K56)</f>
         <v>rebeccal@livingproperties.com</v>
       </c>
       <c r="G59"/>
@@ -3922,27 +3898,27 @@
     </row>
     <row r="60" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
-        <f>IF(LEN(ContactData!H59)&lt;3,"",ContactData!H59)</f>
+        <f>IF(LEN(ContactData!H57)&lt;3,"",ContactData!H57)</f>
         <v>182</v>
       </c>
       <c r="B60" s="3" t="str">
-        <f>ContactData!E59</f>
+        <f>ContactData!E57</f>
         <v>Kelvin Chan</v>
       </c>
       <c r="C60" s="3" t="str">
-        <f>ContactData!G59</f>
+        <f>ContactData!G57</f>
         <v>Administrative Assistant</v>
       </c>
       <c r="D60" s="9" t="str">
-        <f>IF(LEN(ContactData!I59)&lt;3,"",ContactData!I59)</f>
+        <f>IF(LEN(ContactData!I57)&lt;3,"",ContactData!I57)</f>
         <v>---</v>
       </c>
       <c r="E60" s="3" t="str">
-        <f>ContactData!J59</f>
+        <f>ContactData!J57</f>
         <v>---</v>
       </c>
       <c r="F60" s="3" t="str">
-        <f>IF(LEN(ContactData!K59)&lt;3,"",ContactData!K59)</f>
+        <f>IF(LEN(ContactData!K57)&lt;3,"",ContactData!K57)</f>
         <v>kelvinc@livingproperties.com</v>
       </c>
       <c r="G60"/>
@@ -3954,27 +3930,27 @@
     </row>
     <row r="61" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="str">
-        <f>IF(LEN(ContactData!H60)&lt;3,"",ContactData!H60)</f>
+        <f>IF(LEN(ContactData!H58)&lt;3,"",ContactData!H58)</f>
         <v>---</v>
       </c>
       <c r="B61" s="3" t="str">
-        <f>ContactData!E60</f>
+        <f>ContactData!E58</f>
         <v>Calmaine Hewitt</v>
       </c>
       <c r="C61" s="3" t="str">
-        <f>ContactData!G60</f>
+        <f>ContactData!G58</f>
         <v>Handyman</v>
       </c>
       <c r="D61" s="9" t="str">
-        <f>IF(LEN(ContactData!I60)&lt;3,"",ContactData!I60)</f>
+        <f>IF(LEN(ContactData!I58)&lt;3,"",ContactData!I58)</f>
         <v>---</v>
       </c>
       <c r="E61" s="3" t="str">
-        <f>ContactData!J60</f>
+        <f>ContactData!J58</f>
         <v>(905) 477-2090</v>
       </c>
       <c r="F61" s="3" t="str">
-        <f>IF(LEN(ContactData!K60)&lt;3,"",ContactData!K60)</f>
+        <f>IF(LEN(ContactData!K58)&lt;3,"",ContactData!K58)</f>
         <v>calmaineh@livingproperties.com</v>
       </c>
       <c r="G61"/>
@@ -3986,27 +3962,27 @@
     </row>
     <row r="62" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
-        <f>IF(LEN(ContactData!H61)&lt;3,"",ContactData!H61)</f>
+        <f>IF(LEN(ContactData!H59)&lt;3,"",ContactData!H59)</f>
         <v>229</v>
       </c>
       <c r="B62" s="3" t="str">
-        <f>ContactData!E61</f>
+        <f>ContactData!E59</f>
         <v>Matthew Wong</v>
       </c>
       <c r="C62" s="3" t="str">
-        <f>ContactData!G61</f>
+        <f>ContactData!G59</f>
         <v>Accounting Clerk</v>
       </c>
       <c r="D62" s="9" t="str">
-        <f>IF(LEN(ContactData!I61)&lt;3,"",ContactData!I61)</f>
+        <f>IF(LEN(ContactData!I59)&lt;3,"",ContactData!I59)</f>
         <v>---</v>
       </c>
       <c r="E62" s="3" t="str">
-        <f>ContactData!J61</f>
+        <f>ContactData!J59</f>
         <v>---</v>
       </c>
       <c r="F62" s="3" t="str">
-        <f>IF(LEN(ContactData!K61)&lt;3,"",ContactData!K61)</f>
+        <f>IF(LEN(ContactData!K59)&lt;3,"",ContactData!K59)</f>
         <v>mattheww@livingproperties.com</v>
       </c>
       <c r="G62"/>
@@ -4018,27 +3994,27 @@
     </row>
     <row r="63" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A63" s="9" t="str">
-        <f>IF(LEN(ContactData!H62)&lt;3,"",ContactData!H62)</f>
+        <f>IF(LEN(ContactData!H60)&lt;3,"",ContactData!H60)</f>
         <v/>
       </c>
       <c r="B63" s="3" t="str">
-        <f>ContactData!E62</f>
+        <f>ContactData!E60</f>
         <v>Centro Towers Office</v>
       </c>
       <c r="C63" s="3" t="str">
-        <f>ContactData!G62</f>
+        <f>ContactData!G60</f>
         <v>25 Town Centre Crt, Scarborough, ON, M1P 0B4</v>
       </c>
       <c r="D63" s="9" t="str">
-        <f>IF(LEN(ContactData!I62)&lt;3,"",ContactData!I62)</f>
+        <f>IF(LEN(ContactData!I60)&lt;3,"",ContactData!I60)</f>
         <v/>
       </c>
       <c r="E63" s="3" t="str">
-        <f>ContactData!J62</f>
+        <f>ContactData!J60</f>
         <v>T: (416) 290-1242</v>
       </c>
       <c r="F63" s="3" t="str">
-        <f>IF(LEN(ContactData!K62)&lt;3,"",ContactData!K62)</f>
+        <f>IF(LEN(ContactData!K60)&lt;3,"",ContactData!K60)</f>
         <v/>
       </c>
       <c r="G63"/>
@@ -4050,27 +4026,27 @@
     </row>
     <row r="64" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="str">
-        <f>IF(LEN(ContactData!H63)&lt;3,"",ContactData!H63)</f>
+        <f>IF(LEN(ContactData!H61)&lt;3,"",ContactData!H61)</f>
         <v>---</v>
       </c>
       <c r="B64" s="3" t="str">
-        <f>ContactData!E63</f>
+        <f>ContactData!E61</f>
         <v>Henry Fu</v>
       </c>
       <c r="C64" s="3" t="str">
-        <f>ContactData!G63</f>
+        <f>ContactData!G61</f>
         <v>Property Manager</v>
       </c>
       <c r="D64" s="9" t="str">
-        <f>IF(LEN(ContactData!I63)&lt;3,"",ContactData!I63)</f>
+        <f>IF(LEN(ContactData!I61)&lt;3,"",ContactData!I61)</f>
         <v>(416) 278-2953</v>
       </c>
       <c r="E64" s="3" t="str">
-        <f>ContactData!J63</f>
+        <f>ContactData!J61</f>
         <v>(416) 290-1242</v>
       </c>
       <c r="F64" s="3" t="str">
-        <f>IF(LEN(ContactData!K63)&lt;3,"",ContactData!K63)</f>
+        <f>IF(LEN(ContactData!K61)&lt;3,"",ContactData!K61)</f>
         <v>henry@centrotowers.com</v>
       </c>
       <c r="G64"/>
@@ -4082,27 +4058,27 @@
     </row>
     <row r="65" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A65" s="9" t="str">
-        <f>IF(LEN(ContactData!H64)&lt;3,"",ContactData!H64)</f>
+        <f>IF(LEN(ContactData!H62)&lt;3,"",ContactData!H62)</f>
         <v>---</v>
       </c>
       <c r="B65" s="3" t="str">
-        <f>ContactData!E64</f>
+        <f>ContactData!E62</f>
         <v>Sophia Yip</v>
       </c>
       <c r="C65" s="3" t="str">
-        <f>ContactData!G64</f>
+        <f>ContactData!G62</f>
         <v>Property Administrator</v>
       </c>
       <c r="D65" s="9" t="str">
-        <f>IF(LEN(ContactData!I64)&lt;3,"",ContactData!I64)</f>
+        <f>IF(LEN(ContactData!I62)&lt;3,"",ContactData!I62)</f>
         <v>---</v>
       </c>
       <c r="E65" s="3" t="str">
-        <f>ContactData!J64</f>
+        <f>ContactData!J62</f>
         <v>(416) 290-1242</v>
       </c>
       <c r="F65" s="3" t="str">
-        <f>IF(LEN(ContactData!K64)&lt;3,"",ContactData!K64)</f>
+        <f>IF(LEN(ContactData!K62)&lt;3,"",ContactData!K62)</f>
         <v>sophia@centrotowers.com</v>
       </c>
       <c r="G65"/>
@@ -4114,27 +4090,27 @@
     </row>
     <row r="66" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="str">
-        <f>IF(LEN(ContactData!H65)&lt;3,"",ContactData!H65)</f>
+        <f>IF(LEN(ContactData!H63)&lt;3,"",ContactData!H63)</f>
         <v>---</v>
       </c>
       <c r="B66" s="3" t="str">
-        <f>ContactData!E65</f>
+        <f>ContactData!E63</f>
         <v xml:space="preserve">Security Desk </v>
       </c>
       <c r="C66" s="3" t="str">
-        <f>ContactData!G65</f>
+        <f>ContactData!G63</f>
         <v xml:space="preserve">Centro Security Desk </v>
       </c>
       <c r="D66" s="9" t="str">
-        <f>IF(LEN(ContactData!I65)&lt;3,"",ContactData!I65)</f>
+        <f>IF(LEN(ContactData!I63)&lt;3,"",ContactData!I63)</f>
         <v>---</v>
       </c>
       <c r="E66" s="3" t="str">
-        <f>ContactData!J65</f>
+        <f>ContactData!J63</f>
         <v>(416) 296-0099</v>
       </c>
       <c r="F66" s="3" t="str">
-        <f>IF(LEN(ContactData!K65)&lt;3,"",ContactData!K65)</f>
+        <f>IF(LEN(ContactData!K63)&lt;3,"",ContactData!K63)</f>
         <v>---</v>
       </c>
       <c r="G66"/>
@@ -4146,27 +4122,27 @@
     </row>
     <row r="67" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A67" s="9" t="str">
-        <f>IF(LEN(ContactData!H66)&lt;3,"",ContactData!H66)</f>
+        <f>IF(LEN(ContactData!H64)&lt;3,"",ContactData!H64)</f>
         <v/>
       </c>
       <c r="B67" s="3" t="str">
-        <f>ContactData!E66</f>
+        <f>ContactData!E64</f>
         <v>EQ1 Office</v>
       </c>
       <c r="C67" s="3" t="str">
-        <f>ContactData!G66</f>
+        <f>ContactData!G64</f>
         <v>70 Town Centre Court, Scarborough, ON, M1P 0B2</v>
       </c>
       <c r="D67" s="9" t="str">
-        <f>IF(LEN(ContactData!I66)&lt;3,"",ContactData!I66)</f>
+        <f>IF(LEN(ContactData!I64)&lt;3,"",ContactData!I64)</f>
         <v/>
       </c>
       <c r="E67" s="3" t="str">
-        <f>ContactData!J66</f>
+        <f>ContactData!J64</f>
         <v xml:space="preserve">T: (416) 279-0603 </v>
       </c>
       <c r="F67" s="3" t="str">
-        <f>IF(LEN(ContactData!K66)&lt;3,"",ContactData!K66)</f>
+        <f>IF(LEN(ContactData!K64)&lt;3,"",ContactData!K64)</f>
         <v>eq1@livingproperties.com</v>
       </c>
       <c r="G67"/>
@@ -4178,27 +4154,27 @@
     </row>
     <row r="68" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="str">
-        <f>IF(LEN(ContactData!H67)&lt;3,"",ContactData!H67)</f>
+        <f>IF(LEN(ContactData!H65)&lt;3,"",ContactData!H65)</f>
         <v>---</v>
       </c>
       <c r="B68" s="3" t="str">
-        <f>ContactData!E67</f>
+        <f>ContactData!E65</f>
         <v>Ming Ip</v>
       </c>
       <c r="C68" s="3" t="str">
-        <f>ContactData!G67</f>
+        <f>ContactData!G65</f>
         <v>Property Manager</v>
       </c>
       <c r="D68" s="9" t="str">
-        <f>IF(LEN(ContactData!I67)&lt;3,"",ContactData!I67)</f>
+        <f>IF(LEN(ContactData!I65)&lt;3,"",ContactData!I65)</f>
         <v>(647) 286-0147</v>
       </c>
       <c r="E68" s="3" t="str">
-        <f>ContactData!J67</f>
+        <f>ContactData!J65</f>
         <v xml:space="preserve">(416) 279-0603 </v>
       </c>
       <c r="F68" s="3" t="str">
-        <f>IF(LEN(ContactData!K67)&lt;3,"",ContactData!K67)</f>
+        <f>IF(LEN(ContactData!K65)&lt;3,"",ContactData!K65)</f>
         <v>eq1manager@livingproperties.com</v>
       </c>
       <c r="G68"/>
@@ -4210,27 +4186,27 @@
     </row>
     <row r="69" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A69" s="9" t="str">
-        <f>IF(LEN(ContactData!H68)&lt;3,"",ContactData!H68)</f>
+        <f>IF(LEN(ContactData!H66)&lt;3,"",ContactData!H66)</f>
         <v>---</v>
       </c>
       <c r="B69" s="3" t="str">
-        <f>ContactData!E68</f>
+        <f>ContactData!E66</f>
         <v xml:space="preserve">Security Desk </v>
       </c>
       <c r="C69" s="3" t="str">
-        <f>ContactData!G68</f>
+        <f>ContactData!G66</f>
         <v xml:space="preserve">EQ1 Security Desk </v>
       </c>
       <c r="D69" s="9" t="str">
-        <f>IF(LEN(ContactData!I68)&lt;3,"",ContactData!I68)</f>
+        <f>IF(LEN(ContactData!I66)&lt;3,"",ContactData!I66)</f>
         <v>---</v>
       </c>
       <c r="E69" s="3" t="str">
-        <f>ContactData!J68</f>
+        <f>ContactData!J66</f>
         <v>(416) 279-1894</v>
       </c>
       <c r="F69" s="3" t="str">
-        <f>IF(LEN(ContactData!K68)&lt;3,"",ContactData!K68)</f>
+        <f>IF(LEN(ContactData!K66)&lt;3,"",ContactData!K66)</f>
         <v>---</v>
       </c>
       <c r="G69"/>
@@ -4242,27 +4218,27 @@
     </row>
     <row r="70" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="str">
-        <f>IF(LEN(ContactData!H69)&lt;3,"",ContactData!H69)</f>
+        <f>IF(LEN(ContactData!H67)&lt;3,"",ContactData!H67)</f>
         <v/>
       </c>
       <c r="B70" s="3" t="str">
-        <f>ContactData!E69</f>
+        <f>ContactData!E67</f>
         <v>EQ2 Office</v>
       </c>
       <c r="C70" s="3" t="str">
-        <f>ContactData!G69</f>
+        <f>ContactData!G67</f>
         <v>60 Town Centre Court, Scarborough, ON, M1P 0B1</v>
       </c>
       <c r="D70" s="9" t="str">
-        <f>IF(LEN(ContactData!I69)&lt;3,"",ContactData!I69)</f>
+        <f>IF(LEN(ContactData!I67)&lt;3,"",ContactData!I67)</f>
         <v/>
       </c>
       <c r="E70" s="3" t="str">
-        <f>ContactData!J69</f>
+        <f>ContactData!J67</f>
         <v xml:space="preserve">T: (416) 279-0591 </v>
       </c>
       <c r="F70" s="3" t="str">
-        <f>IF(LEN(ContactData!K69)&lt;3,"",ContactData!K69)</f>
+        <f>IF(LEN(ContactData!K67)&lt;3,"",ContactData!K67)</f>
         <v/>
       </c>
       <c r="G70"/>
@@ -4274,27 +4250,27 @@
     </row>
     <row r="71" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="str">
-        <f>IF(LEN(ContactData!H70)&lt;3,"",ContactData!H70)</f>
+        <f>IF(LEN(ContactData!H68)&lt;3,"",ContactData!H68)</f>
         <v>---</v>
       </c>
       <c r="B71" s="3" t="str">
-        <f>ContactData!E70</f>
+        <f>ContactData!E68</f>
         <v>Aaron Ma</v>
       </c>
       <c r="C71" s="3" t="str">
-        <f>ContactData!G70</f>
+        <f>ContactData!G68</f>
         <v>Property Manager</v>
       </c>
       <c r="D71" s="9" t="str">
-        <f>IF(LEN(ContactData!I70)&lt;3,"",ContactData!I70)</f>
+        <f>IF(LEN(ContactData!I68)&lt;3,"",ContactData!I68)</f>
         <v>(416) 684-2236</v>
       </c>
       <c r="E71" s="3" t="str">
-        <f>ContactData!J70</f>
+        <f>ContactData!J68</f>
         <v>(416) 279-0591</v>
       </c>
       <c r="F71" s="3" t="str">
-        <f>IF(LEN(ContactData!K70)&lt;3,"",ContactData!K70)</f>
+        <f>IF(LEN(ContactData!K68)&lt;3,"",ContactData!K68)</f>
         <v>eq2manager@livingproperties.com</v>
       </c>
       <c r="G71"/>
@@ -4306,27 +4282,27 @@
     </row>
     <row r="72" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A72" s="9" t="str">
-        <f>IF(LEN(ContactData!H71)&lt;3,"",ContactData!H71)</f>
+        <f>IF(LEN(ContactData!H69)&lt;3,"",ContactData!H69)</f>
         <v>---</v>
       </c>
       <c r="B72" s="3" t="str">
-        <f>ContactData!E71</f>
+        <f>ContactData!E69</f>
         <v xml:space="preserve">Security Desk </v>
       </c>
       <c r="C72" s="3" t="str">
-        <f>ContactData!G71</f>
+        <f>ContactData!G69</f>
         <v xml:space="preserve">EQ2 Security Desk </v>
       </c>
       <c r="D72" s="9" t="str">
-        <f>IF(LEN(ContactData!I71)&lt;3,"",ContactData!I71)</f>
+        <f>IF(LEN(ContactData!I69)&lt;3,"",ContactData!I69)</f>
         <v>---</v>
       </c>
       <c r="E72" s="3" t="str">
-        <f>ContactData!J71</f>
+        <f>ContactData!J69</f>
         <v>(416) 279-1211</v>
       </c>
       <c r="F72" s="3" t="str">
-        <f>IF(LEN(ContactData!K71)&lt;3,"",ContactData!K71)</f>
+        <f>IF(LEN(ContactData!K69)&lt;3,"",ContactData!K69)</f>
         <v>---</v>
       </c>
       <c r="G72"/>
@@ -4338,27 +4314,27 @@
     </row>
     <row r="73" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A73" s="9" t="str">
-        <f>IF(LEN(ContactData!H72)&lt;3,"",ContactData!H72)</f>
+        <f>IF(LEN(ContactData!H70)&lt;3,"",ContactData!H70)</f>
         <v/>
       </c>
       <c r="B73" s="3" t="str">
-        <f>ContactData!E72</f>
+        <f>ContactData!E70</f>
         <v>Alton Tower Office</v>
       </c>
       <c r="C73" s="3" t="str">
-        <f>ContactData!G72</f>
+        <f>ContactData!G70</f>
         <v>160 Alton Towers Cir, Toronto, ON, M1V 4X8</v>
       </c>
       <c r="D73" s="9" t="str">
-        <f>IF(LEN(ContactData!I72)&lt;3,"",ContactData!I72)</f>
+        <f>IF(LEN(ContactData!I70)&lt;3,"",ContactData!I70)</f>
         <v/>
       </c>
       <c r="E73" s="3" t="str">
-        <f>ContactData!J72</f>
+        <f>ContactData!J70</f>
         <v>T: (437)-533-1208</v>
       </c>
       <c r="F73" s="3" t="str">
-        <f>IF(LEN(ContactData!K72)&lt;3,"",ContactData!K72)</f>
+        <f>IF(LEN(ContactData!K70)&lt;3,"",ContactData!K70)</f>
         <v/>
       </c>
       <c r="G73"/>
@@ -4370,27 +4346,27 @@
     </row>
     <row r="74" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A74" s="9" t="str">
-        <f>IF(LEN(ContactData!H73)&lt;3,"",ContactData!H73)</f>
+        <f>IF(LEN(ContactData!H71)&lt;3,"",ContactData!H71)</f>
         <v>---</v>
       </c>
       <c r="B74" s="3" t="str">
-        <f>ContactData!E73</f>
+        <f>ContactData!E71</f>
         <v>Ken Kam</v>
       </c>
       <c r="C74" s="3" t="str">
-        <f>ContactData!G73</f>
+        <f>ContactData!G71</f>
         <v>Property Manager</v>
       </c>
       <c r="D74" s="9" t="str">
-        <f>IF(LEN(ContactData!I73)&lt;3,"",ContactData!I73)</f>
+        <f>IF(LEN(ContactData!I71)&lt;3,"",ContactData!I71)</f>
         <v>(647) 204-4455</v>
       </c>
       <c r="E74" s="3" t="str">
-        <f>ContactData!J73</f>
+        <f>ContactData!J71</f>
         <v>(905) 477-2090</v>
       </c>
       <c r="F74" s="3" t="str">
-        <f>IF(LEN(ContactData!K73)&lt;3,"",ContactData!K73)</f>
+        <f>IF(LEN(ContactData!K71)&lt;3,"",ContactData!K71)</f>
         <v>kenk@livingproperties.com</v>
       </c>
       <c r="G74"/>
@@ -4402,27 +4378,27 @@
     </row>
     <row r="75" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A75" s="9" t="str">
-        <f>IF(LEN(ContactData!H74)&lt;3,"",ContactData!H74)</f>
+        <f>IF(LEN(ContactData!H72)&lt;3,"",ContactData!H72)</f>
         <v>---</v>
       </c>
       <c r="B75" s="3" t="str">
-        <f>ContactData!E74</f>
+        <f>ContactData!E72</f>
         <v>Christie Ip</v>
       </c>
       <c r="C75" s="3" t="str">
-        <f>ContactData!G74</f>
+        <f>ContactData!G72</f>
         <v>Administrative Assistant</v>
       </c>
       <c r="D75" s="9" t="str">
-        <f>IF(LEN(ContactData!I74)&lt;3,"",ContactData!I74)</f>
+        <f>IF(LEN(ContactData!I72)&lt;3,"",ContactData!I72)</f>
         <v>(437)-533-1208</v>
       </c>
       <c r="E75" s="3" t="str">
-        <f>ContactData!J74</f>
+        <f>ContactData!J72</f>
         <v>---</v>
       </c>
       <c r="F75" s="3" t="str">
-        <f>IF(LEN(ContactData!K74)&lt;3,"",ContactData!K74)</f>
+        <f>IF(LEN(ContactData!K72)&lt;3,"",ContactData!K72)</f>
         <v xml:space="preserve">optima2@livingproperties.com </v>
       </c>
       <c r="G75"/>
@@ -4434,27 +4410,27 @@
     </row>
     <row r="76" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A76" s="9" t="str">
-        <f>IF(LEN(ContactData!H75)&lt;3,"",ContactData!H75)</f>
+        <f>IF(LEN(ContactData!H73)&lt;3,"",ContactData!H73)</f>
         <v>---</v>
       </c>
       <c r="B76" s="3" t="str">
-        <f>ContactData!E75</f>
+        <f>ContactData!E73</f>
         <v xml:space="preserve">Security Desk </v>
       </c>
       <c r="C76" s="3" t="str">
-        <f>ContactData!G75</f>
+        <f>ContactData!G73</f>
         <v xml:space="preserve">Alton Tower Security Desk </v>
       </c>
       <c r="D76" s="9" t="str">
-        <f>IF(LEN(ContactData!I75)&lt;3,"",ContactData!I75)</f>
+        <f>IF(LEN(ContactData!I73)&lt;3,"",ContactData!I73)</f>
         <v>---</v>
       </c>
       <c r="E76" s="3" t="str">
-        <f>ContactData!J75</f>
+        <f>ContactData!J73</f>
         <v>(416) 754-3131</v>
       </c>
       <c r="F76" s="3" t="str">
-        <f>IF(LEN(ContactData!K75)&lt;3,"",ContactData!K75)</f>
+        <f>IF(LEN(ContactData!K73)&lt;3,"",ContactData!K73)</f>
         <v>---</v>
       </c>
       <c r="G76"/>
@@ -4466,27 +4442,27 @@
     </row>
     <row r="77" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A77" s="9" t="str">
-        <f>IF(LEN(ContactData!H76)&lt;3,"",ContactData!H76)</f>
+        <f>IF(LEN(ContactData!H74)&lt;3,"",ContactData!H74)</f>
         <v/>
       </c>
       <c r="B77" s="3" t="str">
-        <f>ContactData!E76</f>
+        <f>ContactData!E74</f>
         <v>IHMG Office</v>
       </c>
       <c r="C77" s="3" t="str">
-        <f>ContactData!G76</f>
+        <f>ContactData!G74</f>
         <v>8 Steelcase Road West, Markham, ON, L3R 1B2</v>
       </c>
       <c r="D77" s="9" t="str">
-        <f>IF(LEN(ContactData!I76)&lt;3,"",ContactData!I76)</f>
+        <f>IF(LEN(ContactData!I74)&lt;3,"",ContactData!I74)</f>
         <v/>
       </c>
       <c r="E77" s="3" t="str">
-        <f>ContactData!J76</f>
+        <f>ContactData!J74</f>
         <v>T: (905) 475-6000</v>
       </c>
       <c r="F77" s="3" t="str">
-        <f>IF(LEN(ContactData!K76)&lt;3,"",ContactData!K76)</f>
+        <f>IF(LEN(ContactData!K74)&lt;3,"",ContactData!K74)</f>
         <v>info@ihmg.ca</v>
       </c>
       <c r="G77"/>
@@ -4498,27 +4474,27 @@
     </row>
     <row r="78" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A78" s="9" t="str">
-        <f>IF(LEN(ContactData!H77)&lt;3,"",ContactData!H77)</f>
+        <f>IF(LEN(ContactData!H75)&lt;3,"",ContactData!H75)</f>
         <v/>
       </c>
       <c r="B78" s="3" t="str">
-        <f>ContactData!E77</f>
+        <f>ContactData!E75</f>
         <v>IHMGRI Office</v>
       </c>
       <c r="C78" s="3" t="str">
-        <f>ContactData!G77</f>
+        <f>ContactData!G75</f>
         <v>8 Steelcase Road West, Unit E, Markham, ON, L3R 1B2</v>
       </c>
       <c r="D78" s="9" t="str">
-        <f>IF(LEN(ContactData!I77)&lt;3,"",ContactData!I77)</f>
+        <f>IF(LEN(ContactData!I75)&lt;3,"",ContactData!I75)</f>
         <v/>
       </c>
       <c r="E78" s="3" t="str">
-        <f>ContactData!J77</f>
+        <f>ContactData!J75</f>
         <v>T: (905) 489-8989</v>
       </c>
       <c r="F78" s="3" t="str">
-        <f>IF(LEN(ContactData!K77)&lt;3,"",ContactData!K77)</f>
+        <f>IF(LEN(ContactData!K75)&lt;3,"",ContactData!K75)</f>
         <v>realestate@ihmg.ca</v>
       </c>
       <c r="G78"/>
@@ -4530,27 +4506,27 @@
     </row>
     <row r="79" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
-        <f>IF(LEN(ContactData!H78)&lt;3,"",ContactData!H78)</f>
+        <f>IF(LEN(ContactData!H76)&lt;3,"",ContactData!H76)</f>
         <v>120</v>
       </c>
       <c r="B79" s="3" t="str">
-        <f>ContactData!E78</f>
+        <f>ContactData!E76</f>
         <v>Eddie Tang</v>
       </c>
       <c r="C79" s="3" t="str">
-        <f>ContactData!G78</f>
+        <f>ContactData!G76</f>
         <v>Financial Controller</v>
       </c>
       <c r="D79" s="9" t="str">
-        <f>IF(LEN(ContactData!I78)&lt;3,"",ContactData!I78)</f>
+        <f>IF(LEN(ContactData!I76)&lt;3,"",ContactData!I76)</f>
         <v>(416) 723-8329</v>
       </c>
       <c r="E79" s="3" t="str">
-        <f>ContactData!J78</f>
+        <f>ContactData!J76</f>
         <v>(905) 489-0186</v>
       </c>
       <c r="F79" s="3" t="str">
-        <f>IF(LEN(ContactData!K78)&lt;3,"",ContactData!K78)</f>
+        <f>IF(LEN(ContactData!K76)&lt;3,"",ContactData!K76)</f>
         <v>eddie@ihmg.ca</v>
       </c>
       <c r="G79"/>
@@ -4562,27 +4538,27 @@
     </row>
     <row r="80" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
-        <f>IF(LEN(ContactData!H79)&lt;3,"",ContactData!H79)</f>
+        <f>IF(LEN(ContactData!H77)&lt;3,"",ContactData!H77)</f>
         <v>187</v>
       </c>
       <c r="B80" s="3" t="str">
-        <f>ContactData!E79</f>
+        <f>ContactData!E77</f>
         <v>Lily Hou</v>
       </c>
       <c r="C80" s="3" t="str">
-        <f>ContactData!G79</f>
+        <f>ContactData!G77</f>
         <v>Senior Accounting Analyst &amp; Operations Support</v>
       </c>
       <c r="D80" s="9" t="str">
-        <f>IF(LEN(ContactData!I79)&lt;3,"",ContactData!I79)</f>
+        <f>IF(LEN(ContactData!I77)&lt;3,"",ContactData!I77)</f>
         <v>(647) 774-8994</v>
       </c>
       <c r="E80" s="3" t="str">
-        <f>ContactData!J79</f>
+        <f>ContactData!J77</f>
         <v>---</v>
       </c>
       <c r="F80" s="3" t="str">
-        <f>IF(LEN(ContactData!K79)&lt;3,"",ContactData!K79)</f>
+        <f>IF(LEN(ContactData!K77)&lt;3,"",ContactData!K77)</f>
         <v>lily@ihmg.ca</v>
       </c>
       <c r="G80"/>
@@ -8661,7 +8637,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -8672,7 +8648,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>3</v>
@@ -9066,27 +9042,27 @@
     </row>
     <row r="16" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
-        <f>IF(LEN(ContactData!H15)&lt;3,"",ContactData!H15)</f>
+        <f>IF(LEN(ContactData!H16)&lt;3,"",ContactData!H16)</f>
         <v>123</v>
       </c>
       <c r="B16" s="3" t="str">
-        <f>ContactData!E15</f>
+        <f>ContactData!E16</f>
         <v>Wendy Chung</v>
       </c>
       <c r="C16" s="3" t="str">
-        <f>ContactData!G15</f>
+        <f>ContactData!G16</f>
         <v xml:space="preserve">Administration Officer </v>
       </c>
       <c r="D16" s="9" t="str">
-        <f>IF(LEN(ContactData!I15)&lt;3,"",ContactData!I15)</f>
+        <f>IF(LEN(ContactData!I16)&lt;3,"",ContactData!I16)</f>
         <v>---</v>
       </c>
       <c r="E16" s="3" t="str">
-        <f>ContactData!J15</f>
+        <f>ContactData!J16</f>
         <v>---</v>
       </c>
       <c r="F16" s="3" t="str">
-        <f>IF(LEN(ContactData!K15)&lt;3,"",ContactData!K15)</f>
+        <f>IF(LEN(ContactData!K16)&lt;3,"",ContactData!K16)</f>
         <v>wendychung@livingrealtykw.com</v>
       </c>
       <c r="G16"/>
@@ -9095,27 +9071,27 @@
     </row>
     <row r="17" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
-        <f>IF(LEN(ContactData!H16)&lt;3,"",ContactData!H16)</f>
+        <f>IF(LEN(ContactData!H17)&lt;3,"",ContactData!H17)</f>
         <v>206</v>
       </c>
       <c r="B17" s="3" t="str">
-        <f>ContactData!E16</f>
+        <f>ContactData!E17</f>
         <v>Benjamin Wong</v>
       </c>
       <c r="C17" s="3" t="str">
-        <f>ContactData!G16</f>
+        <f>ContactData!G17</f>
         <v>Assistant to the Broker of Record</v>
       </c>
       <c r="D17" s="9" t="str">
-        <f>IF(LEN(ContactData!I16)&lt;3,"",ContactData!I16)</f>
+        <f>IF(LEN(ContactData!I17)&lt;3,"",ContactData!I17)</f>
         <v>---</v>
       </c>
       <c r="E17" s="3" t="str">
-        <f>ContactData!J16</f>
+        <f>ContactData!J17</f>
         <v>---</v>
       </c>
       <c r="F17" s="3" t="str">
-        <f>IF(LEN(ContactData!K16)&lt;3,"",ContactData!K16)</f>
+        <f>IF(LEN(ContactData!K17)&lt;3,"",ContactData!K17)</f>
         <v>benjaminwongici@livingrealtykw.com</v>
       </c>
       <c r="G17"/>
@@ -9124,27 +9100,27 @@
     </row>
     <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
-        <f>IF(LEN(ContactData!H17)&lt;3,"",ContactData!H17)</f>
+        <f>IF(LEN(ContactData!H18)&lt;3,"",ContactData!H18)</f>
         <v>507</v>
       </c>
       <c r="B18" s="3" t="str">
-        <f>ContactData!E17</f>
+        <f>ContactData!E18</f>
         <v>Luvie Chao</v>
       </c>
       <c r="C18" s="3" t="str">
-        <f>ContactData!G17</f>
+        <f>ContactData!G18</f>
         <v>Senior Deal Administrator</v>
       </c>
       <c r="D18" s="9" t="str">
-        <f>IF(LEN(ContactData!I17)&lt;3,"",ContactData!I17)</f>
+        <f>IF(LEN(ContactData!I18)&lt;3,"",ContactData!I18)</f>
         <v>---</v>
       </c>
       <c r="E18" s="3" t="str">
-        <f>ContactData!J17</f>
+        <f>ContactData!J18</f>
         <v>(905) 752-3507</v>
       </c>
       <c r="F18" s="3" t="str">
-        <f>IF(LEN(ContactData!K17)&lt;3,"",ContactData!K17)</f>
+        <f>IF(LEN(ContactData!K18)&lt;3,"",ContactData!K18)</f>
         <v>luvie@livingrealtykw.com</v>
       </c>
       <c r="G18"/>
@@ -9153,27 +9129,27 @@
     </row>
     <row r="19" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
-        <f>IF(LEN(ContactData!H18)&lt;3,"",ContactData!H18)</f>
+        <f>IF(LEN(ContactData!H19)&lt;3,"",ContactData!H19)</f>
         <v>508</v>
       </c>
       <c r="B19" s="3" t="str">
-        <f>ContactData!E18</f>
+        <f>ContactData!E19</f>
         <v>Maria Leung</v>
       </c>
       <c r="C19" s="3" t="str">
-        <f>ContactData!G18</f>
+        <f>ContactData!G19</f>
         <v>Deal Administrator</v>
       </c>
       <c r="D19" s="9" t="str">
-        <f>IF(LEN(ContactData!I18)&lt;3,"",ContactData!I18)</f>
+        <f>IF(LEN(ContactData!I19)&lt;3,"",ContactData!I19)</f>
         <v>---</v>
       </c>
       <c r="E19" s="3" t="str">
-        <f>ContactData!J18</f>
+        <f>ContactData!J19</f>
         <v>(905) 752-3508</v>
       </c>
       <c r="F19" s="3" t="str">
-        <f>IF(LEN(ContactData!K18)&lt;3,"",ContactData!K18)</f>
+        <f>IF(LEN(ContactData!K19)&lt;3,"",ContactData!K19)</f>
         <v>marialeung@livingrealtykw.com</v>
       </c>
       <c r="G19"/>
@@ -9182,27 +9158,27 @@
     </row>
     <row r="20" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
-        <f>IF(LEN(ContactData!H19)&lt;3,"",ContactData!H19)</f>
+        <f>IF(LEN(ContactData!H20)&lt;3,"",ContactData!H20)</f>
         <v>255</v>
       </c>
       <c r="B20" s="3" t="str">
-        <f>ContactData!E19</f>
+        <f>ContactData!E20</f>
         <v>Ken Cheung</v>
       </c>
       <c r="C20" s="3" t="str">
-        <f>ContactData!G19</f>
+        <f>ContactData!G20</f>
         <v>Deal Administrator</v>
       </c>
       <c r="D20" s="9" t="str">
-        <f>IF(LEN(ContactData!I19)&lt;3,"",ContactData!I19)</f>
+        <f>IF(LEN(ContactData!I20)&lt;3,"",ContactData!I20)</f>
         <v>---</v>
       </c>
       <c r="E20" s="3" t="str">
-        <f>ContactData!J19</f>
+        <f>ContactData!J20</f>
         <v>---</v>
       </c>
       <c r="F20" s="3" t="str">
-        <f>IF(LEN(ContactData!K19)&lt;3,"",ContactData!K19)</f>
+        <f>IF(LEN(ContactData!K20)&lt;3,"",ContactData!K20)</f>
         <v>kencheung@livingrealtykw.com</v>
       </c>
       <c r="G20"/>
@@ -9211,27 +9187,27 @@
     </row>
     <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
-        <f>IF(LEN(ContactData!H20)&lt;3,"",ContactData!H20)</f>
+        <f>IF(LEN(ContactData!H21)&lt;3,"",ContactData!H21)</f>
         <v>506</v>
       </c>
       <c r="B21" s="3" t="str">
-        <f>ContactData!E20</f>
+        <f>ContactData!E21</f>
         <v>Connie Cheung</v>
       </c>
       <c r="C21" s="3" t="str">
-        <f>ContactData!G20</f>
+        <f>ContactData!G21</f>
         <v>Accounting Bookkeeper</v>
       </c>
       <c r="D21" s="9" t="str">
-        <f>IF(LEN(ContactData!I20)&lt;3,"",ContactData!I20)</f>
+        <f>IF(LEN(ContactData!I21)&lt;3,"",ContactData!I21)</f>
         <v>---</v>
       </c>
       <c r="E21" s="3" t="str">
-        <f>ContactData!J20</f>
+        <f>ContactData!J21</f>
         <v>(905) 752-3506</v>
       </c>
       <c r="F21" s="3" t="str">
-        <f>IF(LEN(ContactData!K20)&lt;3,"",ContactData!K20)</f>
+        <f>IF(LEN(ContactData!K21)&lt;3,"",ContactData!K21)</f>
         <v>conniecheung@livingrealtykw.com</v>
       </c>
       <c r="G21"/>
@@ -9240,27 +9216,27 @@
     </row>
     <row r="22" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
-        <f>IF(LEN(ContactData!H21)&lt;3,"",ContactData!H21)</f>
+        <f>IF(LEN(ContactData!H22)&lt;3,"",ContactData!H22)</f>
         <v>519</v>
       </c>
       <c r="B22" s="3" t="str">
-        <f>ContactData!E21</f>
+        <f>ContactData!E22</f>
         <v>Simon Chan</v>
       </c>
       <c r="C22" s="3" t="str">
-        <f>ContactData!G21</f>
+        <f>ContactData!G22</f>
         <v>Operations Assistant</v>
       </c>
       <c r="D22" s="9" t="str">
-        <f>IF(LEN(ContactData!I21)&lt;3,"",ContactData!I21)</f>
+        <f>IF(LEN(ContactData!I22)&lt;3,"",ContactData!I22)</f>
         <v>---</v>
       </c>
       <c r="E22" s="3" t="str">
-        <f>ContactData!J21</f>
+        <f>ContactData!J22</f>
         <v>(905) 752-3519</v>
       </c>
       <c r="F22" s="3" t="str">
-        <f>IF(LEN(ContactData!K21)&lt;3,"",ContactData!K21)</f>
+        <f>IF(LEN(ContactData!K22)&lt;3,"",ContactData!K22)</f>
         <v>simonchan@livingrealtykw.com</v>
       </c>
       <c r="G22"/>
@@ -9268,29 +9244,29 @@
       <c r="I22"/>
     </row>
     <row r="23" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="str">
-        <f>IF(LEN(ContactData!H22)&lt;3,"",ContactData!H22)</f>
-        <v>---</v>
-      </c>
-      <c r="B23" s="3" t="str">
-        <f>ContactData!E22</f>
-        <v>Ben Dowson</v>
-      </c>
-      <c r="C23" s="3" t="str">
-        <f>ContactData!G22</f>
-        <v>Digitial Marketing &amp; Web Developer</v>
-      </c>
-      <c r="D23" s="9" t="str">
-        <f>IF(LEN(ContactData!I22)&lt;3,"",ContactData!I22)</f>
-        <v>---</v>
-      </c>
-      <c r="E23" s="3" t="str">
-        <f>ContactData!J22</f>
-        <v>---</v>
-      </c>
-      <c r="F23" s="3" t="str">
-        <f>IF(LEN(ContactData!K22)&lt;3,"",ContactData!K22)</f>
-        <v>socialmedia@livingrealtykw.com</v>
+      <c r="A23" s="9" t="e">
+        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B23" s="3" t="e">
+        <f>ContactData!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C23" s="3" t="e">
+        <f>ContactData!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D23" s="9" t="e">
+        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E23" s="3" t="e">
+        <f>ContactData!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F23" s="3" t="e">
+        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
+        <v>#REF!</v>
       </c>
       <c r="G23"/>
       <c r="H23"/>
@@ -9535,7 +9511,7 @@
       </c>
       <c r="B32" s="3" t="str">
         <f>ContactData!E31</f>
-        <v>Hui Wang</v>
+        <v>Cassandra Pacitto</v>
       </c>
       <c r="C32" s="3" t="str">
         <f>ContactData!G31</f>
@@ -9543,7 +9519,7 @@
       </c>
       <c r="D32" s="9" t="str">
         <f>IF(LEN(ContactData!I31)&lt;3,"",ContactData!I31)</f>
-        <v>(416) 274-9789</v>
+        <v>(905) 896-0002</v>
       </c>
       <c r="E32" s="3" t="str">
         <f>ContactData!J31</f>
@@ -9551,36 +9527,36 @@
       </c>
       <c r="F32" s="3" t="str">
         <f>IF(LEN(ContactData!K31)&lt;3,"",ContactData!K31)</f>
-        <v>huiwang@livingrealtykw.com</v>
+        <v>cassandrapacitto@livingrealtykw.com</v>
       </c>
       <c r="G32"/>
       <c r="H32"/>
       <c r="I32"/>
     </row>
     <row r="33" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A33" s="9" t="str">
-        <f>IF(LEN(ContactData!H32)&lt;3,"",ContactData!H32)</f>
-        <v>---</v>
-      </c>
-      <c r="B33" s="3" t="str">
-        <f>ContactData!E32</f>
-        <v>Vasanthan Jeyapragasam</v>
-      </c>
-      <c r="C33" s="3" t="str">
-        <f>ContactData!G32</f>
-        <v>Secretary</v>
-      </c>
-      <c r="D33" s="9" t="str">
-        <f>IF(LEN(ContactData!I32)&lt;3,"",ContactData!I32)</f>
-        <v>---</v>
-      </c>
-      <c r="E33" s="3" t="str">
-        <f>ContactData!J32</f>
-        <v>(905) 896-0002</v>
-      </c>
-      <c r="F33" s="3" t="str">
-        <f>IF(LEN(ContactData!K32)&lt;3,"",ContactData!K32)</f>
-        <v>vasanthanj@livingrealtykw.com</v>
+      <c r="A33" s="9" t="e">
+        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B33" s="3" t="e">
+        <f>ContactData!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C33" s="3" t="e">
+        <f>ContactData!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D33" s="9" t="e">
+        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E33" s="3" t="e">
+        <f>ContactData!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F33" s="3" t="e">
+        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
+        <v>#REF!</v>
       </c>
       <c r="G33"/>
       <c r="H33"/>
@@ -9588,27 +9564,27 @@
     </row>
     <row r="34" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="str">
-        <f>IF(LEN(ContactData!H33)&lt;3,"",ContactData!H33)</f>
+        <f>IF(LEN(ContactData!H32)&lt;3,"",ContactData!H32)</f>
         <v>---</v>
       </c>
       <c r="B34" s="3" t="str">
-        <f>ContactData!E33</f>
+        <f>ContactData!E32</f>
         <v>Katie Wong</v>
       </c>
       <c r="C34" s="3" t="str">
-        <f>ContactData!G33</f>
+        <f>ContactData!G32</f>
         <v>Secretary</v>
       </c>
       <c r="D34" s="9" t="str">
-        <f>IF(LEN(ContactData!I33)&lt;3,"",ContactData!I33)</f>
+        <f>IF(LEN(ContactData!I32)&lt;3,"",ContactData!I32)</f>
         <v>---</v>
       </c>
       <c r="E34" s="3" t="str">
-        <f>ContactData!J33</f>
+        <f>ContactData!J32</f>
         <v>(905) 896-0002</v>
       </c>
       <c r="F34" s="3" t="str">
-        <f>IF(LEN(ContactData!K33)&lt;3,"",ContactData!K33)</f>
+        <f>IF(LEN(ContactData!K32)&lt;3,"",ContactData!K32)</f>
         <v>katiewong@livingrealtykw.com</v>
       </c>
       <c r="G34"/>
@@ -9617,27 +9593,27 @@
     </row>
     <row r="35" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="str">
-        <f>IF(LEN(ContactData!H34)&lt;3,"",ContactData!H34)</f>
+        <f>IF(LEN(ContactData!H33)&lt;3,"",ContactData!H33)</f>
         <v/>
       </c>
       <c r="B35" s="3" t="str">
-        <f>ContactData!E34</f>
+        <f>ContactData!E33</f>
         <v>Woodbine Office</v>
       </c>
       <c r="C35" s="3" t="str">
-        <f>ContactData!G34</f>
+        <f>ContactData!G33</f>
         <v>8 Steelcase Road West, Markham, ON, L3R 1B2</v>
       </c>
       <c r="D35" s="9" t="str">
-        <f>IF(LEN(ContactData!I34)&lt;3,"",ContactData!I34)</f>
+        <f>IF(LEN(ContactData!I33)&lt;3,"",ContactData!I33)</f>
         <v/>
       </c>
       <c r="E35" s="3" t="str">
-        <f>ContactData!J34</f>
+        <f>ContactData!J33</f>
         <v>T: (905) 474-0500</v>
       </c>
       <c r="F35" s="3" t="str">
-        <f>IF(LEN(ContactData!K34)&lt;3,"",ContactData!K34)</f>
+        <f>IF(LEN(ContactData!K33)&lt;3,"",ContactData!K33)</f>
         <v>woodbine@livingrealtykw.com</v>
       </c>
       <c r="G35"/>
@@ -9646,27 +9622,27 @@
     </row>
     <row r="36" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
-        <f>IF(LEN(ContactData!H35)&lt;3,"",ContactData!H35)</f>
+        <f>IF(LEN(ContactData!H34)&lt;3,"",ContactData!H34)</f>
         <v>176</v>
       </c>
       <c r="B36" s="3" t="str">
-        <f>ContactData!E35</f>
+        <f>ContactData!E34</f>
         <v>Anita Huang</v>
       </c>
       <c r="C36" s="3" t="str">
-        <f>ContactData!G35</f>
+        <f>ContactData!G34</f>
         <v>Manager Woobine Branch</v>
       </c>
       <c r="D36" s="9" t="str">
-        <f>IF(LEN(ContactData!I35)&lt;3,"",ContactData!I35)</f>
+        <f>IF(LEN(ContactData!I34)&lt;3,"",ContactData!I34)</f>
         <v>(416) 523-1888</v>
       </c>
       <c r="E36" s="3" t="str">
-        <f>ContactData!J35</f>
+        <f>ContactData!J34</f>
         <v>---</v>
       </c>
       <c r="F36" s="3" t="str">
-        <f>IF(LEN(ContactData!K35)&lt;3,"",ContactData!K35)</f>
+        <f>IF(LEN(ContactData!K34)&lt;3,"",ContactData!K34)</f>
         <v>anitahuang@livingrealtykw.com</v>
       </c>
       <c r="G36"/>
@@ -9675,28 +9651,28 @@
     </row>
     <row r="37" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
-        <f>IF(LEN(ContactData!H36)&lt;3,"",ContactData!H36)</f>
+        <f>IF(LEN(ContactData!H35)&lt;3,"",ContactData!H35)</f>
         <v>104</v>
       </c>
       <c r="B37" s="3" t="str">
-        <f>ContactData!E36</f>
-        <v>Jimmy Lo</v>
+        <f>ContactData!E35</f>
+        <v>Kim Jin</v>
       </c>
       <c r="C37" s="3" t="str">
-        <f>ContactData!G36</f>
+        <f>ContactData!G35</f>
         <v>Secretary</v>
       </c>
       <c r="D37" s="9" t="str">
-        <f>IF(LEN(ContactData!I36)&lt;3,"",ContactData!I36)</f>
+        <f>IF(LEN(ContactData!I35)&lt;3,"",ContactData!I35)</f>
         <v>---</v>
       </c>
       <c r="E37" s="3" t="str">
-        <f>ContactData!J36</f>
+        <f>ContactData!J35</f>
         <v>(905) 474-0500</v>
       </c>
       <c r="F37" s="3" t="str">
-        <f>IF(LEN(ContactData!K36)&lt;3,"",ContactData!K36)</f>
-        <v>jimmylo@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K35)&lt;3,"",ContactData!K35)</f>
+        <v>kimjin@livingrealtykw.com</v>
       </c>
       <c r="G37"/>
       <c r="H37"/>
@@ -9704,27 +9680,27 @@
     </row>
     <row r="38" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
-        <f>IF(LEN(ContactData!H37)&lt;3,"",ContactData!H37)</f>
+        <f>IF(LEN(ContactData!H36)&lt;3,"",ContactData!H36)</f>
         <v>100</v>
       </c>
       <c r="B38" s="3" t="str">
-        <f>ContactData!E37</f>
+        <f>ContactData!E36</f>
         <v>Savanna Joo</v>
       </c>
       <c r="C38" s="3" t="str">
-        <f>ContactData!G37</f>
+        <f>ContactData!G36</f>
         <v>Secretary</v>
       </c>
       <c r="D38" s="9" t="str">
-        <f>IF(LEN(ContactData!I37)&lt;3,"",ContactData!I37)</f>
+        <f>IF(LEN(ContactData!I36)&lt;3,"",ContactData!I36)</f>
         <v>---</v>
       </c>
       <c r="E38" s="3" t="str">
-        <f>ContactData!J37</f>
+        <f>ContactData!J36</f>
         <v>(905) 474-0500</v>
       </c>
       <c r="F38" s="3" t="str">
-        <f>IF(LEN(ContactData!K37)&lt;3,"",ContactData!K37)</f>
+        <f>IF(LEN(ContactData!K36)&lt;3,"",ContactData!K36)</f>
         <v>savannajoo@livingrealtykw.com</v>
       </c>
       <c r="G38"/>
@@ -9733,27 +9709,27 @@
     </row>
     <row r="39" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="str">
-        <f>IF(LEN(ContactData!H38)&lt;3,"",ContactData!H38)</f>
+        <f>IF(LEN(ContactData!H37)&lt;3,"",ContactData!H37)</f>
         <v/>
       </c>
       <c r="B39" s="3" t="str">
-        <f>ContactData!E38</f>
+        <f>ContactData!E37</f>
         <v>Yonge &amp; Eglinton Office</v>
       </c>
       <c r="C39" s="3" t="str">
-        <f>ContactData!G38</f>
+        <f>ContactData!G37</f>
         <v>2301 Yonge Street, Toronto, ON, M4P 2C6</v>
       </c>
       <c r="D39" s="9" t="str">
-        <f>IF(LEN(ContactData!I38)&lt;3,"",ContactData!I38)</f>
+        <f>IF(LEN(ContactData!I37)&lt;3,"",ContactData!I37)</f>
         <v/>
       </c>
       <c r="E39" s="3" t="str">
-        <f>ContactData!J38</f>
+        <f>ContactData!J37</f>
         <v>T: (416) 223-8833</v>
       </c>
       <c r="F39" s="3" t="str">
-        <f>IF(LEN(ContactData!K38)&lt;3,"",ContactData!K38)</f>
+        <f>IF(LEN(ContactData!K37)&lt;3,"",ContactData!K37)</f>
         <v>ye@livingrealtykw.com</v>
       </c>
       <c r="G39"/>
@@ -9762,27 +9738,27 @@
     </row>
     <row r="40" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="str">
-        <f>IF(LEN(ContactData!H39)&lt;3,"",ContactData!H39)</f>
+        <f>IF(LEN(ContactData!H38)&lt;3,"",ContactData!H38)</f>
         <v>---</v>
       </c>
       <c r="B40" s="3" t="str">
-        <f>ContactData!E39</f>
+        <f>ContactData!E38</f>
         <v xml:space="preserve">Tony Prochilo </v>
       </c>
       <c r="C40" s="3" t="str">
-        <f>ContactData!G39</f>
+        <f>ContactData!G38</f>
         <v>Manager Yonge &amp; Eglinton</v>
       </c>
       <c r="D40" s="9" t="str">
-        <f>IF(LEN(ContactData!I39)&lt;3,"",ContactData!I39)</f>
+        <f>IF(LEN(ContactData!I38)&lt;3,"",ContactData!I38)</f>
         <v>(416) 576-6312</v>
       </c>
       <c r="E40" s="3" t="str">
-        <f>ContactData!J39</f>
+        <f>ContactData!J38</f>
         <v>---</v>
       </c>
       <c r="F40" s="3" t="str">
-        <f>IF(LEN(ContactData!K39)&lt;3,"",ContactData!K39)</f>
+        <f>IF(LEN(ContactData!K38)&lt;3,"",ContactData!K38)</f>
         <v>tonyprochilo@livingrealtykw.com</v>
       </c>
       <c r="G40"/>
@@ -9791,27 +9767,27 @@
     </row>
     <row r="41" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="str">
-        <f>IF(LEN(ContactData!H40)&lt;3,"",ContactData!H40)</f>
+        <f>IF(LEN(ContactData!H39)&lt;3,"",ContactData!H39)</f>
         <v>---</v>
       </c>
       <c r="B41" s="3" t="str">
-        <f>ContactData!E40</f>
+        <f>ContactData!E39</f>
         <v>Lydia Ng</v>
       </c>
       <c r="C41" s="3" t="str">
-        <f>ContactData!G40</f>
+        <f>ContactData!G39</f>
         <v>Secretary</v>
       </c>
       <c r="D41" s="9" t="str">
-        <f>IF(LEN(ContactData!I40)&lt;3,"",ContactData!I40)</f>
+        <f>IF(LEN(ContactData!I39)&lt;3,"",ContactData!I39)</f>
         <v>---</v>
       </c>
       <c r="E41" s="3" t="str">
-        <f>ContactData!J40</f>
+        <f>ContactData!J39</f>
         <v>(416) 223-8833</v>
       </c>
       <c r="F41" s="3" t="str">
-        <f>IF(LEN(ContactData!K40)&lt;3,"",ContactData!K40)</f>
+        <f>IF(LEN(ContactData!K39)&lt;3,"",ContactData!K39)</f>
         <v>lydiang@livingrealtykw.com</v>
       </c>
       <c r="G41"/>
@@ -9820,27 +9796,27 @@
     </row>
     <row r="42" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="str">
-        <f>IF(LEN(ContactData!H41)&lt;3,"",ContactData!H41)</f>
+        <f>IF(LEN(ContactData!H40)&lt;3,"",ContactData!H40)</f>
         <v/>
       </c>
       <c r="B42" s="3" t="str">
-        <f>ContactData!E41</f>
+        <f>ContactData!E40</f>
         <v>I.C.&amp;I. Office</v>
       </c>
       <c r="C42" s="3" t="str">
-        <f>ContactData!G41</f>
+        <f>ContactData!G40</f>
         <v>8 Steelcase Road West, Unit C, Markham, ON, L3R 1B2</v>
       </c>
       <c r="D42" s="9" t="str">
-        <f>IF(LEN(ContactData!I41)&lt;3,"",ContactData!I41)</f>
+        <f>IF(LEN(ContactData!I40)&lt;3,"",ContactData!I40)</f>
         <v/>
       </c>
       <c r="E42" s="3" t="str">
-        <f>ContactData!J41</f>
+        <f>ContactData!J40</f>
         <v>T: (905) 474-1772</v>
       </c>
       <c r="F42" s="3" t="str">
-        <f>IF(LEN(ContactData!K41)&lt;3,"",ContactData!K41)</f>
+        <f>IF(LEN(ContactData!K40)&lt;3,"",ContactData!K40)</f>
         <v/>
       </c>
       <c r="G42"/>
@@ -9849,27 +9825,27 @@
     </row>
     <row r="43" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A43" s="9">
-        <f>IF(LEN(ContactData!H42)&lt;3,"",ContactData!H42)</f>
+        <f>IF(LEN(ContactData!H41)&lt;3,"",ContactData!H41)</f>
         <v>228</v>
       </c>
       <c r="B43" s="3" t="str">
-        <f>ContactData!E42</f>
+        <f>ContactData!E41</f>
         <v>Kelvin Wong</v>
       </c>
       <c r="C43" s="3" t="str">
-        <f>ContactData!G42</f>
+        <f>ContactData!G41</f>
         <v>Manager I.C.&amp;I. Branch</v>
       </c>
       <c r="D43" s="9" t="str">
-        <f>IF(LEN(ContactData!I42)&lt;3,"",ContactData!I42)</f>
+        <f>IF(LEN(ContactData!I41)&lt;3,"",ContactData!I41)</f>
         <v>(416) 567-7882</v>
       </c>
       <c r="E43" s="3" t="str">
-        <f>ContactData!J42</f>
+        <f>ContactData!J41</f>
         <v>---</v>
       </c>
       <c r="F43" s="3" t="str">
-        <f>IF(LEN(ContactData!K42)&lt;3,"",ContactData!K42)</f>
+        <f>IF(LEN(ContactData!K41)&lt;3,"",ContactData!K41)</f>
         <v>kelvin@livingrealtykw.com</v>
       </c>
       <c r="G43"/>
@@ -9878,27 +9854,27 @@
     </row>
     <row r="44" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="str">
-        <f>IF(LEN(ContactData!H43)&lt;3,"",ContactData!H43)</f>
+        <f>IF(LEN(ContactData!H42)&lt;3,"",ContactData!H42)</f>
         <v/>
       </c>
       <c r="B44" s="3" t="str">
-        <f>ContactData!E43</f>
+        <f>ContactData!E42</f>
         <v>LPI Head Office</v>
       </c>
       <c r="C44" s="3" t="str">
-        <f>ContactData!G43</f>
+        <f>ContactData!G42</f>
         <v>8 Steelcase Road West, Markham, ON, L3R 1B2</v>
       </c>
       <c r="D44" s="9" t="str">
-        <f>IF(LEN(ContactData!I43)&lt;3,"",ContactData!I43)</f>
+        <f>IF(LEN(ContactData!I42)&lt;3,"",ContactData!I42)</f>
         <v/>
       </c>
       <c r="E44" s="3" t="str">
-        <f>ContactData!J43</f>
+        <f>ContactData!J42</f>
         <v>T: (905) 477-2090</v>
       </c>
       <c r="F44" s="3" t="str">
-        <f>IF(LEN(ContactData!K43)&lt;3,"",ContactData!K43)</f>
+        <f>IF(LEN(ContactData!K42)&lt;3,"",ContactData!K42)</f>
         <v/>
       </c>
       <c r="G44"/>
@@ -9907,27 +9883,27 @@
     </row>
     <row r="45" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A45" s="9">
-        <f>IF(LEN(ContactData!H44)&lt;3,"",ContactData!H44)</f>
+        <f>IF(LEN(ContactData!H43)&lt;3,"",ContactData!H43)</f>
         <v>521</v>
       </c>
       <c r="B45" s="3" t="str">
-        <f>ContactData!E44</f>
+        <f>ContactData!E43</f>
         <v>Ben Wong</v>
       </c>
       <c r="C45" s="3" t="str">
-        <f>ContactData!G44</f>
+        <f>ContactData!G43</f>
         <v>President</v>
       </c>
       <c r="D45" s="9" t="str">
-        <f>IF(LEN(ContactData!I44)&lt;3,"",ContactData!I44)</f>
+        <f>IF(LEN(ContactData!I43)&lt;3,"",ContactData!I43)</f>
         <v>(416) 399-2311</v>
       </c>
       <c r="E45" s="3" t="str">
-        <f>ContactData!J44</f>
+        <f>ContactData!J43</f>
         <v>(905) 752-3521</v>
       </c>
       <c r="F45" s="3" t="str">
-        <f>IF(LEN(ContactData!K44)&lt;3,"",ContactData!K44)</f>
+        <f>IF(LEN(ContactData!K43)&lt;3,"",ContactData!K43)</f>
         <v>benw@livingproperties.com</v>
       </c>
       <c r="G45"/>
@@ -9936,27 +9912,27 @@
     </row>
     <row r="46" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A46" s="9">
-        <f>IF(LEN(ContactData!H45)&lt;3,"",ContactData!H45)</f>
+        <f>IF(LEN(ContactData!H44)&lt;3,"",ContactData!H44)</f>
         <v>514</v>
       </c>
       <c r="B46" s="3" t="str">
-        <f>ContactData!E45</f>
+        <f>ContactData!E44</f>
         <v>Winnie Tsui</v>
       </c>
       <c r="C46" s="3" t="str">
-        <f>ContactData!G45</f>
+        <f>ContactData!G44</f>
         <v>Director of Operations</v>
       </c>
       <c r="D46" s="9" t="str">
-        <f>IF(LEN(ContactData!I45)&lt;3,"",ContactData!I45)</f>
+        <f>IF(LEN(ContactData!I44)&lt;3,"",ContactData!I44)</f>
         <v>(647) 286-0145</v>
       </c>
       <c r="E46" s="3" t="str">
-        <f>ContactData!J45</f>
+        <f>ContactData!J44</f>
         <v xml:space="preserve">(905) 752-3514 </v>
       </c>
       <c r="F46" s="3" t="str">
-        <f>IF(LEN(ContactData!K45)&lt;3,"",ContactData!K45)</f>
+        <f>IF(LEN(ContactData!K44)&lt;3,"",ContactData!K44)</f>
         <v>winniet@livingproperties.com</v>
       </c>
       <c r="G46"/>
@@ -9965,27 +9941,27 @@
     </row>
     <row r="47" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
-        <f>IF(LEN(ContactData!H46)&lt;3,"",ContactData!H46)</f>
+        <f>IF(LEN(ContactData!H45)&lt;3,"",ContactData!H45)</f>
         <v>286</v>
       </c>
       <c r="B47" s="3" t="str">
-        <f>ContactData!E46</f>
+        <f>ContactData!E45</f>
         <v>Frederick Tang</v>
       </c>
       <c r="C47" s="3" t="str">
-        <f>ContactData!G46</f>
+        <f>ContactData!G45</f>
         <v>Director of Business Development</v>
       </c>
       <c r="D47" s="9" t="str">
-        <f>IF(LEN(ContactData!I46)&lt;3,"",ContactData!I46)</f>
+        <f>IF(LEN(ContactData!I45)&lt;3,"",ContactData!I45)</f>
         <v>(416) 618-5898</v>
       </c>
       <c r="E47" s="3" t="str">
-        <f>ContactData!J46</f>
+        <f>ContactData!J45</f>
         <v>-</v>
       </c>
       <c r="F47" s="3" t="str">
-        <f>IF(LEN(ContactData!K46)&lt;3,"",ContactData!K46)</f>
+        <f>IF(LEN(ContactData!K45)&lt;3,"",ContactData!K45)</f>
         <v>fredt@livingproperties.com</v>
       </c>
       <c r="G47"/>
@@ -9993,29 +9969,29 @@
       <c r="I47"/>
     </row>
     <row r="48" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A48" s="9">
-        <f>IF(LEN(ContactData!H47)&lt;3,"",ContactData!H47)</f>
-        <v>516</v>
-      </c>
-      <c r="B48" s="3" t="str">
-        <f>ContactData!E47</f>
-        <v>Karl Park</v>
-      </c>
-      <c r="C48" s="3" t="str">
-        <f>ContactData!G47</f>
-        <v>Senior Property Manager</v>
-      </c>
-      <c r="D48" s="9" t="str">
-        <f>IF(LEN(ContactData!I47)&lt;3,"",ContactData!I47)</f>
-        <v>(647) 286-0142</v>
-      </c>
-      <c r="E48" s="3" t="str">
-        <f>ContactData!J47</f>
-        <v>(905) 752-3516</v>
-      </c>
-      <c r="F48" s="3" t="str">
-        <f>IF(LEN(ContactData!K47)&lt;3,"",ContactData!K47)</f>
-        <v>karlp@livingproperties.com</v>
+      <c r="A48" s="9" t="e">
+        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B48" s="3" t="e">
+        <f>ContactData!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C48" s="3" t="e">
+        <f>ContactData!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D48" s="9" t="e">
+        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="E48" s="3" t="e">
+        <f>ContactData!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F48" s="3" t="e">
+        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
+        <v>#REF!</v>
       </c>
       <c r="G48"/>
       <c r="H48"/>
@@ -10023,27 +9999,27 @@
     </row>
     <row r="49" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
-        <f>IF(LEN(ContactData!H48)&lt;3,"",ContactData!H48)</f>
+        <f>IF(LEN(ContactData!H46)&lt;3,"",ContactData!H46)</f>
         <v>512</v>
       </c>
       <c r="B49" s="3" t="str">
-        <f>ContactData!E48</f>
+        <f>ContactData!E46</f>
         <v>Stanley Chow</v>
       </c>
       <c r="C49" s="3" t="str">
-        <f>ContactData!G48</f>
+        <f>ContactData!G46</f>
         <v>Property Manager</v>
       </c>
       <c r="D49" s="9" t="str">
-        <f>IF(LEN(ContactData!I48)&lt;3,"",ContactData!I48)</f>
+        <f>IF(LEN(ContactData!I46)&lt;3,"",ContactData!I46)</f>
         <v>(416) 277-6098</v>
       </c>
       <c r="E49" s="3" t="str">
-        <f>ContactData!J48</f>
+        <f>ContactData!J46</f>
         <v>(905) 752-3512</v>
       </c>
       <c r="F49" s="3" t="str">
-        <f>IF(LEN(ContactData!K48)&lt;3,"",ContactData!K48)</f>
+        <f>IF(LEN(ContactData!K46)&lt;3,"",ContactData!K46)</f>
         <v>stanleyc@livingproperties.com</v>
       </c>
       <c r="G49"/>
@@ -10052,27 +10028,27 @@
     </row>
     <row r="50" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A50" s="9">
-        <f>IF(LEN(ContactData!H49)&lt;3,"",ContactData!H49)</f>
+        <f>IF(LEN(ContactData!H47)&lt;3,"",ContactData!H47)</f>
         <v>284</v>
       </c>
       <c r="B50" s="3" t="str">
-        <f>ContactData!E49</f>
+        <f>ContactData!E47</f>
         <v>Richard Baksh</v>
       </c>
       <c r="C50" s="3" t="str">
-        <f>ContactData!G49</f>
+        <f>ContactData!G47</f>
         <v>Property Manager</v>
       </c>
       <c r="D50" s="9" t="str">
-        <f>IF(LEN(ContactData!I49)&lt;3,"",ContactData!I49)</f>
+        <f>IF(LEN(ContactData!I47)&lt;3,"",ContactData!I47)</f>
         <v>(647) 967-0088</v>
       </c>
       <c r="E50" s="3" t="str">
-        <f>ContactData!J49</f>
+        <f>ContactData!J47</f>
         <v>(905) 258-0632</v>
       </c>
       <c r="F50" s="3" t="str">
-        <f>IF(LEN(ContactData!K49)&lt;3,"",ContactData!K49)</f>
+        <f>IF(LEN(ContactData!K47)&lt;3,"",ContactData!K47)</f>
         <v>richardb@livingproperties.com</v>
       </c>
       <c r="G50"/>
@@ -10081,27 +10057,27 @@
     </row>
     <row r="51" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
-        <f>IF(LEN(ContactData!H50)&lt;3,"",ContactData!H50)</f>
+        <f>IF(LEN(ContactData!H48)&lt;3,"",ContactData!H48)</f>
         <v>517</v>
       </c>
       <c r="B51" s="3" t="str">
-        <f>ContactData!E50</f>
+        <f>ContactData!E48</f>
         <v>Ken Kam</v>
       </c>
       <c r="C51" s="3" t="str">
-        <f>ContactData!G50</f>
+        <f>ContactData!G48</f>
         <v>Property Manager</v>
       </c>
       <c r="D51" s="9" t="str">
-        <f>IF(LEN(ContactData!I50)&lt;3,"",ContactData!I50)</f>
+        <f>IF(LEN(ContactData!I48)&lt;3,"",ContactData!I48)</f>
         <v>(647) 204-4455</v>
       </c>
       <c r="E51" s="3" t="str">
-        <f>ContactData!J50</f>
+        <f>ContactData!J48</f>
         <v>(905) 477-2090</v>
       </c>
       <c r="F51" s="3" t="str">
-        <f>IF(LEN(ContactData!K50)&lt;3,"",ContactData!K50)</f>
+        <f>IF(LEN(ContactData!K48)&lt;3,"",ContactData!K48)</f>
         <v>kenk@livingproperties.com</v>
       </c>
       <c r="G51"/>
@@ -10110,27 +10086,27 @@
     </row>
     <row r="52" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
-        <f>IF(LEN(ContactData!H51)&lt;3,"",ContactData!H51)</f>
+        <f>IF(LEN(ContactData!H49)&lt;3,"",ContactData!H49)</f>
         <v>520</v>
       </c>
       <c r="B52" s="3" t="str">
-        <f>ContactData!E51</f>
+        <f>ContactData!E49</f>
         <v>Raymond Chin</v>
       </c>
       <c r="C52" s="3" t="str">
-        <f>ContactData!G51</f>
+        <f>ContactData!G49</f>
         <v>Property Manager</v>
       </c>
       <c r="D52" s="9" t="str">
-        <f>IF(LEN(ContactData!I51)&lt;3,"",ContactData!I51)</f>
+        <f>IF(LEN(ContactData!I49)&lt;3,"",ContactData!I49)</f>
         <v>(437) 331-6038</v>
       </c>
       <c r="E52" s="3" t="str">
-        <f>ContactData!J51</f>
+        <f>ContactData!J49</f>
         <v>(905) 477-2090</v>
       </c>
       <c r="F52" s="3" t="str">
-        <f>IF(LEN(ContactData!K51)&lt;3,"",ContactData!K51)</f>
+        <f>IF(LEN(ContactData!K49)&lt;3,"",ContactData!K49)</f>
         <v>raymondc@livingproperties.com</v>
       </c>
       <c r="G52"/>
@@ -10139,27 +10115,27 @@
     </row>
     <row r="53" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
-        <f>IF(LEN(ContactData!H52)&lt;3,"",ContactData!H52)</f>
+        <f>IF(LEN(ContactData!H50)&lt;3,"",ContactData!H50)</f>
         <v>168</v>
       </c>
       <c r="B53" s="3" t="str">
-        <f>ContactData!E52</f>
+        <f>ContactData!E50</f>
         <v>Thomas Lee</v>
       </c>
       <c r="C53" s="3" t="str">
-        <f>ContactData!G52</f>
+        <f>ContactData!G50</f>
         <v>Assistant Property Manager</v>
       </c>
       <c r="D53" s="9" t="str">
-        <f>IF(LEN(ContactData!I52)&lt;3,"",ContactData!I52)</f>
+        <f>IF(LEN(ContactData!I50)&lt;3,"",ContactData!I50)</f>
         <v>(416) 567-4274</v>
       </c>
       <c r="E53" s="3" t="str">
-        <f>ContactData!J52</f>
+        <f>ContactData!J50</f>
         <v>(905) 477-2090</v>
       </c>
       <c r="F53" s="3" t="str">
-        <f>IF(LEN(ContactData!K52)&lt;3,"",ContactData!K52)</f>
+        <f>IF(LEN(ContactData!K50)&lt;3,"",ContactData!K50)</f>
         <v>Thomasl@livingproperties.com</v>
       </c>
       <c r="G53"/>
@@ -10168,27 +10144,27 @@
     </row>
     <row r="54" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
-        <f>IF(LEN(ContactData!H53)&lt;3,"",ContactData!H53)</f>
+        <f>IF(LEN(ContactData!H51)&lt;3,"",ContactData!H51)</f>
         <v>210</v>
       </c>
       <c r="B54" s="3" t="str">
-        <f>ContactData!E53</f>
+        <f>ContactData!E51</f>
         <v>Loretta Leung</v>
       </c>
       <c r="C54" s="3" t="str">
-        <f>ContactData!G53</f>
+        <f>ContactData!G51</f>
         <v>Executive Assistant</v>
       </c>
       <c r="D54" s="9" t="str">
-        <f>IF(LEN(ContactData!I53)&lt;3,"",ContactData!I53)</f>
+        <f>IF(LEN(ContactData!I51)&lt;3,"",ContactData!I51)</f>
         <v>---</v>
       </c>
       <c r="E54" s="3" t="str">
-        <f>ContactData!J53</f>
+        <f>ContactData!J51</f>
         <v>---</v>
       </c>
       <c r="F54" s="3" t="str">
-        <f>IF(LEN(ContactData!K53)&lt;3,"",ContactData!K53)</f>
+        <f>IF(LEN(ContactData!K51)&lt;3,"",ContactData!K51)</f>
         <v>lorettal@livingproperties.com</v>
       </c>
       <c r="G54"/>
@@ -10197,27 +10173,27 @@
     </row>
     <row r="55" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
-        <f>IF(LEN(ContactData!H54)&lt;3,"",ContactData!H54)</f>
+        <f>IF(LEN(ContactData!H52)&lt;3,"",ContactData!H52)</f>
         <v>518</v>
       </c>
       <c r="B55" s="3" t="str">
-        <f>ContactData!E54</f>
+        <f>ContactData!E52</f>
         <v>Simon Li</v>
       </c>
       <c r="C55" s="3" t="str">
-        <f>ContactData!G54</f>
+        <f>ContactData!G52</f>
         <v>Senior Accountant</v>
       </c>
       <c r="D55" s="9" t="str">
-        <f>IF(LEN(ContactData!I54)&lt;3,"",ContactData!I54)</f>
+        <f>IF(LEN(ContactData!I52)&lt;3,"",ContactData!I52)</f>
         <v>---</v>
       </c>
       <c r="E55" s="3" t="str">
-        <f>ContactData!J54</f>
+        <f>ContactData!J52</f>
         <v>(905) 752-3518</v>
       </c>
       <c r="F55" s="3" t="str">
-        <f>IF(LEN(ContactData!K54)&lt;3,"",ContactData!K54)</f>
+        <f>IF(LEN(ContactData!K52)&lt;3,"",ContactData!K52)</f>
         <v>simonl@livingproperties.com</v>
       </c>
       <c r="G55"/>
@@ -10226,27 +10202,27 @@
     </row>
     <row r="56" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
-        <f>IF(LEN(ContactData!H55)&lt;3,"",ContactData!H55)</f>
+        <f>IF(LEN(ContactData!H53)&lt;3,"",ContactData!H53)</f>
         <v>281</v>
       </c>
       <c r="B56" s="3" t="str">
-        <f>ContactData!E55</f>
+        <f>ContactData!E53</f>
         <v>Nicole Leung</v>
       </c>
       <c r="C56" s="3" t="str">
-        <f>ContactData!G55</f>
+        <f>ContactData!G53</f>
         <v>Property Accountant</v>
       </c>
       <c r="D56" s="9" t="str">
-        <f>IF(LEN(ContactData!I55)&lt;3,"",ContactData!I55)</f>
+        <f>IF(LEN(ContactData!I53)&lt;3,"",ContactData!I53)</f>
         <v>---</v>
       </c>
       <c r="E56" s="3" t="str">
-        <f>ContactData!J55</f>
+        <f>ContactData!J53</f>
         <v>---</v>
       </c>
       <c r="F56" s="3" t="str">
-        <f>IF(LEN(ContactData!K55)&lt;3,"",ContactData!K55)</f>
+        <f>IF(LEN(ContactData!K53)&lt;3,"",ContactData!K53)</f>
         <v>nicolel@livingproperties.com</v>
       </c>
       <c r="G56"/>
@@ -10255,27 +10231,27 @@
     </row>
     <row r="57" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
-        <f>IF(LEN(ContactData!H56)&lt;3,"",ContactData!H56)</f>
+        <f>IF(LEN(ContactData!H54)&lt;3,"",ContactData!H54)</f>
         <v>523</v>
       </c>
       <c r="B57" s="3" t="str">
-        <f>ContactData!E56</f>
+        <f>ContactData!E54</f>
         <v>Vivian Lum</v>
       </c>
       <c r="C57" s="3" t="str">
-        <f>ContactData!G56</f>
+        <f>ContactData!G54</f>
         <v>Accounts Receivable Clerk</v>
       </c>
       <c r="D57" s="9" t="str">
-        <f>IF(LEN(ContactData!I56)&lt;3,"",ContactData!I56)</f>
+        <f>IF(LEN(ContactData!I54)&lt;3,"",ContactData!I54)</f>
         <v>---</v>
       </c>
       <c r="E57" s="3" t="str">
-        <f>ContactData!J56</f>
+        <f>ContactData!J54</f>
         <v>(905) 752-3523</v>
       </c>
       <c r="F57" s="3" t="str">
-        <f>IF(LEN(ContactData!K56)&lt;3,"",ContactData!K56)</f>
+        <f>IF(LEN(ContactData!K54)&lt;3,"",ContactData!K54)</f>
         <v>vivianl@livingproperties.com</v>
       </c>
       <c r="G57"/>
@@ -10284,27 +10260,27 @@
     </row>
     <row r="58" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
-        <f>IF(LEN(ContactData!H57)&lt;3,"",ContactData!H57)</f>
+        <f>IF(LEN(ContactData!H55)&lt;3,"",ContactData!H55)</f>
         <v>223</v>
       </c>
       <c r="B58" s="3" t="str">
-        <f>ContactData!E57</f>
+        <f>ContactData!E55</f>
         <v>Jessica Lee</v>
       </c>
       <c r="C58" s="3" t="str">
-        <f>ContactData!G57</f>
+        <f>ContactData!G55</f>
         <v xml:space="preserve">Accounting Clerk </v>
       </c>
       <c r="D58" s="9" t="str">
-        <f>IF(LEN(ContactData!I57)&lt;3,"",ContactData!I57)</f>
+        <f>IF(LEN(ContactData!I55)&lt;3,"",ContactData!I55)</f>
         <v>---</v>
       </c>
       <c r="E58" s="3" t="str">
-        <f>ContactData!J57</f>
+        <f>ContactData!J55</f>
         <v>---</v>
       </c>
       <c r="F58" s="3" t="str">
-        <f>IF(LEN(ContactData!K57)&lt;3,"",ContactData!K57)</f>
+        <f>IF(LEN(ContactData!K55)&lt;3,"",ContactData!K55)</f>
         <v>jessical@livingproperties.com</v>
       </c>
       <c r="G58"/>
@@ -10313,27 +10289,27 @@
     </row>
     <row r="59" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
-        <f>IF(LEN(ContactData!H58)&lt;3,"",ContactData!H58)</f>
+        <f>IF(LEN(ContactData!H56)&lt;3,"",ContactData!H56)</f>
         <v>172</v>
       </c>
       <c r="B59" s="3" t="str">
-        <f>ContactData!E58</f>
+        <f>ContactData!E56</f>
         <v>Rebecca Lau</v>
       </c>
       <c r="C59" s="3" t="str">
-        <f>ContactData!G58</f>
+        <f>ContactData!G56</f>
         <v>Administrative Assistant</v>
       </c>
       <c r="D59" s="9" t="str">
-        <f>IF(LEN(ContactData!I58)&lt;3,"",ContactData!I58)</f>
+        <f>IF(LEN(ContactData!I56)&lt;3,"",ContactData!I56)</f>
         <v>---</v>
       </c>
       <c r="E59" s="3" t="str">
-        <f>ContactData!J58</f>
+        <f>ContactData!J56</f>
         <v>---</v>
       </c>
       <c r="F59" s="3" t="str">
-        <f>IF(LEN(ContactData!K58)&lt;3,"",ContactData!K58)</f>
+        <f>IF(LEN(ContactData!K56)&lt;3,"",ContactData!K56)</f>
         <v>rebeccal@livingproperties.com</v>
       </c>
       <c r="G59"/>
@@ -10342,27 +10318,27 @@
     </row>
     <row r="60" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
-        <f>IF(LEN(ContactData!H59)&lt;3,"",ContactData!H59)</f>
+        <f>IF(LEN(ContactData!H57)&lt;3,"",ContactData!H57)</f>
         <v>182</v>
       </c>
       <c r="B60" s="3" t="str">
-        <f>ContactData!E59</f>
+        <f>ContactData!E57</f>
         <v>Kelvin Chan</v>
       </c>
       <c r="C60" s="3" t="str">
-        <f>ContactData!G59</f>
+        <f>ContactData!G57</f>
         <v>Administrative Assistant</v>
       </c>
       <c r="D60" s="9" t="str">
-        <f>IF(LEN(ContactData!I59)&lt;3,"",ContactData!I59)</f>
+        <f>IF(LEN(ContactData!I57)&lt;3,"",ContactData!I57)</f>
         <v>---</v>
       </c>
       <c r="E60" s="3" t="str">
-        <f>ContactData!J59</f>
+        <f>ContactData!J57</f>
         <v>---</v>
       </c>
       <c r="F60" s="3" t="str">
-        <f>IF(LEN(ContactData!K59)&lt;3,"",ContactData!K59)</f>
+        <f>IF(LEN(ContactData!K57)&lt;3,"",ContactData!K57)</f>
         <v>kelvinc@livingproperties.com</v>
       </c>
       <c r="G60"/>
@@ -10371,27 +10347,27 @@
     </row>
     <row r="61" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="str">
-        <f>IF(LEN(ContactData!H60)&lt;3,"",ContactData!H60)</f>
+        <f>IF(LEN(ContactData!H58)&lt;3,"",ContactData!H58)</f>
         <v>---</v>
       </c>
       <c r="B61" s="3" t="str">
-        <f>ContactData!E60</f>
+        <f>ContactData!E58</f>
         <v>Calmaine Hewitt</v>
       </c>
       <c r="C61" s="3" t="str">
-        <f>ContactData!G60</f>
+        <f>ContactData!G58</f>
         <v>Handyman</v>
       </c>
       <c r="D61" s="9" t="str">
-        <f>IF(LEN(ContactData!I60)&lt;3,"",ContactData!I60)</f>
+        <f>IF(LEN(ContactData!I58)&lt;3,"",ContactData!I58)</f>
         <v>---</v>
       </c>
       <c r="E61" s="3" t="str">
-        <f>ContactData!J60</f>
+        <f>ContactData!J58</f>
         <v>(905) 477-2090</v>
       </c>
       <c r="F61" s="3" t="str">
-        <f>IF(LEN(ContactData!K60)&lt;3,"",ContactData!K60)</f>
+        <f>IF(LEN(ContactData!K58)&lt;3,"",ContactData!K58)</f>
         <v>calmaineh@livingproperties.com</v>
       </c>
       <c r="G61"/>
@@ -10400,27 +10376,27 @@
     </row>
     <row r="62" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
-        <f>IF(LEN(ContactData!H61)&lt;3,"",ContactData!H61)</f>
+        <f>IF(LEN(ContactData!H59)&lt;3,"",ContactData!H59)</f>
         <v>229</v>
       </c>
       <c r="B62" s="3" t="str">
-        <f>ContactData!E61</f>
+        <f>ContactData!E59</f>
         <v>Matthew Wong</v>
       </c>
       <c r="C62" s="3" t="str">
-        <f>ContactData!G61</f>
+        <f>ContactData!G59</f>
         <v>Accounting Clerk</v>
       </c>
       <c r="D62" s="9" t="str">
-        <f>IF(LEN(ContactData!I61)&lt;3,"",ContactData!I61)</f>
+        <f>IF(LEN(ContactData!I59)&lt;3,"",ContactData!I59)</f>
         <v>---</v>
       </c>
       <c r="E62" s="3" t="str">
-        <f>ContactData!J61</f>
+        <f>ContactData!J59</f>
         <v>---</v>
       </c>
       <c r="F62" s="3" t="str">
-        <f>IF(LEN(ContactData!K61)&lt;3,"",ContactData!K61)</f>
+        <f>IF(LEN(ContactData!K59)&lt;3,"",ContactData!K59)</f>
         <v>mattheww@livingproperties.com</v>
       </c>
       <c r="G62"/>
@@ -10429,27 +10405,27 @@
     </row>
     <row r="63" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A63" s="9" t="str">
-        <f>IF(LEN(ContactData!H62)&lt;3,"",ContactData!H62)</f>
+        <f>IF(LEN(ContactData!H60)&lt;3,"",ContactData!H60)</f>
         <v/>
       </c>
       <c r="B63" s="3" t="str">
-        <f>ContactData!E62</f>
+        <f>ContactData!E60</f>
         <v>Centro Towers Office</v>
       </c>
       <c r="C63" s="3" t="str">
-        <f>ContactData!G62</f>
+        <f>ContactData!G60</f>
         <v>25 Town Centre Crt, Scarborough, ON, M1P 0B4</v>
       </c>
       <c r="D63" s="9" t="str">
-        <f>IF(LEN(ContactData!I62)&lt;3,"",ContactData!I62)</f>
+        <f>IF(LEN(ContactData!I60)&lt;3,"",ContactData!I60)</f>
         <v/>
       </c>
       <c r="E63" s="3" t="str">
-        <f>ContactData!J62</f>
+        <f>ContactData!J60</f>
         <v>T: (416) 290-1242</v>
       </c>
       <c r="F63" s="3" t="str">
-        <f>IF(LEN(ContactData!K62)&lt;3,"",ContactData!K62)</f>
+        <f>IF(LEN(ContactData!K60)&lt;3,"",ContactData!K60)</f>
         <v/>
       </c>
       <c r="G63"/>
@@ -10458,27 +10434,27 @@
     </row>
     <row r="64" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="str">
-        <f>IF(LEN(ContactData!H63)&lt;3,"",ContactData!H63)</f>
+        <f>IF(LEN(ContactData!H61)&lt;3,"",ContactData!H61)</f>
         <v>---</v>
       </c>
       <c r="B64" s="3" t="str">
-        <f>ContactData!E63</f>
+        <f>ContactData!E61</f>
         <v>Henry Fu</v>
       </c>
       <c r="C64" s="3" t="str">
-        <f>ContactData!G63</f>
+        <f>ContactData!G61</f>
         <v>Property Manager</v>
       </c>
       <c r="D64" s="9" t="str">
-        <f>IF(LEN(ContactData!I63)&lt;3,"",ContactData!I63)</f>
+        <f>IF(LEN(ContactData!I61)&lt;3,"",ContactData!I61)</f>
         <v>(416) 278-2953</v>
       </c>
       <c r="E64" s="3" t="str">
-        <f>ContactData!J63</f>
+        <f>ContactData!J61</f>
         <v>(416) 290-1242</v>
       </c>
       <c r="F64" s="3" t="str">
-        <f>IF(LEN(ContactData!K63)&lt;3,"",ContactData!K63)</f>
+        <f>IF(LEN(ContactData!K61)&lt;3,"",ContactData!K61)</f>
         <v>henry@centrotowers.com</v>
       </c>
       <c r="G64"/>
@@ -10487,27 +10463,27 @@
     </row>
     <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A65" s="9" t="str">
-        <f>IF(LEN(ContactData!H64)&lt;3,"",ContactData!H64)</f>
+        <f>IF(LEN(ContactData!H62)&lt;3,"",ContactData!H62)</f>
         <v>---</v>
       </c>
       <c r="B65" s="3" t="str">
-        <f>ContactData!E64</f>
+        <f>ContactData!E62</f>
         <v>Sophia Yip</v>
       </c>
       <c r="C65" s="3" t="str">
-        <f>ContactData!G64</f>
+        <f>ContactData!G62</f>
         <v>Property Administrator</v>
       </c>
       <c r="D65" s="9" t="str">
-        <f>IF(LEN(ContactData!I64)&lt;3,"",ContactData!I64)</f>
+        <f>IF(LEN(ContactData!I62)&lt;3,"",ContactData!I62)</f>
         <v>---</v>
       </c>
       <c r="E65" s="3" t="str">
-        <f>ContactData!J64</f>
+        <f>ContactData!J62</f>
         <v>(416) 290-1242</v>
       </c>
       <c r="F65" s="3" t="str">
-        <f>IF(LEN(ContactData!K64)&lt;3,"",ContactData!K64)</f>
+        <f>IF(LEN(ContactData!K62)&lt;3,"",ContactData!K62)</f>
         <v>sophia@centrotowers.com</v>
       </c>
       <c r="G65"/>
@@ -10516,27 +10492,27 @@
     </row>
     <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="str">
-        <f>IF(LEN(ContactData!H65)&lt;3,"",ContactData!H65)</f>
+        <f>IF(LEN(ContactData!H63)&lt;3,"",ContactData!H63)</f>
         <v>---</v>
       </c>
       <c r="B66" s="3" t="str">
-        <f>ContactData!E65</f>
+        <f>ContactData!E63</f>
         <v xml:space="preserve">Security Desk </v>
       </c>
       <c r="C66" s="3" t="str">
-        <f>ContactData!G65</f>
+        <f>ContactData!G63</f>
         <v xml:space="preserve">Centro Security Desk </v>
       </c>
       <c r="D66" s="9" t="str">
-        <f>IF(LEN(ContactData!I65)&lt;3,"",ContactData!I65)</f>
+        <f>IF(LEN(ContactData!I63)&lt;3,"",ContactData!I63)</f>
         <v>---</v>
       </c>
       <c r="E66" s="3" t="str">
-        <f>ContactData!J65</f>
+        <f>ContactData!J63</f>
         <v>(416) 296-0099</v>
       </c>
       <c r="F66" s="3" t="str">
-        <f>IF(LEN(ContactData!K65)&lt;3,"",ContactData!K65)</f>
+        <f>IF(LEN(ContactData!K63)&lt;3,"",ContactData!K63)</f>
         <v>---</v>
       </c>
       <c r="G66"/>
@@ -10545,27 +10521,27 @@
     </row>
     <row r="67" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A67" s="9" t="str">
-        <f>IF(LEN(ContactData!H66)&lt;3,"",ContactData!H66)</f>
+        <f>IF(LEN(ContactData!H64)&lt;3,"",ContactData!H64)</f>
         <v/>
       </c>
       <c r="B67" s="3" t="str">
-        <f>ContactData!E66</f>
+        <f>ContactData!E64</f>
         <v>EQ1 Office</v>
       </c>
       <c r="C67" s="3" t="str">
-        <f>ContactData!G66</f>
+        <f>ContactData!G64</f>
         <v>70 Town Centre Court, Scarborough, ON, M1P 0B2</v>
       </c>
       <c r="D67" s="9" t="str">
-        <f>IF(LEN(ContactData!I66)&lt;3,"",ContactData!I66)</f>
+        <f>IF(LEN(ContactData!I64)&lt;3,"",ContactData!I64)</f>
         <v/>
       </c>
       <c r="E67" s="3" t="str">
-        <f>ContactData!J66</f>
+        <f>ContactData!J64</f>
         <v xml:space="preserve">T: (416) 279-0603 </v>
       </c>
       <c r="F67" s="3" t="str">
-        <f>IF(LEN(ContactData!K66)&lt;3,"",ContactData!K66)</f>
+        <f>IF(LEN(ContactData!K64)&lt;3,"",ContactData!K64)</f>
         <v>eq1@livingproperties.com</v>
       </c>
       <c r="G67"/>
@@ -10574,27 +10550,27 @@
     </row>
     <row r="68" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="str">
-        <f>IF(LEN(ContactData!H67)&lt;3,"",ContactData!H67)</f>
+        <f>IF(LEN(ContactData!H65)&lt;3,"",ContactData!H65)</f>
         <v>---</v>
       </c>
       <c r="B68" s="3" t="str">
-        <f>ContactData!E67</f>
+        <f>ContactData!E65</f>
         <v>Ming Ip</v>
       </c>
       <c r="C68" s="3" t="str">
-        <f>ContactData!G67</f>
+        <f>ContactData!G65</f>
         <v>Property Manager</v>
       </c>
       <c r="D68" s="9" t="str">
-        <f>IF(LEN(ContactData!I67)&lt;3,"",ContactData!I67)</f>
+        <f>IF(LEN(ContactData!I65)&lt;3,"",ContactData!I65)</f>
         <v>(647) 286-0147</v>
       </c>
       <c r="E68" s="3" t="str">
-        <f>ContactData!J67</f>
+        <f>ContactData!J65</f>
         <v xml:space="preserve">(416) 279-0603 </v>
       </c>
       <c r="F68" s="3" t="str">
-        <f>IF(LEN(ContactData!K67)&lt;3,"",ContactData!K67)</f>
+        <f>IF(LEN(ContactData!K65)&lt;3,"",ContactData!K65)</f>
         <v>eq1manager@livingproperties.com</v>
       </c>
       <c r="G68"/>
@@ -10603,27 +10579,27 @@
     </row>
     <row r="69" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A69" s="9" t="str">
-        <f>IF(LEN(ContactData!H68)&lt;3,"",ContactData!H68)</f>
+        <f>IF(LEN(ContactData!H66)&lt;3,"",ContactData!H66)</f>
         <v>---</v>
       </c>
       <c r="B69" s="3" t="str">
-        <f>ContactData!E68</f>
+        <f>ContactData!E66</f>
         <v xml:space="preserve">Security Desk </v>
       </c>
       <c r="C69" s="3" t="str">
-        <f>ContactData!G68</f>
+        <f>ContactData!G66</f>
         <v xml:space="preserve">EQ1 Security Desk </v>
       </c>
       <c r="D69" s="9" t="str">
-        <f>IF(LEN(ContactData!I68)&lt;3,"",ContactData!I68)</f>
+        <f>IF(LEN(ContactData!I66)&lt;3,"",ContactData!I66)</f>
         <v>---</v>
       </c>
       <c r="E69" s="3" t="str">
-        <f>ContactData!J68</f>
+        <f>ContactData!J66</f>
         <v>(416) 279-1894</v>
       </c>
       <c r="F69" s="3" t="str">
-        <f>IF(LEN(ContactData!K68)&lt;3,"",ContactData!K68)</f>
+        <f>IF(LEN(ContactData!K66)&lt;3,"",ContactData!K66)</f>
         <v>---</v>
       </c>
       <c r="G69"/>
@@ -10632,27 +10608,27 @@
     </row>
     <row r="70" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="str">
-        <f>IF(LEN(ContactData!H69)&lt;3,"",ContactData!H69)</f>
+        <f>IF(LEN(ContactData!H67)&lt;3,"",ContactData!H67)</f>
         <v/>
       </c>
       <c r="B70" s="3" t="str">
-        <f>ContactData!E69</f>
+        <f>ContactData!E67</f>
         <v>EQ2 Office</v>
       </c>
       <c r="C70" s="3" t="str">
-        <f>ContactData!G69</f>
+        <f>ContactData!G67</f>
         <v>60 Town Centre Court, Scarborough, ON, M1P 0B1</v>
       </c>
       <c r="D70" s="9" t="str">
-        <f>IF(LEN(ContactData!I69)&lt;3,"",ContactData!I69)</f>
+        <f>IF(LEN(ContactData!I67)&lt;3,"",ContactData!I67)</f>
         <v/>
       </c>
       <c r="E70" s="3" t="str">
-        <f>ContactData!J69</f>
+        <f>ContactData!J67</f>
         <v xml:space="preserve">T: (416) 279-0591 </v>
       </c>
       <c r="F70" s="3" t="str">
-        <f>IF(LEN(ContactData!K69)&lt;3,"",ContactData!K69)</f>
+        <f>IF(LEN(ContactData!K67)&lt;3,"",ContactData!K67)</f>
         <v/>
       </c>
       <c r="G70"/>
@@ -10661,27 +10637,27 @@
     </row>
     <row r="71" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="str">
-        <f>IF(LEN(ContactData!H70)&lt;3,"",ContactData!H70)</f>
+        <f>IF(LEN(ContactData!H68)&lt;3,"",ContactData!H68)</f>
         <v>---</v>
       </c>
       <c r="B71" s="3" t="str">
-        <f>ContactData!E70</f>
+        <f>ContactData!E68</f>
         <v>Aaron Ma</v>
       </c>
       <c r="C71" s="3" t="str">
-        <f>ContactData!G70</f>
+        <f>ContactData!G68</f>
         <v>Property Manager</v>
       </c>
       <c r="D71" s="9" t="str">
-        <f>IF(LEN(ContactData!I70)&lt;3,"",ContactData!I70)</f>
+        <f>IF(LEN(ContactData!I68)&lt;3,"",ContactData!I68)</f>
         <v>(416) 684-2236</v>
       </c>
       <c r="E71" s="3" t="str">
-        <f>ContactData!J70</f>
+        <f>ContactData!J68</f>
         <v>(416) 279-0591</v>
       </c>
       <c r="F71" s="3" t="str">
-        <f>IF(LEN(ContactData!K70)&lt;3,"",ContactData!K70)</f>
+        <f>IF(LEN(ContactData!K68)&lt;3,"",ContactData!K68)</f>
         <v>eq2manager@livingproperties.com</v>
       </c>
       <c r="G71"/>
@@ -10690,27 +10666,27 @@
     </row>
     <row r="72" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A72" s="9" t="str">
-        <f>IF(LEN(ContactData!H71)&lt;3,"",ContactData!H71)</f>
+        <f>IF(LEN(ContactData!H69)&lt;3,"",ContactData!H69)</f>
         <v>---</v>
       </c>
       <c r="B72" s="3" t="str">
-        <f>ContactData!E71</f>
+        <f>ContactData!E69</f>
         <v xml:space="preserve">Security Desk </v>
       </c>
       <c r="C72" s="3" t="str">
-        <f>ContactData!G71</f>
+        <f>ContactData!G69</f>
         <v xml:space="preserve">EQ2 Security Desk </v>
       </c>
       <c r="D72" s="9" t="str">
-        <f>IF(LEN(ContactData!I71)&lt;3,"",ContactData!I71)</f>
+        <f>IF(LEN(ContactData!I69)&lt;3,"",ContactData!I69)</f>
         <v>---</v>
       </c>
       <c r="E72" s="3" t="str">
-        <f>ContactData!J71</f>
+        <f>ContactData!J69</f>
         <v>(416) 279-1211</v>
       </c>
       <c r="F72" s="3" t="str">
-        <f>IF(LEN(ContactData!K71)&lt;3,"",ContactData!K71)</f>
+        <f>IF(LEN(ContactData!K69)&lt;3,"",ContactData!K69)</f>
         <v>---</v>
       </c>
       <c r="G72"/>
@@ -10719,27 +10695,27 @@
     </row>
     <row r="73" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A73" s="9" t="str">
-        <f>IF(LEN(ContactData!H72)&lt;3,"",ContactData!H72)</f>
+        <f>IF(LEN(ContactData!H70)&lt;3,"",ContactData!H70)</f>
         <v/>
       </c>
       <c r="B73" s="3" t="str">
-        <f>ContactData!E72</f>
+        <f>ContactData!E70</f>
         <v>Alton Tower Office</v>
       </c>
       <c r="C73" s="3" t="str">
-        <f>ContactData!G72</f>
+        <f>ContactData!G70</f>
         <v>160 Alton Towers Cir, Toronto, ON, M1V 4X8</v>
       </c>
       <c r="D73" s="9" t="str">
-        <f>IF(LEN(ContactData!I72)&lt;3,"",ContactData!I72)</f>
+        <f>IF(LEN(ContactData!I70)&lt;3,"",ContactData!I70)</f>
         <v/>
       </c>
       <c r="E73" s="3" t="str">
-        <f>ContactData!J72</f>
+        <f>ContactData!J70</f>
         <v>T: (437)-533-1208</v>
       </c>
       <c r="F73" s="3" t="str">
-        <f>IF(LEN(ContactData!K72)&lt;3,"",ContactData!K72)</f>
+        <f>IF(LEN(ContactData!K70)&lt;3,"",ContactData!K70)</f>
         <v/>
       </c>
       <c r="G73"/>
@@ -10748,27 +10724,27 @@
     </row>
     <row r="74" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A74" s="9" t="str">
-        <f>IF(LEN(ContactData!H73)&lt;3,"",ContactData!H73)</f>
+        <f>IF(LEN(ContactData!H71)&lt;3,"",ContactData!H71)</f>
         <v>---</v>
       </c>
       <c r="B74" s="3" t="str">
-        <f>ContactData!E73</f>
+        <f>ContactData!E71</f>
         <v>Ken Kam</v>
       </c>
       <c r="C74" s="3" t="str">
-        <f>ContactData!G73</f>
+        <f>ContactData!G71</f>
         <v>Property Manager</v>
       </c>
       <c r="D74" s="9" t="str">
-        <f>IF(LEN(ContactData!I73)&lt;3,"",ContactData!I73)</f>
+        <f>IF(LEN(ContactData!I71)&lt;3,"",ContactData!I71)</f>
         <v>(647) 204-4455</v>
       </c>
       <c r="E74" s="3" t="str">
-        <f>ContactData!J73</f>
+        <f>ContactData!J71</f>
         <v>(905) 477-2090</v>
       </c>
       <c r="F74" s="3" t="str">
-        <f>IF(LEN(ContactData!K73)&lt;3,"",ContactData!K73)</f>
+        <f>IF(LEN(ContactData!K71)&lt;3,"",ContactData!K71)</f>
         <v>kenk@livingproperties.com</v>
       </c>
       <c r="G74"/>
@@ -10777,27 +10753,27 @@
     </row>
     <row r="75" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A75" s="9" t="str">
-        <f>IF(LEN(ContactData!H74)&lt;3,"",ContactData!H74)</f>
+        <f>IF(LEN(ContactData!H72)&lt;3,"",ContactData!H72)</f>
         <v>---</v>
       </c>
       <c r="B75" s="3" t="str">
-        <f>ContactData!E74</f>
+        <f>ContactData!E72</f>
         <v>Christie Ip</v>
       </c>
       <c r="C75" s="3" t="str">
-        <f>ContactData!G74</f>
+        <f>ContactData!G72</f>
         <v>Administrative Assistant</v>
       </c>
       <c r="D75" s="9" t="str">
-        <f>IF(LEN(ContactData!I74)&lt;3,"",ContactData!I74)</f>
+        <f>IF(LEN(ContactData!I72)&lt;3,"",ContactData!I72)</f>
         <v>(437)-533-1208</v>
       </c>
       <c r="E75" s="3" t="str">
-        <f>ContactData!J74</f>
+        <f>ContactData!J72</f>
         <v>---</v>
       </c>
       <c r="F75" s="3" t="str">
-        <f>IF(LEN(ContactData!K74)&lt;3,"",ContactData!K74)</f>
+        <f>IF(LEN(ContactData!K72)&lt;3,"",ContactData!K72)</f>
         <v xml:space="preserve">optima2@livingproperties.com </v>
       </c>
       <c r="G75"/>
@@ -10806,27 +10782,27 @@
     </row>
     <row r="76" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A76" s="9" t="str">
-        <f>IF(LEN(ContactData!H75)&lt;3,"",ContactData!H75)</f>
+        <f>IF(LEN(ContactData!H73)&lt;3,"",ContactData!H73)</f>
         <v>---</v>
       </c>
       <c r="B76" s="3" t="str">
-        <f>ContactData!E75</f>
+        <f>ContactData!E73</f>
         <v xml:space="preserve">Security Desk </v>
       </c>
       <c r="C76" s="3" t="str">
-        <f>ContactData!G75</f>
+        <f>ContactData!G73</f>
         <v xml:space="preserve">Alton Tower Security Desk </v>
       </c>
       <c r="D76" s="9" t="str">
-        <f>IF(LEN(ContactData!I75)&lt;3,"",ContactData!I75)</f>
+        <f>IF(LEN(ContactData!I73)&lt;3,"",ContactData!I73)</f>
         <v>---</v>
       </c>
       <c r="E76" s="3" t="str">
-        <f>ContactData!J75</f>
+        <f>ContactData!J73</f>
         <v>(416) 754-3131</v>
       </c>
       <c r="F76" s="3" t="str">
-        <f>IF(LEN(ContactData!K75)&lt;3,"",ContactData!K75)</f>
+        <f>IF(LEN(ContactData!K73)&lt;3,"",ContactData!K73)</f>
         <v>---</v>
       </c>
       <c r="G76"/>
@@ -10835,27 +10811,27 @@
     </row>
     <row r="77" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A77" s="9" t="str">
-        <f>IF(LEN(ContactData!H76)&lt;3,"",ContactData!H76)</f>
+        <f>IF(LEN(ContactData!H74)&lt;3,"",ContactData!H74)</f>
         <v/>
       </c>
       <c r="B77" s="3" t="str">
-        <f>ContactData!E76</f>
+        <f>ContactData!E74</f>
         <v>IHMG Office</v>
       </c>
       <c r="C77" s="3" t="str">
-        <f>ContactData!G76</f>
+        <f>ContactData!G74</f>
         <v>8 Steelcase Road West, Markham, ON, L3R 1B2</v>
       </c>
       <c r="D77" s="9" t="str">
-        <f>IF(LEN(ContactData!I76)&lt;3,"",ContactData!I76)</f>
+        <f>IF(LEN(ContactData!I74)&lt;3,"",ContactData!I74)</f>
         <v/>
       </c>
       <c r="E77" s="3" t="str">
-        <f>ContactData!J76</f>
+        <f>ContactData!J74</f>
         <v>T: (905) 475-6000</v>
       </c>
       <c r="F77" s="3" t="str">
-        <f>IF(LEN(ContactData!K76)&lt;3,"",ContactData!K76)</f>
+        <f>IF(LEN(ContactData!K74)&lt;3,"",ContactData!K74)</f>
         <v>info@ihmg.ca</v>
       </c>
       <c r="G77"/>
@@ -10864,27 +10840,27 @@
     </row>
     <row r="78" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A78" s="9" t="str">
-        <f>IF(LEN(ContactData!H77)&lt;3,"",ContactData!H77)</f>
+        <f>IF(LEN(ContactData!H75)&lt;3,"",ContactData!H75)</f>
         <v/>
       </c>
       <c r="B78" s="3" t="str">
-        <f>ContactData!E77</f>
+        <f>ContactData!E75</f>
         <v>IHMGRI Office</v>
       </c>
       <c r="C78" s="3" t="str">
-        <f>ContactData!G77</f>
+        <f>ContactData!G75</f>
         <v>8 Steelcase Road West, Unit E, Markham, ON, L3R 1B2</v>
       </c>
       <c r="D78" s="9" t="str">
-        <f>IF(LEN(ContactData!I77)&lt;3,"",ContactData!I77)</f>
+        <f>IF(LEN(ContactData!I75)&lt;3,"",ContactData!I75)</f>
         <v/>
       </c>
       <c r="E78" s="3" t="str">
-        <f>ContactData!J77</f>
+        <f>ContactData!J75</f>
         <v>T: (905) 489-8989</v>
       </c>
       <c r="F78" s="3" t="str">
-        <f>IF(LEN(ContactData!K77)&lt;3,"",ContactData!K77)</f>
+        <f>IF(LEN(ContactData!K75)&lt;3,"",ContactData!K75)</f>
         <v>realestate@ihmg.ca</v>
       </c>
       <c r="G78"/>
@@ -10893,27 +10869,27 @@
     </row>
     <row r="79" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
-        <f>IF(LEN(ContactData!H78)&lt;3,"",ContactData!H78)</f>
+        <f>IF(LEN(ContactData!H76)&lt;3,"",ContactData!H76)</f>
         <v>120</v>
       </c>
       <c r="B79" s="3" t="str">
-        <f>ContactData!E78</f>
+        <f>ContactData!E76</f>
         <v>Eddie Tang</v>
       </c>
       <c r="C79" s="3" t="str">
-        <f>ContactData!G78</f>
+        <f>ContactData!G76</f>
         <v>Financial Controller</v>
       </c>
       <c r="D79" s="9" t="str">
-        <f>IF(LEN(ContactData!I78)&lt;3,"",ContactData!I78)</f>
+        <f>IF(LEN(ContactData!I76)&lt;3,"",ContactData!I76)</f>
         <v>(416) 723-8329</v>
       </c>
       <c r="E79" s="3" t="str">
-        <f>ContactData!J78</f>
+        <f>ContactData!J76</f>
         <v>(905) 489-0186</v>
       </c>
       <c r="F79" s="3" t="str">
-        <f>IF(LEN(ContactData!K78)&lt;3,"",ContactData!K78)</f>
+        <f>IF(LEN(ContactData!K76)&lt;3,"",ContactData!K76)</f>
         <v>eddie@ihmg.ca</v>
       </c>
       <c r="G79"/>
@@ -10922,27 +10898,27 @@
     </row>
     <row r="80" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
-        <f>IF(LEN(ContactData!H79)&lt;3,"",ContactData!H79)</f>
+        <f>IF(LEN(ContactData!H77)&lt;3,"",ContactData!H77)</f>
         <v>187</v>
       </c>
       <c r="B80" s="3" t="str">
-        <f>ContactData!E79</f>
+        <f>ContactData!E77</f>
         <v>Lily Hou</v>
       </c>
       <c r="C80" s="3" t="str">
-        <f>ContactData!G79</f>
+        <f>ContactData!G77</f>
         <v>Senior Accounting Analyst &amp; Operations Support</v>
       </c>
       <c r="D80" s="9" t="str">
-        <f>IF(LEN(ContactData!I79)&lt;3,"",ContactData!I79)</f>
+        <f>IF(LEN(ContactData!I77)&lt;3,"",ContactData!I77)</f>
         <v>(647) 774-8994</v>
       </c>
       <c r="E80" s="3" t="str">
-        <f>ContactData!J79</f>
+        <f>ContactData!J77</f>
         <v>---</v>
       </c>
       <c r="F80" s="3" t="str">
-        <f>IF(LEN(ContactData!K79)&lt;3,"",ContactData!K79)</f>
+        <f>IF(LEN(ContactData!K77)&lt;3,"",ContactData!K77)</f>
         <v>lily@ihmg.ca</v>
       </c>
       <c r="G80"/>
@@ -14186,7 +14162,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D4DBD61-A264-4E77-BA12-BABDDFA736C5}">
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
@@ -14205,43 +14181,43 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="B1" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C1" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D1" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="E1" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="F1" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="G1" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="H1" t="s">
         <v>1</v>
       </c>
       <c r="I1" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="J1" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="K1" t="s">
         <v>5</v>
       </c>
       <c r="L1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="M1" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -14249,10 +14225,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -14264,22 +14240,22 @@
         <v>9</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="J2" t="s">
         <v>10</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="L2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="M2" t="str">
-        <f t="shared" ref="M2:M32" si="0">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A2 &amp; "','" &amp; D2 &amp; "','" &amp; E2 &amp; "','" &amp; G2 &amp; "','" &amp; H2 &amp; "','" &amp; I2 &amp;  "','" &amp; J2 &amp;  "','" &amp; K2 &amp;  "','" &amp; L2 &amp; "');"</f>
+        <f t="shared" ref="M2:M31" si="0">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A2 &amp; "','" &amp; D2 &amp; "','" &amp; E2 &amp; "','" &amp; G2 &amp; "','" &amp; H2 &amp; "','" &amp; I2 &amp;  "','" &amp; J2 &amp;  "','" &amp; K2 &amp;  "','" &amp; L2 &amp; "');"</f>
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('1','1','LRI Head Office','8 Steelcase Road West, Markham, ON, L3R 1B2','--','--','T: (905) 474-0590','--','Office Header');</v>
       </c>
     </row>
@@ -14288,10 +14264,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C3" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -14300,7 +14276,7 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G3" t="s">
         <v>12</v>
@@ -14312,13 +14288,13 @@
         <v>13</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="L3" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M3" t="str">
         <f t="shared" si="0"/>
@@ -14330,10 +14306,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C4" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -14342,7 +14318,7 @@
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -14354,13 +14330,13 @@
         <v>16</v>
       </c>
       <c r="J4" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="L4" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M4" t="str">
         <f t="shared" si="0"/>
@@ -14372,10 +14348,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C5" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -14384,10 +14360,10 @@
         <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G5" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="H5">
         <v>228</v>
@@ -14399,10 +14375,10 @@
         <v>13</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="L5" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M5" t="str">
         <f t="shared" si="0"/>
@@ -14414,22 +14390,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C6" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="F6" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G6" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="H6">
         <v>521</v>
@@ -14441,10 +14417,10 @@
         <v>25</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="L6" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M6" t="str">
         <f t="shared" ref="M6:M7" si="1">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A6 &amp; "','" &amp; D6 &amp; "','" &amp; E6 &amp; "','" &amp; G6 &amp; "','" &amp; H6 &amp; "','" &amp; I6 &amp;  "','" &amp; J6 &amp;  "','" &amp; K6 &amp;  "','" &amp; L6 &amp; "');"</f>
@@ -14456,10 +14432,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C7" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -14468,7 +14444,7 @@
         <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G7" t="s">
         <v>21</v>
@@ -14480,13 +14456,13 @@
         <v>22</v>
       </c>
       <c r="J7" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="L7" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M7" t="str">
         <f t="shared" si="1"/>
@@ -14498,10 +14474,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C8" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -14510,10 +14486,10 @@
         <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G8" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="H8">
         <v>502</v>
@@ -14525,10 +14501,10 @@
         <v>29</v>
       </c>
       <c r="K8" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="L8" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M8" t="str">
         <f t="shared" si="0"/>
@@ -14540,37 +14516,37 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C9" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="F9" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G9" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I9" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>13</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="L9" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M9" t="str">
         <f t="shared" si="0"/>
@@ -14582,10 +14558,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C10" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -14594,10 +14570,10 @@
         <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G10" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>13</v>
@@ -14609,10 +14585,10 @@
         <v>13</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="L10" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M10" t="str">
         <f t="shared" ref="M10" si="2">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A10 &amp; "','" &amp; D10 &amp; "','" &amp; E10 &amp; "','" &amp; G10 &amp; "','" &amp; H10 &amp; "','" &amp; I10 &amp;  "','" &amp; J10 &amp;  "','" &amp; K10 &amp;  "','" &amp; L10 &amp; "');"</f>
@@ -14624,37 +14600,37 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C11" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="F11" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G11" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="H11">
         <v>509</v>
       </c>
       <c r="I11" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>13</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="L11" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M11" t="str">
         <f t="shared" ref="M11" si="3">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A11 &amp; "','" &amp; D11 &amp; "','" &amp; E11 &amp; "','" &amp; G11 &amp; "','" &amp; H11 &amp; "','" &amp; I11 &amp;  "','" &amp; J11 &amp;  "','" &amp; K11 &amp;  "','" &amp; L11 &amp; "');"</f>
@@ -14666,34 +14642,34 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C12" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="G12" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="H12">
         <v>504</v>
       </c>
       <c r="I12" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="J12" t="s">
         <v>30</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="L12" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M12" t="str">
         <f t="shared" si="0"/>
@@ -14705,10 +14681,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C13" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -14717,7 +14693,7 @@
         <v>31</v>
       </c>
       <c r="F13" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G13" t="s">
         <v>32</v>
@@ -14726,16 +14702,16 @@
         <v>514</v>
       </c>
       <c r="I13" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J13" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="K13" t="s">
         <v>34</v>
       </c>
       <c r="L13" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M13" t="str">
         <f t="shared" si="0"/>
@@ -14747,22 +14723,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C14" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="F14" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G14" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="H14">
         <v>224</v>
@@ -14771,13 +14747,13 @@
         <v>13</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="L14" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M14" t="str">
         <f t="shared" ref="M14" si="4">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A14 &amp; "','" &amp; D14 &amp; "','" &amp; E14 &amp; "','" &amp; G14 &amp; "','" &amp; H14 &amp; "','" &amp; I14 &amp;  "','" &amp; J14 &amp;  "','" &amp; K14 &amp;  "','" &amp; L14 &amp; "');"</f>
@@ -14786,28 +14762,28 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C15" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>61</v>
+        <v>314</v>
       </c>
       <c r="F15" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G15" t="s">
-        <v>223</v>
+        <v>315</v>
       </c>
       <c r="H15">
-        <v>123</v>
+        <v>282</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
@@ -14816,308 +14792,308 @@
         <v>13</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>258</v>
+        <v>316</v>
       </c>
       <c r="L15" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M15" t="str">
+        <f t="shared" ref="M15" si="5">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A15 &amp; "','" &amp; D15 &amp; "','" &amp; E15 &amp; "','" &amp; G15 &amp; "','" &amp; H15 &amp; "','" &amp; I15 &amp;  "','" &amp; J15 &amp;  "','" &amp; K15 &amp;  "','" &amp; L15 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('13','1','Joanna Xie','Agent Services Coordinator','282','---','---','joannaxie@livingrealtykw.com','Staff');</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>180</v>
+      </c>
+      <c r="C16" t="s">
+        <v>172</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" t="s">
+        <v>289</v>
+      </c>
+      <c r="G16" t="s">
+        <v>213</v>
+      </c>
+      <c r="H16">
+        <v>123</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="L16" t="s">
+        <v>160</v>
+      </c>
+      <c r="M16" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('14','1','Wendy Chung','Administration Officer ','123','---','---','wendychung@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="5">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
-        <v>187</v>
-      </c>
-      <c r="C16" t="s">
-        <v>179</v>
-      </c>
-      <c r="D16">
+      <c r="B17" t="s">
+        <v>180</v>
+      </c>
+      <c r="C17" t="s">
+        <v>172</v>
+      </c>
+      <c r="D17">
         <v>1</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E17" t="s">
         <v>23</v>
       </c>
-      <c r="F16" t="s">
-        <v>304</v>
-      </c>
-      <c r="G16" t="s">
-        <v>236</v>
-      </c>
-      <c r="H16">
+      <c r="F17" t="s">
+        <v>289</v>
+      </c>
+      <c r="G17" t="s">
+        <v>226</v>
+      </c>
+      <c r="H17">
         <v>206</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I17" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J16" s="6" t="s">
+      <c r="J17" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K16" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="L16" t="s">
-        <v>167</v>
-      </c>
-      <c r="M16" t="str">
+      <c r="K17" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="L17" t="s">
+        <v>160</v>
+      </c>
+      <c r="M17" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('15','1','Benjamin Wong','Assistant to the Broker of Record','206','---','---','benjaminwongici@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="5">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
-        <v>187</v>
-      </c>
-      <c r="C17" t="s">
-        <v>179</v>
-      </c>
-      <c r="D17">
+      <c r="B18" t="s">
+        <v>180</v>
+      </c>
+      <c r="C18" t="s">
+        <v>172</v>
+      </c>
+      <c r="D18">
         <v>1</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E18" t="s">
         <v>39</v>
       </c>
-      <c r="F17" t="s">
-        <v>304</v>
-      </c>
-      <c r="G17" t="s">
+      <c r="F18" t="s">
+        <v>289</v>
+      </c>
+      <c r="G18" t="s">
         <v>40</v>
       </c>
-      <c r="H17">
+      <c r="H18">
         <v>507</v>
       </c>
-      <c r="I17" s="6" t="s">
+      <c r="I18" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J18" t="s">
         <v>41</v>
       </c>
-      <c r="K17" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="L17" t="s">
-        <v>167</v>
-      </c>
-      <c r="M17" t="str">
+      <c r="K18" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="L18" t="s">
+        <v>160</v>
+      </c>
+      <c r="M18" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('16','1','Luvie Chao','Senior Deal Administrator','507','---','(905) 752-3507','luvie@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="5">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
-        <v>187</v>
-      </c>
-      <c r="C18" t="s">
-        <v>179</v>
-      </c>
-      <c r="D18">
+      <c r="B19" t="s">
+        <v>180</v>
+      </c>
+      <c r="C19" t="s">
+        <v>172</v>
+      </c>
+      <c r="D19">
         <v>1</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E19" t="s">
         <v>42</v>
       </c>
-      <c r="F18" t="s">
-        <v>304</v>
-      </c>
-      <c r="G18" t="s">
+      <c r="F19" t="s">
+        <v>289</v>
+      </c>
+      <c r="G19" t="s">
         <v>37</v>
       </c>
-      <c r="H18">
+      <c r="H19">
         <v>508</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="I19" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J19" t="s">
         <v>38</v>
       </c>
-      <c r="K18" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="L18" t="s">
-        <v>167</v>
-      </c>
-      <c r="M18" t="str">
+      <c r="K19" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="L19" t="s">
+        <v>160</v>
+      </c>
+      <c r="M19" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('17','1','Maria Leung','Deal Administrator','508','---','(905) 752-3508','marialeung@livingrealtykw.com','Staff');</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="5">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>187</v>
-      </c>
-      <c r="C19" t="s">
-        <v>179</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19" t="s">
-        <v>79</v>
-      </c>
-      <c r="F19" t="s">
-        <v>304</v>
-      </c>
-      <c r="G19" t="s">
-        <v>37</v>
-      </c>
-      <c r="H19">
-        <v>255</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="L19" t="s">
-        <v>167</v>
-      </c>
-      <c r="M19" t="str">
-        <f t="shared" ref="M19" si="5">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A19 &amp; "','" &amp; D19 &amp; "','" &amp; E19 &amp; "','" &amp; G19 &amp; "','" &amp; H19 &amp; "','" &amp; I19 &amp;  "','" &amp; J19 &amp;  "','" &amp; K19 &amp;  "','" &amp; L19 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('18','1','Ken Cheung','Deal Administrator','255','---','---','kencheung@livingrealtykw.com','Staff');</v>
-      </c>
-    </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C20" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>292</v>
+        <v>77</v>
       </c>
       <c r="F20" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G20" t="s">
-        <v>170</v>
+        <v>37</v>
       </c>
       <c r="H20">
-        <v>506</v>
+        <v>255</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J20" t="s">
-        <v>36</v>
+      <c r="J20" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>293</v>
+        <v>252</v>
       </c>
       <c r="L20" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M20" t="str">
         <f t="shared" ref="M20" si="6">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A20 &amp; "','" &amp; D20 &amp; "','" &amp; E20 &amp; "','" &amp; G20 &amp; "','" &amp; H20 &amp; "','" &amp; I20 &amp;  "','" &amp; J20 &amp;  "','" &amp; K20 &amp;  "','" &amp; L20 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('19','1','Connie Cheung','Accounting Bookkeeper','506','---','(905) 752-3506','conniecheung@livingrealtykw.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('18','1','Ken Cheung','Deal Administrator','255','---','---','kencheung@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C21" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>43</v>
+        <v>277</v>
       </c>
       <c r="F21" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G21" t="s">
-        <v>44</v>
+        <v>163</v>
       </c>
       <c r="H21">
-        <v>519</v>
+        <v>506</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J21" t="s">
+        <v>36</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="L21" t="s">
+        <v>160</v>
+      </c>
+      <c r="M21" t="str">
+        <f t="shared" ref="M21" si="7">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A21 &amp; "','" &amp; D21 &amp; "','" &amp; E21 &amp; "','" &amp; G21 &amp; "','" &amp; H21 &amp; "','" &amp; I21 &amp;  "','" &amp; J21 &amp;  "','" &amp; K21 &amp;  "','" &amp; L21 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('19','1','Connie Cheung','Accounting Bookkeeper','506','---','(905) 752-3506','conniecheung@livingrealtykw.com','Staff');</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>180</v>
+      </c>
+      <c r="C22" t="s">
+        <v>172</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" t="s">
+        <v>289</v>
+      </c>
+      <c r="G22" t="s">
+        <v>44</v>
+      </c>
+      <c r="H22">
+        <v>519</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J22" t="s">
         <v>45</v>
       </c>
-      <c r="K21" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="L21" t="s">
-        <v>167</v>
-      </c>
-      <c r="M21" t="str">
+      <c r="K22" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="L22" t="s">
+        <v>160</v>
+      </c>
+      <c r="M22" t="str">
         <f t="shared" si="0"/>
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('20','1','Simon Chan','Operations Assistant','519','---','(905) 752-3519','simonchan@livingrealtykw.com','Staff');</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="5">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>187</v>
-      </c>
-      <c r="C22" t="s">
-        <v>179</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22" t="s">
-        <v>215</v>
-      </c>
-      <c r="F22" t="s">
-        <v>304</v>
-      </c>
-      <c r="G22" t="s">
-        <v>216</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="L22" t="s">
-        <v>167</v>
-      </c>
-      <c r="M22" t="str">
-        <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A22 &amp; "','" &amp; D22 &amp; "','" &amp; E22 &amp; "','" &amp; G22 &amp; "','" &amp; H22 &amp; "','" &amp; I22 &amp;  "','" &amp; J22 &amp;  "','" &amp; K22 &amp;  "','" &amp; L22 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('21','1','Ben Dowson','Digitial Marketing &amp; Web Developer','---','---','---','socialmedia@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
@@ -15125,22 +15101,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C23" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="F23" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G23" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="H23">
         <v>121</v>
@@ -15152,13 +15128,13 @@
         <v>13</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="L23" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M23" t="str">
-        <f t="shared" ref="M23" si="7">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A23 &amp; "','" &amp; D23 &amp; "','" &amp; E23 &amp; "','" &amp; G23 &amp; "','" &amp; H23 &amp; "','" &amp; I23 &amp;  "','" &amp; J23 &amp;  "','" &amp; K23 &amp;  "','" &amp; L23 &amp; "');"</f>
+        <f t="shared" ref="M23" si="8">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A23 &amp; "','" &amp; D23 &amp; "','" &amp; E23 &amp; "','" &amp; G23 &amp; "','" &amp; H23 &amp; "','" &amp; I23 &amp;  "','" &amp; J23 &amp;  "','" &amp; K23 &amp;  "','" &amp; L23 &amp; "');"</f>
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('22','1','Kelly Wan','Digital Artist &amp; Content Creator ','121','---','---','kellywan@livingrealtykw.com','Staff');</v>
       </c>
     </row>
@@ -15167,10 +15143,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C24" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -15179,10 +15155,10 @@
         <v>46</v>
       </c>
       <c r="F24" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G24" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="H24">
         <v>522</v>
@@ -15194,10 +15170,10 @@
         <v>48</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="L24" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M24" t="str">
         <f t="shared" si="0"/>
@@ -15209,10 +15185,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C25" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -15233,10 +15209,10 @@
         <v>48</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="L25" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M25" t="str">
         <f t="shared" si="0"/>
@@ -15251,7 +15227,7 @@
         <v>51</v>
       </c>
       <c r="C26" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D26">
         <v>2</v>
@@ -15260,25 +15236,25 @@
         <v>52</v>
       </c>
       <c r="F26" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G26" t="s">
         <v>53</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="J26" t="s">
         <v>54</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="L26" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="M26" t="str">
         <f t="shared" si="0"/>
@@ -15293,7 +15269,7 @@
         <v>51</v>
       </c>
       <c r="C27" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -15302,7 +15278,7 @@
         <v>55</v>
       </c>
       <c r="F27" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G27" t="s">
         <v>56</v>
@@ -15317,10 +15293,10 @@
         <v>13</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="L27" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M27" t="str">
         <f t="shared" si="0"/>
@@ -15335,7 +15311,7 @@
         <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D28">
         <v>2</v>
@@ -15344,10 +15320,10 @@
         <v>59</v>
       </c>
       <c r="F28" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G28" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>13</v>
@@ -15359,10 +15335,10 @@
         <v>58</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="L28" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M28" t="str">
         <f t="shared" si="0"/>
@@ -15377,16 +15353,16 @@
         <v>51</v>
       </c>
       <c r="C29" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D29">
         <v>2</v>
       </c>
       <c r="E29" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="F29" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G29" t="s">
         <v>60</v>
@@ -15401,13 +15377,13 @@
         <v>58</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="L29" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M29" t="str">
-        <f t="shared" ref="M29" si="8">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A29 &amp; "','" &amp; D29 &amp; "','" &amp; E29 &amp; "','" &amp; G29 &amp; "','" &amp; H29 &amp; "','" &amp; I29 &amp;  "','" &amp; J29 &amp;  "','" &amp; K29 &amp;  "','" &amp; L29 &amp; "');"</f>
+        <f t="shared" ref="M29" si="9">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A29 &amp; "','" &amp; D29 &amp; "','" &amp; E29 &amp; "','" &amp; G29 &amp; "','" &amp; H29 &amp; "','" &amp; I29 &amp;  "','" &amp; J29 &amp;  "','" &amp; K29 &amp;  "','" &amp; L29 &amp; "');"</f>
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('28','2','Kiran Li','Secretary','---','---','(905) 888-8188','kiranli@livingrealtykw.com','Staff');</v>
       </c>
     </row>
@@ -15419,7 +15395,7 @@
         <v>67</v>
       </c>
       <c r="C30" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D30">
         <v>4</v>
@@ -15428,25 +15404,25 @@
         <v>68</v>
       </c>
       <c r="F30" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G30" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="J30" t="s">
         <v>69</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="L30" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="M30" t="str">
         <f t="shared" si="0"/>
@@ -15461,58 +15437,58 @@
         <v>67</v>
       </c>
       <c r="C31" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D31">
         <v>4</v>
       </c>
       <c r="E31" t="s">
+        <v>317</v>
+      </c>
+      <c r="F31" t="s">
+        <v>289</v>
+      </c>
+      <c r="G31" t="s">
         <v>70</v>
-      </c>
-      <c r="F31" t="s">
-        <v>304</v>
-      </c>
-      <c r="G31" t="s">
-        <v>71</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I31" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J31" s="6" t="s">
         <v>13</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>273</v>
+        <v>318</v>
       </c>
       <c r="L31" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M31" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('30','4','Hui Wang','Manager Mississauga Branch','---','(416) 274-9789','---','huiwang@livingrealtykw.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('30','4','Cassandra Pacitto','Manager Mississauga Branch','---','(905) 896-0002','---','cassandrapacitto@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" t="s">
         <v>67</v>
       </c>
       <c r="C32" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D32">
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F32" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G32" t="s">
         <v>60</v>
@@ -15524,169 +15500,169 @@
         <v>13</v>
       </c>
       <c r="J32" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="L32" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M32" t="str">
-        <f t="shared" si="0"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('31','4','Vasanthan Jeyapragasam','Secretary','---','---','(905) 896-0002','vasanthanj@livingrealtykw.com','Staff');</v>
+        <f t="shared" ref="M32:M60" si="10">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A32 &amp; "','" &amp; D32 &amp; "','" &amp; E32 &amp; "','" &amp; G32 &amp; "','" &amp; H32 &amp; "','" &amp; I32 &amp;  "','" &amp; J32 &amp;  "','" &amp; K32 &amp;  "','" &amp; L32 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('32','4','Katie Wong','Secretary','---','---','(905) 896-0002','katiewong@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C33" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E33" t="s">
-        <v>296</v>
+        <v>73</v>
       </c>
       <c r="F33" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G33" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>13</v>
+        <v>196</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>13</v>
+        <v>196</v>
       </c>
       <c r="J33" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>297</v>
+        <v>262</v>
       </c>
       <c r="L33" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="M33" t="str">
-        <f t="shared" ref="M33:M62" si="9">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A33 &amp; "','" &amp; D33 &amp; "','" &amp; E33 &amp; "','" &amp; G33 &amp; "','" &amp; H33 &amp; "','" &amp; I33 &amp;  "','" &amp; J33 &amp;  "','" &amp; K33 &amp;  "','" &amp; L33 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('32','4','Katie Wong','Secretary','---','---','(905) 896-0002','katiewong@livingrealtykw.com','Staff');</v>
+        <f t="shared" si="10"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('33','5','Woodbine Office','8 Steelcase Road West, Markham, ON, L3R 1B2','--','--','T: (905) 474-0500','woodbine@livingrealtykw.com','Office Header');</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B34" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C34" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D34">
         <v>5</v>
       </c>
       <c r="E34" t="s">
+        <v>76</v>
+      </c>
+      <c r="F34" t="s">
+        <v>289</v>
+      </c>
+      <c r="G34" t="s">
         <v>75</v>
       </c>
-      <c r="F34" t="s">
-        <v>304</v>
-      </c>
-      <c r="G34" t="s">
-        <v>9</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="J34" t="s">
-        <v>76</v>
+      <c r="H34">
+        <v>176</v>
+      </c>
+      <c r="I34" t="s">
+        <v>175</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="L34" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="M34" t="str">
-        <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('33','5','Woodbine Office','8 Steelcase Road West, Markham, ON, L3R 1B2','--','--','T: (905) 474-0500','woodbine@livingrealtykw.com','Office Header');</v>
+        <f t="shared" si="10"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('34','5','Anita Huang','Manager Woobine Branch','176','(416) 523-1888','---','anitahuang@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C35" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D35">
         <v>5</v>
       </c>
       <c r="E35" t="s">
-        <v>78</v>
+        <v>319</v>
       </c>
       <c r="F35" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G35" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="H35">
-        <v>176</v>
-      </c>
-      <c r="I35" t="s">
-        <v>182</v>
-      </c>
-      <c r="J35" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I35" s="6" t="s">
         <v>13</v>
       </c>
+      <c r="J35" t="s">
+        <v>19</v>
+      </c>
       <c r="K35" s="4" t="s">
-        <v>275</v>
+        <v>320</v>
       </c>
       <c r="L35" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M35" t="str">
-        <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('34','5','Anita Huang','Manager Woobine Branch','176','(416) 523-1888','---','anitahuang@livingrealtykw.com','Staff');</v>
+        <f t="shared" si="10"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('35','5','Kim Jin','Secretary','104','---','(905) 474-0500','kimjin@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="D36">
         <v>5</v>
       </c>
       <c r="E36" t="s">
-        <v>214</v>
+        <v>79</v>
       </c>
       <c r="F36" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G36" t="s">
         <v>60</v>
       </c>
       <c r="H36">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I36" s="6" t="s">
         <v>13</v>
@@ -15695,676 +15671,673 @@
         <v>19</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="L36" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M36" t="str">
-        <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('35','5','Jimmy Lo','Secretary','104','---','(905) 474-0500','jimmylo@livingrealtykw.com','Staff');</v>
+        <f t="shared" si="10"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('36','5','Savanna Joo','Secretary','100','---','(905) 474-0500','savannajoo@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="C37" t="s">
-        <v>183</v>
+        <v>231</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E37" t="s">
-        <v>81</v>
+        <v>230</v>
       </c>
       <c r="F37" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G37" t="s">
-        <v>60</v>
-      </c>
-      <c r="H37">
-        <v>100</v>
+        <v>222</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>13</v>
+        <v>196</v>
       </c>
       <c r="J37" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="L37" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="M37" t="str">
-        <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('36','5','Savanna Joo','Secretary','100','---','(905) 474-0500','savannajoo@livingrealtykw.com','Staff');</v>
+        <f t="shared" si="10"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('37','3','Yonge &amp; Eglinton Office','2301 Yonge Street, Toronto, ON, M4P 2C6','--','--','T: (416) 223-8833','ye@livingrealtykw.com','Office Header');</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" t="s">
         <v>62</v>
       </c>
       <c r="C38" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="D38">
         <v>3</v>
       </c>
       <c r="E38" t="s">
-        <v>240</v>
+        <v>292</v>
       </c>
       <c r="F38" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G38" t="s">
-        <v>232</v>
+        <v>293</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="J38" t="s">
-        <v>63</v>
+        <v>13</v>
+      </c>
+      <c r="I38" t="s">
+        <v>294</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="L38" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="M38" t="str">
-        <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('37','3','Yonge &amp; Eglinton Office','2301 Yonge Street, Toronto, ON, M4P 2C6','--','--','T: (416) 223-8833','ye@livingrealtykw.com','Office Header');</v>
+        <f t="shared" si="10"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('38','3','Tony Prochilo ','Manager Yonge &amp; Eglinton','---','(416) 576-6312','---','tonyprochilo@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" t="s">
         <v>62</v>
       </c>
       <c r="C39" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="D39">
         <v>3</v>
       </c>
       <c r="E39" t="s">
-        <v>307</v>
+        <v>234</v>
       </c>
       <c r="F39" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="G39" t="s">
-        <v>308</v>
+        <v>60</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I39" t="s">
-        <v>309</v>
-      </c>
-      <c r="J39" s="6" t="s">
+      <c r="I39" s="6" t="s">
         <v>13</v>
       </c>
+      <c r="J39" t="s">
+        <v>66</v>
+      </c>
       <c r="K39" s="4" t="s">
-        <v>310</v>
+        <v>264</v>
       </c>
       <c r="L39" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M39" t="str">
-        <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('38','3','Tony Prochilo ','Manager Yonge &amp; Eglinton','---','(416) 576-6312','---','tonyprochilo@livingrealtykw.com','Staff');</v>
+        <f t="shared" si="10"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('39','3','Lydia Ng','Secretary','---','---','(416) 223-8833','lydiang@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40" t="s">
-        <v>62</v>
+        <v>178</v>
       </c>
       <c r="C40" t="s">
-        <v>241</v>
+        <v>178</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E40" t="s">
-        <v>244</v>
-      </c>
-      <c r="F40" t="s">
-        <v>304</v>
+        <v>81</v>
       </c>
       <c r="G40" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>13</v>
+        <v>196</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>13</v>
+        <v>196</v>
       </c>
       <c r="J40" t="s">
-        <v>66</v>
-      </c>
-      <c r="K40" s="4" t="s">
-        <v>277</v>
+        <v>83</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="L40" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="M40" t="str">
-        <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('39','3','Lydia Ng','Secretary','---','---','(416) 223-8833','lydiang@livingrealtykw.com','Staff');</v>
+        <f t="shared" si="10"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('40','7','I.C.&amp;I. Office','8 Steelcase Road West, Unit C, Markham, ON, L3R 1B2','--','--','T: (905) 474-1772','--','Office Header');</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="C41" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D41">
         <v>7</v>
       </c>
       <c r="E41" t="s">
-        <v>83</v>
+        <v>17</v>
+      </c>
+      <c r="F41" t="s">
+        <v>289</v>
       </c>
       <c r="G41" t="s">
         <v>84</v>
       </c>
-      <c r="H41" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="J41" t="s">
-        <v>85</v>
-      </c>
-      <c r="K41" s="6" t="s">
-        <v>203</v>
+      <c r="H41">
+        <v>228</v>
+      </c>
+      <c r="I41" t="s">
+        <v>18</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>241</v>
       </c>
       <c r="L41" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="M41" t="str">
-        <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('40','7','I.C.&amp;I. Office','8 Steelcase Road West, Unit C, Markham, ON, L3R 1B2','--','--','T: (905) 474-1772','--','Office Header');</v>
+        <f t="shared" si="10"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('41','7','Kelvin Wong','Manager I.C.&amp;I. Branch','228','(416) 567-7882','---','kelvin@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C42" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E42" t="s">
-        <v>17</v>
-      </c>
-      <c r="F42" t="s">
-        <v>304</v>
+        <v>86</v>
       </c>
       <c r="G42" t="s">
-        <v>86</v>
-      </c>
-      <c r="H42">
-        <v>228</v>
-      </c>
-      <c r="I42" t="s">
-        <v>18</v>
-      </c>
-      <c r="J42" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K42" s="4" t="s">
-        <v>251</v>
+        <v>9</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J42" t="s">
+        <v>87</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="L42" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="M42" t="str">
-        <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('41','7','Kelvin Wong','Manager I.C.&amp;I. Branch','228','(416) 567-7882','---','kelvin@livingrealtykw.com','Staff');</v>
+        <f t="shared" si="10"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('42','8','LPI Head Office','8 Steelcase Road West, Markham, ON, L3R 1B2','--','--','T: (905) 477-2090','--','Office Header');</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C43" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D43">
         <v>8</v>
       </c>
       <c r="E43" t="s">
-        <v>88</v>
+        <v>209</v>
       </c>
       <c r="G43" t="s">
-        <v>9</v>
-      </c>
-      <c r="H43" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="I43" s="6" t="s">
-        <v>203</v>
+        <v>15</v>
+      </c>
+      <c r="H43">
+        <v>521</v>
+      </c>
+      <c r="I43" t="s">
+        <v>24</v>
       </c>
       <c r="J43" t="s">
-        <v>89</v>
-      </c>
-      <c r="K43" s="6" t="s">
-        <v>203</v>
+        <v>25</v>
+      </c>
+      <c r="K43" t="s">
+        <v>26</v>
       </c>
       <c r="L43" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="M43" t="str">
-        <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('42','8','LPI Head Office','8 Steelcase Road West, Markham, ON, L3R 1B2','--','--','T: (905) 477-2090','--','Office Header');</v>
+        <f t="shared" si="10"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('43','8','Ben Wong','President','521','(416) 399-2311','(905) 752-3521','benw@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C44" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D44">
         <v>8</v>
       </c>
       <c r="E44" t="s">
-        <v>219</v>
+        <v>31</v>
       </c>
       <c r="G44" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="H44">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="I44" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="J44" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K44" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L44" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M44" t="str">
-        <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('43','8','Ben Wong','President','521','(416) 399-2311','(905) 752-3521','benw@livingproperties.com','Staff');</v>
+        <f t="shared" si="10"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('44','8','Winnie Tsui','Director of Operations','514','(647) 286-0145','(905) 752-3514 ','winniet@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C45" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D45">
         <v>8</v>
       </c>
       <c r="E45" t="s">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="G45" t="s">
-        <v>90</v>
+        <v>201</v>
       </c>
       <c r="H45">
-        <v>514</v>
+        <v>286</v>
       </c>
       <c r="I45" t="s">
-        <v>91</v>
-      </c>
-      <c r="J45" t="s">
-        <v>33</v>
-      </c>
-      <c r="K45" t="s">
-        <v>34</v>
+        <v>101</v>
+      </c>
+      <c r="J45" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="L45" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M45" t="str">
-        <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('44','8','Winnie Tsui','Director of Operations','514','(647) 286-0145','(905) 752-3514 ','winniet@livingproperties.com','Staff');</v>
+        <f t="shared" si="10"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('45','8','Frederick Tang','Director of Business Development','286','(416) 618-5898','-','fredt@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B46" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C46" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D46">
         <v>8</v>
       </c>
       <c r="E46" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="G46" t="s">
-        <v>208</v>
+        <v>91</v>
       </c>
       <c r="H46">
-        <v>286</v>
+        <v>512</v>
       </c>
       <c r="I46" t="s">
-        <v>107</v>
-      </c>
-      <c r="J46" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="K46" s="4" t="s">
-        <v>108</v>
+        <v>92</v>
+      </c>
+      <c r="J46" t="s">
+        <v>93</v>
+      </c>
+      <c r="K46" t="s">
+        <v>94</v>
       </c>
       <c r="L46" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M46" t="str">
-        <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('45','8','Frederick Tang','Director of Business Development','286','(416) 618-5898','-','fredt@livingproperties.com','Staff');</v>
+        <f t="shared" si="10"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('47','8','Stanley Chow','Property Manager','512','(416) 277-6098','(905) 752-3512','stanleyc@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B47" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C47" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D47">
         <v>8</v>
       </c>
       <c r="E47" t="s">
+        <v>96</v>
+      </c>
+      <c r="G47" t="s">
+        <v>91</v>
+      </c>
+      <c r="H47">
+        <v>284</v>
+      </c>
+      <c r="I47" t="s">
+        <v>97</v>
+      </c>
+      <c r="J47" t="s">
         <v>98</v>
       </c>
-      <c r="G47" t="s">
-        <v>148</v>
-      </c>
-      <c r="H47">
-        <v>516</v>
-      </c>
-      <c r="I47" s="6" t="s">
+      <c r="K47" t="s">
         <v>99</v>
       </c>
-      <c r="J47" t="s">
-        <v>100</v>
-      </c>
-      <c r="K47" t="s">
-        <v>101</v>
-      </c>
       <c r="L47" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M47" t="str">
-        <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('46','8','Karl Park','Senior Property Manager','516','(647) 286-0142','(905) 752-3516','karlp@livingproperties.com','Staff');</v>
+        <f t="shared" si="10"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('48','8','Richard Baksh','Property Manager','284','(647) 967-0088','(905) 258-0632','richardb@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="C48" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D48">
         <v>8</v>
       </c>
       <c r="E48" t="s">
-        <v>92</v>
+        <v>207</v>
       </c>
       <c r="G48" t="s">
-        <v>93</v>
-      </c>
-      <c r="H48">
-        <v>512</v>
-      </c>
-      <c r="I48" t="s">
-        <v>94</v>
+        <v>91</v>
+      </c>
+      <c r="H48" s="6">
+        <v>517</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>212</v>
       </c>
       <c r="J48" t="s">
         <v>95</v>
       </c>
-      <c r="K48" t="s">
-        <v>96</v>
+      <c r="K48" s="4" t="s">
+        <v>208</v>
       </c>
       <c r="L48" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M48" t="str">
-        <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('47','8','Stanley Chow','Property Manager','512','(416) 277-6098','(905) 752-3512','stanleyc@livingproperties.com','Staff');</v>
+        <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A48 &amp; "','" &amp; D48 &amp; "','" &amp; E48 &amp; "','" &amp; G48 &amp; "','" &amp; H48 &amp; "','" &amp; I48 &amp;  "','" &amp; J48 &amp;  "','" &amp; K48 &amp;  "','" &amp; L48 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('49','8','Ken Kam','Property Manager','517','(647) 204-4455','(905) 477-2090','kenk@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B49" t="s">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="C49" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D49">
         <v>8</v>
       </c>
       <c r="E49" t="s">
-        <v>102</v>
+        <v>285</v>
       </c>
       <c r="G49" t="s">
-        <v>93</v>
-      </c>
-      <c r="H49">
-        <v>284</v>
-      </c>
-      <c r="I49" t="s">
-        <v>103</v>
+        <v>91</v>
+      </c>
+      <c r="H49" s="6">
+        <v>520</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>287</v>
       </c>
       <c r="J49" t="s">
-        <v>104</v>
-      </c>
-      <c r="K49" t="s">
-        <v>105</v>
+        <v>95</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>286</v>
       </c>
       <c r="L49" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M49" t="str">
-        <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('48','8','Richard Baksh','Property Manager','284','(647) 967-0088','(905) 258-0632','richardb@livingproperties.com','Staff');</v>
+        <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A49 &amp; "','" &amp; D49 &amp; "','" &amp; E49 &amp; "','" &amp; G49 &amp; "','" &amp; H49 &amp; "','" &amp; I49 &amp;  "','" &amp; J49 &amp;  "','" &amp; K49 &amp;  "','" &amp; L49 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('50','8','Raymond Chin','Property Manager','520','(437) 331-6038','(905) 477-2090','raymondc@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="C50" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D50">
         <v>8</v>
       </c>
       <c r="E50" t="s">
-        <v>217</v>
+        <v>296</v>
       </c>
       <c r="G50" t="s">
-        <v>93</v>
-      </c>
-      <c r="H50" s="6">
-        <v>517</v>
+        <v>237</v>
+      </c>
+      <c r="H50">
+        <v>168</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>222</v>
+        <v>298</v>
       </c>
       <c r="J50" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="L50" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M50" t="str">
-        <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A50 &amp; "','" &amp; D50 &amp; "','" &amp; E50 &amp; "','" &amp; G50 &amp; "','" &amp; H50 &amp; "','" &amp; I50 &amp;  "','" &amp; J50 &amp;  "','" &amp; K50 &amp;  "','" &amp; L50 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('49','8','Ken Kam','Property Manager','517','(647) 204-4455','(905) 477-2090','kenk@livingproperties.com','Staff');</v>
+        <f t="shared" ref="M50" si="11">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A50 &amp; "','" &amp; D50 &amp; "','" &amp; E50 &amp; "','" &amp; G50 &amp; "','" &amp; H50 &amp; "','" &amp; I50 &amp;  "','" &amp; J50 &amp;  "','" &amp; K50 &amp;  "','" &amp; L50 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('51','8','Thomas Lee','Assistant Property Manager','168','(416) 567-4274','(905) 477-2090','Thomasl@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B51" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="C51" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="D51">
         <v>8</v>
       </c>
       <c r="E51" t="s">
-        <v>300</v>
+        <v>110</v>
       </c>
       <c r="G51" t="s">
-        <v>93</v>
-      </c>
-      <c r="H51" s="6">
-        <v>520</v>
+        <v>35</v>
+      </c>
+      <c r="H51">
+        <v>210</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="J51" t="s">
-        <v>97</v>
-      </c>
-      <c r="K51" s="4" t="s">
-        <v>301</v>
+        <v>13</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K51" t="s">
+        <v>111</v>
       </c>
       <c r="L51" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M51" t="str">
-        <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A51 &amp; "','" &amp; D51 &amp; "','" &amp; E51 &amp; "','" &amp; G51 &amp; "','" &amp; H51 &amp; "','" &amp; I51 &amp;  "','" &amp; J51 &amp;  "','" &amp; K51 &amp;  "','" &amp; L51 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('50','8','Raymond Chin','Property Manager','520','(437) 331-6038','(905) 477-2090','raymondc@livingproperties.com','Staff');</v>
+        <f t="shared" si="10"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('52','8','Loretta Leung','Executive Assistant','210','---','---','lorettal@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B52" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C52" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D52">
         <v>8</v>
       </c>
       <c r="E52" t="s">
-        <v>311</v>
+        <v>103</v>
       </c>
       <c r="G52" t="s">
-        <v>247</v>
+        <v>280</v>
       </c>
       <c r="H52">
-        <v>168</v>
+        <v>518</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>313</v>
+        <v>13</v>
       </c>
       <c r="J52" t="s">
-        <v>97</v>
-      </c>
-      <c r="K52" s="4" t="s">
-        <v>312</v>
+        <v>156</v>
+      </c>
+      <c r="K52" t="s">
+        <v>104</v>
       </c>
       <c r="L52" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M52" t="str">
-        <f t="shared" ref="M52" si="10">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A52 &amp; "','" &amp; D52 &amp; "','" &amp; E52 &amp; "','" &amp; G52 &amp; "','" &amp; H52 &amp; "','" &amp; I52 &amp;  "','" &amp; J52 &amp;  "','" &amp; K52 &amp;  "','" &amp; L52 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('51','8','Thomas Lee','Assistant Property Manager','168','(416) 567-4274','(905) 477-2090','Thomasl@livingproperties.com','Staff');</v>
+        <f t="shared" ref="M52" si="12">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A52 &amp; "','" &amp; D52 &amp; "','" &amp; E52 &amp; "','" &amp; G52 &amp; "','" &amp; H52 &amp; "','" &amp; I52 &amp;  "','" &amp; J52 &amp;  "','" &amp; K52 &amp;  "','" &amp; L52 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('53','8','Simon Li','Senior Accountant','518','---','(905) 752-3518','simonl@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C53" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D53">
         <v>8</v>
       </c>
       <c r="E53" t="s">
-        <v>116</v>
+        <v>210</v>
       </c>
       <c r="G53" t="s">
-        <v>35</v>
+        <v>182</v>
       </c>
       <c r="H53">
-        <v>210</v>
+        <v>281</v>
       </c>
       <c r="I53" s="6" t="s">
         <v>13</v>
@@ -16372,77 +16345,77 @@
       <c r="J53" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K53" t="s">
-        <v>117</v>
+      <c r="K53" s="4" t="s">
+        <v>211</v>
       </c>
       <c r="L53" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M53" t="str">
-        <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('52','8','Loretta Leung','Executive Assistant','210','---','---','lorettal@livingproperties.com','Staff');</v>
+        <f t="shared" ref="M53" si="13">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A53 &amp; "','" &amp; D53 &amp; "','" &amp; E53 &amp; "','" &amp; G53 &amp; "','" &amp; H53 &amp; "','" &amp; I53 &amp;  "','" &amp; J53 &amp;  "','" &amp; K53 &amp;  "','" &amp; L53 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('54','8','Nicole Leung','Property Accountant','281','---','---','nicolel@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B54" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C54" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D54">
         <v>8</v>
       </c>
       <c r="E54" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G54" t="s">
-        <v>295</v>
+        <v>108</v>
       </c>
       <c r="H54">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="I54" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J54" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="K54" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="L54" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M54" t="str">
-        <f t="shared" ref="M54" si="11">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A54 &amp; "','" &amp; D54 &amp; "','" &amp; E54 &amp; "','" &amp; G54 &amp; "','" &amp; H54 &amp; "','" &amp; I54 &amp;  "','" &amp; J54 &amp;  "','" &amp; K54 &amp;  "','" &amp; L54 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('53','8','Simon Li','Senior Accountant','518','---','(905) 752-3518','simonl@livingproperties.com','Staff');</v>
+        <f t="shared" si="10"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('55','8','Vivian Lum','Accounts Receivable Clerk','523','---','(905) 752-3523','vivianl@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B55" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C55" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D55">
         <v>8</v>
       </c>
       <c r="E55" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="G55" t="s">
-        <v>189</v>
+        <v>279</v>
       </c>
       <c r="H55">
-        <v>281</v>
+        <v>223</v>
       </c>
       <c r="I55" s="6" t="s">
         <v>13</v>
@@ -16451,76 +16424,76 @@
         <v>13</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="L55" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M55" t="str">
-        <f t="shared" ref="M55" si="12">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A55 &amp; "','" &amp; D55 &amp; "','" &amp; E55 &amp; "','" &amp; G55 &amp; "','" &amp; H55 &amp; "','" &amp; I55 &amp;  "','" &amp; J55 &amp;  "','" &amp; K55 &amp;  "','" &amp; L55 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('54','8','Nicole Leung','Property Accountant','281','---','---','nicolel@livingproperties.com','Staff');</v>
+        <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A55 &amp; "','" &amp; D55 &amp; "','" &amp; E55 &amp; "','" &amp; G55 &amp; "','" &amp; H55 &amp; "','" &amp; I55 &amp;  "','" &amp; J55 &amp;  "','" &amp; K55 &amp;  "','" &amp; L55 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('56','8','Jessica Lee','Accounting Clerk ','223','---','---','jessical@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C56" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D56">
         <v>8</v>
       </c>
       <c r="E56" t="s">
-        <v>111</v>
+        <v>238</v>
       </c>
       <c r="G56" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H56">
-        <v>523</v>
+        <v>172</v>
       </c>
       <c r="I56" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J56" t="s">
-        <v>164</v>
-      </c>
-      <c r="K56" t="s">
-        <v>113</v>
+      <c r="J56" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>239</v>
       </c>
       <c r="L56" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M56" t="str">
-        <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('55','8','Vivian Lum','Accounts Receivable Clerk','523','---','(905) 752-3523','vivianl@livingproperties.com','Staff');</v>
+        <f t="shared" ref="M56" si="14">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A56 &amp; "','" &amp; D56 &amp; "','" &amp; E56 &amp; "','" &amp; G56 &amp; "','" &amp; H56 &amp; "','" &amp; I56 &amp;  "','" &amp; J56 &amp;  "','" &amp; K56 &amp;  "','" &amp; L56 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('57','8','Rebecca Lau','Administrative Assistant','172','---','---','rebeccal@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B57" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C57" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D57">
         <v>8</v>
       </c>
       <c r="E57" t="s">
-        <v>212</v>
+        <v>283</v>
       </c>
       <c r="G57" t="s">
-        <v>294</v>
+        <v>109</v>
       </c>
       <c r="H57">
-        <v>223</v>
+        <v>182</v>
       </c>
       <c r="I57" s="6" t="s">
         <v>13</v>
@@ -16529,76 +16502,76 @@
         <v>13</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>213</v>
+        <v>284</v>
       </c>
       <c r="L57" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M57" t="str">
-        <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A57 &amp; "','" &amp; D57 &amp; "','" &amp; E57 &amp; "','" &amp; G57 &amp; "','" &amp; H57 &amp; "','" &amp; I57 &amp;  "','" &amp; J57 &amp;  "','" &amp; K57 &amp;  "','" &amp; L57 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('56','8','Jessica Lee','Accounting Clerk ','223','---','---','jessical@livingproperties.com','Staff');</v>
+        <f t="shared" ref="M57" si="15">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A57 &amp; "','" &amp; D57 &amp; "','" &amp; E57 &amp; "','" &amp; G57 &amp; "','" &amp; H57 &amp; "','" &amp; I57 &amp;  "','" &amp; J57 &amp;  "','" &amp; K57 &amp;  "','" &amp; L57 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('58','8','Kelvin Chan','Administrative Assistant','182','---','---','kelvinc@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C58" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D58">
         <v>8</v>
       </c>
       <c r="E58" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="G58" t="s">
-        <v>115</v>
-      </c>
-      <c r="H58">
-        <v>172</v>
+        <v>183</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="I58" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J58" s="6" t="s">
-        <v>13</v>
+      <c r="J58" t="s">
+        <v>95</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="L58" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M58" t="str">
-        <f t="shared" ref="M58" si="13">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A58 &amp; "','" &amp; D58 &amp; "','" &amp; E58 &amp; "','" &amp; G58 &amp; "','" &amp; H58 &amp; "','" &amp; I58 &amp;  "','" &amp; J58 &amp;  "','" &amp; K58 &amp;  "','" &amp; L58 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('57','8','Rebecca Lau','Administrative Assistant','172','---','---','rebeccal@livingproperties.com','Staff');</v>
+        <f t="shared" si="10"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('59','8','Calmaine Hewitt','Handyman','---','---','(905) 477-2090','calmaineh@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C59" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D59">
         <v>8</v>
       </c>
       <c r="E59" t="s">
-        <v>298</v>
+        <v>155</v>
       </c>
       <c r="G59" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="H59">
-        <v>182</v>
+        <v>229</v>
       </c>
       <c r="I59" s="6" t="s">
         <v>13</v>
@@ -16606,809 +16579,809 @@
       <c r="J59" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K59" s="4" t="s">
-        <v>299</v>
+      <c r="K59" t="s">
+        <v>112</v>
       </c>
       <c r="L59" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M59" t="str">
-        <f t="shared" ref="M59" si="14">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A59 &amp; "','" &amp; D59 &amp; "','" &amp; E59 &amp; "','" &amp; G59 &amp; "','" &amp; H59 &amp; "','" &amp; I59 &amp;  "','" &amp; J59 &amp;  "','" &amp; K59 &amp;  "','" &amp; L59 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('58','8','Kelvin Chan','Administrative Assistant','182','---','---','kelvinc@livingproperties.com','Staff');</v>
+        <f t="shared" si="10"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('60','8','Matthew Wong','Accounting Clerk','229','---','---','mattheww@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>188</v>
+        <v>113</v>
       </c>
       <c r="C60" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D60">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E60" t="s">
-        <v>242</v>
+        <v>114</v>
       </c>
       <c r="G60" t="s">
-        <v>190</v>
+        <v>115</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>13</v>
+        <v>196</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>13</v>
+        <v>196</v>
       </c>
       <c r="J60" t="s">
-        <v>97</v>
-      </c>
-      <c r="K60" s="4" t="s">
-        <v>243</v>
+        <v>116</v>
+      </c>
+      <c r="K60" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="L60" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="M60" t="str">
-        <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('59','8','Calmaine Hewitt','Handyman','---','---','(905) 477-2090','calmaineh@livingproperties.com','Staff');</v>
+        <f t="shared" si="10"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('61','9','Centro Towers Office','25 Town Centre Crt, Scarborough, ON, M1P 0B4','--','--','T: (416) 290-1242','--','Office Header');</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>188</v>
+        <v>113</v>
       </c>
       <c r="C61" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D61">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E61" t="s">
-        <v>162</v>
+        <v>117</v>
       </c>
       <c r="G61" t="s">
-        <v>112</v>
-      </c>
-      <c r="H61">
-        <v>229</v>
-      </c>
-      <c r="I61" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H61" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J61" s="6" t="s">
-        <v>13</v>
+      <c r="I61" t="s">
+        <v>118</v>
+      </c>
+      <c r="J61" t="s">
+        <v>119</v>
       </c>
       <c r="K61" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L61" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M61" t="str">
-        <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('60','8','Matthew Wong','Accounting Clerk','229','---','---','mattheww@livingproperties.com','Staff');</v>
+        <f t="shared" ref="M61:M83" si="16">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A61 &amp; "','" &amp; D61 &amp; "','" &amp; E61 &amp; "','" &amp; G61 &amp; "','" &amp; H61 &amp; "','" &amp; I61 &amp;  "','" &amp; J61 &amp;  "','" &amp; K61 &amp;  "','" &amp; L61 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('62','9','Henry Fu','Property Manager','---','(416) 278-2953','(416) 290-1242','henry@centrotowers.com','Staff');</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C62" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D62">
         <v>9</v>
       </c>
       <c r="E62" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G62" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>203</v>
+        <v>13</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>203</v>
+        <v>13</v>
       </c>
       <c r="J62" t="s">
-        <v>122</v>
-      </c>
-      <c r="K62" s="6" t="s">
-        <v>203</v>
+        <v>119</v>
+      </c>
+      <c r="K62" t="s">
+        <v>123</v>
       </c>
       <c r="L62" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="M62" t="str">
-        <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('61','9','Centro Towers Office','25 Town Centre Crt, Scarborough, ON, M1P 0B4','--','--','T: (416) 290-1242','--','Office Header');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('63','9','Sophia Yip','Property Administrator','---','---','(416) 290-1242','sophia@centrotowers.com','Staff');</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C63" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D63">
         <v>9</v>
       </c>
       <c r="E63" t="s">
-        <v>123</v>
+        <v>299</v>
       </c>
       <c r="G63" t="s">
-        <v>93</v>
+        <v>302</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I63" t="s">
-        <v>124</v>
-      </c>
-      <c r="J63" t="s">
-        <v>125</v>
-      </c>
-      <c r="K63" t="s">
-        <v>126</v>
-      </c>
-      <c r="L63" t="s">
-        <v>167</v>
+      <c r="I63" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J63" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="K63" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="M63" t="str">
-        <f t="shared" ref="M63:M85" si="15">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A63 &amp; "','" &amp; D63 &amp; "','" &amp; E63 &amp; "','" &amp; G63 &amp; "','" &amp; H63 &amp; "','" &amp; I63 &amp;  "','" &amp; J63 &amp;  "','" &amp; K63 &amp;  "','" &amp; L63 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('62','9','Henry Fu','Property Manager','---','(416) 278-2953','(416) 290-1242','henry@centrotowers.com','Staff');</v>
+        <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A63 &amp; "','" &amp; D63 &amp; "','" &amp; E63 &amp; "','" &amp; G63 &amp; "','" &amp; H63 &amp; "','" &amp; I63 &amp;  "','" &amp; J63 &amp;  "','" &amp; K63 &amp;  "','" &amp; L63 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('64','9','Security Desk ','Centro Security Desk ','---','---','(416) 296-0099','---','');</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="C64" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D64">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E64" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="G64" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>13</v>
+        <v>196</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>13</v>
+        <v>196</v>
       </c>
       <c r="J64" t="s">
-        <v>125</v>
-      </c>
-      <c r="K64" t="s">
-        <v>129</v>
+        <v>141</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>223</v>
       </c>
       <c r="L64" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="M64" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('63','9','Sophia Yip','Property Administrator','---','---','(416) 290-1242','sophia@centrotowers.com','Staff');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('65','11','EQ1 Office','70 Town Centre Court, Scarborough, ON, M1P 0B2','--','--','T: (416) 279-0603 ','eq1@livingproperties.com','Office Header');</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B65" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="C65" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D65">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E65" t="s">
-        <v>314</v>
+        <v>227</v>
       </c>
       <c r="G65" t="s">
-        <v>317</v>
+        <v>91</v>
       </c>
       <c r="H65" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I65" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J65" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="K65" s="6" t="s">
-        <v>13</v>
+      <c r="I65" t="s">
+        <v>224</v>
+      </c>
+      <c r="J65" t="s">
+        <v>142</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="L65" t="s">
+        <v>160</v>
       </c>
       <c r="M65" t="str">
-        <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A65 &amp; "','" &amp; D65 &amp; "','" &amp; E65 &amp; "','" &amp; G65 &amp; "','" &amp; H65 &amp; "','" &amp; I65 &amp;  "','" &amp; J65 &amp;  "','" &amp; K65 &amp;  "','" &amp; L65 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('64','9','Security Desk ','Centro Security Desk ','---','---','(416) 296-0099','---','');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('66','11','Ming Ip','Property Manager','---','(647) 286-0147','(416) 279-0603 ','eq1manager@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C66" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D66">
         <v>11</v>
       </c>
       <c r="E66" t="s">
-        <v>145</v>
+        <v>299</v>
       </c>
       <c r="G66" t="s">
-        <v>146</v>
+        <v>308</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>203</v>
+        <v>13</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="J66" t="s">
-        <v>147</v>
-      </c>
-      <c r="K66" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="L66" t="s">
-        <v>165</v>
+        <v>13</v>
+      </c>
+      <c r="J66" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="K66" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="M66" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('65','11','EQ1 Office','70 Town Centre Court, Scarborough, ON, M1P 0B2','--','--','T: (416) 279-0603 ','eq1@livingproperties.com','Office Header');</v>
+        <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A66 &amp; "','" &amp; D66 &amp; "','" &amp; E66 &amp; "','" &amp; G66 &amp; "','" &amp; H66 &amp; "','" &amp; I66 &amp;  "','" &amp; J66 &amp;  "','" &amp; K66 &amp;  "','" &amp; L66 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('67','11','Security Desk ','EQ1 Security Desk ','---','---','(416) 279-1894','---','');</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>144</v>
+        <v>304</v>
       </c>
       <c r="C67" t="s">
-        <v>193</v>
+        <v>305</v>
       </c>
       <c r="D67">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E67" t="s">
-        <v>237</v>
+        <v>270</v>
       </c>
       <c r="G67" t="s">
-        <v>93</v>
+        <v>272</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I67" t="s">
-        <v>234</v>
+        <v>196</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="J67" t="s">
-        <v>149</v>
-      </c>
-      <c r="K67" s="4" t="s">
-        <v>250</v>
+        <v>273</v>
+      </c>
+      <c r="K67" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="L67" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="M67" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('66','11','Ming Ip','Property Manager','---','(647) 286-0147','(416) 279-0603 ','eq1manager@livingproperties.com','Staff');</v>
+        <f t="shared" ref="M67:M68" si="17">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A67 &amp; "','" &amp; D67 &amp; "','" &amp; E67 &amp; "','" &amp; G67 &amp; "','" &amp; H67 &amp; "','" &amp; I67 &amp;  "','" &amp; J67 &amp;  "','" &amp; K67 &amp;  "','" &amp; L67 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('68','12','EQ2 Office','60 Town Centre Court, Scarborough, ON, M1P 0B1','--','--','T: (416) 279-0591 ','--','Office Header');</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>144</v>
+        <v>304</v>
       </c>
       <c r="C68" t="s">
-        <v>193</v>
+        <v>305</v>
       </c>
       <c r="D68">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E68" t="s">
-        <v>314</v>
+        <v>271</v>
       </c>
       <c r="G68" t="s">
-        <v>323</v>
+        <v>91</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I68" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J68" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="K68" s="6" t="s">
-        <v>13</v>
+      <c r="I68" t="s">
+        <v>275</v>
+      </c>
+      <c r="J68" t="s">
+        <v>274</v>
+      </c>
+      <c r="K68" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="L68" t="s">
+        <v>160</v>
       </c>
       <c r="M68" t="str">
-        <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A68 &amp; "','" &amp; D68 &amp; "','" &amp; E68 &amp; "','" &amp; G68 &amp; "','" &amp; H68 &amp; "','" &amp; I68 &amp;  "','" &amp; J68 &amp;  "','" &amp; K68 &amp;  "','" &amp; L68 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('67','11','Security Desk ','EQ1 Security Desk ','---','---','(416) 279-1894','---','');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('69','12','Aaron Ma','Property Manager','---','(416) 684-2236','(416) 279-0591','eq2manager@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="C69" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="D69">
         <v>12</v>
       </c>
       <c r="E69" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="G69" t="s">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>203</v>
+        <v>13</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>203</v>
+        <v>13</v>
       </c>
       <c r="J69" t="s">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="L69" t="s">
-        <v>165</v>
+        <v>13</v>
       </c>
       <c r="M69" t="str">
-        <f t="shared" ref="M69:M70" si="16">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A69 &amp; "','" &amp; D69 &amp; "','" &amp; E69 &amp; "','" &amp; G69 &amp; "','" &amp; H69 &amp; "','" &amp; I69 &amp;  "','" &amp; J69 &amp;  "','" &amp; K69 &amp;  "','" &amp; L69 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('68','12','EQ2 Office','60 Town Centre Court, Scarborough, ON, M1P 0B1','--','--','T: (416) 279-0591 ','--','Office Header');</v>
+        <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A69 &amp; "','" &amp; D69 &amp; "','" &amp; E69 &amp; "','" &amp; G69 &amp; "','" &amp; H69 &amp; "','" &amp; I69 &amp;  "','" &amp; J69 &amp;  "','" &amp; K69 &amp;  "','" &amp; L69 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('70','12','Security Desk ','EQ2 Security Desk ','---','---','(416) 279-1211','---','');</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>319</v>
+        <v>214</v>
       </c>
       <c r="C70" t="s">
-        <v>320</v>
+        <v>215</v>
       </c>
       <c r="D70">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E70" t="s">
-        <v>286</v>
+        <v>217</v>
       </c>
       <c r="G70" t="s">
-        <v>93</v>
+        <v>218</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I70" t="s">
-        <v>290</v>
-      </c>
-      <c r="J70" t="s">
-        <v>289</v>
-      </c>
-      <c r="K70" s="4" t="s">
-        <v>291</v>
+        <v>196</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="J70" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="K70" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="L70" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="M70" t="str">
         <f t="shared" si="16"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('69','12','Aaron Ma','Property Manager','---','(416) 684-2236','(416) 279-0591','eq2manager@livingproperties.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('71','13','Alton Tower Office','160 Alton Towers Cir, Toronto, ON, M1V 4X8','--','--','T: (437)-533-1208','--','Office Header');</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B71" t="s">
-        <v>319</v>
+        <v>214</v>
       </c>
       <c r="C71" t="s">
-        <v>320</v>
+        <v>215</v>
       </c>
       <c r="D71">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E71" t="s">
-        <v>314</v>
+        <v>207</v>
       </c>
       <c r="G71" t="s">
-        <v>324</v>
+        <v>91</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>13</v>
+        <v>212</v>
       </c>
       <c r="J71" t="s">
-        <v>322</v>
-      </c>
-      <c r="K71" s="6" t="s">
-        <v>13</v>
+        <v>95</v>
+      </c>
+      <c r="K71" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="L71" t="s">
+        <v>160</v>
       </c>
       <c r="M71" t="str">
         <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A71 &amp; "','" &amp; D71 &amp; "','" &amp; E71 &amp; "','" &amp; G71 &amp; "','" &amp; H71 &amp; "','" &amp; I71 &amp;  "','" &amp; J71 &amp;  "','" &amp; K71 &amp;  "','" &amp; L71 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('70','12','Security Desk ','EQ2 Security Desk ','---','---','(416) 279-1211','---','');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('72','13','Ken Kam','Property Manager','---','(647) 204-4455','(905) 477-2090','kenk@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B72" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="C72" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="D72">
         <v>13</v>
       </c>
       <c r="E72" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="G72" t="s">
+        <v>109</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I72" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="H72" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="I72" s="6" t="s">
-        <v>203</v>
-      </c>
       <c r="J72" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="K72" s="6" t="s">
-        <v>203</v>
+        <v>13</v>
+      </c>
+      <c r="K72" s="4" t="s">
+        <v>216</v>
       </c>
       <c r="L72" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="M72" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('71','13','Alton Tower Office','160 Alton Towers Cir, Toronto, ON, M1V 4X8','--','--','T: (437)-533-1208','--','Office Header');</v>
+        <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A72 &amp; "','" &amp; D72 &amp; "','" &amp; E72 &amp; "','" &amp; G72 &amp; "','" &amp; H72 &amp; "','" &amp; I72 &amp;  "','" &amp; J72 &amp;  "','" &amp; K72 &amp;  "','" &amp; L72 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('73','13','Christie Ip','Administrative Assistant','---','(437)-533-1208','---','optima2@livingproperties.com ','Staff');</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B73" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="C73" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="D73">
         <v>13</v>
       </c>
       <c r="E73" t="s">
-        <v>217</v>
+        <v>299</v>
       </c>
       <c r="G73" t="s">
-        <v>93</v>
+        <v>300</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="J73" t="s">
-        <v>97</v>
-      </c>
-      <c r="K73" s="4" t="s">
-        <v>218</v>
+        <v>13</v>
+      </c>
+      <c r="J73" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="K73" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="L73" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="M73" t="str">
         <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A73 &amp; "','" &amp; D73 &amp; "','" &amp; E73 &amp; "','" &amp; G73 &amp; "','" &amp; H73 &amp; "','" &amp; I73 &amp;  "','" &amp; J73 &amp;  "','" &amp; K73 &amp;  "','" &amp; L73 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('72','13','Ken Kam','Property Manager','---','(647) 204-4455','(905) 477-2090','kenk@livingproperties.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('74','13','Security Desk ','Alton Tower Security Desk ','---','---','(416) 754-3131','---','Staff');</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>224</v>
+        <v>125</v>
       </c>
       <c r="C74" t="s">
-        <v>225</v>
+        <v>125</v>
       </c>
       <c r="D74">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E74" t="s">
-        <v>245</v>
+        <v>126</v>
       </c>
       <c r="G74" t="s">
-        <v>115</v>
+        <v>9</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>13</v>
+        <v>196</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="J74" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K74" s="4" t="s">
-        <v>226</v>
+        <v>196</v>
+      </c>
+      <c r="J74" t="s">
+        <v>127</v>
+      </c>
+      <c r="K74" t="s">
+        <v>128</v>
       </c>
       <c r="L74" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="M74" t="str">
-        <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A74 &amp; "','" &amp; D74 &amp; "','" &amp; E74 &amp; "','" &amp; G74 &amp; "','" &amp; H74 &amp; "','" &amp; I74 &amp;  "','" &amp; J74 &amp;  "','" &amp; K74 &amp;  "','" &amp; L74 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('73','13','Christie Ip','Administrative Assistant','---','(437)-533-1208','---','optima2@livingproperties.com ','Staff');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('75','14','IHMG Office','8 Steelcase Road West, Markham, ON, L3R 1B2','--','--','T: (905) 475-6000','info@ihmg.ca','Office Header');</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>224</v>
+        <v>125</v>
       </c>
       <c r="C75" t="s">
-        <v>225</v>
+        <v>125</v>
       </c>
       <c r="D75">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E75" t="s">
-        <v>314</v>
+        <v>129</v>
       </c>
       <c r="G75" t="s">
-        <v>315</v>
+        <v>130</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>13</v>
+        <v>196</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J75" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="K75" s="6" t="s">
-        <v>13</v>
+        <v>196</v>
+      </c>
+      <c r="J75" t="s">
+        <v>131</v>
+      </c>
+      <c r="K75" s="4" t="s">
+        <v>132</v>
       </c>
       <c r="L75" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="M75" t="str">
-        <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A75 &amp; "','" &amp; D75 &amp; "','" &amp; E75 &amp; "','" &amp; G75 &amp; "','" &amp; H75 &amp; "','" &amp; I75 &amp;  "','" &amp; J75 &amp;  "','" &amp; K75 &amp;  "','" &amp; L75 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('74','13','Security Desk ','Alton Tower Security Desk ','---','---','(416) 754-3131','---','Staff');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('76','14','IHMGRI Office','8 Steelcase Road West, Unit E, Markham, ON, L3R 1B2','--','--','T: (905) 489-8989','realestate@ihmg.ca','Office Header');</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B76" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C76" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D76">
         <v>14</v>
       </c>
       <c r="E76" t="s">
-        <v>132</v>
+        <v>187</v>
       </c>
       <c r="G76" t="s">
-        <v>9</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="I76" s="6" t="s">
-        <v>203</v>
+        <v>188</v>
+      </c>
+      <c r="H76">
+        <v>120</v>
+      </c>
+      <c r="I76" t="s">
+        <v>189</v>
       </c>
       <c r="J76" t="s">
         <v>133</v>
       </c>
-      <c r="K76" t="s">
-        <v>134</v>
+      <c r="K76" s="4" t="s">
+        <v>190</v>
       </c>
       <c r="L76" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="M76" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('75','14','IHMG Office','8 Steelcase Road West, Markham, ON, L3R 1B2','--','--','T: (905) 475-6000','info@ihmg.ca','Office Header');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('77','14','Eddie Tang','Financial Controller','120','(416) 723-8329','(905) 489-0186','eddie@ihmg.ca','Staff');</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C77" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D77">
         <v>14</v>
       </c>
       <c r="E77" t="s">
+        <v>134</v>
+      </c>
+      <c r="G77" t="s">
+        <v>191</v>
+      </c>
+      <c r="H77">
+        <v>187</v>
+      </c>
+      <c r="I77" t="s">
         <v>135</v>
       </c>
-      <c r="G77" t="s">
+      <c r="J77" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K77" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="H77" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="I77" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="J77" t="s">
-        <v>137</v>
-      </c>
-      <c r="K77" s="4" t="s">
-        <v>138</v>
-      </c>
       <c r="L77" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="M77" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('76','14','IHMGRI Office','8 Steelcase Road West, Unit E, Markham, ON, L3R 1B2','--','--','T: (905) 489-8989','realestate@ihmg.ca','Office Header');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('78','14','Lily Hou','Senior Accounting Analyst &amp; Operations Support','187','(647) 774-8994','---','lily@ihmg.ca','Staff');</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B78" t="s">
-        <v>131</v>
+        <v>180</v>
       </c>
       <c r="C78" t="s">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="D78">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E78" t="s">
+        <v>143</v>
+      </c>
+      <c r="G78" t="s">
+        <v>192</v>
+      </c>
+      <c r="H78">
+        <v>541</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J78" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K78" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="G78" t="s">
-        <v>195</v>
-      </c>
-      <c r="H78">
-        <v>120</v>
-      </c>
-      <c r="I78" t="s">
-        <v>196</v>
-      </c>
-      <c r="J78" t="s">
-        <v>139</v>
-      </c>
-      <c r="K78" s="4" t="s">
-        <v>197</v>
-      </c>
       <c r="L78" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="M78" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('77','14','Eddie Tang','Financial Controller','120','(416) 723-8329','(905) 489-0186','eddie@ihmg.ca','Staff');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('79','1','Lunch Room','Meeting Room','541','---','---','-','Meeting Room');</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B79" t="s">
-        <v>131</v>
+        <v>180</v>
       </c>
       <c r="C79" t="s">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="D79">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E79" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G79" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="H79">
-        <v>187</v>
-      </c>
-      <c r="I79" t="s">
-        <v>141</v>
+        <v>250</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="J79" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K79" s="4" t="s">
-        <v>142</v>
+      <c r="K79" s="6" t="s">
+        <v>194</v>
       </c>
       <c r="L79" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="M79" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('78','14','Lily Hou','Senior Accounting Analyst &amp; Operations Support','187','(647) 774-8994','---','lily@ihmg.ca','Staff');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('80','1','Markham Room','Meeting Room','250','---','---','-','Meeting Room');</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C80" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D80">
         <v>1</v>
       </c>
       <c r="E80" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G80" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="H80">
-        <v>541</v>
+        <v>226</v>
       </c>
       <c r="I80" s="6" t="s">
         <v>13</v>
@@ -17417,37 +17390,37 @@
         <v>13</v>
       </c>
       <c r="K80" s="6" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="L80" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="M80" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('79','1','Lunch Room','Meeting Room','541','---','---','-','Meeting Room');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('81','1','Mississauga Room','Meeting Room','226','---','---','-','Meeting Room');</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C81" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D81">
         <v>1</v>
       </c>
       <c r="E81" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G81" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="H81">
-        <v>250</v>
+        <v>288</v>
       </c>
       <c r="I81" s="6" t="s">
         <v>13</v>
@@ -17456,37 +17429,37 @@
         <v>13</v>
       </c>
       <c r="K81" s="6" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="L81" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="M81" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('80','1','Markham Room','Meeting Room','250','---','---','-','Meeting Room');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('82','1','The Living Room','Meeting Room','288','---','---','-','Meeting Room');</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B82" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C82" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D82">
         <v>1</v>
       </c>
       <c r="E82" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G82" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="H82">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="I82" s="6" t="s">
         <v>13</v>
@@ -17495,37 +17468,37 @@
         <v>13</v>
       </c>
       <c r="K82" s="6" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="L82" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="M82" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('81','1','Mississauga Room','Meeting Room','226','---','---','-','Meeting Room');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('83','1','Toronto Room','Meeting Room','208','---','---','-','Meeting Room');</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B83" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="C83" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="D83">
         <v>1</v>
       </c>
       <c r="E83" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G83" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="H83">
-        <v>288</v>
+        <v>524</v>
       </c>
       <c r="I83" s="6" t="s">
         <v>13</v>
@@ -17534,91 +17507,13 @@
         <v>13</v>
       </c>
       <c r="K83" s="6" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="L83" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="M83" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('82','1','The Living Room','Meeting Room','288','---','---','-','Meeting Room');</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A84" s="5">
-        <v>83</v>
-      </c>
-      <c r="B84" t="s">
-        <v>187</v>
-      </c>
-      <c r="C84" t="s">
-        <v>179</v>
-      </c>
-      <c r="D84">
-        <v>1</v>
-      </c>
-      <c r="E84" t="s">
-        <v>154</v>
-      </c>
-      <c r="G84" t="s">
-        <v>199</v>
-      </c>
-      <c r="H84">
-        <v>208</v>
-      </c>
-      <c r="I84" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J84" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K84" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="L84" t="s">
-        <v>199</v>
-      </c>
-      <c r="M84" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('83','1','Toronto Room','Meeting Room','208','---','---','-','Meeting Room');</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A85" s="5">
-        <v>84</v>
-      </c>
-      <c r="B85" t="s">
-        <v>187</v>
-      </c>
-      <c r="C85" t="s">
-        <v>179</v>
-      </c>
-      <c r="D85">
-        <v>1</v>
-      </c>
-      <c r="E85" t="s">
-        <v>155</v>
-      </c>
-      <c r="G85" t="s">
-        <v>199</v>
-      </c>
-      <c r="H85">
-        <v>524</v>
-      </c>
-      <c r="I85" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J85" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K85" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="L85" t="s">
-        <v>199</v>
-      </c>
-      <c r="M85" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('84','1','York Room','Meeting Room','524','---','---','-','Meeting Room');</v>
       </c>
     </row>
@@ -17628,61 +17523,60 @@
     <hyperlink ref="K3" r:id="rId2" xr:uid="{61A355EB-7392-482E-A31B-18A81475FEA2}"/>
     <hyperlink ref="K4" r:id="rId3" xr:uid="{AAC52350-63BC-49E4-AB30-AA515B855C94}"/>
     <hyperlink ref="K30" r:id="rId4" xr:uid="{00DF1362-6E25-4F93-817E-87B7D5053E83}"/>
-    <hyperlink ref="K46" r:id="rId5" xr:uid="{52D2CA8B-EEC2-437B-8358-39021C3922A5}"/>
-    <hyperlink ref="K78" r:id="rId6" xr:uid="{39562F23-6CA7-49AB-9C7B-CFFD135D5569}"/>
-    <hyperlink ref="K79" r:id="rId7" xr:uid="{7D0A575D-6D1E-459A-8BE1-834C87DE6FF3}"/>
-    <hyperlink ref="K77" r:id="rId8" xr:uid="{9DB04ED1-2784-42AB-8591-C19CE3C56BAB}"/>
+    <hyperlink ref="K45" r:id="rId5" xr:uid="{52D2CA8B-EEC2-437B-8358-39021C3922A5}"/>
+    <hyperlink ref="K76" r:id="rId6" xr:uid="{39562F23-6CA7-49AB-9C7B-CFFD135D5569}"/>
+    <hyperlink ref="K77" r:id="rId7" xr:uid="{7D0A575D-6D1E-459A-8BE1-834C87DE6FF3}"/>
+    <hyperlink ref="K75" r:id="rId8" xr:uid="{9DB04ED1-2784-42AB-8591-C19CE3C56BAB}"/>
     <hyperlink ref="K9" r:id="rId9" xr:uid="{20EDEC14-38F2-4118-8479-655D5EFC4DEE}"/>
-    <hyperlink ref="K33" r:id="rId10" xr:uid="{C9F0094A-C483-4C7B-ABF0-879EAE2A2AB2}"/>
-    <hyperlink ref="K60" r:id="rId11" xr:uid="{859B2763-7E68-453C-A061-50B98A6FFD08}"/>
+    <hyperlink ref="K32" r:id="rId10" xr:uid="{C9F0094A-C483-4C7B-ABF0-879EAE2A2AB2}"/>
+    <hyperlink ref="K58" r:id="rId11" xr:uid="{859B2763-7E68-453C-A061-50B98A6FFD08}"/>
     <hyperlink ref="K31" r:id="rId12" xr:uid="{2A81680F-E264-4A37-BA66-E7145340240C}"/>
-    <hyperlink ref="K32" r:id="rId13" xr:uid="{8B99D816-A362-440E-B492-F1CAC014AD59}"/>
-    <hyperlink ref="K24" r:id="rId14" xr:uid="{C415D613-1570-441D-A891-ED3A35DEB1A5}"/>
-    <hyperlink ref="K37" r:id="rId15" xr:uid="{5DA780DA-5AE3-4673-B2D5-44E74D6CADF4}"/>
-    <hyperlink ref="K23" r:id="rId16" xr:uid="{D1B93B60-C4A2-4C1E-A23F-AA7F2DF69C12}"/>
-    <hyperlink ref="K57" r:id="rId17" xr:uid="{605D06FB-BDCA-4D83-A43A-BE83330B88FB}"/>
-    <hyperlink ref="K19" r:id="rId18" xr:uid="{B648B368-E192-405E-AF40-90D54C14ED98}"/>
-    <hyperlink ref="K58" r:id="rId19" xr:uid="{808CD1D5-334F-4AE6-8D51-87CD2C3A649E}"/>
-    <hyperlink ref="K22" r:id="rId20" xr:uid="{59A214C0-704A-4745-9A31-9E1C388968F8}"/>
-    <hyperlink ref="K55" r:id="rId21" xr:uid="{E8B48719-363A-49FC-B3C8-181E5CD398EA}"/>
-    <hyperlink ref="K50" r:id="rId22" xr:uid="{741920D7-852F-438F-9B8A-B9ABD3DE381E}"/>
-    <hyperlink ref="K74" r:id="rId23" display="mailto:optima2@livingproperties.com" xr:uid="{FC418030-4EE8-4439-92C7-DD13F00F4D6A}"/>
-    <hyperlink ref="K66" r:id="rId24" xr:uid="{51FF6984-1DC6-430F-8E60-254E7A49BE1B}"/>
-    <hyperlink ref="K73" r:id="rId25" xr:uid="{9681E0BE-E957-4347-8DBD-4A244171852E}"/>
-    <hyperlink ref="K67" r:id="rId26" xr:uid="{30A38D56-4D68-485C-9630-D527FE1A7375}"/>
-    <hyperlink ref="K16" r:id="rId27" xr:uid="{B4D2F180-C9A6-4272-89D7-2F45E07DF9D9}"/>
-    <hyperlink ref="K36" r:id="rId28" xr:uid="{4019B0FA-2C32-4BF7-AF0E-13643AFC8680}"/>
-    <hyperlink ref="K52" r:id="rId29" xr:uid="{A9377D63-6925-44E0-9C10-08AA1C1392A0}"/>
-    <hyperlink ref="K5" r:id="rId30" xr:uid="{4DE7FF7F-49C2-494C-9ADB-BFB49C469051}"/>
-    <hyperlink ref="K12" r:id="rId31" xr:uid="{90CB7667-927C-4A55-A4D2-5ECF1714DD75}"/>
-    <hyperlink ref="K15" r:id="rId32" xr:uid="{D736220D-F75D-48ED-8215-388BFD7FD301}"/>
-    <hyperlink ref="K17" r:id="rId33" xr:uid="{817B083C-1611-4901-8A1D-B030947152E8}"/>
-    <hyperlink ref="K18" r:id="rId34" xr:uid="{752CA09E-105C-4C44-8813-DDB06D0C764D}"/>
-    <hyperlink ref="K20" r:id="rId35" xr:uid="{A7F2B0B7-6CD2-46B0-BB3A-E30D6262FA40}"/>
-    <hyperlink ref="K21" r:id="rId36" xr:uid="{9B61C4AA-A004-4FEE-9055-CCAA2E34D986}"/>
-    <hyperlink ref="K25" r:id="rId37" xr:uid="{50B74B28-16D3-4C9C-B649-AC16BE018A83}"/>
-    <hyperlink ref="K26" r:id="rId38" xr:uid="{A3065F38-759F-4602-8D3C-7233C32A3032}"/>
-    <hyperlink ref="K27" r:id="rId39" xr:uid="{C3F36426-076E-4E31-9F0B-0EA3A6B1DD75}"/>
-    <hyperlink ref="K28" r:id="rId40" xr:uid="{E62BDC17-BE73-4321-AC87-B2F1AC44C52D}"/>
-    <hyperlink ref="K34" r:id="rId41" xr:uid="{26ECB104-FD6B-4BA7-BC13-956EEDFA68E3}"/>
-    <hyperlink ref="K35" r:id="rId42" xr:uid="{F9DADC4C-0A70-47E0-AB40-D008FA823714}"/>
-    <hyperlink ref="K42" r:id="rId43" xr:uid="{778E5024-226B-4920-B0C2-E54E318B7AA7}"/>
-    <hyperlink ref="K6" r:id="rId44" xr:uid="{7327C3B3-FC73-4FD4-8E3A-EAE29080795C}"/>
-    <hyperlink ref="K7" r:id="rId45" xr:uid="{9835C5DD-A107-49DA-A102-1D32512F3959}"/>
-    <hyperlink ref="K11" r:id="rId46" xr:uid="{F46283B7-7116-414C-8181-21C8009155F7}"/>
-    <hyperlink ref="K70" r:id="rId47" xr:uid="{CF0A0F84-6B70-448A-A7E4-353F76C06344}"/>
-    <hyperlink ref="K38" r:id="rId48" xr:uid="{F255A40E-E7F9-46E9-80A6-89E7F5CECB64}"/>
-    <hyperlink ref="K39" r:id="rId49" xr:uid="{F33CFE79-8711-4EBC-9CB7-252D909356D4}"/>
-    <hyperlink ref="K40" r:id="rId50" xr:uid="{B46830F1-4C98-4965-8EC5-D6EBD7A32C28}"/>
-    <hyperlink ref="K59" r:id="rId51" xr:uid="{9D43AF14-0E24-4C14-AD35-9A3EEC0FCFA3}"/>
-    <hyperlink ref="K51" r:id="rId52" xr:uid="{C4723849-58CB-441D-8956-C096D16EB2A8}"/>
-    <hyperlink ref="K10" r:id="rId53" xr:uid="{D399DD4D-94FB-4195-932E-DB5272684B27}"/>
-    <hyperlink ref="K14" r:id="rId54" xr:uid="{A9480283-62BB-4C10-B422-024E9E2E5277}"/>
+    <hyperlink ref="K24" r:id="rId13" xr:uid="{C415D613-1570-441D-A891-ED3A35DEB1A5}"/>
+    <hyperlink ref="K36" r:id="rId14" xr:uid="{5DA780DA-5AE3-4673-B2D5-44E74D6CADF4}"/>
+    <hyperlink ref="K23" r:id="rId15" xr:uid="{D1B93B60-C4A2-4C1E-A23F-AA7F2DF69C12}"/>
+    <hyperlink ref="K55" r:id="rId16" xr:uid="{605D06FB-BDCA-4D83-A43A-BE83330B88FB}"/>
+    <hyperlink ref="K20" r:id="rId17" xr:uid="{B648B368-E192-405E-AF40-90D54C14ED98}"/>
+    <hyperlink ref="K56" r:id="rId18" xr:uid="{808CD1D5-334F-4AE6-8D51-87CD2C3A649E}"/>
+    <hyperlink ref="K53" r:id="rId19" xr:uid="{E8B48719-363A-49FC-B3C8-181E5CD398EA}"/>
+    <hyperlink ref="K48" r:id="rId20" xr:uid="{741920D7-852F-438F-9B8A-B9ABD3DE381E}"/>
+    <hyperlink ref="K72" r:id="rId21" display="mailto:optima2@livingproperties.com" xr:uid="{FC418030-4EE8-4439-92C7-DD13F00F4D6A}"/>
+    <hyperlink ref="K64" r:id="rId22" xr:uid="{51FF6984-1DC6-430F-8E60-254E7A49BE1B}"/>
+    <hyperlink ref="K71" r:id="rId23" xr:uid="{9681E0BE-E957-4347-8DBD-4A244171852E}"/>
+    <hyperlink ref="K65" r:id="rId24" xr:uid="{30A38D56-4D68-485C-9630-D527FE1A7375}"/>
+    <hyperlink ref="K17" r:id="rId25" xr:uid="{B4D2F180-C9A6-4272-89D7-2F45E07DF9D9}"/>
+    <hyperlink ref="K35" r:id="rId26" xr:uid="{4019B0FA-2C32-4BF7-AF0E-13643AFC8680}"/>
+    <hyperlink ref="K50" r:id="rId27" xr:uid="{A9377D63-6925-44E0-9C10-08AA1C1392A0}"/>
+    <hyperlink ref="K5" r:id="rId28" xr:uid="{4DE7FF7F-49C2-494C-9ADB-BFB49C469051}"/>
+    <hyperlink ref="K12" r:id="rId29" xr:uid="{90CB7667-927C-4A55-A4D2-5ECF1714DD75}"/>
+    <hyperlink ref="K16" r:id="rId30" xr:uid="{D736220D-F75D-48ED-8215-388BFD7FD301}"/>
+    <hyperlink ref="K18" r:id="rId31" xr:uid="{817B083C-1611-4901-8A1D-B030947152E8}"/>
+    <hyperlink ref="K19" r:id="rId32" xr:uid="{752CA09E-105C-4C44-8813-DDB06D0C764D}"/>
+    <hyperlink ref="K21" r:id="rId33" xr:uid="{A7F2B0B7-6CD2-46B0-BB3A-E30D6262FA40}"/>
+    <hyperlink ref="K22" r:id="rId34" xr:uid="{9B61C4AA-A004-4FEE-9055-CCAA2E34D986}"/>
+    <hyperlink ref="K25" r:id="rId35" xr:uid="{50B74B28-16D3-4C9C-B649-AC16BE018A83}"/>
+    <hyperlink ref="K26" r:id="rId36" xr:uid="{A3065F38-759F-4602-8D3C-7233C32A3032}"/>
+    <hyperlink ref="K27" r:id="rId37" xr:uid="{C3F36426-076E-4E31-9F0B-0EA3A6B1DD75}"/>
+    <hyperlink ref="K28" r:id="rId38" xr:uid="{E62BDC17-BE73-4321-AC87-B2F1AC44C52D}"/>
+    <hyperlink ref="K33" r:id="rId39" xr:uid="{26ECB104-FD6B-4BA7-BC13-956EEDFA68E3}"/>
+    <hyperlink ref="K34" r:id="rId40" xr:uid="{F9DADC4C-0A70-47E0-AB40-D008FA823714}"/>
+    <hyperlink ref="K41" r:id="rId41" xr:uid="{778E5024-226B-4920-B0C2-E54E318B7AA7}"/>
+    <hyperlink ref="K6" r:id="rId42" xr:uid="{7327C3B3-FC73-4FD4-8E3A-EAE29080795C}"/>
+    <hyperlink ref="K7" r:id="rId43" xr:uid="{9835C5DD-A107-49DA-A102-1D32512F3959}"/>
+    <hyperlink ref="K11" r:id="rId44" xr:uid="{F46283B7-7116-414C-8181-21C8009155F7}"/>
+    <hyperlink ref="K68" r:id="rId45" xr:uid="{CF0A0F84-6B70-448A-A7E4-353F76C06344}"/>
+    <hyperlink ref="K37" r:id="rId46" xr:uid="{F255A40E-E7F9-46E9-80A6-89E7F5CECB64}"/>
+    <hyperlink ref="K38" r:id="rId47" xr:uid="{F33CFE79-8711-4EBC-9CB7-252D909356D4}"/>
+    <hyperlink ref="K39" r:id="rId48" xr:uid="{B46830F1-4C98-4965-8EC5-D6EBD7A32C28}"/>
+    <hyperlink ref="K57" r:id="rId49" xr:uid="{9D43AF14-0E24-4C14-AD35-9A3EEC0FCFA3}"/>
+    <hyperlink ref="K49" r:id="rId50" xr:uid="{C4723849-58CB-441D-8956-C096D16EB2A8}"/>
+    <hyperlink ref="K10" r:id="rId51" xr:uid="{D399DD4D-94FB-4195-932E-DB5272684B27}"/>
+    <hyperlink ref="K14" r:id="rId52" xr:uid="{A9480283-62BB-4C10-B422-024E9E2E5277}"/>
+    <hyperlink ref="K15" r:id="rId53" xr:uid="{E60717EF-9C6B-447A-B1BA-FB4D65924041}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId55"/>
+  <pageSetup orientation="portrait" r:id="rId54"/>
   <tableParts count="1">
-    <tablePart r:id="rId56"/>
+    <tablePart r:id="rId55"/>
   </tableParts>
 </worksheet>
 </file>
@@ -17719,47 +17613,47 @@
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -17768,21 +17662,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FCEEF5D6F9A2C14292C82E7F88E7D4C7" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="770a5493e01cc46570af888c0fd11107">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6e07a911-1c82-455b-ae09-b73935b22a66" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="de63ad8f9259e2f5a7ae7a5921e0e8ad" ns2:_="">
     <xsd:import namespace="6e07a911-1c82-455b-ae09-b73935b22a66"/>
@@ -17914,31 +17793,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDCD3F55-29C2-4E12-8D9A-9EC0083C9C49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="6e07a911-1c82-455b-ae09-b73935b22a66"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C569B7B-6177-4C5F-B641-1220485D9B3F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4188865-1BAB-459E-8F28-5F6AB5F6EAC9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17954,4 +17824,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C569B7B-6177-4C5F-B641-1220485D9B3F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDCD3F55-29C2-4E12-8D9A-9EC0083C9C49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="6e07a911-1c82-455b-ae09-b73935b22a66"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/companydirectorypdf/companydir.xlsx
+++ b/companydirectorypdf/companydir.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\kwlrportal\companydirectorypdf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D1132CD-A6D9-4ACB-AD99-E614CF9250CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C607374-DB22-4D41-9F53-3FC9E017085A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{AE6EE1E0-C559-4053-97E8-B14EEDB6E6F6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AE6EE1E0-C559-4053-97E8-B14EEDB6E6F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Letter Size" sheetId="8" r:id="rId1"/>
@@ -19,8 +19,8 @@
     <sheet name="Sorting" sheetId="3" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Legal Size'!$A$1:$F$80</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Letter Size'!$A$1:$I$79</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Legal Size'!$A$1:$F$78</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Letter Size'!$A$1:$I$77</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="322">
   <si>
     <t>Company Directory</t>
   </si>
@@ -979,9 +979,6 @@
     <t>dan@livingrealtykw.com</t>
   </si>
   <si>
-    <t>Update Date: Nov 3, 2025</t>
-  </si>
-  <si>
     <t>(905) 489-8989</t>
   </si>
   <si>
@@ -1004,6 +1001,12 @@
   </si>
   <si>
     <t>kimjin@livingrealtykw.com</t>
+  </si>
+  <si>
+    <t>Update Date: Mar 05, 2026</t>
+  </si>
+  <si>
+    <t>Update Date: Mar 5, 2026</t>
   </si>
 </sst>
 </file>
@@ -1980,7 +1983,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L364"/>
+  <dimension ref="A1:L362"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="8" customWidth="1"/>
@@ -2003,7 +2006,7 @@
       </c>
       <c r="H1" s="11"/>
       <c r="I1" s="11" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15" x14ac:dyDescent="0.25">
@@ -2490,28 +2493,28 @@
     </row>
     <row r="16" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
-        <f>IF(LEN(ContactData!H16)&lt;3,"",ContactData!H16)</f>
-        <v>123</v>
+        <f>IF(LEN(ContactData!H15)&lt;3,"",ContactData!H15)</f>
+        <v>282</v>
       </c>
       <c r="B16" s="3" t="str">
-        <f>ContactData!E16</f>
-        <v>Wendy Chung</v>
+        <f>ContactData!E15</f>
+        <v>Joanna Xie</v>
       </c>
       <c r="C16" s="3" t="str">
-        <f>ContactData!G16</f>
-        <v xml:space="preserve">Administration Officer </v>
+        <f>ContactData!G15</f>
+        <v>Agent Services Coordinator</v>
       </c>
       <c r="D16" s="9" t="str">
-        <f>IF(LEN(ContactData!I16)&lt;3,"",ContactData!I16)</f>
+        <f>IF(LEN(ContactData!I15)&lt;3,"",ContactData!I15)</f>
         <v>---</v>
       </c>
       <c r="E16" s="3" t="str">
-        <f>ContactData!J16</f>
+        <f>ContactData!J15</f>
         <v>---</v>
       </c>
       <c r="F16" s="3" t="str">
-        <f>IF(LEN(ContactData!K16)&lt;3,"",ContactData!K16)</f>
-        <v>wendychung@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K15)&lt;3,"",ContactData!K15)</f>
+        <v>joannaxie@livingrealtykw.com</v>
       </c>
       <c r="G16"/>
       <c r="H16"/>
@@ -2522,28 +2525,28 @@
     </row>
     <row r="17" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
-        <f>IF(LEN(ContactData!H17)&lt;3,"",ContactData!H17)</f>
-        <v>206</v>
+        <f>IF(LEN(ContactData!H16)&lt;3,"",ContactData!H16)</f>
+        <v>123</v>
       </c>
       <c r="B17" s="3" t="str">
-        <f>ContactData!E17</f>
-        <v>Benjamin Wong</v>
+        <f>ContactData!E16</f>
+        <v>Wendy Chung</v>
       </c>
       <c r="C17" s="3" t="str">
-        <f>ContactData!G17</f>
-        <v>Assistant to the Broker of Record</v>
+        <f>ContactData!G16</f>
+        <v xml:space="preserve">Administration Officer </v>
       </c>
       <c r="D17" s="9" t="str">
-        <f>IF(LEN(ContactData!I17)&lt;3,"",ContactData!I17)</f>
+        <f>IF(LEN(ContactData!I16)&lt;3,"",ContactData!I16)</f>
         <v>---</v>
       </c>
       <c r="E17" s="3" t="str">
-        <f>ContactData!J17</f>
+        <f>ContactData!J16</f>
         <v>---</v>
       </c>
       <c r="F17" s="3" t="str">
-        <f>IF(LEN(ContactData!K17)&lt;3,"",ContactData!K17)</f>
-        <v>benjaminwongici@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K16)&lt;3,"",ContactData!K16)</f>
+        <v>wendychung@livingrealtykw.com</v>
       </c>
       <c r="G17"/>
       <c r="H17"/>
@@ -2554,28 +2557,28 @@
     </row>
     <row r="18" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
-        <f>IF(LEN(ContactData!H18)&lt;3,"",ContactData!H18)</f>
-        <v>507</v>
+        <f>IF(LEN(ContactData!H17)&lt;3,"",ContactData!H17)</f>
+        <v>206</v>
       </c>
       <c r="B18" s="3" t="str">
-        <f>ContactData!E18</f>
-        <v>Luvie Chao</v>
+        <f>ContactData!E17</f>
+        <v>Benjamin Wong</v>
       </c>
       <c r="C18" s="3" t="str">
-        <f>ContactData!G18</f>
-        <v>Senior Deal Administrator</v>
+        <f>ContactData!G17</f>
+        <v>Assistant to the Broker of Record</v>
       </c>
       <c r="D18" s="9" t="str">
-        <f>IF(LEN(ContactData!I18)&lt;3,"",ContactData!I18)</f>
+        <f>IF(LEN(ContactData!I17)&lt;3,"",ContactData!I17)</f>
         <v>---</v>
       </c>
       <c r="E18" s="3" t="str">
-        <f>ContactData!J18</f>
-        <v>(905) 752-3507</v>
+        <f>ContactData!J17</f>
+        <v>---</v>
       </c>
       <c r="F18" s="3" t="str">
-        <f>IF(LEN(ContactData!K18)&lt;3,"",ContactData!K18)</f>
-        <v>luvie@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K17)&lt;3,"",ContactData!K17)</f>
+        <v>benjaminwongici@livingrealtykw.com</v>
       </c>
       <c r="G18"/>
       <c r="H18"/>
@@ -2586,28 +2589,28 @@
     </row>
     <row r="19" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
-        <f>IF(LEN(ContactData!H19)&lt;3,"",ContactData!H19)</f>
-        <v>508</v>
+        <f>IF(LEN(ContactData!H18)&lt;3,"",ContactData!H18)</f>
+        <v>507</v>
       </c>
       <c r="B19" s="3" t="str">
-        <f>ContactData!E19</f>
-        <v>Maria Leung</v>
+        <f>ContactData!E18</f>
+        <v>Luvie Chao</v>
       </c>
       <c r="C19" s="3" t="str">
-        <f>ContactData!G19</f>
-        <v>Deal Administrator</v>
+        <f>ContactData!G18</f>
+        <v>Senior Deal Administrator</v>
       </c>
       <c r="D19" s="9" t="str">
-        <f>IF(LEN(ContactData!I19)&lt;3,"",ContactData!I19)</f>
+        <f>IF(LEN(ContactData!I18)&lt;3,"",ContactData!I18)</f>
         <v>---</v>
       </c>
       <c r="E19" s="3" t="str">
-        <f>ContactData!J19</f>
-        <v>(905) 752-3508</v>
+        <f>ContactData!J18</f>
+        <v>(905) 752-3507</v>
       </c>
       <c r="F19" s="3" t="str">
-        <f>IF(LEN(ContactData!K19)&lt;3,"",ContactData!K19)</f>
-        <v>marialeung@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K18)&lt;3,"",ContactData!K18)</f>
+        <v>luvie@livingrealtykw.com</v>
       </c>
       <c r="G19"/>
       <c r="H19"/>
@@ -2618,28 +2621,28 @@
     </row>
     <row r="20" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
-        <f>IF(LEN(ContactData!H20)&lt;3,"",ContactData!H20)</f>
-        <v>255</v>
+        <f>IF(LEN(ContactData!H19)&lt;3,"",ContactData!H19)</f>
+        <v>508</v>
       </c>
       <c r="B20" s="3" t="str">
-        <f>ContactData!E20</f>
-        <v>Ken Cheung</v>
+        <f>ContactData!E19</f>
+        <v>Maria Leung</v>
       </c>
       <c r="C20" s="3" t="str">
-        <f>ContactData!G20</f>
+        <f>ContactData!G19</f>
         <v>Deal Administrator</v>
       </c>
       <c r="D20" s="9" t="str">
-        <f>IF(LEN(ContactData!I20)&lt;3,"",ContactData!I20)</f>
+        <f>IF(LEN(ContactData!I19)&lt;3,"",ContactData!I19)</f>
         <v>---</v>
       </c>
       <c r="E20" s="3" t="str">
-        <f>ContactData!J20</f>
-        <v>---</v>
+        <f>ContactData!J19</f>
+        <v>(905) 752-3508</v>
       </c>
       <c r="F20" s="3" t="str">
-        <f>IF(LEN(ContactData!K20)&lt;3,"",ContactData!K20)</f>
-        <v>kencheung@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K19)&lt;3,"",ContactData!K19)</f>
+        <v>marialeung@livingrealtykw.com</v>
       </c>
       <c r="G20"/>
       <c r="H20"/>
@@ -2650,28 +2653,28 @@
     </row>
     <row r="21" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
-        <f>IF(LEN(ContactData!H21)&lt;3,"",ContactData!H21)</f>
-        <v>506</v>
+        <f>IF(LEN(ContactData!H20)&lt;3,"",ContactData!H20)</f>
+        <v>255</v>
       </c>
       <c r="B21" s="3" t="str">
-        <f>ContactData!E21</f>
-        <v>Connie Cheung</v>
+        <f>ContactData!E20</f>
+        <v>Ken Cheung</v>
       </c>
       <c r="C21" s="3" t="str">
-        <f>ContactData!G21</f>
-        <v>Accounting Bookkeeper</v>
+        <f>ContactData!G20</f>
+        <v>Deal Administrator</v>
       </c>
       <c r="D21" s="9" t="str">
-        <f>IF(LEN(ContactData!I21)&lt;3,"",ContactData!I21)</f>
+        <f>IF(LEN(ContactData!I20)&lt;3,"",ContactData!I20)</f>
         <v>---</v>
       </c>
       <c r="E21" s="3" t="str">
-        <f>ContactData!J21</f>
-        <v>(905) 752-3506</v>
+        <f>ContactData!J20</f>
+        <v>---</v>
       </c>
       <c r="F21" s="3" t="str">
-        <f>IF(LEN(ContactData!K21)&lt;3,"",ContactData!K21)</f>
-        <v>conniecheung@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K20)&lt;3,"",ContactData!K20)</f>
+        <v>kencheung@livingrealtykw.com</v>
       </c>
       <c r="G21"/>
       <c r="H21"/>
@@ -2682,28 +2685,28 @@
     </row>
     <row r="22" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
-        <f>IF(LEN(ContactData!H22)&lt;3,"",ContactData!H22)</f>
-        <v>519</v>
+        <f>IF(LEN(ContactData!H21)&lt;3,"",ContactData!H21)</f>
+        <v>506</v>
       </c>
       <c r="B22" s="3" t="str">
-        <f>ContactData!E22</f>
-        <v>Simon Chan</v>
+        <f>ContactData!E21</f>
+        <v>Connie Cheung</v>
       </c>
       <c r="C22" s="3" t="str">
-        <f>ContactData!G22</f>
-        <v>Operations Assistant</v>
+        <f>ContactData!G21</f>
+        <v>Accounting Bookkeeper</v>
       </c>
       <c r="D22" s="9" t="str">
-        <f>IF(LEN(ContactData!I22)&lt;3,"",ContactData!I22)</f>
+        <f>IF(LEN(ContactData!I21)&lt;3,"",ContactData!I21)</f>
         <v>---</v>
       </c>
       <c r="E22" s="3" t="str">
-        <f>ContactData!J22</f>
-        <v>(905) 752-3519</v>
+        <f>ContactData!J21</f>
+        <v>(905) 752-3506</v>
       </c>
       <c r="F22" s="3" t="str">
-        <f>IF(LEN(ContactData!K22)&lt;3,"",ContactData!K22)</f>
-        <v>simonchan@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K21)&lt;3,"",ContactData!K21)</f>
+        <v>conniecheung@livingrealtykw.com</v>
       </c>
       <c r="G22"/>
       <c r="H22"/>
@@ -2713,29 +2716,29 @@
       <c r="L22"/>
     </row>
     <row r="23" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="e">
-        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B23" s="3" t="e">
-        <f>ContactData!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C23" s="3" t="e">
-        <f>ContactData!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D23" s="9" t="e">
-        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E23" s="3" t="e">
-        <f>ContactData!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F23" s="3" t="e">
-        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
-        <v>#REF!</v>
+      <c r="A23" s="9">
+        <f>IF(LEN(ContactData!H22)&lt;3,"",ContactData!H22)</f>
+        <v>519</v>
+      </c>
+      <c r="B23" s="3" t="str">
+        <f>ContactData!E22</f>
+        <v>Simon Chan</v>
+      </c>
+      <c r="C23" s="3" t="str">
+        <f>ContactData!G22</f>
+        <v>Operations Assistant</v>
+      </c>
+      <c r="D23" s="9" t="str">
+        <f>IF(LEN(ContactData!I22)&lt;3,"",ContactData!I22)</f>
+        <v>---</v>
+      </c>
+      <c r="E23" s="3" t="str">
+        <f>ContactData!J22</f>
+        <v>(905) 752-3519</v>
+      </c>
+      <c r="F23" s="3" t="str">
+        <f>IF(LEN(ContactData!K22)&lt;3,"",ContactData!K22)</f>
+        <v>simonchan@livingrealtykw.com</v>
       </c>
       <c r="G23"/>
       <c r="H23"/>
@@ -3033,29 +3036,29 @@
       <c r="L32"/>
     </row>
     <row r="33" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A33" s="9" t="e">
-        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B33" s="3" t="e">
-        <f>ContactData!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C33" s="3" t="e">
-        <f>ContactData!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D33" s="9" t="e">
-        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E33" s="3" t="e">
-        <f>ContactData!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F33" s="3" t="e">
-        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
-        <v>#REF!</v>
+      <c r="A33" s="9" t="str">
+        <f>IF(LEN(ContactData!H32)&lt;3,"",ContactData!H32)</f>
+        <v>---</v>
+      </c>
+      <c r="B33" s="3" t="str">
+        <f>ContactData!E32</f>
+        <v>Katie Wong</v>
+      </c>
+      <c r="C33" s="3" t="str">
+        <f>ContactData!G32</f>
+        <v>Secretary</v>
+      </c>
+      <c r="D33" s="9" t="str">
+        <f>IF(LEN(ContactData!I32)&lt;3,"",ContactData!I32)</f>
+        <v>---</v>
+      </c>
+      <c r="E33" s="3" t="str">
+        <f>ContactData!J32</f>
+        <v>(905) 896-0002</v>
+      </c>
+      <c r="F33" s="3" t="str">
+        <f>IF(LEN(ContactData!K32)&lt;3,"",ContactData!K32)</f>
+        <v>katiewong@livingrealtykw.com</v>
       </c>
       <c r="G33"/>
       <c r="H33"/>
@@ -3066,28 +3069,28 @@
     </row>
     <row r="34" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="str">
-        <f>IF(LEN(ContactData!H32)&lt;3,"",ContactData!H32)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!H33)&lt;3,"",ContactData!H33)</f>
+        <v/>
       </c>
       <c r="B34" s="3" t="str">
-        <f>ContactData!E32</f>
-        <v>Katie Wong</v>
+        <f>ContactData!E33</f>
+        <v>Woodbine Office</v>
       </c>
       <c r="C34" s="3" t="str">
-        <f>ContactData!G32</f>
-        <v>Secretary</v>
+        <f>ContactData!G33</f>
+        <v>8 Steelcase Road West, Markham, ON, L3R 1B2</v>
       </c>
       <c r="D34" s="9" t="str">
-        <f>IF(LEN(ContactData!I32)&lt;3,"",ContactData!I32)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!I33)&lt;3,"",ContactData!I33)</f>
+        <v/>
       </c>
       <c r="E34" s="3" t="str">
-        <f>ContactData!J32</f>
-        <v>(905) 896-0002</v>
+        <f>ContactData!J33</f>
+        <v>T: (905) 474-0500</v>
       </c>
       <c r="F34" s="3" t="str">
-        <f>IF(LEN(ContactData!K32)&lt;3,"",ContactData!K32)</f>
-        <v>katiewong@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K33)&lt;3,"",ContactData!K33)</f>
+        <v>woodbine@livingrealtykw.com</v>
       </c>
       <c r="G34"/>
       <c r="H34"/>
@@ -3097,29 +3100,29 @@
       <c r="L34"/>
     </row>
     <row r="35" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A35" s="9" t="str">
-        <f>IF(LEN(ContactData!H33)&lt;3,"",ContactData!H33)</f>
-        <v/>
+      <c r="A35" s="9">
+        <f>IF(LEN(ContactData!H34)&lt;3,"",ContactData!H34)</f>
+        <v>176</v>
       </c>
       <c r="B35" s="3" t="str">
-        <f>ContactData!E33</f>
-        <v>Woodbine Office</v>
+        <f>ContactData!E34</f>
+        <v>Anita Huang</v>
       </c>
       <c r="C35" s="3" t="str">
-        <f>ContactData!G33</f>
-        <v>8 Steelcase Road West, Markham, ON, L3R 1B2</v>
+        <f>ContactData!G34</f>
+        <v>Manager Woobine Branch</v>
       </c>
       <c r="D35" s="9" t="str">
-        <f>IF(LEN(ContactData!I33)&lt;3,"",ContactData!I33)</f>
-        <v/>
+        <f>IF(LEN(ContactData!I34)&lt;3,"",ContactData!I34)</f>
+        <v>(416) 523-1888</v>
       </c>
       <c r="E35" s="3" t="str">
-        <f>ContactData!J33</f>
-        <v>T: (905) 474-0500</v>
+        <f>ContactData!J34</f>
+        <v>---</v>
       </c>
       <c r="F35" s="3" t="str">
-        <f>IF(LEN(ContactData!K33)&lt;3,"",ContactData!K33)</f>
-        <v>woodbine@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K34)&lt;3,"",ContactData!K34)</f>
+        <v>anitahuang@livingrealtykw.com</v>
       </c>
       <c r="G35"/>
       <c r="H35"/>
@@ -3130,28 +3133,28 @@
     </row>
     <row r="36" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
-        <f>IF(LEN(ContactData!H34)&lt;3,"",ContactData!H34)</f>
-        <v>176</v>
+        <f>IF(LEN(ContactData!H35)&lt;3,"",ContactData!H35)</f>
+        <v>104</v>
       </c>
       <c r="B36" s="3" t="str">
-        <f>ContactData!E34</f>
-        <v>Anita Huang</v>
+        <f>ContactData!E35</f>
+        <v>Kim Jin</v>
       </c>
       <c r="C36" s="3" t="str">
-        <f>ContactData!G34</f>
-        <v>Manager Woobine Branch</v>
+        <f>ContactData!G35</f>
+        <v>Secretary</v>
       </c>
       <c r="D36" s="9" t="str">
-        <f>IF(LEN(ContactData!I34)&lt;3,"",ContactData!I34)</f>
-        <v>(416) 523-1888</v>
+        <f>IF(LEN(ContactData!I35)&lt;3,"",ContactData!I35)</f>
+        <v>---</v>
       </c>
       <c r="E36" s="3" t="str">
-        <f>ContactData!J34</f>
-        <v>---</v>
+        <f>ContactData!J35</f>
+        <v>(905) 474-0500</v>
       </c>
       <c r="F36" s="3" t="str">
-        <f>IF(LEN(ContactData!K34)&lt;3,"",ContactData!K34)</f>
-        <v>anitahuang@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K35)&lt;3,"",ContactData!K35)</f>
+        <v>kimjin@livingrealtykw.com</v>
       </c>
       <c r="G36"/>
       <c r="H36"/>
@@ -3162,28 +3165,28 @@
     </row>
     <row r="37" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
-        <f>IF(LEN(ContactData!H35)&lt;3,"",ContactData!H35)</f>
-        <v>104</v>
+        <f>IF(LEN(ContactData!H36)&lt;3,"",ContactData!H36)</f>
+        <v>100</v>
       </c>
       <c r="B37" s="3" t="str">
-        <f>ContactData!E35</f>
-        <v>Kim Jin</v>
+        <f>ContactData!E36</f>
+        <v>Savanna Joo</v>
       </c>
       <c r="C37" s="3" t="str">
-        <f>ContactData!G35</f>
+        <f>ContactData!G36</f>
         <v>Secretary</v>
       </c>
       <c r="D37" s="9" t="str">
-        <f>IF(LEN(ContactData!I35)&lt;3,"",ContactData!I35)</f>
+        <f>IF(LEN(ContactData!I36)&lt;3,"",ContactData!I36)</f>
         <v>---</v>
       </c>
       <c r="E37" s="3" t="str">
-        <f>ContactData!J35</f>
+        <f>ContactData!J36</f>
         <v>(905) 474-0500</v>
       </c>
       <c r="F37" s="3" t="str">
-        <f>IF(LEN(ContactData!K35)&lt;3,"",ContactData!K35)</f>
-        <v>kimjin@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K36)&lt;3,"",ContactData!K36)</f>
+        <v>savannajoo@livingrealtykw.com</v>
       </c>
       <c r="G37"/>
       <c r="H37"/>
@@ -3193,29 +3196,29 @@
       <c r="L37"/>
     </row>
     <row r="38" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A38" s="9">
-        <f>IF(LEN(ContactData!H36)&lt;3,"",ContactData!H36)</f>
-        <v>100</v>
+      <c r="A38" s="9" t="str">
+        <f>IF(LEN(ContactData!H37)&lt;3,"",ContactData!H37)</f>
+        <v/>
       </c>
       <c r="B38" s="3" t="str">
-        <f>ContactData!E36</f>
-        <v>Savanna Joo</v>
+        <f>ContactData!E37</f>
+        <v>Yonge &amp; Eglinton Office</v>
       </c>
       <c r="C38" s="3" t="str">
-        <f>ContactData!G36</f>
-        <v>Secretary</v>
+        <f>ContactData!G37</f>
+        <v>2301 Yonge Street, Toronto, ON, M4P 2C6</v>
       </c>
       <c r="D38" s="9" t="str">
-        <f>IF(LEN(ContactData!I36)&lt;3,"",ContactData!I36)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!I37)&lt;3,"",ContactData!I37)</f>
+        <v/>
       </c>
       <c r="E38" s="3" t="str">
-        <f>ContactData!J36</f>
-        <v>(905) 474-0500</v>
+        <f>ContactData!J37</f>
+        <v>T: (416) 223-8833</v>
       </c>
       <c r="F38" s="3" t="str">
-        <f>IF(LEN(ContactData!K36)&lt;3,"",ContactData!K36)</f>
-        <v>savannajoo@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K37)&lt;3,"",ContactData!K37)</f>
+        <v>ye@livingrealtykw.com</v>
       </c>
       <c r="G38"/>
       <c r="H38"/>
@@ -3226,28 +3229,28 @@
     </row>
     <row r="39" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="str">
-        <f>IF(LEN(ContactData!H37)&lt;3,"",ContactData!H37)</f>
-        <v/>
+        <f>IF(LEN(ContactData!H38)&lt;3,"",ContactData!H38)</f>
+        <v>---</v>
       </c>
       <c r="B39" s="3" t="str">
-        <f>ContactData!E37</f>
-        <v>Yonge &amp; Eglinton Office</v>
+        <f>ContactData!E38</f>
+        <v xml:space="preserve">Tony Prochilo </v>
       </c>
       <c r="C39" s="3" t="str">
-        <f>ContactData!G37</f>
-        <v>2301 Yonge Street, Toronto, ON, M4P 2C6</v>
+        <f>ContactData!G38</f>
+        <v>Manager Yonge &amp; Eglinton</v>
       </c>
       <c r="D39" s="9" t="str">
-        <f>IF(LEN(ContactData!I37)&lt;3,"",ContactData!I37)</f>
-        <v/>
+        <f>IF(LEN(ContactData!I38)&lt;3,"",ContactData!I38)</f>
+        <v>(416) 576-6312</v>
       </c>
       <c r="E39" s="3" t="str">
-        <f>ContactData!J37</f>
-        <v>T: (416) 223-8833</v>
+        <f>ContactData!J38</f>
+        <v>---</v>
       </c>
       <c r="F39" s="3" t="str">
-        <f>IF(LEN(ContactData!K37)&lt;3,"",ContactData!K37)</f>
-        <v>ye@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K38)&lt;3,"",ContactData!K38)</f>
+        <v>tonyprochilo@livingrealtykw.com</v>
       </c>
       <c r="G39"/>
       <c r="H39"/>
@@ -3258,28 +3261,28 @@
     </row>
     <row r="40" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="str">
-        <f>IF(LEN(ContactData!H38)&lt;3,"",ContactData!H38)</f>
+        <f>IF(LEN(ContactData!H39)&lt;3,"",ContactData!H39)</f>
         <v>---</v>
       </c>
       <c r="B40" s="3" t="str">
-        <f>ContactData!E38</f>
-        <v xml:space="preserve">Tony Prochilo </v>
+        <f>ContactData!E39</f>
+        <v>Lydia Ng</v>
       </c>
       <c r="C40" s="3" t="str">
-        <f>ContactData!G38</f>
-        <v>Manager Yonge &amp; Eglinton</v>
+        <f>ContactData!G39</f>
+        <v>Secretary</v>
       </c>
       <c r="D40" s="9" t="str">
-        <f>IF(LEN(ContactData!I38)&lt;3,"",ContactData!I38)</f>
-        <v>(416) 576-6312</v>
+        <f>IF(LEN(ContactData!I39)&lt;3,"",ContactData!I39)</f>
+        <v>---</v>
       </c>
       <c r="E40" s="3" t="str">
-        <f>ContactData!J38</f>
-        <v>---</v>
+        <f>ContactData!J39</f>
+        <v>(416) 223-8833</v>
       </c>
       <c r="F40" s="3" t="str">
-        <f>IF(LEN(ContactData!K38)&lt;3,"",ContactData!K38)</f>
-        <v>tonyprochilo@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K39)&lt;3,"",ContactData!K39)</f>
+        <v>lydiang@livingrealtykw.com</v>
       </c>
       <c r="G40"/>
       <c r="H40"/>
@@ -3290,28 +3293,28 @@
     </row>
     <row r="41" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="str">
-        <f>IF(LEN(ContactData!H39)&lt;3,"",ContactData!H39)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!H40)&lt;3,"",ContactData!H40)</f>
+        <v/>
       </c>
       <c r="B41" s="3" t="str">
-        <f>ContactData!E39</f>
-        <v>Lydia Ng</v>
+        <f>ContactData!E40</f>
+        <v>I.C.&amp;I. Office</v>
       </c>
       <c r="C41" s="3" t="str">
-        <f>ContactData!G39</f>
-        <v>Secretary</v>
+        <f>ContactData!G40</f>
+        <v>8 Steelcase Road West, Unit C, Markham, ON, L3R 1B2</v>
       </c>
       <c r="D41" s="9" t="str">
-        <f>IF(LEN(ContactData!I39)&lt;3,"",ContactData!I39)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!I40)&lt;3,"",ContactData!I40)</f>
+        <v/>
       </c>
       <c r="E41" s="3" t="str">
-        <f>ContactData!J39</f>
-        <v>(416) 223-8833</v>
+        <f>ContactData!J40</f>
+        <v>T: (905) 474-1772</v>
       </c>
       <c r="F41" s="3" t="str">
-        <f>IF(LEN(ContactData!K39)&lt;3,"",ContactData!K39)</f>
-        <v>lydiang@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K40)&lt;3,"",ContactData!K40)</f>
+        <v/>
       </c>
       <c r="G41"/>
       <c r="H41"/>
@@ -3321,29 +3324,29 @@
       <c r="L41"/>
     </row>
     <row r="42" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A42" s="9" t="str">
-        <f>IF(LEN(ContactData!H40)&lt;3,"",ContactData!H40)</f>
-        <v/>
+      <c r="A42" s="9">
+        <f>IF(LEN(ContactData!H41)&lt;3,"",ContactData!H41)</f>
+        <v>228</v>
       </c>
       <c r="B42" s="3" t="str">
-        <f>ContactData!E40</f>
-        <v>I.C.&amp;I. Office</v>
+        <f>ContactData!E41</f>
+        <v>Kelvin Wong</v>
       </c>
       <c r="C42" s="3" t="str">
-        <f>ContactData!G40</f>
-        <v>8 Steelcase Road West, Unit C, Markham, ON, L3R 1B2</v>
+        <f>ContactData!G41</f>
+        <v>Manager I.C.&amp;I. Branch</v>
       </c>
       <c r="D42" s="9" t="str">
-        <f>IF(LEN(ContactData!I40)&lt;3,"",ContactData!I40)</f>
-        <v/>
+        <f>IF(LEN(ContactData!I41)&lt;3,"",ContactData!I41)</f>
+        <v>(416) 567-7882</v>
       </c>
       <c r="E42" s="3" t="str">
-        <f>ContactData!J40</f>
-        <v>T: (905) 474-1772</v>
+        <f>ContactData!J41</f>
+        <v>---</v>
       </c>
       <c r="F42" s="3" t="str">
-        <f>IF(LEN(ContactData!K40)&lt;3,"",ContactData!K40)</f>
-        <v/>
+        <f>IF(LEN(ContactData!K41)&lt;3,"",ContactData!K41)</f>
+        <v>kelvin@livingrealtykw.com</v>
       </c>
       <c r="G42"/>
       <c r="H42"/>
@@ -3353,29 +3356,29 @@
       <c r="L42"/>
     </row>
     <row r="43" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A43" s="9">
-        <f>IF(LEN(ContactData!H41)&lt;3,"",ContactData!H41)</f>
-        <v>228</v>
+      <c r="A43" s="9" t="str">
+        <f>IF(LEN(ContactData!H42)&lt;3,"",ContactData!H42)</f>
+        <v/>
       </c>
       <c r="B43" s="3" t="str">
-        <f>ContactData!E41</f>
-        <v>Kelvin Wong</v>
+        <f>ContactData!E42</f>
+        <v>LPI Head Office</v>
       </c>
       <c r="C43" s="3" t="str">
-        <f>ContactData!G41</f>
-        <v>Manager I.C.&amp;I. Branch</v>
+        <f>ContactData!G42</f>
+        <v>8 Steelcase Road West, Markham, ON, L3R 1B2</v>
       </c>
       <c r="D43" s="9" t="str">
-        <f>IF(LEN(ContactData!I41)&lt;3,"",ContactData!I41)</f>
-        <v>(416) 567-7882</v>
+        <f>IF(LEN(ContactData!I42)&lt;3,"",ContactData!I42)</f>
+        <v/>
       </c>
       <c r="E43" s="3" t="str">
-        <f>ContactData!J41</f>
-        <v>---</v>
+        <f>ContactData!J42</f>
+        <v>T: (905) 477-2090</v>
       </c>
       <c r="F43" s="3" t="str">
-        <f>IF(LEN(ContactData!K41)&lt;3,"",ContactData!K41)</f>
-        <v>kelvin@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K42)&lt;3,"",ContactData!K42)</f>
+        <v/>
       </c>
       <c r="G43"/>
       <c r="H43"/>
@@ -3385,29 +3388,29 @@
       <c r="L43"/>
     </row>
     <row r="44" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A44" s="9" t="str">
-        <f>IF(LEN(ContactData!H42)&lt;3,"",ContactData!H42)</f>
-        <v/>
+      <c r="A44" s="9">
+        <f>IF(LEN(ContactData!H43)&lt;3,"",ContactData!H43)</f>
+        <v>521</v>
       </c>
       <c r="B44" s="3" t="str">
-        <f>ContactData!E42</f>
-        <v>LPI Head Office</v>
+        <f>ContactData!E43</f>
+        <v>Ben Wong</v>
       </c>
       <c r="C44" s="3" t="str">
-        <f>ContactData!G42</f>
-        <v>8 Steelcase Road West, Markham, ON, L3R 1B2</v>
+        <f>ContactData!G43</f>
+        <v>President</v>
       </c>
       <c r="D44" s="9" t="str">
-        <f>IF(LEN(ContactData!I42)&lt;3,"",ContactData!I42)</f>
-        <v/>
+        <f>IF(LEN(ContactData!I43)&lt;3,"",ContactData!I43)</f>
+        <v>(416) 399-2311</v>
       </c>
       <c r="E44" s="3" t="str">
-        <f>ContactData!J42</f>
-        <v>T: (905) 477-2090</v>
+        <f>ContactData!J43</f>
+        <v>(905) 752-3521</v>
       </c>
       <c r="F44" s="3" t="str">
-        <f>IF(LEN(ContactData!K42)&lt;3,"",ContactData!K42)</f>
-        <v/>
+        <f>IF(LEN(ContactData!K43)&lt;3,"",ContactData!K43)</f>
+        <v>benw@livingproperties.com</v>
       </c>
       <c r="G44"/>
       <c r="H44"/>
@@ -3418,28 +3421,28 @@
     </row>
     <row r="45" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A45" s="9">
-        <f>IF(LEN(ContactData!H43)&lt;3,"",ContactData!H43)</f>
-        <v>521</v>
+        <f>IF(LEN(ContactData!H44)&lt;3,"",ContactData!H44)</f>
+        <v>514</v>
       </c>
       <c r="B45" s="3" t="str">
-        <f>ContactData!E43</f>
-        <v>Ben Wong</v>
+        <f>ContactData!E44</f>
+        <v>Winnie Tsui</v>
       </c>
       <c r="C45" s="3" t="str">
-        <f>ContactData!G43</f>
-        <v>President</v>
+        <f>ContactData!G44</f>
+        <v>Director of Operations</v>
       </c>
       <c r="D45" s="9" t="str">
-        <f>IF(LEN(ContactData!I43)&lt;3,"",ContactData!I43)</f>
-        <v>(416) 399-2311</v>
+        <f>IF(LEN(ContactData!I44)&lt;3,"",ContactData!I44)</f>
+        <v>(647) 286-0145</v>
       </c>
       <c r="E45" s="3" t="str">
-        <f>ContactData!J43</f>
-        <v>(905) 752-3521</v>
+        <f>ContactData!J44</f>
+        <v xml:space="preserve">(905) 752-3514 </v>
       </c>
       <c r="F45" s="3" t="str">
-        <f>IF(LEN(ContactData!K43)&lt;3,"",ContactData!K43)</f>
-        <v>benw@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K44)&lt;3,"",ContactData!K44)</f>
+        <v>winniet@livingproperties.com</v>
       </c>
       <c r="G45"/>
       <c r="H45"/>
@@ -3450,28 +3453,28 @@
     </row>
     <row r="46" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A46" s="9">
-        <f>IF(LEN(ContactData!H44)&lt;3,"",ContactData!H44)</f>
-        <v>514</v>
+        <f>IF(LEN(ContactData!H45)&lt;3,"",ContactData!H45)</f>
+        <v>286</v>
       </c>
       <c r="B46" s="3" t="str">
-        <f>ContactData!E44</f>
-        <v>Winnie Tsui</v>
+        <f>ContactData!E45</f>
+        <v>Frederick Tang</v>
       </c>
       <c r="C46" s="3" t="str">
-        <f>ContactData!G44</f>
-        <v>Director of Operations</v>
+        <f>ContactData!G45</f>
+        <v>Director of Business Development</v>
       </c>
       <c r="D46" s="9" t="str">
-        <f>IF(LEN(ContactData!I44)&lt;3,"",ContactData!I44)</f>
-        <v>(647) 286-0145</v>
+        <f>IF(LEN(ContactData!I45)&lt;3,"",ContactData!I45)</f>
+        <v>(416) 618-5898</v>
       </c>
       <c r="E46" s="3" t="str">
-        <f>ContactData!J44</f>
-        <v xml:space="preserve">(905) 752-3514 </v>
+        <f>ContactData!J45</f>
+        <v>-</v>
       </c>
       <c r="F46" s="3" t="str">
-        <f>IF(LEN(ContactData!K44)&lt;3,"",ContactData!K44)</f>
-        <v>winniet@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K45)&lt;3,"",ContactData!K45)</f>
+        <v>fredt@livingproperties.com</v>
       </c>
       <c r="G46"/>
       <c r="H46"/>
@@ -3482,28 +3485,28 @@
     </row>
     <row r="47" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
-        <f>IF(LEN(ContactData!H45)&lt;3,"",ContactData!H45)</f>
-        <v>286</v>
+        <f>IF(LEN(ContactData!H46)&lt;3,"",ContactData!H46)</f>
+        <v>512</v>
       </c>
       <c r="B47" s="3" t="str">
-        <f>ContactData!E45</f>
-        <v>Frederick Tang</v>
+        <f>ContactData!E46</f>
+        <v>Stanley Chow</v>
       </c>
       <c r="C47" s="3" t="str">
-        <f>ContactData!G45</f>
-        <v>Director of Business Development</v>
+        <f>ContactData!G46</f>
+        <v>Property Manager</v>
       </c>
       <c r="D47" s="9" t="str">
-        <f>IF(LEN(ContactData!I45)&lt;3,"",ContactData!I45)</f>
-        <v>(416) 618-5898</v>
+        <f>IF(LEN(ContactData!I46)&lt;3,"",ContactData!I46)</f>
+        <v>(416) 277-6098</v>
       </c>
       <c r="E47" s="3" t="str">
-        <f>ContactData!J45</f>
-        <v>-</v>
+        <f>ContactData!J46</f>
+        <v>(905) 752-3512</v>
       </c>
       <c r="F47" s="3" t="str">
-        <f>IF(LEN(ContactData!K45)&lt;3,"",ContactData!K45)</f>
-        <v>fredt@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K46)&lt;3,"",ContactData!K46)</f>
+        <v>stanleyc@livingproperties.com</v>
       </c>
       <c r="G47"/>
       <c r="H47"/>
@@ -3513,29 +3516,29 @@
       <c r="L47"/>
     </row>
     <row r="48" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A48" s="9" t="e">
-        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B48" s="3" t="e">
-        <f>ContactData!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C48" s="3" t="e">
-        <f>ContactData!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D48" s="9" t="e">
-        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E48" s="3" t="e">
-        <f>ContactData!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F48" s="3" t="e">
-        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
-        <v>#REF!</v>
+      <c r="A48" s="9">
+        <f>IF(LEN(ContactData!H47)&lt;3,"",ContactData!H47)</f>
+        <v>284</v>
+      </c>
+      <c r="B48" s="3" t="str">
+        <f>ContactData!E47</f>
+        <v>Richard Baksh</v>
+      </c>
+      <c r="C48" s="3" t="str">
+        <f>ContactData!G47</f>
+        <v>Property Manager</v>
+      </c>
+      <c r="D48" s="9" t="str">
+        <f>IF(LEN(ContactData!I47)&lt;3,"",ContactData!I47)</f>
+        <v>(647) 967-0088</v>
+      </c>
+      <c r="E48" s="3" t="str">
+        <f>ContactData!J47</f>
+        <v>(905) 258-0632</v>
+      </c>
+      <c r="F48" s="3" t="str">
+        <f>IF(LEN(ContactData!K47)&lt;3,"",ContactData!K47)</f>
+        <v>richardb@livingproperties.com</v>
       </c>
       <c r="G48"/>
       <c r="H48"/>
@@ -3546,28 +3549,28 @@
     </row>
     <row r="49" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
-        <f>IF(LEN(ContactData!H46)&lt;3,"",ContactData!H46)</f>
-        <v>512</v>
+        <f>IF(LEN(ContactData!H48)&lt;3,"",ContactData!H48)</f>
+        <v>517</v>
       </c>
       <c r="B49" s="3" t="str">
-        <f>ContactData!E46</f>
-        <v>Stanley Chow</v>
+        <f>ContactData!E48</f>
+        <v>Ken Kam</v>
       </c>
       <c r="C49" s="3" t="str">
-        <f>ContactData!G46</f>
+        <f>ContactData!G48</f>
         <v>Property Manager</v>
       </c>
       <c r="D49" s="9" t="str">
-        <f>IF(LEN(ContactData!I46)&lt;3,"",ContactData!I46)</f>
-        <v>(416) 277-6098</v>
+        <f>IF(LEN(ContactData!I48)&lt;3,"",ContactData!I48)</f>
+        <v>(647) 204-4455</v>
       </c>
       <c r="E49" s="3" t="str">
-        <f>ContactData!J46</f>
-        <v>(905) 752-3512</v>
+        <f>ContactData!J48</f>
+        <v>(905) 477-2090</v>
       </c>
       <c r="F49" s="3" t="str">
-        <f>IF(LEN(ContactData!K46)&lt;3,"",ContactData!K46)</f>
-        <v>stanleyc@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K48)&lt;3,"",ContactData!K48)</f>
+        <v>kenk@livingproperties.com</v>
       </c>
       <c r="G49"/>
       <c r="H49"/>
@@ -3578,28 +3581,28 @@
     </row>
     <row r="50" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A50" s="9">
-        <f>IF(LEN(ContactData!H47)&lt;3,"",ContactData!H47)</f>
-        <v>284</v>
+        <f>IF(LEN(ContactData!H49)&lt;3,"",ContactData!H49)</f>
+        <v>520</v>
       </c>
       <c r="B50" s="3" t="str">
-        <f>ContactData!E47</f>
-        <v>Richard Baksh</v>
+        <f>ContactData!E49</f>
+        <v>Raymond Chin</v>
       </c>
       <c r="C50" s="3" t="str">
-        <f>ContactData!G47</f>
+        <f>ContactData!G49</f>
         <v>Property Manager</v>
       </c>
       <c r="D50" s="9" t="str">
-        <f>IF(LEN(ContactData!I47)&lt;3,"",ContactData!I47)</f>
-        <v>(647) 967-0088</v>
+        <f>IF(LEN(ContactData!I49)&lt;3,"",ContactData!I49)</f>
+        <v>(437) 331-6038</v>
       </c>
       <c r="E50" s="3" t="str">
-        <f>ContactData!J47</f>
-        <v>(905) 258-0632</v>
+        <f>ContactData!J49</f>
+        <v>(905) 477-2090</v>
       </c>
       <c r="F50" s="3" t="str">
-        <f>IF(LEN(ContactData!K47)&lt;3,"",ContactData!K47)</f>
-        <v>richardb@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K49)&lt;3,"",ContactData!K49)</f>
+        <v>raymondc@livingproperties.com</v>
       </c>
       <c r="G50"/>
       <c r="H50"/>
@@ -3610,28 +3613,28 @@
     </row>
     <row r="51" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
-        <f>IF(LEN(ContactData!H48)&lt;3,"",ContactData!H48)</f>
-        <v>517</v>
+        <f>IF(LEN(ContactData!H50)&lt;3,"",ContactData!H50)</f>
+        <v>168</v>
       </c>
       <c r="B51" s="3" t="str">
-        <f>ContactData!E48</f>
-        <v>Ken Kam</v>
+        <f>ContactData!E50</f>
+        <v>Thomas Lee</v>
       </c>
       <c r="C51" s="3" t="str">
-        <f>ContactData!G48</f>
-        <v>Property Manager</v>
+        <f>ContactData!G50</f>
+        <v>Assistant Property Manager</v>
       </c>
       <c r="D51" s="9" t="str">
-        <f>IF(LEN(ContactData!I48)&lt;3,"",ContactData!I48)</f>
-        <v>(647) 204-4455</v>
+        <f>IF(LEN(ContactData!I50)&lt;3,"",ContactData!I50)</f>
+        <v>(416) 567-4274</v>
       </c>
       <c r="E51" s="3" t="str">
-        <f>ContactData!J48</f>
+        <f>ContactData!J50</f>
         <v>(905) 477-2090</v>
       </c>
       <c r="F51" s="3" t="str">
-        <f>IF(LEN(ContactData!K48)&lt;3,"",ContactData!K48)</f>
-        <v>kenk@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K50)&lt;3,"",ContactData!K50)</f>
+        <v>Thomasl@livingproperties.com</v>
       </c>
       <c r="G51"/>
       <c r="H51"/>
@@ -3642,28 +3645,28 @@
     </row>
     <row r="52" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
-        <f>IF(LEN(ContactData!H49)&lt;3,"",ContactData!H49)</f>
-        <v>520</v>
+        <f>IF(LEN(ContactData!H51)&lt;3,"",ContactData!H51)</f>
+        <v>210</v>
       </c>
       <c r="B52" s="3" t="str">
-        <f>ContactData!E49</f>
-        <v>Raymond Chin</v>
+        <f>ContactData!E51</f>
+        <v>Loretta Leung</v>
       </c>
       <c r="C52" s="3" t="str">
-        <f>ContactData!G49</f>
-        <v>Property Manager</v>
+        <f>ContactData!G51</f>
+        <v>Executive Assistant</v>
       </c>
       <c r="D52" s="9" t="str">
-        <f>IF(LEN(ContactData!I49)&lt;3,"",ContactData!I49)</f>
-        <v>(437) 331-6038</v>
+        <f>IF(LEN(ContactData!I51)&lt;3,"",ContactData!I51)</f>
+        <v>---</v>
       </c>
       <c r="E52" s="3" t="str">
-        <f>ContactData!J49</f>
-        <v>(905) 477-2090</v>
+        <f>ContactData!J51</f>
+        <v>---</v>
       </c>
       <c r="F52" s="3" t="str">
-        <f>IF(LEN(ContactData!K49)&lt;3,"",ContactData!K49)</f>
-        <v>raymondc@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K51)&lt;3,"",ContactData!K51)</f>
+        <v>lorettal@livingproperties.com</v>
       </c>
       <c r="G52"/>
       <c r="H52"/>
@@ -3674,28 +3677,28 @@
     </row>
     <row r="53" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
-        <f>IF(LEN(ContactData!H50)&lt;3,"",ContactData!H50)</f>
-        <v>168</v>
+        <f>IF(LEN(ContactData!H52)&lt;3,"",ContactData!H52)</f>
+        <v>518</v>
       </c>
       <c r="B53" s="3" t="str">
-        <f>ContactData!E50</f>
-        <v>Thomas Lee</v>
+        <f>ContactData!E52</f>
+        <v>Simon Li</v>
       </c>
       <c r="C53" s="3" t="str">
-        <f>ContactData!G50</f>
-        <v>Assistant Property Manager</v>
+        <f>ContactData!G52</f>
+        <v>Senior Accountant</v>
       </c>
       <c r="D53" s="9" t="str">
-        <f>IF(LEN(ContactData!I50)&lt;3,"",ContactData!I50)</f>
-        <v>(416) 567-4274</v>
+        <f>IF(LEN(ContactData!I52)&lt;3,"",ContactData!I52)</f>
+        <v>---</v>
       </c>
       <c r="E53" s="3" t="str">
-        <f>ContactData!J50</f>
-        <v>(905) 477-2090</v>
+        <f>ContactData!J52</f>
+        <v>(905) 752-3518</v>
       </c>
       <c r="F53" s="3" t="str">
-        <f>IF(LEN(ContactData!K50)&lt;3,"",ContactData!K50)</f>
-        <v>Thomasl@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K52)&lt;3,"",ContactData!K52)</f>
+        <v>simonl@livingproperties.com</v>
       </c>
       <c r="G53"/>
       <c r="H53"/>
@@ -3706,28 +3709,28 @@
     </row>
     <row r="54" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
-        <f>IF(LEN(ContactData!H51)&lt;3,"",ContactData!H51)</f>
-        <v>210</v>
+        <f>IF(LEN(ContactData!H53)&lt;3,"",ContactData!H53)</f>
+        <v>281</v>
       </c>
       <c r="B54" s="3" t="str">
-        <f>ContactData!E51</f>
-        <v>Loretta Leung</v>
+        <f>ContactData!E53</f>
+        <v>Nicole Leung</v>
       </c>
       <c r="C54" s="3" t="str">
-        <f>ContactData!G51</f>
-        <v>Executive Assistant</v>
+        <f>ContactData!G53</f>
+        <v>Property Accountant</v>
       </c>
       <c r="D54" s="9" t="str">
-        <f>IF(LEN(ContactData!I51)&lt;3,"",ContactData!I51)</f>
+        <f>IF(LEN(ContactData!I53)&lt;3,"",ContactData!I53)</f>
         <v>---</v>
       </c>
       <c r="E54" s="3" t="str">
-        <f>ContactData!J51</f>
+        <f>ContactData!J53</f>
         <v>---</v>
       </c>
       <c r="F54" s="3" t="str">
-        <f>IF(LEN(ContactData!K51)&lt;3,"",ContactData!K51)</f>
-        <v>lorettal@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K53)&lt;3,"",ContactData!K53)</f>
+        <v>nicolel@livingproperties.com</v>
       </c>
       <c r="G54"/>
       <c r="H54"/>
@@ -3738,28 +3741,28 @@
     </row>
     <row r="55" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
-        <f>IF(LEN(ContactData!H52)&lt;3,"",ContactData!H52)</f>
-        <v>518</v>
+        <f>IF(LEN(ContactData!H54)&lt;3,"",ContactData!H54)</f>
+        <v>523</v>
       </c>
       <c r="B55" s="3" t="str">
-        <f>ContactData!E52</f>
-        <v>Simon Li</v>
+        <f>ContactData!E54</f>
+        <v>Vivian Lum</v>
       </c>
       <c r="C55" s="3" t="str">
-        <f>ContactData!G52</f>
-        <v>Senior Accountant</v>
+        <f>ContactData!G54</f>
+        <v>Accounts Receivable Clerk</v>
       </c>
       <c r="D55" s="9" t="str">
-        <f>IF(LEN(ContactData!I52)&lt;3,"",ContactData!I52)</f>
+        <f>IF(LEN(ContactData!I54)&lt;3,"",ContactData!I54)</f>
         <v>---</v>
       </c>
       <c r="E55" s="3" t="str">
-        <f>ContactData!J52</f>
-        <v>(905) 752-3518</v>
+        <f>ContactData!J54</f>
+        <v>(905) 752-3523</v>
       </c>
       <c r="F55" s="3" t="str">
-        <f>IF(LEN(ContactData!K52)&lt;3,"",ContactData!K52)</f>
-        <v>simonl@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K54)&lt;3,"",ContactData!K54)</f>
+        <v>vivianl@livingproperties.com</v>
       </c>
       <c r="G55"/>
       <c r="H55"/>
@@ -3770,28 +3773,28 @@
     </row>
     <row r="56" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
-        <f>IF(LEN(ContactData!H53)&lt;3,"",ContactData!H53)</f>
-        <v>281</v>
+        <f>IF(LEN(ContactData!H55)&lt;3,"",ContactData!H55)</f>
+        <v>223</v>
       </c>
       <c r="B56" s="3" t="str">
-        <f>ContactData!E53</f>
-        <v>Nicole Leung</v>
+        <f>ContactData!E55</f>
+        <v>Jessica Lee</v>
       </c>
       <c r="C56" s="3" t="str">
-        <f>ContactData!G53</f>
-        <v>Property Accountant</v>
+        <f>ContactData!G55</f>
+        <v xml:space="preserve">Accounting Clerk </v>
       </c>
       <c r="D56" s="9" t="str">
-        <f>IF(LEN(ContactData!I53)&lt;3,"",ContactData!I53)</f>
+        <f>IF(LEN(ContactData!I55)&lt;3,"",ContactData!I55)</f>
         <v>---</v>
       </c>
       <c r="E56" s="3" t="str">
-        <f>ContactData!J53</f>
+        <f>ContactData!J55</f>
         <v>---</v>
       </c>
       <c r="F56" s="3" t="str">
-        <f>IF(LEN(ContactData!K53)&lt;3,"",ContactData!K53)</f>
-        <v>nicolel@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K55)&lt;3,"",ContactData!K55)</f>
+        <v>jessical@livingproperties.com</v>
       </c>
       <c r="G56"/>
       <c r="H56"/>
@@ -3802,28 +3805,28 @@
     </row>
     <row r="57" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
-        <f>IF(LEN(ContactData!H54)&lt;3,"",ContactData!H54)</f>
-        <v>523</v>
+        <f>IF(LEN(ContactData!H56)&lt;3,"",ContactData!H56)</f>
+        <v>172</v>
       </c>
       <c r="B57" s="3" t="str">
-        <f>ContactData!E54</f>
-        <v>Vivian Lum</v>
+        <f>ContactData!E56</f>
+        <v>Rebecca Lau</v>
       </c>
       <c r="C57" s="3" t="str">
-        <f>ContactData!G54</f>
-        <v>Accounts Receivable Clerk</v>
+        <f>ContactData!G56</f>
+        <v>Administrative Assistant</v>
       </c>
       <c r="D57" s="9" t="str">
-        <f>IF(LEN(ContactData!I54)&lt;3,"",ContactData!I54)</f>
+        <f>IF(LEN(ContactData!I56)&lt;3,"",ContactData!I56)</f>
         <v>---</v>
       </c>
       <c r="E57" s="3" t="str">
-        <f>ContactData!J54</f>
-        <v>(905) 752-3523</v>
+        <f>ContactData!J56</f>
+        <v>---</v>
       </c>
       <c r="F57" s="3" t="str">
-        <f>IF(LEN(ContactData!K54)&lt;3,"",ContactData!K54)</f>
-        <v>vivianl@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K56)&lt;3,"",ContactData!K56)</f>
+        <v>rebeccal@livingproperties.com</v>
       </c>
       <c r="G57"/>
       <c r="H57"/>
@@ -3834,28 +3837,28 @@
     </row>
     <row r="58" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
-        <f>IF(LEN(ContactData!H55)&lt;3,"",ContactData!H55)</f>
-        <v>223</v>
+        <f>IF(LEN(ContactData!H57)&lt;3,"",ContactData!H57)</f>
+        <v>182</v>
       </c>
       <c r="B58" s="3" t="str">
-        <f>ContactData!E55</f>
-        <v>Jessica Lee</v>
+        <f>ContactData!E57</f>
+        <v>Kelvin Chan</v>
       </c>
       <c r="C58" s="3" t="str">
-        <f>ContactData!G55</f>
-        <v xml:space="preserve">Accounting Clerk </v>
+        <f>ContactData!G57</f>
+        <v>Administrative Assistant</v>
       </c>
       <c r="D58" s="9" t="str">
-        <f>IF(LEN(ContactData!I55)&lt;3,"",ContactData!I55)</f>
+        <f>IF(LEN(ContactData!I57)&lt;3,"",ContactData!I57)</f>
         <v>---</v>
       </c>
       <c r="E58" s="3" t="str">
-        <f>ContactData!J55</f>
+        <f>ContactData!J57</f>
         <v>---</v>
       </c>
       <c r="F58" s="3" t="str">
-        <f>IF(LEN(ContactData!K55)&lt;3,"",ContactData!K55)</f>
-        <v>jessical@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K57)&lt;3,"",ContactData!K57)</f>
+        <v>kelvinc@livingproperties.com</v>
       </c>
       <c r="G58"/>
       <c r="H58"/>
@@ -3865,29 +3868,29 @@
       <c r="L58"/>
     </row>
     <row r="59" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A59" s="9">
-        <f>IF(LEN(ContactData!H56)&lt;3,"",ContactData!H56)</f>
-        <v>172</v>
+      <c r="A59" s="9" t="str">
+        <f>IF(LEN(ContactData!H58)&lt;3,"",ContactData!H58)</f>
+        <v>---</v>
       </c>
       <c r="B59" s="3" t="str">
-        <f>ContactData!E56</f>
-        <v>Rebecca Lau</v>
+        <f>ContactData!E58</f>
+        <v>Calmaine Hewitt</v>
       </c>
       <c r="C59" s="3" t="str">
-        <f>ContactData!G56</f>
-        <v>Administrative Assistant</v>
+        <f>ContactData!G58</f>
+        <v>Handyman</v>
       </c>
       <c r="D59" s="9" t="str">
-        <f>IF(LEN(ContactData!I56)&lt;3,"",ContactData!I56)</f>
+        <f>IF(LEN(ContactData!I58)&lt;3,"",ContactData!I58)</f>
         <v>---</v>
       </c>
       <c r="E59" s="3" t="str">
-        <f>ContactData!J56</f>
-        <v>---</v>
+        <f>ContactData!J58</f>
+        <v>(905) 477-2090</v>
       </c>
       <c r="F59" s="3" t="str">
-        <f>IF(LEN(ContactData!K56)&lt;3,"",ContactData!K56)</f>
-        <v>rebeccal@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K58)&lt;3,"",ContactData!K58)</f>
+        <v>calmaineh@livingproperties.com</v>
       </c>
       <c r="G59"/>
       <c r="H59"/>
@@ -3898,28 +3901,28 @@
     </row>
     <row r="60" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
-        <f>IF(LEN(ContactData!H57)&lt;3,"",ContactData!H57)</f>
-        <v>182</v>
+        <f>IF(LEN(ContactData!H59)&lt;3,"",ContactData!H59)</f>
+        <v>229</v>
       </c>
       <c r="B60" s="3" t="str">
-        <f>ContactData!E57</f>
-        <v>Kelvin Chan</v>
+        <f>ContactData!E59</f>
+        <v>Matthew Wong</v>
       </c>
       <c r="C60" s="3" t="str">
-        <f>ContactData!G57</f>
-        <v>Administrative Assistant</v>
+        <f>ContactData!G59</f>
+        <v>Accounting Clerk</v>
       </c>
       <c r="D60" s="9" t="str">
-        <f>IF(LEN(ContactData!I57)&lt;3,"",ContactData!I57)</f>
+        <f>IF(LEN(ContactData!I59)&lt;3,"",ContactData!I59)</f>
         <v>---</v>
       </c>
       <c r="E60" s="3" t="str">
-        <f>ContactData!J57</f>
+        <f>ContactData!J59</f>
         <v>---</v>
       </c>
       <c r="F60" s="3" t="str">
-        <f>IF(LEN(ContactData!K57)&lt;3,"",ContactData!K57)</f>
-        <v>kelvinc@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K59)&lt;3,"",ContactData!K59)</f>
+        <v>mattheww@livingproperties.com</v>
       </c>
       <c r="G60"/>
       <c r="H60"/>
@@ -3930,28 +3933,28 @@
     </row>
     <row r="61" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="str">
-        <f>IF(LEN(ContactData!H58)&lt;3,"",ContactData!H58)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!H60)&lt;3,"",ContactData!H60)</f>
+        <v/>
       </c>
       <c r="B61" s="3" t="str">
-        <f>ContactData!E58</f>
-        <v>Calmaine Hewitt</v>
+        <f>ContactData!E60</f>
+        <v>Centro Towers Office</v>
       </c>
       <c r="C61" s="3" t="str">
-        <f>ContactData!G58</f>
-        <v>Handyman</v>
+        <f>ContactData!G60</f>
+        <v>25 Town Centre Crt, Scarborough, ON, M1P 0B4</v>
       </c>
       <c r="D61" s="9" t="str">
-        <f>IF(LEN(ContactData!I58)&lt;3,"",ContactData!I58)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!I60)&lt;3,"",ContactData!I60)</f>
+        <v/>
       </c>
       <c r="E61" s="3" t="str">
-        <f>ContactData!J58</f>
-        <v>(905) 477-2090</v>
+        <f>ContactData!J60</f>
+        <v>T: (416) 290-1242</v>
       </c>
       <c r="F61" s="3" t="str">
-        <f>IF(LEN(ContactData!K58)&lt;3,"",ContactData!K58)</f>
-        <v>calmaineh@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K60)&lt;3,"",ContactData!K60)</f>
+        <v/>
       </c>
       <c r="G61"/>
       <c r="H61"/>
@@ -3961,29 +3964,29 @@
       <c r="L61"/>
     </row>
     <row r="62" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A62" s="9">
-        <f>IF(LEN(ContactData!H59)&lt;3,"",ContactData!H59)</f>
-        <v>229</v>
+      <c r="A62" s="9" t="str">
+        <f>IF(LEN(ContactData!H61)&lt;3,"",ContactData!H61)</f>
+        <v>---</v>
       </c>
       <c r="B62" s="3" t="str">
-        <f>ContactData!E59</f>
-        <v>Matthew Wong</v>
+        <f>ContactData!E61</f>
+        <v>Henry Fu</v>
       </c>
       <c r="C62" s="3" t="str">
-        <f>ContactData!G59</f>
-        <v>Accounting Clerk</v>
+        <f>ContactData!G61</f>
+        <v>Property Manager</v>
       </c>
       <c r="D62" s="9" t="str">
-        <f>IF(LEN(ContactData!I59)&lt;3,"",ContactData!I59)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!I61)&lt;3,"",ContactData!I61)</f>
+        <v>(416) 278-2953</v>
       </c>
       <c r="E62" s="3" t="str">
-        <f>ContactData!J59</f>
-        <v>---</v>
+        <f>ContactData!J61</f>
+        <v>(416) 290-1242</v>
       </c>
       <c r="F62" s="3" t="str">
-        <f>IF(LEN(ContactData!K59)&lt;3,"",ContactData!K59)</f>
-        <v>mattheww@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K61)&lt;3,"",ContactData!K61)</f>
+        <v>henry@centrotowers.com</v>
       </c>
       <c r="G62"/>
       <c r="H62"/>
@@ -3994,28 +3997,28 @@
     </row>
     <row r="63" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A63" s="9" t="str">
-        <f>IF(LEN(ContactData!H60)&lt;3,"",ContactData!H60)</f>
-        <v/>
+        <f>IF(LEN(ContactData!H62)&lt;3,"",ContactData!H62)</f>
+        <v>---</v>
       </c>
       <c r="B63" s="3" t="str">
-        <f>ContactData!E60</f>
-        <v>Centro Towers Office</v>
+        <f>ContactData!E62</f>
+        <v>Sophia Yip</v>
       </c>
       <c r="C63" s="3" t="str">
-        <f>ContactData!G60</f>
-        <v>25 Town Centre Crt, Scarborough, ON, M1P 0B4</v>
+        <f>ContactData!G62</f>
+        <v>Property Administrator</v>
       </c>
       <c r="D63" s="9" t="str">
-        <f>IF(LEN(ContactData!I60)&lt;3,"",ContactData!I60)</f>
-        <v/>
+        <f>IF(LEN(ContactData!I62)&lt;3,"",ContactData!I62)</f>
+        <v>---</v>
       </c>
       <c r="E63" s="3" t="str">
-        <f>ContactData!J60</f>
-        <v>T: (416) 290-1242</v>
+        <f>ContactData!J62</f>
+        <v>(416) 290-1242</v>
       </c>
       <c r="F63" s="3" t="str">
-        <f>IF(LEN(ContactData!K60)&lt;3,"",ContactData!K60)</f>
-        <v/>
+        <f>IF(LEN(ContactData!K62)&lt;3,"",ContactData!K62)</f>
+        <v>sophia@centrotowers.com</v>
       </c>
       <c r="G63"/>
       <c r="H63"/>
@@ -4026,28 +4029,28 @@
     </row>
     <row r="64" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="str">
-        <f>IF(LEN(ContactData!H61)&lt;3,"",ContactData!H61)</f>
+        <f>IF(LEN(ContactData!H63)&lt;3,"",ContactData!H63)</f>
         <v>---</v>
       </c>
       <c r="B64" s="3" t="str">
-        <f>ContactData!E61</f>
-        <v>Henry Fu</v>
+        <f>ContactData!E63</f>
+        <v xml:space="preserve">Security Desk </v>
       </c>
       <c r="C64" s="3" t="str">
-        <f>ContactData!G61</f>
-        <v>Property Manager</v>
+        <f>ContactData!G63</f>
+        <v xml:space="preserve">Centro Security Desk </v>
       </c>
       <c r="D64" s="9" t="str">
-        <f>IF(LEN(ContactData!I61)&lt;3,"",ContactData!I61)</f>
-        <v>(416) 278-2953</v>
+        <f>IF(LEN(ContactData!I63)&lt;3,"",ContactData!I63)</f>
+        <v>---</v>
       </c>
       <c r="E64" s="3" t="str">
-        <f>ContactData!J61</f>
-        <v>(416) 290-1242</v>
+        <f>ContactData!J63</f>
+        <v>(416) 296-0099</v>
       </c>
       <c r="F64" s="3" t="str">
-        <f>IF(LEN(ContactData!K61)&lt;3,"",ContactData!K61)</f>
-        <v>henry@centrotowers.com</v>
+        <f>IF(LEN(ContactData!K63)&lt;3,"",ContactData!K63)</f>
+        <v>---</v>
       </c>
       <c r="G64"/>
       <c r="H64"/>
@@ -4058,28 +4061,28 @@
     </row>
     <row r="65" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A65" s="9" t="str">
-        <f>IF(LEN(ContactData!H62)&lt;3,"",ContactData!H62)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!H64)&lt;3,"",ContactData!H64)</f>
+        <v/>
       </c>
       <c r="B65" s="3" t="str">
-        <f>ContactData!E62</f>
-        <v>Sophia Yip</v>
+        <f>ContactData!E64</f>
+        <v>EQ1 Office</v>
       </c>
       <c r="C65" s="3" t="str">
-        <f>ContactData!G62</f>
-        <v>Property Administrator</v>
+        <f>ContactData!G64</f>
+        <v>70 Town Centre Court, Scarborough, ON, M1P 0B2</v>
       </c>
       <c r="D65" s="9" t="str">
-        <f>IF(LEN(ContactData!I62)&lt;3,"",ContactData!I62)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!I64)&lt;3,"",ContactData!I64)</f>
+        <v/>
       </c>
       <c r="E65" s="3" t="str">
-        <f>ContactData!J62</f>
-        <v>(416) 290-1242</v>
+        <f>ContactData!J64</f>
+        <v xml:space="preserve">T: (416) 279-0603 </v>
       </c>
       <c r="F65" s="3" t="str">
-        <f>IF(LEN(ContactData!K62)&lt;3,"",ContactData!K62)</f>
-        <v>sophia@centrotowers.com</v>
+        <f>IF(LEN(ContactData!K64)&lt;3,"",ContactData!K64)</f>
+        <v>eq1@livingproperties.com</v>
       </c>
       <c r="G65"/>
       <c r="H65"/>
@@ -4090,28 +4093,28 @@
     </row>
     <row r="66" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="str">
-        <f>IF(LEN(ContactData!H63)&lt;3,"",ContactData!H63)</f>
+        <f>IF(LEN(ContactData!H65)&lt;3,"",ContactData!H65)</f>
         <v>---</v>
       </c>
       <c r="B66" s="3" t="str">
-        <f>ContactData!E63</f>
-        <v xml:space="preserve">Security Desk </v>
+        <f>ContactData!E65</f>
+        <v>Ming Ip</v>
       </c>
       <c r="C66" s="3" t="str">
-        <f>ContactData!G63</f>
-        <v xml:space="preserve">Centro Security Desk </v>
+        <f>ContactData!G65</f>
+        <v>Property Manager</v>
       </c>
       <c r="D66" s="9" t="str">
-        <f>IF(LEN(ContactData!I63)&lt;3,"",ContactData!I63)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!I65)&lt;3,"",ContactData!I65)</f>
+        <v>(647) 286-0147</v>
       </c>
       <c r="E66" s="3" t="str">
-        <f>ContactData!J63</f>
-        <v>(416) 296-0099</v>
+        <f>ContactData!J65</f>
+        <v xml:space="preserve">(416) 279-0603 </v>
       </c>
       <c r="F66" s="3" t="str">
-        <f>IF(LEN(ContactData!K63)&lt;3,"",ContactData!K63)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!K65)&lt;3,"",ContactData!K65)</f>
+        <v>eq1manager@livingproperties.com</v>
       </c>
       <c r="G66"/>
       <c r="H66"/>
@@ -4122,28 +4125,28 @@
     </row>
     <row r="67" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A67" s="9" t="str">
-        <f>IF(LEN(ContactData!H64)&lt;3,"",ContactData!H64)</f>
-        <v/>
+        <f>IF(LEN(ContactData!H66)&lt;3,"",ContactData!H66)</f>
+        <v>---</v>
       </c>
       <c r="B67" s="3" t="str">
-        <f>ContactData!E64</f>
-        <v>EQ1 Office</v>
+        <f>ContactData!E66</f>
+        <v xml:space="preserve">Security Desk </v>
       </c>
       <c r="C67" s="3" t="str">
-        <f>ContactData!G64</f>
-        <v>70 Town Centre Court, Scarborough, ON, M1P 0B2</v>
+        <f>ContactData!G66</f>
+        <v xml:space="preserve">EQ1 Security Desk </v>
       </c>
       <c r="D67" s="9" t="str">
-        <f>IF(LEN(ContactData!I64)&lt;3,"",ContactData!I64)</f>
-        <v/>
+        <f>IF(LEN(ContactData!I66)&lt;3,"",ContactData!I66)</f>
+        <v>---</v>
       </c>
       <c r="E67" s="3" t="str">
-        <f>ContactData!J64</f>
-        <v xml:space="preserve">T: (416) 279-0603 </v>
+        <f>ContactData!J66</f>
+        <v>(416) 279-1894</v>
       </c>
       <c r="F67" s="3" t="str">
-        <f>IF(LEN(ContactData!K64)&lt;3,"",ContactData!K64)</f>
-        <v>eq1@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K66)&lt;3,"",ContactData!K66)</f>
+        <v>---</v>
       </c>
       <c r="G67"/>
       <c r="H67"/>
@@ -4154,28 +4157,28 @@
     </row>
     <row r="68" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="str">
-        <f>IF(LEN(ContactData!H65)&lt;3,"",ContactData!H65)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!H67)&lt;3,"",ContactData!H67)</f>
+        <v/>
       </c>
       <c r="B68" s="3" t="str">
-        <f>ContactData!E65</f>
-        <v>Ming Ip</v>
+        <f>ContactData!E67</f>
+        <v>EQ2 Office</v>
       </c>
       <c r="C68" s="3" t="str">
-        <f>ContactData!G65</f>
-        <v>Property Manager</v>
+        <f>ContactData!G67</f>
+        <v>60 Town Centre Court, Scarborough, ON, M1P 0B1</v>
       </c>
       <c r="D68" s="9" t="str">
-        <f>IF(LEN(ContactData!I65)&lt;3,"",ContactData!I65)</f>
-        <v>(647) 286-0147</v>
+        <f>IF(LEN(ContactData!I67)&lt;3,"",ContactData!I67)</f>
+        <v/>
       </c>
       <c r="E68" s="3" t="str">
-        <f>ContactData!J65</f>
-        <v xml:space="preserve">(416) 279-0603 </v>
+        <f>ContactData!J67</f>
+        <v xml:space="preserve">T: (416) 279-0591 </v>
       </c>
       <c r="F68" s="3" t="str">
-        <f>IF(LEN(ContactData!K65)&lt;3,"",ContactData!K65)</f>
-        <v>eq1manager@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K67)&lt;3,"",ContactData!K67)</f>
+        <v/>
       </c>
       <c r="G68"/>
       <c r="H68"/>
@@ -4186,28 +4189,28 @@
     </row>
     <row r="69" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A69" s="9" t="str">
-        <f>IF(LEN(ContactData!H66)&lt;3,"",ContactData!H66)</f>
+        <f>IF(LEN(ContactData!H68)&lt;3,"",ContactData!H68)</f>
         <v>---</v>
       </c>
       <c r="B69" s="3" t="str">
-        <f>ContactData!E66</f>
-        <v xml:space="preserve">Security Desk </v>
+        <f>ContactData!E68</f>
+        <v>Aaron Ma</v>
       </c>
       <c r="C69" s="3" t="str">
-        <f>ContactData!G66</f>
-        <v xml:space="preserve">EQ1 Security Desk </v>
+        <f>ContactData!G68</f>
+        <v>Property Manager</v>
       </c>
       <c r="D69" s="9" t="str">
-        <f>IF(LEN(ContactData!I66)&lt;3,"",ContactData!I66)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!I68)&lt;3,"",ContactData!I68)</f>
+        <v>(416) 684-2236</v>
       </c>
       <c r="E69" s="3" t="str">
-        <f>ContactData!J66</f>
-        <v>(416) 279-1894</v>
+        <f>ContactData!J68</f>
+        <v>(416) 279-0591</v>
       </c>
       <c r="F69" s="3" t="str">
-        <f>IF(LEN(ContactData!K66)&lt;3,"",ContactData!K66)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!K68)&lt;3,"",ContactData!K68)</f>
+        <v>eq2manager@livingproperties.com</v>
       </c>
       <c r="G69"/>
       <c r="H69"/>
@@ -4218,28 +4221,28 @@
     </row>
     <row r="70" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="str">
-        <f>IF(LEN(ContactData!H67)&lt;3,"",ContactData!H67)</f>
-        <v/>
+        <f>IF(LEN(ContactData!H69)&lt;3,"",ContactData!H69)</f>
+        <v>---</v>
       </c>
       <c r="B70" s="3" t="str">
-        <f>ContactData!E67</f>
-        <v>EQ2 Office</v>
+        <f>ContactData!E69</f>
+        <v xml:space="preserve">Security Desk </v>
       </c>
       <c r="C70" s="3" t="str">
-        <f>ContactData!G67</f>
-        <v>60 Town Centre Court, Scarborough, ON, M1P 0B1</v>
+        <f>ContactData!G69</f>
+        <v xml:space="preserve">EQ2 Security Desk </v>
       </c>
       <c r="D70" s="9" t="str">
-        <f>IF(LEN(ContactData!I67)&lt;3,"",ContactData!I67)</f>
-        <v/>
+        <f>IF(LEN(ContactData!I69)&lt;3,"",ContactData!I69)</f>
+        <v>---</v>
       </c>
       <c r="E70" s="3" t="str">
-        <f>ContactData!J67</f>
-        <v xml:space="preserve">T: (416) 279-0591 </v>
+        <f>ContactData!J69</f>
+        <v>(416) 279-1211</v>
       </c>
       <c r="F70" s="3" t="str">
-        <f>IF(LEN(ContactData!K67)&lt;3,"",ContactData!K67)</f>
-        <v/>
+        <f>IF(LEN(ContactData!K69)&lt;3,"",ContactData!K69)</f>
+        <v>---</v>
       </c>
       <c r="G70"/>
       <c r="H70"/>
@@ -4250,28 +4253,28 @@
     </row>
     <row r="71" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="str">
-        <f>IF(LEN(ContactData!H68)&lt;3,"",ContactData!H68)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!H70)&lt;3,"",ContactData!H70)</f>
+        <v/>
       </c>
       <c r="B71" s="3" t="str">
-        <f>ContactData!E68</f>
-        <v>Aaron Ma</v>
+        <f>ContactData!E70</f>
+        <v>Alton Tower Office</v>
       </c>
       <c r="C71" s="3" t="str">
-        <f>ContactData!G68</f>
-        <v>Property Manager</v>
+        <f>ContactData!G70</f>
+        <v>160 Alton Towers Cir, Toronto, ON, M1V 4X8</v>
       </c>
       <c r="D71" s="9" t="str">
-        <f>IF(LEN(ContactData!I68)&lt;3,"",ContactData!I68)</f>
-        <v>(416) 684-2236</v>
+        <f>IF(LEN(ContactData!I70)&lt;3,"",ContactData!I70)</f>
+        <v/>
       </c>
       <c r="E71" s="3" t="str">
-        <f>ContactData!J68</f>
-        <v>(416) 279-0591</v>
+        <f>ContactData!J70</f>
+        <v>T: (437)-533-1208</v>
       </c>
       <c r="F71" s="3" t="str">
-        <f>IF(LEN(ContactData!K68)&lt;3,"",ContactData!K68)</f>
-        <v>eq2manager@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K70)&lt;3,"",ContactData!K70)</f>
+        <v/>
       </c>
       <c r="G71"/>
       <c r="H71"/>
@@ -4282,28 +4285,28 @@
     </row>
     <row r="72" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A72" s="9" t="str">
-        <f>IF(LEN(ContactData!H69)&lt;3,"",ContactData!H69)</f>
+        <f>IF(LEN(ContactData!H71)&lt;3,"",ContactData!H71)</f>
         <v>---</v>
       </c>
       <c r="B72" s="3" t="str">
-        <f>ContactData!E69</f>
-        <v xml:space="preserve">Security Desk </v>
+        <f>ContactData!E71</f>
+        <v>Ken Kam</v>
       </c>
       <c r="C72" s="3" t="str">
-        <f>ContactData!G69</f>
-        <v xml:space="preserve">EQ2 Security Desk </v>
+        <f>ContactData!G71</f>
+        <v>Property Manager</v>
       </c>
       <c r="D72" s="9" t="str">
-        <f>IF(LEN(ContactData!I69)&lt;3,"",ContactData!I69)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!I71)&lt;3,"",ContactData!I71)</f>
+        <v>(647) 204-4455</v>
       </c>
       <c r="E72" s="3" t="str">
-        <f>ContactData!J69</f>
-        <v>(416) 279-1211</v>
+        <f>ContactData!J71</f>
+        <v>(905) 477-2090</v>
       </c>
       <c r="F72" s="3" t="str">
-        <f>IF(LEN(ContactData!K69)&lt;3,"",ContactData!K69)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!K71)&lt;3,"",ContactData!K71)</f>
+        <v>kenk@livingproperties.com</v>
       </c>
       <c r="G72"/>
       <c r="H72"/>
@@ -4314,28 +4317,28 @@
     </row>
     <row r="73" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A73" s="9" t="str">
-        <f>IF(LEN(ContactData!H70)&lt;3,"",ContactData!H70)</f>
-        <v/>
+        <f>IF(LEN(ContactData!H72)&lt;3,"",ContactData!H72)</f>
+        <v>---</v>
       </c>
       <c r="B73" s="3" t="str">
-        <f>ContactData!E70</f>
-        <v>Alton Tower Office</v>
+        <f>ContactData!E72</f>
+        <v>Christie Ip</v>
       </c>
       <c r="C73" s="3" t="str">
-        <f>ContactData!G70</f>
-        <v>160 Alton Towers Cir, Toronto, ON, M1V 4X8</v>
+        <f>ContactData!G72</f>
+        <v>Administrative Assistant</v>
       </c>
       <c r="D73" s="9" t="str">
-        <f>IF(LEN(ContactData!I70)&lt;3,"",ContactData!I70)</f>
-        <v/>
+        <f>IF(LEN(ContactData!I72)&lt;3,"",ContactData!I72)</f>
+        <v>(437)-533-1208</v>
       </c>
       <c r="E73" s="3" t="str">
-        <f>ContactData!J70</f>
-        <v>T: (437)-533-1208</v>
+        <f>ContactData!J72</f>
+        <v>---</v>
       </c>
       <c r="F73" s="3" t="str">
-        <f>IF(LEN(ContactData!K70)&lt;3,"",ContactData!K70)</f>
-        <v/>
+        <f>IF(LEN(ContactData!K72)&lt;3,"",ContactData!K72)</f>
+        <v xml:space="preserve">optima2@livingproperties.com </v>
       </c>
       <c r="G73"/>
       <c r="H73"/>
@@ -4346,28 +4349,28 @@
     </row>
     <row r="74" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A74" s="9" t="str">
-        <f>IF(LEN(ContactData!H71)&lt;3,"",ContactData!H71)</f>
+        <f>IF(LEN(ContactData!H73)&lt;3,"",ContactData!H73)</f>
         <v>---</v>
       </c>
       <c r="B74" s="3" t="str">
-        <f>ContactData!E71</f>
-        <v>Ken Kam</v>
+        <f>ContactData!E73</f>
+        <v xml:space="preserve">Security Desk </v>
       </c>
       <c r="C74" s="3" t="str">
-        <f>ContactData!G71</f>
-        <v>Property Manager</v>
+        <f>ContactData!G73</f>
+        <v xml:space="preserve">Alton Tower Security Desk </v>
       </c>
       <c r="D74" s="9" t="str">
-        <f>IF(LEN(ContactData!I71)&lt;3,"",ContactData!I71)</f>
-        <v>(647) 204-4455</v>
+        <f>IF(LEN(ContactData!I73)&lt;3,"",ContactData!I73)</f>
+        <v>---</v>
       </c>
       <c r="E74" s="3" t="str">
-        <f>ContactData!J71</f>
-        <v>(905) 477-2090</v>
+        <f>ContactData!J73</f>
+        <v>(416) 754-3131</v>
       </c>
       <c r="F74" s="3" t="str">
-        <f>IF(LEN(ContactData!K71)&lt;3,"",ContactData!K71)</f>
-        <v>kenk@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K73)&lt;3,"",ContactData!K73)</f>
+        <v>---</v>
       </c>
       <c r="G74"/>
       <c r="H74"/>
@@ -4378,28 +4381,28 @@
     </row>
     <row r="75" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A75" s="9" t="str">
-        <f>IF(LEN(ContactData!H72)&lt;3,"",ContactData!H72)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!H74)&lt;3,"",ContactData!H74)</f>
+        <v/>
       </c>
       <c r="B75" s="3" t="str">
-        <f>ContactData!E72</f>
-        <v>Christie Ip</v>
+        <f>ContactData!E74</f>
+        <v>IHMG Office</v>
       </c>
       <c r="C75" s="3" t="str">
-        <f>ContactData!G72</f>
-        <v>Administrative Assistant</v>
+        <f>ContactData!G74</f>
+        <v>8 Steelcase Road West, Markham, ON, L3R 1B2</v>
       </c>
       <c r="D75" s="9" t="str">
-        <f>IF(LEN(ContactData!I72)&lt;3,"",ContactData!I72)</f>
-        <v>(437)-533-1208</v>
+        <f>IF(LEN(ContactData!I74)&lt;3,"",ContactData!I74)</f>
+        <v/>
       </c>
       <c r="E75" s="3" t="str">
-        <f>ContactData!J72</f>
-        <v>---</v>
+        <f>ContactData!J74</f>
+        <v>T: (905) 475-6000</v>
       </c>
       <c r="F75" s="3" t="str">
-        <f>IF(LEN(ContactData!K72)&lt;3,"",ContactData!K72)</f>
-        <v xml:space="preserve">optima2@livingproperties.com </v>
+        <f>IF(LEN(ContactData!K74)&lt;3,"",ContactData!K74)</f>
+        <v>info@ihmg.ca</v>
       </c>
       <c r="G75"/>
       <c r="H75"/>
@@ -4410,28 +4413,28 @@
     </row>
     <row r="76" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="A76" s="9" t="str">
-        <f>IF(LEN(ContactData!H73)&lt;3,"",ContactData!H73)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!H75)&lt;3,"",ContactData!H75)</f>
+        <v/>
       </c>
       <c r="B76" s="3" t="str">
-        <f>ContactData!E73</f>
-        <v xml:space="preserve">Security Desk </v>
+        <f>ContactData!E75</f>
+        <v>IHMGRI Office</v>
       </c>
       <c r="C76" s="3" t="str">
-        <f>ContactData!G73</f>
-        <v xml:space="preserve">Alton Tower Security Desk </v>
+        <f>ContactData!G75</f>
+        <v>8 Steelcase Road West, Unit E, Markham, ON, L3R 1B2</v>
       </c>
       <c r="D76" s="9" t="str">
-        <f>IF(LEN(ContactData!I73)&lt;3,"",ContactData!I73)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!I75)&lt;3,"",ContactData!I75)</f>
+        <v/>
       </c>
       <c r="E76" s="3" t="str">
-        <f>ContactData!J73</f>
-        <v>(416) 754-3131</v>
+        <f>ContactData!J75</f>
+        <v>T: (905) 489-8989</v>
       </c>
       <c r="F76" s="3" t="str">
-        <f>IF(LEN(ContactData!K73)&lt;3,"",ContactData!K73)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!K75)&lt;3,"",ContactData!K75)</f>
+        <v>realestate@ihmg.ca</v>
       </c>
       <c r="G76"/>
       <c r="H76"/>
@@ -4441,29 +4444,29 @@
       <c r="L76"/>
     </row>
     <row r="77" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A77" s="9" t="str">
-        <f>IF(LEN(ContactData!H74)&lt;3,"",ContactData!H74)</f>
-        <v/>
+      <c r="A77" s="9">
+        <f>IF(LEN(ContactData!H76)&lt;3,"",ContactData!H76)</f>
+        <v>120</v>
       </c>
       <c r="B77" s="3" t="str">
-        <f>ContactData!E74</f>
-        <v>IHMG Office</v>
+        <f>ContactData!E76</f>
+        <v>Eddie Tang</v>
       </c>
       <c r="C77" s="3" t="str">
-        <f>ContactData!G74</f>
-        <v>8 Steelcase Road West, Markham, ON, L3R 1B2</v>
+        <f>ContactData!G76</f>
+        <v>Financial Controller</v>
       </c>
       <c r="D77" s="9" t="str">
-        <f>IF(LEN(ContactData!I74)&lt;3,"",ContactData!I74)</f>
-        <v/>
+        <f>IF(LEN(ContactData!I76)&lt;3,"",ContactData!I76)</f>
+        <v>(416) 723-8329</v>
       </c>
       <c r="E77" s="3" t="str">
-        <f>ContactData!J74</f>
-        <v>T: (905) 475-6000</v>
+        <f>ContactData!J76</f>
+        <v>(905) 489-0186</v>
       </c>
       <c r="F77" s="3" t="str">
-        <f>IF(LEN(ContactData!K74)&lt;3,"",ContactData!K74)</f>
-        <v>info@ihmg.ca</v>
+        <f>IF(LEN(ContactData!K76)&lt;3,"",ContactData!K76)</f>
+        <v>eddie@ihmg.ca</v>
       </c>
       <c r="G77"/>
       <c r="H77"/>
@@ -4473,29 +4476,29 @@
       <c r="L77"/>
     </row>
     <row r="78" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A78" s="9" t="str">
-        <f>IF(LEN(ContactData!H75)&lt;3,"",ContactData!H75)</f>
-        <v/>
+      <c r="A78" s="9">
+        <f>IF(LEN(ContactData!H77)&lt;3,"",ContactData!H77)</f>
+        <v>187</v>
       </c>
       <c r="B78" s="3" t="str">
-        <f>ContactData!E75</f>
-        <v>IHMGRI Office</v>
+        <f>ContactData!E77</f>
+        <v>Lily Hou</v>
       </c>
       <c r="C78" s="3" t="str">
-        <f>ContactData!G75</f>
-        <v>8 Steelcase Road West, Unit E, Markham, ON, L3R 1B2</v>
+        <f>ContactData!G77</f>
+        <v>Senior Accounting Analyst &amp; Operations Support</v>
       </c>
       <c r="D78" s="9" t="str">
-        <f>IF(LEN(ContactData!I75)&lt;3,"",ContactData!I75)</f>
-        <v/>
+        <f>IF(LEN(ContactData!I77)&lt;3,"",ContactData!I77)</f>
+        <v>(647) 774-8994</v>
       </c>
       <c r="E78" s="3" t="str">
-        <f>ContactData!J75</f>
-        <v>T: (905) 489-8989</v>
+        <f>ContactData!J77</f>
+        <v>---</v>
       </c>
       <c r="F78" s="3" t="str">
-        <f>IF(LEN(ContactData!K75)&lt;3,"",ContactData!K75)</f>
-        <v>realestate@ihmg.ca</v>
+        <f>IF(LEN(ContactData!K77)&lt;3,"",ContactData!K77)</f>
+        <v>lily@ihmg.ca</v>
       </c>
       <c r="G78"/>
       <c r="H78"/>
@@ -4505,30 +4508,12 @@
       <c r="L78"/>
     </row>
     <row r="79" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A79" s="9">
-        <f>IF(LEN(ContactData!H76)&lt;3,"",ContactData!H76)</f>
-        <v>120</v>
-      </c>
-      <c r="B79" s="3" t="str">
-        <f>ContactData!E76</f>
-        <v>Eddie Tang</v>
-      </c>
-      <c r="C79" s="3" t="str">
-        <f>ContactData!G76</f>
-        <v>Financial Controller</v>
-      </c>
-      <c r="D79" s="9" t="str">
-        <f>IF(LEN(ContactData!I76)&lt;3,"",ContactData!I76)</f>
-        <v>(416) 723-8329</v>
-      </c>
-      <c r="E79" s="3" t="str">
-        <f>ContactData!J76</f>
-        <v>(905) 489-0186</v>
-      </c>
-      <c r="F79" s="3" t="str">
-        <f>IF(LEN(ContactData!K76)&lt;3,"",ContactData!K76)</f>
-        <v>eddie@ihmg.ca</v>
-      </c>
+      <c r="A79" s="1"/>
+      <c r="B79"/>
+      <c r="C79"/>
+      <c r="D79"/>
+      <c r="E79"/>
+      <c r="F79"/>
       <c r="G79"/>
       <c r="H79"/>
       <c r="I79"/>
@@ -4537,30 +4522,12 @@
       <c r="L79"/>
     </row>
     <row r="80" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A80" s="9">
-        <f>IF(LEN(ContactData!H77)&lt;3,"",ContactData!H77)</f>
-        <v>187</v>
-      </c>
-      <c r="B80" s="3" t="str">
-        <f>ContactData!E77</f>
-        <v>Lily Hou</v>
-      </c>
-      <c r="C80" s="3" t="str">
-        <f>ContactData!G77</f>
-        <v>Senior Accounting Analyst &amp; Operations Support</v>
-      </c>
-      <c r="D80" s="9" t="str">
-        <f>IF(LEN(ContactData!I77)&lt;3,"",ContactData!I77)</f>
-        <v>(647) 774-8994</v>
-      </c>
-      <c r="E80" s="3" t="str">
-        <f>ContactData!J77</f>
-        <v>---</v>
-      </c>
-      <c r="F80" s="3" t="str">
-        <f>IF(LEN(ContactData!K77)&lt;3,"",ContactData!K77)</f>
-        <v>lily@ihmg.ca</v>
-      </c>
+      <c r="A80" s="1"/>
+      <c r="B80"/>
+      <c r="C80"/>
+      <c r="D80"/>
+      <c r="E80"/>
+      <c r="F80"/>
       <c r="G80"/>
       <c r="H80"/>
       <c r="I80"/>
@@ -8516,51 +8483,23 @@
       <c r="K362"/>
       <c r="L362"/>
     </row>
-    <row r="363" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A363" s="1"/>
-      <c r="B363"/>
-      <c r="C363"/>
-      <c r="D363"/>
-      <c r="E363"/>
-      <c r="F363"/>
-      <c r="G363"/>
-      <c r="H363"/>
-      <c r="I363"/>
-      <c r="J363"/>
-      <c r="K363"/>
-      <c r="L363"/>
-    </row>
-    <row r="364" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="A364" s="1"/>
-      <c r="B364"/>
-      <c r="C364"/>
-      <c r="D364"/>
-      <c r="E364"/>
-      <c r="F364"/>
-      <c r="G364"/>
-      <c r="H364"/>
-      <c r="I364"/>
-      <c r="J364"/>
-      <c r="K364"/>
-      <c r="L364"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A3:A80 D3:D80">
+  <conditionalFormatting sqref="A3:A78 D3:D78">
     <cfRule type="containsBlanks" dxfId="31" priority="17">
       <formula>LEN(TRIM(A3))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B3:B80">
+  <conditionalFormatting sqref="B3:B78">
     <cfRule type="containsText" dxfId="30" priority="16" operator="containsText" text="Office">
       <formula>NOT(ISERROR(SEARCH("Office",B3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C80">
+  <conditionalFormatting sqref="C3:C78">
     <cfRule type="containsText" dxfId="29" priority="15" operator="containsText" text="ON,">
       <formula>NOT(ISERROR(SEARCH("ON,",C3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E80">
+  <conditionalFormatting sqref="E3:E78">
     <cfRule type="containsText" dxfId="28" priority="13" operator="containsText" text="T">
       <formula>NOT(ISERROR(SEARCH("T",E3)))</formula>
     </cfRule>
@@ -8575,7 +8514,7 @@
       <formula>LEN(TRIM(F3))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F80">
+  <conditionalFormatting sqref="F4:F78">
     <cfRule type="containsText" dxfId="25" priority="1" operator="containsText" text="ye@">
       <formula>NOT(ISERROR(SEARCH("ye@",F4)))</formula>
     </cfRule>
@@ -8618,7 +8557,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I368"/>
+  <dimension ref="A1:I366"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="8" customWidth="1"/>
@@ -8637,7 +8576,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.25">
@@ -9042,28 +8981,28 @@
     </row>
     <row r="16" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
-        <f>IF(LEN(ContactData!H16)&lt;3,"",ContactData!H16)</f>
-        <v>123</v>
+        <f>IF(LEN(ContactData!H15)&lt;3,"",ContactData!H15)</f>
+        <v>282</v>
       </c>
       <c r="B16" s="3" t="str">
-        <f>ContactData!E16</f>
-        <v>Wendy Chung</v>
+        <f>ContactData!E15</f>
+        <v>Joanna Xie</v>
       </c>
       <c r="C16" s="3" t="str">
-        <f>ContactData!G16</f>
-        <v xml:space="preserve">Administration Officer </v>
+        <f>ContactData!G15</f>
+        <v>Agent Services Coordinator</v>
       </c>
       <c r="D16" s="9" t="str">
-        <f>IF(LEN(ContactData!I16)&lt;3,"",ContactData!I16)</f>
+        <f>IF(LEN(ContactData!I15)&lt;3,"",ContactData!I15)</f>
         <v>---</v>
       </c>
       <c r="E16" s="3" t="str">
-        <f>ContactData!J16</f>
+        <f>ContactData!J15</f>
         <v>---</v>
       </c>
       <c r="F16" s="3" t="str">
-        <f>IF(LEN(ContactData!K16)&lt;3,"",ContactData!K16)</f>
-        <v>wendychung@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K15)&lt;3,"",ContactData!K15)</f>
+        <v>joannaxie@livingrealtykw.com</v>
       </c>
       <c r="G16"/>
       <c r="H16"/>
@@ -9071,28 +9010,28 @@
     </row>
     <row r="17" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
-        <f>IF(LEN(ContactData!H17)&lt;3,"",ContactData!H17)</f>
-        <v>206</v>
+        <f>IF(LEN(ContactData!H16)&lt;3,"",ContactData!H16)</f>
+        <v>123</v>
       </c>
       <c r="B17" s="3" t="str">
-        <f>ContactData!E17</f>
-        <v>Benjamin Wong</v>
+        <f>ContactData!E16</f>
+        <v>Wendy Chung</v>
       </c>
       <c r="C17" s="3" t="str">
-        <f>ContactData!G17</f>
-        <v>Assistant to the Broker of Record</v>
+        <f>ContactData!G16</f>
+        <v xml:space="preserve">Administration Officer </v>
       </c>
       <c r="D17" s="9" t="str">
-        <f>IF(LEN(ContactData!I17)&lt;3,"",ContactData!I17)</f>
+        <f>IF(LEN(ContactData!I16)&lt;3,"",ContactData!I16)</f>
         <v>---</v>
       </c>
       <c r="E17" s="3" t="str">
-        <f>ContactData!J17</f>
+        <f>ContactData!J16</f>
         <v>---</v>
       </c>
       <c r="F17" s="3" t="str">
-        <f>IF(LEN(ContactData!K17)&lt;3,"",ContactData!K17)</f>
-        <v>benjaminwongici@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K16)&lt;3,"",ContactData!K16)</f>
+        <v>wendychung@livingrealtykw.com</v>
       </c>
       <c r="G17"/>
       <c r="H17"/>
@@ -9100,28 +9039,28 @@
     </row>
     <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
-        <f>IF(LEN(ContactData!H18)&lt;3,"",ContactData!H18)</f>
-        <v>507</v>
+        <f>IF(LEN(ContactData!H17)&lt;3,"",ContactData!H17)</f>
+        <v>206</v>
       </c>
       <c r="B18" s="3" t="str">
-        <f>ContactData!E18</f>
-        <v>Luvie Chao</v>
+        <f>ContactData!E17</f>
+        <v>Benjamin Wong</v>
       </c>
       <c r="C18" s="3" t="str">
-        <f>ContactData!G18</f>
-        <v>Senior Deal Administrator</v>
+        <f>ContactData!G17</f>
+        <v>Assistant to the Broker of Record</v>
       </c>
       <c r="D18" s="9" t="str">
-        <f>IF(LEN(ContactData!I18)&lt;3,"",ContactData!I18)</f>
+        <f>IF(LEN(ContactData!I17)&lt;3,"",ContactData!I17)</f>
         <v>---</v>
       </c>
       <c r="E18" s="3" t="str">
-        <f>ContactData!J18</f>
-        <v>(905) 752-3507</v>
+        <f>ContactData!J17</f>
+        <v>---</v>
       </c>
       <c r="F18" s="3" t="str">
-        <f>IF(LEN(ContactData!K18)&lt;3,"",ContactData!K18)</f>
-        <v>luvie@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K17)&lt;3,"",ContactData!K17)</f>
+        <v>benjaminwongici@livingrealtykw.com</v>
       </c>
       <c r="G18"/>
       <c r="H18"/>
@@ -9129,28 +9068,28 @@
     </row>
     <row r="19" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
-        <f>IF(LEN(ContactData!H19)&lt;3,"",ContactData!H19)</f>
-        <v>508</v>
+        <f>IF(LEN(ContactData!H18)&lt;3,"",ContactData!H18)</f>
+        <v>507</v>
       </c>
       <c r="B19" s="3" t="str">
-        <f>ContactData!E19</f>
-        <v>Maria Leung</v>
+        <f>ContactData!E18</f>
+        <v>Luvie Chao</v>
       </c>
       <c r="C19" s="3" t="str">
-        <f>ContactData!G19</f>
-        <v>Deal Administrator</v>
+        <f>ContactData!G18</f>
+        <v>Senior Deal Administrator</v>
       </c>
       <c r="D19" s="9" t="str">
-        <f>IF(LEN(ContactData!I19)&lt;3,"",ContactData!I19)</f>
+        <f>IF(LEN(ContactData!I18)&lt;3,"",ContactData!I18)</f>
         <v>---</v>
       </c>
       <c r="E19" s="3" t="str">
-        <f>ContactData!J19</f>
-        <v>(905) 752-3508</v>
+        <f>ContactData!J18</f>
+        <v>(905) 752-3507</v>
       </c>
       <c r="F19" s="3" t="str">
-        <f>IF(LEN(ContactData!K19)&lt;3,"",ContactData!K19)</f>
-        <v>marialeung@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K18)&lt;3,"",ContactData!K18)</f>
+        <v>luvie@livingrealtykw.com</v>
       </c>
       <c r="G19"/>
       <c r="H19"/>
@@ -9158,28 +9097,28 @@
     </row>
     <row r="20" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
-        <f>IF(LEN(ContactData!H20)&lt;3,"",ContactData!H20)</f>
-        <v>255</v>
+        <f>IF(LEN(ContactData!H19)&lt;3,"",ContactData!H19)</f>
+        <v>508</v>
       </c>
       <c r="B20" s="3" t="str">
-        <f>ContactData!E20</f>
-        <v>Ken Cheung</v>
+        <f>ContactData!E19</f>
+        <v>Maria Leung</v>
       </c>
       <c r="C20" s="3" t="str">
-        <f>ContactData!G20</f>
+        <f>ContactData!G19</f>
         <v>Deal Administrator</v>
       </c>
       <c r="D20" s="9" t="str">
-        <f>IF(LEN(ContactData!I20)&lt;3,"",ContactData!I20)</f>
+        <f>IF(LEN(ContactData!I19)&lt;3,"",ContactData!I19)</f>
         <v>---</v>
       </c>
       <c r="E20" s="3" t="str">
-        <f>ContactData!J20</f>
-        <v>---</v>
+        <f>ContactData!J19</f>
+        <v>(905) 752-3508</v>
       </c>
       <c r="F20" s="3" t="str">
-        <f>IF(LEN(ContactData!K20)&lt;3,"",ContactData!K20)</f>
-        <v>kencheung@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K19)&lt;3,"",ContactData!K19)</f>
+        <v>marialeung@livingrealtykw.com</v>
       </c>
       <c r="G20"/>
       <c r="H20"/>
@@ -9187,28 +9126,28 @@
     </row>
     <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
-        <f>IF(LEN(ContactData!H21)&lt;3,"",ContactData!H21)</f>
-        <v>506</v>
+        <f>IF(LEN(ContactData!H20)&lt;3,"",ContactData!H20)</f>
+        <v>255</v>
       </c>
       <c r="B21" s="3" t="str">
-        <f>ContactData!E21</f>
-        <v>Connie Cheung</v>
+        <f>ContactData!E20</f>
+        <v>Ken Cheung</v>
       </c>
       <c r="C21" s="3" t="str">
-        <f>ContactData!G21</f>
-        <v>Accounting Bookkeeper</v>
+        <f>ContactData!G20</f>
+        <v>Deal Administrator</v>
       </c>
       <c r="D21" s="9" t="str">
-        <f>IF(LEN(ContactData!I21)&lt;3,"",ContactData!I21)</f>
+        <f>IF(LEN(ContactData!I20)&lt;3,"",ContactData!I20)</f>
         <v>---</v>
       </c>
       <c r="E21" s="3" t="str">
-        <f>ContactData!J21</f>
-        <v>(905) 752-3506</v>
+        <f>ContactData!J20</f>
+        <v>---</v>
       </c>
       <c r="F21" s="3" t="str">
-        <f>IF(LEN(ContactData!K21)&lt;3,"",ContactData!K21)</f>
-        <v>conniecheung@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K20)&lt;3,"",ContactData!K20)</f>
+        <v>kencheung@livingrealtykw.com</v>
       </c>
       <c r="G21"/>
       <c r="H21"/>
@@ -9216,57 +9155,57 @@
     </row>
     <row r="22" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
-        <f>IF(LEN(ContactData!H22)&lt;3,"",ContactData!H22)</f>
-        <v>519</v>
+        <f>IF(LEN(ContactData!H21)&lt;3,"",ContactData!H21)</f>
+        <v>506</v>
       </c>
       <c r="B22" s="3" t="str">
-        <f>ContactData!E22</f>
-        <v>Simon Chan</v>
+        <f>ContactData!E21</f>
+        <v>Connie Cheung</v>
       </c>
       <c r="C22" s="3" t="str">
-        <f>ContactData!G22</f>
-        <v>Operations Assistant</v>
+        <f>ContactData!G21</f>
+        <v>Accounting Bookkeeper</v>
       </c>
       <c r="D22" s="9" t="str">
-        <f>IF(LEN(ContactData!I22)&lt;3,"",ContactData!I22)</f>
+        <f>IF(LEN(ContactData!I21)&lt;3,"",ContactData!I21)</f>
         <v>---</v>
       </c>
       <c r="E22" s="3" t="str">
-        <f>ContactData!J22</f>
-        <v>(905) 752-3519</v>
+        <f>ContactData!J21</f>
+        <v>(905) 752-3506</v>
       </c>
       <c r="F22" s="3" t="str">
-        <f>IF(LEN(ContactData!K22)&lt;3,"",ContactData!K22)</f>
-        <v>simonchan@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K21)&lt;3,"",ContactData!K21)</f>
+        <v>conniecheung@livingrealtykw.com</v>
       </c>
       <c r="G22"/>
       <c r="H22"/>
       <c r="I22"/>
     </row>
     <row r="23" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="e">
-        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B23" s="3" t="e">
-        <f>ContactData!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C23" s="3" t="e">
-        <f>ContactData!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D23" s="9" t="e">
-        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E23" s="3" t="e">
-        <f>ContactData!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F23" s="3" t="e">
-        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
-        <v>#REF!</v>
+      <c r="A23" s="9">
+        <f>IF(LEN(ContactData!H22)&lt;3,"",ContactData!H22)</f>
+        <v>519</v>
+      </c>
+      <c r="B23" s="3" t="str">
+        <f>ContactData!E22</f>
+        <v>Simon Chan</v>
+      </c>
+      <c r="C23" s="3" t="str">
+        <f>ContactData!G22</f>
+        <v>Operations Assistant</v>
+      </c>
+      <c r="D23" s="9" t="str">
+        <f>IF(LEN(ContactData!I22)&lt;3,"",ContactData!I22)</f>
+        <v>---</v>
+      </c>
+      <c r="E23" s="3" t="str">
+        <f>ContactData!J22</f>
+        <v>(905) 752-3519</v>
+      </c>
+      <c r="F23" s="3" t="str">
+        <f>IF(LEN(ContactData!K22)&lt;3,"",ContactData!K22)</f>
+        <v>simonchan@livingrealtykw.com</v>
       </c>
       <c r="G23"/>
       <c r="H23"/>
@@ -9534,29 +9473,29 @@
       <c r="I32"/>
     </row>
     <row r="33" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A33" s="9" t="e">
-        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B33" s="3" t="e">
-        <f>ContactData!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C33" s="3" t="e">
-        <f>ContactData!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D33" s="9" t="e">
-        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E33" s="3" t="e">
-        <f>ContactData!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F33" s="3" t="e">
-        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
-        <v>#REF!</v>
+      <c r="A33" s="9" t="str">
+        <f>IF(LEN(ContactData!H32)&lt;3,"",ContactData!H32)</f>
+        <v>---</v>
+      </c>
+      <c r="B33" s="3" t="str">
+        <f>ContactData!E32</f>
+        <v>Katie Wong</v>
+      </c>
+      <c r="C33" s="3" t="str">
+        <f>ContactData!G32</f>
+        <v>Secretary</v>
+      </c>
+      <c r="D33" s="9" t="str">
+        <f>IF(LEN(ContactData!I32)&lt;3,"",ContactData!I32)</f>
+        <v>---</v>
+      </c>
+      <c r="E33" s="3" t="str">
+        <f>ContactData!J32</f>
+        <v>(905) 896-0002</v>
+      </c>
+      <c r="F33" s="3" t="str">
+        <f>IF(LEN(ContactData!K32)&lt;3,"",ContactData!K32)</f>
+        <v>katiewong@livingrealtykw.com</v>
       </c>
       <c r="G33"/>
       <c r="H33"/>
@@ -9564,57 +9503,57 @@
     </row>
     <row r="34" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="str">
-        <f>IF(LEN(ContactData!H32)&lt;3,"",ContactData!H32)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!H33)&lt;3,"",ContactData!H33)</f>
+        <v/>
       </c>
       <c r="B34" s="3" t="str">
-        <f>ContactData!E32</f>
-        <v>Katie Wong</v>
+        <f>ContactData!E33</f>
+        <v>Woodbine Office</v>
       </c>
       <c r="C34" s="3" t="str">
-        <f>ContactData!G32</f>
-        <v>Secretary</v>
+        <f>ContactData!G33</f>
+        <v>8 Steelcase Road West, Markham, ON, L3R 1B2</v>
       </c>
       <c r="D34" s="9" t="str">
-        <f>IF(LEN(ContactData!I32)&lt;3,"",ContactData!I32)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!I33)&lt;3,"",ContactData!I33)</f>
+        <v/>
       </c>
       <c r="E34" s="3" t="str">
-        <f>ContactData!J32</f>
-        <v>(905) 896-0002</v>
+        <f>ContactData!J33</f>
+        <v>T: (905) 474-0500</v>
       </c>
       <c r="F34" s="3" t="str">
-        <f>IF(LEN(ContactData!K32)&lt;3,"",ContactData!K32)</f>
-        <v>katiewong@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K33)&lt;3,"",ContactData!K33)</f>
+        <v>woodbine@livingrealtykw.com</v>
       </c>
       <c r="G34"/>
       <c r="H34"/>
       <c r="I34"/>
     </row>
     <row r="35" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A35" s="9" t="str">
-        <f>IF(LEN(ContactData!H33)&lt;3,"",ContactData!H33)</f>
-        <v/>
+      <c r="A35" s="9">
+        <f>IF(LEN(ContactData!H34)&lt;3,"",ContactData!H34)</f>
+        <v>176</v>
       </c>
       <c r="B35" s="3" t="str">
-        <f>ContactData!E33</f>
-        <v>Woodbine Office</v>
+        <f>ContactData!E34</f>
+        <v>Anita Huang</v>
       </c>
       <c r="C35" s="3" t="str">
-        <f>ContactData!G33</f>
-        <v>8 Steelcase Road West, Markham, ON, L3R 1B2</v>
+        <f>ContactData!G34</f>
+        <v>Manager Woobine Branch</v>
       </c>
       <c r="D35" s="9" t="str">
-        <f>IF(LEN(ContactData!I33)&lt;3,"",ContactData!I33)</f>
-        <v/>
+        <f>IF(LEN(ContactData!I34)&lt;3,"",ContactData!I34)</f>
+        <v>(416) 523-1888</v>
       </c>
       <c r="E35" s="3" t="str">
-        <f>ContactData!J33</f>
-        <v>T: (905) 474-0500</v>
+        <f>ContactData!J34</f>
+        <v>---</v>
       </c>
       <c r="F35" s="3" t="str">
-        <f>IF(LEN(ContactData!K33)&lt;3,"",ContactData!K33)</f>
-        <v>woodbine@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K34)&lt;3,"",ContactData!K34)</f>
+        <v>anitahuang@livingrealtykw.com</v>
       </c>
       <c r="G35"/>
       <c r="H35"/>
@@ -9622,28 +9561,28 @@
     </row>
     <row r="36" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
-        <f>IF(LEN(ContactData!H34)&lt;3,"",ContactData!H34)</f>
-        <v>176</v>
+        <f>IF(LEN(ContactData!H35)&lt;3,"",ContactData!H35)</f>
+        <v>104</v>
       </c>
       <c r="B36" s="3" t="str">
-        <f>ContactData!E34</f>
-        <v>Anita Huang</v>
+        <f>ContactData!E35</f>
+        <v>Kim Jin</v>
       </c>
       <c r="C36" s="3" t="str">
-        <f>ContactData!G34</f>
-        <v>Manager Woobine Branch</v>
+        <f>ContactData!G35</f>
+        <v>Secretary</v>
       </c>
       <c r="D36" s="9" t="str">
-        <f>IF(LEN(ContactData!I34)&lt;3,"",ContactData!I34)</f>
-        <v>(416) 523-1888</v>
+        <f>IF(LEN(ContactData!I35)&lt;3,"",ContactData!I35)</f>
+        <v>---</v>
       </c>
       <c r="E36" s="3" t="str">
-        <f>ContactData!J34</f>
-        <v>---</v>
+        <f>ContactData!J35</f>
+        <v>(905) 474-0500</v>
       </c>
       <c r="F36" s="3" t="str">
-        <f>IF(LEN(ContactData!K34)&lt;3,"",ContactData!K34)</f>
-        <v>anitahuang@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K35)&lt;3,"",ContactData!K35)</f>
+        <v>kimjin@livingrealtykw.com</v>
       </c>
       <c r="G36"/>
       <c r="H36"/>
@@ -9651,57 +9590,57 @@
     </row>
     <row r="37" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
-        <f>IF(LEN(ContactData!H35)&lt;3,"",ContactData!H35)</f>
-        <v>104</v>
+        <f>IF(LEN(ContactData!H36)&lt;3,"",ContactData!H36)</f>
+        <v>100</v>
       </c>
       <c r="B37" s="3" t="str">
-        <f>ContactData!E35</f>
-        <v>Kim Jin</v>
+        <f>ContactData!E36</f>
+        <v>Savanna Joo</v>
       </c>
       <c r="C37" s="3" t="str">
-        <f>ContactData!G35</f>
+        <f>ContactData!G36</f>
         <v>Secretary</v>
       </c>
       <c r="D37" s="9" t="str">
-        <f>IF(LEN(ContactData!I35)&lt;3,"",ContactData!I35)</f>
+        <f>IF(LEN(ContactData!I36)&lt;3,"",ContactData!I36)</f>
         <v>---</v>
       </c>
       <c r="E37" s="3" t="str">
-        <f>ContactData!J35</f>
+        <f>ContactData!J36</f>
         <v>(905) 474-0500</v>
       </c>
       <c r="F37" s="3" t="str">
-        <f>IF(LEN(ContactData!K35)&lt;3,"",ContactData!K35)</f>
-        <v>kimjin@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K36)&lt;3,"",ContactData!K36)</f>
+        <v>savannajoo@livingrealtykw.com</v>
       </c>
       <c r="G37"/>
       <c r="H37"/>
       <c r="I37"/>
     </row>
     <row r="38" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A38" s="9">
-        <f>IF(LEN(ContactData!H36)&lt;3,"",ContactData!H36)</f>
-        <v>100</v>
+      <c r="A38" s="9" t="str">
+        <f>IF(LEN(ContactData!H37)&lt;3,"",ContactData!H37)</f>
+        <v/>
       </c>
       <c r="B38" s="3" t="str">
-        <f>ContactData!E36</f>
-        <v>Savanna Joo</v>
+        <f>ContactData!E37</f>
+        <v>Yonge &amp; Eglinton Office</v>
       </c>
       <c r="C38" s="3" t="str">
-        <f>ContactData!G36</f>
-        <v>Secretary</v>
+        <f>ContactData!G37</f>
+        <v>2301 Yonge Street, Toronto, ON, M4P 2C6</v>
       </c>
       <c r="D38" s="9" t="str">
-        <f>IF(LEN(ContactData!I36)&lt;3,"",ContactData!I36)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!I37)&lt;3,"",ContactData!I37)</f>
+        <v/>
       </c>
       <c r="E38" s="3" t="str">
-        <f>ContactData!J36</f>
-        <v>(905) 474-0500</v>
+        <f>ContactData!J37</f>
+        <v>T: (416) 223-8833</v>
       </c>
       <c r="F38" s="3" t="str">
-        <f>IF(LEN(ContactData!K36)&lt;3,"",ContactData!K36)</f>
-        <v>savannajoo@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K37)&lt;3,"",ContactData!K37)</f>
+        <v>ye@livingrealtykw.com</v>
       </c>
       <c r="G38"/>
       <c r="H38"/>
@@ -9709,28 +9648,28 @@
     </row>
     <row r="39" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="str">
-        <f>IF(LEN(ContactData!H37)&lt;3,"",ContactData!H37)</f>
-        <v/>
+        <f>IF(LEN(ContactData!H38)&lt;3,"",ContactData!H38)</f>
+        <v>---</v>
       </c>
       <c r="B39" s="3" t="str">
-        <f>ContactData!E37</f>
-        <v>Yonge &amp; Eglinton Office</v>
+        <f>ContactData!E38</f>
+        <v xml:space="preserve">Tony Prochilo </v>
       </c>
       <c r="C39" s="3" t="str">
-        <f>ContactData!G37</f>
-        <v>2301 Yonge Street, Toronto, ON, M4P 2C6</v>
+        <f>ContactData!G38</f>
+        <v>Manager Yonge &amp; Eglinton</v>
       </c>
       <c r="D39" s="9" t="str">
-        <f>IF(LEN(ContactData!I37)&lt;3,"",ContactData!I37)</f>
-        <v/>
+        <f>IF(LEN(ContactData!I38)&lt;3,"",ContactData!I38)</f>
+        <v>(416) 576-6312</v>
       </c>
       <c r="E39" s="3" t="str">
-        <f>ContactData!J37</f>
-        <v>T: (416) 223-8833</v>
+        <f>ContactData!J38</f>
+        <v>---</v>
       </c>
       <c r="F39" s="3" t="str">
-        <f>IF(LEN(ContactData!K37)&lt;3,"",ContactData!K37)</f>
-        <v>ye@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K38)&lt;3,"",ContactData!K38)</f>
+        <v>tonyprochilo@livingrealtykw.com</v>
       </c>
       <c r="G39"/>
       <c r="H39"/>
@@ -9738,28 +9677,28 @@
     </row>
     <row r="40" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="str">
-        <f>IF(LEN(ContactData!H38)&lt;3,"",ContactData!H38)</f>
+        <f>IF(LEN(ContactData!H39)&lt;3,"",ContactData!H39)</f>
         <v>---</v>
       </c>
       <c r="B40" s="3" t="str">
-        <f>ContactData!E38</f>
-        <v xml:space="preserve">Tony Prochilo </v>
+        <f>ContactData!E39</f>
+        <v>Lydia Ng</v>
       </c>
       <c r="C40" s="3" t="str">
-        <f>ContactData!G38</f>
-        <v>Manager Yonge &amp; Eglinton</v>
+        <f>ContactData!G39</f>
+        <v>Secretary</v>
       </c>
       <c r="D40" s="9" t="str">
-        <f>IF(LEN(ContactData!I38)&lt;3,"",ContactData!I38)</f>
-        <v>(416) 576-6312</v>
+        <f>IF(LEN(ContactData!I39)&lt;3,"",ContactData!I39)</f>
+        <v>---</v>
       </c>
       <c r="E40" s="3" t="str">
-        <f>ContactData!J38</f>
-        <v>---</v>
+        <f>ContactData!J39</f>
+        <v>(416) 223-8833</v>
       </c>
       <c r="F40" s="3" t="str">
-        <f>IF(LEN(ContactData!K38)&lt;3,"",ContactData!K38)</f>
-        <v>tonyprochilo@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K39)&lt;3,"",ContactData!K39)</f>
+        <v>lydiang@livingrealtykw.com</v>
       </c>
       <c r="G40"/>
       <c r="H40"/>
@@ -9767,115 +9706,115 @@
     </row>
     <row r="41" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="str">
-        <f>IF(LEN(ContactData!H39)&lt;3,"",ContactData!H39)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!H40)&lt;3,"",ContactData!H40)</f>
+        <v/>
       </c>
       <c r="B41" s="3" t="str">
-        <f>ContactData!E39</f>
-        <v>Lydia Ng</v>
+        <f>ContactData!E40</f>
+        <v>I.C.&amp;I. Office</v>
       </c>
       <c r="C41" s="3" t="str">
-        <f>ContactData!G39</f>
-        <v>Secretary</v>
+        <f>ContactData!G40</f>
+        <v>8 Steelcase Road West, Unit C, Markham, ON, L3R 1B2</v>
       </c>
       <c r="D41" s="9" t="str">
-        <f>IF(LEN(ContactData!I39)&lt;3,"",ContactData!I39)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!I40)&lt;3,"",ContactData!I40)</f>
+        <v/>
       </c>
       <c r="E41" s="3" t="str">
-        <f>ContactData!J39</f>
-        <v>(416) 223-8833</v>
+        <f>ContactData!J40</f>
+        <v>T: (905) 474-1772</v>
       </c>
       <c r="F41" s="3" t="str">
-        <f>IF(LEN(ContactData!K39)&lt;3,"",ContactData!K39)</f>
-        <v>lydiang@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K40)&lt;3,"",ContactData!K40)</f>
+        <v/>
       </c>
       <c r="G41"/>
       <c r="H41"/>
       <c r="I41"/>
     </row>
     <row r="42" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A42" s="9" t="str">
-        <f>IF(LEN(ContactData!H40)&lt;3,"",ContactData!H40)</f>
-        <v/>
+      <c r="A42" s="9">
+        <f>IF(LEN(ContactData!H41)&lt;3,"",ContactData!H41)</f>
+        <v>228</v>
       </c>
       <c r="B42" s="3" t="str">
-        <f>ContactData!E40</f>
-        <v>I.C.&amp;I. Office</v>
+        <f>ContactData!E41</f>
+        <v>Kelvin Wong</v>
       </c>
       <c r="C42" s="3" t="str">
-        <f>ContactData!G40</f>
-        <v>8 Steelcase Road West, Unit C, Markham, ON, L3R 1B2</v>
+        <f>ContactData!G41</f>
+        <v>Manager I.C.&amp;I. Branch</v>
       </c>
       <c r="D42" s="9" t="str">
-        <f>IF(LEN(ContactData!I40)&lt;3,"",ContactData!I40)</f>
-        <v/>
+        <f>IF(LEN(ContactData!I41)&lt;3,"",ContactData!I41)</f>
+        <v>(416) 567-7882</v>
       </c>
       <c r="E42" s="3" t="str">
-        <f>ContactData!J40</f>
-        <v>T: (905) 474-1772</v>
+        <f>ContactData!J41</f>
+        <v>---</v>
       </c>
       <c r="F42" s="3" t="str">
-        <f>IF(LEN(ContactData!K40)&lt;3,"",ContactData!K40)</f>
-        <v/>
+        <f>IF(LEN(ContactData!K41)&lt;3,"",ContactData!K41)</f>
+        <v>kelvin@livingrealtykw.com</v>
       </c>
       <c r="G42"/>
       <c r="H42"/>
       <c r="I42"/>
     </row>
     <row r="43" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A43" s="9">
-        <f>IF(LEN(ContactData!H41)&lt;3,"",ContactData!H41)</f>
-        <v>228</v>
+      <c r="A43" s="9" t="str">
+        <f>IF(LEN(ContactData!H42)&lt;3,"",ContactData!H42)</f>
+        <v/>
       </c>
       <c r="B43" s="3" t="str">
-        <f>ContactData!E41</f>
-        <v>Kelvin Wong</v>
+        <f>ContactData!E42</f>
+        <v>LPI Head Office</v>
       </c>
       <c r="C43" s="3" t="str">
-        <f>ContactData!G41</f>
-        <v>Manager I.C.&amp;I. Branch</v>
+        <f>ContactData!G42</f>
+        <v>8 Steelcase Road West, Markham, ON, L3R 1B2</v>
       </c>
       <c r="D43" s="9" t="str">
-        <f>IF(LEN(ContactData!I41)&lt;3,"",ContactData!I41)</f>
-        <v>(416) 567-7882</v>
+        <f>IF(LEN(ContactData!I42)&lt;3,"",ContactData!I42)</f>
+        <v/>
       </c>
       <c r="E43" s="3" t="str">
-        <f>ContactData!J41</f>
-        <v>---</v>
+        <f>ContactData!J42</f>
+        <v>T: (905) 477-2090</v>
       </c>
       <c r="F43" s="3" t="str">
-        <f>IF(LEN(ContactData!K41)&lt;3,"",ContactData!K41)</f>
-        <v>kelvin@livingrealtykw.com</v>
+        <f>IF(LEN(ContactData!K42)&lt;3,"",ContactData!K42)</f>
+        <v/>
       </c>
       <c r="G43"/>
       <c r="H43"/>
       <c r="I43"/>
     </row>
     <row r="44" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A44" s="9" t="str">
-        <f>IF(LEN(ContactData!H42)&lt;3,"",ContactData!H42)</f>
-        <v/>
+      <c r="A44" s="9">
+        <f>IF(LEN(ContactData!H43)&lt;3,"",ContactData!H43)</f>
+        <v>521</v>
       </c>
       <c r="B44" s="3" t="str">
-        <f>ContactData!E42</f>
-        <v>LPI Head Office</v>
+        <f>ContactData!E43</f>
+        <v>Ben Wong</v>
       </c>
       <c r="C44" s="3" t="str">
-        <f>ContactData!G42</f>
-        <v>8 Steelcase Road West, Markham, ON, L3R 1B2</v>
+        <f>ContactData!G43</f>
+        <v>President</v>
       </c>
       <c r="D44" s="9" t="str">
-        <f>IF(LEN(ContactData!I42)&lt;3,"",ContactData!I42)</f>
-        <v/>
+        <f>IF(LEN(ContactData!I43)&lt;3,"",ContactData!I43)</f>
+        <v>(416) 399-2311</v>
       </c>
       <c r="E44" s="3" t="str">
-        <f>ContactData!J42</f>
-        <v>T: (905) 477-2090</v>
+        <f>ContactData!J43</f>
+        <v>(905) 752-3521</v>
       </c>
       <c r="F44" s="3" t="str">
-        <f>IF(LEN(ContactData!K42)&lt;3,"",ContactData!K42)</f>
-        <v/>
+        <f>IF(LEN(ContactData!K43)&lt;3,"",ContactData!K43)</f>
+        <v>benw@livingproperties.com</v>
       </c>
       <c r="G44"/>
       <c r="H44"/>
@@ -9883,28 +9822,28 @@
     </row>
     <row r="45" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A45" s="9">
-        <f>IF(LEN(ContactData!H43)&lt;3,"",ContactData!H43)</f>
-        <v>521</v>
+        <f>IF(LEN(ContactData!H44)&lt;3,"",ContactData!H44)</f>
+        <v>514</v>
       </c>
       <c r="B45" s="3" t="str">
-        <f>ContactData!E43</f>
-        <v>Ben Wong</v>
+        <f>ContactData!E44</f>
+        <v>Winnie Tsui</v>
       </c>
       <c r="C45" s="3" t="str">
-        <f>ContactData!G43</f>
-        <v>President</v>
+        <f>ContactData!G44</f>
+        <v>Director of Operations</v>
       </c>
       <c r="D45" s="9" t="str">
-        <f>IF(LEN(ContactData!I43)&lt;3,"",ContactData!I43)</f>
-        <v>(416) 399-2311</v>
+        <f>IF(LEN(ContactData!I44)&lt;3,"",ContactData!I44)</f>
+        <v>(647) 286-0145</v>
       </c>
       <c r="E45" s="3" t="str">
-        <f>ContactData!J43</f>
-        <v>(905) 752-3521</v>
+        <f>ContactData!J44</f>
+        <v xml:space="preserve">(905) 752-3514 </v>
       </c>
       <c r="F45" s="3" t="str">
-        <f>IF(LEN(ContactData!K43)&lt;3,"",ContactData!K43)</f>
-        <v>benw@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K44)&lt;3,"",ContactData!K44)</f>
+        <v>winniet@livingproperties.com</v>
       </c>
       <c r="G45"/>
       <c r="H45"/>
@@ -9912,28 +9851,28 @@
     </row>
     <row r="46" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A46" s="9">
-        <f>IF(LEN(ContactData!H44)&lt;3,"",ContactData!H44)</f>
-        <v>514</v>
+        <f>IF(LEN(ContactData!H45)&lt;3,"",ContactData!H45)</f>
+        <v>286</v>
       </c>
       <c r="B46" s="3" t="str">
-        <f>ContactData!E44</f>
-        <v>Winnie Tsui</v>
+        <f>ContactData!E45</f>
+        <v>Frederick Tang</v>
       </c>
       <c r="C46" s="3" t="str">
-        <f>ContactData!G44</f>
-        <v>Director of Operations</v>
+        <f>ContactData!G45</f>
+        <v>Director of Business Development</v>
       </c>
       <c r="D46" s="9" t="str">
-        <f>IF(LEN(ContactData!I44)&lt;3,"",ContactData!I44)</f>
-        <v>(647) 286-0145</v>
+        <f>IF(LEN(ContactData!I45)&lt;3,"",ContactData!I45)</f>
+        <v>(416) 618-5898</v>
       </c>
       <c r="E46" s="3" t="str">
-        <f>ContactData!J44</f>
-        <v xml:space="preserve">(905) 752-3514 </v>
+        <f>ContactData!J45</f>
+        <v>-</v>
       </c>
       <c r="F46" s="3" t="str">
-        <f>IF(LEN(ContactData!K44)&lt;3,"",ContactData!K44)</f>
-        <v>winniet@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K45)&lt;3,"",ContactData!K45)</f>
+        <v>fredt@livingproperties.com</v>
       </c>
       <c r="G46"/>
       <c r="H46"/>
@@ -9941,57 +9880,57 @@
     </row>
     <row r="47" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
-        <f>IF(LEN(ContactData!H45)&lt;3,"",ContactData!H45)</f>
-        <v>286</v>
+        <f>IF(LEN(ContactData!H46)&lt;3,"",ContactData!H46)</f>
+        <v>512</v>
       </c>
       <c r="B47" s="3" t="str">
-        <f>ContactData!E45</f>
-        <v>Frederick Tang</v>
+        <f>ContactData!E46</f>
+        <v>Stanley Chow</v>
       </c>
       <c r="C47" s="3" t="str">
-        <f>ContactData!G45</f>
-        <v>Director of Business Development</v>
+        <f>ContactData!G46</f>
+        <v>Property Manager</v>
       </c>
       <c r="D47" s="9" t="str">
-        <f>IF(LEN(ContactData!I45)&lt;3,"",ContactData!I45)</f>
-        <v>(416) 618-5898</v>
+        <f>IF(LEN(ContactData!I46)&lt;3,"",ContactData!I46)</f>
+        <v>(416) 277-6098</v>
       </c>
       <c r="E47" s="3" t="str">
-        <f>ContactData!J45</f>
-        <v>-</v>
+        <f>ContactData!J46</f>
+        <v>(905) 752-3512</v>
       </c>
       <c r="F47" s="3" t="str">
-        <f>IF(LEN(ContactData!K45)&lt;3,"",ContactData!K45)</f>
-        <v>fredt@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K46)&lt;3,"",ContactData!K46)</f>
+        <v>stanleyc@livingproperties.com</v>
       </c>
       <c r="G47"/>
       <c r="H47"/>
       <c r="I47"/>
     </row>
     <row r="48" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A48" s="9" t="e">
-        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="B48" s="3" t="e">
-        <f>ContactData!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C48" s="3" t="e">
-        <f>ContactData!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="D48" s="9" t="e">
-        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E48" s="3" t="e">
-        <f>ContactData!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="F48" s="3" t="e">
-        <f>IF(LEN(ContactData!#REF!)&lt;3,"",ContactData!#REF!)</f>
-        <v>#REF!</v>
+      <c r="A48" s="9">
+        <f>IF(LEN(ContactData!H47)&lt;3,"",ContactData!H47)</f>
+        <v>284</v>
+      </c>
+      <c r="B48" s="3" t="str">
+        <f>ContactData!E47</f>
+        <v>Richard Baksh</v>
+      </c>
+      <c r="C48" s="3" t="str">
+        <f>ContactData!G47</f>
+        <v>Property Manager</v>
+      </c>
+      <c r="D48" s="9" t="str">
+        <f>IF(LEN(ContactData!I47)&lt;3,"",ContactData!I47)</f>
+        <v>(647) 967-0088</v>
+      </c>
+      <c r="E48" s="3" t="str">
+        <f>ContactData!J47</f>
+        <v>(905) 258-0632</v>
+      </c>
+      <c r="F48" s="3" t="str">
+        <f>IF(LEN(ContactData!K47)&lt;3,"",ContactData!K47)</f>
+        <v>richardb@livingproperties.com</v>
       </c>
       <c r="G48"/>
       <c r="H48"/>
@@ -9999,28 +9938,28 @@
     </row>
     <row r="49" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
-        <f>IF(LEN(ContactData!H46)&lt;3,"",ContactData!H46)</f>
-        <v>512</v>
+        <f>IF(LEN(ContactData!H48)&lt;3,"",ContactData!H48)</f>
+        <v>517</v>
       </c>
       <c r="B49" s="3" t="str">
-        <f>ContactData!E46</f>
-        <v>Stanley Chow</v>
+        <f>ContactData!E48</f>
+        <v>Ken Kam</v>
       </c>
       <c r="C49" s="3" t="str">
-        <f>ContactData!G46</f>
+        <f>ContactData!G48</f>
         <v>Property Manager</v>
       </c>
       <c r="D49" s="9" t="str">
-        <f>IF(LEN(ContactData!I46)&lt;3,"",ContactData!I46)</f>
-        <v>(416) 277-6098</v>
+        <f>IF(LEN(ContactData!I48)&lt;3,"",ContactData!I48)</f>
+        <v>(647) 204-4455</v>
       </c>
       <c r="E49" s="3" t="str">
-        <f>ContactData!J46</f>
-        <v>(905) 752-3512</v>
+        <f>ContactData!J48</f>
+        <v>(905) 477-2090</v>
       </c>
       <c r="F49" s="3" t="str">
-        <f>IF(LEN(ContactData!K46)&lt;3,"",ContactData!K46)</f>
-        <v>stanleyc@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K48)&lt;3,"",ContactData!K48)</f>
+        <v>kenk@livingproperties.com</v>
       </c>
       <c r="G49"/>
       <c r="H49"/>
@@ -10028,28 +9967,28 @@
     </row>
     <row r="50" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A50" s="9">
-        <f>IF(LEN(ContactData!H47)&lt;3,"",ContactData!H47)</f>
-        <v>284</v>
+        <f>IF(LEN(ContactData!H49)&lt;3,"",ContactData!H49)</f>
+        <v>520</v>
       </c>
       <c r="B50" s="3" t="str">
-        <f>ContactData!E47</f>
-        <v>Richard Baksh</v>
+        <f>ContactData!E49</f>
+        <v>Raymond Chin</v>
       </c>
       <c r="C50" s="3" t="str">
-        <f>ContactData!G47</f>
+        <f>ContactData!G49</f>
         <v>Property Manager</v>
       </c>
       <c r="D50" s="9" t="str">
-        <f>IF(LEN(ContactData!I47)&lt;3,"",ContactData!I47)</f>
-        <v>(647) 967-0088</v>
+        <f>IF(LEN(ContactData!I49)&lt;3,"",ContactData!I49)</f>
+        <v>(437) 331-6038</v>
       </c>
       <c r="E50" s="3" t="str">
-        <f>ContactData!J47</f>
-        <v>(905) 258-0632</v>
+        <f>ContactData!J49</f>
+        <v>(905) 477-2090</v>
       </c>
       <c r="F50" s="3" t="str">
-        <f>IF(LEN(ContactData!K47)&lt;3,"",ContactData!K47)</f>
-        <v>richardb@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K49)&lt;3,"",ContactData!K49)</f>
+        <v>raymondc@livingproperties.com</v>
       </c>
       <c r="G50"/>
       <c r="H50"/>
@@ -10057,28 +9996,28 @@
     </row>
     <row r="51" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
-        <f>IF(LEN(ContactData!H48)&lt;3,"",ContactData!H48)</f>
-        <v>517</v>
+        <f>IF(LEN(ContactData!H50)&lt;3,"",ContactData!H50)</f>
+        <v>168</v>
       </c>
       <c r="B51" s="3" t="str">
-        <f>ContactData!E48</f>
-        <v>Ken Kam</v>
+        <f>ContactData!E50</f>
+        <v>Thomas Lee</v>
       </c>
       <c r="C51" s="3" t="str">
-        <f>ContactData!G48</f>
-        <v>Property Manager</v>
+        <f>ContactData!G50</f>
+        <v>Assistant Property Manager</v>
       </c>
       <c r="D51" s="9" t="str">
-        <f>IF(LEN(ContactData!I48)&lt;3,"",ContactData!I48)</f>
-        <v>(647) 204-4455</v>
+        <f>IF(LEN(ContactData!I50)&lt;3,"",ContactData!I50)</f>
+        <v>(416) 567-4274</v>
       </c>
       <c r="E51" s="3" t="str">
-        <f>ContactData!J48</f>
+        <f>ContactData!J50</f>
         <v>(905) 477-2090</v>
       </c>
       <c r="F51" s="3" t="str">
-        <f>IF(LEN(ContactData!K48)&lt;3,"",ContactData!K48)</f>
-        <v>kenk@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K50)&lt;3,"",ContactData!K50)</f>
+        <v>Thomasl@livingproperties.com</v>
       </c>
       <c r="G51"/>
       <c r="H51"/>
@@ -10086,28 +10025,28 @@
     </row>
     <row r="52" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
-        <f>IF(LEN(ContactData!H49)&lt;3,"",ContactData!H49)</f>
-        <v>520</v>
+        <f>IF(LEN(ContactData!H51)&lt;3,"",ContactData!H51)</f>
+        <v>210</v>
       </c>
       <c r="B52" s="3" t="str">
-        <f>ContactData!E49</f>
-        <v>Raymond Chin</v>
+        <f>ContactData!E51</f>
+        <v>Loretta Leung</v>
       </c>
       <c r="C52" s="3" t="str">
-        <f>ContactData!G49</f>
-        <v>Property Manager</v>
+        <f>ContactData!G51</f>
+        <v>Executive Assistant</v>
       </c>
       <c r="D52" s="9" t="str">
-        <f>IF(LEN(ContactData!I49)&lt;3,"",ContactData!I49)</f>
-        <v>(437) 331-6038</v>
+        <f>IF(LEN(ContactData!I51)&lt;3,"",ContactData!I51)</f>
+        <v>---</v>
       </c>
       <c r="E52" s="3" t="str">
-        <f>ContactData!J49</f>
-        <v>(905) 477-2090</v>
+        <f>ContactData!J51</f>
+        <v>---</v>
       </c>
       <c r="F52" s="3" t="str">
-        <f>IF(LEN(ContactData!K49)&lt;3,"",ContactData!K49)</f>
-        <v>raymondc@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K51)&lt;3,"",ContactData!K51)</f>
+        <v>lorettal@livingproperties.com</v>
       </c>
       <c r="G52"/>
       <c r="H52"/>
@@ -10115,28 +10054,28 @@
     </row>
     <row r="53" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
-        <f>IF(LEN(ContactData!H50)&lt;3,"",ContactData!H50)</f>
-        <v>168</v>
+        <f>IF(LEN(ContactData!H52)&lt;3,"",ContactData!H52)</f>
+        <v>518</v>
       </c>
       <c r="B53" s="3" t="str">
-        <f>ContactData!E50</f>
-        <v>Thomas Lee</v>
+        <f>ContactData!E52</f>
+        <v>Simon Li</v>
       </c>
       <c r="C53" s="3" t="str">
-        <f>ContactData!G50</f>
-        <v>Assistant Property Manager</v>
+        <f>ContactData!G52</f>
+        <v>Senior Accountant</v>
       </c>
       <c r="D53" s="9" t="str">
-        <f>IF(LEN(ContactData!I50)&lt;3,"",ContactData!I50)</f>
-        <v>(416) 567-4274</v>
+        <f>IF(LEN(ContactData!I52)&lt;3,"",ContactData!I52)</f>
+        <v>---</v>
       </c>
       <c r="E53" s="3" t="str">
-        <f>ContactData!J50</f>
-        <v>(905) 477-2090</v>
+        <f>ContactData!J52</f>
+        <v>(905) 752-3518</v>
       </c>
       <c r="F53" s="3" t="str">
-        <f>IF(LEN(ContactData!K50)&lt;3,"",ContactData!K50)</f>
-        <v>Thomasl@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K52)&lt;3,"",ContactData!K52)</f>
+        <v>simonl@livingproperties.com</v>
       </c>
       <c r="G53"/>
       <c r="H53"/>
@@ -10144,28 +10083,28 @@
     </row>
     <row r="54" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
-        <f>IF(LEN(ContactData!H51)&lt;3,"",ContactData!H51)</f>
-        <v>210</v>
+        <f>IF(LEN(ContactData!H53)&lt;3,"",ContactData!H53)</f>
+        <v>281</v>
       </c>
       <c r="B54" s="3" t="str">
-        <f>ContactData!E51</f>
-        <v>Loretta Leung</v>
+        <f>ContactData!E53</f>
+        <v>Nicole Leung</v>
       </c>
       <c r="C54" s="3" t="str">
-        <f>ContactData!G51</f>
-        <v>Executive Assistant</v>
+        <f>ContactData!G53</f>
+        <v>Property Accountant</v>
       </c>
       <c r="D54" s="9" t="str">
-        <f>IF(LEN(ContactData!I51)&lt;3,"",ContactData!I51)</f>
+        <f>IF(LEN(ContactData!I53)&lt;3,"",ContactData!I53)</f>
         <v>---</v>
       </c>
       <c r="E54" s="3" t="str">
-        <f>ContactData!J51</f>
+        <f>ContactData!J53</f>
         <v>---</v>
       </c>
       <c r="F54" s="3" t="str">
-        <f>IF(LEN(ContactData!K51)&lt;3,"",ContactData!K51)</f>
-        <v>lorettal@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K53)&lt;3,"",ContactData!K53)</f>
+        <v>nicolel@livingproperties.com</v>
       </c>
       <c r="G54"/>
       <c r="H54"/>
@@ -10173,28 +10112,28 @@
     </row>
     <row r="55" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
-        <f>IF(LEN(ContactData!H52)&lt;3,"",ContactData!H52)</f>
-        <v>518</v>
+        <f>IF(LEN(ContactData!H54)&lt;3,"",ContactData!H54)</f>
+        <v>523</v>
       </c>
       <c r="B55" s="3" t="str">
-        <f>ContactData!E52</f>
-        <v>Simon Li</v>
+        <f>ContactData!E54</f>
+        <v>Vivian Lum</v>
       </c>
       <c r="C55" s="3" t="str">
-        <f>ContactData!G52</f>
-        <v>Senior Accountant</v>
+        <f>ContactData!G54</f>
+        <v>Accounts Receivable Clerk</v>
       </c>
       <c r="D55" s="9" t="str">
-        <f>IF(LEN(ContactData!I52)&lt;3,"",ContactData!I52)</f>
+        <f>IF(LEN(ContactData!I54)&lt;3,"",ContactData!I54)</f>
         <v>---</v>
       </c>
       <c r="E55" s="3" t="str">
-        <f>ContactData!J52</f>
-        <v>(905) 752-3518</v>
+        <f>ContactData!J54</f>
+        <v>(905) 752-3523</v>
       </c>
       <c r="F55" s="3" t="str">
-        <f>IF(LEN(ContactData!K52)&lt;3,"",ContactData!K52)</f>
-        <v>simonl@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K54)&lt;3,"",ContactData!K54)</f>
+        <v>vivianl@livingproperties.com</v>
       </c>
       <c r="G55"/>
       <c r="H55"/>
@@ -10202,28 +10141,28 @@
     </row>
     <row r="56" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
-        <f>IF(LEN(ContactData!H53)&lt;3,"",ContactData!H53)</f>
-        <v>281</v>
+        <f>IF(LEN(ContactData!H55)&lt;3,"",ContactData!H55)</f>
+        <v>223</v>
       </c>
       <c r="B56" s="3" t="str">
-        <f>ContactData!E53</f>
-        <v>Nicole Leung</v>
+        <f>ContactData!E55</f>
+        <v>Jessica Lee</v>
       </c>
       <c r="C56" s="3" t="str">
-        <f>ContactData!G53</f>
-        <v>Property Accountant</v>
+        <f>ContactData!G55</f>
+        <v xml:space="preserve">Accounting Clerk </v>
       </c>
       <c r="D56" s="9" t="str">
-        <f>IF(LEN(ContactData!I53)&lt;3,"",ContactData!I53)</f>
+        <f>IF(LEN(ContactData!I55)&lt;3,"",ContactData!I55)</f>
         <v>---</v>
       </c>
       <c r="E56" s="3" t="str">
-        <f>ContactData!J53</f>
+        <f>ContactData!J55</f>
         <v>---</v>
       </c>
       <c r="F56" s="3" t="str">
-        <f>IF(LEN(ContactData!K53)&lt;3,"",ContactData!K53)</f>
-        <v>nicolel@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K55)&lt;3,"",ContactData!K55)</f>
+        <v>jessical@livingproperties.com</v>
       </c>
       <c r="G56"/>
       <c r="H56"/>
@@ -10231,28 +10170,28 @@
     </row>
     <row r="57" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
-        <f>IF(LEN(ContactData!H54)&lt;3,"",ContactData!H54)</f>
-        <v>523</v>
+        <f>IF(LEN(ContactData!H56)&lt;3,"",ContactData!H56)</f>
+        <v>172</v>
       </c>
       <c r="B57" s="3" t="str">
-        <f>ContactData!E54</f>
-        <v>Vivian Lum</v>
+        <f>ContactData!E56</f>
+        <v>Rebecca Lau</v>
       </c>
       <c r="C57" s="3" t="str">
-        <f>ContactData!G54</f>
-        <v>Accounts Receivable Clerk</v>
+        <f>ContactData!G56</f>
+        <v>Administrative Assistant</v>
       </c>
       <c r="D57" s="9" t="str">
-        <f>IF(LEN(ContactData!I54)&lt;3,"",ContactData!I54)</f>
+        <f>IF(LEN(ContactData!I56)&lt;3,"",ContactData!I56)</f>
         <v>---</v>
       </c>
       <c r="E57" s="3" t="str">
-        <f>ContactData!J54</f>
-        <v>(905) 752-3523</v>
+        <f>ContactData!J56</f>
+        <v>---</v>
       </c>
       <c r="F57" s="3" t="str">
-        <f>IF(LEN(ContactData!K54)&lt;3,"",ContactData!K54)</f>
-        <v>vivianl@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K56)&lt;3,"",ContactData!K56)</f>
+        <v>rebeccal@livingproperties.com</v>
       </c>
       <c r="G57"/>
       <c r="H57"/>
@@ -10260,57 +10199,57 @@
     </row>
     <row r="58" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
-        <f>IF(LEN(ContactData!H55)&lt;3,"",ContactData!H55)</f>
-        <v>223</v>
+        <f>IF(LEN(ContactData!H57)&lt;3,"",ContactData!H57)</f>
+        <v>182</v>
       </c>
       <c r="B58" s="3" t="str">
-        <f>ContactData!E55</f>
-        <v>Jessica Lee</v>
+        <f>ContactData!E57</f>
+        <v>Kelvin Chan</v>
       </c>
       <c r="C58" s="3" t="str">
-        <f>ContactData!G55</f>
-        <v xml:space="preserve">Accounting Clerk </v>
+        <f>ContactData!G57</f>
+        <v>Administrative Assistant</v>
       </c>
       <c r="D58" s="9" t="str">
-        <f>IF(LEN(ContactData!I55)&lt;3,"",ContactData!I55)</f>
+        <f>IF(LEN(ContactData!I57)&lt;3,"",ContactData!I57)</f>
         <v>---</v>
       </c>
       <c r="E58" s="3" t="str">
-        <f>ContactData!J55</f>
+        <f>ContactData!J57</f>
         <v>---</v>
       </c>
       <c r="F58" s="3" t="str">
-        <f>IF(LEN(ContactData!K55)&lt;3,"",ContactData!K55)</f>
-        <v>jessical@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K57)&lt;3,"",ContactData!K57)</f>
+        <v>kelvinc@livingproperties.com</v>
       </c>
       <c r="G58"/>
       <c r="H58"/>
       <c r="I58"/>
     </row>
     <row r="59" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A59" s="9">
-        <f>IF(LEN(ContactData!H56)&lt;3,"",ContactData!H56)</f>
-        <v>172</v>
+      <c r="A59" s="9" t="str">
+        <f>IF(LEN(ContactData!H58)&lt;3,"",ContactData!H58)</f>
+        <v>---</v>
       </c>
       <c r="B59" s="3" t="str">
-        <f>ContactData!E56</f>
-        <v>Rebecca Lau</v>
+        <f>ContactData!E58</f>
+        <v>Calmaine Hewitt</v>
       </c>
       <c r="C59" s="3" t="str">
-        <f>ContactData!G56</f>
-        <v>Administrative Assistant</v>
+        <f>ContactData!G58</f>
+        <v>Handyman</v>
       </c>
       <c r="D59" s="9" t="str">
-        <f>IF(LEN(ContactData!I56)&lt;3,"",ContactData!I56)</f>
+        <f>IF(LEN(ContactData!I58)&lt;3,"",ContactData!I58)</f>
         <v>---</v>
       </c>
       <c r="E59" s="3" t="str">
-        <f>ContactData!J56</f>
-        <v>---</v>
+        <f>ContactData!J58</f>
+        <v>(905) 477-2090</v>
       </c>
       <c r="F59" s="3" t="str">
-        <f>IF(LEN(ContactData!K56)&lt;3,"",ContactData!K56)</f>
-        <v>rebeccal@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K58)&lt;3,"",ContactData!K58)</f>
+        <v>calmaineh@livingproperties.com</v>
       </c>
       <c r="G59"/>
       <c r="H59"/>
@@ -10318,28 +10257,28 @@
     </row>
     <row r="60" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
-        <f>IF(LEN(ContactData!H57)&lt;3,"",ContactData!H57)</f>
-        <v>182</v>
+        <f>IF(LEN(ContactData!H59)&lt;3,"",ContactData!H59)</f>
+        <v>229</v>
       </c>
       <c r="B60" s="3" t="str">
-        <f>ContactData!E57</f>
-        <v>Kelvin Chan</v>
+        <f>ContactData!E59</f>
+        <v>Matthew Wong</v>
       </c>
       <c r="C60" s="3" t="str">
-        <f>ContactData!G57</f>
-        <v>Administrative Assistant</v>
+        <f>ContactData!G59</f>
+        <v>Accounting Clerk</v>
       </c>
       <c r="D60" s="9" t="str">
-        <f>IF(LEN(ContactData!I57)&lt;3,"",ContactData!I57)</f>
+        <f>IF(LEN(ContactData!I59)&lt;3,"",ContactData!I59)</f>
         <v>---</v>
       </c>
       <c r="E60" s="3" t="str">
-        <f>ContactData!J57</f>
+        <f>ContactData!J59</f>
         <v>---</v>
       </c>
       <c r="F60" s="3" t="str">
-        <f>IF(LEN(ContactData!K57)&lt;3,"",ContactData!K57)</f>
-        <v>kelvinc@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K59)&lt;3,"",ContactData!K59)</f>
+        <v>mattheww@livingproperties.com</v>
       </c>
       <c r="G60"/>
       <c r="H60"/>
@@ -10347,57 +10286,57 @@
     </row>
     <row r="61" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="str">
-        <f>IF(LEN(ContactData!H58)&lt;3,"",ContactData!H58)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!H60)&lt;3,"",ContactData!H60)</f>
+        <v/>
       </c>
       <c r="B61" s="3" t="str">
-        <f>ContactData!E58</f>
-        <v>Calmaine Hewitt</v>
+        <f>ContactData!E60</f>
+        <v>Centro Towers Office</v>
       </c>
       <c r="C61" s="3" t="str">
-        <f>ContactData!G58</f>
-        <v>Handyman</v>
+        <f>ContactData!G60</f>
+        <v>25 Town Centre Crt, Scarborough, ON, M1P 0B4</v>
       </c>
       <c r="D61" s="9" t="str">
-        <f>IF(LEN(ContactData!I58)&lt;3,"",ContactData!I58)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!I60)&lt;3,"",ContactData!I60)</f>
+        <v/>
       </c>
       <c r="E61" s="3" t="str">
-        <f>ContactData!J58</f>
-        <v>(905) 477-2090</v>
+        <f>ContactData!J60</f>
+        <v>T: (416) 290-1242</v>
       </c>
       <c r="F61" s="3" t="str">
-        <f>IF(LEN(ContactData!K58)&lt;3,"",ContactData!K58)</f>
-        <v>calmaineh@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K60)&lt;3,"",ContactData!K60)</f>
+        <v/>
       </c>
       <c r="G61"/>
       <c r="H61"/>
       <c r="I61"/>
     </row>
     <row r="62" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A62" s="9">
-        <f>IF(LEN(ContactData!H59)&lt;3,"",ContactData!H59)</f>
-        <v>229</v>
+      <c r="A62" s="9" t="str">
+        <f>IF(LEN(ContactData!H61)&lt;3,"",ContactData!H61)</f>
+        <v>---</v>
       </c>
       <c r="B62" s="3" t="str">
-        <f>ContactData!E59</f>
-        <v>Matthew Wong</v>
+        <f>ContactData!E61</f>
+        <v>Henry Fu</v>
       </c>
       <c r="C62" s="3" t="str">
-        <f>ContactData!G59</f>
-        <v>Accounting Clerk</v>
+        <f>ContactData!G61</f>
+        <v>Property Manager</v>
       </c>
       <c r="D62" s="9" t="str">
-        <f>IF(LEN(ContactData!I59)&lt;3,"",ContactData!I59)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!I61)&lt;3,"",ContactData!I61)</f>
+        <v>(416) 278-2953</v>
       </c>
       <c r="E62" s="3" t="str">
-        <f>ContactData!J59</f>
-        <v>---</v>
+        <f>ContactData!J61</f>
+        <v>(416) 290-1242</v>
       </c>
       <c r="F62" s="3" t="str">
-        <f>IF(LEN(ContactData!K59)&lt;3,"",ContactData!K59)</f>
-        <v>mattheww@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K61)&lt;3,"",ContactData!K61)</f>
+        <v>henry@centrotowers.com</v>
       </c>
       <c r="G62"/>
       <c r="H62"/>
@@ -10405,28 +10344,28 @@
     </row>
     <row r="63" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A63" s="9" t="str">
-        <f>IF(LEN(ContactData!H60)&lt;3,"",ContactData!H60)</f>
-        <v/>
+        <f>IF(LEN(ContactData!H62)&lt;3,"",ContactData!H62)</f>
+        <v>---</v>
       </c>
       <c r="B63" s="3" t="str">
-        <f>ContactData!E60</f>
-        <v>Centro Towers Office</v>
+        <f>ContactData!E62</f>
+        <v>Sophia Yip</v>
       </c>
       <c r="C63" s="3" t="str">
-        <f>ContactData!G60</f>
-        <v>25 Town Centre Crt, Scarborough, ON, M1P 0B4</v>
+        <f>ContactData!G62</f>
+        <v>Property Administrator</v>
       </c>
       <c r="D63" s="9" t="str">
-        <f>IF(LEN(ContactData!I60)&lt;3,"",ContactData!I60)</f>
-        <v/>
+        <f>IF(LEN(ContactData!I62)&lt;3,"",ContactData!I62)</f>
+        <v>---</v>
       </c>
       <c r="E63" s="3" t="str">
-        <f>ContactData!J60</f>
-        <v>T: (416) 290-1242</v>
+        <f>ContactData!J62</f>
+        <v>(416) 290-1242</v>
       </c>
       <c r="F63" s="3" t="str">
-        <f>IF(LEN(ContactData!K60)&lt;3,"",ContactData!K60)</f>
-        <v/>
+        <f>IF(LEN(ContactData!K62)&lt;3,"",ContactData!K62)</f>
+        <v>sophia@centrotowers.com</v>
       </c>
       <c r="G63"/>
       <c r="H63"/>
@@ -10434,28 +10373,28 @@
     </row>
     <row r="64" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="str">
-        <f>IF(LEN(ContactData!H61)&lt;3,"",ContactData!H61)</f>
+        <f>IF(LEN(ContactData!H63)&lt;3,"",ContactData!H63)</f>
         <v>---</v>
       </c>
       <c r="B64" s="3" t="str">
-        <f>ContactData!E61</f>
-        <v>Henry Fu</v>
+        <f>ContactData!E63</f>
+        <v xml:space="preserve">Security Desk </v>
       </c>
       <c r="C64" s="3" t="str">
-        <f>ContactData!G61</f>
-        <v>Property Manager</v>
+        <f>ContactData!G63</f>
+        <v xml:space="preserve">Centro Security Desk </v>
       </c>
       <c r="D64" s="9" t="str">
-        <f>IF(LEN(ContactData!I61)&lt;3,"",ContactData!I61)</f>
-        <v>(416) 278-2953</v>
+        <f>IF(LEN(ContactData!I63)&lt;3,"",ContactData!I63)</f>
+        <v>---</v>
       </c>
       <c r="E64" s="3" t="str">
-        <f>ContactData!J61</f>
-        <v>(416) 290-1242</v>
+        <f>ContactData!J63</f>
+        <v>(416) 296-0099</v>
       </c>
       <c r="F64" s="3" t="str">
-        <f>IF(LEN(ContactData!K61)&lt;3,"",ContactData!K61)</f>
-        <v>henry@centrotowers.com</v>
+        <f>IF(LEN(ContactData!K63)&lt;3,"",ContactData!K63)</f>
+        <v>---</v>
       </c>
       <c r="G64"/>
       <c r="H64"/>
@@ -10463,28 +10402,28 @@
     </row>
     <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A65" s="9" t="str">
-        <f>IF(LEN(ContactData!H62)&lt;3,"",ContactData!H62)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!H64)&lt;3,"",ContactData!H64)</f>
+        <v/>
       </c>
       <c r="B65" s="3" t="str">
-        <f>ContactData!E62</f>
-        <v>Sophia Yip</v>
+        <f>ContactData!E64</f>
+        <v>EQ1 Office</v>
       </c>
       <c r="C65" s="3" t="str">
-        <f>ContactData!G62</f>
-        <v>Property Administrator</v>
+        <f>ContactData!G64</f>
+        <v>70 Town Centre Court, Scarborough, ON, M1P 0B2</v>
       </c>
       <c r="D65" s="9" t="str">
-        <f>IF(LEN(ContactData!I62)&lt;3,"",ContactData!I62)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!I64)&lt;3,"",ContactData!I64)</f>
+        <v/>
       </c>
       <c r="E65" s="3" t="str">
-        <f>ContactData!J62</f>
-        <v>(416) 290-1242</v>
+        <f>ContactData!J64</f>
+        <v xml:space="preserve">T: (416) 279-0603 </v>
       </c>
       <c r="F65" s="3" t="str">
-        <f>IF(LEN(ContactData!K62)&lt;3,"",ContactData!K62)</f>
-        <v>sophia@centrotowers.com</v>
+        <f>IF(LEN(ContactData!K64)&lt;3,"",ContactData!K64)</f>
+        <v>eq1@livingproperties.com</v>
       </c>
       <c r="G65"/>
       <c r="H65"/>
@@ -10492,28 +10431,28 @@
     </row>
     <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="str">
-        <f>IF(LEN(ContactData!H63)&lt;3,"",ContactData!H63)</f>
+        <f>IF(LEN(ContactData!H65)&lt;3,"",ContactData!H65)</f>
         <v>---</v>
       </c>
       <c r="B66" s="3" t="str">
-        <f>ContactData!E63</f>
-        <v xml:space="preserve">Security Desk </v>
+        <f>ContactData!E65</f>
+        <v>Ming Ip</v>
       </c>
       <c r="C66" s="3" t="str">
-        <f>ContactData!G63</f>
-        <v xml:space="preserve">Centro Security Desk </v>
+        <f>ContactData!G65</f>
+        <v>Property Manager</v>
       </c>
       <c r="D66" s="9" t="str">
-        <f>IF(LEN(ContactData!I63)&lt;3,"",ContactData!I63)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!I65)&lt;3,"",ContactData!I65)</f>
+        <v>(647) 286-0147</v>
       </c>
       <c r="E66" s="3" t="str">
-        <f>ContactData!J63</f>
-        <v>(416) 296-0099</v>
+        <f>ContactData!J65</f>
+        <v xml:space="preserve">(416) 279-0603 </v>
       </c>
       <c r="F66" s="3" t="str">
-        <f>IF(LEN(ContactData!K63)&lt;3,"",ContactData!K63)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!K65)&lt;3,"",ContactData!K65)</f>
+        <v>eq1manager@livingproperties.com</v>
       </c>
       <c r="G66"/>
       <c r="H66"/>
@@ -10521,28 +10460,28 @@
     </row>
     <row r="67" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A67" s="9" t="str">
-        <f>IF(LEN(ContactData!H64)&lt;3,"",ContactData!H64)</f>
-        <v/>
+        <f>IF(LEN(ContactData!H66)&lt;3,"",ContactData!H66)</f>
+        <v>---</v>
       </c>
       <c r="B67" s="3" t="str">
-        <f>ContactData!E64</f>
-        <v>EQ1 Office</v>
+        <f>ContactData!E66</f>
+        <v xml:space="preserve">Security Desk </v>
       </c>
       <c r="C67" s="3" t="str">
-        <f>ContactData!G64</f>
-        <v>70 Town Centre Court, Scarborough, ON, M1P 0B2</v>
+        <f>ContactData!G66</f>
+        <v xml:space="preserve">EQ1 Security Desk </v>
       </c>
       <c r="D67" s="9" t="str">
-        <f>IF(LEN(ContactData!I64)&lt;3,"",ContactData!I64)</f>
-        <v/>
+        <f>IF(LEN(ContactData!I66)&lt;3,"",ContactData!I66)</f>
+        <v>---</v>
       </c>
       <c r="E67" s="3" t="str">
-        <f>ContactData!J64</f>
-        <v xml:space="preserve">T: (416) 279-0603 </v>
+        <f>ContactData!J66</f>
+        <v>(416) 279-1894</v>
       </c>
       <c r="F67" s="3" t="str">
-        <f>IF(LEN(ContactData!K64)&lt;3,"",ContactData!K64)</f>
-        <v>eq1@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K66)&lt;3,"",ContactData!K66)</f>
+        <v>---</v>
       </c>
       <c r="G67"/>
       <c r="H67"/>
@@ -10550,28 +10489,28 @@
     </row>
     <row r="68" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="str">
-        <f>IF(LEN(ContactData!H65)&lt;3,"",ContactData!H65)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!H67)&lt;3,"",ContactData!H67)</f>
+        <v/>
       </c>
       <c r="B68" s="3" t="str">
-        <f>ContactData!E65</f>
-        <v>Ming Ip</v>
+        <f>ContactData!E67</f>
+        <v>EQ2 Office</v>
       </c>
       <c r="C68" s="3" t="str">
-        <f>ContactData!G65</f>
-        <v>Property Manager</v>
+        <f>ContactData!G67</f>
+        <v>60 Town Centre Court, Scarborough, ON, M1P 0B1</v>
       </c>
       <c r="D68" s="9" t="str">
-        <f>IF(LEN(ContactData!I65)&lt;3,"",ContactData!I65)</f>
-        <v>(647) 286-0147</v>
+        <f>IF(LEN(ContactData!I67)&lt;3,"",ContactData!I67)</f>
+        <v/>
       </c>
       <c r="E68" s="3" t="str">
-        <f>ContactData!J65</f>
-        <v xml:space="preserve">(416) 279-0603 </v>
+        <f>ContactData!J67</f>
+        <v xml:space="preserve">T: (416) 279-0591 </v>
       </c>
       <c r="F68" s="3" t="str">
-        <f>IF(LEN(ContactData!K65)&lt;3,"",ContactData!K65)</f>
-        <v>eq1manager@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K67)&lt;3,"",ContactData!K67)</f>
+        <v/>
       </c>
       <c r="G68"/>
       <c r="H68"/>
@@ -10579,28 +10518,28 @@
     </row>
     <row r="69" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A69" s="9" t="str">
-        <f>IF(LEN(ContactData!H66)&lt;3,"",ContactData!H66)</f>
+        <f>IF(LEN(ContactData!H68)&lt;3,"",ContactData!H68)</f>
         <v>---</v>
       </c>
       <c r="B69" s="3" t="str">
-        <f>ContactData!E66</f>
-        <v xml:space="preserve">Security Desk </v>
+        <f>ContactData!E68</f>
+        <v>Aaron Ma</v>
       </c>
       <c r="C69" s="3" t="str">
-        <f>ContactData!G66</f>
-        <v xml:space="preserve">EQ1 Security Desk </v>
+        <f>ContactData!G68</f>
+        <v>Property Manager</v>
       </c>
       <c r="D69" s="9" t="str">
-        <f>IF(LEN(ContactData!I66)&lt;3,"",ContactData!I66)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!I68)&lt;3,"",ContactData!I68)</f>
+        <v>(416) 684-2236</v>
       </c>
       <c r="E69" s="3" t="str">
-        <f>ContactData!J66</f>
-        <v>(416) 279-1894</v>
+        <f>ContactData!J68</f>
+        <v>(416) 279-0591</v>
       </c>
       <c r="F69" s="3" t="str">
-        <f>IF(LEN(ContactData!K66)&lt;3,"",ContactData!K66)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!K68)&lt;3,"",ContactData!K68)</f>
+        <v>eq2manager@livingproperties.com</v>
       </c>
       <c r="G69"/>
       <c r="H69"/>
@@ -10608,28 +10547,28 @@
     </row>
     <row r="70" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="str">
-        <f>IF(LEN(ContactData!H67)&lt;3,"",ContactData!H67)</f>
-        <v/>
+        <f>IF(LEN(ContactData!H69)&lt;3,"",ContactData!H69)</f>
+        <v>---</v>
       </c>
       <c r="B70" s="3" t="str">
-        <f>ContactData!E67</f>
-        <v>EQ2 Office</v>
+        <f>ContactData!E69</f>
+        <v xml:space="preserve">Security Desk </v>
       </c>
       <c r="C70" s="3" t="str">
-        <f>ContactData!G67</f>
-        <v>60 Town Centre Court, Scarborough, ON, M1P 0B1</v>
+        <f>ContactData!G69</f>
+        <v xml:space="preserve">EQ2 Security Desk </v>
       </c>
       <c r="D70" s="9" t="str">
-        <f>IF(LEN(ContactData!I67)&lt;3,"",ContactData!I67)</f>
-        <v/>
+        <f>IF(LEN(ContactData!I69)&lt;3,"",ContactData!I69)</f>
+        <v>---</v>
       </c>
       <c r="E70" s="3" t="str">
-        <f>ContactData!J67</f>
-        <v xml:space="preserve">T: (416) 279-0591 </v>
+        <f>ContactData!J69</f>
+        <v>(416) 279-1211</v>
       </c>
       <c r="F70" s="3" t="str">
-        <f>IF(LEN(ContactData!K67)&lt;3,"",ContactData!K67)</f>
-        <v/>
+        <f>IF(LEN(ContactData!K69)&lt;3,"",ContactData!K69)</f>
+        <v>---</v>
       </c>
       <c r="G70"/>
       <c r="H70"/>
@@ -10637,28 +10576,28 @@
     </row>
     <row r="71" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="str">
-        <f>IF(LEN(ContactData!H68)&lt;3,"",ContactData!H68)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!H70)&lt;3,"",ContactData!H70)</f>
+        <v/>
       </c>
       <c r="B71" s="3" t="str">
-        <f>ContactData!E68</f>
-        <v>Aaron Ma</v>
+        <f>ContactData!E70</f>
+        <v>Alton Tower Office</v>
       </c>
       <c r="C71" s="3" t="str">
-        <f>ContactData!G68</f>
-        <v>Property Manager</v>
+        <f>ContactData!G70</f>
+        <v>160 Alton Towers Cir, Toronto, ON, M1V 4X8</v>
       </c>
       <c r="D71" s="9" t="str">
-        <f>IF(LEN(ContactData!I68)&lt;3,"",ContactData!I68)</f>
-        <v>(416) 684-2236</v>
+        <f>IF(LEN(ContactData!I70)&lt;3,"",ContactData!I70)</f>
+        <v/>
       </c>
       <c r="E71" s="3" t="str">
-        <f>ContactData!J68</f>
-        <v>(416) 279-0591</v>
+        <f>ContactData!J70</f>
+        <v>T: (437)-533-1208</v>
       </c>
       <c r="F71" s="3" t="str">
-        <f>IF(LEN(ContactData!K68)&lt;3,"",ContactData!K68)</f>
-        <v>eq2manager@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K70)&lt;3,"",ContactData!K70)</f>
+        <v/>
       </c>
       <c r="G71"/>
       <c r="H71"/>
@@ -10666,28 +10605,28 @@
     </row>
     <row r="72" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A72" s="9" t="str">
-        <f>IF(LEN(ContactData!H69)&lt;3,"",ContactData!H69)</f>
+        <f>IF(LEN(ContactData!H71)&lt;3,"",ContactData!H71)</f>
         <v>---</v>
       </c>
       <c r="B72" s="3" t="str">
-        <f>ContactData!E69</f>
-        <v xml:space="preserve">Security Desk </v>
+        <f>ContactData!E71</f>
+        <v>Ken Kam</v>
       </c>
       <c r="C72" s="3" t="str">
-        <f>ContactData!G69</f>
-        <v xml:space="preserve">EQ2 Security Desk </v>
+        <f>ContactData!G71</f>
+        <v>Property Manager</v>
       </c>
       <c r="D72" s="9" t="str">
-        <f>IF(LEN(ContactData!I69)&lt;3,"",ContactData!I69)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!I71)&lt;3,"",ContactData!I71)</f>
+        <v>(647) 204-4455</v>
       </c>
       <c r="E72" s="3" t="str">
-        <f>ContactData!J69</f>
-        <v>(416) 279-1211</v>
+        <f>ContactData!J71</f>
+        <v>(905) 477-2090</v>
       </c>
       <c r="F72" s="3" t="str">
-        <f>IF(LEN(ContactData!K69)&lt;3,"",ContactData!K69)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!K71)&lt;3,"",ContactData!K71)</f>
+        <v>kenk@livingproperties.com</v>
       </c>
       <c r="G72"/>
       <c r="H72"/>
@@ -10695,28 +10634,28 @@
     </row>
     <row r="73" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A73" s="9" t="str">
-        <f>IF(LEN(ContactData!H70)&lt;3,"",ContactData!H70)</f>
-        <v/>
+        <f>IF(LEN(ContactData!H72)&lt;3,"",ContactData!H72)</f>
+        <v>---</v>
       </c>
       <c r="B73" s="3" t="str">
-        <f>ContactData!E70</f>
-        <v>Alton Tower Office</v>
+        <f>ContactData!E72</f>
+        <v>Christie Ip</v>
       </c>
       <c r="C73" s="3" t="str">
-        <f>ContactData!G70</f>
-        <v>160 Alton Towers Cir, Toronto, ON, M1V 4X8</v>
+        <f>ContactData!G72</f>
+        <v>Administrative Assistant</v>
       </c>
       <c r="D73" s="9" t="str">
-        <f>IF(LEN(ContactData!I70)&lt;3,"",ContactData!I70)</f>
-        <v/>
+        <f>IF(LEN(ContactData!I72)&lt;3,"",ContactData!I72)</f>
+        <v>(437)-533-1208</v>
       </c>
       <c r="E73" s="3" t="str">
-        <f>ContactData!J70</f>
-        <v>T: (437)-533-1208</v>
+        <f>ContactData!J72</f>
+        <v>---</v>
       </c>
       <c r="F73" s="3" t="str">
-        <f>IF(LEN(ContactData!K70)&lt;3,"",ContactData!K70)</f>
-        <v/>
+        <f>IF(LEN(ContactData!K72)&lt;3,"",ContactData!K72)</f>
+        <v xml:space="preserve">optima2@livingproperties.com </v>
       </c>
       <c r="G73"/>
       <c r="H73"/>
@@ -10724,28 +10663,28 @@
     </row>
     <row r="74" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A74" s="9" t="str">
-        <f>IF(LEN(ContactData!H71)&lt;3,"",ContactData!H71)</f>
+        <f>IF(LEN(ContactData!H73)&lt;3,"",ContactData!H73)</f>
         <v>---</v>
       </c>
       <c r="B74" s="3" t="str">
-        <f>ContactData!E71</f>
-        <v>Ken Kam</v>
+        <f>ContactData!E73</f>
+        <v xml:space="preserve">Security Desk </v>
       </c>
       <c r="C74" s="3" t="str">
-        <f>ContactData!G71</f>
-        <v>Property Manager</v>
+        <f>ContactData!G73</f>
+        <v xml:space="preserve">Alton Tower Security Desk </v>
       </c>
       <c r="D74" s="9" t="str">
-        <f>IF(LEN(ContactData!I71)&lt;3,"",ContactData!I71)</f>
-        <v>(647) 204-4455</v>
+        <f>IF(LEN(ContactData!I73)&lt;3,"",ContactData!I73)</f>
+        <v>---</v>
       </c>
       <c r="E74" s="3" t="str">
-        <f>ContactData!J71</f>
-        <v>(905) 477-2090</v>
+        <f>ContactData!J73</f>
+        <v>(416) 754-3131</v>
       </c>
       <c r="F74" s="3" t="str">
-        <f>IF(LEN(ContactData!K71)&lt;3,"",ContactData!K71)</f>
-        <v>kenk@livingproperties.com</v>
+        <f>IF(LEN(ContactData!K73)&lt;3,"",ContactData!K73)</f>
+        <v>---</v>
       </c>
       <c r="G74"/>
       <c r="H74"/>
@@ -10753,28 +10692,28 @@
     </row>
     <row r="75" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A75" s="9" t="str">
-        <f>IF(LEN(ContactData!H72)&lt;3,"",ContactData!H72)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!H74)&lt;3,"",ContactData!H74)</f>
+        <v/>
       </c>
       <c r="B75" s="3" t="str">
-        <f>ContactData!E72</f>
-        <v>Christie Ip</v>
+        <f>ContactData!E74</f>
+        <v>IHMG Office</v>
       </c>
       <c r="C75" s="3" t="str">
-        <f>ContactData!G72</f>
-        <v>Administrative Assistant</v>
+        <f>ContactData!G74</f>
+        <v>8 Steelcase Road West, Markham, ON, L3R 1B2</v>
       </c>
       <c r="D75" s="9" t="str">
-        <f>IF(LEN(ContactData!I72)&lt;3,"",ContactData!I72)</f>
-        <v>(437)-533-1208</v>
+        <f>IF(LEN(ContactData!I74)&lt;3,"",ContactData!I74)</f>
+        <v/>
       </c>
       <c r="E75" s="3" t="str">
-        <f>ContactData!J72</f>
-        <v>---</v>
+        <f>ContactData!J74</f>
+        <v>T: (905) 475-6000</v>
       </c>
       <c r="F75" s="3" t="str">
-        <f>IF(LEN(ContactData!K72)&lt;3,"",ContactData!K72)</f>
-        <v xml:space="preserve">optima2@livingproperties.com </v>
+        <f>IF(LEN(ContactData!K74)&lt;3,"",ContactData!K74)</f>
+        <v>info@ihmg.ca</v>
       </c>
       <c r="G75"/>
       <c r="H75"/>
@@ -10782,145 +10721,109 @@
     </row>
     <row r="76" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A76" s="9" t="str">
-        <f>IF(LEN(ContactData!H73)&lt;3,"",ContactData!H73)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!H75)&lt;3,"",ContactData!H75)</f>
+        <v/>
       </c>
       <c r="B76" s="3" t="str">
-        <f>ContactData!E73</f>
-        <v xml:space="preserve">Security Desk </v>
+        <f>ContactData!E75</f>
+        <v>IHMGRI Office</v>
       </c>
       <c r="C76" s="3" t="str">
-        <f>ContactData!G73</f>
-        <v xml:space="preserve">Alton Tower Security Desk </v>
+        <f>ContactData!G75</f>
+        <v>8 Steelcase Road West, Unit E, Markham, ON, L3R 1B2</v>
       </c>
       <c r="D76" s="9" t="str">
-        <f>IF(LEN(ContactData!I73)&lt;3,"",ContactData!I73)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!I75)&lt;3,"",ContactData!I75)</f>
+        <v/>
       </c>
       <c r="E76" s="3" t="str">
-        <f>ContactData!J73</f>
-        <v>(416) 754-3131</v>
+        <f>ContactData!J75</f>
+        <v>T: (905) 489-8989</v>
       </c>
       <c r="F76" s="3" t="str">
-        <f>IF(LEN(ContactData!K73)&lt;3,"",ContactData!K73)</f>
-        <v>---</v>
+        <f>IF(LEN(ContactData!K75)&lt;3,"",ContactData!K75)</f>
+        <v>realestate@ihmg.ca</v>
       </c>
       <c r="G76"/>
       <c r="H76"/>
       <c r="I76"/>
     </row>
     <row r="77" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A77" s="9" t="str">
-        <f>IF(LEN(ContactData!H74)&lt;3,"",ContactData!H74)</f>
-        <v/>
+      <c r="A77" s="9">
+        <f>IF(LEN(ContactData!H76)&lt;3,"",ContactData!H76)</f>
+        <v>120</v>
       </c>
       <c r="B77" s="3" t="str">
-        <f>ContactData!E74</f>
-        <v>IHMG Office</v>
+        <f>ContactData!E76</f>
+        <v>Eddie Tang</v>
       </c>
       <c r="C77" s="3" t="str">
-        <f>ContactData!G74</f>
-        <v>8 Steelcase Road West, Markham, ON, L3R 1B2</v>
+        <f>ContactData!G76</f>
+        <v>Financial Controller</v>
       </c>
       <c r="D77" s="9" t="str">
-        <f>IF(LEN(ContactData!I74)&lt;3,"",ContactData!I74)</f>
-        <v/>
+        <f>IF(LEN(ContactData!I76)&lt;3,"",ContactData!I76)</f>
+        <v>(416) 723-8329</v>
       </c>
       <c r="E77" s="3" t="str">
-        <f>ContactData!J74</f>
-        <v>T: (905) 475-6000</v>
+        <f>ContactData!J76</f>
+        <v>(905) 489-0186</v>
       </c>
       <c r="F77" s="3" t="str">
-        <f>IF(LEN(ContactData!K74)&lt;3,"",ContactData!K74)</f>
-        <v>info@ihmg.ca</v>
+        <f>IF(LEN(ContactData!K76)&lt;3,"",ContactData!K76)</f>
+        <v>eddie@ihmg.ca</v>
       </c>
       <c r="G77"/>
       <c r="H77"/>
       <c r="I77"/>
     </row>
     <row r="78" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A78" s="9" t="str">
-        <f>IF(LEN(ContactData!H75)&lt;3,"",ContactData!H75)</f>
-        <v/>
+      <c r="A78" s="9">
+        <f>IF(LEN(ContactData!H77)&lt;3,"",ContactData!H77)</f>
+        <v>187</v>
       </c>
       <c r="B78" s="3" t="str">
-        <f>ContactData!E75</f>
-        <v>IHMGRI Office</v>
+        <f>ContactData!E77</f>
+        <v>Lily Hou</v>
       </c>
       <c r="C78" s="3" t="str">
-        <f>ContactData!G75</f>
-        <v>8 Steelcase Road West, Unit E, Markham, ON, L3R 1B2</v>
+        <f>ContactData!G77</f>
+        <v>Senior Accounting Analyst &amp; Operations Support</v>
       </c>
       <c r="D78" s="9" t="str">
-        <f>IF(LEN(ContactData!I75)&lt;3,"",ContactData!I75)</f>
-        <v/>
+        <f>IF(LEN(ContactData!I77)&lt;3,"",ContactData!I77)</f>
+        <v>(647) 774-8994</v>
       </c>
       <c r="E78" s="3" t="str">
-        <f>ContactData!J75</f>
-        <v>T: (905) 489-8989</v>
+        <f>ContactData!J77</f>
+        <v>---</v>
       </c>
       <c r="F78" s="3" t="str">
-        <f>IF(LEN(ContactData!K75)&lt;3,"",ContactData!K75)</f>
-        <v>realestate@ihmg.ca</v>
+        <f>IF(LEN(ContactData!K77)&lt;3,"",ContactData!K77)</f>
+        <v>lily@ihmg.ca</v>
       </c>
       <c r="G78"/>
       <c r="H78"/>
       <c r="I78"/>
     </row>
     <row r="79" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A79" s="9">
-        <f>IF(LEN(ContactData!H76)&lt;3,"",ContactData!H76)</f>
-        <v>120</v>
-      </c>
-      <c r="B79" s="3" t="str">
-        <f>ContactData!E76</f>
-        <v>Eddie Tang</v>
-      </c>
-      <c r="C79" s="3" t="str">
-        <f>ContactData!G76</f>
-        <v>Financial Controller</v>
-      </c>
-      <c r="D79" s="9" t="str">
-        <f>IF(LEN(ContactData!I76)&lt;3,"",ContactData!I76)</f>
-        <v>(416) 723-8329</v>
-      </c>
-      <c r="E79" s="3" t="str">
-        <f>ContactData!J76</f>
-        <v>(905) 489-0186</v>
-      </c>
-      <c r="F79" s="3" t="str">
-        <f>IF(LEN(ContactData!K76)&lt;3,"",ContactData!K76)</f>
-        <v>eddie@ihmg.ca</v>
-      </c>
+      <c r="A79" s="1"/>
+      <c r="B79"/>
+      <c r="C79"/>
+      <c r="D79"/>
+      <c r="E79"/>
+      <c r="F79"/>
       <c r="G79"/>
       <c r="H79"/>
       <c r="I79"/>
     </row>
     <row r="80" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A80" s="9">
-        <f>IF(LEN(ContactData!H77)&lt;3,"",ContactData!H77)</f>
-        <v>187</v>
-      </c>
-      <c r="B80" s="3" t="str">
-        <f>ContactData!E77</f>
-        <v>Lily Hou</v>
-      </c>
-      <c r="C80" s="3" t="str">
-        <f>ContactData!G77</f>
-        <v>Senior Accounting Analyst &amp; Operations Support</v>
-      </c>
-      <c r="D80" s="9" t="str">
-        <f>IF(LEN(ContactData!I77)&lt;3,"",ContactData!I77)</f>
-        <v>(647) 774-8994</v>
-      </c>
-      <c r="E80" s="3" t="str">
-        <f>ContactData!J77</f>
-        <v>---</v>
-      </c>
-      <c r="F80" s="3" t="str">
-        <f>IF(LEN(ContactData!K77)&lt;3,"",ContactData!K77)</f>
-        <v>lily@ihmg.ca</v>
-      </c>
+      <c r="A80" s="1"/>
+      <c r="B80"/>
+      <c r="C80"/>
+      <c r="D80"/>
+      <c r="E80"/>
+      <c r="F80"/>
       <c r="G80"/>
       <c r="H80"/>
       <c r="I80"/>
@@ -14071,45 +13974,23 @@
       <c r="H366"/>
       <c r="I366"/>
     </row>
-    <row r="367" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A367" s="1"/>
-      <c r="B367"/>
-      <c r="C367"/>
-      <c r="D367"/>
-      <c r="E367"/>
-      <c r="F367"/>
-      <c r="G367"/>
-      <c r="H367"/>
-      <c r="I367"/>
-    </row>
-    <row r="368" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A368" s="1"/>
-      <c r="B368"/>
-      <c r="C368"/>
-      <c r="D368"/>
-      <c r="E368"/>
-      <c r="F368"/>
-      <c r="G368"/>
-      <c r="H368"/>
-      <c r="I368"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A3:A80 D3:D80">
+  <conditionalFormatting sqref="A3:A78 D3:D78">
     <cfRule type="containsBlanks" dxfId="15" priority="18">
       <formula>LEN(TRIM(A3))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B3:B80">
+  <conditionalFormatting sqref="B3:B78">
     <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="Office">
       <formula>NOT(ISERROR(SEARCH("Office",B3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C80">
+  <conditionalFormatting sqref="C3:C78">
     <cfRule type="containsText" dxfId="13" priority="15" operator="containsText" text="ON,">
       <formula>NOT(ISERROR(SEARCH("ON,",C3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E80">
+  <conditionalFormatting sqref="E3:E78">
     <cfRule type="containsText" dxfId="12" priority="13" operator="containsText" text="T">
       <formula>NOT(ISERROR(SEARCH("T",E3)))</formula>
     </cfRule>
@@ -14119,7 +14000,7 @@
       <formula>LEN(TRIM(F3))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F80">
+  <conditionalFormatting sqref="F4:F78">
     <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="ye@">
       <formula>NOT(ISERROR(SEARCH("ye@",F4)))</formula>
     </cfRule>
@@ -14747,7 +14628,7 @@
         <v>13</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>311</v>
@@ -14774,13 +14655,13 @@
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F15" t="s">
         <v>289</v>
       </c>
       <c r="G15" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H15">
         <v>282</v>
@@ -14792,7 +14673,7 @@
         <v>13</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L15" t="s">
         <v>160</v>
@@ -15443,7 +15324,7 @@
         <v>4</v>
       </c>
       <c r="E31" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F31" t="s">
         <v>289</v>
@@ -15461,7 +15342,7 @@
         <v>13</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L31" t="s">
         <v>160</v>
@@ -15611,7 +15492,7 @@
         <v>5</v>
       </c>
       <c r="E35" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F35" t="s">
         <v>289</v>
@@ -15629,7 +15510,7 @@
         <v>19</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L35" t="s">
         <v>160</v>
@@ -17662,6 +17543,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FCEEF5D6F9A2C14292C82E7F88E7D4C7" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="770a5493e01cc46570af888c0fd11107">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6e07a911-1c82-455b-ae09-b73935b22a66" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="de63ad8f9259e2f5a7ae7a5921e0e8ad" ns2:_="">
     <xsd:import namespace="6e07a911-1c82-455b-ae09-b73935b22a66"/>
@@ -17793,22 +17689,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDCD3F55-29C2-4E12-8D9A-9EC0083C9C49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="6e07a911-1c82-455b-ae09-b73935b22a66"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C569B7B-6177-4C5F-B641-1220485D9B3F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4188865-1BAB-459E-8F28-5F6AB5F6EAC9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17824,28 +17729,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C569B7B-6177-4C5F-B641-1220485D9B3F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDCD3F55-29C2-4E12-8D9A-9EC0083C9C49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="6e07a911-1c82-455b-ae09-b73935b22a66"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/companydirectorypdf/companydir.xlsx
+++ b/companydirectorypdf/companydir.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nelso\Documents\GitHub\kwlivingrealtydrive\kwlrportal\companydirectorypdf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B2A0C7-2680-43AD-B8FE-3A7DC0833C55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{669F11D5-078A-4D8B-9BBB-D4732D6120A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-16440" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{AE6EE1E0-C559-4053-97E8-B14EEDB6E6F6}"/>
+    <workbookView xWindow="-90" yWindow="-16440" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{AE6EE1E0-C559-4053-97E8-B14EEDB6E6F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Letter Size" sheetId="8" r:id="rId1"/>
@@ -535,9 +535,6 @@
     <t>Accounting Bookkeeper</t>
   </si>
   <si>
-    <t>Senior Technical Specialist</t>
-  </si>
-  <si>
     <t>Head Secretary</t>
   </si>
   <si>
@@ -992,6 +989,9 @@
   </si>
   <si>
     <t>Update Date: Apr 8, 2026</t>
+  </si>
+  <si>
+    <t>Senior Technical Specialist &amp; System Architect</t>
   </si>
 </sst>
 </file>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="H1" s="11"/>
       <c r="I1" s="11" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
@@ -2002,7 +2002,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>3</v>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="G2"/>
       <c r="H2" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I2" s="10" t="s">
         <v>1</v>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="C24" s="3" t="str">
         <f>ContactData!G23</f>
-        <v>Senior Technical Specialist</v>
+        <v>Senior Technical Specialist &amp; System Architect</v>
       </c>
       <c r="D24" s="9" t="str">
         <f>IF(LEN(ContactData!I23)&lt;3,"",ContactData!I23)</f>
@@ -8529,7 +8529,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -8540,7 +8540,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>3</v>
@@ -9175,7 +9175,7 @@
       </c>
       <c r="C24" s="3" t="str">
         <f>ContactData!G23</f>
-        <v>Senior Technical Specialist</v>
+        <v>Senior Technical Specialist &amp; System Architect</v>
       </c>
       <c r="D24" s="9" t="str">
         <f>IF(LEN(ContactData!I23)&lt;3,"",ContactData!I23)</f>
@@ -13986,22 +13986,22 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B1" t="s">
         <v>166</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>167</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E1" t="s">
         <v>168</v>
       </c>
-      <c r="D1" t="s">
-        <v>202</v>
-      </c>
-      <c r="E1" t="s">
-        <v>169</v>
-      </c>
       <c r="F1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G1" t="s">
         <v>149</v>
@@ -14010,19 +14010,19 @@
         <v>1</v>
       </c>
       <c r="I1" t="s">
+        <v>169</v>
+      </c>
+      <c r="J1" t="s">
         <v>170</v>
-      </c>
-      <c r="J1" t="s">
-        <v>171</v>
       </c>
       <c r="K1" t="s">
         <v>5</v>
       </c>
       <c r="L1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -14030,10 +14030,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -14045,16 +14045,16 @@
         <v>9</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J2" t="s">
         <v>10</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L2" t="s">
         <v>158</v>
@@ -14069,10 +14069,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -14081,7 +14081,7 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G3" t="s">
         <v>12</v>
@@ -14093,7 +14093,7 @@
         <v>13</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>159</v>
@@ -14111,10 +14111,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -14123,7 +14123,7 @@
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -14135,7 +14135,7 @@
         <v>16</v>
       </c>
       <c r="J4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>150</v>
@@ -14153,10 +14153,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -14165,10 +14165,10 @@
         <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H5">
         <v>228</v>
@@ -14180,7 +14180,7 @@
         <v>13</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L5" t="s">
         <v>160</v>
@@ -14195,22 +14195,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H6">
         <v>521</v>
@@ -14222,7 +14222,7 @@
         <v>25</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L6" t="s">
         <v>160</v>
@@ -14237,10 +14237,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -14249,7 +14249,7 @@
         <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G7" t="s">
         <v>21</v>
@@ -14264,7 +14264,7 @@
         <v>154</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L7" t="s">
         <v>160</v>
@@ -14279,10 +14279,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -14291,10 +14291,10 @@
         <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H8">
         <v>502</v>
@@ -14321,34 +14321,34 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>13</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L9" t="s">
         <v>160</v>
@@ -14363,10 +14363,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -14375,10 +14375,10 @@
         <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>13</v>
@@ -14390,7 +14390,7 @@
         <v>13</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L10" t="s">
         <v>160</v>
@@ -14405,19 +14405,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F11" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G11" t="s">
         <v>161</v>
@@ -14426,13 +14426,13 @@
         <v>509</v>
       </c>
       <c r="I11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>13</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L11" t="s">
         <v>160</v>
@@ -14447,31 +14447,31 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G12" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H12">
         <v>504</v>
       </c>
       <c r="I12" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J12" t="s">
         <v>30</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L12" t="s">
         <v>160</v>
@@ -14486,10 +14486,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C13" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -14498,7 +14498,7 @@
         <v>31</v>
       </c>
       <c r="F13" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G13" t="s">
         <v>32</v>
@@ -14528,22 +14528,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" t="s">
+        <v>304</v>
+      </c>
+      <c r="F14" t="s">
+        <v>285</v>
+      </c>
+      <c r="G14" t="s">
         <v>305</v>
-      </c>
-      <c r="F14" t="s">
-        <v>286</v>
-      </c>
-      <c r="G14" t="s">
-        <v>306</v>
       </c>
       <c r="H14">
         <v>282</v>
@@ -14555,7 +14555,7 @@
         <v>13</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L14" t="s">
         <v>160</v>
@@ -14570,10 +14570,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -14582,10 +14582,10 @@
         <v>61</v>
       </c>
       <c r="F15" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H15">
         <v>123</v>
@@ -14597,7 +14597,7 @@
         <v>13</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L15" t="s">
         <v>160</v>
@@ -14612,10 +14612,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -14624,10 +14624,10 @@
         <v>23</v>
       </c>
       <c r="F16" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H16">
         <v>206</v>
@@ -14639,7 +14639,7 @@
         <v>13</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L16" t="s">
         <v>160</v>
@@ -14654,10 +14654,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C17" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -14666,7 +14666,7 @@
         <v>39</v>
       </c>
       <c r="F17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G17" t="s">
         <v>40</v>
@@ -14681,7 +14681,7 @@
         <v>41</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L17" t="s">
         <v>160</v>
@@ -14696,10 +14696,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C18" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -14708,7 +14708,7 @@
         <v>42</v>
       </c>
       <c r="F18" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G18" t="s">
         <v>37</v>
@@ -14723,7 +14723,7 @@
         <v>38</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L18" t="s">
         <v>160</v>
@@ -14738,10 +14738,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -14750,7 +14750,7 @@
         <v>77</v>
       </c>
       <c r="F19" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G19" t="s">
         <v>37</v>
@@ -14765,7 +14765,7 @@
         <v>13</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L19" t="s">
         <v>160</v>
@@ -14780,19 +14780,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G20" t="s">
         <v>163</v>
@@ -14807,7 +14807,7 @@
         <v>36</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L20" t="s">
         <v>160</v>
@@ -14822,10 +14822,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C21" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -14834,7 +14834,7 @@
         <v>43</v>
       </c>
       <c r="F21" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G21" t="s">
         <v>44</v>
@@ -14849,7 +14849,7 @@
         <v>45</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L21" t="s">
         <v>160</v>
@@ -14864,22 +14864,22 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22" t="s">
+        <v>202</v>
+      </c>
+      <c r="F22" t="s">
+        <v>285</v>
+      </c>
+      <c r="G22" t="s">
         <v>203</v>
-      </c>
-      <c r="F22" t="s">
-        <v>286</v>
-      </c>
-      <c r="G22" t="s">
-        <v>204</v>
       </c>
       <c r="H22">
         <v>121</v>
@@ -14891,7 +14891,7 @@
         <v>13</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L22" t="s">
         <v>160</v>
@@ -14906,10 +14906,10 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -14918,10 +14918,10 @@
         <v>46</v>
       </c>
       <c r="F23" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G23" t="s">
-        <v>164</v>
+        <v>316</v>
       </c>
       <c r="H23">
         <v>522</v>
@@ -14933,14 +14933,14 @@
         <v>48</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L23" t="s">
         <v>160</v>
       </c>
       <c r="M23" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('23','1','Nelson Lau','Senior Technical Specialist','522','(647) 701-8828','(905) 752-3522','nelsonlau@livingrealtykw.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('23','1','Nelson Lau','Senior Technical Specialist &amp; System Architect','522','(647) 701-8828','(905) 752-3522','nelsonlau@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
@@ -14948,10 +14948,10 @@
         <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C24" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -14972,7 +14972,7 @@
         <v>48</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L24" t="s">
         <v>160</v>
@@ -14990,7 +14990,7 @@
         <v>51</v>
       </c>
       <c r="C25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -14999,22 +14999,22 @@
         <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G25" t="s">
         <v>53</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J25" t="s">
         <v>54</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L25" t="s">
         <v>158</v>
@@ -15032,7 +15032,7 @@
         <v>51</v>
       </c>
       <c r="C26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D26">
         <v>2</v>
@@ -15041,7 +15041,7 @@
         <v>55</v>
       </c>
       <c r="F26" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G26" t="s">
         <v>56</v>
@@ -15056,7 +15056,7 @@
         <v>13</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L26" t="s">
         <v>160</v>
@@ -15074,7 +15074,7 @@
         <v>51</v>
       </c>
       <c r="C27" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -15083,10 +15083,10 @@
         <v>59</v>
       </c>
       <c r="F27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G27" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>13</v>
@@ -15098,7 +15098,7 @@
         <v>58</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L27" t="s">
         <v>160</v>
@@ -15116,16 +15116,16 @@
         <v>51</v>
       </c>
       <c r="C28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D28">
         <v>2</v>
       </c>
       <c r="E28" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F28" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G28" t="s">
         <v>60</v>
@@ -15140,7 +15140,7 @@
         <v>58</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L28" t="s">
         <v>160</v>
@@ -15158,7 +15158,7 @@
         <v>67</v>
       </c>
       <c r="C29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D29">
         <v>4</v>
@@ -15167,22 +15167,22 @@
         <v>68</v>
       </c>
       <c r="F29" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G29" t="s">
         <v>152</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J29" t="s">
         <v>69</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L29" t="s">
         <v>158</v>
@@ -15200,16 +15200,16 @@
         <v>67</v>
       </c>
       <c r="C30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D30">
         <v>4</v>
       </c>
       <c r="E30" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F30" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G30" t="s">
         <v>70</v>
@@ -15224,7 +15224,7 @@
         <v>13</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L30" t="s">
         <v>160</v>
@@ -15242,16 +15242,16 @@
         <v>67</v>
       </c>
       <c r="C31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D31">
         <v>4</v>
       </c>
       <c r="E31" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F31" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G31" t="s">
         <v>60</v>
@@ -15266,7 +15266,7 @@
         <v>71</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L31" t="s">
         <v>160</v>
@@ -15284,16 +15284,16 @@
         <v>67</v>
       </c>
       <c r="C32" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D32">
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F32" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G32" t="s">
         <v>60</v>
@@ -15308,7 +15308,7 @@
         <v>71</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L32" t="s">
         <v>160</v>
@@ -15326,7 +15326,7 @@
         <v>72</v>
       </c>
       <c r="C33" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -15335,22 +15335,22 @@
         <v>73</v>
       </c>
       <c r="F33" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G33" t="s">
         <v>9</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J33" t="s">
         <v>74</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L33" t="s">
         <v>158</v>
@@ -15368,7 +15368,7 @@
         <v>72</v>
       </c>
       <c r="C34" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D34">
         <v>5</v>
@@ -15377,7 +15377,7 @@
         <v>76</v>
       </c>
       <c r="F34" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G34" t="s">
         <v>75</v>
@@ -15386,13 +15386,13 @@
         <v>176</v>
       </c>
       <c r="I34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J34" s="6" t="s">
         <v>13</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L34" t="s">
         <v>160</v>
@@ -15410,7 +15410,7 @@
         <v>72</v>
       </c>
       <c r="C35" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D35">
         <v>5</v>
@@ -15419,7 +15419,7 @@
         <v>79</v>
       </c>
       <c r="F35" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G35" t="s">
         <v>60</v>
@@ -15434,7 +15434,7 @@
         <v>19</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L35" t="s">
         <v>160</v>
@@ -15452,31 +15452,31 @@
         <v>62</v>
       </c>
       <c r="C36" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D36">
         <v>3</v>
       </c>
       <c r="E36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F36" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G36" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J36" t="s">
         <v>63</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L36" t="s">
         <v>158</v>
@@ -15494,31 +15494,31 @@
         <v>62</v>
       </c>
       <c r="C37" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D37">
         <v>3</v>
       </c>
       <c r="E37" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F37" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G37" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I37" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J37" s="6" t="s">
         <v>13</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L37" t="s">
         <v>160</v>
@@ -15536,16 +15536,16 @@
         <v>62</v>
       </c>
       <c r="C38" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D38">
         <v>3</v>
       </c>
       <c r="E38" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F38" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G38" t="s">
         <v>60</v>
@@ -15560,7 +15560,7 @@
         <v>66</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L38" t="s">
         <v>160</v>
@@ -15575,10 +15575,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C39" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D39">
         <v>7</v>
@@ -15590,16 +15590,16 @@
         <v>82</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J39" t="s">
         <v>83</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L39" t="s">
         <v>158</v>
@@ -15614,10 +15614,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C40" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D40">
         <v>7</v>
@@ -15626,7 +15626,7 @@
         <v>17</v>
       </c>
       <c r="F40" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G40" t="s">
         <v>84</v>
@@ -15641,7 +15641,7 @@
         <v>13</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L40" t="s">
         <v>160</v>
@@ -15656,10 +15656,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C41" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D41">
         <v>8</v>
@@ -15671,16 +15671,16 @@
         <v>9</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J41" t="s">
         <v>87</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L41" t="s">
         <v>158</v>
@@ -15695,16 +15695,16 @@
         <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C42" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D42">
         <v>8</v>
       </c>
       <c r="E42" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G42" t="s">
         <v>15</v>
@@ -15734,10 +15734,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C43" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D43">
         <v>8</v>
@@ -15773,10 +15773,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C44" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D44">
         <v>8</v>
@@ -15785,7 +15785,7 @@
         <v>100</v>
       </c>
       <c r="G44" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H44">
         <v>286</v>
@@ -15794,7 +15794,7 @@
         <v>101</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K44" s="4" t="s">
         <v>102</v>
@@ -15812,10 +15812,10 @@
         <v>47</v>
       </c>
       <c r="B45" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C45" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D45">
         <v>8</v>
@@ -15851,10 +15851,10 @@
         <v>48</v>
       </c>
       <c r="B46" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C46" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D46">
         <v>8</v>
@@ -15893,13 +15893,13 @@
         <v>153</v>
       </c>
       <c r="C47" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D47">
         <v>8</v>
       </c>
       <c r="E47" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G47" t="s">
         <v>91</v>
@@ -15908,13 +15908,13 @@
         <v>517</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J47" t="s">
         <v>95</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L47" t="s">
         <v>160</v>
@@ -15932,13 +15932,13 @@
         <v>153</v>
       </c>
       <c r="C48" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D48">
         <v>8</v>
       </c>
       <c r="E48" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G48" t="s">
         <v>91</v>
@@ -15947,13 +15947,13 @@
         <v>520</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J48" t="s">
         <v>95</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L48" t="s">
         <v>160</v>
@@ -15968,31 +15968,31 @@
         <v>51</v>
       </c>
       <c r="B49" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C49" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D49">
         <v>8</v>
       </c>
       <c r="E49" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G49" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H49">
         <v>168</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J49" t="s">
         <v>95</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="L49" t="s">
         <v>160</v>
@@ -16007,10 +16007,10 @@
         <v>52</v>
       </c>
       <c r="B50" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C50" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D50">
         <v>8</v>
@@ -16046,10 +16046,10 @@
         <v>53</v>
       </c>
       <c r="B51" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C51" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D51">
         <v>8</v>
@@ -16058,7 +16058,7 @@
         <v>103</v>
       </c>
       <c r="G51" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H51">
         <v>518</v>
@@ -16085,19 +16085,19 @@
         <v>54</v>
       </c>
       <c r="B52" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C52" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D52">
         <v>8</v>
       </c>
       <c r="E52" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G52" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H52">
         <v>281</v>
@@ -16109,7 +16109,7 @@
         <v>13</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L52" t="s">
         <v>160</v>
@@ -16124,10 +16124,10 @@
         <v>55</v>
       </c>
       <c r="B53" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C53" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D53">
         <v>8</v>
@@ -16163,19 +16163,19 @@
         <v>56</v>
       </c>
       <c r="B54" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C54" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D54">
         <v>8</v>
       </c>
       <c r="E54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G54" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H54">
         <v>223</v>
@@ -16187,7 +16187,7 @@
         <v>13</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L54" t="s">
         <v>160</v>
@@ -16202,16 +16202,16 @@
         <v>57</v>
       </c>
       <c r="B55" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C55" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D55">
         <v>8</v>
       </c>
       <c r="E55" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G55" t="s">
         <v>109</v>
@@ -16226,7 +16226,7 @@
         <v>13</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L55" t="s">
         <v>160</v>
@@ -16241,16 +16241,16 @@
         <v>58</v>
       </c>
       <c r="B56" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C56" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D56">
         <v>8</v>
       </c>
       <c r="E56" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G56" t="s">
         <v>109</v>
@@ -16265,7 +16265,7 @@
         <v>13</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L56" t="s">
         <v>160</v>
@@ -16280,10 +16280,10 @@
         <v>60</v>
       </c>
       <c r="B57" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C57" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D57">
         <v>8</v>
@@ -16319,19 +16319,19 @@
         <v>59</v>
       </c>
       <c r="B58" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C58" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D58">
         <v>8</v>
       </c>
       <c r="E58" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G58" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>13</v>
@@ -16343,7 +16343,7 @@
         <v>95</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L58" t="s">
         <v>160</v>
@@ -16361,7 +16361,7 @@
         <v>113</v>
       </c>
       <c r="C59" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D59">
         <v>9</v>
@@ -16373,16 +16373,16 @@
         <v>115</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J59" t="s">
         <v>116</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L59" t="s">
         <v>158</v>
@@ -16400,7 +16400,7 @@
         <v>113</v>
       </c>
       <c r="C60" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D60">
         <v>9</v>
@@ -16439,7 +16439,7 @@
         <v>113</v>
       </c>
       <c r="C61" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D61">
         <v>9</v>
@@ -16478,16 +16478,16 @@
         <v>113</v>
       </c>
       <c r="C62" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D62">
         <v>9</v>
       </c>
       <c r="E62" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G62" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>13</v>
@@ -16496,7 +16496,7 @@
         <v>13</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>13</v>
@@ -16514,7 +16514,7 @@
         <v>138</v>
       </c>
       <c r="C63" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D63">
         <v>11</v>
@@ -16526,16 +16526,16 @@
         <v>140</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J63" t="s">
         <v>141</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L63" t="s">
         <v>158</v>
@@ -16553,13 +16553,13 @@
         <v>138</v>
       </c>
       <c r="C64" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D64">
         <v>11</v>
       </c>
       <c r="E64" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G64" t="s">
         <v>91</v>
@@ -16568,13 +16568,13 @@
         <v>13</v>
       </c>
       <c r="I64" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="J64" t="s">
         <v>142</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L64" t="s">
         <v>160</v>
@@ -16592,16 +16592,16 @@
         <v>138</v>
       </c>
       <c r="C65" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D65">
         <v>11</v>
       </c>
       <c r="E65" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G65" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H65" s="6" t="s">
         <v>13</v>
@@ -16610,7 +16610,7 @@
         <v>13</v>
       </c>
       <c r="J65" s="13" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K65" s="6" t="s">
         <v>13</v>
@@ -16625,31 +16625,31 @@
         <v>68</v>
       </c>
       <c r="B66" t="s">
+        <v>298</v>
+      </c>
+      <c r="C66" t="s">
         <v>299</v>
-      </c>
-      <c r="C66" t="s">
-        <v>300</v>
       </c>
       <c r="D66">
         <v>12</v>
       </c>
       <c r="E66" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G66" t="s">
+        <v>268</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="J66" t="s">
         <v>269</v>
       </c>
-      <c r="H66" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="I66" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="J66" t="s">
-        <v>270</v>
-      </c>
       <c r="K66" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L66" t="s">
         <v>158</v>
@@ -16664,16 +16664,16 @@
         <v>69</v>
       </c>
       <c r="B67" t="s">
+        <v>298</v>
+      </c>
+      <c r="C67" t="s">
         <v>299</v>
-      </c>
-      <c r="C67" t="s">
-        <v>300</v>
       </c>
       <c r="D67">
         <v>12</v>
       </c>
       <c r="E67" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G67" t="s">
         <v>91</v>
@@ -16682,13 +16682,13 @@
         <v>13</v>
       </c>
       <c r="I67" t="s">
+        <v>271</v>
+      </c>
+      <c r="J67" t="s">
+        <v>270</v>
+      </c>
+      <c r="K67" s="4" t="s">
         <v>272</v>
-      </c>
-      <c r="J67" t="s">
-        <v>271</v>
-      </c>
-      <c r="K67" s="4" t="s">
-        <v>273</v>
       </c>
       <c r="L67" t="s">
         <v>160</v>
@@ -16703,19 +16703,19 @@
         <v>70</v>
       </c>
       <c r="B68" t="s">
+        <v>298</v>
+      </c>
+      <c r="C68" t="s">
         <v>299</v>
-      </c>
-      <c r="C68" t="s">
-        <v>300</v>
       </c>
       <c r="D68">
         <v>12</v>
       </c>
       <c r="E68" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G68" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>13</v>
@@ -16724,7 +16724,7 @@
         <v>13</v>
       </c>
       <c r="J68" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>13</v>
@@ -16739,31 +16739,31 @@
         <v>71</v>
       </c>
       <c r="B69" t="s">
+        <v>213</v>
+      </c>
+      <c r="C69" t="s">
         <v>214</v>
-      </c>
-      <c r="C69" t="s">
-        <v>215</v>
       </c>
       <c r="D69">
         <v>13</v>
       </c>
       <c r="E69" t="s">
+        <v>216</v>
+      </c>
+      <c r="G69" t="s">
         <v>217</v>
       </c>
-      <c r="G69" t="s">
-        <v>218</v>
-      </c>
       <c r="H69" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L69" t="s">
         <v>158</v>
@@ -16778,16 +16778,16 @@
         <v>72</v>
       </c>
       <c r="B70" t="s">
+        <v>213</v>
+      </c>
+      <c r="C70" t="s">
         <v>214</v>
-      </c>
-      <c r="C70" t="s">
-        <v>215</v>
       </c>
       <c r="D70">
         <v>13</v>
       </c>
       <c r="E70" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G70" t="s">
         <v>91</v>
@@ -16796,13 +16796,13 @@
         <v>13</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J70" t="s">
         <v>95</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L70" t="s">
         <v>160</v>
@@ -16817,16 +16817,16 @@
         <v>73</v>
       </c>
       <c r="B71" t="s">
+        <v>213</v>
+      </c>
+      <c r="C71" t="s">
         <v>214</v>
-      </c>
-      <c r="C71" t="s">
-        <v>215</v>
       </c>
       <c r="D71">
         <v>13</v>
       </c>
       <c r="E71" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G71" t="s">
         <v>109</v>
@@ -16835,13 +16835,13 @@
         <v>13</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J71" s="6" t="s">
         <v>13</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L71" t="s">
         <v>160</v>
@@ -16856,19 +16856,19 @@
         <v>74</v>
       </c>
       <c r="B72" t="s">
+        <v>213</v>
+      </c>
+      <c r="C72" t="s">
         <v>214</v>
-      </c>
-      <c r="C72" t="s">
-        <v>215</v>
       </c>
       <c r="D72">
         <v>13</v>
       </c>
       <c r="E72" t="s">
+        <v>293</v>
+      </c>
+      <c r="G72" t="s">
         <v>294</v>
-      </c>
-      <c r="G72" t="s">
-        <v>295</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>13</v>
@@ -16877,7 +16877,7 @@
         <v>13</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>13</v>
@@ -16910,10 +16910,10 @@
         <v>9</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J73" t="s">
         <v>127</v>
@@ -16949,10 +16949,10 @@
         <v>130</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J74" t="s">
         <v>131</v>
@@ -16982,22 +16982,22 @@
         <v>14</v>
       </c>
       <c r="E75" t="s">
+        <v>186</v>
+      </c>
+      <c r="G75" t="s">
         <v>187</v>
-      </c>
-      <c r="G75" t="s">
-        <v>188</v>
       </c>
       <c r="H75">
         <v>120</v>
       </c>
       <c r="I75" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J75" t="s">
         <v>133</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L75" t="s">
         <v>160</v>
@@ -17024,7 +17024,7 @@
         <v>134</v>
       </c>
       <c r="G76" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H76">
         <v>187</v>
@@ -17051,10 +17051,10 @@
         <v>79</v>
       </c>
       <c r="B77" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C77" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -17063,7 +17063,7 @@
         <v>143</v>
       </c>
       <c r="G77" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H77">
         <v>541</v>
@@ -17075,10 +17075,10 @@
         <v>13</v>
       </c>
       <c r="K77" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L77" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M77" t="str">
         <f t="shared" si="16"/>
@@ -17090,10 +17090,10 @@
         <v>80</v>
       </c>
       <c r="B78" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C78" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -17102,7 +17102,7 @@
         <v>144</v>
       </c>
       <c r="G78" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H78">
         <v>250</v>
@@ -17114,10 +17114,10 @@
         <v>13</v>
       </c>
       <c r="K78" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L78" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M78" t="str">
         <f t="shared" si="16"/>
@@ -17129,10 +17129,10 @@
         <v>81</v>
       </c>
       <c r="B79" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C79" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -17141,7 +17141,7 @@
         <v>145</v>
       </c>
       <c r="G79" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H79">
         <v>226</v>
@@ -17153,10 +17153,10 @@
         <v>13</v>
       </c>
       <c r="K79" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L79" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M79" t="str">
         <f t="shared" si="16"/>
@@ -17168,10 +17168,10 @@
         <v>82</v>
       </c>
       <c r="B80" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C80" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -17180,7 +17180,7 @@
         <v>146</v>
       </c>
       <c r="G80" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H80">
         <v>288</v>
@@ -17192,10 +17192,10 @@
         <v>13</v>
       </c>
       <c r="K80" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L80" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M80" t="str">
         <f t="shared" si="16"/>
@@ -17207,10 +17207,10 @@
         <v>83</v>
       </c>
       <c r="B81" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C81" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -17219,7 +17219,7 @@
         <v>147</v>
       </c>
       <c r="G81" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H81">
         <v>208</v>
@@ -17231,10 +17231,10 @@
         <v>13</v>
       </c>
       <c r="K81" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L81" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M81" t="str">
         <f t="shared" si="16"/>
@@ -17246,10 +17246,10 @@
         <v>84</v>
       </c>
       <c r="B82" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C82" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -17258,7 +17258,7 @@
         <v>148</v>
       </c>
       <c r="G82" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H82">
         <v>524</v>
@@ -17270,10 +17270,10 @@
         <v>13</v>
       </c>
       <c r="K82" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L82" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M82" t="str">
         <f t="shared" si="16"/>
@@ -17424,6 +17424,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FCEEF5D6F9A2C14292C82E7F88E7D4C7" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="770a5493e01cc46570af888c0fd11107">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6e07a911-1c82-455b-ae09-b73935b22a66" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="de63ad8f9259e2f5a7ae7a5921e0e8ad" ns2:_="">
     <xsd:import namespace="6e07a911-1c82-455b-ae09-b73935b22a66"/>
@@ -17555,22 +17570,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDCD3F55-29C2-4E12-8D9A-9EC0083C9C49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="6e07a911-1c82-455b-ae09-b73935b22a66"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C569B7B-6177-4C5F-B641-1220485D9B3F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4188865-1BAB-459E-8F28-5F6AB5F6EAC9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17586,28 +17610,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C569B7B-6177-4C5F-B641-1220485D9B3F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDCD3F55-29C2-4E12-8D9A-9EC0083C9C49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="6e07a911-1c82-455b-ae09-b73935b22a66"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/companydirectorypdf/companydir.xlsx
+++ b/companydirectorypdf/companydir.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nelso\Documents\GitHub\kwlivingrealtydrive\kwlrportal\companydirectorypdf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{669F11D5-078A-4D8B-9BBB-D4732D6120A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0CFD71B-6C94-40B3-9C86-1DE6F0377A57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-16440" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{AE6EE1E0-C559-4053-97E8-B14EEDB6E6F6}"/>
   </bookViews>
@@ -763,9 +763,6 @@
     <t>President &amp; C.L.O.</t>
   </si>
   <si>
-    <t>Vice Presidnet, New Homes, Broker</t>
-  </si>
-  <si>
     <t>Market Center Administrator, Executive Group Controller</t>
   </si>
   <si>
@@ -992,6 +989,9 @@
   </si>
   <si>
     <t>Senior Technical Specialist &amp; System Architect</t>
+  </si>
+  <si>
+    <t>Vice President, New Homes, Broker</t>
   </si>
 </sst>
 </file>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="H1" s="11"/>
       <c r="I1" s="11" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C10" s="3" t="str">
         <f>ContactData!G9</f>
-        <v>Vice Presidnet, New Homes, Broker</v>
+        <v>Vice President, New Homes, Broker</v>
       </c>
       <c r="D10" s="9" t="str">
         <f>IF(LEN(ContactData!I9)&lt;3,"",ContactData!I9)</f>
@@ -8529,7 +8529,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="C10" s="3" t="str">
         <f>ContactData!G9</f>
-        <v>Vice Presidnet, New Homes, Broker</v>
+        <v>Vice President, New Homes, Broker</v>
       </c>
       <c r="D10" s="9" t="str">
         <f>IF(LEN(ContactData!I9)&lt;3,"",ContactData!I9)</f>
@@ -14001,7 +14001,7 @@
         <v>168</v>
       </c>
       <c r="F1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G1" t="s">
         <v>149</v>
@@ -14081,7 +14081,7 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G3" t="s">
         <v>12</v>
@@ -14123,7 +14123,7 @@
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -14165,7 +14165,7 @@
         <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G5" t="s">
         <v>238</v>
@@ -14207,7 +14207,7 @@
         <v>208</v>
       </c>
       <c r="F6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G6" t="s">
         <v>239</v>
@@ -14222,7 +14222,7 @@
         <v>25</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L6" t="s">
         <v>160</v>
@@ -14249,7 +14249,7 @@
         <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G7" t="s">
         <v>21</v>
@@ -14264,7 +14264,7 @@
         <v>154</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L7" t="s">
         <v>160</v>
@@ -14291,10 +14291,10 @@
         <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H8">
         <v>502</v>
@@ -14333,10 +14333,10 @@
         <v>198</v>
       </c>
       <c r="F9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G9" t="s">
-        <v>240</v>
+        <v>316</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>13</v>
@@ -14348,14 +14348,14 @@
         <v>13</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L9" t="s">
         <v>160</v>
       </c>
       <c r="M9" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('8','1','Alan Cheung','Vice Presidnet, New Homes, Broker','---','(416) 669-0325','---','alancheung@livingrealtykw.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('8','1','Alan Cheung','Vice President, New Homes, Broker','---','(416) 669-0325','---','alancheung@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -14375,10 +14375,10 @@
         <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>13</v>
@@ -14390,7 +14390,7 @@
         <v>13</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L10" t="s">
         <v>160</v>
@@ -14417,7 +14417,7 @@
         <v>219</v>
       </c>
       <c r="F11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G11" t="s">
         <v>161</v>
@@ -14459,7 +14459,7 @@
         <v>186</v>
       </c>
       <c r="G12" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H12">
         <v>504</v>
@@ -14471,7 +14471,7 @@
         <v>30</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L12" t="s">
         <v>160</v>
@@ -14498,7 +14498,7 @@
         <v>31</v>
       </c>
       <c r="F13" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G13" t="s">
         <v>32</v>
@@ -14537,13 +14537,13 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
+        <v>303</v>
+      </c>
+      <c r="F14" t="s">
+        <v>284</v>
+      </c>
+      <c r="G14" t="s">
         <v>304</v>
-      </c>
-      <c r="F14" t="s">
-        <v>285</v>
-      </c>
-      <c r="G14" t="s">
-        <v>305</v>
       </c>
       <c r="H14">
         <v>282</v>
@@ -14555,7 +14555,7 @@
         <v>13</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L14" t="s">
         <v>160</v>
@@ -14582,7 +14582,7 @@
         <v>61</v>
       </c>
       <c r="F15" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G15" t="s">
         <v>212</v>
@@ -14597,7 +14597,7 @@
         <v>13</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L15" t="s">
         <v>160</v>
@@ -14624,7 +14624,7 @@
         <v>23</v>
       </c>
       <c r="F16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G16" t="s">
         <v>225</v>
@@ -14639,7 +14639,7 @@
         <v>13</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L16" t="s">
         <v>160</v>
@@ -14666,7 +14666,7 @@
         <v>39</v>
       </c>
       <c r="F17" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G17" t="s">
         <v>40</v>
@@ -14681,7 +14681,7 @@
         <v>41</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L17" t="s">
         <v>160</v>
@@ -14708,7 +14708,7 @@
         <v>42</v>
       </c>
       <c r="F18" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G18" t="s">
         <v>37</v>
@@ -14723,7 +14723,7 @@
         <v>38</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L18" t="s">
         <v>160</v>
@@ -14750,7 +14750,7 @@
         <v>77</v>
       </c>
       <c r="F19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G19" t="s">
         <v>37</v>
@@ -14765,7 +14765,7 @@
         <v>13</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L19" t="s">
         <v>160</v>
@@ -14789,10 +14789,10 @@
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F20" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G20" t="s">
         <v>163</v>
@@ -14807,7 +14807,7 @@
         <v>36</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L20" t="s">
         <v>160</v>
@@ -14834,7 +14834,7 @@
         <v>43</v>
       </c>
       <c r="F21" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G21" t="s">
         <v>44</v>
@@ -14849,7 +14849,7 @@
         <v>45</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L21" t="s">
         <v>160</v>
@@ -14876,7 +14876,7 @@
         <v>202</v>
       </c>
       <c r="F22" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G22" t="s">
         <v>203</v>
@@ -14891,7 +14891,7 @@
         <v>13</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L22" t="s">
         <v>160</v>
@@ -14918,10 +14918,10 @@
         <v>46</v>
       </c>
       <c r="F23" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G23" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H23">
         <v>522</v>
@@ -14933,7 +14933,7 @@
         <v>48</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L23" t="s">
         <v>160</v>
@@ -14972,7 +14972,7 @@
         <v>48</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L24" t="s">
         <v>160</v>
@@ -14999,7 +14999,7 @@
         <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G25" t="s">
         <v>53</v>
@@ -15014,7 +15014,7 @@
         <v>54</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L25" t="s">
         <v>158</v>
@@ -15041,7 +15041,7 @@
         <v>55</v>
       </c>
       <c r="F26" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G26" t="s">
         <v>56</v>
@@ -15056,7 +15056,7 @@
         <v>13</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L26" t="s">
         <v>160</v>
@@ -15083,7 +15083,7 @@
         <v>59</v>
       </c>
       <c r="F27" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G27" t="s">
         <v>164</v>
@@ -15098,7 +15098,7 @@
         <v>58</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L27" t="s">
         <v>160</v>
@@ -15125,7 +15125,7 @@
         <v>224</v>
       </c>
       <c r="F28" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G28" t="s">
         <v>60</v>
@@ -15140,7 +15140,7 @@
         <v>58</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L28" t="s">
         <v>160</v>
@@ -15167,7 +15167,7 @@
         <v>68</v>
       </c>
       <c r="F29" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G29" t="s">
         <v>152</v>
@@ -15182,7 +15182,7 @@
         <v>69</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L29" t="s">
         <v>158</v>
@@ -15206,10 +15206,10 @@
         <v>4</v>
       </c>
       <c r="E30" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F30" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G30" t="s">
         <v>70</v>
@@ -15224,7 +15224,7 @@
         <v>13</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L30" t="s">
         <v>160</v>
@@ -15248,10 +15248,10 @@
         <v>4</v>
       </c>
       <c r="E31" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F31" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G31" t="s">
         <v>60</v>
@@ -15266,7 +15266,7 @@
         <v>71</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L31" t="s">
         <v>160</v>
@@ -15290,10 +15290,10 @@
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F32" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G32" t="s">
         <v>60</v>
@@ -15308,7 +15308,7 @@
         <v>71</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="L32" t="s">
         <v>160</v>
@@ -15335,7 +15335,7 @@
         <v>73</v>
       </c>
       <c r="F33" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G33" t="s">
         <v>9</v>
@@ -15350,7 +15350,7 @@
         <v>74</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L33" t="s">
         <v>158</v>
@@ -15377,7 +15377,7 @@
         <v>76</v>
       </c>
       <c r="F34" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G34" t="s">
         <v>75</v>
@@ -15392,7 +15392,7 @@
         <v>13</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L34" t="s">
         <v>160</v>
@@ -15419,7 +15419,7 @@
         <v>79</v>
       </c>
       <c r="F35" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G35" t="s">
         <v>60</v>
@@ -15434,7 +15434,7 @@
         <v>19</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L35" t="s">
         <v>160</v>
@@ -15461,7 +15461,7 @@
         <v>228</v>
       </c>
       <c r="F36" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G36" t="s">
         <v>221</v>
@@ -15476,7 +15476,7 @@
         <v>63</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L36" t="s">
         <v>158</v>
@@ -15500,25 +15500,25 @@
         <v>3</v>
       </c>
       <c r="E37" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F37" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G37" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I37" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J37" s="6" t="s">
         <v>13</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="L37" t="s">
         <v>160</v>
@@ -15545,7 +15545,7 @@
         <v>230</v>
       </c>
       <c r="F38" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G38" t="s">
         <v>60</v>
@@ -15560,7 +15560,7 @@
         <v>66</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L38" t="s">
         <v>160</v>
@@ -15626,7 +15626,7 @@
         <v>17</v>
       </c>
       <c r="F40" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G40" t="s">
         <v>84</v>
@@ -15938,7 +15938,7 @@
         <v>8</v>
       </c>
       <c r="E48" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G48" t="s">
         <v>91</v>
@@ -15947,13 +15947,13 @@
         <v>520</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J48" t="s">
         <v>95</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L48" t="s">
         <v>160</v>
@@ -15977,7 +15977,7 @@
         <v>8</v>
       </c>
       <c r="E49" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G49" t="s">
         <v>233</v>
@@ -15986,13 +15986,13 @@
         <v>168</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J49" t="s">
         <v>95</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L49" t="s">
         <v>160</v>
@@ -16058,7 +16058,7 @@
         <v>103</v>
       </c>
       <c r="G51" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H51">
         <v>518</v>
@@ -16175,7 +16175,7 @@
         <v>204</v>
       </c>
       <c r="G54" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H54">
         <v>223</v>
@@ -16250,7 +16250,7 @@
         <v>8</v>
       </c>
       <c r="E56" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G56" t="s">
         <v>109</v>
@@ -16265,7 +16265,7 @@
         <v>13</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L56" t="s">
         <v>160</v>
@@ -16328,7 +16328,7 @@
         <v>8</v>
       </c>
       <c r="E58" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G58" t="s">
         <v>182</v>
@@ -16343,7 +16343,7 @@
         <v>95</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L58" t="s">
         <v>160</v>
@@ -16484,10 +16484,10 @@
         <v>9</v>
       </c>
       <c r="E62" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G62" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>13</v>
@@ -16496,7 +16496,7 @@
         <v>13</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>13</v>
@@ -16598,10 +16598,10 @@
         <v>11</v>
       </c>
       <c r="E65" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G65" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H65" s="6" t="s">
         <v>13</v>
@@ -16610,7 +16610,7 @@
         <v>13</v>
       </c>
       <c r="J65" s="13" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="K65" s="6" t="s">
         <v>13</v>
@@ -16625,19 +16625,19 @@
         <v>68</v>
       </c>
       <c r="B66" t="s">
+        <v>297</v>
+      </c>
+      <c r="C66" t="s">
         <v>298</v>
-      </c>
-      <c r="C66" t="s">
-        <v>299</v>
       </c>
       <c r="D66">
         <v>12</v>
       </c>
       <c r="E66" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G66" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H66" s="6" t="s">
         <v>195</v>
@@ -16646,7 +16646,7 @@
         <v>195</v>
       </c>
       <c r="J66" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>195</v>
@@ -16664,16 +16664,16 @@
         <v>69</v>
       </c>
       <c r="B67" t="s">
+        <v>297</v>
+      </c>
+      <c r="C67" t="s">
         <v>298</v>
-      </c>
-      <c r="C67" t="s">
-        <v>299</v>
       </c>
       <c r="D67">
         <v>12</v>
       </c>
       <c r="E67" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G67" t="s">
         <v>91</v>
@@ -16682,13 +16682,13 @@
         <v>13</v>
       </c>
       <c r="I67" t="s">
+        <v>270</v>
+      </c>
+      <c r="J67" t="s">
+        <v>269</v>
+      </c>
+      <c r="K67" s="4" t="s">
         <v>271</v>
-      </c>
-      <c r="J67" t="s">
-        <v>270</v>
-      </c>
-      <c r="K67" s="4" t="s">
-        <v>272</v>
       </c>
       <c r="L67" t="s">
         <v>160</v>
@@ -16703,19 +16703,19 @@
         <v>70</v>
       </c>
       <c r="B68" t="s">
+        <v>297</v>
+      </c>
+      <c r="C68" t="s">
         <v>298</v>
-      </c>
-      <c r="C68" t="s">
-        <v>299</v>
       </c>
       <c r="D68">
         <v>12</v>
       </c>
       <c r="E68" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G68" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>13</v>
@@ -16724,7 +16724,7 @@
         <v>13</v>
       </c>
       <c r="J68" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>13</v>
@@ -16865,10 +16865,10 @@
         <v>13</v>
       </c>
       <c r="E72" t="s">
+        <v>292</v>
+      </c>
+      <c r="G72" t="s">
         <v>293</v>
-      </c>
-      <c r="G72" t="s">
-        <v>294</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>13</v>
@@ -16877,7 +16877,7 @@
         <v>13</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>13</v>
@@ -17424,21 +17424,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FCEEF5D6F9A2C14292C82E7F88E7D4C7" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="770a5493e01cc46570af888c0fd11107">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6e07a911-1c82-455b-ae09-b73935b22a66" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="de63ad8f9259e2f5a7ae7a5921e0e8ad" ns2:_="">
     <xsd:import namespace="6e07a911-1c82-455b-ae09-b73935b22a66"/>
@@ -17570,31 +17555,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDCD3F55-29C2-4E12-8D9A-9EC0083C9C49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="6e07a911-1c82-455b-ae09-b73935b22a66"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C569B7B-6177-4C5F-B641-1220485D9B3F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4188865-1BAB-459E-8F28-5F6AB5F6EAC9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17610,4 +17586,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C569B7B-6177-4C5F-B641-1220485D9B3F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDCD3F55-29C2-4E12-8D9A-9EC0083C9C49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="6e07a911-1c82-455b-ae09-b73935b22a66"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/companydirectorypdf/companydir.xlsx
+++ b/companydirectorypdf/companydir.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nelso\Documents\GitHub\kwlivingrealtydrive\kwlrportal\companydirectorypdf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0CFD71B-6C94-40B3-9C86-1DE6F0377A57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86FACFF-339B-40FD-B720-E9D85609D651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-16440" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{AE6EE1E0-C559-4053-97E8-B14EEDB6E6F6}"/>
+    <workbookView xWindow="-90" yWindow="-16440" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{AE6EE1E0-C559-4053-97E8-B14EEDB6E6F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Letter Size" sheetId="8" r:id="rId1"/>
@@ -19,8 +19,8 @@
     <sheet name="Sorting" sheetId="3" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Legal Size'!$A$1:$F$77</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Letter Size'!$A$1:$I$76</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Legal Size'!$A$1:$F$78</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Letter Size'!$A$1:$I$77</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="318">
   <si>
     <t>Company Directory</t>
   </si>
@@ -742,9 +742,6 @@
     <t>T: (437)-533-1208</t>
   </si>
   <si>
-    <t>Assistant Property Manager</t>
-  </si>
-  <si>
     <t>Rebecca Lau</t>
   </si>
   <si>
@@ -985,13 +982,19 @@
     <t>gusb@livcontruction.ca</t>
   </si>
   <si>
-    <t>Update Date: Apr 8, 2026</t>
-  </si>
-  <si>
     <t>Senior Technical Specialist &amp; System Architect</t>
   </si>
   <si>
     <t>Vice President, New Homes, Broker</t>
+  </si>
+  <si>
+    <t>Stanley Wu</t>
+  </si>
+  <si>
+    <t>stanleyw@livingproperties.com</t>
+  </si>
+  <si>
+    <t>Update Date: Apr 21, 2026</t>
   </si>
 </sst>
 </file>
@@ -1645,8 +1648,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{64C18C99-1B03-459F-9F00-A5922F0E9AD8}" name="Table2" displayName="Table2" ref="A1:M82" totalsRowShown="0">
-  <autoFilter ref="A1:M82" xr:uid="{64C18C99-1B03-459F-9F00-A5922F0E9AD8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{64C18C99-1B03-459F-9F00-A5922F0E9AD8}" name="Table2" displayName="Table2" ref="A1:M83" totalsRowShown="0">
+  <autoFilter ref="A1:M83" xr:uid="{64C18C99-1B03-459F-9F00-A5922F0E9AD8}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{84EE687C-25F0-49A0-A543-1CDE4F771B0E}" name="DisplayOrder" dataDxfId="33"/>
     <tableColumn id="2" xr3:uid="{289F04FD-E089-4D5D-A4E6-C7BA80BB6642}" name="OfficeCode"/>
@@ -1968,7 +1971,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L361"/>
+  <dimension ref="A1:L362"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.44140625" style="8" customWidth="1"/>
@@ -1991,7 +1994,7 @@
       </c>
       <c r="H1" s="11"/>
       <c r="I1" s="11" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
@@ -2051,11 +2054,11 @@
       </c>
       <c r="G3"/>
       <c r="H3" t="str">
-        <f>ContactData!E77</f>
+        <f>ContactData!E78</f>
         <v>Lunch Room</v>
       </c>
       <c r="I3">
-        <f>ContactData!H77</f>
+        <f>ContactData!H78</f>
         <v>541</v>
       </c>
       <c r="J3"/>
@@ -2089,11 +2092,11 @@
       </c>
       <c r="G4"/>
       <c r="H4" t="str">
-        <f>ContactData!E78</f>
+        <f>ContactData!E79</f>
         <v>Markham Room</v>
       </c>
       <c r="I4">
-        <f>ContactData!H78</f>
+        <f>ContactData!H79</f>
         <v>250</v>
       </c>
       <c r="J4"/>
@@ -2127,11 +2130,11 @@
       </c>
       <c r="G5"/>
       <c r="H5" t="str">
-        <f>ContactData!E79</f>
+        <f>ContactData!E80</f>
         <v>Mississauga Room</v>
       </c>
       <c r="I5">
-        <f>ContactData!H79</f>
+        <f>ContactData!H80</f>
         <v>226</v>
       </c>
       <c r="J5"/>
@@ -2165,11 +2168,11 @@
       </c>
       <c r="G6"/>
       <c r="H6" t="str">
-        <f>ContactData!E80</f>
+        <f>ContactData!E81</f>
         <v>The Living Room</v>
       </c>
       <c r="I6">
-        <f>ContactData!H80</f>
+        <f>ContactData!H81</f>
         <v>288</v>
       </c>
       <c r="J6"/>
@@ -2203,11 +2206,11 @@
       </c>
       <c r="G7"/>
       <c r="H7" t="str">
-        <f>ContactData!E81</f>
+        <f>ContactData!E82</f>
         <v>Toronto Room</v>
       </c>
       <c r="I7">
-        <f>ContactData!H81</f>
+        <f>ContactData!H82</f>
         <v>208</v>
       </c>
       <c r="J7"/>
@@ -2241,11 +2244,11 @@
       </c>
       <c r="G8"/>
       <c r="H8" t="str">
-        <f>ContactData!E82</f>
+        <f>ContactData!E83</f>
         <v>York Room</v>
       </c>
       <c r="I8">
-        <f>ContactData!H82</f>
+        <f>ContactData!H83</f>
         <v>524</v>
       </c>
       <c r="J8"/>
@@ -3575,7 +3578,7 @@
       </c>
       <c r="C50" s="3" t="str">
         <f>ContactData!G49</f>
-        <v>Assistant Property Manager</v>
+        <v>Property Manager</v>
       </c>
       <c r="D50" s="9" t="str">
         <f>IF(LEN(ContactData!I49)&lt;3,"",ContactData!I49)</f>
@@ -3599,15 +3602,15 @@
     <row r="51" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="9">
         <f>IF(LEN(ContactData!H50)&lt;3,"",ContactData!H50)</f>
-        <v>210</v>
+        <v>168</v>
       </c>
       <c r="B51" s="3" t="str">
         <f>ContactData!E50</f>
-        <v>Loretta Leung</v>
+        <v>Stanley Wu</v>
       </c>
       <c r="C51" s="3" t="str">
         <f>ContactData!G50</f>
-        <v>Executive Assistant</v>
+        <v>Property Manager</v>
       </c>
       <c r="D51" s="9" t="str">
         <f>IF(LEN(ContactData!I50)&lt;3,"",ContactData!I50)</f>
@@ -3615,11 +3618,11 @@
       </c>
       <c r="E51" s="3" t="str">
         <f>ContactData!J50</f>
-        <v>---</v>
+        <v>(905) 477-2090</v>
       </c>
       <c r="F51" s="3" t="str">
         <f>IF(LEN(ContactData!K50)&lt;3,"",ContactData!K50)</f>
-        <v>lorettal@livingproperties.com</v>
+        <v>stanleyw@livingproperties.com</v>
       </c>
       <c r="G51"/>
       <c r="H51"/>
@@ -3631,15 +3634,15 @@
     <row r="52" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="9">
         <f>IF(LEN(ContactData!H51)&lt;3,"",ContactData!H51)</f>
-        <v>518</v>
+        <v>210</v>
       </c>
       <c r="B52" s="3" t="str">
         <f>ContactData!E51</f>
-        <v>Simon Li</v>
+        <v>Loretta Leung</v>
       </c>
       <c r="C52" s="3" t="str">
         <f>ContactData!G51</f>
-        <v>Senior Accountant</v>
+        <v>Executive Assistant</v>
       </c>
       <c r="D52" s="9" t="str">
         <f>IF(LEN(ContactData!I51)&lt;3,"",ContactData!I51)</f>
@@ -3647,11 +3650,11 @@
       </c>
       <c r="E52" s="3" t="str">
         <f>ContactData!J51</f>
-        <v>(905) 752-3518</v>
+        <v>---</v>
       </c>
       <c r="F52" s="3" t="str">
         <f>IF(LEN(ContactData!K51)&lt;3,"",ContactData!K51)</f>
-        <v>simonl@livingproperties.com</v>
+        <v>lorettal@livingproperties.com</v>
       </c>
       <c r="G52"/>
       <c r="H52"/>
@@ -3663,15 +3666,15 @@
     <row r="53" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="9">
         <f>IF(LEN(ContactData!H52)&lt;3,"",ContactData!H52)</f>
-        <v>281</v>
+        <v>518</v>
       </c>
       <c r="B53" s="3" t="str">
         <f>ContactData!E52</f>
-        <v>Nicole Leung</v>
+        <v>Simon Li</v>
       </c>
       <c r="C53" s="3" t="str">
         <f>ContactData!G52</f>
-        <v>Property Accountant</v>
+        <v>Senior Accountant</v>
       </c>
       <c r="D53" s="9" t="str">
         <f>IF(LEN(ContactData!I52)&lt;3,"",ContactData!I52)</f>
@@ -3679,11 +3682,11 @@
       </c>
       <c r="E53" s="3" t="str">
         <f>ContactData!J52</f>
-        <v>---</v>
+        <v>(905) 752-3518</v>
       </c>
       <c r="F53" s="3" t="str">
         <f>IF(LEN(ContactData!K52)&lt;3,"",ContactData!K52)</f>
-        <v>nicolel@livingproperties.com</v>
+        <v>simonl@livingproperties.com</v>
       </c>
       <c r="G53"/>
       <c r="H53"/>
@@ -3695,15 +3698,15 @@
     <row r="54" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="9">
         <f>IF(LEN(ContactData!H53)&lt;3,"",ContactData!H53)</f>
-        <v>523</v>
+        <v>281</v>
       </c>
       <c r="B54" s="3" t="str">
         <f>ContactData!E53</f>
-        <v>Vivian Lum</v>
+        <v>Nicole Leung</v>
       </c>
       <c r="C54" s="3" t="str">
         <f>ContactData!G53</f>
-        <v>Accounts Receivable Clerk</v>
+        <v>Property Accountant</v>
       </c>
       <c r="D54" s="9" t="str">
         <f>IF(LEN(ContactData!I53)&lt;3,"",ContactData!I53)</f>
@@ -3711,11 +3714,11 @@
       </c>
       <c r="E54" s="3" t="str">
         <f>ContactData!J53</f>
-        <v>(905) 752-3523</v>
+        <v>---</v>
       </c>
       <c r="F54" s="3" t="str">
         <f>IF(LEN(ContactData!K53)&lt;3,"",ContactData!K53)</f>
-        <v>vivianl@livingproperties.com</v>
+        <v>nicolel@livingproperties.com</v>
       </c>
       <c r="G54"/>
       <c r="H54"/>
@@ -3727,15 +3730,15 @@
     <row r="55" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="9">
         <f>IF(LEN(ContactData!H54)&lt;3,"",ContactData!H54)</f>
-        <v>223</v>
+        <v>523</v>
       </c>
       <c r="B55" s="3" t="str">
         <f>ContactData!E54</f>
-        <v>Jessica Lee</v>
+        <v>Vivian Lum</v>
       </c>
       <c r="C55" s="3" t="str">
         <f>ContactData!G54</f>
-        <v xml:space="preserve">Accounting Clerk </v>
+        <v>Accounts Receivable Clerk</v>
       </c>
       <c r="D55" s="9" t="str">
         <f>IF(LEN(ContactData!I54)&lt;3,"",ContactData!I54)</f>
@@ -3743,11 +3746,11 @@
       </c>
       <c r="E55" s="3" t="str">
         <f>ContactData!J54</f>
-        <v>---</v>
+        <v>(905) 752-3523</v>
       </c>
       <c r="F55" s="3" t="str">
         <f>IF(LEN(ContactData!K54)&lt;3,"",ContactData!K54)</f>
-        <v>jessical@livingproperties.com</v>
+        <v>vivianl@livingproperties.com</v>
       </c>
       <c r="G55"/>
       <c r="H55"/>
@@ -3759,15 +3762,15 @@
     <row r="56" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="9">
         <f>IF(LEN(ContactData!H55)&lt;3,"",ContactData!H55)</f>
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="B56" s="3" t="str">
         <f>ContactData!E55</f>
-        <v>Rebecca Lau</v>
+        <v>Jessica Lee</v>
       </c>
       <c r="C56" s="3" t="str">
         <f>ContactData!G55</f>
-        <v>Administrative Assistant</v>
+        <v xml:space="preserve">Accounting Clerk </v>
       </c>
       <c r="D56" s="9" t="str">
         <f>IF(LEN(ContactData!I55)&lt;3,"",ContactData!I55)</f>
@@ -3779,7 +3782,7 @@
       </c>
       <c r="F56" s="3" t="str">
         <f>IF(LEN(ContactData!K55)&lt;3,"",ContactData!K55)</f>
-        <v>rebeccal@livingproperties.com</v>
+        <v>jessical@livingproperties.com</v>
       </c>
       <c r="G56"/>
       <c r="H56"/>
@@ -3791,11 +3794,11 @@
     <row r="57" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="9">
         <f>IF(LEN(ContactData!H56)&lt;3,"",ContactData!H56)</f>
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B57" s="3" t="str">
         <f>ContactData!E56</f>
-        <v>Kelvin Chan</v>
+        <v>Rebecca Lau</v>
       </c>
       <c r="C57" s="3" t="str">
         <f>ContactData!G56</f>
@@ -3811,7 +3814,7 @@
       </c>
       <c r="F57" s="3" t="str">
         <f>IF(LEN(ContactData!K56)&lt;3,"",ContactData!K56)</f>
-        <v>kelvinc@livingproperties.com</v>
+        <v>rebeccal@livingproperties.com</v>
       </c>
       <c r="G57"/>
       <c r="H57"/>
@@ -3823,15 +3826,15 @@
     <row r="58" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="9">
         <f>IF(LEN(ContactData!H57)&lt;3,"",ContactData!H57)</f>
-        <v>229</v>
+        <v>182</v>
       </c>
       <c r="B58" s="3" t="str">
         <f>ContactData!E57</f>
-        <v>Matthew Wong</v>
+        <v>Kelvin Chan</v>
       </c>
       <c r="C58" s="3" t="str">
         <f>ContactData!G57</f>
-        <v>Accounting Clerk</v>
+        <v>Administrative Assistant</v>
       </c>
       <c r="D58" s="9" t="str">
         <f>IF(LEN(ContactData!I57)&lt;3,"",ContactData!I57)</f>
@@ -3843,7 +3846,7 @@
       </c>
       <c r="F58" s="3" t="str">
         <f>IF(LEN(ContactData!K57)&lt;3,"",ContactData!K57)</f>
-        <v>mattheww@livingproperties.com</v>
+        <v>kelvinc@livingproperties.com</v>
       </c>
       <c r="G58"/>
       <c r="H58"/>
@@ -3853,17 +3856,17 @@
       <c r="L58"/>
     </row>
     <row r="59" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A59" s="9" t="str">
+      <c r="A59" s="9">
         <f>IF(LEN(ContactData!H58)&lt;3,"",ContactData!H58)</f>
-        <v>---</v>
+        <v>229</v>
       </c>
       <c r="B59" s="3" t="str">
         <f>ContactData!E58</f>
-        <v>Gus B</v>
+        <v>Matthew Wong</v>
       </c>
       <c r="C59" s="3" t="str">
         <f>ContactData!G58</f>
-        <v>Handyman</v>
+        <v>Accounting Clerk</v>
       </c>
       <c r="D59" s="9" t="str">
         <f>IF(LEN(ContactData!I58)&lt;3,"",ContactData!I58)</f>
@@ -3871,11 +3874,11 @@
       </c>
       <c r="E59" s="3" t="str">
         <f>ContactData!J58</f>
-        <v>(905) 477-2090</v>
+        <v>---</v>
       </c>
       <c r="F59" s="3" t="str">
         <f>IF(LEN(ContactData!K58)&lt;3,"",ContactData!K58)</f>
-        <v>gusb@livcontruction.ca</v>
+        <v>mattheww@livingproperties.com</v>
       </c>
       <c r="G59"/>
       <c r="H59"/>
@@ -3887,27 +3890,27 @@
     <row r="60" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="str">
         <f>IF(LEN(ContactData!H59)&lt;3,"",ContactData!H59)</f>
-        <v/>
+        <v>---</v>
       </c>
       <c r="B60" s="3" t="str">
         <f>ContactData!E59</f>
-        <v>Centro Towers Office</v>
+        <v>Gus B</v>
       </c>
       <c r="C60" s="3" t="str">
         <f>ContactData!G59</f>
-        <v>25 Town Centre Crt, Scarborough, ON, M1P 0B4</v>
+        <v>Handyman</v>
       </c>
       <c r="D60" s="9" t="str">
         <f>IF(LEN(ContactData!I59)&lt;3,"",ContactData!I59)</f>
-        <v/>
+        <v>---</v>
       </c>
       <c r="E60" s="3" t="str">
         <f>ContactData!J59</f>
-        <v>T: (416) 290-1242</v>
+        <v>(905) 477-2090</v>
       </c>
       <c r="F60" s="3" t="str">
         <f>IF(LEN(ContactData!K59)&lt;3,"",ContactData!K59)</f>
-        <v/>
+        <v>gusb@livcontruction.ca</v>
       </c>
       <c r="G60"/>
       <c r="H60"/>
@@ -3919,27 +3922,27 @@
     <row r="61" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="str">
         <f>IF(LEN(ContactData!H60)&lt;3,"",ContactData!H60)</f>
-        <v>---</v>
+        <v/>
       </c>
       <c r="B61" s="3" t="str">
         <f>ContactData!E60</f>
-        <v>Henry Fu</v>
+        <v>Centro Towers Office</v>
       </c>
       <c r="C61" s="3" t="str">
         <f>ContactData!G60</f>
-        <v>Property Manager</v>
+        <v>25 Town Centre Crt, Scarborough, ON, M1P 0B4</v>
       </c>
       <c r="D61" s="9" t="str">
         <f>IF(LEN(ContactData!I60)&lt;3,"",ContactData!I60)</f>
-        <v>(416) 278-2953</v>
+        <v/>
       </c>
       <c r="E61" s="3" t="str">
         <f>ContactData!J60</f>
-        <v>(416) 290-1242</v>
+        <v>T: (416) 290-1242</v>
       </c>
       <c r="F61" s="3" t="str">
         <f>IF(LEN(ContactData!K60)&lt;3,"",ContactData!K60)</f>
-        <v>henry@centrotowers.com</v>
+        <v/>
       </c>
       <c r="G61"/>
       <c r="H61"/>
@@ -3955,15 +3958,15 @@
       </c>
       <c r="B62" s="3" t="str">
         <f>ContactData!E61</f>
-        <v>Sophia Yip</v>
+        <v>Henry Fu</v>
       </c>
       <c r="C62" s="3" t="str">
         <f>ContactData!G61</f>
-        <v>Property Administrator</v>
+        <v>Property Manager</v>
       </c>
       <c r="D62" s="9" t="str">
         <f>IF(LEN(ContactData!I61)&lt;3,"",ContactData!I61)</f>
-        <v>---</v>
+        <v>(416) 278-2953</v>
       </c>
       <c r="E62" s="3" t="str">
         <f>ContactData!J61</f>
@@ -3971,7 +3974,7 @@
       </c>
       <c r="F62" s="3" t="str">
         <f>IF(LEN(ContactData!K61)&lt;3,"",ContactData!K61)</f>
-        <v>sophia@centrotowers.com</v>
+        <v>henry@centrotowers.com</v>
       </c>
       <c r="G62"/>
       <c r="H62"/>
@@ -3987,11 +3990,11 @@
       </c>
       <c r="B63" s="3" t="str">
         <f>ContactData!E62</f>
-        <v xml:space="preserve">Security Desk </v>
+        <v>Sophia Yip</v>
       </c>
       <c r="C63" s="3" t="str">
         <f>ContactData!G62</f>
-        <v xml:space="preserve">Centro Security Desk </v>
+        <v>Property Administrator</v>
       </c>
       <c r="D63" s="9" t="str">
         <f>IF(LEN(ContactData!I62)&lt;3,"",ContactData!I62)</f>
@@ -3999,11 +4002,11 @@
       </c>
       <c r="E63" s="3" t="str">
         <f>ContactData!J62</f>
-        <v>(416) 296-0099</v>
+        <v>(416) 290-1242</v>
       </c>
       <c r="F63" s="3" t="str">
         <f>IF(LEN(ContactData!K62)&lt;3,"",ContactData!K62)</f>
-        <v>---</v>
+        <v>sophia@centrotowers.com</v>
       </c>
       <c r="G63"/>
       <c r="H63"/>
@@ -4015,27 +4018,27 @@
     <row r="64" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="str">
         <f>IF(LEN(ContactData!H63)&lt;3,"",ContactData!H63)</f>
-        <v/>
+        <v>---</v>
       </c>
       <c r="B64" s="3" t="str">
         <f>ContactData!E63</f>
-        <v>EQ1 Office</v>
+        <v xml:space="preserve">Security Desk </v>
       </c>
       <c r="C64" s="3" t="str">
         <f>ContactData!G63</f>
-        <v>70 Town Centre Court, Scarborough, ON, M1P 0B2</v>
+        <v xml:space="preserve">Centro Security Desk </v>
       </c>
       <c r="D64" s="9" t="str">
         <f>IF(LEN(ContactData!I63)&lt;3,"",ContactData!I63)</f>
-        <v/>
+        <v>---</v>
       </c>
       <c r="E64" s="3" t="str">
         <f>ContactData!J63</f>
-        <v xml:space="preserve">T: (416) 279-0603 </v>
+        <v>(416) 296-0099</v>
       </c>
       <c r="F64" s="3" t="str">
         <f>IF(LEN(ContactData!K63)&lt;3,"",ContactData!K63)</f>
-        <v>eq1@livingproperties.com</v>
+        <v>---</v>
       </c>
       <c r="G64"/>
       <c r="H64"/>
@@ -4047,27 +4050,27 @@
     <row r="65" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="9" t="str">
         <f>IF(LEN(ContactData!H64)&lt;3,"",ContactData!H64)</f>
-        <v>---</v>
+        <v/>
       </c>
       <c r="B65" s="3" t="str">
         <f>ContactData!E64</f>
-        <v>Ming Ip</v>
+        <v>EQ1 Office</v>
       </c>
       <c r="C65" s="3" t="str">
         <f>ContactData!G64</f>
-        <v>Property Manager</v>
+        <v>70 Town Centre Court, Scarborough, ON, M1P 0B2</v>
       </c>
       <c r="D65" s="9" t="str">
         <f>IF(LEN(ContactData!I64)&lt;3,"",ContactData!I64)</f>
-        <v>(647) 286-0147</v>
+        <v/>
       </c>
       <c r="E65" s="3" t="str">
         <f>ContactData!J64</f>
-        <v xml:space="preserve">(416) 279-0603 </v>
+        <v xml:space="preserve">T: (416) 279-0603 </v>
       </c>
       <c r="F65" s="3" t="str">
         <f>IF(LEN(ContactData!K64)&lt;3,"",ContactData!K64)</f>
-        <v>eq1manager@livingproperties.com</v>
+        <v>eq1@livingproperties.com</v>
       </c>
       <c r="G65"/>
       <c r="H65"/>
@@ -4083,23 +4086,23 @@
       </c>
       <c r="B66" s="3" t="str">
         <f>ContactData!E65</f>
-        <v xml:space="preserve">Security Desk </v>
+        <v>Ming Ip</v>
       </c>
       <c r="C66" s="3" t="str">
         <f>ContactData!G65</f>
-        <v xml:space="preserve">EQ1 Security Desk </v>
+        <v>Property Manager</v>
       </c>
       <c r="D66" s="9" t="str">
         <f>IF(LEN(ContactData!I65)&lt;3,"",ContactData!I65)</f>
-        <v>---</v>
+        <v>(647) 286-0147</v>
       </c>
       <c r="E66" s="3" t="str">
         <f>ContactData!J65</f>
-        <v>(416) 279-1894</v>
+        <v xml:space="preserve">(416) 279-0603 </v>
       </c>
       <c r="F66" s="3" t="str">
         <f>IF(LEN(ContactData!K65)&lt;3,"",ContactData!K65)</f>
-        <v>---</v>
+        <v>eq1manager@livingproperties.com</v>
       </c>
       <c r="G66"/>
       <c r="H66"/>
@@ -4111,27 +4114,27 @@
     <row r="67" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="str">
         <f>IF(LEN(ContactData!H66)&lt;3,"",ContactData!H66)</f>
-        <v/>
+        <v>---</v>
       </c>
       <c r="B67" s="3" t="str">
         <f>ContactData!E66</f>
-        <v>EQ2 Office</v>
+        <v xml:space="preserve">Security Desk </v>
       </c>
       <c r="C67" s="3" t="str">
         <f>ContactData!G66</f>
-        <v>60 Town Centre Court, Scarborough, ON, M1P 0B1</v>
+        <v xml:space="preserve">EQ1 Security Desk </v>
       </c>
       <c r="D67" s="9" t="str">
         <f>IF(LEN(ContactData!I66)&lt;3,"",ContactData!I66)</f>
-        <v/>
+        <v>---</v>
       </c>
       <c r="E67" s="3" t="str">
         <f>ContactData!J66</f>
-        <v xml:space="preserve">T: (416) 279-0591 </v>
+        <v>(416) 279-1894</v>
       </c>
       <c r="F67" s="3" t="str">
         <f>IF(LEN(ContactData!K66)&lt;3,"",ContactData!K66)</f>
-        <v/>
+        <v>---</v>
       </c>
       <c r="G67"/>
       <c r="H67"/>
@@ -4143,27 +4146,27 @@
     <row r="68" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="9" t="str">
         <f>IF(LEN(ContactData!H67)&lt;3,"",ContactData!H67)</f>
-        <v>---</v>
+        <v/>
       </c>
       <c r="B68" s="3" t="str">
         <f>ContactData!E67</f>
-        <v>Aaron Ma</v>
+        <v>EQ2 Office</v>
       </c>
       <c r="C68" s="3" t="str">
         <f>ContactData!G67</f>
-        <v>Property Manager</v>
+        <v>60 Town Centre Court, Scarborough, ON, M1P 0B1</v>
       </c>
       <c r="D68" s="9" t="str">
         <f>IF(LEN(ContactData!I67)&lt;3,"",ContactData!I67)</f>
-        <v>(416) 684-2236</v>
+        <v/>
       </c>
       <c r="E68" s="3" t="str">
         <f>ContactData!J67</f>
-        <v>(416) 279-0591</v>
+        <v xml:space="preserve">T: (416) 279-0591 </v>
       </c>
       <c r="F68" s="3" t="str">
         <f>IF(LEN(ContactData!K67)&lt;3,"",ContactData!K67)</f>
-        <v>eq2manager@livingproperties.com</v>
+        <v/>
       </c>
       <c r="G68"/>
       <c r="H68"/>
@@ -4179,23 +4182,23 @@
       </c>
       <c r="B69" s="3" t="str">
         <f>ContactData!E68</f>
-        <v xml:space="preserve">Security Desk </v>
+        <v>Aaron Ma</v>
       </c>
       <c r="C69" s="3" t="str">
         <f>ContactData!G68</f>
-        <v xml:space="preserve">EQ2 Security Desk </v>
+        <v>Property Manager</v>
       </c>
       <c r="D69" s="9" t="str">
         <f>IF(LEN(ContactData!I68)&lt;3,"",ContactData!I68)</f>
-        <v>---</v>
+        <v>(416) 684-2236</v>
       </c>
       <c r="E69" s="3" t="str">
         <f>ContactData!J68</f>
-        <v>(416) 279-1211</v>
+        <v>(416) 279-0591</v>
       </c>
       <c r="F69" s="3" t="str">
         <f>IF(LEN(ContactData!K68)&lt;3,"",ContactData!K68)</f>
-        <v>---</v>
+        <v>eq2manager@livingproperties.com</v>
       </c>
       <c r="G69"/>
       <c r="H69"/>
@@ -4207,27 +4210,27 @@
     <row r="70" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="9" t="str">
         <f>IF(LEN(ContactData!H69)&lt;3,"",ContactData!H69)</f>
-        <v/>
+        <v>---</v>
       </c>
       <c r="B70" s="3" t="str">
         <f>ContactData!E69</f>
-        <v>Alton Tower Office</v>
+        <v xml:space="preserve">Security Desk </v>
       </c>
       <c r="C70" s="3" t="str">
         <f>ContactData!G69</f>
-        <v>160 Alton Towers Cir, Toronto, ON, M1V 4X8</v>
+        <v xml:space="preserve">EQ2 Security Desk </v>
       </c>
       <c r="D70" s="9" t="str">
         <f>IF(LEN(ContactData!I69)&lt;3,"",ContactData!I69)</f>
-        <v/>
+        <v>---</v>
       </c>
       <c r="E70" s="3" t="str">
         <f>ContactData!J69</f>
-        <v>T: (437)-533-1208</v>
+        <v>(416) 279-1211</v>
       </c>
       <c r="F70" s="3" t="str">
         <f>IF(LEN(ContactData!K69)&lt;3,"",ContactData!K69)</f>
-        <v/>
+        <v>---</v>
       </c>
       <c r="G70"/>
       <c r="H70"/>
@@ -4239,27 +4242,27 @@
     <row r="71" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="9" t="str">
         <f>IF(LEN(ContactData!H70)&lt;3,"",ContactData!H70)</f>
-        <v>---</v>
+        <v/>
       </c>
       <c r="B71" s="3" t="str">
         <f>ContactData!E70</f>
-        <v>Ken Kam</v>
+        <v>Alton Tower Office</v>
       </c>
       <c r="C71" s="3" t="str">
         <f>ContactData!G70</f>
-        <v>Property Manager</v>
+        <v>160 Alton Towers Cir, Toronto, ON, M1V 4X8</v>
       </c>
       <c r="D71" s="9" t="str">
         <f>IF(LEN(ContactData!I70)&lt;3,"",ContactData!I70)</f>
-        <v>(647) 204-4455</v>
+        <v/>
       </c>
       <c r="E71" s="3" t="str">
         <f>ContactData!J70</f>
-        <v>(905) 477-2090</v>
+        <v>T: (437)-533-1208</v>
       </c>
       <c r="F71" s="3" t="str">
         <f>IF(LEN(ContactData!K70)&lt;3,"",ContactData!K70)</f>
-        <v>kenk@livingproperties.com</v>
+        <v/>
       </c>
       <c r="G71"/>
       <c r="H71"/>
@@ -4275,23 +4278,23 @@
       </c>
       <c r="B72" s="3" t="str">
         <f>ContactData!E71</f>
-        <v>Christie Ip</v>
+        <v>Ken Kam</v>
       </c>
       <c r="C72" s="3" t="str">
         <f>ContactData!G71</f>
-        <v>Administrative Assistant</v>
+        <v>Property Manager</v>
       </c>
       <c r="D72" s="9" t="str">
         <f>IF(LEN(ContactData!I71)&lt;3,"",ContactData!I71)</f>
-        <v>(437)-533-1208</v>
+        <v>(647) 204-4455</v>
       </c>
       <c r="E72" s="3" t="str">
         <f>ContactData!J71</f>
-        <v>---</v>
+        <v>(905) 477-2090</v>
       </c>
       <c r="F72" s="3" t="str">
         <f>IF(LEN(ContactData!K71)&lt;3,"",ContactData!K71)</f>
-        <v xml:space="preserve">optima2@livingproperties.com </v>
+        <v>kenk@livingproperties.com</v>
       </c>
       <c r="G72"/>
       <c r="H72"/>
@@ -4307,23 +4310,23 @@
       </c>
       <c r="B73" s="3" t="str">
         <f>ContactData!E72</f>
-        <v xml:space="preserve">Security Desk </v>
+        <v>Christie Ip</v>
       </c>
       <c r="C73" s="3" t="str">
         <f>ContactData!G72</f>
-        <v xml:space="preserve">Alton Tower Security Desk </v>
+        <v>Administrative Assistant</v>
       </c>
       <c r="D73" s="9" t="str">
         <f>IF(LEN(ContactData!I72)&lt;3,"",ContactData!I72)</f>
-        <v>---</v>
+        <v>(437)-533-1208</v>
       </c>
       <c r="E73" s="3" t="str">
         <f>ContactData!J72</f>
-        <v>(416) 754-3131</v>
+        <v>---</v>
       </c>
       <c r="F73" s="3" t="str">
         <f>IF(LEN(ContactData!K72)&lt;3,"",ContactData!K72)</f>
-        <v>---</v>
+        <v xml:space="preserve">optima2@livingproperties.com </v>
       </c>
       <c r="G73"/>
       <c r="H73"/>
@@ -4335,27 +4338,27 @@
     <row r="74" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="9" t="str">
         <f>IF(LEN(ContactData!H73)&lt;3,"",ContactData!H73)</f>
-        <v/>
+        <v>---</v>
       </c>
       <c r="B74" s="3" t="str">
         <f>ContactData!E73</f>
-        <v>IHMG Office</v>
+        <v xml:space="preserve">Security Desk </v>
       </c>
       <c r="C74" s="3" t="str">
         <f>ContactData!G73</f>
-        <v>8 Steelcase Road West, Markham, ON, L3R 1B2</v>
+        <v xml:space="preserve">Alton Tower Security Desk </v>
       </c>
       <c r="D74" s="9" t="str">
         <f>IF(LEN(ContactData!I73)&lt;3,"",ContactData!I73)</f>
-        <v/>
+        <v>---</v>
       </c>
       <c r="E74" s="3" t="str">
         <f>ContactData!J73</f>
-        <v>T: (905) 475-6000</v>
+        <v>(416) 754-3131</v>
       </c>
       <c r="F74" s="3" t="str">
         <f>IF(LEN(ContactData!K73)&lt;3,"",ContactData!K73)</f>
-        <v>info@ihmg.ca</v>
+        <v>---</v>
       </c>
       <c r="G74"/>
       <c r="H74"/>
@@ -4371,11 +4374,11 @@
       </c>
       <c r="B75" s="3" t="str">
         <f>ContactData!E74</f>
-        <v>IHMGRI Office</v>
+        <v>IHMG Office</v>
       </c>
       <c r="C75" s="3" t="str">
         <f>ContactData!G74</f>
-        <v>8 Steelcase Road West, Unit E, Markham, ON, L3R 1B2</v>
+        <v>8 Steelcase Road West, Markham, ON, L3R 1B2</v>
       </c>
       <c r="D75" s="9" t="str">
         <f>IF(LEN(ContactData!I74)&lt;3,"",ContactData!I74)</f>
@@ -4383,11 +4386,11 @@
       </c>
       <c r="E75" s="3" t="str">
         <f>ContactData!J74</f>
-        <v>T: (905) 489-8989</v>
+        <v>T: (905) 475-6000</v>
       </c>
       <c r="F75" s="3" t="str">
         <f>IF(LEN(ContactData!K74)&lt;3,"",ContactData!K74)</f>
-        <v>realestate@ihmg.ca</v>
+        <v>info@ihmg.ca</v>
       </c>
       <c r="G75"/>
       <c r="H75"/>
@@ -4397,29 +4400,29 @@
       <c r="L75"/>
     </row>
     <row r="76" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A76" s="9">
+      <c r="A76" s="9" t="str">
         <f>IF(LEN(ContactData!H75)&lt;3,"",ContactData!H75)</f>
-        <v>120</v>
+        <v/>
       </c>
       <c r="B76" s="3" t="str">
         <f>ContactData!E75</f>
-        <v>Eddie Tang</v>
+        <v>IHMGRI Office</v>
       </c>
       <c r="C76" s="3" t="str">
         <f>ContactData!G75</f>
-        <v>Financial Controller</v>
+        <v>8 Steelcase Road West, Unit E, Markham, ON, L3R 1B2</v>
       </c>
       <c r="D76" s="9" t="str">
         <f>IF(LEN(ContactData!I75)&lt;3,"",ContactData!I75)</f>
-        <v>(416) 723-8329</v>
+        <v/>
       </c>
       <c r="E76" s="3" t="str">
         <f>ContactData!J75</f>
-        <v>(905) 489-0186</v>
+        <v>T: (905) 489-8989</v>
       </c>
       <c r="F76" s="3" t="str">
         <f>IF(LEN(ContactData!K75)&lt;3,"",ContactData!K75)</f>
-        <v>eddie@ihmg.ca</v>
+        <v>realestate@ihmg.ca</v>
       </c>
       <c r="G76"/>
       <c r="H76"/>
@@ -4431,27 +4434,27 @@
     <row r="77" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="9">
         <f>IF(LEN(ContactData!H76)&lt;3,"",ContactData!H76)</f>
-        <v>187</v>
+        <v>120</v>
       </c>
       <c r="B77" s="3" t="str">
         <f>ContactData!E76</f>
-        <v>Lily Hou</v>
+        <v>Eddie Tang</v>
       </c>
       <c r="C77" s="3" t="str">
         <f>ContactData!G76</f>
-        <v>Senior Accounting Analyst &amp; Operations Support</v>
+        <v>Financial Controller</v>
       </c>
       <c r="D77" s="9" t="str">
         <f>IF(LEN(ContactData!I76)&lt;3,"",ContactData!I76)</f>
-        <v>(647) 774-8994</v>
+        <v>(416) 723-8329</v>
       </c>
       <c r="E77" s="3" t="str">
         <f>ContactData!J76</f>
-        <v>---</v>
+        <v>(905) 489-0186</v>
       </c>
       <c r="F77" s="3" t="str">
         <f>IF(LEN(ContactData!K76)&lt;3,"",ContactData!K76)</f>
-        <v>lily@ihmg.ca</v>
+        <v>eddie@ihmg.ca</v>
       </c>
       <c r="G77"/>
       <c r="H77"/>
@@ -4461,12 +4464,30 @@
       <c r="L77"/>
     </row>
     <row r="78" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A78" s="1"/>
-      <c r="B78"/>
-      <c r="C78"/>
-      <c r="D78"/>
-      <c r="E78"/>
-      <c r="F78"/>
+      <c r="A78" s="9">
+        <f>IF(LEN(ContactData!H77)&lt;3,"",ContactData!H77)</f>
+        <v>187</v>
+      </c>
+      <c r="B78" s="3" t="str">
+        <f>ContactData!E77</f>
+        <v>Lily Hou</v>
+      </c>
+      <c r="C78" s="3" t="str">
+        <f>ContactData!G77</f>
+        <v>Senior Accounting Analyst &amp; Operations Support</v>
+      </c>
+      <c r="D78" s="9" t="str">
+        <f>IF(LEN(ContactData!I77)&lt;3,"",ContactData!I77)</f>
+        <v>(647) 774-8994</v>
+      </c>
+      <c r="E78" s="3" t="str">
+        <f>ContactData!J77</f>
+        <v>---</v>
+      </c>
+      <c r="F78" s="3" t="str">
+        <f>IF(LEN(ContactData!K77)&lt;3,"",ContactData!K77)</f>
+        <v>lily@ihmg.ca</v>
+      </c>
       <c r="G78"/>
       <c r="H78"/>
       <c r="I78"/>
@@ -8436,23 +8457,37 @@
       <c r="K361"/>
       <c r="L361"/>
     </row>
+    <row r="362" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A362" s="1"/>
+      <c r="B362"/>
+      <c r="C362"/>
+      <c r="D362"/>
+      <c r="E362"/>
+      <c r="F362"/>
+      <c r="G362"/>
+      <c r="H362"/>
+      <c r="I362"/>
+      <c r="J362"/>
+      <c r="K362"/>
+      <c r="L362"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A3:A77 D3:D77">
+  <conditionalFormatting sqref="A3:A78 D3:D78">
     <cfRule type="containsBlanks" dxfId="31" priority="17">
       <formula>LEN(TRIM(A3))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B3:B77">
+  <conditionalFormatting sqref="B3:B78">
     <cfRule type="containsText" dxfId="30" priority="16" operator="containsText" text="Office">
       <formula>NOT(ISERROR(SEARCH("Office",B3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C77">
+  <conditionalFormatting sqref="C3:C78">
     <cfRule type="containsText" dxfId="29" priority="15" operator="containsText" text="ON,">
       <formula>NOT(ISERROR(SEARCH("ON,",C3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E77">
+  <conditionalFormatting sqref="E3:E78">
     <cfRule type="containsText" dxfId="28" priority="13" operator="containsText" text="T">
       <formula>NOT(ISERROR(SEARCH("T",E3)))</formula>
     </cfRule>
@@ -8467,7 +8502,7 @@
       <formula>LEN(TRIM(F3))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F77">
+  <conditionalFormatting sqref="F4:F78">
     <cfRule type="containsText" dxfId="25" priority="1" operator="containsText" text="ye@">
       <formula>NOT(ISERROR(SEARCH("ye@",F4)))</formula>
     </cfRule>
@@ -8510,7 +8545,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I365"/>
+  <dimension ref="A1:I366"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.44140625" style="8" customWidth="1"/>
@@ -8529,7 +8564,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -9929,7 +9964,7 @@
       </c>
       <c r="C50" s="3" t="str">
         <f>ContactData!G49</f>
-        <v>Assistant Property Manager</v>
+        <v>Property Manager</v>
       </c>
       <c r="D50" s="9" t="str">
         <f>IF(LEN(ContactData!I49)&lt;3,"",ContactData!I49)</f>
@@ -9950,15 +9985,15 @@
     <row r="51" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="9">
         <f>IF(LEN(ContactData!H50)&lt;3,"",ContactData!H50)</f>
-        <v>210</v>
+        <v>168</v>
       </c>
       <c r="B51" s="3" t="str">
         <f>ContactData!E50</f>
-        <v>Loretta Leung</v>
+        <v>Stanley Wu</v>
       </c>
       <c r="C51" s="3" t="str">
         <f>ContactData!G50</f>
-        <v>Executive Assistant</v>
+        <v>Property Manager</v>
       </c>
       <c r="D51" s="9" t="str">
         <f>IF(LEN(ContactData!I50)&lt;3,"",ContactData!I50)</f>
@@ -9966,11 +10001,11 @@
       </c>
       <c r="E51" s="3" t="str">
         <f>ContactData!J50</f>
-        <v>---</v>
+        <v>(905) 477-2090</v>
       </c>
       <c r="F51" s="3" t="str">
         <f>IF(LEN(ContactData!K50)&lt;3,"",ContactData!K50)</f>
-        <v>lorettal@livingproperties.com</v>
+        <v>stanleyw@livingproperties.com</v>
       </c>
       <c r="G51"/>
       <c r="H51"/>
@@ -9979,15 +10014,15 @@
     <row r="52" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="9">
         <f>IF(LEN(ContactData!H51)&lt;3,"",ContactData!H51)</f>
-        <v>518</v>
+        <v>210</v>
       </c>
       <c r="B52" s="3" t="str">
         <f>ContactData!E51</f>
-        <v>Simon Li</v>
+        <v>Loretta Leung</v>
       </c>
       <c r="C52" s="3" t="str">
         <f>ContactData!G51</f>
-        <v>Senior Accountant</v>
+        <v>Executive Assistant</v>
       </c>
       <c r="D52" s="9" t="str">
         <f>IF(LEN(ContactData!I51)&lt;3,"",ContactData!I51)</f>
@@ -9995,11 +10030,11 @@
       </c>
       <c r="E52" s="3" t="str">
         <f>ContactData!J51</f>
-        <v>(905) 752-3518</v>
+        <v>---</v>
       </c>
       <c r="F52" s="3" t="str">
         <f>IF(LEN(ContactData!K51)&lt;3,"",ContactData!K51)</f>
-        <v>simonl@livingproperties.com</v>
+        <v>lorettal@livingproperties.com</v>
       </c>
       <c r="G52"/>
       <c r="H52"/>
@@ -10008,15 +10043,15 @@
     <row r="53" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="9">
         <f>IF(LEN(ContactData!H52)&lt;3,"",ContactData!H52)</f>
-        <v>281</v>
+        <v>518</v>
       </c>
       <c r="B53" s="3" t="str">
         <f>ContactData!E52</f>
-        <v>Nicole Leung</v>
+        <v>Simon Li</v>
       </c>
       <c r="C53" s="3" t="str">
         <f>ContactData!G52</f>
-        <v>Property Accountant</v>
+        <v>Senior Accountant</v>
       </c>
       <c r="D53" s="9" t="str">
         <f>IF(LEN(ContactData!I52)&lt;3,"",ContactData!I52)</f>
@@ -10024,11 +10059,11 @@
       </c>
       <c r="E53" s="3" t="str">
         <f>ContactData!J52</f>
-        <v>---</v>
+        <v>(905) 752-3518</v>
       </c>
       <c r="F53" s="3" t="str">
         <f>IF(LEN(ContactData!K52)&lt;3,"",ContactData!K52)</f>
-        <v>nicolel@livingproperties.com</v>
+        <v>simonl@livingproperties.com</v>
       </c>
       <c r="G53"/>
       <c r="H53"/>
@@ -10037,15 +10072,15 @@
     <row r="54" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="9">
         <f>IF(LEN(ContactData!H53)&lt;3,"",ContactData!H53)</f>
-        <v>523</v>
+        <v>281</v>
       </c>
       <c r="B54" s="3" t="str">
         <f>ContactData!E53</f>
-        <v>Vivian Lum</v>
+        <v>Nicole Leung</v>
       </c>
       <c r="C54" s="3" t="str">
         <f>ContactData!G53</f>
-        <v>Accounts Receivable Clerk</v>
+        <v>Property Accountant</v>
       </c>
       <c r="D54" s="9" t="str">
         <f>IF(LEN(ContactData!I53)&lt;3,"",ContactData!I53)</f>
@@ -10053,11 +10088,11 @@
       </c>
       <c r="E54" s="3" t="str">
         <f>ContactData!J53</f>
-        <v>(905) 752-3523</v>
+        <v>---</v>
       </c>
       <c r="F54" s="3" t="str">
         <f>IF(LEN(ContactData!K53)&lt;3,"",ContactData!K53)</f>
-        <v>vivianl@livingproperties.com</v>
+        <v>nicolel@livingproperties.com</v>
       </c>
       <c r="G54"/>
       <c r="H54"/>
@@ -10066,15 +10101,15 @@
     <row r="55" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="9">
         <f>IF(LEN(ContactData!H54)&lt;3,"",ContactData!H54)</f>
-        <v>223</v>
+        <v>523</v>
       </c>
       <c r="B55" s="3" t="str">
         <f>ContactData!E54</f>
-        <v>Jessica Lee</v>
+        <v>Vivian Lum</v>
       </c>
       <c r="C55" s="3" t="str">
         <f>ContactData!G54</f>
-        <v xml:space="preserve">Accounting Clerk </v>
+        <v>Accounts Receivable Clerk</v>
       </c>
       <c r="D55" s="9" t="str">
         <f>IF(LEN(ContactData!I54)&lt;3,"",ContactData!I54)</f>
@@ -10082,11 +10117,11 @@
       </c>
       <c r="E55" s="3" t="str">
         <f>ContactData!J54</f>
-        <v>---</v>
+        <v>(905) 752-3523</v>
       </c>
       <c r="F55" s="3" t="str">
         <f>IF(LEN(ContactData!K54)&lt;3,"",ContactData!K54)</f>
-        <v>jessical@livingproperties.com</v>
+        <v>vivianl@livingproperties.com</v>
       </c>
       <c r="G55"/>
       <c r="H55"/>
@@ -10095,15 +10130,15 @@
     <row r="56" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="9">
         <f>IF(LEN(ContactData!H55)&lt;3,"",ContactData!H55)</f>
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="B56" s="3" t="str">
         <f>ContactData!E55</f>
-        <v>Rebecca Lau</v>
+        <v>Jessica Lee</v>
       </c>
       <c r="C56" s="3" t="str">
         <f>ContactData!G55</f>
-        <v>Administrative Assistant</v>
+        <v xml:space="preserve">Accounting Clerk </v>
       </c>
       <c r="D56" s="9" t="str">
         <f>IF(LEN(ContactData!I55)&lt;3,"",ContactData!I55)</f>
@@ -10115,7 +10150,7 @@
       </c>
       <c r="F56" s="3" t="str">
         <f>IF(LEN(ContactData!K55)&lt;3,"",ContactData!K55)</f>
-        <v>rebeccal@livingproperties.com</v>
+        <v>jessical@livingproperties.com</v>
       </c>
       <c r="G56"/>
       <c r="H56"/>
@@ -10124,11 +10159,11 @@
     <row r="57" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="9">
         <f>IF(LEN(ContactData!H56)&lt;3,"",ContactData!H56)</f>
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B57" s="3" t="str">
         <f>ContactData!E56</f>
-        <v>Kelvin Chan</v>
+        <v>Rebecca Lau</v>
       </c>
       <c r="C57" s="3" t="str">
         <f>ContactData!G56</f>
@@ -10144,7 +10179,7 @@
       </c>
       <c r="F57" s="3" t="str">
         <f>IF(LEN(ContactData!K56)&lt;3,"",ContactData!K56)</f>
-        <v>kelvinc@livingproperties.com</v>
+        <v>rebeccal@livingproperties.com</v>
       </c>
       <c r="G57"/>
       <c r="H57"/>
@@ -10153,15 +10188,15 @@
     <row r="58" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="9">
         <f>IF(LEN(ContactData!H57)&lt;3,"",ContactData!H57)</f>
-        <v>229</v>
+        <v>182</v>
       </c>
       <c r="B58" s="3" t="str">
         <f>ContactData!E57</f>
-        <v>Matthew Wong</v>
+        <v>Kelvin Chan</v>
       </c>
       <c r="C58" s="3" t="str">
         <f>ContactData!G57</f>
-        <v>Accounting Clerk</v>
+        <v>Administrative Assistant</v>
       </c>
       <c r="D58" s="9" t="str">
         <f>IF(LEN(ContactData!I57)&lt;3,"",ContactData!I57)</f>
@@ -10173,24 +10208,24 @@
       </c>
       <c r="F58" s="3" t="str">
         <f>IF(LEN(ContactData!K57)&lt;3,"",ContactData!K57)</f>
-        <v>mattheww@livingproperties.com</v>
+        <v>kelvinc@livingproperties.com</v>
       </c>
       <c r="G58"/>
       <c r="H58"/>
       <c r="I58"/>
     </row>
     <row r="59" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A59" s="9" t="str">
+      <c r="A59" s="9">
         <f>IF(LEN(ContactData!H58)&lt;3,"",ContactData!H58)</f>
-        <v>---</v>
+        <v>229</v>
       </c>
       <c r="B59" s="3" t="str">
         <f>ContactData!E58</f>
-        <v>Gus B</v>
+        <v>Matthew Wong</v>
       </c>
       <c r="C59" s="3" t="str">
         <f>ContactData!G58</f>
-        <v>Handyman</v>
+        <v>Accounting Clerk</v>
       </c>
       <c r="D59" s="9" t="str">
         <f>IF(LEN(ContactData!I58)&lt;3,"",ContactData!I58)</f>
@@ -10198,11 +10233,11 @@
       </c>
       <c r="E59" s="3" t="str">
         <f>ContactData!J58</f>
-        <v>(905) 477-2090</v>
+        <v>---</v>
       </c>
       <c r="F59" s="3" t="str">
         <f>IF(LEN(ContactData!K58)&lt;3,"",ContactData!K58)</f>
-        <v>gusb@livcontruction.ca</v>
+        <v>mattheww@livingproperties.com</v>
       </c>
       <c r="G59"/>
       <c r="H59"/>
@@ -10211,27 +10246,27 @@
     <row r="60" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="9" t="str">
         <f>IF(LEN(ContactData!H59)&lt;3,"",ContactData!H59)</f>
-        <v/>
+        <v>---</v>
       </c>
       <c r="B60" s="3" t="str">
         <f>ContactData!E59</f>
-        <v>Centro Towers Office</v>
+        <v>Gus B</v>
       </c>
       <c r="C60" s="3" t="str">
         <f>ContactData!G59</f>
-        <v>25 Town Centre Crt, Scarborough, ON, M1P 0B4</v>
+        <v>Handyman</v>
       </c>
       <c r="D60" s="9" t="str">
         <f>IF(LEN(ContactData!I59)&lt;3,"",ContactData!I59)</f>
-        <v/>
+        <v>---</v>
       </c>
       <c r="E60" s="3" t="str">
         <f>ContactData!J59</f>
-        <v>T: (416) 290-1242</v>
+        <v>(905) 477-2090</v>
       </c>
       <c r="F60" s="3" t="str">
         <f>IF(LEN(ContactData!K59)&lt;3,"",ContactData!K59)</f>
-        <v/>
+        <v>gusb@livcontruction.ca</v>
       </c>
       <c r="G60"/>
       <c r="H60"/>
@@ -10240,27 +10275,27 @@
     <row r="61" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="str">
         <f>IF(LEN(ContactData!H60)&lt;3,"",ContactData!H60)</f>
-        <v>---</v>
+        <v/>
       </c>
       <c r="B61" s="3" t="str">
         <f>ContactData!E60</f>
-        <v>Henry Fu</v>
+        <v>Centro Towers Office</v>
       </c>
       <c r="C61" s="3" t="str">
         <f>ContactData!G60</f>
-        <v>Property Manager</v>
+        <v>25 Town Centre Crt, Scarborough, ON, M1P 0B4</v>
       </c>
       <c r="D61" s="9" t="str">
         <f>IF(LEN(ContactData!I60)&lt;3,"",ContactData!I60)</f>
-        <v>(416) 278-2953</v>
+        <v/>
       </c>
       <c r="E61" s="3" t="str">
         <f>ContactData!J60</f>
-        <v>(416) 290-1242</v>
+        <v>T: (416) 290-1242</v>
       </c>
       <c r="F61" s="3" t="str">
         <f>IF(LEN(ContactData!K60)&lt;3,"",ContactData!K60)</f>
-        <v>henry@centrotowers.com</v>
+        <v/>
       </c>
       <c r="G61"/>
       <c r="H61"/>
@@ -10273,15 +10308,15 @@
       </c>
       <c r="B62" s="3" t="str">
         <f>ContactData!E61</f>
-        <v>Sophia Yip</v>
+        <v>Henry Fu</v>
       </c>
       <c r="C62" s="3" t="str">
         <f>ContactData!G61</f>
-        <v>Property Administrator</v>
+        <v>Property Manager</v>
       </c>
       <c r="D62" s="9" t="str">
         <f>IF(LEN(ContactData!I61)&lt;3,"",ContactData!I61)</f>
-        <v>---</v>
+        <v>(416) 278-2953</v>
       </c>
       <c r="E62" s="3" t="str">
         <f>ContactData!J61</f>
@@ -10289,7 +10324,7 @@
       </c>
       <c r="F62" s="3" t="str">
         <f>IF(LEN(ContactData!K61)&lt;3,"",ContactData!K61)</f>
-        <v>sophia@centrotowers.com</v>
+        <v>henry@centrotowers.com</v>
       </c>
       <c r="G62"/>
       <c r="H62"/>
@@ -10302,11 +10337,11 @@
       </c>
       <c r="B63" s="3" t="str">
         <f>ContactData!E62</f>
-        <v xml:space="preserve">Security Desk </v>
+        <v>Sophia Yip</v>
       </c>
       <c r="C63" s="3" t="str">
         <f>ContactData!G62</f>
-        <v xml:space="preserve">Centro Security Desk </v>
+        <v>Property Administrator</v>
       </c>
       <c r="D63" s="9" t="str">
         <f>IF(LEN(ContactData!I62)&lt;3,"",ContactData!I62)</f>
@@ -10314,11 +10349,11 @@
       </c>
       <c r="E63" s="3" t="str">
         <f>ContactData!J62</f>
-        <v>(416) 296-0099</v>
+        <v>(416) 290-1242</v>
       </c>
       <c r="F63" s="3" t="str">
         <f>IF(LEN(ContactData!K62)&lt;3,"",ContactData!K62)</f>
-        <v>---</v>
+        <v>sophia@centrotowers.com</v>
       </c>
       <c r="G63"/>
       <c r="H63"/>
@@ -10327,27 +10362,27 @@
     <row r="64" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="str">
         <f>IF(LEN(ContactData!H63)&lt;3,"",ContactData!H63)</f>
-        <v/>
+        <v>---</v>
       </c>
       <c r="B64" s="3" t="str">
         <f>ContactData!E63</f>
-        <v>EQ1 Office</v>
+        <v xml:space="preserve">Security Desk </v>
       </c>
       <c r="C64" s="3" t="str">
         <f>ContactData!G63</f>
-        <v>70 Town Centre Court, Scarborough, ON, M1P 0B2</v>
+        <v xml:space="preserve">Centro Security Desk </v>
       </c>
       <c r="D64" s="9" t="str">
         <f>IF(LEN(ContactData!I63)&lt;3,"",ContactData!I63)</f>
-        <v/>
+        <v>---</v>
       </c>
       <c r="E64" s="3" t="str">
         <f>ContactData!J63</f>
-        <v xml:space="preserve">T: (416) 279-0603 </v>
+        <v>(416) 296-0099</v>
       </c>
       <c r="F64" s="3" t="str">
         <f>IF(LEN(ContactData!K63)&lt;3,"",ContactData!K63)</f>
-        <v>eq1@livingproperties.com</v>
+        <v>---</v>
       </c>
       <c r="G64"/>
       <c r="H64"/>
@@ -10356,27 +10391,27 @@
     <row r="65" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="9" t="str">
         <f>IF(LEN(ContactData!H64)&lt;3,"",ContactData!H64)</f>
-        <v>---</v>
+        <v/>
       </c>
       <c r="B65" s="3" t="str">
         <f>ContactData!E64</f>
-        <v>Ming Ip</v>
+        <v>EQ1 Office</v>
       </c>
       <c r="C65" s="3" t="str">
         <f>ContactData!G64</f>
-        <v>Property Manager</v>
+        <v>70 Town Centre Court, Scarborough, ON, M1P 0B2</v>
       </c>
       <c r="D65" s="9" t="str">
         <f>IF(LEN(ContactData!I64)&lt;3,"",ContactData!I64)</f>
-        <v>(647) 286-0147</v>
+        <v/>
       </c>
       <c r="E65" s="3" t="str">
         <f>ContactData!J64</f>
-        <v xml:space="preserve">(416) 279-0603 </v>
+        <v xml:space="preserve">T: (416) 279-0603 </v>
       </c>
       <c r="F65" s="3" t="str">
         <f>IF(LEN(ContactData!K64)&lt;3,"",ContactData!K64)</f>
-        <v>eq1manager@livingproperties.com</v>
+        <v>eq1@livingproperties.com</v>
       </c>
       <c r="G65"/>
       <c r="H65"/>
@@ -10389,23 +10424,23 @@
       </c>
       <c r="B66" s="3" t="str">
         <f>ContactData!E65</f>
-        <v xml:space="preserve">Security Desk </v>
+        <v>Ming Ip</v>
       </c>
       <c r="C66" s="3" t="str">
         <f>ContactData!G65</f>
-        <v xml:space="preserve">EQ1 Security Desk </v>
+        <v>Property Manager</v>
       </c>
       <c r="D66" s="9" t="str">
         <f>IF(LEN(ContactData!I65)&lt;3,"",ContactData!I65)</f>
-        <v>---</v>
+        <v>(647) 286-0147</v>
       </c>
       <c r="E66" s="3" t="str">
         <f>ContactData!J65</f>
-        <v>(416) 279-1894</v>
+        <v xml:space="preserve">(416) 279-0603 </v>
       </c>
       <c r="F66" s="3" t="str">
         <f>IF(LEN(ContactData!K65)&lt;3,"",ContactData!K65)</f>
-        <v>---</v>
+        <v>eq1manager@livingproperties.com</v>
       </c>
       <c r="G66"/>
       <c r="H66"/>
@@ -10414,27 +10449,27 @@
     <row r="67" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="9" t="str">
         <f>IF(LEN(ContactData!H66)&lt;3,"",ContactData!H66)</f>
-        <v/>
+        <v>---</v>
       </c>
       <c r="B67" s="3" t="str">
         <f>ContactData!E66</f>
-        <v>EQ2 Office</v>
+        <v xml:space="preserve">Security Desk </v>
       </c>
       <c r="C67" s="3" t="str">
         <f>ContactData!G66</f>
-        <v>60 Town Centre Court, Scarborough, ON, M1P 0B1</v>
+        <v xml:space="preserve">EQ1 Security Desk </v>
       </c>
       <c r="D67" s="9" t="str">
         <f>IF(LEN(ContactData!I66)&lt;3,"",ContactData!I66)</f>
-        <v/>
+        <v>---</v>
       </c>
       <c r="E67" s="3" t="str">
         <f>ContactData!J66</f>
-        <v xml:space="preserve">T: (416) 279-0591 </v>
+        <v>(416) 279-1894</v>
       </c>
       <c r="F67" s="3" t="str">
         <f>IF(LEN(ContactData!K66)&lt;3,"",ContactData!K66)</f>
-        <v/>
+        <v>---</v>
       </c>
       <c r="G67"/>
       <c r="H67"/>
@@ -10443,27 +10478,27 @@
     <row r="68" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="9" t="str">
         <f>IF(LEN(ContactData!H67)&lt;3,"",ContactData!H67)</f>
-        <v>---</v>
+        <v/>
       </c>
       <c r="B68" s="3" t="str">
         <f>ContactData!E67</f>
-        <v>Aaron Ma</v>
+        <v>EQ2 Office</v>
       </c>
       <c r="C68" s="3" t="str">
         <f>ContactData!G67</f>
-        <v>Property Manager</v>
+        <v>60 Town Centre Court, Scarborough, ON, M1P 0B1</v>
       </c>
       <c r="D68" s="9" t="str">
         <f>IF(LEN(ContactData!I67)&lt;3,"",ContactData!I67)</f>
-        <v>(416) 684-2236</v>
+        <v/>
       </c>
       <c r="E68" s="3" t="str">
         <f>ContactData!J67</f>
-        <v>(416) 279-0591</v>
+        <v xml:space="preserve">T: (416) 279-0591 </v>
       </c>
       <c r="F68" s="3" t="str">
         <f>IF(LEN(ContactData!K67)&lt;3,"",ContactData!K67)</f>
-        <v>eq2manager@livingproperties.com</v>
+        <v/>
       </c>
       <c r="G68"/>
       <c r="H68"/>
@@ -10476,23 +10511,23 @@
       </c>
       <c r="B69" s="3" t="str">
         <f>ContactData!E68</f>
-        <v xml:space="preserve">Security Desk </v>
+        <v>Aaron Ma</v>
       </c>
       <c r="C69" s="3" t="str">
         <f>ContactData!G68</f>
-        <v xml:space="preserve">EQ2 Security Desk </v>
+        <v>Property Manager</v>
       </c>
       <c r="D69" s="9" t="str">
         <f>IF(LEN(ContactData!I68)&lt;3,"",ContactData!I68)</f>
-        <v>---</v>
+        <v>(416) 684-2236</v>
       </c>
       <c r="E69" s="3" t="str">
         <f>ContactData!J68</f>
-        <v>(416) 279-1211</v>
+        <v>(416) 279-0591</v>
       </c>
       <c r="F69" s="3" t="str">
         <f>IF(LEN(ContactData!K68)&lt;3,"",ContactData!K68)</f>
-        <v>---</v>
+        <v>eq2manager@livingproperties.com</v>
       </c>
       <c r="G69"/>
       <c r="H69"/>
@@ -10501,27 +10536,27 @@
     <row r="70" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="9" t="str">
         <f>IF(LEN(ContactData!H69)&lt;3,"",ContactData!H69)</f>
-        <v/>
+        <v>---</v>
       </c>
       <c r="B70" s="3" t="str">
         <f>ContactData!E69</f>
-        <v>Alton Tower Office</v>
+        <v xml:space="preserve">Security Desk </v>
       </c>
       <c r="C70" s="3" t="str">
         <f>ContactData!G69</f>
-        <v>160 Alton Towers Cir, Toronto, ON, M1V 4X8</v>
+        <v xml:space="preserve">EQ2 Security Desk </v>
       </c>
       <c r="D70" s="9" t="str">
         <f>IF(LEN(ContactData!I69)&lt;3,"",ContactData!I69)</f>
-        <v/>
+        <v>---</v>
       </c>
       <c r="E70" s="3" t="str">
         <f>ContactData!J69</f>
-        <v>T: (437)-533-1208</v>
+        <v>(416) 279-1211</v>
       </c>
       <c r="F70" s="3" t="str">
         <f>IF(LEN(ContactData!K69)&lt;3,"",ContactData!K69)</f>
-        <v/>
+        <v>---</v>
       </c>
       <c r="G70"/>
       <c r="H70"/>
@@ -10530,27 +10565,27 @@
     <row r="71" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="9" t="str">
         <f>IF(LEN(ContactData!H70)&lt;3,"",ContactData!H70)</f>
-        <v>---</v>
+        <v/>
       </c>
       <c r="B71" s="3" t="str">
         <f>ContactData!E70</f>
-        <v>Ken Kam</v>
+        <v>Alton Tower Office</v>
       </c>
       <c r="C71" s="3" t="str">
         <f>ContactData!G70</f>
-        <v>Property Manager</v>
+        <v>160 Alton Towers Cir, Toronto, ON, M1V 4X8</v>
       </c>
       <c r="D71" s="9" t="str">
         <f>IF(LEN(ContactData!I70)&lt;3,"",ContactData!I70)</f>
-        <v>(647) 204-4455</v>
+        <v/>
       </c>
       <c r="E71" s="3" t="str">
         <f>ContactData!J70</f>
-        <v>(905) 477-2090</v>
+        <v>T: (437)-533-1208</v>
       </c>
       <c r="F71" s="3" t="str">
         <f>IF(LEN(ContactData!K70)&lt;3,"",ContactData!K70)</f>
-        <v>kenk@livingproperties.com</v>
+        <v/>
       </c>
       <c r="G71"/>
       <c r="H71"/>
@@ -10563,23 +10598,23 @@
       </c>
       <c r="B72" s="3" t="str">
         <f>ContactData!E71</f>
-        <v>Christie Ip</v>
+        <v>Ken Kam</v>
       </c>
       <c r="C72" s="3" t="str">
         <f>ContactData!G71</f>
-        <v>Administrative Assistant</v>
+        <v>Property Manager</v>
       </c>
       <c r="D72" s="9" t="str">
         <f>IF(LEN(ContactData!I71)&lt;3,"",ContactData!I71)</f>
-        <v>(437)-533-1208</v>
+        <v>(647) 204-4455</v>
       </c>
       <c r="E72" s="3" t="str">
         <f>ContactData!J71</f>
-        <v>---</v>
+        <v>(905) 477-2090</v>
       </c>
       <c r="F72" s="3" t="str">
         <f>IF(LEN(ContactData!K71)&lt;3,"",ContactData!K71)</f>
-        <v xml:space="preserve">optima2@livingproperties.com </v>
+        <v>kenk@livingproperties.com</v>
       </c>
       <c r="G72"/>
       <c r="H72"/>
@@ -10592,23 +10627,23 @@
       </c>
       <c r="B73" s="3" t="str">
         <f>ContactData!E72</f>
-        <v xml:space="preserve">Security Desk </v>
+        <v>Christie Ip</v>
       </c>
       <c r="C73" s="3" t="str">
         <f>ContactData!G72</f>
-        <v xml:space="preserve">Alton Tower Security Desk </v>
+        <v>Administrative Assistant</v>
       </c>
       <c r="D73" s="9" t="str">
         <f>IF(LEN(ContactData!I72)&lt;3,"",ContactData!I72)</f>
-        <v>---</v>
+        <v>(437)-533-1208</v>
       </c>
       <c r="E73" s="3" t="str">
         <f>ContactData!J72</f>
-        <v>(416) 754-3131</v>
+        <v>---</v>
       </c>
       <c r="F73" s="3" t="str">
         <f>IF(LEN(ContactData!K72)&lt;3,"",ContactData!K72)</f>
-        <v>---</v>
+        <v xml:space="preserve">optima2@livingproperties.com </v>
       </c>
       <c r="G73"/>
       <c r="H73"/>
@@ -10617,27 +10652,27 @@
     <row r="74" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="9" t="str">
         <f>IF(LEN(ContactData!H73)&lt;3,"",ContactData!H73)</f>
-        <v/>
+        <v>---</v>
       </c>
       <c r="B74" s="3" t="str">
         <f>ContactData!E73</f>
-        <v>IHMG Office</v>
+        <v xml:space="preserve">Security Desk </v>
       </c>
       <c r="C74" s="3" t="str">
         <f>ContactData!G73</f>
-        <v>8 Steelcase Road West, Markham, ON, L3R 1B2</v>
+        <v xml:space="preserve">Alton Tower Security Desk </v>
       </c>
       <c r="D74" s="9" t="str">
         <f>IF(LEN(ContactData!I73)&lt;3,"",ContactData!I73)</f>
-        <v/>
+        <v>---</v>
       </c>
       <c r="E74" s="3" t="str">
         <f>ContactData!J73</f>
-        <v>T: (905) 475-6000</v>
+        <v>(416) 754-3131</v>
       </c>
       <c r="F74" s="3" t="str">
         <f>IF(LEN(ContactData!K73)&lt;3,"",ContactData!K73)</f>
-        <v>info@ihmg.ca</v>
+        <v>---</v>
       </c>
       <c r="G74"/>
       <c r="H74"/>
@@ -10650,11 +10685,11 @@
       </c>
       <c r="B75" s="3" t="str">
         <f>ContactData!E74</f>
-        <v>IHMGRI Office</v>
+        <v>IHMG Office</v>
       </c>
       <c r="C75" s="3" t="str">
         <f>ContactData!G74</f>
-        <v>8 Steelcase Road West, Unit E, Markham, ON, L3R 1B2</v>
+        <v>8 Steelcase Road West, Markham, ON, L3R 1B2</v>
       </c>
       <c r="D75" s="9" t="str">
         <f>IF(LEN(ContactData!I74)&lt;3,"",ContactData!I74)</f>
@@ -10662,40 +10697,40 @@
       </c>
       <c r="E75" s="3" t="str">
         <f>ContactData!J74</f>
-        <v>T: (905) 489-8989</v>
+        <v>T: (905) 475-6000</v>
       </c>
       <c r="F75" s="3" t="str">
         <f>IF(LEN(ContactData!K74)&lt;3,"",ContactData!K74)</f>
-        <v>realestate@ihmg.ca</v>
+        <v>info@ihmg.ca</v>
       </c>
       <c r="G75"/>
       <c r="H75"/>
       <c r="I75"/>
     </row>
     <row r="76" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A76" s="9">
+      <c r="A76" s="9" t="str">
         <f>IF(LEN(ContactData!H75)&lt;3,"",ContactData!H75)</f>
-        <v>120</v>
+        <v/>
       </c>
       <c r="B76" s="3" t="str">
         <f>ContactData!E75</f>
-        <v>Eddie Tang</v>
+        <v>IHMGRI Office</v>
       </c>
       <c r="C76" s="3" t="str">
         <f>ContactData!G75</f>
-        <v>Financial Controller</v>
+        <v>8 Steelcase Road West, Unit E, Markham, ON, L3R 1B2</v>
       </c>
       <c r="D76" s="9" t="str">
         <f>IF(LEN(ContactData!I75)&lt;3,"",ContactData!I75)</f>
-        <v>(416) 723-8329</v>
+        <v/>
       </c>
       <c r="E76" s="3" t="str">
         <f>ContactData!J75</f>
-        <v>(905) 489-0186</v>
+        <v>T: (905) 489-8989</v>
       </c>
       <c r="F76" s="3" t="str">
         <f>IF(LEN(ContactData!K75)&lt;3,"",ContactData!K75)</f>
-        <v>eddie@ihmg.ca</v>
+        <v>realestate@ihmg.ca</v>
       </c>
       <c r="G76"/>
       <c r="H76"/>
@@ -10704,39 +10739,57 @@
     <row r="77" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="9">
         <f>IF(LEN(ContactData!H76)&lt;3,"",ContactData!H76)</f>
-        <v>187</v>
+        <v>120</v>
       </c>
       <c r="B77" s="3" t="str">
         <f>ContactData!E76</f>
-        <v>Lily Hou</v>
+        <v>Eddie Tang</v>
       </c>
       <c r="C77" s="3" t="str">
         <f>ContactData!G76</f>
-        <v>Senior Accounting Analyst &amp; Operations Support</v>
+        <v>Financial Controller</v>
       </c>
       <c r="D77" s="9" t="str">
         <f>IF(LEN(ContactData!I76)&lt;3,"",ContactData!I76)</f>
-        <v>(647) 774-8994</v>
+        <v>(416) 723-8329</v>
       </c>
       <c r="E77" s="3" t="str">
         <f>ContactData!J76</f>
-        <v>---</v>
+        <v>(905) 489-0186</v>
       </c>
       <c r="F77" s="3" t="str">
         <f>IF(LEN(ContactData!K76)&lt;3,"",ContactData!K76)</f>
-        <v>lily@ihmg.ca</v>
+        <v>eddie@ihmg.ca</v>
       </c>
       <c r="G77"/>
       <c r="H77"/>
       <c r="I77"/>
     </row>
     <row r="78" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A78" s="1"/>
-      <c r="B78"/>
-      <c r="C78"/>
-      <c r="D78"/>
-      <c r="E78"/>
-      <c r="F78"/>
+      <c r="A78" s="9">
+        <f>IF(LEN(ContactData!H77)&lt;3,"",ContactData!H77)</f>
+        <v>187</v>
+      </c>
+      <c r="B78" s="3" t="str">
+        <f>ContactData!E77</f>
+        <v>Lily Hou</v>
+      </c>
+      <c r="C78" s="3" t="str">
+        <f>ContactData!G77</f>
+        <v>Senior Accounting Analyst &amp; Operations Support</v>
+      </c>
+      <c r="D78" s="9" t="str">
+        <f>IF(LEN(ContactData!I77)&lt;3,"",ContactData!I77)</f>
+        <v>(647) 774-8994</v>
+      </c>
+      <c r="E78" s="3" t="str">
+        <f>ContactData!J77</f>
+        <v>---</v>
+      </c>
+      <c r="F78" s="3" t="str">
+        <f>IF(LEN(ContactData!K77)&lt;3,"",ContactData!K77)</f>
+        <v>lily@ihmg.ca</v>
+      </c>
       <c r="G78"/>
       <c r="H78"/>
       <c r="I78"/>
@@ -13898,23 +13951,34 @@
       <c r="H365"/>
       <c r="I365"/>
     </row>
+    <row r="366" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A366" s="1"/>
+      <c r="B366"/>
+      <c r="C366"/>
+      <c r="D366"/>
+      <c r="E366"/>
+      <c r="F366"/>
+      <c r="G366"/>
+      <c r="H366"/>
+      <c r="I366"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A3:A77 D3:D77">
+  <conditionalFormatting sqref="A3:A78 D3:D78">
     <cfRule type="containsBlanks" dxfId="15" priority="18">
       <formula>LEN(TRIM(A3))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B3:B77">
+  <conditionalFormatting sqref="B3:B78">
     <cfRule type="containsText" dxfId="14" priority="16" operator="containsText" text="Office">
       <formula>NOT(ISERROR(SEARCH("Office",B3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C77">
+  <conditionalFormatting sqref="C3:C78">
     <cfRule type="containsText" dxfId="13" priority="15" operator="containsText" text="ON,">
       <formula>NOT(ISERROR(SEARCH("ON,",C3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E77">
+  <conditionalFormatting sqref="E3:E78">
     <cfRule type="containsText" dxfId="12" priority="13" operator="containsText" text="T">
       <formula>NOT(ISERROR(SEARCH("T",E3)))</formula>
     </cfRule>
@@ -13924,7 +13988,7 @@
       <formula>LEN(TRIM(F3))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F77">
+  <conditionalFormatting sqref="F4:F78">
     <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="ye@">
       <formula>NOT(ISERROR(SEARCH("ye@",F4)))</formula>
     </cfRule>
@@ -13967,7 +14031,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D4DBD61-A264-4E77-BA12-BABDDFA736C5}">
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.88671875" customWidth="1"/>
@@ -14001,7 +14065,7 @@
         <v>168</v>
       </c>
       <c r="F1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G1" t="s">
         <v>149</v>
@@ -14081,7 +14145,7 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G3" t="s">
         <v>12</v>
@@ -14123,7 +14187,7 @@
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -14165,10 +14229,10 @@
         <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H5">
         <v>228</v>
@@ -14180,7 +14244,7 @@
         <v>13</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L5" t="s">
         <v>160</v>
@@ -14207,10 +14271,10 @@
         <v>208</v>
       </c>
       <c r="F6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H6">
         <v>521</v>
@@ -14222,7 +14286,7 @@
         <v>25</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L6" t="s">
         <v>160</v>
@@ -14249,7 +14313,7 @@
         <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G7" t="s">
         <v>21</v>
@@ -14264,7 +14328,7 @@
         <v>154</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L7" t="s">
         <v>160</v>
@@ -14291,10 +14355,10 @@
         <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H8">
         <v>502</v>
@@ -14333,10 +14397,10 @@
         <v>198</v>
       </c>
       <c r="F9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G9" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>13</v>
@@ -14348,7 +14412,7 @@
         <v>13</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L9" t="s">
         <v>160</v>
@@ -14375,10 +14439,10 @@
         <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G10" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>13</v>
@@ -14390,7 +14454,7 @@
         <v>13</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L10" t="s">
         <v>160</v>
@@ -14417,7 +14481,7 @@
         <v>219</v>
       </c>
       <c r="F11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G11" t="s">
         <v>161</v>
@@ -14459,7 +14523,7 @@
         <v>186</v>
       </c>
       <c r="G12" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H12">
         <v>504</v>
@@ -14471,7 +14535,7 @@
         <v>30</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L12" t="s">
         <v>160</v>
@@ -14498,7 +14562,7 @@
         <v>31</v>
       </c>
       <c r="F13" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G13" t="s">
         <v>32</v>
@@ -14537,13 +14601,13 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
+        <v>302</v>
+      </c>
+      <c r="F14" t="s">
+        <v>283</v>
+      </c>
+      <c r="G14" t="s">
         <v>303</v>
-      </c>
-      <c r="F14" t="s">
-        <v>284</v>
-      </c>
-      <c r="G14" t="s">
-        <v>304</v>
       </c>
       <c r="H14">
         <v>282</v>
@@ -14555,7 +14619,7 @@
         <v>13</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L14" t="s">
         <v>160</v>
@@ -14582,7 +14646,7 @@
         <v>61</v>
       </c>
       <c r="F15" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G15" t="s">
         <v>212</v>
@@ -14597,7 +14661,7 @@
         <v>13</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L15" t="s">
         <v>160</v>
@@ -14624,7 +14688,7 @@
         <v>23</v>
       </c>
       <c r="F16" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G16" t="s">
         <v>225</v>
@@ -14639,7 +14703,7 @@
         <v>13</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L16" t="s">
         <v>160</v>
@@ -14666,7 +14730,7 @@
         <v>39</v>
       </c>
       <c r="F17" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G17" t="s">
         <v>40</v>
@@ -14681,7 +14745,7 @@
         <v>41</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L17" t="s">
         <v>160</v>
@@ -14708,7 +14772,7 @@
         <v>42</v>
       </c>
       <c r="F18" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G18" t="s">
         <v>37</v>
@@ -14723,7 +14787,7 @@
         <v>38</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L18" t="s">
         <v>160</v>
@@ -14750,7 +14814,7 @@
         <v>77</v>
       </c>
       <c r="F19" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G19" t="s">
         <v>37</v>
@@ -14765,7 +14829,7 @@
         <v>13</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L19" t="s">
         <v>160</v>
@@ -14789,10 +14853,10 @@
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F20" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G20" t="s">
         <v>163</v>
@@ -14807,7 +14871,7 @@
         <v>36</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L20" t="s">
         <v>160</v>
@@ -14834,7 +14898,7 @@
         <v>43</v>
       </c>
       <c r="F21" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G21" t="s">
         <v>44</v>
@@ -14849,7 +14913,7 @@
         <v>45</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L21" t="s">
         <v>160</v>
@@ -14861,7 +14925,7 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
         <v>179</v>
@@ -14876,7 +14940,7 @@
         <v>202</v>
       </c>
       <c r="F22" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G22" t="s">
         <v>203</v>
@@ -14891,19 +14955,19 @@
         <v>13</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L22" t="s">
         <v>160</v>
       </c>
       <c r="M22" t="str">
         <f t="shared" ref="M22" si="7">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A22 &amp; "','" &amp; D22 &amp; "','" &amp; E22 &amp; "','" &amp; G22 &amp; "','" &amp; H22 &amp; "','" &amp; I22 &amp;  "','" &amp; J22 &amp;  "','" &amp; K22 &amp;  "','" &amp; L22 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('22','1','Kelly Wan','Digital Artist &amp; Content Creator ','121','---','---','kellywan@livingrealtykw.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('21','1','Kelly Wan','Digital Artist &amp; Content Creator ','121','---','---','kellywan@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
         <v>179</v>
@@ -14918,10 +14982,10 @@
         <v>46</v>
       </c>
       <c r="F23" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G23" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H23">
         <v>522</v>
@@ -14933,19 +14997,19 @@
         <v>48</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L23" t="s">
         <v>160</v>
       </c>
       <c r="M23" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('23','1','Nelson Lau','Senior Technical Specialist &amp; System Architect','522','(647) 701-8828','(905) 752-3522','nelsonlau@livingrealtykw.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('22','1','Nelson Lau','Senior Technical Specialist &amp; System Architect','522','(647) 701-8828','(905) 752-3522','nelsonlau@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
         <v>179</v>
@@ -14972,19 +15036,19 @@
         <v>48</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L24" t="s">
         <v>160</v>
       </c>
       <c r="M24" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('24','1','IT Support','Information Technology Technical Support','522','---','(905) 752-3522','itsupport@livingrealtykw.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('23','1','IT Support','Information Technology Technical Support','522','---','(905) 752-3522','itsupport@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
         <v>51</v>
@@ -14999,7 +15063,7 @@
         <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G25" t="s">
         <v>53</v>
@@ -15014,19 +15078,19 @@
         <v>54</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L25" t="s">
         <v>158</v>
       </c>
       <c r="M25" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('25','2','North Markham Office','735 Markland St, Unit 12&amp;13, Markham, ON, L6C 0G6','--','--','T: (905) 888-8188','northmarkham@livingrealtykw.com','Office Header');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('24','2','North Markham Office','735 Markland St, Unit 12&amp;13, Markham, ON, L6C 0G6','--','--','T: (905) 888-8188','northmarkham@livingrealtykw.com','Office Header');</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
         <v>51</v>
@@ -15041,7 +15105,7 @@
         <v>55</v>
       </c>
       <c r="F26" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G26" t="s">
         <v>56</v>
@@ -15056,19 +15120,19 @@
         <v>13</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L26" t="s">
         <v>160</v>
       </c>
       <c r="M26" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('26','2','Chris Tam','Manager North Markham Branch','---','(416) 505-6625','---','christam@livingrealtykw.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('25','2','Chris Tam','Manager North Markham Branch','---','(416) 505-6625','---','christam@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
         <v>51</v>
@@ -15083,7 +15147,7 @@
         <v>59</v>
       </c>
       <c r="F27" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G27" t="s">
         <v>164</v>
@@ -15098,19 +15162,19 @@
         <v>58</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L27" t="s">
         <v>160</v>
       </c>
       <c r="M27" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('27','2','Grace Chui','Head Secretary','---','---','(905) 888-8188','gracemschui@livingrealtykw.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('26','2','Grace Chui','Head Secretary','---','---','(905) 888-8188','gracemschui@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
         <v>51</v>
@@ -15125,7 +15189,7 @@
         <v>224</v>
       </c>
       <c r="F28" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G28" t="s">
         <v>60</v>
@@ -15140,19 +15204,19 @@
         <v>58</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L28" t="s">
         <v>160</v>
       </c>
       <c r="M28" t="str">
         <f t="shared" ref="M28" si="8">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A28 &amp; "','" &amp; D28 &amp; "','" &amp; E28 &amp; "','" &amp; G28 &amp; "','" &amp; H28 &amp; "','" &amp; I28 &amp;  "','" &amp; J28 &amp;  "','" &amp; K28 &amp;  "','" &amp; L28 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('28','2','Kiran Li','Secretary','---','---','(905) 888-8188','kiranli@livingrealtykw.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('27','2','Kiran Li','Secretary','---','---','(905) 888-8188','kiranli@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" t="s">
         <v>67</v>
@@ -15167,7 +15231,7 @@
         <v>68</v>
       </c>
       <c r="F29" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G29" t="s">
         <v>152</v>
@@ -15182,19 +15246,19 @@
         <v>69</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L29" t="s">
         <v>158</v>
       </c>
       <c r="M29" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('29','4','Mississauga Office','1177 Central Parkway West, Golden Square, Unit 32, Mississauga, ON, L5C 4P3','--','--','T: (905) 896-0002','mississauga@livingrealtykw.com','Office Header');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('28','4','Mississauga Office','1177 Central Parkway West, Golden Square, Unit 32, Mississauga, ON, L5C 4P3','--','--','T: (905) 896-0002','mississauga@livingrealtykw.com','Office Header');</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" t="s">
         <v>67</v>
@@ -15206,10 +15270,10 @@
         <v>4</v>
       </c>
       <c r="E30" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F30" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G30" t="s">
         <v>70</v>
@@ -15224,19 +15288,19 @@
         <v>13</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L30" t="s">
         <v>160</v>
       </c>
       <c r="M30" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('30','4','Cassandra Pacitto','Manager Mississauga Branch','---','(905) 896-0002','---','cassandrapacitto@livingrealtykw.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('29','4','Cassandra Pacitto','Manager Mississauga Branch','---','(905) 896-0002','---','cassandrapacitto@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B31" t="s">
         <v>67</v>
@@ -15248,10 +15312,10 @@
         <v>4</v>
       </c>
       <c r="E31" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F31" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G31" t="s">
         <v>60</v>
@@ -15266,19 +15330,19 @@
         <v>71</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L31" t="s">
         <v>160</v>
       </c>
       <c r="M31" t="str">
-        <f t="shared" ref="M31:M59" si="9">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A31 &amp; "','" &amp; D31 &amp; "','" &amp; E31 &amp; "','" &amp; G31 &amp; "','" &amp; H31 &amp; "','" &amp; I31 &amp;  "','" &amp; J31 &amp;  "','" &amp; K31 &amp;  "','" &amp; L31 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('32','4','Katie Wong','Secretary','---','---','(905) 896-0002','katiewong@livingrealtykw.com','Staff');</v>
+        <f t="shared" ref="M31:M60" si="9">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A31 &amp; "','" &amp; D31 &amp; "','" &amp; E31 &amp; "','" &amp; G31 &amp; "','" &amp; H31 &amp; "','" &amp; I31 &amp;  "','" &amp; J31 &amp;  "','" &amp; K31 &amp;  "','" &amp; L31 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('30','4','Katie Wong','Secretary','---','---','(905) 896-0002','katiewong@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
         <v>67</v>
@@ -15290,10 +15354,10 @@
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F32" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G32" t="s">
         <v>60</v>
@@ -15308,19 +15372,19 @@
         <v>71</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L32" t="s">
         <v>160</v>
       </c>
       <c r="M32" t="str">
         <f t="shared" ref="M32" si="10">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A32 &amp; "','" &amp; D32 &amp; "','" &amp; E32 &amp; "','" &amp; G32 &amp; "','" &amp; H32 &amp; "','" &amp; I32 &amp;  "','" &amp; J32 &amp;  "','" &amp; K32 &amp;  "','" &amp; L32 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('32','4','Juliana Monize','Secretary','---','---','(905) 896-0002','julianamonize@livingrealtykw.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('31','4','Juliana Monize','Secretary','---','---','(905) 896-0002','julianamonize@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
         <v>72</v>
@@ -15335,7 +15399,7 @@
         <v>73</v>
       </c>
       <c r="F33" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G33" t="s">
         <v>9</v>
@@ -15350,19 +15414,19 @@
         <v>74</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L33" t="s">
         <v>158</v>
       </c>
       <c r="M33" t="str">
         <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('33','5','Woodbine Office','8 Steelcase Road West, Markham, ON, L3R 1B2','--','--','T: (905) 474-0500','woodbine@livingrealtykw.com','Office Header');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('32','5','Woodbine Office','8 Steelcase Road West, Markham, ON, L3R 1B2','--','--','T: (905) 474-0500','woodbine@livingrealtykw.com','Office Header');</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
         <v>72</v>
@@ -15377,7 +15441,7 @@
         <v>76</v>
       </c>
       <c r="F34" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G34" t="s">
         <v>75</v>
@@ -15392,19 +15456,19 @@
         <v>13</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L34" t="s">
         <v>160</v>
       </c>
       <c r="M34" t="str">
         <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('34','5','Anita Huang','Manager Woobine Branch','176','(416) 523-1888','---','anitahuang@livingrealtykw.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('33','5','Anita Huang','Manager Woobine Branch','176','(416) 523-1888','---','anitahuang@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B35" t="s">
         <v>72</v>
@@ -15419,7 +15483,7 @@
         <v>79</v>
       </c>
       <c r="F35" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G35" t="s">
         <v>60</v>
@@ -15434,19 +15498,19 @@
         <v>19</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L35" t="s">
         <v>160</v>
       </c>
       <c r="M35" t="str">
         <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('36','5','Savanna Joo','Secretary','100','---','(905) 474-0500','savannajoo@livingrealtykw.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('34','5','Savanna Joo','Secretary','100','---','(905) 474-0500','savannajoo@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
         <v>62</v>
@@ -15461,7 +15525,7 @@
         <v>228</v>
       </c>
       <c r="F36" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G36" t="s">
         <v>221</v>
@@ -15476,19 +15540,19 @@
         <v>63</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L36" t="s">
         <v>158</v>
       </c>
       <c r="M36" t="str">
         <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('37','3','Yonge &amp; Eglinton Office','2301 Yonge Street, Toronto, ON, M4P 2C6','--','--','T: (416) 223-8833','ye@livingrealtykw.com','Office Header');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('35','3','Yonge &amp; Eglinton Office','2301 Yonge Street, Toronto, ON, M4P 2C6','--','--','T: (416) 223-8833','ye@livingrealtykw.com','Office Header');</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B37" t="s">
         <v>62</v>
@@ -15500,37 +15564,37 @@
         <v>3</v>
       </c>
       <c r="E37" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F37" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G37" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I37" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J37" s="6" t="s">
         <v>13</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L37" t="s">
         <v>160</v>
       </c>
       <c r="M37" t="str">
         <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('38','3','Francesco Armogida','Manager Yonge &amp; Eglinton','---','(416) 576-6312','---','francescoarmogida@livingrealtykw.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('36','3','Francesco Armogida','Manager Yonge &amp; Eglinton','---','(416) 576-6312','---','francescoarmogida@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B38" t="s">
         <v>62</v>
@@ -15545,7 +15609,7 @@
         <v>230</v>
       </c>
       <c r="F38" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G38" t="s">
         <v>60</v>
@@ -15560,19 +15624,19 @@
         <v>66</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L38" t="s">
         <v>160</v>
       </c>
       <c r="M38" t="str">
         <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('39','3','Lydia Ng','Secretary','---','---','(416) 223-8833','lydiang@livingrealtykw.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('37','3','Lydia Ng','Secretary','---','---','(416) 223-8833','lydiang@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B39" t="s">
         <v>177</v>
@@ -15606,12 +15670,12 @@
       </c>
       <c r="M39" t="str">
         <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('40','7','I.C.&amp;I. Office','8 Steelcase Road West, Unit C, Markham, ON, L3R 1B2','--','--','T: (905) 474-1772','--','Office Header');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('38','7','I.C.&amp;I. Office','8 Steelcase Road West, Unit C, Markham, ON, L3R 1B2','--','--','T: (905) 474-1772','--','Office Header');</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B40" t="s">
         <v>177</v>
@@ -15626,7 +15690,7 @@
         <v>17</v>
       </c>
       <c r="F40" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G40" t="s">
         <v>84</v>
@@ -15641,19 +15705,19 @@
         <v>13</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L40" t="s">
         <v>160</v>
       </c>
       <c r="M40" t="str">
         <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('41','7','Kelvin Wong','Manager I.C.&amp;I. Branch','228','(416) 567-7882','---','kelvin@livingrealtykw.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('39','7','Kelvin Wong','Manager I.C.&amp;I. Branch','228','(416) 567-7882','---','kelvin@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
         <v>180</v>
@@ -15687,12 +15751,12 @@
       </c>
       <c r="M41" t="str">
         <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('42','8','LPI Head Office','8 Steelcase Road West, Markham, ON, L3R 1B2','--','--','T: (905) 477-2090','--','Office Header');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('40','8','LPI Head Office','8 Steelcase Road West, Markham, ON, L3R 1B2','--','--','T: (905) 477-2090','--','Office Header');</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B42" t="s">
         <v>180</v>
@@ -15726,12 +15790,12 @@
       </c>
       <c r="M42" t="str">
         <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('43','8','Ben Wong','President','521','(416) 399-2311','(905) 752-3521','benw@livingproperties.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('41','8','Ben Wong','President','521','(416) 399-2311','(905) 752-3521','benw@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B43" t="s">
         <v>180</v>
@@ -15765,12 +15829,12 @@
       </c>
       <c r="M43" t="str">
         <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('44','8','Winnie Tsui','Director of Operations','514','(647) 286-0145','(905) 752-3514 ','winniet@livingproperties.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('42','8','Winnie Tsui','Director of Operations','514','(647) 286-0145','(905) 752-3514 ','winniet@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B44" t="s">
         <v>180</v>
@@ -15804,12 +15868,12 @@
       </c>
       <c r="M44" t="str">
         <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('45','8','Frederick Tang','Director of Business Development','286','(416) 618-5898','-','fredt@livingproperties.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('43','8','Frederick Tang','Director of Business Development','286','(416) 618-5898','-','fredt@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B45" t="s">
         <v>180</v>
@@ -15843,12 +15907,12 @@
       </c>
       <c r="M45" t="str">
         <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('47','8','Stanley Chow','Property Manager','512','(416) 277-6098','(905) 752-3512','stanleyc@livingproperties.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('44','8','Stanley Chow','Property Manager','512','(416) 277-6098','(905) 752-3512','stanleyc@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
         <v>180</v>
@@ -15882,12 +15946,12 @@
       </c>
       <c r="M46" t="str">
         <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('48','8','Richard Baksh','Property Manager','284','(647) 967-0088','(905) 258-0632','richardb@livingproperties.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('45','8','Richard Baksh','Property Manager','284','(647) 967-0088','(905) 258-0632','richardb@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
         <v>153</v>
@@ -15921,12 +15985,12 @@
       </c>
       <c r="M47" t="str">
         <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A47 &amp; "','" &amp; D47 &amp; "','" &amp; E47 &amp; "','" &amp; G47 &amp; "','" &amp; H47 &amp; "','" &amp; I47 &amp;  "','" &amp; J47 &amp;  "','" &amp; K47 &amp;  "','" &amp; L47 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('49','8','Ken Kam','Property Manager','517','(647) 204-4455','(905) 477-2090','kenk@livingproperties.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('46','8','Ken Kam','Property Manager','517','(647) 204-4455','(905) 477-2090','kenk@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B48" t="s">
         <v>153</v>
@@ -15938,7 +16002,7 @@
         <v>8</v>
       </c>
       <c r="E48" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G48" t="s">
         <v>91</v>
@@ -15947,25 +16011,25 @@
         <v>520</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J48" t="s">
         <v>95</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L48" t="s">
         <v>160</v>
       </c>
       <c r="M48" t="str">
         <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A48 &amp; "','" &amp; D48 &amp; "','" &amp; E48 &amp; "','" &amp; G48 &amp; "','" &amp; H48 &amp; "','" &amp; I48 &amp;  "','" &amp; J48 &amp;  "','" &amp; K48 &amp;  "','" &amp; L48 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('50','8','Raymond Chin','Property Manager','520','(437) 331-6038','(905) 477-2090','raymondc@livingproperties.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('47','8','Raymond Chin','Property Manager','520','(437) 331-6038','(905) 477-2090','raymondc@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B49" t="s">
         <v>180</v>
@@ -15977,34 +16041,34 @@
         <v>8</v>
       </c>
       <c r="E49" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G49" t="s">
-        <v>233</v>
+        <v>91</v>
       </c>
       <c r="H49">
         <v>168</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J49" t="s">
         <v>95</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L49" t="s">
         <v>160</v>
       </c>
       <c r="M49" t="str">
         <f t="shared" ref="M49" si="11">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A49 &amp; "','" &amp; D49 &amp; "','" &amp; E49 &amp; "','" &amp; G49 &amp; "','" &amp; H49 &amp; "','" &amp; I49 &amp;  "','" &amp; J49 &amp;  "','" &amp; K49 &amp;  "','" &amp; L49 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('51','8','Thomas Lee','Assistant Property Manager','168','(416) 567-4274','(905) 477-2090','Thomasl@livingproperties.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('48','8','Thomas Lee','Property Manager','168','(416) 567-4274','(905) 477-2090','Thomasl@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B50" t="s">
         <v>180</v>
@@ -16016,34 +16080,34 @@
         <v>8</v>
       </c>
       <c r="E50" t="s">
-        <v>110</v>
+        <v>315</v>
       </c>
       <c r="G50" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="H50">
-        <v>210</v>
+        <v>168</v>
       </c>
       <c r="I50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J50" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K50" t="s">
-        <v>111</v>
+      <c r="J50" t="s">
+        <v>95</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>316</v>
       </c>
       <c r="L50" t="s">
         <v>160</v>
       </c>
       <c r="M50" t="str">
-        <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('52','8','Loretta Leung','Executive Assistant','210','---','---','lorettal@livingproperties.com','Staff');</v>
+        <f t="shared" ref="M50" si="12">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A50 &amp; "','" &amp; D50 &amp; "','" &amp; E50 &amp; "','" &amp; G50 &amp; "','" &amp; H50 &amp; "','" &amp; I50 &amp;  "','" &amp; J50 &amp;  "','" &amp; K50 &amp;  "','" &amp; L50 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('49','8','Stanley Wu','Property Manager','168','---','(905) 477-2090','stanleyw@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B51" t="s">
         <v>180</v>
@@ -16055,34 +16119,34 @@
         <v>8</v>
       </c>
       <c r="E51" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="G51" t="s">
-        <v>275</v>
+        <v>35</v>
       </c>
       <c r="H51">
-        <v>518</v>
+        <v>210</v>
       </c>
       <c r="I51" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J51" t="s">
-        <v>156</v>
+      <c r="J51" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="K51" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L51" t="s">
         <v>160</v>
       </c>
       <c r="M51" t="str">
-        <f t="shared" ref="M51" si="12">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A51 &amp; "','" &amp; D51 &amp; "','" &amp; E51 &amp; "','" &amp; G51 &amp; "','" &amp; H51 &amp; "','" &amp; I51 &amp;  "','" &amp; J51 &amp;  "','" &amp; K51 &amp;  "','" &amp; L51 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('53','8','Simon Li','Senior Accountant','518','---','(905) 752-3518','simonl@livingproperties.com','Staff');</v>
+        <f t="shared" si="9"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('50','8','Loretta Leung','Executive Assistant','210','---','---','lorettal@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B52" t="s">
         <v>180</v>
@@ -16094,34 +16158,34 @@
         <v>8</v>
       </c>
       <c r="E52" t="s">
-        <v>209</v>
+        <v>103</v>
       </c>
       <c r="G52" t="s">
-        <v>181</v>
+        <v>274</v>
       </c>
       <c r="H52">
-        <v>281</v>
+        <v>518</v>
       </c>
       <c r="I52" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J52" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K52" s="4" t="s">
-        <v>210</v>
+      <c r="J52" t="s">
+        <v>156</v>
+      </c>
+      <c r="K52" t="s">
+        <v>104</v>
       </c>
       <c r="L52" t="s">
         <v>160</v>
       </c>
       <c r="M52" t="str">
         <f t="shared" ref="M52" si="13">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A52 &amp; "','" &amp; D52 &amp; "','" &amp; E52 &amp; "','" &amp; G52 &amp; "','" &amp; H52 &amp; "','" &amp; I52 &amp;  "','" &amp; J52 &amp;  "','" &amp; K52 &amp;  "','" &amp; L52 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('54','8','Nicole Leung','Property Accountant','281','---','---','nicolel@livingproperties.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('51','8','Simon Li','Senior Accountant','518','---','(905) 752-3518','simonl@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B53" t="s">
         <v>180</v>
@@ -16133,34 +16197,34 @@
         <v>8</v>
       </c>
       <c r="E53" t="s">
-        <v>105</v>
+        <v>209</v>
       </c>
       <c r="G53" t="s">
-        <v>108</v>
+        <v>181</v>
       </c>
       <c r="H53">
-        <v>523</v>
+        <v>281</v>
       </c>
       <c r="I53" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J53" t="s">
-        <v>157</v>
-      </c>
-      <c r="K53" t="s">
-        <v>107</v>
+      <c r="J53" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>210</v>
       </c>
       <c r="L53" t="s">
         <v>160</v>
       </c>
       <c r="M53" t="str">
-        <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('55','8','Vivian Lum','Accounts Receivable Clerk','523','---','(905) 752-3523','vivianl@livingproperties.com','Staff');</v>
+        <f t="shared" ref="M53" si="14">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A53 &amp; "','" &amp; D53 &amp; "','" &amp; E53 &amp; "','" &amp; G53 &amp; "','" &amp; H53 &amp; "','" &amp; I53 &amp;  "','" &amp; J53 &amp;  "','" &amp; K53 &amp;  "','" &amp; L53 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('52','8','Nicole Leung','Property Accountant','281','---','---','nicolel@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54" s="5">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B54" t="s">
         <v>180</v>
@@ -16172,34 +16236,34 @@
         <v>8</v>
       </c>
       <c r="E54" t="s">
-        <v>204</v>
+        <v>105</v>
       </c>
       <c r="G54" t="s">
-        <v>274</v>
+        <v>108</v>
       </c>
       <c r="H54">
-        <v>223</v>
+        <v>523</v>
       </c>
       <c r="I54" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J54" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="K54" s="4" t="s">
-        <v>205</v>
+      <c r="J54" t="s">
+        <v>157</v>
+      </c>
+      <c r="K54" t="s">
+        <v>107</v>
       </c>
       <c r="L54" t="s">
         <v>160</v>
       </c>
       <c r="M54" t="str">
-        <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A54 &amp; "','" &amp; D54 &amp; "','" &amp; E54 &amp; "','" &amp; G54 &amp; "','" &amp; H54 &amp; "','" &amp; I54 &amp;  "','" &amp; J54 &amp;  "','" &amp; K54 &amp;  "','" &amp; L54 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('56','8','Jessica Lee','Accounting Clerk ','223','---','---','jessical@livingproperties.com','Staff');</v>
+        <f t="shared" si="9"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('53','8','Vivian Lum','Accounts Receivable Clerk','523','---','(905) 752-3523','vivianl@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B55" t="s">
         <v>180</v>
@@ -16211,13 +16275,13 @@
         <v>8</v>
       </c>
       <c r="E55" t="s">
-        <v>234</v>
+        <v>204</v>
       </c>
       <c r="G55" t="s">
-        <v>109</v>
+        <v>273</v>
       </c>
       <c r="H55">
-        <v>172</v>
+        <v>223</v>
       </c>
       <c r="I55" s="6" t="s">
         <v>13</v>
@@ -16226,19 +16290,19 @@
         <v>13</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
       <c r="L55" t="s">
         <v>160</v>
       </c>
       <c r="M55" t="str">
-        <f t="shared" ref="M55" si="14">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A55 &amp; "','" &amp; D55 &amp; "','" &amp; E55 &amp; "','" &amp; G55 &amp; "','" &amp; H55 &amp; "','" &amp; I55 &amp;  "','" &amp; J55 &amp;  "','" &amp; K55 &amp;  "','" &amp; L55 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('57','8','Rebecca Lau','Administrative Assistant','172','---','---','rebeccal@livingproperties.com','Staff');</v>
+        <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A55 &amp; "','" &amp; D55 &amp; "','" &amp; E55 &amp; "','" &amp; G55 &amp; "','" &amp; H55 &amp; "','" &amp; I55 &amp;  "','" &amp; J55 &amp;  "','" &amp; K55 &amp;  "','" &amp; L55 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('54','8','Jessica Lee','Accounting Clerk ','223','---','---','jessical@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56" s="5">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B56" t="s">
         <v>180</v>
@@ -16250,13 +16314,13 @@
         <v>8</v>
       </c>
       <c r="E56" t="s">
-        <v>278</v>
+        <v>233</v>
       </c>
       <c r="G56" t="s">
         <v>109</v>
       </c>
       <c r="H56">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="I56" s="6" t="s">
         <v>13</v>
@@ -16265,19 +16329,19 @@
         <v>13</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>279</v>
+        <v>234</v>
       </c>
       <c r="L56" t="s">
         <v>160</v>
       </c>
       <c r="M56" t="str">
-        <f t="shared" ref="M56:M57" si="15">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A56 &amp; "','" &amp; D56 &amp; "','" &amp; E56 &amp; "','" &amp; G56 &amp; "','" &amp; H56 &amp; "','" &amp; I56 &amp;  "','" &amp; J56 &amp;  "','" &amp; K56 &amp;  "','" &amp; L56 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('58','8','Kelvin Chan','Administrative Assistant','182','---','---','kelvinc@livingproperties.com','Staff');</v>
+        <f t="shared" ref="M56" si="15">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A56 &amp; "','" &amp; D56 &amp; "','" &amp; E56 &amp; "','" &amp; G56 &amp; "','" &amp; H56 &amp; "','" &amp; I56 &amp;  "','" &amp; J56 &amp;  "','" &amp; K56 &amp;  "','" &amp; L56 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('55','8','Rebecca Lau','Administrative Assistant','172','---','---','rebeccal@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B57" t="s">
         <v>180</v>
@@ -16289,13 +16353,13 @@
         <v>8</v>
       </c>
       <c r="E57" t="s">
-        <v>155</v>
+        <v>277</v>
       </c>
       <c r="G57" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="H57">
-        <v>229</v>
+        <v>182</v>
       </c>
       <c r="I57" s="6" t="s">
         <v>13</v>
@@ -16303,20 +16367,20 @@
       <c r="J57" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K57" t="s">
-        <v>112</v>
+      <c r="K57" s="4" t="s">
+        <v>278</v>
       </c>
       <c r="L57" t="s">
         <v>160</v>
       </c>
       <c r="M57" t="str">
-        <f t="shared" si="15"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('60','8','Matthew Wong','Accounting Clerk','229','---','---','mattheww@livingproperties.com','Staff');</v>
+        <f t="shared" ref="M57:M58" si="16">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A57 &amp; "','" &amp; D57 &amp; "','" &amp; E57 &amp; "','" &amp; G57 &amp; "','" &amp; H57 &amp; "','" &amp; I57 &amp;  "','" &amp; J57 &amp;  "','" &amp; K57 &amp;  "','" &amp; L57 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('56','8','Kelvin Chan','Administrative Assistant','182','---','---','kelvinc@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58" s="5">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B58" t="s">
         <v>180</v>
@@ -16328,73 +16392,73 @@
         <v>8</v>
       </c>
       <c r="E58" t="s">
-        <v>312</v>
+        <v>155</v>
       </c>
       <c r="G58" t="s">
-        <v>182</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>13</v>
+        <v>106</v>
+      </c>
+      <c r="H58">
+        <v>229</v>
       </c>
       <c r="I58" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J58" t="s">
-        <v>95</v>
-      </c>
-      <c r="K58" s="4" t="s">
-        <v>313</v>
+      <c r="J58" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K58" t="s">
+        <v>112</v>
       </c>
       <c r="L58" t="s">
         <v>160</v>
       </c>
       <c r="M58" t="str">
-        <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('59','8','Gus B','Handyman','---','---','(905) 477-2090','gusb@livcontruction.ca','Staff');</v>
+        <f t="shared" si="16"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('57','8','Matthew Wong','Accounting Clerk','229','---','---','mattheww@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>113</v>
+        <v>180</v>
       </c>
       <c r="C59" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D59">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E59" t="s">
-        <v>114</v>
+        <v>311</v>
       </c>
       <c r="G59" t="s">
-        <v>115</v>
+        <v>182</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>195</v>
+        <v>13</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>195</v>
+        <v>13</v>
       </c>
       <c r="J59" t="s">
-        <v>116</v>
-      </c>
-      <c r="K59" s="6" t="s">
-        <v>195</v>
+        <v>95</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>312</v>
       </c>
       <c r="L59" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M59" t="str">
         <f t="shared" si="9"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('61','9','Centro Towers Office','25 Town Centre Crt, Scarborough, ON, M1P 0B4','--','--','T: (416) 290-1242','--','Office Header');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('58','8','Gus B','Handyman','---','---','(905) 477-2090','gusb@livcontruction.ca','Staff');</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60" s="5">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B60" t="s">
         <v>113</v>
@@ -16406,34 +16470,34 @@
         <v>9</v>
       </c>
       <c r="E60" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G60" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I60" t="s">
-        <v>118</v>
+        <v>195</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>195</v>
       </c>
       <c r="J60" t="s">
-        <v>119</v>
-      </c>
-      <c r="K60" t="s">
-        <v>120</v>
+        <v>116</v>
+      </c>
+      <c r="K60" s="6" t="s">
+        <v>195</v>
       </c>
       <c r="L60" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="M60" t="str">
-        <f t="shared" ref="M60:M82" si="16">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A60 &amp; "','" &amp; D60 &amp; "','" &amp; E60 &amp; "','" &amp; G60 &amp; "','" &amp; H60 &amp; "','" &amp; I60 &amp;  "','" &amp; J60 &amp;  "','" &amp; K60 &amp;  "','" &amp; L60 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('62','9','Henry Fu','Property Manager','---','(416) 278-2953','(416) 290-1242','henry@centrotowers.com','Staff');</v>
+        <f t="shared" si="9"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('59','9','Centro Towers Office','25 Town Centre Crt, Scarborough, ON, M1P 0B4','--','--','T: (416) 290-1242','--','Office Header');</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B61" t="s">
         <v>113</v>
@@ -16445,34 +16509,34 @@
         <v>9</v>
       </c>
       <c r="E61" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G61" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="H61" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I61" s="6" t="s">
-        <v>13</v>
+      <c r="I61" t="s">
+        <v>118</v>
       </c>
       <c r="J61" t="s">
         <v>119</v>
       </c>
       <c r="K61" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="L61" t="s">
         <v>160</v>
       </c>
       <c r="M61" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('63','9','Sophia Yip','Property Administrator','---','---','(416) 290-1242','sophia@centrotowers.com','Staff');</v>
+        <f t="shared" ref="M61:M83" si="17">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A61 &amp; "','" &amp; D61 &amp; "','" &amp; E61 &amp; "','" &amp; G61 &amp; "','" &amp; H61 &amp; "','" &amp; I61 &amp;  "','" &amp; J61 &amp;  "','" &amp; K61 &amp;  "','" &amp; L61 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('60','9','Henry Fu','Property Manager','---','(416) 278-2953','(416) 290-1242','henry@centrotowers.com','Staff');</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62" s="5">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B62" t="s">
         <v>113</v>
@@ -16484,10 +16548,10 @@
         <v>9</v>
       </c>
       <c r="E62" t="s">
-        <v>292</v>
+        <v>121</v>
       </c>
       <c r="G62" t="s">
-        <v>295</v>
+        <v>122</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>13</v>
@@ -16495,59 +16559,59 @@
       <c r="I62" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J62" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="K62" s="6" t="s">
-        <v>13</v>
+      <c r="J62" t="s">
+        <v>119</v>
+      </c>
+      <c r="K62" t="s">
+        <v>123</v>
+      </c>
+      <c r="L62" t="s">
+        <v>160</v>
       </c>
       <c r="M62" t="str">
-        <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A62 &amp; "','" &amp; D62 &amp; "','" &amp; E62 &amp; "','" &amp; G62 &amp; "','" &amp; H62 &amp; "','" &amp; I62 &amp;  "','" &amp; J62 &amp;  "','" &amp; K62 &amp;  "','" &amp; L62 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('64','9','Security Desk ','Centro Security Desk ','---','---','(416) 296-0099','---','');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('61','9','Sophia Yip','Property Administrator','---','---','(416) 290-1242','sophia@centrotowers.com','Staff');</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="C63" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D63">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E63" t="s">
-        <v>139</v>
+        <v>291</v>
       </c>
       <c r="G63" t="s">
-        <v>140</v>
+        <v>294</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>195</v>
+        <v>13</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="J63" t="s">
-        <v>141</v>
-      </c>
-      <c r="K63" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="L63" t="s">
-        <v>158</v>
+        <v>13</v>
+      </c>
+      <c r="J63" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="K63" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="M63" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('65','11','EQ1 Office','70 Town Centre Court, Scarborough, ON, M1P 0B2','--','--','T: (416) 279-0603 ','eq1@livingproperties.com','Office Header');</v>
+        <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A63 &amp; "','" &amp; D63 &amp; "','" &amp; E63 &amp; "','" &amp; G63 &amp; "','" &amp; H63 &amp; "','" &amp; I63 &amp;  "','" &amp; J63 &amp;  "','" &amp; K63 &amp;  "','" &amp; L63 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('62','9','Security Desk ','Centro Security Desk ','---','---','(416) 296-0099','---','');</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64" s="5">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B64" t="s">
         <v>138</v>
@@ -16559,34 +16623,34 @@
         <v>11</v>
       </c>
       <c r="E64" t="s">
-        <v>226</v>
+        <v>139</v>
       </c>
       <c r="G64" t="s">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I64" t="s">
-        <v>223</v>
+        <v>195</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>195</v>
       </c>
       <c r="J64" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="L64" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="M64" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('66','11','Ming Ip','Property Manager','---','(647) 286-0147','(416) 279-0603 ','eq1manager@livingproperties.com','Staff');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('63','11','EQ1 Office','70 Town Centre Court, Scarborough, ON, M1P 0B2','--','--','T: (416) 279-0603 ','eq1@livingproperties.com','Office Header');</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B65" t="s">
         <v>138</v>
@@ -16598,184 +16662,184 @@
         <v>11</v>
       </c>
       <c r="E65" t="s">
-        <v>292</v>
+        <v>226</v>
       </c>
       <c r="G65" t="s">
-        <v>301</v>
+        <v>91</v>
       </c>
       <c r="H65" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I65" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="J65" s="13" t="s">
-        <v>299</v>
-      </c>
-      <c r="K65" s="6" t="s">
-        <v>13</v>
+      <c r="I65" t="s">
+        <v>223</v>
+      </c>
+      <c r="J65" t="s">
+        <v>142</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="L65" t="s">
+        <v>160</v>
       </c>
       <c r="M65" t="str">
-        <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A65 &amp; "','" &amp; D65 &amp; "','" &amp; E65 &amp; "','" &amp; G65 &amp; "','" &amp; H65 &amp; "','" &amp; I65 &amp;  "','" &amp; J65 &amp;  "','" &amp; K65 &amp;  "','" &amp; L65 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('67','11','Security Desk ','EQ1 Security Desk ','---','---','(416) 279-1894','---','');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('64','11','Ming Ip','Property Manager','---','(647) 286-0147','(416) 279-0603 ','eq1manager@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66" s="5">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>297</v>
+        <v>138</v>
       </c>
       <c r="C66" t="s">
+        <v>185</v>
+      </c>
+      <c r="D66">
+        <v>11</v>
+      </c>
+      <c r="E66" t="s">
+        <v>291</v>
+      </c>
+      <c r="G66" t="s">
+        <v>300</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J66" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="D66">
-        <v>12</v>
-      </c>
-      <c r="E66" t="s">
-        <v>265</v>
-      </c>
-      <c r="G66" t="s">
-        <v>267</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="I66" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="J66" t="s">
-        <v>268</v>
-      </c>
       <c r="K66" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="L66" t="s">
-        <v>158</v>
+        <v>13</v>
       </c>
       <c r="M66" t="str">
-        <f t="shared" ref="M66:M67" si="17">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A66 &amp; "','" &amp; D66 &amp; "','" &amp; E66 &amp; "','" &amp; G66 &amp; "','" &amp; H66 &amp; "','" &amp; I66 &amp;  "','" &amp; J66 &amp;  "','" &amp; K66 &amp;  "','" &amp; L66 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('68','12','EQ2 Office','60 Town Centre Court, Scarborough, ON, M1P 0B1','--','--','T: (416) 279-0591 ','--','Office Header');</v>
+        <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A66 &amp; "','" &amp; D66 &amp; "','" &amp; E66 &amp; "','" &amp; G66 &amp; "','" &amp; H66 &amp; "','" &amp; I66 &amp;  "','" &amp; J66 &amp;  "','" &amp; K66 &amp;  "','" &amp; L66 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('65','11','Security Desk ','EQ1 Security Desk ','---','---','(416) 279-1894','---','');</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B67" t="s">
+        <v>296</v>
+      </c>
+      <c r="C67" t="s">
         <v>297</v>
-      </c>
-      <c r="C67" t="s">
-        <v>298</v>
       </c>
       <c r="D67">
         <v>12</v>
       </c>
       <c r="E67" t="s">
+        <v>264</v>
+      </c>
+      <c r="G67" t="s">
         <v>266</v>
       </c>
-      <c r="G67" t="s">
-        <v>91</v>
-      </c>
       <c r="H67" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I67" t="s">
-        <v>270</v>
+        <v>195</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>195</v>
       </c>
       <c r="J67" t="s">
-        <v>269</v>
-      </c>
-      <c r="K67" s="4" t="s">
-        <v>271</v>
+        <v>267</v>
+      </c>
+      <c r="K67" s="6" t="s">
+        <v>195</v>
       </c>
       <c r="L67" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="M67" t="str">
-        <f t="shared" si="17"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('69','12','Aaron Ma','Property Manager','---','(416) 684-2236','(416) 279-0591','eq2manager@livingproperties.com','Staff');</v>
+        <f t="shared" ref="M67:M68" si="18">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A67 &amp; "','" &amp; D67 &amp; "','" &amp; E67 &amp; "','" &amp; G67 &amp; "','" &amp; H67 &amp; "','" &amp; I67 &amp;  "','" &amp; J67 &amp;  "','" &amp; K67 &amp;  "','" &amp; L67 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('66','12','EQ2 Office','60 Town Centre Court, Scarborough, ON, M1P 0B1','--','--','T: (416) 279-0591 ','--','Office Header');</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68" s="5">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B68" t="s">
+        <v>296</v>
+      </c>
+      <c r="C68" t="s">
         <v>297</v>
-      </c>
-      <c r="C68" t="s">
-        <v>298</v>
       </c>
       <c r="D68">
         <v>12</v>
       </c>
       <c r="E68" t="s">
-        <v>292</v>
+        <v>265</v>
       </c>
       <c r="G68" t="s">
-        <v>302</v>
+        <v>91</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I68" s="6" t="s">
-        <v>13</v>
+      <c r="I68" t="s">
+        <v>269</v>
       </c>
       <c r="J68" t="s">
-        <v>300</v>
-      </c>
-      <c r="K68" s="6" t="s">
-        <v>13</v>
+        <v>268</v>
+      </c>
+      <c r="K68" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="L68" t="s">
+        <v>160</v>
       </c>
       <c r="M68" t="str">
-        <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A68 &amp; "','" &amp; D68 &amp; "','" &amp; E68 &amp; "','" &amp; G68 &amp; "','" &amp; H68 &amp; "','" &amp; I68 &amp;  "','" &amp; J68 &amp;  "','" &amp; K68 &amp;  "','" &amp; L68 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('70','12','Security Desk ','EQ2 Security Desk ','---','---','(416) 279-1211','---','');</v>
+        <f t="shared" si="18"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('67','12','Aaron Ma','Property Manager','---','(416) 684-2236','(416) 279-0591','eq2manager@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>213</v>
+        <v>296</v>
       </c>
       <c r="C69" t="s">
-        <v>214</v>
+        <v>297</v>
       </c>
       <c r="D69">
+        <v>12</v>
+      </c>
+      <c r="E69" t="s">
+        <v>291</v>
+      </c>
+      <c r="G69" t="s">
+        <v>301</v>
+      </c>
+      <c r="H69" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E69" t="s">
-        <v>216</v>
-      </c>
-      <c r="G69" t="s">
-        <v>217</v>
-      </c>
-      <c r="H69" s="6" t="s">
-        <v>195</v>
-      </c>
       <c r="I69" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="J69" s="6" t="s">
-        <v>232</v>
+        <v>13</v>
+      </c>
+      <c r="J69" t="s">
+        <v>299</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="L69" t="s">
-        <v>158</v>
+        <v>13</v>
       </c>
       <c r="M69" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('71','13','Alton Tower Office','160 Alton Towers Cir, Toronto, ON, M1V 4X8','--','--','T: (437)-533-1208','--','Office Header');</v>
+        <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A69 &amp; "','" &amp; D69 &amp; "','" &amp; E69 &amp; "','" &amp; G69 &amp; "','" &amp; H69 &amp; "','" &amp; I69 &amp;  "','" &amp; J69 &amp;  "','" &amp; K69 &amp;  "','" &amp; L69 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('68','12','Security Desk ','EQ2 Security Desk ','---','---','(416) 279-1211','---','');</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70" s="5">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B70" t="s">
         <v>213</v>
@@ -16787,34 +16851,34 @@
         <v>13</v>
       </c>
       <c r="E70" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="G70" t="s">
-        <v>91</v>
+        <v>217</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>13</v>
+        <v>195</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="J70" t="s">
-        <v>95</v>
-      </c>
-      <c r="K70" s="4" t="s">
-        <v>207</v>
+        <v>195</v>
+      </c>
+      <c r="J70" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="K70" s="6" t="s">
+        <v>195</v>
       </c>
       <c r="L70" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="M70" t="str">
-        <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A70 &amp; "','" &amp; D70 &amp; "','" &amp; E70 &amp; "','" &amp; G70 &amp; "','" &amp; H70 &amp; "','" &amp; I70 &amp;  "','" &amp; J70 &amp;  "','" &amp; K70 &amp;  "','" &amp; L70 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('72','13','Ken Kam','Property Manager','---','(647) 204-4455','(905) 477-2090','kenk@livingproperties.com','Staff');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('69','13','Alton Tower Office','160 Alton Towers Cir, Toronto, ON, M1V 4X8','--','--','T: (437)-533-1208','--','Office Header');</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B71" t="s">
         <v>213</v>
@@ -16826,34 +16890,34 @@
         <v>13</v>
       </c>
       <c r="E71" t="s">
-        <v>231</v>
+        <v>206</v>
       </c>
       <c r="G71" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="J71" s="6" t="s">
-        <v>13</v>
+        <v>211</v>
+      </c>
+      <c r="J71" t="s">
+        <v>95</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="L71" t="s">
         <v>160</v>
       </c>
       <c r="M71" t="str">
         <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A71 &amp; "','" &amp; D71 &amp; "','" &amp; E71 &amp; "','" &amp; G71 &amp; "','" &amp; H71 &amp; "','" &amp; I71 &amp;  "','" &amp; J71 &amp;  "','" &amp; K71 &amp;  "','" &amp; L71 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('73','13','Christie Ip','Administrative Assistant','---','(437)-533-1208','---','optima2@livingproperties.com ','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('70','13','Ken Kam','Property Manager','---','(647) 204-4455','(905) 477-2090','kenk@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72" s="5">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B72" t="s">
         <v>213</v>
@@ -16865,73 +16929,73 @@
         <v>13</v>
       </c>
       <c r="E72" t="s">
-        <v>292</v>
+        <v>231</v>
       </c>
       <c r="G72" t="s">
-        <v>293</v>
+        <v>109</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I72" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="J72" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J72" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="K72" s="6" t="s">
-        <v>13</v>
+      <c r="K72" s="4" t="s">
+        <v>215</v>
       </c>
       <c r="L72" t="s">
         <v>160</v>
       </c>
       <c r="M72" t="str">
         <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A72 &amp; "','" &amp; D72 &amp; "','" &amp; E72 &amp; "','" &amp; G72 &amp; "','" &amp; H72 &amp; "','" &amp; I72 &amp;  "','" &amp; J72 &amp;  "','" &amp; K72 &amp;  "','" &amp; L72 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('74','13','Security Desk ','Alton Tower Security Desk ','---','---','(416) 754-3131','---','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('71','13','Christie Ip','Administrative Assistant','---','(437)-533-1208','---','optima2@livingproperties.com ','Staff');</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>125</v>
+        <v>213</v>
       </c>
       <c r="C73" t="s">
-        <v>125</v>
+        <v>214</v>
       </c>
       <c r="D73">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E73" t="s">
-        <v>126</v>
+        <v>291</v>
       </c>
       <c r="G73" t="s">
-        <v>9</v>
+        <v>292</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>195</v>
+        <v>13</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="J73" t="s">
-        <v>127</v>
-      </c>
-      <c r="K73" t="s">
-        <v>128</v>
+        <v>13</v>
+      </c>
+      <c r="J73" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="K73" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="L73" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M73" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('75','14','IHMG Office','8 Steelcase Road West, Markham, ON, L3R 1B2','--','--','T: (905) 475-6000','info@ihmg.ca','Office Header');</v>
+        <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A73 &amp; "','" &amp; D73 &amp; "','" &amp; E73 &amp; "','" &amp; G73 &amp; "','" &amp; H73 &amp; "','" &amp; I73 &amp;  "','" &amp; J73 &amp;  "','" &amp; K73 &amp;  "','" &amp; L73 &amp; "');"</f>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('72','13','Security Desk ','Alton Tower Security Desk ','---','---','(416) 754-3131','---','Staff');</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74" s="5">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B74" t="s">
         <v>125</v>
@@ -16943,10 +17007,10 @@
         <v>14</v>
       </c>
       <c r="E74" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G74" t="s">
-        <v>130</v>
+        <v>9</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>195</v>
@@ -16955,22 +17019,22 @@
         <v>195</v>
       </c>
       <c r="J74" t="s">
-        <v>131</v>
-      </c>
-      <c r="K74" s="4" t="s">
-        <v>132</v>
+        <v>127</v>
+      </c>
+      <c r="K74" t="s">
+        <v>128</v>
       </c>
       <c r="L74" t="s">
         <v>158</v>
       </c>
       <c r="M74" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('76','14','IHMGRI Office','8 Steelcase Road West, Unit E, Markham, ON, L3R 1B2','--','--','T: (905) 489-8989','realestate@ihmg.ca','Office Header');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('73','14','IHMG Office','8 Steelcase Road West, Markham, ON, L3R 1B2','--','--','T: (905) 475-6000','info@ihmg.ca','Office Header');</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B75" t="s">
         <v>125</v>
@@ -16982,34 +17046,34 @@
         <v>14</v>
       </c>
       <c r="E75" t="s">
-        <v>186</v>
+        <v>129</v>
       </c>
       <c r="G75" t="s">
-        <v>187</v>
-      </c>
-      <c r="H75">
-        <v>120</v>
-      </c>
-      <c r="I75" t="s">
-        <v>188</v>
+        <v>130</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="I75" s="6" t="s">
+        <v>195</v>
       </c>
       <c r="J75" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>189</v>
+        <v>132</v>
       </c>
       <c r="L75" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="M75" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('77','14','Eddie Tang','Financial Controller','120','(416) 723-8329','(905) 489-0186','eddie@ihmg.ca','Staff');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('74','14','IHMGRI Office','8 Steelcase Road West, Unit E, Markham, ON, L3R 1B2','--','--','T: (905) 489-8989','realestate@ihmg.ca','Office Header');</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76" s="5">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B76" t="s">
         <v>125</v>
@@ -17021,73 +17085,73 @@
         <v>14</v>
       </c>
       <c r="E76" t="s">
-        <v>134</v>
+        <v>186</v>
       </c>
       <c r="G76" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H76">
-        <v>187</v>
+        <v>120</v>
       </c>
       <c r="I76" t="s">
-        <v>135</v>
-      </c>
-      <c r="J76" s="6" t="s">
-        <v>13</v>
+        <v>188</v>
+      </c>
+      <c r="J76" t="s">
+        <v>133</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>136</v>
+        <v>189</v>
       </c>
       <c r="L76" t="s">
         <v>160</v>
       </c>
       <c r="M76" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('78','14','Lily Hou','Senior Accounting Analyst &amp; Operations Support','187','(647) 774-8994','---','lily@ihmg.ca','Staff');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('75','14','Eddie Tang','Financial Controller','120','(416) 723-8329','(905) 489-0186','eddie@ihmg.ca','Staff');</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>179</v>
+        <v>125</v>
       </c>
       <c r="C77" t="s">
-        <v>171</v>
+        <v>125</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E77" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="G77" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H77">
-        <v>541</v>
-      </c>
-      <c r="I77" s="6" t="s">
-        <v>13</v>
+        <v>187</v>
+      </c>
+      <c r="I77" t="s">
+        <v>135</v>
       </c>
       <c r="J77" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K77" s="6" t="s">
-        <v>193</v>
+      <c r="K77" s="4" t="s">
+        <v>136</v>
       </c>
       <c r="L77" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="M77" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('79','1','Lunch Room','Meeting Room','541','---','---','-','Meeting Room');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('76','14','Lily Hou','Senior Accounting Analyst &amp; Operations Support','187','(647) 774-8994','---','lily@ihmg.ca','Staff');</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78" s="5">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B78" t="s">
         <v>179</v>
@@ -17099,13 +17163,13 @@
         <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G78" t="s">
         <v>191</v>
       </c>
       <c r="H78">
-        <v>250</v>
+        <v>541</v>
       </c>
       <c r="I78" s="6" t="s">
         <v>13</v>
@@ -17120,13 +17184,13 @@
         <v>191</v>
       </c>
       <c r="M78" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('80','1','Markham Room','Meeting Room','250','---','---','-','Meeting Room');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('77','1','Lunch Room','Meeting Room','541','---','---','-','Meeting Room');</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B79" t="s">
         <v>179</v>
@@ -17138,13 +17202,13 @@
         <v>1</v>
       </c>
       <c r="E79" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G79" t="s">
         <v>191</v>
       </c>
       <c r="H79">
-        <v>226</v>
+        <v>250</v>
       </c>
       <c r="I79" s="6" t="s">
         <v>13</v>
@@ -17159,13 +17223,13 @@
         <v>191</v>
       </c>
       <c r="M79" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('81','1','Mississauga Room','Meeting Room','226','---','---','-','Meeting Room');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('78','1','Markham Room','Meeting Room','250','---','---','-','Meeting Room');</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80" s="5">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B80" t="s">
         <v>179</v>
@@ -17177,13 +17241,13 @@
         <v>1</v>
       </c>
       <c r="E80" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G80" t="s">
         <v>191</v>
       </c>
       <c r="H80">
-        <v>288</v>
+        <v>226</v>
       </c>
       <c r="I80" s="6" t="s">
         <v>13</v>
@@ -17198,13 +17262,13 @@
         <v>191</v>
       </c>
       <c r="M80" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('82','1','The Living Room','Meeting Room','288','---','---','-','Meeting Room');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('79','1','Mississauga Room','Meeting Room','226','---','---','-','Meeting Room');</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B81" t="s">
         <v>179</v>
@@ -17216,13 +17280,13 @@
         <v>1</v>
       </c>
       <c r="E81" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G81" t="s">
         <v>191</v>
       </c>
       <c r="H81">
-        <v>208</v>
+        <v>288</v>
       </c>
       <c r="I81" s="6" t="s">
         <v>13</v>
@@ -17237,13 +17301,13 @@
         <v>191</v>
       </c>
       <c r="M81" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('83','1','Toronto Room','Meeting Room','208','---','---','-','Meeting Room');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('80','1','The Living Room','Meeting Room','288','---','---','-','Meeting Room');</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82" s="5">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B82" t="s">
         <v>179</v>
@@ -17255,13 +17319,13 @@
         <v>1</v>
       </c>
       <c r="E82" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G82" t="s">
         <v>191</v>
       </c>
       <c r="H82">
-        <v>524</v>
+        <v>208</v>
       </c>
       <c r="I82" s="6" t="s">
         <v>13</v>
@@ -17276,8 +17340,47 @@
         <v>191</v>
       </c>
       <c r="M82" t="str">
-        <f t="shared" si="16"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('84','1','York Room','Meeting Room','524','---','---','-','Meeting Room');</v>
+        <f t="shared" si="17"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('81','1','Toronto Room','Meeting Room','208','---','---','-','Meeting Room');</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A83" s="5">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>179</v>
+      </c>
+      <c r="C83" t="s">
+        <v>171</v>
+      </c>
+      <c r="D83">
+        <v>1</v>
+      </c>
+      <c r="E83" t="s">
+        <v>148</v>
+      </c>
+      <c r="G83" t="s">
+        <v>191</v>
+      </c>
+      <c r="H83">
+        <v>524</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J83" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K83" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="L83" t="s">
+        <v>191</v>
+      </c>
+      <c r="M83" t="str">
+        <f t="shared" si="17"/>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('82','1','York Room','Meeting Room','524','---','---','-','Meeting Room');</v>
       </c>
     </row>
   </sheetData>
@@ -17287,27 +17390,27 @@
     <hyperlink ref="K4" r:id="rId3" xr:uid="{AAC52350-63BC-49E4-AB30-AA515B855C94}"/>
     <hyperlink ref="K29" r:id="rId4" xr:uid="{00DF1362-6E25-4F93-817E-87B7D5053E83}"/>
     <hyperlink ref="K44" r:id="rId5" xr:uid="{52D2CA8B-EEC2-437B-8358-39021C3922A5}"/>
-    <hyperlink ref="K75" r:id="rId6" xr:uid="{39562F23-6CA7-49AB-9C7B-CFFD135D5569}"/>
-    <hyperlink ref="K76" r:id="rId7" xr:uid="{7D0A575D-6D1E-459A-8BE1-834C87DE6FF3}"/>
-    <hyperlink ref="K74" r:id="rId8" xr:uid="{9DB04ED1-2784-42AB-8591-C19CE3C56BAB}"/>
+    <hyperlink ref="K76" r:id="rId6" xr:uid="{39562F23-6CA7-49AB-9C7B-CFFD135D5569}"/>
+    <hyperlink ref="K77" r:id="rId7" xr:uid="{7D0A575D-6D1E-459A-8BE1-834C87DE6FF3}"/>
+    <hyperlink ref="K75" r:id="rId8" xr:uid="{9DB04ED1-2784-42AB-8591-C19CE3C56BAB}"/>
     <hyperlink ref="K9" r:id="rId9" xr:uid="{20EDEC14-38F2-4118-8479-655D5EFC4DEE}"/>
     <hyperlink ref="K31" r:id="rId10" xr:uid="{C9F0094A-C483-4C7B-ABF0-879EAE2A2AB2}"/>
-    <hyperlink ref="K58" r:id="rId11" xr:uid="{859B2763-7E68-453C-A061-50B98A6FFD08}"/>
+    <hyperlink ref="K59" r:id="rId11" xr:uid="{859B2763-7E68-453C-A061-50B98A6FFD08}"/>
     <hyperlink ref="K30" r:id="rId12" xr:uid="{2A81680F-E264-4A37-BA66-E7145340240C}"/>
     <hyperlink ref="K23" r:id="rId13" xr:uid="{C415D613-1570-441D-A891-ED3A35DEB1A5}"/>
     <hyperlink ref="K35" r:id="rId14" xr:uid="{5DA780DA-5AE3-4673-B2D5-44E74D6CADF4}"/>
     <hyperlink ref="K22" r:id="rId15" xr:uid="{D1B93B60-C4A2-4C1E-A23F-AA7F2DF69C12}"/>
-    <hyperlink ref="K54" r:id="rId16" xr:uid="{605D06FB-BDCA-4D83-A43A-BE83330B88FB}"/>
+    <hyperlink ref="K55" r:id="rId16" xr:uid="{605D06FB-BDCA-4D83-A43A-BE83330B88FB}"/>
     <hyperlink ref="K19" r:id="rId17" xr:uid="{B648B368-E192-405E-AF40-90D54C14ED98}"/>
-    <hyperlink ref="K55" r:id="rId18" xr:uid="{808CD1D5-334F-4AE6-8D51-87CD2C3A649E}"/>
-    <hyperlink ref="K52" r:id="rId19" xr:uid="{E8B48719-363A-49FC-B3C8-181E5CD398EA}"/>
+    <hyperlink ref="K56" r:id="rId18" xr:uid="{808CD1D5-334F-4AE6-8D51-87CD2C3A649E}"/>
+    <hyperlink ref="K53" r:id="rId19" xr:uid="{E8B48719-363A-49FC-B3C8-181E5CD398EA}"/>
     <hyperlink ref="K47" r:id="rId20" xr:uid="{741920D7-852F-438F-9B8A-B9ABD3DE381E}"/>
-    <hyperlink ref="K71" r:id="rId21" display="mailto:optima2@livingproperties.com" xr:uid="{FC418030-4EE8-4439-92C7-DD13F00F4D6A}"/>
-    <hyperlink ref="K63" r:id="rId22" xr:uid="{51FF6984-1DC6-430F-8E60-254E7A49BE1B}"/>
-    <hyperlink ref="K70" r:id="rId23" xr:uid="{9681E0BE-E957-4347-8DBD-4A244171852E}"/>
-    <hyperlink ref="K64" r:id="rId24" xr:uid="{30A38D56-4D68-485C-9630-D527FE1A7375}"/>
+    <hyperlink ref="K72" r:id="rId21" display="mailto:optima2@livingproperties.com" xr:uid="{FC418030-4EE8-4439-92C7-DD13F00F4D6A}"/>
+    <hyperlink ref="K64" r:id="rId22" xr:uid="{51FF6984-1DC6-430F-8E60-254E7A49BE1B}"/>
+    <hyperlink ref="K71" r:id="rId23" xr:uid="{9681E0BE-E957-4347-8DBD-4A244171852E}"/>
+    <hyperlink ref="K65" r:id="rId24" xr:uid="{30A38D56-4D68-485C-9630-D527FE1A7375}"/>
     <hyperlink ref="K16" r:id="rId25" xr:uid="{B4D2F180-C9A6-4272-89D7-2F45E07DF9D9}"/>
-    <hyperlink ref="K49" r:id="rId26" xr:uid="{A9377D63-6925-44E0-9C10-08AA1C1392A0}"/>
+    <hyperlink ref="K50" r:id="rId26" xr:uid="{A9377D63-6925-44E0-9C10-08AA1C1392A0}"/>
     <hyperlink ref="K5" r:id="rId27" xr:uid="{4DE7FF7F-49C2-494C-9ADB-BFB49C469051}"/>
     <hyperlink ref="K12" r:id="rId28" xr:uid="{90CB7667-927C-4A55-A4D2-5ECF1714DD75}"/>
     <hyperlink ref="K15" r:id="rId29" xr:uid="{D736220D-F75D-48ED-8215-388BFD7FD301}"/>
@@ -17325,20 +17428,21 @@
     <hyperlink ref="K6" r:id="rId41" xr:uid="{7327C3B3-FC73-4FD4-8E3A-EAE29080795C}"/>
     <hyperlink ref="K7" r:id="rId42" xr:uid="{9835C5DD-A107-49DA-A102-1D32512F3959}"/>
     <hyperlink ref="K11" r:id="rId43" xr:uid="{F46283B7-7116-414C-8181-21C8009155F7}"/>
-    <hyperlink ref="K67" r:id="rId44" xr:uid="{CF0A0F84-6B70-448A-A7E4-353F76C06344}"/>
+    <hyperlink ref="K68" r:id="rId44" xr:uid="{CF0A0F84-6B70-448A-A7E4-353F76C06344}"/>
     <hyperlink ref="K36" r:id="rId45" xr:uid="{F255A40E-E7F9-46E9-80A6-89E7F5CECB64}"/>
     <hyperlink ref="K37" r:id="rId46" xr:uid="{F33CFE79-8711-4EBC-9CB7-252D909356D4}"/>
     <hyperlink ref="K38" r:id="rId47" xr:uid="{B46830F1-4C98-4965-8EC5-D6EBD7A32C28}"/>
-    <hyperlink ref="K56" r:id="rId48" xr:uid="{9D43AF14-0E24-4C14-AD35-9A3EEC0FCFA3}"/>
+    <hyperlink ref="K57" r:id="rId48" xr:uid="{9D43AF14-0E24-4C14-AD35-9A3EEC0FCFA3}"/>
     <hyperlink ref="K48" r:id="rId49" xr:uid="{C4723849-58CB-441D-8956-C096D16EB2A8}"/>
     <hyperlink ref="K10" r:id="rId50" xr:uid="{D399DD4D-94FB-4195-932E-DB5272684B27}"/>
     <hyperlink ref="K14" r:id="rId51" xr:uid="{E60717EF-9C6B-447A-B1BA-FB4D65924041}"/>
     <hyperlink ref="K32" r:id="rId52" xr:uid="{B8F1F465-51CE-4CE4-A2D0-B12797D52113}"/>
+    <hyperlink ref="K49" r:id="rId53" xr:uid="{1E2A7E5E-93B3-44C9-BC85-0CC63A34D9F1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId53"/>
+  <pageSetup orientation="portrait" r:id="rId54"/>
   <tableParts count="1">
-    <tablePart r:id="rId54"/>
+    <tablePart r:id="rId55"/>
   </tableParts>
 </worksheet>
 </file>
@@ -17424,6 +17528,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FCEEF5D6F9A2C14292C82E7F88E7D4C7" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="770a5493e01cc46570af888c0fd11107">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6e07a911-1c82-455b-ae09-b73935b22a66" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="de63ad8f9259e2f5a7ae7a5921e0e8ad" ns2:_="">
     <xsd:import namespace="6e07a911-1c82-455b-ae09-b73935b22a66"/>
@@ -17555,22 +17674,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDCD3F55-29C2-4E12-8D9A-9EC0083C9C49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="6e07a911-1c82-455b-ae09-b73935b22a66"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C569B7B-6177-4C5F-B641-1220485D9B3F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4188865-1BAB-459E-8F28-5F6AB5F6EAC9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17586,28 +17714,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C569B7B-6177-4C5F-B641-1220485D9B3F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDCD3F55-29C2-4E12-8D9A-9EC0083C9C49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="6e07a911-1c82-455b-ae09-b73935b22a66"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/companydirectorypdf/companydir.xlsx
+++ b/companydirectorypdf/companydir.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nelso\Documents\GitHub\intranetportal\companydirectorypdf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E455100-B071-48BE-BB27-2A81CFA06E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00745D77-F093-4E29-8846-2DE0307914F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-16440" windowWidth="29040" windowHeight="15720" xr2:uid="{AE6EE1E0-C559-4053-97E8-B14EEDB6E6F6}"/>
+    <workbookView xWindow="-90" yWindow="-16440" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{AE6EE1E0-C559-4053-97E8-B14EEDB6E6F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Letter Size" sheetId="8" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="323">
   <si>
     <t>Company Directory</t>
   </si>
@@ -907,18 +907,9 @@
     <t>Education and Training Co-ordinator</t>
   </si>
   <si>
-    <t xml:space="preserve">Tony Prochilo </t>
-  </si>
-  <si>
     <t>Manager Yonge &amp; Eglinton</t>
   </si>
   <si>
-    <t>(416) 576-6312</t>
-  </si>
-  <si>
-    <t>tonyprochilo@livingrealtykw.com</t>
-  </si>
-  <si>
     <t>Thomas Lee</t>
   </si>
   <si>
@@ -1013,6 +1004,12 @@
   </si>
   <si>
     <t>Senior Technical Specialist &amp; System Architech</t>
+  </si>
+  <si>
+    <t>francescoarmogida@livingrealtykw.com</t>
+  </si>
+  <si>
+    <t>Francesco Armogida</t>
   </si>
 </sst>
 </file>
@@ -2012,7 +2009,7 @@
       </c>
       <c r="H1" s="11"/>
       <c r="I1" s="11" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
@@ -3272,7 +3269,7 @@
       </c>
       <c r="B40" s="3" t="str">
         <f>ContactData!E39</f>
-        <v xml:space="preserve">Tony Prochilo </v>
+        <v>Francesco Armogida</v>
       </c>
       <c r="C40" s="3" t="str">
         <f>ContactData!G39</f>
@@ -3280,7 +3277,7 @@
       </c>
       <c r="D40" s="9" t="str">
         <f>IF(LEN(ContactData!I39)&lt;3,"",ContactData!I39)</f>
-        <v>(416) 576-6312</v>
+        <v>---</v>
       </c>
       <c r="E40" s="3" t="str">
         <f>ContactData!J39</f>
@@ -3288,7 +3285,7 @@
       </c>
       <c r="F40" s="3" t="str">
         <f>IF(LEN(ContactData!K39)&lt;3,"",ContactData!K39)</f>
-        <v>tonyprochilo@livingrealtykw.com</v>
+        <v>francescoarmogida@livingrealtykw.com</v>
       </c>
       <c r="G40"/>
       <c r="H40"/>
@@ -8646,7 +8643,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -9752,7 +9749,7 @@
       </c>
       <c r="B40" s="3" t="str">
         <f>ContactData!E39</f>
-        <v xml:space="preserve">Tony Prochilo </v>
+        <v>Francesco Armogida</v>
       </c>
       <c r="C40" s="3" t="str">
         <f>ContactData!G39</f>
@@ -9760,7 +9757,7 @@
       </c>
       <c r="D40" s="9" t="str">
         <f>IF(LEN(ContactData!I39)&lt;3,"",ContactData!I39)</f>
-        <v>(416) 576-6312</v>
+        <v>---</v>
       </c>
       <c r="E40" s="3" t="str">
         <f>ContactData!J39</f>
@@ -9768,7 +9765,7 @@
       </c>
       <c r="F40" s="3" t="str">
         <f>IF(LEN(ContactData!K39)&lt;3,"",ContactData!K39)</f>
-        <v>tonyprochilo@livingrealtykw.com</v>
+        <v>francescoarmogida@livingrealtykw.com</v>
       </c>
       <c r="G40"/>
       <c r="H40"/>
@@ -14747,7 +14744,7 @@
         <v>285</v>
       </c>
       <c r="G14" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="H14">
         <v>224</v>
@@ -14756,10 +14753,10 @@
         <v>13</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="L14" t="s">
         <v>160</v>
@@ -14783,13 +14780,13 @@
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F15" t="s">
         <v>285</v>
       </c>
       <c r="G15" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="H15">
         <v>282</v>
@@ -14801,7 +14798,7 @@
         <v>13</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="L15" t="s">
         <v>160</v>
@@ -15167,7 +15164,7 @@
         <v>285</v>
       </c>
       <c r="G24" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H24">
         <v>522</v>
@@ -15452,7 +15449,7 @@
         <v>4</v>
       </c>
       <c r="E31" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F31" t="s">
         <v>285</v>
@@ -15470,7 +15467,7 @@
         <v>13</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="L31" t="s">
         <v>160</v>
@@ -15536,7 +15533,7 @@
         <v>4</v>
       </c>
       <c r="E33" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F33" t="s">
         <v>285</v>
@@ -15554,7 +15551,7 @@
         <v>71</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="L33" t="s">
         <v>160</v>
@@ -15704,7 +15701,7 @@
         <v>5</v>
       </c>
       <c r="E37" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F37" t="s">
         <v>285</v>
@@ -15722,7 +15719,7 @@
         <v>19</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="L37" t="s">
         <v>160</v>
@@ -15788,32 +15785,32 @@
         <v>3</v>
       </c>
       <c r="E39" t="s">
-        <v>288</v>
+        <v>322</v>
       </c>
       <c r="F39" t="s">
         <v>285</v>
       </c>
       <c r="G39" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="I39" t="s">
-        <v>290</v>
+      <c r="I39" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="J39" s="6" t="s">
         <v>13</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>291</v>
+        <v>321</v>
       </c>
       <c r="L39" t="s">
         <v>160</v>
       </c>
       <c r="M39" t="str">
         <f t="shared" si="10"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('38','3','Tony Prochilo ','Manager Yonge &amp; Eglinton','---','(416) 576-6312','---','tonyprochilo@livingrealtykw.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('38','3','Francesco Armogida','Manager Yonge &amp; Eglinton','---','---','---','francescoarmogida@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
@@ -16265,7 +16262,7 @@
         <v>8</v>
       </c>
       <c r="E51" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="G51" t="s">
         <v>91</v>
@@ -16274,13 +16271,13 @@
         <v>168</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="J51" t="s">
         <v>95</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="L51" t="s">
         <v>160</v>
@@ -16304,7 +16301,7 @@
         <v>8</v>
       </c>
       <c r="E52" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="G52" t="s">
         <v>91</v>
@@ -16319,7 +16316,7 @@
         <v>95</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="L52" t="s">
         <v>160</v>
@@ -16616,7 +16613,7 @@
         <v>8</v>
       </c>
       <c r="E60" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G60" t="s">
         <v>182</v>
@@ -16631,7 +16628,7 @@
         <v>95</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="L60" t="s">
         <v>160</v>
@@ -16811,10 +16808,10 @@
         <v>9</v>
       </c>
       <c r="E65" t="s">
+        <v>292</v>
+      </c>
+      <c r="G65" t="s">
         <v>295</v>
-      </c>
-      <c r="G65" t="s">
-        <v>298</v>
       </c>
       <c r="H65" s="6" t="s">
         <v>13</v>
@@ -16823,7 +16820,7 @@
         <v>13</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="K65" s="6" t="s">
         <v>13</v>
@@ -16925,10 +16922,10 @@
         <v>11</v>
       </c>
       <c r="E68" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G68" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>13</v>
@@ -16937,7 +16934,7 @@
         <v>13</v>
       </c>
       <c r="J68" s="13" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>13</v>
@@ -16952,10 +16949,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C69" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D69">
         <v>12</v>
@@ -16991,10 +16988,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C70" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D70">
         <v>12</v>
@@ -17030,19 +17027,19 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C71" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D71">
         <v>12</v>
       </c>
       <c r="E71" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G71" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>13</v>
@@ -17051,7 +17048,7 @@
         <v>13</v>
       </c>
       <c r="J71" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>13</v>
@@ -17192,10 +17189,10 @@
         <v>13</v>
       </c>
       <c r="E75" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G75" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>13</v>
@@ -17204,7 +17201,7 @@
         <v>13</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>13</v>
@@ -17754,6 +17751,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FCEEF5D6F9A2C14292C82E7F88E7D4C7" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="770a5493e01cc46570af888c0fd11107">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6e07a911-1c82-455b-ae09-b73935b22a66" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="de63ad8f9259e2f5a7ae7a5921e0e8ad" ns2:_="">
     <xsd:import namespace="6e07a911-1c82-455b-ae09-b73935b22a66"/>
@@ -17885,22 +17897,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDCD3F55-29C2-4E12-8D9A-9EC0083C9C49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="6e07a911-1c82-455b-ae09-b73935b22a66"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C569B7B-6177-4C5F-B641-1220485D9B3F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4188865-1BAB-459E-8F28-5F6AB5F6EAC9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17916,28 +17937,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C569B7B-6177-4C5F-B641-1220485D9B3F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDCD3F55-29C2-4E12-8D9A-9EC0083C9C49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="6e07a911-1c82-455b-ae09-b73935b22a66"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/companydirectorypdf/companydir.xlsx
+++ b/companydirectorypdf/companydir.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nelso\Documents\GitHub\intranetportal\companydirectorypdf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00745D77-F093-4E29-8846-2DE0307914F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B65ED78-C8E5-4D5C-B9EB-C22FFA48DBD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-16440" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{AE6EE1E0-C559-4053-97E8-B14EEDB6E6F6}"/>
+    <workbookView xWindow="-90" yWindow="-16440" windowWidth="29040" windowHeight="15720" xr2:uid="{AE6EE1E0-C559-4053-97E8-B14EEDB6E6F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Letter Size" sheetId="8" r:id="rId1"/>
@@ -988,9 +988,6 @@
     <t>stanleyw@livingproperties.com</t>
   </si>
   <si>
-    <t>Update Date: Apr 28, 2026</t>
-  </si>
-  <si>
     <t>Juliana Monize</t>
   </si>
   <si>
@@ -1010,6 +1007,9 @@
   </si>
   <si>
     <t>Francesco Armogida</t>
+  </si>
+  <si>
+    <t>Update Date: May 4, 2026</t>
   </si>
 </sst>
 </file>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="H1" s="11"/>
       <c r="I1" s="11" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
@@ -3681,7 +3681,7 @@
     <row r="53" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="9">
         <f>IF(LEN(ContactData!H52)&lt;3,"",ContactData!H52)</f>
-        <v>168</v>
+        <v>516</v>
       </c>
       <c r="B53" s="3" t="str">
         <f>ContactData!E52</f>
@@ -8643,7 +8643,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -10122,7 +10122,7 @@
     <row r="53" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="9">
         <f>IF(LEN(ContactData!H52)&lt;3,"",ContactData!H52)</f>
-        <v>168</v>
+        <v>516</v>
       </c>
       <c r="B53" s="3" t="str">
         <f>ContactData!E52</f>
@@ -15164,7 +15164,7 @@
         <v>285</v>
       </c>
       <c r="G24" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H24">
         <v>522</v>
@@ -15533,7 +15533,7 @@
         <v>4</v>
       </c>
       <c r="E33" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F33" t="s">
         <v>285</v>
@@ -15551,7 +15551,7 @@
         <v>71</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L33" t="s">
         <v>160</v>
@@ -15785,7 +15785,7 @@
         <v>3</v>
       </c>
       <c r="E39" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F39" t="s">
         <v>285</v>
@@ -15803,7 +15803,7 @@
         <v>13</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L39" t="s">
         <v>160</v>
@@ -16307,7 +16307,7 @@
         <v>91</v>
       </c>
       <c r="H52">
-        <v>168</v>
+        <v>516</v>
       </c>
       <c r="I52" s="6" t="s">
         <v>13</v>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="M52" t="str">
         <f t="shared" ref="M52" si="14">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A52 &amp; "','" &amp; D52 &amp; "','" &amp; E52 &amp; "','" &amp; G52 &amp; "','" &amp; H52 &amp; "','" &amp; I52 &amp;  "','" &amp; J52 &amp;  "','" &amp; K52 &amp;  "','" &amp; L52 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('51','8','Stanley Wu','Property Manager','168','---','(905) 477-2090','stanleyw@livingproperties.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('51','8','Stanley Wu','Property Manager','516','---','(905) 477-2090','stanleyw@livingproperties.com','Staff');</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.3">
@@ -16613,7 +16613,7 @@
         <v>8</v>
       </c>
       <c r="E60" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G60" t="s">
         <v>182</v>
@@ -16628,7 +16628,7 @@
         <v>95</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="L60" t="s">
         <v>160</v>
@@ -17751,21 +17751,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FCEEF5D6F9A2C14292C82E7F88E7D4C7" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="770a5493e01cc46570af888c0fd11107">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6e07a911-1c82-455b-ae09-b73935b22a66" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="de63ad8f9259e2f5a7ae7a5921e0e8ad" ns2:_="">
     <xsd:import namespace="6e07a911-1c82-455b-ae09-b73935b22a66"/>
@@ -17897,31 +17882,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDCD3F55-29C2-4E12-8D9A-9EC0083C9C49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="6e07a911-1c82-455b-ae09-b73935b22a66"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C569B7B-6177-4C5F-B641-1220485D9B3F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4188865-1BAB-459E-8F28-5F6AB5F6EAC9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17937,4 +17913,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C569B7B-6177-4C5F-B641-1220485D9B3F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDCD3F55-29C2-4E12-8D9A-9EC0083C9C49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="6e07a911-1c82-455b-ae09-b73935b22a66"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/companydirectorypdf/companydir.xlsx
+++ b/companydirectorypdf/companydir.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nelso\Documents\GitHub\intranetportal\companydirectorypdf\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nelso\Documents\GitHub\kwlivingrealtydrive\kwlrportal\companydirectorypdf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B65ED78-C8E5-4D5C-B9EB-C22FFA48DBD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43432359-15C2-4174-9CD9-DBEB4D35369A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-16440" windowWidth="29040" windowHeight="15720" xr2:uid="{AE6EE1E0-C559-4053-97E8-B14EEDB6E6F6}"/>
+    <workbookView xWindow="-90" yWindow="-16440" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{AE6EE1E0-C559-4053-97E8-B14EEDB6E6F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Letter Size" sheetId="8" r:id="rId1"/>
@@ -112,9 +112,6 @@
     <t>(416) 230-8866</t>
   </si>
   <si>
-    <t>Benjamin Wong</t>
-  </si>
-  <si>
     <t>(416) 399-2311</t>
   </si>
   <si>
@@ -835,9 +832,6 @@
     <t>Broker of Record, Living Realty</t>
   </si>
   <si>
-    <t>benjaminwongici@livingrealtykw.com</t>
-  </si>
-  <si>
     <t>ye@livingrealtykw.com</t>
   </si>
   <si>
@@ -961,15 +955,9 @@
     <t>(905) 489-8989</t>
   </si>
   <si>
-    <t>Joanna Xie</t>
-  </si>
-  <si>
     <t>Agent Services Coordinator</t>
   </si>
   <si>
-    <t>joannaxie@livingrealtykw.com</t>
-  </si>
-  <si>
     <t>Cassandra Pacitto</t>
   </si>
   <si>
@@ -1010,6 +998,18 @@
   </si>
   <si>
     <t>Update Date: May 4, 2026</t>
+  </si>
+  <si>
+    <t>Alvir Tanghal</t>
+  </si>
+  <si>
+    <t>alvirtanghal@livingrealtykw.com</t>
+  </si>
+  <si>
+    <t>sunnyren@livingrealtykw.com</t>
+  </si>
+  <si>
+    <t>Sunny Ren</t>
   </si>
 </sst>
 </file>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="H1" s="11"/>
       <c r="I1" s="11" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
@@ -2020,7 +2020,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>3</v>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="G2"/>
       <c r="H2" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I2" s="10" t="s">
         <v>1</v>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="B16" s="3" t="str">
         <f>ContactData!E15</f>
-        <v>Joanna Xie</v>
+        <v>Sunny Ren</v>
       </c>
       <c r="C16" s="3" t="str">
         <f>ContactData!G15</f>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="F16" s="3" t="str">
         <f>IF(LEN(ContactData!K15)&lt;3,"",ContactData!K15)</f>
-        <v>joannaxie@livingrealtykw.com</v>
+        <v>sunnyren@livingrealtykw.com</v>
       </c>
       <c r="G16"/>
       <c r="H16"/>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B18" s="3" t="str">
         <f>ContactData!E17</f>
-        <v>Benjamin Wong</v>
+        <v>Alvir Tanghal</v>
       </c>
       <c r="C18" s="3" t="str">
         <f>ContactData!G17</f>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="F18" s="3" t="str">
         <f>IF(LEN(ContactData!K17)&lt;3,"",ContactData!K17)</f>
-        <v>benjaminwongici@livingrealtykw.com</v>
+        <v>alvirtanghal@livingrealtykw.com</v>
       </c>
       <c r="G18"/>
       <c r="H18"/>
@@ -8643,7 +8643,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -8654,7 +8654,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>3</v>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="B16" s="3" t="str">
         <f>ContactData!E15</f>
-        <v>Joanna Xie</v>
+        <v>Sunny Ren</v>
       </c>
       <c r="C16" s="3" t="str">
         <f>ContactData!G15</f>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="F16" s="3" t="str">
         <f>IF(LEN(ContactData!K15)&lt;3,"",ContactData!K15)</f>
-        <v>joannaxie@livingrealtykw.com</v>
+        <v>sunnyren@livingrealtykw.com</v>
       </c>
       <c r="G16"/>
       <c r="H16"/>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="B18" s="3" t="str">
         <f>ContactData!E17</f>
-        <v>Benjamin Wong</v>
+        <v>Alvir Tanghal</v>
       </c>
       <c r="C18" s="3" t="str">
         <f>ContactData!G17</f>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="F18" s="3" t="str">
         <f>IF(LEN(ContactData!K17)&lt;3,"",ContactData!K17)</f>
-        <v>benjaminwongici@livingrealtykw.com</v>
+        <v>alvirtanghal@livingrealtykw.com</v>
       </c>
       <c r="G18"/>
       <c r="H18"/>
@@ -14187,43 +14187,43 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" t="s">
         <v>165</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>166</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E1" t="s">
         <v>167</v>
       </c>
-      <c r="D1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E1" t="s">
-        <v>168</v>
-      </c>
       <c r="F1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H1" t="s">
         <v>1</v>
       </c>
       <c r="I1" t="s">
+        <v>168</v>
+      </c>
+      <c r="J1" t="s">
         <v>169</v>
-      </c>
-      <c r="J1" t="s">
-        <v>170</v>
       </c>
       <c r="K1" t="s">
         <v>5</v>
       </c>
       <c r="L1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -14231,10 +14231,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -14246,19 +14246,19 @@
         <v>9</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J2" t="s">
         <v>10</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M2" t="str">
         <f t="shared" ref="M2:M31" si="0">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A2 &amp; "','" &amp; D2 &amp; "','" &amp; E2 &amp; "','" &amp; G2 &amp; "','" &amp; H2 &amp; "','" &amp; I2 &amp;  "','" &amp; J2 &amp;  "','" &amp; K2 &amp;  "','" &amp; L2 &amp; "');"</f>
@@ -14270,10 +14270,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -14282,7 +14282,7 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G3" t="s">
         <v>12</v>
@@ -14294,13 +14294,13 @@
         <v>13</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K3" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="L3" t="s">
         <v>159</v>
-      </c>
-      <c r="L3" t="s">
-        <v>160</v>
       </c>
       <c r="M3" t="str">
         <f t="shared" si="0"/>
@@ -14312,10 +14312,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -14324,7 +14324,7 @@
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G4" t="s">
         <v>15</v>
@@ -14336,13 +14336,13 @@
         <v>16</v>
       </c>
       <c r="J4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M4" t="str">
         <f t="shared" si="0"/>
@@ -14354,10 +14354,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -14366,10 +14366,10 @@
         <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H5">
         <v>228</v>
@@ -14381,10 +14381,10 @@
         <v>13</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M5" t="str">
         <f t="shared" si="0"/>
@@ -14396,37 +14396,37 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F6" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H6">
         <v>521</v>
       </c>
       <c r="I6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" t="s">
         <v>24</v>
       </c>
-      <c r="J6" t="s">
-        <v>25</v>
-      </c>
       <c r="K6" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M6" t="str">
         <f t="shared" ref="M6:M7" si="1">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A6 &amp; "','" &amp; D6 &amp; "','" &amp; E6 &amp; "','" &amp; G6 &amp; "','" &amp; H6 &amp; "','" &amp; I6 &amp;  "','" &amp; J6 &amp;  "','" &amp; K6 &amp;  "','" &amp; L6 &amp; "');"</f>
@@ -14438,10 +14438,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C7" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -14450,7 +14450,7 @@
         <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G7" t="s">
         <v>21</v>
@@ -14462,13 +14462,13 @@
         <v>22</v>
       </c>
       <c r="J7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M7" t="str">
         <f t="shared" si="1"/>
@@ -14480,37 +14480,37 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H8">
         <v>502</v>
       </c>
       <c r="I8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" t="s">
         <v>28</v>
       </c>
-      <c r="J8" t="s">
-        <v>29</v>
-      </c>
       <c r="K8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M8" t="str">
         <f t="shared" si="0"/>
@@ -14522,37 +14522,37 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F9" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>13</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M9" t="str">
         <f t="shared" si="0"/>
@@ -14564,37 +14564,37 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F10" t="s">
+        <v>283</v>
+      </c>
+      <c r="G10" t="s">
         <v>285</v>
-      </c>
-      <c r="G10" t="s">
-        <v>287</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>13</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M10" t="str">
         <f t="shared" ref="M10" si="2">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A10 &amp; "','" &amp; D10 &amp; "','" &amp; E10 &amp; "','" &amp; G10 &amp; "','" &amp; H10 &amp; "','" &amp; I10 &amp;  "','" &amp; J10 &amp;  "','" &amp; K10 &amp;  "','" &amp; L10 &amp; "');"</f>
@@ -14606,37 +14606,37 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F11" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H11">
         <v>509</v>
       </c>
       <c r="I11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>13</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M11" t="str">
         <f t="shared" ref="M11" si="3">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A11 &amp; "','" &amp; D11 &amp; "','" &amp; E11 &amp; "','" &amp; G11 &amp; "','" &amp; H11 &amp; "','" &amp; I11 &amp;  "','" &amp; J11 &amp;  "','" &amp; K11 &amp;  "','" &amp; L11 &amp; "');"</f>
@@ -14648,34 +14648,34 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G12" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H12">
         <v>504</v>
       </c>
       <c r="I12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="L12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M12" t="str">
         <f t="shared" si="0"/>
@@ -14687,37 +14687,37 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" t="s">
+        <v>283</v>
+      </c>
+      <c r="G13" t="s">
         <v>31</v>
-      </c>
-      <c r="F13" t="s">
-        <v>285</v>
-      </c>
-      <c r="G13" t="s">
-        <v>32</v>
       </c>
       <c r="H13">
         <v>514</v>
       </c>
       <c r="I13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M13" t="str">
         <f t="shared" si="0"/>
@@ -14729,22 +14729,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C14" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D14">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F14" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G14" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H14">
         <v>224</v>
@@ -14753,13 +14753,13 @@
         <v>13</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="L14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M14" t="str">
         <f t="shared" ref="M14" si="4">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A14 &amp; "','" &amp; D14 &amp; "','" &amp; E14 &amp; "','" &amp; G14 &amp; "','" &amp; H14 &amp; "','" &amp; I14 &amp;  "','" &amp; J14 &amp;  "','" &amp; K14 &amp;  "','" &amp; L14 &amp; "');"</f>
@@ -14771,22 +14771,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C15" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D15">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="F15" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G15" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H15">
         <v>282</v>
@@ -14798,14 +14798,14 @@
         <v>13</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="L15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M15" t="str">
         <f t="shared" ref="M15" si="5">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A15 &amp; "','" &amp; D15 &amp; "','" &amp; E15 &amp; "','" &amp; G15 &amp; "','" &amp; H15 &amp; "','" &amp; I15 &amp;  "','" &amp; J15 &amp;  "','" &amp; K15 &amp;  "','" &amp; L15 &amp; "');"</f>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('14','1','Joanna Xie','Agent Services Coordinator','282','---','---','joannaxie@livingrealtykw.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('14','1','Sunny Ren','Agent Services Coordinator','282','---','---','sunnyren@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
@@ -14813,22 +14813,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F16" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G16" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H16">
         <v>123</v>
@@ -14840,10 +14840,10 @@
         <v>13</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L16" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M16" t="str">
         <f t="shared" si="0"/>
@@ -14855,22 +14855,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>23</v>
+        <v>319</v>
       </c>
       <c r="F17" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G17" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H17">
         <v>206</v>
@@ -14882,14 +14882,14 @@
         <v>13</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>264</v>
+        <v>320</v>
       </c>
       <c r="L17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M17" t="str">
         <f t="shared" si="0"/>
-        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('16','1','Benjamin Wong','Assistant to the Broker of Record','206','---','---','benjaminwongici@livingrealtykw.com','Staff');</v>
+        <v>INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('16','1','Alvir Tanghal','Assistant to the Broker of Record','206','---','---','alvirtanghal@livingrealtykw.com','Staff');</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
@@ -14897,22 +14897,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" t="s">
+        <v>283</v>
+      </c>
+      <c r="G18" t="s">
         <v>39</v>
-      </c>
-      <c r="F18" t="s">
-        <v>285</v>
-      </c>
-      <c r="G18" t="s">
-        <v>40</v>
       </c>
       <c r="H18">
         <v>507</v>
@@ -14921,13 +14921,13 @@
         <v>13</v>
       </c>
       <c r="J18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M18" t="str">
         <f t="shared" si="0"/>
@@ -14939,22 +14939,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F19" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H19">
         <v>508</v>
@@ -14963,13 +14963,13 @@
         <v>13</v>
       </c>
       <c r="J19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M19" t="str">
         <f t="shared" si="0"/>
@@ -14981,22 +14981,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D20">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F20" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H20">
         <v>255</v>
@@ -15008,10 +15008,10 @@
         <v>13</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L20" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M20" t="str">
         <f t="shared" ref="M20" si="6">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A20 &amp; "','" &amp; D20 &amp; "','" &amp; E20 &amp; "','" &amp; G20 &amp; "','" &amp; H20 &amp; "','" &amp; I20 &amp;  "','" &amp; J20 &amp;  "','" &amp; K20 &amp;  "','" &amp; L20 &amp; "');"</f>
@@ -15023,22 +15023,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C21" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D21">
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F21" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G21" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H21">
         <v>506</v>
@@ -15047,13 +15047,13 @@
         <v>13</v>
       </c>
       <c r="J21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="L21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M21" t="str">
         <f t="shared" ref="M21" si="7">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A21 &amp; "','" &amp; D21 &amp; "','" &amp; E21 &amp; "','" &amp; G21 &amp; "','" &amp; H21 &amp; "','" &amp; I21 &amp;  "','" &amp; J21 &amp;  "','" &amp; K21 &amp;  "','" &amp; L21 &amp; "');"</f>
@@ -15065,22 +15065,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C22" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" t="s">
+        <v>283</v>
+      </c>
+      <c r="G22" t="s">
         <v>43</v>
-      </c>
-      <c r="F22" t="s">
-        <v>285</v>
-      </c>
-      <c r="G22" t="s">
-        <v>44</v>
       </c>
       <c r="H22">
         <v>519</v>
@@ -15089,13 +15089,13 @@
         <v>13</v>
       </c>
       <c r="J22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L22" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M22" t="str">
         <f t="shared" si="0"/>
@@ -15107,22 +15107,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D23">
         <v>1</v>
       </c>
       <c r="E23" t="s">
+        <v>201</v>
+      </c>
+      <c r="F23" t="s">
+        <v>283</v>
+      </c>
+      <c r="G23" t="s">
         <v>202</v>
-      </c>
-      <c r="F23" t="s">
-        <v>285</v>
-      </c>
-      <c r="G23" t="s">
-        <v>203</v>
       </c>
       <c r="H23">
         <v>121</v>
@@ -15134,10 +15134,10 @@
         <v>13</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L23" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M23" t="str">
         <f t="shared" ref="M23" si="8">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A23 &amp; "','" &amp; D23 &amp; "','" &amp; E23 &amp; "','" &amp; G23 &amp; "','" &amp; H23 &amp; "','" &amp; I23 &amp;  "','" &amp; J23 &amp;  "','" &amp; K23 &amp;  "','" &amp; L23 &amp; "');"</f>
@@ -15149,37 +15149,37 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D24">
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F24" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G24" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="H24">
         <v>522</v>
       </c>
       <c r="I24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J24" t="s">
         <v>47</v>
       </c>
-      <c r="J24" t="s">
-        <v>48</v>
-      </c>
       <c r="K24" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M24" t="str">
         <f t="shared" si="0"/>
@@ -15191,19 +15191,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C25" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
       <c r="E25" t="s">
+        <v>48</v>
+      </c>
+      <c r="G25" t="s">
         <v>49</v>
-      </c>
-      <c r="G25" t="s">
-        <v>50</v>
       </c>
       <c r="H25">
         <v>522</v>
@@ -15212,13 +15212,13 @@
         <v>13</v>
       </c>
       <c r="J25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L25" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M25" t="str">
         <f t="shared" si="0"/>
@@ -15230,37 +15230,37 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D26">
         <v>2</v>
       </c>
       <c r="E26" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26" t="s">
+        <v>283</v>
+      </c>
+      <c r="G26" t="s">
         <v>52</v>
       </c>
-      <c r="F26" t="s">
-        <v>285</v>
-      </c>
-      <c r="G26" t="s">
+      <c r="H26" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="J26" t="s">
         <v>53</v>
       </c>
-      <c r="H26" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="J26" t="s">
-        <v>54</v>
-      </c>
       <c r="K26" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M26" t="str">
         <f t="shared" si="0"/>
@@ -15272,37 +15272,37 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D27">
         <v>2</v>
       </c>
       <c r="E27" t="s">
+        <v>54</v>
+      </c>
+      <c r="F27" t="s">
+        <v>283</v>
+      </c>
+      <c r="G27" t="s">
         <v>55</v>
-      </c>
-      <c r="F27" t="s">
-        <v>285</v>
-      </c>
-      <c r="G27" t="s">
-        <v>56</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J27" s="6" t="s">
         <v>13</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L27" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M27" t="str">
         <f t="shared" si="0"/>
@@ -15314,22 +15314,22 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D28">
         <v>2</v>
       </c>
       <c r="E28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F28" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>13</v>
@@ -15338,13 +15338,13 @@
         <v>13</v>
       </c>
       <c r="J28" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="L28" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M28" t="str">
         <f t="shared" si="0"/>
@@ -15356,22 +15356,22 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D29">
         <v>2</v>
       </c>
       <c r="E29" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F29" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>13</v>
@@ -15380,13 +15380,13 @@
         <v>13</v>
       </c>
       <c r="J29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="L29" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M29" t="str">
         <f t="shared" ref="M29" si="9">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A29 &amp; "','" &amp; D29 &amp; "','" &amp; E29 &amp; "','" &amp; G29 &amp; "','" &amp; H29 &amp; "','" &amp; I29 &amp;  "','" &amp; J29 &amp;  "','" &amp; K29 &amp;  "','" &amp; L29 &amp; "');"</f>
@@ -15398,37 +15398,37 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D30">
         <v>4</v>
       </c>
       <c r="E30" t="s">
+        <v>67</v>
+      </c>
+      <c r="F30" t="s">
+        <v>283</v>
+      </c>
+      <c r="G30" t="s">
+        <v>151</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="J30" t="s">
         <v>68</v>
       </c>
-      <c r="F30" t="s">
-        <v>285</v>
-      </c>
-      <c r="G30" t="s">
-        <v>152</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="J30" t="s">
-        <v>69</v>
-      </c>
       <c r="K30" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="L30" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M30" t="str">
         <f t="shared" si="0"/>
@@ -15440,37 +15440,37 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D31">
         <v>4</v>
       </c>
       <c r="E31" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F31" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J31" s="6" t="s">
         <v>13</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="L31" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M31" t="str">
         <f t="shared" si="0"/>
@@ -15482,22 +15482,22 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C32" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D32">
         <v>4</v>
       </c>
       <c r="E32" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F32" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>13</v>
@@ -15506,13 +15506,13 @@
         <v>13</v>
       </c>
       <c r="J32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="L32" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M32" t="str">
         <f t="shared" ref="M32:M62" si="10">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A32 &amp; "','" &amp; D32 &amp; "','" &amp; E32 &amp; "','" &amp; G32 &amp; "','" &amp; H32 &amp; "','" &amp; I32 &amp;  "','" &amp; J32 &amp;  "','" &amp; K32 &amp;  "','" &amp; L32 &amp; "');"</f>
@@ -15524,22 +15524,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D33">
         <v>4</v>
       </c>
       <c r="E33" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F33" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>13</v>
@@ -15548,13 +15548,13 @@
         <v>13</v>
       </c>
       <c r="J33" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="L33" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M33" t="str">
         <f t="shared" ref="M33" si="11">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A33 &amp; "','" &amp; D33 &amp; "','" &amp; E33 &amp; "','" &amp; G33 &amp; "','" &amp; H33 &amp; "','" &amp; I33 &amp;  "','" &amp; J33 &amp;  "','" &amp; K33 &amp;  "','" &amp; L33 &amp; "');"</f>
@@ -15566,37 +15566,37 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D34">
         <v>5</v>
       </c>
       <c r="E34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F34" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G34" t="s">
         <v>9</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J34" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L34" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M34" t="str">
         <f t="shared" si="10"/>
@@ -15608,37 +15608,37 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D35">
         <v>5</v>
       </c>
       <c r="E35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F35" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G35" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H35">
         <v>176</v>
       </c>
       <c r="I35" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J35" s="6" t="s">
         <v>13</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L35" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M35" t="str">
         <f t="shared" si="10"/>
@@ -15650,22 +15650,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C36" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D36">
         <v>5</v>
       </c>
       <c r="E36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F36" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H36">
         <v>100</v>
@@ -15677,10 +15677,10 @@
         <v>19</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L36" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M36" t="str">
         <f t="shared" si="10"/>
@@ -15692,22 +15692,22 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C37" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D37">
         <v>5</v>
       </c>
       <c r="E37" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="F37" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H37">
         <v>104</v>
@@ -15719,10 +15719,10 @@
         <v>19</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="L37" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M37" t="str">
         <f t="shared" ref="M37" si="12">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A37 &amp; "','" &amp; D37 &amp; "','" &amp; E37 &amp; "','" &amp; G37 &amp; "','" &amp; H37 &amp; "','" &amp; I37 &amp;  "','" &amp; J37 &amp;  "','" &amp; K37 &amp;  "','" &amp; L37 &amp; "');"</f>
@@ -15734,37 +15734,37 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D38">
         <v>3</v>
       </c>
       <c r="E38" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F38" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G38" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="L38" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M38" t="str">
         <f t="shared" si="10"/>
@@ -15776,22 +15776,22 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D39">
         <v>3</v>
       </c>
       <c r="E39" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F39" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G39" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>13</v>
@@ -15803,10 +15803,10 @@
         <v>13</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="L39" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M39" t="str">
         <f t="shared" si="10"/>
@@ -15818,22 +15818,22 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D40">
         <v>3</v>
       </c>
       <c r="E40" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F40" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>13</v>
@@ -15842,13 +15842,13 @@
         <v>13</v>
       </c>
       <c r="J40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="L40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M40" t="str">
         <f t="shared" si="10"/>
@@ -15860,34 +15860,34 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D41">
         <v>7</v>
       </c>
       <c r="E41" t="s">
+        <v>80</v>
+      </c>
+      <c r="G41" t="s">
         <v>81</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="J41" t="s">
         <v>82</v>
       </c>
-      <c r="H41" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="I41" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="J41" t="s">
-        <v>83</v>
-      </c>
       <c r="K41" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L41" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M41" t="str">
         <f t="shared" si="10"/>
@@ -15899,10 +15899,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C42" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D42">
         <v>7</v>
@@ -15911,10 +15911,10 @@
         <v>17</v>
       </c>
       <c r="F42" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G42" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H42">
         <v>228</v>
@@ -15926,10 +15926,10 @@
         <v>13</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L42" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M42" t="str">
         <f t="shared" si="10"/>
@@ -15941,34 +15941,34 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C43" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D43">
         <v>8</v>
       </c>
       <c r="E43" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G43" t="s">
         <v>9</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J43" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K43" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M43" t="str">
         <f t="shared" si="10"/>
@@ -15980,16 +15980,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C44" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D44">
         <v>8</v>
       </c>
       <c r="E44" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G44" t="s">
         <v>15</v>
@@ -15998,16 +15998,16 @@
         <v>521</v>
       </c>
       <c r="I44" t="s">
+        <v>23</v>
+      </c>
+      <c r="J44" t="s">
         <v>24</v>
       </c>
-      <c r="J44" t="s">
+      <c r="K44" t="s">
         <v>25</v>
       </c>
-      <c r="K44" t="s">
-        <v>26</v>
-      </c>
       <c r="L44" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M44" t="str">
         <f t="shared" si="10"/>
@@ -16019,34 +16019,34 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C45" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D45">
         <v>8</v>
       </c>
       <c r="E45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G45" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H45">
         <v>514</v>
       </c>
       <c r="I45" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J45" t="s">
+        <v>32</v>
+      </c>
+      <c r="K45" t="s">
         <v>33</v>
       </c>
-      <c r="K45" t="s">
-        <v>34</v>
-      </c>
       <c r="L45" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M45" t="str">
         <f t="shared" si="10"/>
@@ -16058,34 +16058,34 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C46" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D46">
         <v>8</v>
       </c>
       <c r="E46" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G46" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H46">
         <v>286</v>
       </c>
       <c r="I46" t="s">
+        <v>100</v>
+      </c>
+      <c r="J46" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="K46" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="J46" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="K46" s="4" t="s">
-        <v>102</v>
-      </c>
       <c r="L46" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M46" t="str">
         <f t="shared" si="10"/>
@@ -16097,34 +16097,34 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C47" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D47">
         <v>8</v>
       </c>
       <c r="E47" t="s">
+        <v>89</v>
+      </c>
+      <c r="G47" t="s">
         <v>90</v>
-      </c>
-      <c r="G47" t="s">
-        <v>91</v>
       </c>
       <c r="H47">
         <v>512</v>
       </c>
       <c r="I47" t="s">
+        <v>91</v>
+      </c>
+      <c r="J47" t="s">
         <v>92</v>
       </c>
-      <c r="J47" t="s">
+      <c r="K47" t="s">
         <v>93</v>
       </c>
-      <c r="K47" t="s">
-        <v>94</v>
-      </c>
       <c r="L47" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M47" t="str">
         <f t="shared" si="10"/>
@@ -16136,34 +16136,34 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C48" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D48">
         <v>8</v>
       </c>
       <c r="E48" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G48" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H48">
         <v>284</v>
       </c>
       <c r="I48" t="s">
+        <v>96</v>
+      </c>
+      <c r="J48" t="s">
         <v>97</v>
       </c>
-      <c r="J48" t="s">
+      <c r="K48" t="s">
         <v>98</v>
       </c>
-      <c r="K48" t="s">
-        <v>99</v>
-      </c>
       <c r="L48" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M48" t="str">
         <f t="shared" si="10"/>
@@ -16175,34 +16175,34 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C49" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D49">
         <v>8</v>
       </c>
       <c r="E49" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G49" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H49" s="6">
         <v>517</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J49" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L49" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M49" t="str">
         <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A49 &amp; "','" &amp; D49 &amp; "','" &amp; E49 &amp; "','" &amp; G49 &amp; "','" &amp; H49 &amp; "','" &amp; I49 &amp;  "','" &amp; J49 &amp;  "','" &amp; K49 &amp;  "','" &amp; L49 &amp; "');"</f>
@@ -16214,34 +16214,34 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C50" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D50">
         <v>8</v>
       </c>
       <c r="E50" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G50" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H50" s="6">
         <v>520</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="J50" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="L50" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M50" t="str">
         <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A50 &amp; "','" &amp; D50 &amp; "','" &amp; E50 &amp; "','" &amp; G50 &amp; "','" &amp; H50 &amp; "','" &amp; I50 &amp;  "','" &amp; J50 &amp;  "','" &amp; K50 &amp;  "','" &amp; L50 &amp; "');"</f>
@@ -16253,34 +16253,34 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D51">
         <v>8</v>
       </c>
       <c r="E51" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H51">
         <v>168</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="J51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="L51" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M51" t="str">
         <f t="shared" ref="M51" si="13">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A51 &amp; "','" &amp; D51 &amp; "','" &amp; E51 &amp; "','" &amp; G51 &amp; "','" &amp; H51 &amp; "','" &amp; I51 &amp;  "','" &amp; J51 &amp;  "','" &amp; K51 &amp;  "','" &amp; L51 &amp; "');"</f>
@@ -16292,19 +16292,19 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C52" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D52">
         <v>8</v>
       </c>
       <c r="E52" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="G52" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H52">
         <v>516</v>
@@ -16313,13 +16313,13 @@
         <v>13</v>
       </c>
       <c r="J52" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="L52" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M52" t="str">
         <f t="shared" ref="M52" si="14">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A52 &amp; "','" &amp; D52 &amp; "','" &amp; E52 &amp; "','" &amp; G52 &amp; "','" &amp; H52 &amp; "','" &amp; I52 &amp;  "','" &amp; J52 &amp;  "','" &amp; K52 &amp;  "','" &amp; L52 &amp; "');"</f>
@@ -16331,19 +16331,19 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C53" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D53">
         <v>8</v>
       </c>
       <c r="E53" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G53" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H53">
         <v>210</v>
@@ -16355,10 +16355,10 @@
         <v>13</v>
       </c>
       <c r="K53" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L53" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M53" t="str">
         <f t="shared" si="10"/>
@@ -16370,19 +16370,19 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C54" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D54">
         <v>8</v>
       </c>
       <c r="E54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G54" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H54">
         <v>518</v>
@@ -16391,13 +16391,13 @@
         <v>13</v>
       </c>
       <c r="J54" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L54" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M54" t="str">
         <f t="shared" ref="M54" si="15">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A54 &amp; "','" &amp; D54 &amp; "','" &amp; E54 &amp; "','" &amp; G54 &amp; "','" &amp; H54 &amp; "','" &amp; I54 &amp;  "','" &amp; J54 &amp;  "','" &amp; K54 &amp;  "','" &amp; L54 &amp; "');"</f>
@@ -16409,19 +16409,19 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C55" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D55">
         <v>8</v>
       </c>
       <c r="E55" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G55" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H55">
         <v>281</v>
@@ -16433,10 +16433,10 @@
         <v>13</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="L55" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M55" t="str">
         <f t="shared" ref="M55" si="16">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A55 &amp; "','" &amp; D55 &amp; "','" &amp; E55 &amp; "','" &amp; G55 &amp; "','" &amp; H55 &amp; "','" &amp; I55 &amp;  "','" &amp; J55 &amp;  "','" &amp; K55 &amp;  "','" &amp; L55 &amp; "');"</f>
@@ -16448,19 +16448,19 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C56" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D56">
         <v>8</v>
       </c>
       <c r="E56" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G56" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H56">
         <v>523</v>
@@ -16469,13 +16469,13 @@
         <v>13</v>
       </c>
       <c r="J56" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K56" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L56" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M56" t="str">
         <f t="shared" si="10"/>
@@ -16487,19 +16487,19 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C57" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D57">
         <v>8</v>
       </c>
       <c r="E57" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G57" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H57">
         <v>223</v>
@@ -16511,10 +16511,10 @@
         <v>13</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L57" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M57" t="str">
         <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A57 &amp; "','" &amp; D57 &amp; "','" &amp; E57 &amp; "','" &amp; G57 &amp; "','" &amp; H57 &amp; "','" &amp; I57 &amp;  "','" &amp; J57 &amp;  "','" &amp; K57 &amp;  "','" &amp; L57 &amp; "');"</f>
@@ -16526,19 +16526,19 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C58" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D58">
         <v>8</v>
       </c>
       <c r="E58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G58" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H58">
         <v>172</v>
@@ -16550,10 +16550,10 @@
         <v>13</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L58" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M58" t="str">
         <f t="shared" ref="M58" si="17">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A58 &amp; "','" &amp; D58 &amp; "','" &amp; E58 &amp; "','" &amp; G58 &amp; "','" &amp; H58 &amp; "','" &amp; I58 &amp;  "','" &amp; J58 &amp;  "','" &amp; K58 &amp;  "','" &amp; L58 &amp; "');"</f>
@@ -16565,19 +16565,19 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C59" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D59">
         <v>8</v>
       </c>
       <c r="E59" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G59" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H59">
         <v>182</v>
@@ -16589,10 +16589,10 @@
         <v>13</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="L59" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M59" t="str">
         <f t="shared" ref="M59" si="18">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A59 &amp; "','" &amp; D59 &amp; "','" &amp; E59 &amp; "','" &amp; G59 &amp; "','" &amp; H59 &amp; "','" &amp; I59 &amp;  "','" &amp; J59 &amp;  "','" &amp; K59 &amp;  "','" &amp; L59 &amp; "');"</f>
@@ -16604,19 +16604,19 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C60" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D60">
         <v>8</v>
       </c>
       <c r="E60" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="G60" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H60" s="6" t="s">
         <v>13</v>
@@ -16625,13 +16625,13 @@
         <v>13</v>
       </c>
       <c r="J60" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="L60" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M60" t="str">
         <f t="shared" si="10"/>
@@ -16643,19 +16643,19 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C61" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D61">
         <v>8</v>
       </c>
       <c r="E61" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G61" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H61">
         <v>229</v>
@@ -16667,10 +16667,10 @@
         <v>13</v>
       </c>
       <c r="K61" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L61" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M61" t="str">
         <f t="shared" si="10"/>
@@ -16682,34 +16682,34 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C62" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D62">
         <v>9</v>
       </c>
       <c r="E62" t="s">
+        <v>113</v>
+      </c>
+      <c r="G62" t="s">
         <v>114</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="J62" t="s">
         <v>115</v>
       </c>
-      <c r="H62" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="I62" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="J62" t="s">
-        <v>116</v>
-      </c>
       <c r="K62" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L62" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M62" t="str">
         <f t="shared" si="10"/>
@@ -16721,34 +16721,34 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C63" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D63">
         <v>9</v>
       </c>
       <c r="E63" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G63" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I63" t="s">
+        <v>117</v>
+      </c>
+      <c r="J63" t="s">
         <v>118</v>
       </c>
-      <c r="J63" t="s">
+      <c r="K63" t="s">
         <v>119</v>
       </c>
-      <c r="K63" t="s">
-        <v>120</v>
-      </c>
       <c r="L63" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M63" t="str">
         <f t="shared" ref="M63:M85" si="19">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A63 &amp; "','" &amp; D63 &amp; "','" &amp; E63 &amp; "','" &amp; G63 &amp; "','" &amp; H63 &amp; "','" &amp; I63 &amp;  "','" &amp; J63 &amp;  "','" &amp; K63 &amp;  "','" &amp; L63 &amp; "');"</f>
@@ -16760,19 +16760,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C64" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D64">
         <v>9</v>
       </c>
       <c r="E64" t="s">
+        <v>120</v>
+      </c>
+      <c r="G64" t="s">
         <v>121</v>
-      </c>
-      <c r="G64" t="s">
-        <v>122</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>13</v>
@@ -16781,13 +16781,13 @@
         <v>13</v>
       </c>
       <c r="J64" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K64" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L64" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M64" t="str">
         <f t="shared" si="19"/>
@@ -16799,19 +16799,19 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C65" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D65">
         <v>9</v>
       </c>
       <c r="E65" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G65" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H65" s="6" t="s">
         <v>13</v>
@@ -16820,7 +16820,7 @@
         <v>13</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="K65" s="6" t="s">
         <v>13</v>
@@ -16835,34 +16835,34 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C66" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D66">
         <v>11</v>
       </c>
       <c r="E66" t="s">
+        <v>138</v>
+      </c>
+      <c r="G66" t="s">
         <v>139</v>
       </c>
-      <c r="G66" t="s">
+      <c r="H66" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="J66" t="s">
         <v>140</v>
       </c>
-      <c r="H66" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="I66" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="J66" t="s">
-        <v>141</v>
-      </c>
       <c r="K66" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L66" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M66" t="str">
         <f t="shared" si="19"/>
@@ -16874,34 +16874,34 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C67" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D67">
         <v>11</v>
       </c>
       <c r="E67" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G67" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H67" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I67" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J67" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L67" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M67" t="str">
         <f t="shared" si="19"/>
@@ -16913,19 +16913,19 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C68" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D68">
         <v>11</v>
       </c>
       <c r="E68" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G68" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>13</v>
@@ -16934,7 +16934,7 @@
         <v>13</v>
       </c>
       <c r="J68" s="13" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>13</v>
@@ -16949,34 +16949,34 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C69" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D69">
         <v>12</v>
       </c>
       <c r="E69" t="s">
+        <v>264</v>
+      </c>
+      <c r="G69" t="s">
         <v>266</v>
       </c>
-      <c r="G69" t="s">
-        <v>268</v>
-      </c>
       <c r="H69" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J69" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L69" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M69" t="str">
         <f t="shared" ref="M69:M70" si="20">"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A69 &amp; "','" &amp; D69 &amp; "','" &amp; E69 &amp; "','" &amp; G69 &amp; "','" &amp; H69 &amp; "','" &amp; I69 &amp;  "','" &amp; J69 &amp;  "','" &amp; K69 &amp;  "','" &amp; L69 &amp; "');"</f>
@@ -16988,34 +16988,34 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C70" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D70">
         <v>12</v>
       </c>
       <c r="E70" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G70" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I70" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="J70" t="s">
+        <v>268</v>
+      </c>
+      <c r="K70" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="K70" s="4" t="s">
-        <v>272</v>
-      </c>
       <c r="L70" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M70" t="str">
         <f t="shared" si="20"/>
@@ -17027,19 +17027,19 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C71" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D71">
         <v>12</v>
       </c>
       <c r="E71" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G71" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>13</v>
@@ -17048,7 +17048,7 @@
         <v>13</v>
       </c>
       <c r="J71" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>13</v>
@@ -17063,34 +17063,34 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
+        <v>212</v>
+      </c>
+      <c r="C72" t="s">
         <v>213</v>
-      </c>
-      <c r="C72" t="s">
-        <v>214</v>
       </c>
       <c r="D72">
         <v>13</v>
       </c>
       <c r="E72" t="s">
+        <v>215</v>
+      </c>
+      <c r="G72" t="s">
         <v>216</v>
       </c>
-      <c r="G72" t="s">
-        <v>217</v>
-      </c>
       <c r="H72" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K72" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L72" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M72" t="str">
         <f t="shared" si="19"/>
@@ -17102,34 +17102,34 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
+        <v>212</v>
+      </c>
+      <c r="C73" t="s">
         <v>213</v>
-      </c>
-      <c r="C73" t="s">
-        <v>214</v>
       </c>
       <c r="D73">
         <v>13</v>
       </c>
       <c r="E73" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G73" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J73" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L73" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M73" t="str">
         <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A73 &amp; "','" &amp; D73 &amp; "','" &amp; E73 &amp; "','" &amp; G73 &amp; "','" &amp; H73 &amp; "','" &amp; I73 &amp;  "','" &amp; J73 &amp;  "','" &amp; K73 &amp;  "','" &amp; L73 &amp; "');"</f>
@@ -17141,34 +17141,34 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
+        <v>212</v>
+      </c>
+      <c r="C74" t="s">
         <v>213</v>
-      </c>
-      <c r="C74" t="s">
-        <v>214</v>
       </c>
       <c r="D74">
         <v>13</v>
       </c>
       <c r="E74" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G74" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>13</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J74" s="6" t="s">
         <v>13</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L74" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M74" t="str">
         <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A74 &amp; "','" &amp; D74 &amp; "','" &amp; E74 &amp; "','" &amp; G74 &amp; "','" &amp; H74 &amp; "','" &amp; I74 &amp;  "','" &amp; J74 &amp;  "','" &amp; K74 &amp;  "','" &amp; L74 &amp; "');"</f>
@@ -17180,19 +17180,19 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
+        <v>212</v>
+      </c>
+      <c r="C75" t="s">
         <v>213</v>
-      </c>
-      <c r="C75" t="s">
-        <v>214</v>
       </c>
       <c r="D75">
         <v>13</v>
       </c>
       <c r="E75" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G75" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>13</v>
@@ -17201,13 +17201,13 @@
         <v>13</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>13</v>
       </c>
       <c r="L75" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M75" t="str">
         <f>"INSERT INTO `directory` (`order`, `office`, `displayname`, `title`, `ext`, `personalTel`, `directTel`, `email`, `contacttype`)  VALUES ('" &amp; A75 &amp; "','" &amp; D75 &amp; "','" &amp; E75 &amp; "','" &amp; G75 &amp; "','" &amp; H75 &amp; "','" &amp; I75 &amp;  "','" &amp; J75 &amp;  "','" &amp; K75 &amp;  "','" &amp; L75 &amp; "');"</f>
@@ -17219,34 +17219,34 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C76" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D76">
         <v>14</v>
       </c>
       <c r="E76" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G76" t="s">
         <v>9</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J76" t="s">
+        <v>126</v>
+      </c>
+      <c r="K76" t="s">
         <v>127</v>
       </c>
-      <c r="K76" t="s">
-        <v>128</v>
-      </c>
       <c r="L76" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M76" t="str">
         <f t="shared" si="19"/>
@@ -17258,34 +17258,34 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C77" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D77">
         <v>14</v>
       </c>
       <c r="E77" t="s">
+        <v>128</v>
+      </c>
+      <c r="G77" t="s">
         <v>129</v>
       </c>
-      <c r="G77" t="s">
+      <c r="H77" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="I77" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="J77" t="s">
         <v>130</v>
       </c>
-      <c r="H77" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="I77" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="J77" t="s">
+      <c r="K77" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="K77" s="4" t="s">
-        <v>132</v>
-      </c>
       <c r="L77" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M77" t="str">
         <f t="shared" si="19"/>
@@ -17297,34 +17297,34 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C78" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D78">
         <v>14</v>
       </c>
       <c r="E78" t="s">
+        <v>185</v>
+      </c>
+      <c r="G78" t="s">
         <v>186</v>
-      </c>
-      <c r="G78" t="s">
-        <v>187</v>
       </c>
       <c r="H78">
         <v>120</v>
       </c>
       <c r="I78" t="s">
+        <v>187</v>
+      </c>
+      <c r="J78" t="s">
+        <v>132</v>
+      </c>
+      <c r="K78" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="J78" t="s">
-        <v>133</v>
-      </c>
-      <c r="K78" s="4" t="s">
-        <v>189</v>
-      </c>
       <c r="L78" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M78" t="str">
         <f t="shared" si="19"/>
@@ -17336,34 +17336,34 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C79" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D79">
         <v>14</v>
       </c>
       <c r="E79" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G79" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H79">
         <v>187</v>
       </c>
       <c r="I79" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J79" s="6" t="s">
         <v>13</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L79" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M79" t="str">
         <f t="shared" si="19"/>
@@ -17375,19 +17375,19 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C80" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D80">
         <v>1</v>
       </c>
       <c r="E80" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G80" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H80">
         <v>541</v>
@@ -17399,10 +17399,10 @@
         <v>13</v>
       </c>
       <c r="K80" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L80" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M80" t="str">
         <f t="shared" si="19"/>
@@ -17414,19 +17414,19 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C81" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D81">
         <v>1</v>
       </c>
       <c r="E81" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G81" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H81">
         <v>250</v>
@@ -17438,10 +17438,10 @@
         <v>13</v>
       </c>
       <c r="K81" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L81" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M81" t="str">
         <f t="shared" si="19"/>
@@ -17453,19 +17453,19 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C82" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D82">
         <v>1</v>
       </c>
       <c r="E82" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G82" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H82">
         <v>226</v>
@@ -17477,10 +17477,10 @@
         <v>13</v>
       </c>
       <c r="K82" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L82" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M82" t="str">
         <f t="shared" si="19"/>
@@ -17492,19 +17492,19 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C83" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D83">
         <v>1</v>
       </c>
       <c r="E83" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G83" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H83">
         <v>288</v>
@@ -17516,10 +17516,10 @@
         <v>13</v>
       </c>
       <c r="K83" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L83" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M83" t="str">
         <f t="shared" si="19"/>
@@ -17531,19 +17531,19 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C84" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D84">
         <v>1</v>
       </c>
       <c r="E84" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G84" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H84">
         <v>208</v>
@@ -17555,10 +17555,10 @@
         <v>13</v>
       </c>
       <c r="K84" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L84" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M84" t="str">
         <f t="shared" si="19"/>
@@ -17570,19 +17570,19 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C85" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D85">
         <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G85" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H85">
         <v>524</v>
@@ -17594,10 +17594,10 @@
         <v>13</v>
       </c>
       <c r="K85" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L85" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M85" t="str">
         <f t="shared" si="19"/>
@@ -17687,62 +17687,62 @@
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -17751,6 +17751,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FCEEF5D6F9A2C14292C82E7F88E7D4C7" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="770a5493e01cc46570af888c0fd11107">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6e07a911-1c82-455b-ae09-b73935b22a66" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="de63ad8f9259e2f5a7ae7a5921e0e8ad" ns2:_="">
     <xsd:import namespace="6e07a911-1c82-455b-ae09-b73935b22a66"/>
@@ -17882,22 +17897,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDCD3F55-29C2-4E12-8D9A-9EC0083C9C49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="6e07a911-1c82-455b-ae09-b73935b22a66"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C569B7B-6177-4C5F-B641-1220485D9B3F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4188865-1BAB-459E-8F28-5F6AB5F6EAC9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -17913,28 +17937,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C569B7B-6177-4C5F-B641-1220485D9B3F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDCD3F55-29C2-4E12-8D9A-9EC0083C9C49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="6e07a911-1c82-455b-ae09-b73935b22a66"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/companydirectorypdf/companydir.xlsx
+++ b/companydirectorypdf/companydir.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nelso\Documents\GitHub\kwlivingrealtydrive\kwlrportal\companydirectorypdf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43432359-15C2-4174-9CD9-DBEB4D35369A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D3CD04-7899-4D54-8D86-E7025FA9A777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-16440" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{AE6EE1E0-C559-4053-97E8-B14EEDB6E6F6}"/>
+    <workbookView xWindow="-90" yWindow="-16440" windowWidth="29040" windowHeight="15720" xr2:uid="{AE6EE1E0-C559-4053-97E8-B14EEDB6E6F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Letter Size" sheetId="8" r:id="rId1"/>
@@ -997,9 +997,6 @@
     <t>Francesco Armogida</t>
   </si>
   <si>
-    <t>Update Date: May 4, 2026</t>
-  </si>
-  <si>
     <t>Alvir Tanghal</t>
   </si>
   <si>
@@ -1010,6 +1007,9 @@
   </si>
   <si>
     <t>Sunny Ren</t>
+  </si>
+  <si>
+    <t>Update Date: June 8, 2026</t>
   </si>
 </sst>
 </file>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="H1" s="11"/>
       <c r="I1" s="11" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
@@ -8643,7 +8643,7 @@
         <v>0</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
@@ -14780,7 +14780,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F15" t="s">
         <v>283</v>
@@ -14798,7 +14798,7 @@
         <v>13</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L15" t="s">
         <v>159</v>
@@ -14864,7 +14864,7 @@
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F17" t="s">
         <v>283</v>
@@ -14882,7 +14882,7 @@
         <v>13</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L17" t="s">
         <v>159</v>
